--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -1485,37 +1485,37 @@
         <v>-0.05</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.011663333423689352</v>
+        <v>-0.01075690836690019</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>50.2</v>
+        <v>51.84</v>
       </c>
       <c r="I2" s="1">
-        <v>17.1</v>
+        <v>17.85</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0010259900740410297</v>
+        <v>-0.000991144563370273</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.0942162725949025</v>
+        <v>-0.09738453650581391</v>
       </c>
       <c r="N2" s="1">
-        <v>41.139240506329116</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>87</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.23</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1535,37 +1535,37 @@
         <v>2.08</v>
       </c>
       <c r="F3" s="2">
-        <v>0.9272373462485994</v>
+        <v>0.9161821744944323</v>
       </c>
       <c r="G3" s="2">
         <v>2.43</v>
       </c>
       <c r="H3" s="2">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="I3" s="2">
-        <v>96.45</v>
+        <v>101.69</v>
       </c>
       <c r="J3" s="2">
-        <v>0.10114846606756325</v>
+        <v>0.10116530279189374</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="M3" s="2">
-        <v>1.0712016182179103</v>
+        <v>1.067252306492782</v>
       </c>
       <c r="N3" s="2">
-        <v>75.82278481012658</v>
+        <v>76.20253164556962</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>88</v>
       </c>
       <c r="P3" s="2">
-        <v>0.07</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1585,37 +1585,37 @@
         <v>2.62</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.26899625488421647</v>
+        <v>-0.2550591684684005</v>
       </c>
       <c r="G4" s="1">
         <v>1.1</v>
       </c>
       <c r="H4" s="1">
-        <v>51.42</v>
+        <v>52.07</v>
       </c>
       <c r="I4" s="1">
-        <v>-26.45</v>
+        <v>-26.14</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.01153365914721776</v>
+        <v>-0.011104402113241044</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>-64</v>
+        <v>-70</v>
       </c>
       <c r="M4" s="1">
-        <v>-0.25892882327797095</v>
+        <v>-0.244494823573411</v>
       </c>
       <c r="N4" s="1">
-        <v>31.392405063291136</v>
+        <v>31.0126582278481</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.48</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1635,37 +1635,37 @@
         <v>0.63</v>
       </c>
       <c r="F5" s="3">
-        <v>-0.12737004963007167</v>
+        <v>-0.13907356913892643</v>
       </c>
       <c r="G5" s="3">
         <v>1.81</v>
       </c>
       <c r="H5" s="3">
-        <v>69.1</v>
+        <v>69.02</v>
       </c>
       <c r="I5" s="3">
-        <v>8.98</v>
+        <v>8.95</v>
       </c>
       <c r="J5" s="3">
-        <v>0.009598896576779906</v>
+        <v>0.009539856733924958</v>
       </c>
       <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="M5" s="3">
-        <v>-0.045823853619483046</v>
+        <v>-0.053502375489511644</v>
       </c>
       <c r="N5" s="3">
-        <v>61.898734177215196</v>
+        <v>61.265822784810126</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P5" s="3">
-        <v>-0.29</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1685,37 +1685,37 @@
         <v>-0.4</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.0022454297573330506</v>
+        <v>-0.026325925062233996</v>
       </c>
       <c r="G6" s="1">
         <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>39.68</v>
+        <v>36.43</v>
       </c>
       <c r="I6" s="1">
-        <v>-14.2</v>
+        <v>-15.36</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.007945217752681385</v>
+        <v>-0.008207055983860102</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="M6" s="1">
-        <v>0.051111957755768156</v>
+        <v>0.02966510288121027</v>
       </c>
       <c r="N6" s="1">
-        <v>40</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="P6" s="1">
-        <v>-1.1</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1735,19 +1735,19 @@
         <v>0.14</v>
       </c>
       <c r="F7" s="3">
-        <v>0.004200633088251748</v>
+        <v>0.012598577802383992</v>
       </c>
       <c r="G7" s="3">
         <v>2.25</v>
       </c>
       <c r="H7" s="3">
-        <v>74.65</v>
+        <v>76.72</v>
       </c>
       <c r="I7" s="3">
-        <v>24.29</v>
+        <v>26.92</v>
       </c>
       <c r="J7" s="3">
-        <v>0.021875639047928542</v>
+        <v>0.0222649083786252</v>
       </c>
       <c r="K7" s="3" t="b">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>0.1300435281663206</v>
+        <v>0.14465288898975248</v>
       </c>
       <c r="N7" s="3">
         <v>64.68354430379746</v>
@@ -1785,28 +1785,28 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="3">
-        <v>0.32504503203206697</v>
+        <v>0.32294341698883905</v>
       </c>
       <c r="G8" s="3">
         <v>0.66</v>
       </c>
       <c r="H8" s="3">
-        <v>80.21</v>
+        <v>83.06</v>
       </c>
       <c r="I8" s="3">
-        <v>23.99</v>
+        <v>24.78</v>
       </c>
       <c r="J8" s="3">
-        <v>0.032764258681061455</v>
+        <v>0.03278600596447727</v>
       </c>
       <c r="K8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>-140</v>
+        <v>-151</v>
       </c>
       <c r="M8" s="3">
-        <v>0.29081576457083225</v>
+        <v>0.2870246443458748</v>
       </c>
       <c r="N8" s="3">
         <v>66.07594936708861</v>
@@ -1829,43 +1829,43 @@
         <v>37.9746835443038</v>
       </c>
       <c r="D9" s="1">
-        <v>46.10112359550562</v>
+        <v>46.2247191011236</v>
       </c>
       <c r="E9" s="1">
         <v>2.14</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.1473961715007092</v>
+        <v>-0.13253579561631276</v>
       </c>
       <c r="G9" s="1">
         <v>1.49</v>
       </c>
       <c r="H9" s="1">
-        <v>40.76</v>
+        <v>43.15</v>
       </c>
       <c r="I9" s="1">
-        <v>-19.37</v>
+        <v>-18.2</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.006469086728507143</v>
+        <v>-0.006074337239468922</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.0980657566301062</v>
+        <v>-0.0807705056308643</v>
       </c>
       <c r="N9" s="1">
-        <v>48.22784810126583</v>
+        <v>49.11392405063291</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.22</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1885,37 +1885,37 @@
         <v>1.07</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.12466793915874205</v>
+        <v>-0.1300139538077629</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>54.34</v>
+        <v>54.79</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.41</v>
+        <v>-3.22</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0013454749718363223</v>
+        <v>0.0013791610554501825</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-83</v>
+        <v>-88</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.08339146957313548</v>
+        <v>-0.08670013973830604</v>
       </c>
       <c r="N10" s="1">
-        <v>47.9746835443038</v>
+        <v>48.22784810126583</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.61</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1935,37 +1935,37 @@
         <v>8.3</v>
       </c>
       <c r="F11" s="3">
-        <v>0.10229427110136965</v>
+        <v>0.14409952072929216</v>
       </c>
       <c r="G11" s="3">
         <v>0.81</v>
       </c>
       <c r="H11" s="3">
-        <v>61.01</v>
+        <v>64.07</v>
       </c>
       <c r="I11" s="3">
-        <v>2.95</v>
+        <v>5.82</v>
       </c>
       <c r="J11" s="3">
-        <v>0.020343612414132753</v>
+        <v>0.02122061710133614</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M11" s="3">
-        <v>0.0831661510495032</v>
+        <v>0.12402726542881215</v>
       </c>
       <c r="N11" s="3">
-        <v>52.78481012658228</v>
+        <v>53.79746835443038</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="3">
-        <v>-1.74</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1985,37 +1985,37 @@
         <v>-0.32</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.3569945976289083</v>
+        <v>-0.33334786344112566</v>
       </c>
       <c r="G12" s="1">
         <v>0.82</v>
       </c>
       <c r="H12" s="1">
-        <v>44.46</v>
+        <v>47.26</v>
       </c>
       <c r="I12" s="1">
-        <v>-39.33</v>
+        <v>-37.79</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.011975099188964425</v>
+        <v>-0.011253071438596102</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.3751159745201502</v>
+        <v>-0.35236368425210673</v>
       </c>
       <c r="N12" s="1">
-        <v>38.607594936708864</v>
+        <v>40.00000000000001</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="P12" s="1">
-        <v>-3.58</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2035,37 +2035,37 @@
         <v>2.73</v>
       </c>
       <c r="F13" s="4">
-        <v>-0.17446739748956364</v>
+        <v>-0.16428932419856557</v>
       </c>
       <c r="G13" s="4">
         <v>1.43</v>
       </c>
       <c r="H13" s="4">
-        <v>54.62</v>
+        <v>54.94</v>
       </c>
       <c r="I13" s="4">
-        <v>6.29</v>
+        <v>6.55</v>
       </c>
       <c r="J13" s="4">
-        <v>-0.0027910483504584526</v>
+        <v>-0.002415330820078252</v>
       </c>
       <c r="K13" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="4">
         <v>21</v>
       </c>
       <c r="M13" s="4">
-        <v>-0.13117744158270794</v>
+        <v>-0.1188626411501108</v>
       </c>
       <c r="N13" s="4">
-        <v>28.60759493670886</v>
+        <v>28.734177215189874</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>98</v>
       </c>
       <c r="P13" s="4">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -2085,37 +2085,37 @@
         <v>0.33</v>
       </c>
       <c r="F14" s="3">
-        <v>-0.15006171822857164</v>
+        <v>-0.11959597331378823</v>
       </c>
       <c r="G14" s="3">
         <v>0.6</v>
       </c>
       <c r="H14" s="3">
-        <v>53.44</v>
+        <v>57.01</v>
       </c>
       <c r="I14" s="3">
-        <v>-7.38</v>
+        <v>-4.92</v>
       </c>
       <c r="J14" s="3">
-        <v>0.00922387263349842</v>
+        <v>0.00997061817242482</v>
       </c>
       <c r="K14" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M14" s="3">
-        <v>-0.19033144465355367</v>
+        <v>-0.16185335289374614</v>
       </c>
       <c r="N14" s="3">
-        <v>52.40506329113924</v>
+        <v>53.79746835443038</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>96</v>
       </c>
       <c r="P14" s="3">
-        <v>-0.88</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -2135,37 +2135,37 @@
         <v>5.78</v>
       </c>
       <c r="F15" s="3">
-        <v>1.3081368249841263</v>
+        <v>1.2489126243752493</v>
       </c>
       <c r="G15" s="3">
         <v>2.22</v>
       </c>
       <c r="H15" s="3">
-        <v>69.54</v>
+        <v>69.71</v>
       </c>
       <c r="I15" s="3">
-        <v>161.09</v>
+        <v>161.42</v>
       </c>
       <c r="J15" s="3">
-        <v>0.12827181009856364</v>
+        <v>0.12753161590932974</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="M15" s="3">
-        <v>1.4309594905803216</v>
+        <v>1.377797632094121</v>
       </c>
       <c r="N15" s="3">
-        <v>69.62025316455697</v>
+        <v>69.36708860759494</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>99</v>
       </c>
       <c r="P15" s="3">
-        <v>-1.06</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2185,37 +2185,37 @@
         <v>4.52</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.053949744493909685</v>
+        <v>-0.08919224264039691</v>
       </c>
       <c r="G16" s="1">
         <v>1.94</v>
       </c>
       <c r="H16" s="1">
-        <v>49.96</v>
+        <v>44.88</v>
       </c>
       <c r="I16" s="1">
-        <v>5.14</v>
+        <v>-0.84</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.001108913400526321</v>
+        <v>-0.0015444274654613306</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M16" s="1">
-        <v>0.040684112604798095</v>
+        <v>0.010112599372504194</v>
       </c>
       <c r="N16" s="1">
-        <v>41.51898734177215</v>
+        <v>40</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P16" s="1">
-        <v>-3.28</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -2235,87 +2235,87 @@
         <v>4.89</v>
       </c>
       <c r="F17" s="4">
-        <v>-0.13709314275384868</v>
+        <v>-0.16244837109199475</v>
       </c>
       <c r="G17" s="4">
         <v>1.73</v>
       </c>
       <c r="H17" s="4">
-        <v>47.52</v>
+        <v>44.61</v>
       </c>
       <c r="I17" s="4">
-        <v>-7.41</v>
+        <v>-9.88</v>
       </c>
       <c r="J17" s="4">
-        <v>-0.01337915315934868</v>
+        <v>-0.013692428469579026</v>
       </c>
       <c r="K17" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M17" s="4">
-        <v>-0.06360089202825647</v>
+        <v>-0.08532865335857154</v>
       </c>
       <c r="N17" s="4">
-        <v>25.69620253164557</v>
+        <v>24.55696202531646</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>94</v>
       </c>
       <c r="P17" s="4">
-        <v>-3.07</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>9.43</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.24729753382067543</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F18" s="1">
+        <v>-0.31475627532154227</v>
+      </c>
+      <c r="G18" s="1">
         <v>1.23</v>
       </c>
-      <c r="H18" s="3">
-        <v>40.23</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-2.64</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.007351262107261573</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="H18" s="1">
+        <v>34.16</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-10.15</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.00862658866383474</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
-        <v>45</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-0.22414244112631077</v>
-      </c>
-      <c r="N18" s="3">
-        <v>51.39240506329114</v>
-      </c>
-      <c r="O18" s="3" t="s">
+      <c r="L18" s="1">
+        <v>44</v>
+      </c>
+      <c r="M18" s="1">
+        <v>-0.29045828206306645</v>
+      </c>
+      <c r="N18" s="1">
+        <v>48.22784810126582</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="P18" s="3">
-        <v>-1.9</v>
+      <c r="P18" s="1">
+        <v>-5.06</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2329,43 +2329,43 @@
         <v>77.21518987341773</v>
       </c>
       <c r="D19" s="3">
-        <v>0.1641630901287553</v>
+        <v>0.20386266094420605</v>
       </c>
       <c r="E19" s="3">
         <v>-0.43</v>
       </c>
       <c r="F19" s="3">
-        <v>-0.01685323071374851</v>
+        <v>-0.05406046894859554</v>
       </c>
       <c r="G19" s="3">
         <v>0.21</v>
       </c>
       <c r="H19" s="3">
-        <v>61.52</v>
+        <v>52.19</v>
       </c>
       <c r="I19" s="3">
-        <v>19.23</v>
+        <v>14.33</v>
       </c>
       <c r="J19" s="3">
-        <v>0.005627047825972646</v>
+        <v>0.004860214961652308</v>
       </c>
       <c r="K19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M19" s="3">
-        <v>-0.09638594040308801</v>
+        <v>-0.13751879361901242</v>
       </c>
       <c r="N19" s="3">
-        <v>54.936708860759495</v>
+        <v>52.78481012658228</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P19" s="3">
-        <v>-2.46</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2385,87 +2385,87 @@
         <v>-2.3</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.2738043840084353</v>
+        <v>-0.27738371895999425</v>
       </c>
       <c r="G20" s="1">
         <v>1.03</v>
       </c>
       <c r="H20" s="1">
-        <v>30.94</v>
+        <v>33.58</v>
       </c>
       <c r="I20" s="1">
-        <v>-16.61</v>
+        <v>-15.74</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.012226518953897278</v>
+        <v>-0.012193955643101766</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.2707841545265617</v>
+        <v>-0.2742144154914974</v>
       </c>
       <c r="N20" s="1">
-        <v>37.974683544303794</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P20" s="1">
-        <v>-1.2</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="3">
         <v>1.02</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="3">
         <v>41.77215189873418</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="3">
         <v>13.990196078431373</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="3">
         <v>5.19</v>
       </c>
-      <c r="F21" s="1">
-        <v>-0.21593560101828907</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="F21" s="3">
+        <v>-0.06041092891357461</v>
+      </c>
+      <c r="G21" s="3">
         <v>1.3</v>
       </c>
-      <c r="H21" s="1">
-        <v>61.57</v>
-      </c>
-      <c r="I21" s="1">
-        <v>11.47</v>
-      </c>
-      <c r="J21" s="1">
-        <v>-0.012796212578615887</v>
-      </c>
-      <c r="K21" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>12</v>
-      </c>
-      <c r="M21" s="1">
-        <v>-0.18573330619955253</v>
-      </c>
-      <c r="N21" s="1">
-        <v>49.36708860759494</v>
-      </c>
-      <c r="O21" s="1" t="s">
+      <c r="H21" s="3">
+        <v>75.29</v>
+      </c>
+      <c r="I21" s="3">
+        <v>32.12</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-0.009010821698179192</v>
+      </c>
+      <c r="K21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-0.028717894228606156</v>
+      </c>
+      <c r="N21" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P21" s="1">
-        <v>-0.36</v>
+      <c r="P21" s="3">
+        <v>5.97</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2485,37 +2485,37 @@
         <v>0.16</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.20888675855375735</v>
+        <v>-0.2226599498002808</v>
       </c>
       <c r="G22" s="1">
         <v>1.36</v>
       </c>
       <c r="H22" s="1">
-        <v>50.44</v>
+        <v>47.63</v>
       </c>
       <c r="I22" s="1">
-        <v>-1.17</v>
+        <v>-2.68</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.014509412458854279</v>
+        <v>-0.014654852890405735</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.1726440047712735</v>
+        <v>-0.18462830817831866</v>
       </c>
       <c r="N22" s="1">
-        <v>41.89873417721519</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.84</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2535,87 +2535,87 @@
         <v>-0.52</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.18629048283899619</v>
+        <v>-0.1900389233125886</v>
       </c>
       <c r="G23" s="1">
         <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>46.61</v>
+        <v>47.08</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.4</v>
+        <v>-8.22</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.00754036703825663</v>
+        <v>-0.007490385149177563</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.16212864698400697</v>
+        <v>-0.16468449556461384</v>
       </c>
       <c r="N23" s="1">
-        <v>44.81012658227848</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.81</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="1">
         <v>-40.16</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="1">
         <v>1.2658227848101267</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="1">
         <v>-0.3107569721115539</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="1">
         <v>9.38</v>
       </c>
-      <c r="F24" s="4">
-        <v>0.06768818537686516</v>
-      </c>
-      <c r="G24" s="4">
+      <c r="F24" s="1">
+        <v>0.13218419798629943</v>
+      </c>
+      <c r="G24" s="1">
         <v>3.57</v>
       </c>
-      <c r="H24" s="4">
-        <v>55.31</v>
-      </c>
-      <c r="I24" s="4">
-        <v>-19.35</v>
-      </c>
-      <c r="J24" s="4">
-        <v>0.03323697165731191</v>
-      </c>
-      <c r="K24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4">
-        <v>31</v>
-      </c>
-      <c r="M24" s="4">
-        <v>0.32642117765737466</v>
-      </c>
-      <c r="N24" s="4">
-        <v>29.240506329113924</v>
-      </c>
-      <c r="O24" s="4" t="s">
+      <c r="H24" s="1">
+        <v>60.53</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-14.66</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.03461953962176362</v>
+      </c>
+      <c r="K24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>32</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.403687861787529</v>
+      </c>
+      <c r="N24" s="1">
+        <v>31.012658227848103</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P24" s="4">
-        <v>-0.9</v>
+      <c r="P24" s="1">
+        <v>0.88</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2635,37 +2635,37 @@
         <v>11.91</v>
       </c>
       <c r="F25" s="4">
-        <v>-0.40681196596295327</v>
+        <v>-0.3842905296912893</v>
       </c>
       <c r="G25" s="4">
         <v>2.23</v>
       </c>
       <c r="H25" s="4">
-        <v>47.6</v>
+        <v>49.84</v>
       </c>
       <c r="I25" s="4">
-        <v>-51.53</v>
+        <v>-49.87</v>
       </c>
       <c r="J25" s="4">
-        <v>-0.004997509901341605</v>
+        <v>-0.004190207254928142</v>
       </c>
       <c r="K25" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="M25" s="4">
-        <v>-0.2829825572061335</v>
+        <v>-0.25434908748291873</v>
       </c>
       <c r="N25" s="4">
-        <v>27.59493670886076</v>
+        <v>27.9746835443038</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>104</v>
       </c>
       <c r="P25" s="4">
-        <v>-0.62</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -2685,37 +2685,37 @@
         <v>4.67</v>
       </c>
       <c r="F26" s="1">
-        <v>0.45754441487363373</v>
+        <v>0.5020833663902557</v>
       </c>
       <c r="G26" s="1">
         <v>3.06</v>
       </c>
       <c r="H26" s="1">
-        <v>67.42</v>
+        <v>69.75</v>
       </c>
       <c r="I26" s="1">
-        <v>17.79</v>
+        <v>22.49</v>
       </c>
       <c r="J26" s="1">
-        <v>0.04382627103448567</v>
+        <v>0.044836941288624664</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="M26" s="1">
-        <v>0.6649335059622912</v>
+        <v>0.719708871227039</v>
       </c>
       <c r="N26" s="1">
-        <v>40.75949367088608</v>
+        <v>41.139240506329116</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P26" s="1">
-        <v>-0.88</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -2735,37 +2735,37 @@
         <v>1.65</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.2092279324806665</v>
+        <v>-0.21166917153997578</v>
       </c>
       <c r="G27" s="1">
         <v>2.63</v>
       </c>
       <c r="H27" s="1">
-        <v>60.59</v>
+        <v>59.81</v>
       </c>
       <c r="I27" s="1">
-        <v>-18.84</v>
+        <v>-19.37</v>
       </c>
       <c r="J27" s="1">
-        <v>0.00759937784017327</v>
+        <v>0.007828341610272474</v>
       </c>
       <c r="K27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="1">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M27" s="1">
-        <v>-0.045128797298864765</v>
+        <v>-0.039470349751647316</v>
       </c>
       <c r="N27" s="1">
-        <v>36.32911392405063</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P27" s="1">
-        <v>-2.85</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -2785,37 +2785,37 @@
         <v>-0.68</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.41429339682936467</v>
+        <v>-0.3942456323090784</v>
       </c>
       <c r="G28" s="1">
         <v>3.14</v>
       </c>
       <c r="H28" s="1">
-        <v>55.69</v>
+        <v>57.94</v>
       </c>
       <c r="I28" s="1">
-        <v>-22.6</v>
+        <v>-21.48</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.011435776749961523</v>
+        <v>-0.010625421345111468</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.1988503604557108</v>
+        <v>-0.16816865155630356</v>
       </c>
       <c r="N28" s="1">
-        <v>34.177215189873415</v>
+        <v>34.30379746835443</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P28" s="1">
-        <v>-0.89</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2835,37 +2835,37 @@
         <v>0.62</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.4322401153499922</v>
+        <v>-0.4036058072820504</v>
       </c>
       <c r="G29" s="1">
         <v>2.11</v>
       </c>
       <c r="H29" s="1">
-        <v>37.79</v>
+        <v>43.77</v>
       </c>
       <c r="I29" s="1">
-        <v>-34.63</v>
+        <v>-31.87</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.016189792270149172</v>
+        <v>-0.015321352173938154</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>-13</v>
+        <v>-26</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.32049162452066704</v>
+        <v>-0.2863415789476672</v>
       </c>
       <c r="N29" s="1">
-        <v>40.12658227848101</v>
+        <v>41.645569620253156</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.42</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2885,37 +2885,37 @@
         <v>2.13</v>
       </c>
       <c r="F30" s="3">
-        <v>-0.1602868733293653</v>
+        <v>-0.18094330743064543</v>
       </c>
       <c r="G30" s="3">
         <v>1.21</v>
       </c>
       <c r="H30" s="3">
-        <v>62.25</v>
+        <v>51.75</v>
       </c>
       <c r="I30" s="3">
-        <v>8.79</v>
+        <v>4.33</v>
       </c>
       <c r="J30" s="3">
-        <v>0.004389755742169037</v>
+        <v>0.004066824753637364</v>
       </c>
       <c r="K30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="3">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M30" s="3">
-        <v>-0.13914526695624974</v>
+        <v>-0.15875818315116752</v>
       </c>
       <c r="N30" s="3">
-        <v>66.9620253164557</v>
+        <v>64.17721518987342</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P30" s="3">
-        <v>-0.71</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2935,37 +2935,37 @@
         <v>0.9</v>
       </c>
       <c r="F31" s="3">
-        <v>0.13986249742490553</v>
+        <v>0.16616848627336422</v>
       </c>
       <c r="G31" s="3">
         <v>1.43</v>
       </c>
       <c r="H31" s="3">
-        <v>63.38</v>
+        <v>66.12</v>
       </c>
       <c r="I31" s="3">
-        <v>24.38</v>
+        <v>27.03</v>
       </c>
       <c r="J31" s="3">
-        <v>0.029818304700280657</v>
+        <v>0.030438719361390046</v>
       </c>
       <c r="K31" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="3">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="M31" s="3">
-        <v>0.18315245333176122</v>
+        <v>0.211595169321819</v>
       </c>
       <c r="N31" s="3">
-        <v>68.73417721518987</v>
+        <v>68.9873417721519</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>105</v>
       </c>
       <c r="P31" s="3">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2985,87 +2985,87 @@
         <v>1.69</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.15569280806639818</v>
+        <v>-0.14369306296906825</v>
       </c>
       <c r="G32" s="1">
         <v>1.61</v>
       </c>
       <c r="H32" s="1">
-        <v>40.79</v>
+        <v>42.1</v>
       </c>
       <c r="I32" s="1">
-        <v>-5.96</v>
+        <v>-5.28</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.006658912912493285</v>
+        <v>-0.006301043397299648</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.09428147526830055</v>
+        <v>-0.07925055910963241</v>
       </c>
       <c r="N32" s="1">
-        <v>35.69620253164557</v>
+        <v>35.31645569620254</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.33</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="3">
         <v>16.79</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="3">
         <v>88.60759493670885</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="3">
         <v>-0.05777248362120303</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="3">
         <v>0.37</v>
       </c>
-      <c r="F33" s="1">
-        <v>-0.11721255165771177</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="F33" s="3">
+        <v>-0.10701325362409692</v>
+      </c>
+      <c r="G33" s="3">
         <v>1.09</v>
       </c>
-      <c r="H33" s="1">
-        <v>45.82</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-13.09</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.002099884336645966</v>
-      </c>
-      <c r="K33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>84</v>
-      </c>
-      <c r="M33" s="1">
-        <v>-0.1081518632120908</v>
-      </c>
-      <c r="N33" s="1">
-        <v>49.24050632911392</v>
-      </c>
-      <c r="O33" s="1" t="s">
+      <c r="H33" s="3">
+        <v>50.31</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-11.68</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.0024153065585720847</v>
+      </c>
+      <c r="K33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>80</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-0.09750534321860638</v>
+      </c>
+      <c r="N33" s="3">
+        <v>50</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="P33" s="1">
-        <v>-1.17</v>
+      <c r="P33" s="3">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -3085,37 +3085,37 @@
         <v>0.58</v>
       </c>
       <c r="F34" s="3">
-        <v>0.15541009815263948</v>
+        <v>0.15410044307464957</v>
       </c>
       <c r="G34" s="3">
         <v>1.26</v>
       </c>
       <c r="H34" s="3">
-        <v>72.95</v>
+        <v>74.16</v>
       </c>
       <c r="I34" s="3">
-        <v>37.68</v>
+        <v>38.16</v>
       </c>
       <c r="J34" s="3">
-        <v>0.02774990278217218</v>
+        <v>0.02784497492099956</v>
       </c>
       <c r="K34" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="M34" s="3">
-        <v>0.1815854203288778</v>
+        <v>0.18156773980162222</v>
       </c>
       <c r="N34" s="3">
-        <v>61.0126582278481</v>
+        <v>61.139240506329116</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P34" s="3">
-        <v>-1.04</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -3135,37 +3135,37 @@
         <v>-0.96</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.3094310253254089</v>
+        <v>-0.3200971245283263</v>
       </c>
       <c r="G35" s="1">
         <v>1</v>
       </c>
       <c r="H35" s="1">
-        <v>27.24</v>
+        <v>26.64</v>
       </c>
       <c r="I35" s="1">
-        <v>-24.79</v>
+        <v>-25.24</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.024614804292338484</v>
+        <v>-0.02473204394272379</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.3094310253254089</v>
+        <v>-0.3200971245283263</v>
       </c>
       <c r="N35" s="1">
-        <v>33.037974683544306</v>
+        <v>32.911392405063296</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="P35" s="1">
-        <v>-0.25</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -3185,37 +3185,37 @@
         <v>-0.97</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.12393980996890615</v>
+        <v>-0.13218519768832587</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>38.47</v>
+        <v>38.09</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.42</v>
+        <v>-15.62</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.011940583495385425</v>
+        <v>-0.011989533227783128</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>-19</v>
+        <v>-29</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.11185889204141153</v>
+        <v>-0.11950798381433847</v>
       </c>
       <c r="N36" s="1">
-        <v>40.379746835443036</v>
+        <v>40.12658227848101</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P36" s="1">
-        <v>-2.22</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -3235,37 +3235,37 @@
         <v>0.52</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.00582186707102858</v>
+        <v>-0.004030313562553567</v>
       </c>
       <c r="G37" s="1">
         <v>1.38</v>
       </c>
       <c r="H37" s="1">
-        <v>37.59</v>
+        <v>37.4</v>
       </c>
       <c r="I37" s="1">
-        <v>-22.21</v>
+        <v>-22.29</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.001998424256916757</v>
+        <v>-0.0018543394895870096</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-134</v>
+        <v>-149</v>
       </c>
       <c r="M37" s="1">
-        <v>0.032434373032704356</v>
+        <v>0.03611419703840646</v>
       </c>
       <c r="N37" s="1">
-        <v>39.11392405063291</v>
+        <v>38.9873417721519</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -3285,37 +3285,37 @@
         <v>-0.1</v>
       </c>
       <c r="F38" s="3">
-        <v>0.24398913034826947</v>
+        <v>0.2822612375138287</v>
       </c>
       <c r="G38" s="3">
         <v>1.1</v>
       </c>
       <c r="H38" s="3">
-        <v>76.72</v>
+        <v>81.07</v>
       </c>
       <c r="I38" s="3">
-        <v>21.33</v>
+        <v>26.13</v>
       </c>
       <c r="J38" s="3">
-        <v>0.03802241423312534</v>
+        <v>0.03887399062219226</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="3">
-        <v>-13</v>
+        <v>-22</v>
       </c>
       <c r="M38" s="3">
-        <v>0.254056561954515</v>
+        <v>0.2928255824088182</v>
       </c>
       <c r="N38" s="3">
-        <v>64.17721518987342</v>
+        <v>64.43037974683544</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>105</v>
       </c>
       <c r="P38" s="3">
-        <v>-1.58</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3335,7 +3335,7 @@
         <v>-7.97</v>
       </c>
       <c r="F39" s="3">
-        <v>0.10061679069979107</v>
+        <v>0.09296357322711366</v>
       </c>
       <c r="G39" s="3">
         <v>1.3</v>
@@ -3344,22 +3344,22 @@
         <v>50.52</v>
       </c>
       <c r="I39" s="3">
-        <v>8.7</v>
+        <v>8.69</v>
       </c>
       <c r="J39" s="3">
-        <v>0.019955656611286822</v>
+        <v>0.01993512563304211</v>
       </c>
       <c r="K39" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="3">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="M39" s="3">
-        <v>0.1308190855185276</v>
+        <v>0.1246566079120821</v>
       </c>
       <c r="N39" s="3">
-        <v>57.46835443037975</v>
+        <v>57.46835443037974</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>92</v>
@@ -3379,43 +3379,43 @@
         <v>5.063291139240507</v>
       </c>
       <c r="D40" s="1">
-        <v>16.730392156862745</v>
+        <v>15.710784313725492</v>
       </c>
       <c r="E40" s="1">
         <v>12.27</v>
       </c>
       <c r="F40" s="1">
-        <v>0.15938562325851427</v>
+        <v>0.23365240377663457</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>45.1</v>
+        <v>47.21</v>
       </c>
       <c r="I40" s="1">
-        <v>-15.1</v>
+        <v>-12.73</v>
       </c>
       <c r="J40" s="1">
-        <v>0.02174357268491645</v>
+        <v>0.022977603412417152</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M40" s="1">
-        <v>0.058711307196059215</v>
+        <v>0.1280089548267398</v>
       </c>
       <c r="N40" s="1">
-        <v>43.164556962025316</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>107</v>
       </c>
       <c r="P40" s="1">
-        <v>-5.6</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3435,37 +3435,37 @@
         <v>-1.75</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.003881387633440661</v>
+        <v>-0.02375885219811577</v>
       </c>
       <c r="G41" s="1">
         <v>1.11</v>
       </c>
       <c r="H41" s="1">
-        <v>75.05</v>
+        <v>74.52</v>
       </c>
       <c r="I41" s="1">
-        <v>-6.73</v>
+        <v>-6.95</v>
       </c>
       <c r="J41" s="1">
-        <v>0.016987040579109956</v>
+        <v>0.01664603618337326</v>
       </c>
       <c r="K41" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="1">
-        <v>0.0071927871334294124</v>
+        <v>-0.012138072813627332</v>
       </c>
       <c r="N41" s="1">
-        <v>44.17721518987342</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>99</v>
       </c>
       <c r="P41" s="1">
-        <v>-1.71</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -3485,87 +3485,87 @@
         <v>-0.1</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.07081192049909094</v>
+        <v>-0.06845247200694075</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>35.29</v>
+        <v>38.68</v>
       </c>
       <c r="I42" s="1">
-        <v>-1.18</v>
+        <v>-0.48</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.006303617146504767</v>
+        <v>-0.006223033526343932</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.13524348277906217</v>
+        <v>-0.13606427933487342</v>
       </c>
       <c r="N42" s="1">
-        <v>42.53164556962025</v>
+        <v>43.41772151898734</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>103</v>
       </c>
       <c r="P42" s="1">
-        <v>0.34</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="3">
         <v>-0.02</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="3">
         <v>27.848101265822784</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="3">
         <v>1214</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="3">
         <v>5.23</v>
       </c>
-      <c r="F43" s="1">
-        <v>-0.12285834708763946</v>
-      </c>
-      <c r="G43" s="1">
+      <c r="F43" s="3">
+        <v>-0.09542337847727217</v>
+      </c>
+      <c r="G43" s="3">
         <v>1.27</v>
       </c>
-      <c r="H43" s="1">
-        <v>40.25</v>
-      </c>
-      <c r="I43" s="1">
-        <v>-19.67</v>
-      </c>
-      <c r="J43" s="1">
-        <v>-0.002011310298098543</v>
-      </c>
-      <c r="K43" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="1">
-        <v>6</v>
-      </c>
-      <c r="M43" s="1">
-        <v>-0.09567628175077658</v>
-      </c>
-      <c r="N43" s="1">
-        <v>49.620253164556964</v>
-      </c>
-      <c r="O43" s="1" t="s">
+      <c r="H43" s="3">
+        <v>42.64</v>
+      </c>
+      <c r="I43" s="3">
+        <v>-18.41</v>
+      </c>
+      <c r="J43" s="3">
+        <v>-0.0014235899909965254</v>
+      </c>
+      <c r="K43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>7</v>
+      </c>
+      <c r="M43" s="3">
+        <v>-0.06689964726080055</v>
+      </c>
+      <c r="N43" s="3">
+        <v>50.379746835443036</v>
+      </c>
+      <c r="O43" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="P43" s="1">
-        <v>-3.12</v>
+      <c r="P43" s="3">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -3585,37 +3585,37 @@
         <v>-1.51</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.4172130832138122</v>
+        <v>-0.4040123402536418</v>
       </c>
       <c r="G44" s="1">
         <v>2.59</v>
       </c>
       <c r="H44" s="1">
-        <v>31.06</v>
+        <v>33.61</v>
       </c>
       <c r="I44" s="1">
-        <v>-32.5</v>
+        <v>-30.98</v>
       </c>
       <c r="J44" s="1">
-        <v>-0.018809502841100965</v>
+        <v>-0.018336993673082717</v>
       </c>
       <c r="K44" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="1">
-        <v>-18</v>
+        <v>-31</v>
       </c>
       <c r="M44" s="1">
-        <v>-0.25714092067450867</v>
+        <v>-0.23603925642330914</v>
       </c>
       <c r="N44" s="1">
-        <v>38.48101265822785</v>
+        <v>38.73417721518987</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P44" s="1">
-        <v>-0.7</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3635,37 +3635,37 @@
         <v>0.94</v>
       </c>
       <c r="F45" s="3">
-        <v>0.19467027904472012</v>
+        <v>0.17378808482099742</v>
       </c>
       <c r="G45" s="3">
         <v>1.46</v>
       </c>
       <c r="H45" s="3">
-        <v>66.37</v>
+        <v>62.91</v>
       </c>
       <c r="I45" s="3">
-        <v>17.57</v>
+        <v>16.56</v>
       </c>
       <c r="J45" s="3">
-        <v>0.025719260561844245</v>
+        <v>0.025482681526180457</v>
       </c>
       <c r="K45" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="M45" s="3">
-        <v>0.24098046443344945</v>
+        <v>0.22238407133794902</v>
       </c>
       <c r="N45" s="3">
-        <v>62.911392405063296</v>
+        <v>61.51898734177216</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P45" s="3">
-        <v>-1.34</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3685,37 +3685,37 @@
         <v>-0.94</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.2531437715271533</v>
+        <v>-0.25477861737604435</v>
       </c>
       <c r="G46" s="3">
         <v>1.51</v>
       </c>
       <c r="H46" s="3">
-        <v>45.26</v>
+        <v>44.64</v>
       </c>
       <c r="I46" s="3">
-        <v>12.28</v>
+        <v>11.29</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.006346632302340967</v>
+        <v>-0.006220806887688156</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.20179987033530122</v>
+        <v>-0.20090045841159798</v>
       </c>
       <c r="N46" s="3">
-        <v>51.89873417721519</v>
+        <v>51.77215189873418</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>95</v>
       </c>
       <c r="P46" s="3">
-        <v>-2.48</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3735,37 +3735,37 @@
         <v>-4.11</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.40569357046220755</v>
+        <v>-0.41131670566831885</v>
       </c>
       <c r="G47" s="1">
         <v>1.47</v>
       </c>
       <c r="H47" s="1">
-        <v>30.79</v>
+        <v>29.36</v>
       </c>
       <c r="I47" s="1">
-        <v>-17.99</v>
+        <v>-18.79</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.02980639450971279</v>
+        <v>-0.029771108480814303</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.3583766419128537</v>
+        <v>-0.3616642846618683</v>
       </c>
       <c r="N47" s="1">
-        <v>39.24050632911393</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P47" s="1">
-        <v>0.61</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -3785,28 +3785,28 @@
         <v>-1.16</v>
       </c>
       <c r="F48" s="3">
-        <v>0.3423766929116371</v>
+        <v>0.3581561024532833</v>
       </c>
       <c r="G48" s="3">
         <v>2.1</v>
       </c>
       <c r="H48" s="3">
-        <v>71.05</v>
+        <v>72.08</v>
       </c>
       <c r="I48" s="3">
-        <v>84.13</v>
+        <v>86.27</v>
       </c>
       <c r="J48" s="3">
-        <v>0.03866879566576634</v>
+        <v>0.03910672973553605</v>
       </c>
       <c r="K48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="M48" s="3">
-        <v>0.4531184405803377</v>
+        <v>0.47436389629816755</v>
       </c>
       <c r="N48" s="3">
         <v>69.87341772151898</v>
@@ -3835,37 +3835,37 @@
         <v>2.02</v>
       </c>
       <c r="F49" s="2">
-        <v>0.6897631070859485</v>
+        <v>0.7701396873881722</v>
       </c>
       <c r="G49" s="2">
         <v>3.8</v>
       </c>
       <c r="H49" s="2">
-        <v>66.09</v>
+        <v>70.05</v>
       </c>
       <c r="I49" s="2">
-        <v>128.7</v>
+        <v>141.2</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06450682197606553</v>
+        <v>0.06599801135342893</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M49" s="2">
-        <v>0.9716511920608226</v>
+        <v>1.0659413444478776</v>
       </c>
       <c r="N49" s="2">
-        <v>73.67088607594935</v>
+        <v>74.55696202531647</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>103</v>
       </c>
       <c r="P49" s="2">
-        <v>-0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3885,37 +3885,37 @@
         <v>2.75</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.4660239458089786</v>
+        <v>-0.4456764354715913</v>
       </c>
       <c r="G50" s="1">
         <v>1.53</v>
       </c>
       <c r="H50" s="1">
-        <v>34.51</v>
+        <v>37.04</v>
       </c>
       <c r="I50" s="1">
-        <v>-26.52</v>
+        <v>-24.92</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.031155315595608774</v>
+        <v>-0.030562508889854904</v>
       </c>
       <c r="K50" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="1">
         <v>7</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.4126665582958774</v>
+        <v>-0.38968540752814707</v>
       </c>
       <c r="N50" s="1">
-        <v>37.848101265822784</v>
+        <v>38.607594936708864</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P50" s="1">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3929,43 +3929,43 @@
         <v>7.59493670886076</v>
       </c>
       <c r="D51" s="1">
-        <v>-6.930412371134021</v>
+        <v>-6.131443298969073</v>
       </c>
       <c r="E51" s="1">
         <v>17.05</v>
       </c>
       <c r="F51" s="1">
-        <v>0.005940090005167903</v>
+        <v>0.040237710631943646</v>
       </c>
       <c r="G51" s="1">
         <v>2.37</v>
       </c>
       <c r="H51" s="1">
-        <v>53.66</v>
+        <v>55.1</v>
       </c>
       <c r="I51" s="1">
-        <v>30.25</v>
+        <v>32.39</v>
       </c>
       <c r="J51" s="1">
-        <v>0.03048577002514034</v>
+        <v>0.03138057009107268</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M51" s="1">
-        <v>0.14386390301073138</v>
+        <v>0.18496923569329948</v>
       </c>
       <c r="N51" s="1">
-        <v>33.16455696202532</v>
+        <v>33.67088607594937</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>109</v>
       </c>
       <c r="P51" s="1">
-        <v>-3</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3985,37 +3985,37 @@
         <v>0.22</v>
       </c>
       <c r="F52" s="3">
-        <v>0.09601435816368467</v>
+        <v>0.08932039831916402</v>
       </c>
       <c r="G52" s="3">
         <v>1.83</v>
       </c>
       <c r="H52" s="3">
-        <v>65.47</v>
+        <v>65.8</v>
       </c>
       <c r="I52" s="3">
-        <v>63.17</v>
+        <v>63.69</v>
       </c>
       <c r="J52" s="3">
-        <v>0.02744412483936847</v>
+        <v>0.027490398754253076</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M52" s="3">
-        <v>0.1795740404955224</v>
+        <v>0.17700446094757671</v>
       </c>
       <c r="N52" s="3">
-        <v>66.9620253164557</v>
+        <v>66.83544303797468</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P52" s="3">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -4035,37 +4035,37 @@
         <v>6.97</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.16396260489390907</v>
+        <v>-0.17683265907237794</v>
       </c>
       <c r="G53" s="1">
         <v>2.59</v>
       </c>
       <c r="H53" s="1">
-        <v>62.25</v>
+        <v>67.9</v>
       </c>
       <c r="I53" s="1">
-        <v>-18.23</v>
+        <v>-15.18</v>
       </c>
       <c r="J53" s="1">
         <v>0.01939648830140087</v>
       </c>
       <c r="K53" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.003890442354605561</v>
+        <v>-0.008859575242045281</v>
       </c>
       <c r="N53" s="1">
-        <v>47.34177215189874</v>
+        <v>48.481012658227854</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>90</v>
       </c>
       <c r="P53" s="1">
-        <v>-3.34</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -4085,37 +4085,37 @@
         <v>-0.44</v>
       </c>
       <c r="F54" s="3">
-        <v>0.027126456303452784</v>
+        <v>0.018459313876989097</v>
       </c>
       <c r="G54" s="3">
         <v>1.46</v>
       </c>
       <c r="H54" s="3">
-        <v>72.09</v>
+        <v>70.31</v>
       </c>
       <c r="I54" s="3">
-        <v>14.38</v>
+        <v>13.43</v>
       </c>
       <c r="J54" s="3">
-        <v>0.03015119994607086</v>
+        <v>0.03012053713667029</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L54" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M54" s="3">
-        <v>0.07343664169218211</v>
+        <v>0.0670553003939407</v>
       </c>
       <c r="N54" s="3">
-        <v>67.34177215189874</v>
+        <v>66.70886075949367</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>89</v>
       </c>
       <c r="P54" s="3">
-        <v>1.31</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -4135,37 +4135,37 @@
         <v>-0.7</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.17630408156618316</v>
+        <v>-0.18835995215135273</v>
       </c>
       <c r="G55" s="1">
         <v>1.2</v>
       </c>
       <c r="H55" s="1">
-        <v>40.95</v>
+        <v>38.01</v>
       </c>
       <c r="I55" s="1">
-        <v>-2.6</v>
+        <v>-3.39</v>
       </c>
       <c r="J55" s="1">
-        <v>0.00017414571048586888</v>
+        <v>0.00004749291211385887</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>10</v>
+        <v>-9</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.15616921835369213</v>
+        <v>-0.16723126236137376</v>
       </c>
       <c r="N55" s="1">
-        <v>48.10126582278481</v>
+        <v>46.9620253164557</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>110</v>
       </c>
       <c r="P55" s="1">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -4185,37 +4185,37 @@
         <v>0.84</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.08979797714747437</v>
+        <v>-0.09444301673683857</v>
       </c>
       <c r="G56" s="1">
         <v>0.26</v>
       </c>
       <c r="H56" s="1">
-        <v>50.37</v>
+        <v>52.57</v>
       </c>
       <c r="I56" s="1">
-        <v>9.87</v>
+        <v>10.48</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.008736154527235907</v>
+        <v>-0.008805394590350426</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.16429697103369112</v>
+        <v>-0.1726191689597607</v>
       </c>
       <c r="N56" s="1">
-        <v>45.316455696202524</v>
+        <v>45.82278481012658</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="P56" s="1">
-        <v>-1.67</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -4235,37 +4235,37 @@
         <v>0.39</v>
       </c>
       <c r="F57" s="2">
-        <v>0.7348539926838897</v>
+        <v>0.6525192474183457</v>
       </c>
       <c r="G57" s="2">
         <v>2</v>
       </c>
       <c r="H57" s="2">
-        <v>80.51</v>
+        <v>75.62</v>
       </c>
       <c r="I57" s="2">
-        <v>162.94</v>
+        <v>155.2</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08578394237617361</v>
+        <v>0.08442887501652538</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L57" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="M57" s="2">
-        <v>0.8355283087463448</v>
+        <v>0.7581626963682404</v>
       </c>
       <c r="N57" s="2">
-        <v>81.89873417721519</v>
+        <v>81.26582278481013</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>112</v>
       </c>
       <c r="P57" s="2">
-        <v>-0.16</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4285,37 +4285,37 @@
         <v>-1.9</v>
       </c>
       <c r="F58" s="3">
-        <v>0.025184429272075204</v>
+        <v>0.031653877808134584</v>
       </c>
       <c r="G58" s="3">
         <v>1.62</v>
       </c>
       <c r="H58" s="3">
-        <v>65.6</v>
+        <v>66.47</v>
       </c>
       <c r="I58" s="3">
-        <v>49.21</v>
+        <v>50.17</v>
       </c>
       <c r="J58" s="3">
-        <v>0.02221447088229275</v>
+        <v>0.022503688978931072</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="M58" s="3">
-        <v>0.08760250523079738</v>
+        <v>0.09715281615706939</v>
       </c>
       <c r="N58" s="3">
-        <v>65.69620253164558</v>
+        <v>65.44303797468355</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>101</v>
       </c>
       <c r="P58" s="3">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4335,37 +4335,37 @@
         <v>-2.43</v>
       </c>
       <c r="F59" s="3">
-        <v>0.17143968554632882</v>
+        <v>0.19376945522803352</v>
       </c>
       <c r="G59" s="3">
         <v>1.24</v>
       </c>
       <c r="H59" s="3">
-        <v>57.14</v>
+        <v>58.84</v>
       </c>
       <c r="I59" s="3">
-        <v>47.69</v>
+        <v>49.42</v>
       </c>
       <c r="J59" s="3">
-        <v>0.02125807090335131</v>
+        <v>0.021752375824627218</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="M59" s="3">
-        <v>0.19560152140131803</v>
+        <v>0.21912388297600827</v>
       </c>
       <c r="N59" s="3">
-        <v>60.00000000000001</v>
+        <v>60.37974683544304</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P59" s="3">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
@@ -4385,37 +4385,37 @@
         <v>-0.23</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.15265457830567258</v>
+        <v>-0.16171986417457856</v>
       </c>
       <c r="G60" s="1">
         <v>0.38</v>
       </c>
       <c r="H60" s="1">
-        <v>39.78</v>
+        <v>37.43</v>
       </c>
       <c r="I60" s="1">
-        <v>-0.37</v>
+        <v>-1.13</v>
       </c>
       <c r="J60" s="1">
-        <v>-0.009990788223235347</v>
+        <v>-0.01014368855251062</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M60" s="1">
-        <v>-0.2150726542643947</v>
+        <v>-0.22721880252351334</v>
       </c>
       <c r="N60" s="1">
-        <v>37.34177215189874</v>
+        <v>36.45569620253164</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="P60" s="1">
-        <v>-0.74</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4435,37 +4435,37 @@
         <v>-0.38</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.1360793060720855</v>
+        <v>-0.15140793649880074</v>
       </c>
       <c r="G61" s="3">
         <v>0.96</v>
       </c>
       <c r="H61" s="3">
-        <v>50.47</v>
+        <v>47.17</v>
       </c>
       <c r="I61" s="3">
-        <v>12.21</v>
+        <v>10.62</v>
       </c>
       <c r="J61" s="3">
-        <v>-0.006797306560263072</v>
+        <v>-0.007013080663460716</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.1401062787145837</v>
+        <v>-0.15563367445679654</v>
       </c>
       <c r="N61" s="3">
-        <v>54.30379746835443</v>
+        <v>53.164556962025316</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>113</v>
       </c>
       <c r="P61" s="3">
-        <v>-0.49</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
@@ -4479,43 +4479,43 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D62" s="2">
-        <v>4.887382690302398</v>
+        <v>4.831074035453597</v>
       </c>
       <c r="E62" s="2">
         <v>-8.63</v>
       </c>
       <c r="F62" s="2">
-        <v>0.7618451208279546</v>
+        <v>0.6801710267948219</v>
       </c>
       <c r="G62" s="2">
         <v>4.76</v>
       </c>
       <c r="H62" s="2">
-        <v>66.54</v>
+        <v>64.4</v>
       </c>
       <c r="I62" s="2">
-        <v>239.46</v>
+        <v>233.09</v>
       </c>
       <c r="J62" s="2">
-        <v>0.1063624984582406</v>
+        <v>0.10546988394515601</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="2">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="M62" s="2">
-        <v>1.1403805492227856</v>
+        <v>1.0773903948464263</v>
       </c>
       <c r="N62" s="2">
-        <v>82.65822784810126</v>
+        <v>81.89873417721519</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="P62" s="2">
-        <v>-0.77</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -4535,37 +4535,37 @@
         <v>-4.36</v>
       </c>
       <c r="F63" s="2">
-        <v>0.703405145655376</v>
+        <v>0.641250149266834</v>
       </c>
       <c r="G63" s="2">
         <v>2.03</v>
       </c>
       <c r="H63" s="2">
-        <v>79.5</v>
+        <v>75.55</v>
       </c>
       <c r="I63" s="2">
-        <v>146.55</v>
+        <v>140.43</v>
       </c>
       <c r="J63" s="2">
-        <v>0.08759379537836388</v>
+        <v>0.08667502892899964</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M63" s="2">
-        <v>0.8070996911997048</v>
+        <v>0.7500629016852256</v>
       </c>
       <c r="N63" s="2">
-        <v>78.60759493670886</v>
+        <v>78.10126582278481</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>103</v>
       </c>
       <c r="P63" s="2">
-        <v>-0.02</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -4585,37 +4585,37 @@
         <v>-0.69</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.07017286841064119</v>
+        <v>-0.0749174419428013</v>
       </c>
       <c r="G64" s="1">
         <v>0.31</v>
       </c>
       <c r="H64" s="1">
-        <v>56.87</v>
+        <v>58.94</v>
       </c>
       <c r="I64" s="1">
-        <v>2.98</v>
+        <v>3.59</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.008769295617096846</v>
+        <v>-0.008835651650888173</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.13963814649373518</v>
+        <v>-0.1478114217182287</v>
       </c>
       <c r="N64" s="1">
-        <v>47.59493670886076</v>
+        <v>48.10126582278482</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>94</v>
       </c>
       <c r="P64" s="1">
-        <v>-0.62</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -4635,87 +4635,87 @@
         <v>-0.19</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.17442380483317776</v>
+        <v>-0.16793335414486013</v>
       </c>
       <c r="G65" s="1">
         <v>1.02</v>
       </c>
       <c r="H65" s="1">
-        <v>39.67</v>
+        <v>42.78</v>
       </c>
       <c r="I65" s="1">
-        <v>-35.08</v>
+        <v>-33.81</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.008314376062091608</v>
+        <v>-0.008093631679428235</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-153</v>
+        <v>-159</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.17241031851192867</v>
+        <v>-0.16582048516586223</v>
       </c>
       <c r="N65" s="1">
-        <v>39.493670886075954</v>
+        <v>40.63291139240506</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>92</v>
       </c>
       <c r="P65" s="1">
-        <v>-3.66</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="3">
         <v>4.01</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="3">
         <v>55.69620253164557</v>
       </c>
-      <c r="D66" s="1">
-        <v>7.0074812967581055</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="D66" s="3">
+        <v>7.102244389027433</v>
+      </c>
+      <c r="E66" s="3">
         <v>-0.9</v>
       </c>
-      <c r="F66" s="1">
-        <v>-0.09402051539926856</v>
-      </c>
-      <c r="G66" s="1">
+      <c r="F66" s="3">
+        <v>-0.08351768096202683</v>
+      </c>
+      <c r="G66" s="3">
         <v>1.15</v>
       </c>
-      <c r="H66" s="1">
-        <v>45.57</v>
-      </c>
-      <c r="I66" s="1">
-        <v>-13.16</v>
-      </c>
-      <c r="J66" s="1">
-        <v>-0.0008039431181507437</v>
-      </c>
-      <c r="K66" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>-32</v>
-      </c>
-      <c r="M66" s="1">
-        <v>-0.07891936798990029</v>
-      </c>
-      <c r="N66" s="1">
-        <v>49.620253164556964</v>
-      </c>
-      <c r="O66" s="1" t="s">
+      <c r="H66" s="3">
+        <v>48.96</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-11.63</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-0.0004928700426987416</v>
+      </c>
+      <c r="K66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
+        <v>-45</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.06767116361954262</v>
+      </c>
+      <c r="N66" s="3">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="O66" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="P66" s="1">
-        <v>-1.75</v>
+      <c r="P66" s="3">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
@@ -4735,37 +4735,37 @@
         <v>0.3</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.15806245476612335</v>
+        <v>-0.17570917181145368</v>
       </c>
       <c r="G67" s="3">
         <v>0.33</v>
       </c>
       <c r="H67" s="3">
-        <v>45.63</v>
+        <v>44.24</v>
       </c>
       <c r="I67" s="3">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.010273104251175044</v>
+        <v>-0.010622393879639721</v>
       </c>
       <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="3">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.22551424652796825</v>
+        <v>-0.2464902826078832</v>
       </c>
       <c r="N67" s="3">
-        <v>61.13924050632912</v>
+        <v>60.253164556962034</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>104</v>
       </c>
       <c r="P67" s="3">
-        <v>-0.23</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -4785,37 +4785,37 @@
         <v>-0.07</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.2575474839966919</v>
+        <v>-0.2737584211342412</v>
       </c>
       <c r="G68" s="1">
         <v>1.49</v>
       </c>
       <c r="H68" s="1">
-        <v>37.17</v>
+        <v>36.06</v>
       </c>
       <c r="I68" s="1">
-        <v>-13.33</v>
+        <v>-13.93</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.01437527470060857</v>
+        <v>-0.014554167016053075</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.20821706912608895</v>
+        <v>-0.2219931311487927</v>
       </c>
       <c r="N68" s="1">
-        <v>37.088607594936704</v>
+        <v>36.835443037974684</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P68" s="1">
-        <v>-1.54</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -4835,37 +4835,37 @@
         <v>1.57</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.20493310164172324</v>
+        <v>-0.2235064032776204</v>
       </c>
       <c r="G69" s="1">
         <v>0.87</v>
       </c>
       <c r="H69" s="1">
-        <v>38.19</v>
+        <v>36.33</v>
       </c>
       <c r="I69" s="1">
-        <v>-14.35</v>
+        <v>-14.98</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.011881568497911374</v>
+        <v>-0.012176986886437771</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L69" s="1">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.2180207627298424</v>
+        <v>-0.23724005164110673</v>
       </c>
       <c r="N69" s="1">
-        <v>40</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>99</v>
       </c>
       <c r="P69" s="1">
-        <v>0.82</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -4885,37 +4885,37 @@
         <v>-0.78</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.43155902764152926</v>
+        <v>-0.44028916275093244</v>
       </c>
       <c r="G70" s="1">
         <v>1.11</v>
       </c>
       <c r="H70" s="1">
-        <v>33.18</v>
+        <v>30.64</v>
       </c>
       <c r="I70" s="1">
-        <v>-32.09</v>
+        <v>-32.84</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.03687278960549945</v>
+        <v>-0.036951733464152266</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>-65</v>
+        <v>-68</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.4204848528746592</v>
+        <v>-0.428668383366444</v>
       </c>
       <c r="N70" s="1">
-        <v>36.20253164556962</v>
+        <v>35.696202531645575</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>114</v>
       </c>
       <c r="P70" s="1">
-        <v>-0.51</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
@@ -4935,37 +4935,37 @@
         <v>0.16</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.2741915255105588</v>
+        <v>-0.28634058494607356</v>
       </c>
       <c r="G71" s="1">
         <v>1.01</v>
       </c>
       <c r="H71" s="1">
-        <v>51.14</v>
+        <v>47.79</v>
       </c>
       <c r="I71" s="1">
-        <v>-6.85</v>
+        <v>-7.91</v>
       </c>
       <c r="J71" s="1">
-        <v>-0.011941605836965647</v>
+        <v>-0.012108627386982845</v>
       </c>
       <c r="K71" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="1">
-        <v>-20</v>
+        <v>-31</v>
       </c>
       <c r="M71" s="1">
-        <v>-0.27318478234993426</v>
+        <v>-0.2852841504565746</v>
       </c>
       <c r="N71" s="1">
-        <v>40.88607594936708</v>
+        <v>39.873417721518976</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P71" s="1">
-        <v>0.34</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
@@ -4985,37 +4985,37 @@
         <v>-1.31</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.29757995170937973</v>
+        <v>-0.30139290482719244</v>
       </c>
       <c r="G72" s="1">
         <v>1.14</v>
       </c>
       <c r="H72" s="1">
-        <v>38.62</v>
+        <v>39.3</v>
       </c>
       <c r="I72" s="1">
-        <v>-9.5</v>
+        <v>-9.3</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.013411187507425424</v>
+        <v>-0.013369079063163274</v>
       </c>
       <c r="K72" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="1">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.28348554746063603</v>
+        <v>-0.28660282197420717</v>
       </c>
       <c r="N72" s="1">
-        <v>38.35443037974683</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>103</v>
       </c>
       <c r="P72" s="1">
-        <v>-0.28</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
@@ -5035,31 +5035,31 @@
         <v>0.1</v>
       </c>
       <c r="F73" s="3">
-        <v>0.2331317413635128</v>
+        <v>0.24304275004610662</v>
       </c>
       <c r="G73" s="3">
         <v>1.17</v>
       </c>
       <c r="H73" s="3">
-        <v>60.9</v>
+        <v>63.2</v>
       </c>
       <c r="I73" s="3">
-        <v>41.03</v>
+        <v>42.78</v>
       </c>
       <c r="J73" s="3">
-        <v>0.03284891822691881</v>
+        <v>0.03311741649197117</v>
       </c>
       <c r="K73" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M73" s="3">
-        <v>0.25024637509413017</v>
+        <v>0.26100213636758873</v>
       </c>
       <c r="N73" s="3">
-        <v>65.31645569620252</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>103</v>
@@ -5083,31 +5083,31 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="3">
-        <v>0.1753839976674314</v>
+        <v>0.171791660070794</v>
       </c>
       <c r="G74" s="3">
         <v>0.79</v>
       </c>
       <c r="H74" s="3">
-        <v>82.28</v>
+        <v>82.84</v>
       </c>
       <c r="I74" s="3">
-        <v>32.14</v>
+        <v>32.17</v>
       </c>
       <c r="J74" s="3">
-        <v>0.02173057394985362</v>
+        <v>0.02173636008250081</v>
       </c>
       <c r="K74" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M74" s="3">
-        <v>0.15424239129431583</v>
+        <v>0.1496065357913161</v>
       </c>
       <c r="N74" s="3">
-        <v>65.31645569620252</v>
+        <v>64.81012658227847</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>117</v>
@@ -5131,31 +5131,31 @@
         <v>-0.71</v>
       </c>
       <c r="F75" s="3">
-        <v>0.07668225279992916</v>
+        <v>0.09844585638263409</v>
       </c>
       <c r="G75" s="3">
         <v>0.96</v>
       </c>
       <c r="H75" s="3">
-        <v>60.77</v>
+        <v>62.95</v>
       </c>
       <c r="I75" s="3">
-        <v>14.98</v>
+        <v>16.76</v>
       </c>
       <c r="J75" s="3">
-        <v>0.00543724097635089</v>
+        <v>0.005947979306673231</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L75" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M75" s="3">
-        <v>0.07265528015743095</v>
+        <v>0.09422011842463829</v>
       </c>
       <c r="N75" s="3">
-        <v>57.84810126582279</v>
+        <v>58.734177215189874</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>103</v>
@@ -5179,31 +5179,31 @@
         <v>2.63</v>
       </c>
       <c r="F76" s="3">
-        <v>0.04419683723007975</v>
+        <v>0.02756734714612362</v>
       </c>
       <c r="G76" s="3">
         <v>0.72</v>
       </c>
       <c r="H76" s="3">
-        <v>61.09</v>
+        <v>57.58</v>
       </c>
       <c r="I76" s="3">
-        <v>20</v>
+        <v>18.15</v>
       </c>
       <c r="J76" s="3">
-        <v>0.018302004746848875</v>
+        <v>0.018042502596555904</v>
       </c>
       <c r="K76" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L76" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M76" s="3">
-        <v>0.016008028732592328</v>
+        <v>-0.0020128185598469184</v>
       </c>
       <c r="N76" s="3">
-        <v>51.13924050632912</v>
+        <v>50.12658227848102</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>88</v>
@@ -5227,31 +5227,31 @@
         <v>-0.34</v>
       </c>
       <c r="F77" s="3">
-        <v>0.030720013957918915</v>
+        <v>0.0154903655561002</v>
       </c>
       <c r="G77" s="3">
         <v>0.98</v>
       </c>
       <c r="H77" s="3">
-        <v>68.51</v>
+        <v>66.8</v>
       </c>
       <c r="I77" s="3">
-        <v>12.46</v>
+        <v>11.55</v>
       </c>
       <c r="J77" s="3">
-        <v>0.008501740925298302</v>
+        <v>0.008300076097574285</v>
       </c>
       <c r="K77" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L77" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M77" s="3">
-        <v>0.02870652763666981</v>
+        <v>0.013377496577102299</v>
       </c>
       <c r="N77" s="3">
-        <v>63.41772151898734</v>
+        <v>62.78481012658227</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>88</v>
@@ -5275,37 +5275,37 @@
         <v>0.57</v>
       </c>
       <c r="F78" s="3">
-        <v>0.14167758728460464</v>
+        <v>0.13994188449510106</v>
       </c>
       <c r="G78" s="3">
         <v>1.26</v>
       </c>
       <c r="H78" s="3">
-        <v>72.26</v>
+        <v>73.36</v>
       </c>
       <c r="I78" s="3">
-        <v>36.39</v>
+        <v>36.83</v>
       </c>
       <c r="J78" s="3">
-        <v>0.026881267332919918</v>
+        <v>0.026968687612936203</v>
       </c>
       <c r="K78" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="M78" s="3">
-        <v>0.16785290946084297</v>
+        <v>0.1674091812220737</v>
       </c>
       <c r="N78" s="3">
-        <v>60.63291139240506</v>
+        <v>60.50632911392405</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P78" s="3">
-        <v>-1.01</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
@@ -5319,43 +5319,43 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="3">
-        <v>2.3322475570032575</v>
+        <v>2.420195439739414</v>
       </c>
       <c r="E79" s="3">
         <v>0.82</v>
       </c>
       <c r="F79" s="3">
-        <v>0.45615623160228125</v>
+        <v>0.4314015762005562</v>
       </c>
       <c r="G79" s="3">
         <v>0.93</v>
       </c>
       <c r="H79" s="3">
-        <v>88.33</v>
+        <v>87.47</v>
       </c>
       <c r="I79" s="3">
-        <v>54.43</v>
+        <v>51.22</v>
       </c>
       <c r="J79" s="3">
-        <v>0.028166568050564732</v>
+        <v>0.02780205335194993</v>
       </c>
       <c r="K79" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L79" s="3">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="M79" s="3">
-        <v>0.4491090294779094</v>
+        <v>0.4240065347740636</v>
       </c>
       <c r="N79" s="3">
-        <v>64.81012658227849</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>109</v>
       </c>
       <c r="P79" s="3">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
@@ -5375,31 +5375,31 @@
         <v>5.52</v>
       </c>
       <c r="F80" s="3">
-        <v>1.0848743349184624</v>
+        <v>1.0797669226250077</v>
       </c>
       <c r="G80" s="3">
         <v>1.01</v>
       </c>
       <c r="H80" s="3">
-        <v>67.56</v>
+        <v>66.73</v>
       </c>
       <c r="I80" s="3">
-        <v>70.9</v>
+        <v>69.04</v>
       </c>
       <c r="J80" s="3">
-        <v>0.05870464401201956</v>
+        <v>0.058703521846975554</v>
       </c>
       <c r="K80" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L80" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M80" s="3">
-        <v>1.085881078079087</v>
+        <v>1.0808233571145067</v>
       </c>
       <c r="N80" s="3">
-        <v>69.36708860759495</v>
+        <v>68.8607594936709</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>96</v>
@@ -5430,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41.139240506329116</v>
+        <v>41.89873417721519</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5438,7 +5438,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>75.82278481012658</v>
+        <v>76.20253164556962</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5446,7 +5446,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>31.392405063291136</v>
+        <v>31.0126582278481</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5454,7 +5454,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>61.898734177215196</v>
+        <v>61.265822784810126</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5462,7 +5462,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>40</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5486,7 +5486,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>48.22784810126583</v>
+        <v>49.11392405063291</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5494,7 +5494,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47.9746835443038</v>
+        <v>48.22784810126583</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5502,7 +5502,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>52.78481012658228</v>
+        <v>53.79746835443038</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5510,7 +5510,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>38.607594936708864</v>
+        <v>40.00000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5518,7 +5518,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>28.60759493670886</v>
+        <v>28.734177215189874</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -5526,7 +5526,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>52.40506329113924</v>
+        <v>53.79746835443038</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -5534,7 +5534,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>69.62025316455697</v>
+        <v>69.36708860759494</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>41.51898734177215</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5550,7 +5550,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25.69620253164557</v>
+        <v>24.55696202531646</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5558,7 +5558,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>51.39240506329114</v>
+        <v>48.22784810126582</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5566,7 +5566,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>54.936708860759495</v>
+        <v>52.78481012658228</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5574,7 +5574,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37.974683544303794</v>
+        <v>37.59493670886076</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -5582,7 +5582,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49.36708860759494</v>
+        <v>55.69620253164557</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -5590,7 +5590,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>41.89873417721519</v>
+        <v>41.265822784810126</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -5598,7 +5598,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>44.81012658227848</v>
+        <v>45.063291139240505</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -5606,7 +5606,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>29.240506329113924</v>
+        <v>31.012658227848103</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5614,7 +5614,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>27.59493670886076</v>
+        <v>27.9746835443038</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -5622,7 +5622,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>40.75949367088608</v>
+        <v>41.139240506329116</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -5630,7 +5630,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>36.32911392405063</v>
+        <v>36.20253164556962</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -5638,7 +5638,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>34.177215189873415</v>
+        <v>34.30379746835443</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -5646,7 +5646,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40.12658227848101</v>
+        <v>41.645569620253156</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5654,7 +5654,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>66.9620253164557</v>
+        <v>64.17721518987342</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -5662,7 +5662,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>68.73417721518987</v>
+        <v>68.9873417721519</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -5670,7 +5670,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>35.69620253164557</v>
+        <v>35.31645569620254</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -5678,7 +5678,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>49.24050632911392</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -5686,7 +5686,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>61.0126582278481</v>
+        <v>61.139240506329116</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -5694,7 +5694,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>33.037974683544306</v>
+        <v>32.911392405063296</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5702,7 +5702,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>40.379746835443036</v>
+        <v>40.12658227848101</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -5710,7 +5710,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>39.11392405063291</v>
+        <v>38.9873417721519</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -5718,7 +5718,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>64.17721518987342</v>
+        <v>64.43037974683544</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -5726,7 +5726,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>57.46835443037975</v>
+        <v>57.46835443037974</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -5734,7 +5734,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>43.164556962025316</v>
+        <v>44.68354430379747</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -5742,7 +5742,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>44.17721518987342</v>
+        <v>43.79746835443038</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -5750,7 +5750,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>42.53164556962025</v>
+        <v>43.41772151898734</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5758,7 +5758,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>49.620253164556964</v>
+        <v>50.379746835443036</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5766,7 +5766,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>38.48101265822785</v>
+        <v>38.73417721518987</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -5774,7 +5774,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>62.911392405063296</v>
+        <v>61.51898734177216</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -5782,7 +5782,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>51.89873417721519</v>
+        <v>51.77215189873418</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5790,7 +5790,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>39.24050632911393</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5806,7 +5806,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>73.67088607594935</v>
+        <v>74.55696202531647</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>37.848101265822784</v>
+        <v>38.607594936708864</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -5822,7 +5822,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>33.16455696202532</v>
+        <v>33.67088607594937</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5830,7 +5830,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>66.9620253164557</v>
+        <v>66.83544303797468</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5838,7 +5838,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>47.34177215189874</v>
+        <v>48.481012658227854</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -5846,7 +5846,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>67.34177215189874</v>
+        <v>66.70886075949367</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -5854,7 +5854,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>48.10126582278481</v>
+        <v>46.9620253164557</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -5862,7 +5862,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>45.316455696202524</v>
+        <v>45.82278481012658</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5870,7 +5870,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>81.89873417721519</v>
+        <v>81.26582278481013</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5878,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>65.69620253164558</v>
+        <v>65.44303797468355</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5886,7 +5886,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>60.00000000000001</v>
+        <v>60.37974683544304</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -5894,7 +5894,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>37.34177215189874</v>
+        <v>36.45569620253164</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -5902,7 +5902,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>54.30379746835443</v>
+        <v>53.164556962025316</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -5910,7 +5910,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>82.65822784810126</v>
+        <v>81.89873417721519</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -5918,7 +5918,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>78.60759493670886</v>
+        <v>78.10126582278481</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -5926,7 +5926,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>47.59493670886076</v>
+        <v>48.10126582278482</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -5934,7 +5934,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>39.493670886075954</v>
+        <v>40.63291139240506</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5942,7 +5942,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>49.620253164556964</v>
+        <v>50.63291139240506</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -5950,7 +5950,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>61.13924050632912</v>
+        <v>60.253164556962034</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -5958,7 +5958,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>37.088607594936704</v>
+        <v>36.835443037974684</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>40</v>
+        <v>38.48101265822785</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -5974,7 +5974,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>36.20253164556962</v>
+        <v>35.696202531645575</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -5982,7 +5982,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>40.88607594936708</v>
+        <v>39.873417721518976</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -5990,7 +5990,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>38.35443037974683</v>
+        <v>39.24050632911392</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -5998,7 +5998,7 @@
         <v>115</v>
       </c>
       <c r="B73">
-        <v>65.31645569620252</v>
+        <v>65.82278481012659</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -6006,7 +6006,7 @@
         <v>116</v>
       </c>
       <c r="B74">
-        <v>65.31645569620252</v>
+        <v>64.81012658227847</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -6014,7 +6014,7 @@
         <v>118</v>
       </c>
       <c r="B75">
-        <v>57.84810126582279</v>
+        <v>58.734177215189874</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -6022,7 +6022,7 @@
         <v>119</v>
       </c>
       <c r="B76">
-        <v>51.13924050632912</v>
+        <v>50.12658227848102</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -6030,7 +6030,7 @@
         <v>120</v>
       </c>
       <c r="B77">
-        <v>63.41772151898734</v>
+        <v>62.78481012658227</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -6038,7 +6038,7 @@
         <v>121</v>
       </c>
       <c r="B78">
-        <v>60.63291139240506</v>
+        <v>60.50632911392405</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -6046,7 +6046,7 @@
         <v>122</v>
       </c>
       <c r="B79">
-        <v>64.81012658227849</v>
+        <v>64.55696202531645</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -6054,7 +6054,7 @@
         <v>123</v>
       </c>
       <c r="B80">
-        <v>69.36708860759495</v>
+        <v>68.8607594936709</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="204">
   <si>
     <t>Ticker</t>
   </si>
@@ -351,7 +351,7 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>2026-04-15</t>
+    <t>2027-04-15</t>
   </si>
   <si>
     <t>2027-04-14</t>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>_date_</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -1485,37 +1488,37 @@
         <v>-0.05</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.01075690836690019</v>
+        <v>0.03656337889124221</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="1">
-        <v>51.84</v>
+        <v>59.38</v>
       </c>
       <c r="I2" s="1">
-        <v>17.85</v>
+        <v>21.6</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.000991144563370273</v>
+        <v>0.0004454689878052024</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.09738453650581391</v>
+        <v>-0.04389366407237705</v>
       </c>
       <c r="N2" s="1">
-        <v>41.89873417721519</v>
+        <v>45.18987341772152</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>87</v>
       </c>
       <c r="P2" s="1">
-        <v>0.53</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1529,43 +1532,43 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>23.98032786885246</v>
+        <v>24.108196721311476</v>
       </c>
       <c r="E3" s="2">
         <v>2.08</v>
       </c>
       <c r="F3" s="2">
-        <v>0.9161821744944323</v>
+        <v>0.7993249441093764</v>
       </c>
       <c r="G3" s="2">
         <v>2.43</v>
       </c>
       <c r="H3" s="2">
-        <v>76.7</v>
+        <v>67.29</v>
       </c>
       <c r="I3" s="2">
-        <v>101.69</v>
+        <v>89.17</v>
       </c>
       <c r="J3" s="2">
-        <v>0.10116530279189374</v>
+        <v>0.09705513962480551</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="M3" s="2">
-        <v>1.067252306492782</v>
+        <v>0.9379437048780217</v>
       </c>
       <c r="N3" s="2">
-        <v>76.20253164556962</v>
+        <v>75.69620253164557</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>88</v>
       </c>
       <c r="P3" s="2">
-        <v>0.45</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1585,37 +1588,37 @@
         <v>2.62</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.2550591684684005</v>
+        <v>-0.2535364508958835</v>
       </c>
       <c r="G4" s="1">
         <v>1.1</v>
       </c>
       <c r="H4" s="1">
-        <v>52.07</v>
+        <v>58.05</v>
       </c>
       <c r="I4" s="1">
-        <v>-26.14</v>
+        <v>-22.73</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.011104402113241044</v>
+        <v>-0.011052941902859758</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>-70</v>
+        <v>-72</v>
       </c>
       <c r="M4" s="1">
-        <v>-0.244494823573411</v>
+        <v>-0.24384283126171247</v>
       </c>
       <c r="N4" s="1">
-        <v>31.0126582278481</v>
+        <v>33.79746835443037</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>89</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.86</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1635,37 +1638,37 @@
         <v>0.63</v>
       </c>
       <c r="F5" s="3">
-        <v>-0.13907356913892643</v>
+        <v>-0.1747058861985029</v>
       </c>
       <c r="G5" s="3">
         <v>1.81</v>
       </c>
       <c r="H5" s="3">
-        <v>69.02</v>
+        <v>57.96</v>
       </c>
       <c r="I5" s="3">
-        <v>8.95</v>
+        <v>3.64</v>
       </c>
       <c r="J5" s="3">
-        <v>0.009539856733924958</v>
+        <v>0.009369255969228586</v>
       </c>
       <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>8</v>
+        <v>-46</v>
       </c>
       <c r="M5" s="3">
-        <v>-0.053502375489511644</v>
+        <v>-0.09618756716171784</v>
       </c>
       <c r="N5" s="3">
-        <v>61.265822784810126</v>
+        <v>59.74683544303797</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P5" s="3">
-        <v>-0.93</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1685,37 +1688,37 @@
         <v>-0.4</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.026325925062233996</v>
+        <v>-0.025082632229554647</v>
       </c>
       <c r="G6" s="1">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H6" s="1">
-        <v>36.43</v>
+        <v>36.73</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.36</v>
+        <v>-15.16</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.008207055983860102</v>
+        <v>-0.011352692562937442</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="M6" s="1">
-        <v>0.02966510288121027</v>
+        <v>0.024354827904717435</v>
       </c>
       <c r="N6" s="1">
-        <v>38.734177215189874</v>
+        <v>37.594936708860764</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>91</v>
       </c>
       <c r="P6" s="1">
-        <v>-2.36</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1729,25 +1732,25 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D7" s="3">
-        <v>6.242857142857143</v>
+        <v>6.293877551020408</v>
       </c>
       <c r="E7" s="3">
         <v>0.14</v>
       </c>
       <c r="F7" s="3">
-        <v>0.012598577802383992</v>
+        <v>0.002710766112608426</v>
       </c>
       <c r="G7" s="3">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="H7" s="3">
-        <v>76.72</v>
+        <v>64.66</v>
       </c>
       <c r="I7" s="3">
-        <v>26.92</v>
+        <v>21.16</v>
       </c>
       <c r="J7" s="3">
-        <v>0.0222649083786252</v>
+        <v>0.023430570277173587</v>
       </c>
       <c r="K7" s="3" t="b">
         <v>0</v>
@@ -1756,16 +1759,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <v>0.14465288898975248</v>
+        <v>0.12485037350316297</v>
       </c>
       <c r="N7" s="3">
-        <v>64.68354430379746</v>
+        <v>63.54430379746835</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="P7" s="3">
-        <v>1.67</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1785,37 +1788,37 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="3">
-        <v>0.32294341698883905</v>
+        <v>0.2685989729401681</v>
       </c>
       <c r="G8" s="3">
         <v>0.66</v>
       </c>
       <c r="H8" s="3">
-        <v>83.06</v>
+        <v>76.94</v>
       </c>
       <c r="I8" s="3">
-        <v>24.78</v>
+        <v>22.89</v>
       </c>
       <c r="J8" s="3">
-        <v>0.03278600596447727</v>
+        <v>0.03334742657966023</v>
       </c>
       <c r="K8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>-151</v>
+        <v>-191</v>
       </c>
       <c r="M8" s="3">
-        <v>0.2870246443458748</v>
+        <v>0.2356406661839867</v>
       </c>
       <c r="N8" s="3">
-        <v>66.07594936708861</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>93</v>
       </c>
       <c r="P8" s="3">
-        <v>-1.05</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1835,37 +1838,37 @@
         <v>2.14</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.13253579561631276</v>
+        <v>-0.13555171012196826</v>
       </c>
       <c r="G9" s="1">
         <v>1.49</v>
       </c>
       <c r="H9" s="1">
-        <v>43.15</v>
+        <v>43.48</v>
       </c>
       <c r="I9" s="1">
-        <v>-18.2</v>
+        <v>-17.98</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.006074337239468922</v>
+        <v>-0.008892293005765361</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>31</v>
+        <v>-6</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.0807705056308643</v>
+        <v>-0.08805297391453037</v>
       </c>
       <c r="N9" s="1">
-        <v>49.11392405063291</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>94</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.34</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1879,43 +1882,43 @@
         <v>67.08860759493672</v>
       </c>
       <c r="D10" s="1">
-        <v>0.5408000000000002</v>
+        <v>0.4912</v>
       </c>
       <c r="E10" s="1">
         <v>1.07</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.1300139538077629</v>
+        <v>-0.17331904401626377</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>54.79</v>
+        <v>47.96</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.22</v>
+        <v>-5.63</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0013791610554501825</v>
+        <v>0.000950680512234819</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-88</v>
+        <v>-128</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.08670013973830604</v>
+        <v>-0.1335752035161627</v>
       </c>
       <c r="N10" s="1">
-        <v>48.22784810126583</v>
+        <v>46.582278481012665</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.36</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1935,37 +1938,37 @@
         <v>8.3</v>
       </c>
       <c r="F11" s="3">
-        <v>0.14409952072929216</v>
+        <v>0.12533555255876536</v>
       </c>
       <c r="G11" s="3">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="H11" s="3">
-        <v>64.07</v>
+        <v>66.24</v>
       </c>
       <c r="I11" s="3">
-        <v>5.82</v>
+        <v>8.13</v>
       </c>
       <c r="J11" s="3">
-        <v>0.02122061710133614</v>
+        <v>0.020811267204622307</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M11" s="3">
-        <v>0.12402726542881215</v>
+        <v>0.10788703721725756</v>
       </c>
       <c r="N11" s="3">
-        <v>53.79746835443038</v>
+        <v>56.07594936708861</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="3">
-        <v>-0.72</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1979,43 +1982,43 @@
         <v>20.253164556962027</v>
       </c>
       <c r="D12" s="1">
-        <v>65.85294117647058</v>
+        <v>65.70588235294117</v>
       </c>
       <c r="E12" s="1">
         <v>-0.32</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.33334786344112566</v>
+        <v>-0.2905302085040573</v>
       </c>
       <c r="G12" s="1">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H12" s="1">
-        <v>47.26</v>
+        <v>52.17</v>
       </c>
       <c r="I12" s="1">
-        <v>-37.79</v>
+        <v>-34.67</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.011253071438596102</v>
+        <v>-0.011095628644533537</v>
       </c>
       <c r="K12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>-16</v>
+        <v>-25</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.35236368425210673</v>
+        <v>-0.307009361882148</v>
       </c>
       <c r="N12" s="1">
-        <v>40.00000000000001</v>
+        <v>41.898734177215196</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="P12" s="1">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2035,37 +2038,37 @@
         <v>2.73</v>
       </c>
       <c r="F13" s="4">
-        <v>-0.16428932419856557</v>
+        <v>-0.24695705804821247</v>
       </c>
       <c r="G13" s="4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H13" s="4">
-        <v>54.94</v>
+        <v>46.37</v>
       </c>
       <c r="I13" s="4">
-        <v>6.55</v>
+        <v>-1.23</v>
       </c>
       <c r="J13" s="4">
-        <v>-0.002415330820078252</v>
+        <v>-0.0006453714211657933</v>
       </c>
       <c r="K13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M13" s="4">
-        <v>-0.1188626411501108</v>
+        <v>-0.20624385558469427</v>
       </c>
       <c r="N13" s="4">
-        <v>28.734177215189874</v>
+        <v>26.962025316455698</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>98</v>
       </c>
       <c r="P13" s="4">
-        <v>-0.85</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -2085,37 +2088,37 @@
         <v>0.33</v>
       </c>
       <c r="F14" s="3">
-        <v>-0.11959597331378823</v>
+        <v>-0.12133656204260415</v>
       </c>
       <c r="G14" s="3">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H14" s="3">
-        <v>57.01</v>
+        <v>59.72</v>
       </c>
       <c r="I14" s="3">
-        <v>-4.92</v>
+        <v>-2.81</v>
       </c>
       <c r="J14" s="3">
-        <v>0.00997061817242482</v>
+        <v>0.008497241964348224</v>
       </c>
       <c r="K14" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M14" s="3">
-        <v>-0.16185335289374614</v>
+        <v>-0.15914167861587103</v>
       </c>
       <c r="N14" s="3">
-        <v>53.79746835443038</v>
+        <v>55.569620253164565</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>96</v>
       </c>
       <c r="P14" s="3">
-        <v>0.51</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -2135,37 +2138,37 @@
         <v>5.78</v>
       </c>
       <c r="F15" s="3">
-        <v>1.2489126243752493</v>
+        <v>1.098693544416193</v>
       </c>
       <c r="G15" s="3">
         <v>2.22</v>
       </c>
       <c r="H15" s="3">
-        <v>69.71</v>
+        <v>62.25</v>
       </c>
       <c r="I15" s="3">
-        <v>161.42</v>
+        <v>142.85</v>
       </c>
       <c r="J15" s="3">
-        <v>0.12753161590932974</v>
+        <v>0.11891077311217498</v>
       </c>
       <c r="K15" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="M15" s="3">
-        <v>1.377797632094121</v>
+        <v>1.2169557039530792</v>
       </c>
       <c r="N15" s="3">
-        <v>69.36708860759494</v>
+        <v>69.11392405063292</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>99</v>
       </c>
       <c r="P15" s="3">
-        <v>-1.32</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2185,37 +2188,37 @@
         <v>4.52</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.08919224264039691</v>
+        <v>-0.04425532051485587</v>
       </c>
       <c r="G16" s="1">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="1">
-        <v>44.88</v>
+        <v>48.96</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.84</v>
+        <v>3.5</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0015444274654613306</v>
+        <v>-0.0005051886203465474</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M16" s="1">
-        <v>0.010112599372504194</v>
+        <v>0.04395661815610019</v>
       </c>
       <c r="N16" s="1">
-        <v>40</v>
+        <v>42.40506329113924</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P16" s="1">
-        <v>-4.79</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -2226,7 +2229,7 @@
         <v>-6.21</v>
       </c>
       <c r="C17" s="4">
-        <v>2.5316455696202533</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="D17" s="4">
         <v>4.355877616747182</v>
@@ -2235,31 +2238,31 @@
         <v>4.89</v>
       </c>
       <c r="F17" s="4">
-        <v>-0.16244837109199475</v>
+        <v>-0.2643194481130663</v>
       </c>
       <c r="G17" s="4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H17" s="4">
-        <v>44.61</v>
+        <v>40.67</v>
       </c>
       <c r="I17" s="4">
-        <v>-9.88</v>
+        <v>-13.46</v>
       </c>
       <c r="J17" s="4">
-        <v>-0.013692428469579026</v>
+        <v>-0.014498611276431882</v>
       </c>
       <c r="K17" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="4">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="M17" s="4">
-        <v>-0.08532865335857154</v>
+        <v>-0.19549474871045225</v>
       </c>
       <c r="N17" s="4">
-        <v>24.55696202531646</v>
+        <v>24.55696202531645</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>94</v>
@@ -2285,37 +2288,37 @@
         <v>9.43</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.31475627532154227</v>
+        <v>-0.34700555328245314</v>
       </c>
       <c r="G18" s="1">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="H18" s="1">
-        <v>34.16</v>
+        <v>31.13</v>
       </c>
       <c r="I18" s="1">
-        <v>-10.15</v>
+        <v>-14.72</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.00862658866383474</v>
+        <v>-0.009012755161265349</v>
       </c>
       <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.29045828206306645</v>
+        <v>-0.32858767597752825</v>
       </c>
       <c r="N18" s="1">
-        <v>48.22784810126582</v>
+        <v>47.08860759493671</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P18" s="1">
-        <v>-5.06</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2329,43 +2332,43 @@
         <v>77.21518987341773</v>
       </c>
       <c r="D19" s="3">
-        <v>0.20386266094420605</v>
+        <v>0.24463519313304713</v>
       </c>
       <c r="E19" s="3">
         <v>-0.43</v>
       </c>
       <c r="F19" s="3">
-        <v>-0.05406046894859554</v>
+        <v>-0.048303366108382144</v>
       </c>
       <c r="G19" s="3">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="3">
-        <v>52.19</v>
+        <v>53.64</v>
       </c>
       <c r="I19" s="3">
-        <v>14.33</v>
+        <v>15.04</v>
       </c>
       <c r="J19" s="3">
-        <v>0.004860214961652308</v>
+        <v>0.004796651054090026</v>
       </c>
       <c r="K19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M19" s="3">
-        <v>-0.13751879361901242</v>
+        <v>-0.1258523231817501</v>
       </c>
       <c r="N19" s="3">
-        <v>52.78481012658228</v>
+        <v>54.17721518987342</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P19" s="3">
-        <v>-4.61</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2379,43 +2382,43 @@
         <v>65.82278481012658</v>
       </c>
       <c r="D20" s="1">
-        <v>0.9456342668863262</v>
+        <v>0.728171334431631</v>
       </c>
       <c r="E20" s="1">
         <v>-2.3</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.27738371895999425</v>
+        <v>-0.1448213611214662</v>
       </c>
       <c r="G20" s="1">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H20" s="1">
-        <v>33.58</v>
+        <v>34.91</v>
       </c>
       <c r="I20" s="1">
-        <v>-15.74</v>
+        <v>-15.3</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.012193955643101766</v>
+        <v>-0.012981356034968689</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.2742144154914974</v>
+        <v>-0.142882637194632</v>
       </c>
       <c r="N20" s="1">
-        <v>37.59493670886076</v>
+        <v>37.21518987341772</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P20" s="1">
-        <v>-1.58</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2429,43 +2432,43 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D21" s="3">
-        <v>13.990196078431373</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3">
         <v>5.19</v>
       </c>
       <c r="F21" s="3">
-        <v>-0.06041092891357461</v>
+        <v>0.0735583537615512</v>
       </c>
       <c r="G21" s="3">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="H21" s="3">
-        <v>75.29</v>
+        <v>79.77</v>
       </c>
       <c r="I21" s="3">
-        <v>32.12</v>
+        <v>45.16</v>
       </c>
       <c r="J21" s="3">
-        <v>-0.009010821698179192</v>
+        <v>0.002149483431858078</v>
       </c>
       <c r="K21" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M21" s="3">
-        <v>-0.028717894228606156</v>
+        <v>0.10845538444456682</v>
       </c>
       <c r="N21" s="3">
-        <v>55.69620253164557</v>
+        <v>62.65822784810127</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>103</v>
       </c>
       <c r="P21" s="3">
-        <v>5.97</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2479,43 +2482,43 @@
         <v>70.88607594936708</v>
       </c>
       <c r="D22" s="1">
-        <v>0.6954377311960543</v>
+        <v>0.6942046855733663</v>
       </c>
       <c r="E22" s="1">
         <v>0.16</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.2226599498002808</v>
+        <v>-0.24902962388139738</v>
       </c>
       <c r="G22" s="1">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H22" s="1">
-        <v>47.63</v>
+        <v>42.03</v>
       </c>
       <c r="I22" s="1">
-        <v>-2.68</v>
+        <v>-6.03</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.014654852890405735</v>
+        <v>-0.014815021759235719</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.18462830817831866</v>
+        <v>-0.21510195516179886</v>
       </c>
       <c r="N22" s="1">
-        <v>41.265822784810126</v>
+        <v>40.50632911392404</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P22" s="1">
-        <v>-1.47</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2529,93 +2532,93 @@
         <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.7593602326426754</v>
+        <v>-0.7706288622319157</v>
       </c>
       <c r="E23" s="1">
         <v>-0.52</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.1900389233125886</v>
+        <v>-0.16990217780303657</v>
       </c>
       <c r="G23" s="1">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H23" s="1">
-        <v>47.08</v>
+        <v>45.59</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.22</v>
+        <v>-8.79</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.007490385149177563</v>
+        <v>-0.0074685167164958485</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.16468449556461384</v>
+        <v>-0.1476068526444433</v>
       </c>
       <c r="N23" s="1">
-        <v>45.063291139240505</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>-40.16</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="4">
         <v>1.2658227848101267</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="4">
         <v>-0.3107569721115539</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="4">
         <v>9.38</v>
       </c>
-      <c r="F24" s="1">
-        <v>0.13218419798629943</v>
-      </c>
-      <c r="G24" s="1">
+      <c r="F24" s="4">
+        <v>-0.03159567105820904</v>
+      </c>
+      <c r="G24" s="4">
         <v>3.57</v>
       </c>
-      <c r="H24" s="1">
-        <v>60.53</v>
-      </c>
-      <c r="I24" s="1">
-        <v>-14.66</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0.03461953962176362</v>
-      </c>
-      <c r="K24" s="1" t="b">
+      <c r="H24" s="4">
+        <v>54.4</v>
+      </c>
+      <c r="I24" s="4">
+        <v>-18.62</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.032115427199283675</v>
+      </c>
+      <c r="K24" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="1">
-        <v>32</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0.403687861787529</v>
-      </c>
-      <c r="N24" s="1">
-        <v>31.012658227848103</v>
-      </c>
-      <c r="O24" s="1" t="s">
+      <c r="L24" s="4">
+        <v>10</v>
+      </c>
+      <c r="M24" s="4">
+        <v>0.2175303535399855</v>
+      </c>
+      <c r="N24" s="4">
+        <v>28.9873417721519</v>
+      </c>
+      <c r="O24" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="P24" s="1">
-        <v>0.88</v>
+      <c r="P24" s="4">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2635,37 +2638,37 @@
         <v>11.91</v>
       </c>
       <c r="F25" s="4">
-        <v>-0.3842905296912893</v>
+        <v>-0.441182512906166</v>
       </c>
       <c r="G25" s="4">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H25" s="4">
-        <v>49.84</v>
+        <v>45.21</v>
       </c>
       <c r="I25" s="4">
-        <v>-49.87</v>
+        <v>-52.93</v>
       </c>
       <c r="J25" s="4">
-        <v>-0.004190207254928142</v>
+        <v>-0.0044881616010012575</v>
       </c>
       <c r="K25" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="4">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M25" s="4">
-        <v>-0.25434908748291873</v>
+        <v>-0.3229203533692798</v>
       </c>
       <c r="N25" s="4">
-        <v>27.9746835443038</v>
+        <v>27.341772151898734</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>104</v>
       </c>
       <c r="P25" s="4">
-        <v>-0.24</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -2685,37 +2688,37 @@
         <v>4.67</v>
       </c>
       <c r="F26" s="1">
-        <v>0.5020833663902557</v>
+        <v>0.21466965129619875</v>
       </c>
       <c r="G26" s="1">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="H26" s="1">
-        <v>69.75</v>
+        <v>58.58</v>
       </c>
       <c r="I26" s="1">
-        <v>22.49</v>
+        <v>10.58</v>
       </c>
       <c r="J26" s="1">
-        <v>0.044836941288624664</v>
+        <v>0.04870818061008482</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-14</v>
+        <v>-33</v>
       </c>
       <c r="M26" s="1">
-        <v>0.719708871227039</v>
+        <v>0.41532757772353834</v>
       </c>
       <c r="N26" s="1">
-        <v>41.139240506329116</v>
+        <v>39.367088607594944</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P26" s="1">
-        <v>-0.5</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -2735,28 +2738,28 @@
         <v>1.65</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.21166917153997578</v>
+        <v>-0.21825818230701438</v>
       </c>
       <c r="G27" s="1">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="H27" s="1">
-        <v>59.81</v>
+        <v>56.69</v>
       </c>
       <c r="I27" s="1">
-        <v>-19.37</v>
+        <v>-21.3</v>
       </c>
       <c r="J27" s="1">
-        <v>0.007828341610272474</v>
+        <v>0.008056962376991866</v>
       </c>
       <c r="K27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M27" s="1">
-        <v>-0.039470349751647316</v>
+        <v>-0.06122154423344428</v>
       </c>
       <c r="N27" s="1">
         <v>36.20253164556962</v>
@@ -2785,37 +2788,37 @@
         <v>-0.68</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.3942456323090784</v>
+        <v>-0.42051181481840655</v>
       </c>
       <c r="G28" s="1">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="H28" s="1">
-        <v>57.94</v>
+        <v>49.44</v>
       </c>
       <c r="I28" s="1">
-        <v>-21.48</v>
+        <v>-25.71</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.010625421345111468</v>
+        <v>-0.009005059235791242</v>
       </c>
       <c r="K28" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.16816865155630356</v>
+        <v>-0.21403771661056437</v>
       </c>
       <c r="N28" s="1">
-        <v>34.30379746835443</v>
+        <v>33.67088607594936</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P28" s="1">
-        <v>-0.76</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2835,37 +2838,37 @@
         <v>0.62</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.4036058072820504</v>
+        <v>-0.419262979032475</v>
       </c>
       <c r="G29" s="1">
         <v>2.11</v>
       </c>
       <c r="H29" s="1">
-        <v>43.77</v>
+        <v>41.09</v>
       </c>
       <c r="I29" s="1">
-        <v>-31.87</v>
+        <v>-33.52</v>
       </c>
       <c r="J29" s="1">
-        <v>-0.015321352173938154</v>
+        <v>-0.015715482245240393</v>
       </c>
       <c r="K29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>-26</v>
+        <v>-45</v>
       </c>
       <c r="M29" s="1">
-        <v>-0.2863415789476672</v>
+        <v>-0.31166380109317693</v>
       </c>
       <c r="N29" s="1">
-        <v>41.645569620253156</v>
+        <v>41.518987341772146</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>102</v>
       </c>
       <c r="P29" s="1">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2879,43 +2882,43 @@
         <v>46.835443037974684</v>
       </c>
       <c r="D30" s="3">
-        <v>1656.8153846153846</v>
+        <v>2523.594871794872</v>
       </c>
       <c r="E30" s="3">
         <v>2.13</v>
       </c>
       <c r="F30" s="3">
-        <v>-0.18094330743064543</v>
+        <v>-0.2195577976440304</v>
       </c>
       <c r="G30" s="3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="3">
-        <v>51.75</v>
+        <v>44.58</v>
       </c>
       <c r="I30" s="3">
-        <v>4.33</v>
+        <v>0.37</v>
       </c>
       <c r="J30" s="3">
-        <v>0.004066824753637364</v>
+        <v>0.0031873692550686795</v>
       </c>
       <c r="K30" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="3">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M30" s="3">
-        <v>-0.15875818315116752</v>
+        <v>-0.20017055837568842</v>
       </c>
       <c r="N30" s="3">
-        <v>64.17721518987342</v>
+        <v>63.037974683544306</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P30" s="3">
-        <v>-3.49</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2929,43 +2932,43 @@
         <v>59.49367088607595</v>
       </c>
       <c r="D31" s="3">
-        <v>10.688109161793372</v>
+        <v>10.690058479532164</v>
       </c>
       <c r="E31" s="3">
         <v>0.9</v>
       </c>
       <c r="F31" s="3">
-        <v>0.16616848627336422</v>
+        <v>0.15822414412232277</v>
       </c>
       <c r="G31" s="3">
         <v>1.43</v>
       </c>
       <c r="H31" s="3">
-        <v>66.12</v>
+        <v>58.64</v>
       </c>
       <c r="I31" s="3">
-        <v>27.03</v>
+        <v>22.59</v>
       </c>
       <c r="J31" s="3">
-        <v>0.030438719361390046</v>
+        <v>0.029369983533265455</v>
       </c>
       <c r="K31" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="3">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="M31" s="3">
-        <v>0.211595169321819</v>
+        <v>0.19990670854925807</v>
       </c>
       <c r="N31" s="3">
-        <v>68.9873417721519</v>
+        <v>68.48101265822785</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>105</v>
       </c>
       <c r="P31" s="3">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2985,37 +2988,37 @@
         <v>1.69</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.14369306296906825</v>
+        <v>-0.38807011843937855</v>
       </c>
       <c r="G32" s="1">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H32" s="1">
-        <v>42.1</v>
+        <v>36.12</v>
       </c>
       <c r="I32" s="1">
-        <v>-5.28</v>
+        <v>-10.07</v>
       </c>
       <c r="J32" s="1">
-        <v>-0.006301043397299648</v>
+        <v>-0.006325061572753529</v>
       </c>
       <c r="K32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.07925055910963241</v>
+        <v>-0.32990840063435256</v>
       </c>
       <c r="N32" s="1">
-        <v>35.31645569620254</v>
+        <v>34.810126582278485</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.71</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -3035,37 +3038,37 @@
         <v>0.37</v>
       </c>
       <c r="F33" s="3">
-        <v>-0.10701325362409692</v>
+        <v>-0.06411046878691452</v>
       </c>
       <c r="G33" s="3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H33" s="3">
-        <v>50.31</v>
+        <v>57.9</v>
       </c>
       <c r="I33" s="3">
-        <v>-11.68</v>
+        <v>-8.9</v>
       </c>
       <c r="J33" s="3">
-        <v>0.0024153065585720847</v>
+        <v>0.0023051794827069136</v>
       </c>
       <c r="K33" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="M33" s="3">
-        <v>-0.09750534321860638</v>
+        <v>-0.056355573079577725</v>
       </c>
       <c r="N33" s="3">
-        <v>50</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P33" s="3">
-        <v>-0.41</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -3079,43 +3082,43 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D34" s="3">
-        <v>-0.6453089244851258</v>
+        <v>-0.6643783371472158</v>
       </c>
       <c r="E34" s="3">
         <v>0.58</v>
       </c>
       <c r="F34" s="3">
-        <v>0.15410044307464957</v>
+        <v>0.16496462914942378</v>
       </c>
       <c r="G34" s="3">
         <v>1.26</v>
       </c>
       <c r="H34" s="3">
-        <v>74.16</v>
+        <v>70.23</v>
       </c>
       <c r="I34" s="3">
-        <v>38.16</v>
+        <v>36.21</v>
       </c>
       <c r="J34" s="3">
-        <v>0.02784497492099956</v>
+        <v>0.02783748309324901</v>
       </c>
       <c r="K34" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="M34" s="3">
-        <v>0.18156773980162222</v>
+        <v>0.19016804019826838</v>
       </c>
       <c r="N34" s="3">
-        <v>61.139240506329116</v>
+        <v>61.01265822784811</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P34" s="3">
-        <v>-0.92</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -3135,37 +3138,37 @@
         <v>-0.96</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.3200971245283263</v>
+        <v>-0.3016835226741067</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H35" s="1">
-        <v>26.64</v>
+        <v>26.06</v>
       </c>
       <c r="I35" s="1">
-        <v>-25.24</v>
+        <v>-25.51</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.02473204394272379</v>
+        <v>-0.02616499403082351</v>
       </c>
       <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.3200971245283263</v>
+        <v>-0.3026528846375238</v>
       </c>
       <c r="N35" s="1">
-        <v>32.911392405063296</v>
+        <v>33.037974683544306</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>106</v>
       </c>
       <c r="P35" s="1">
-        <v>-0.38</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -3185,37 +3188,37 @@
         <v>-0.97</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.13218519768832587</v>
+        <v>-0.19098513098420686</v>
       </c>
       <c r="G36" s="1">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H36" s="1">
-        <v>38.09</v>
+        <v>35.18</v>
       </c>
       <c r="I36" s="1">
-        <v>-15.62</v>
+        <v>-17.99</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.011989533227783128</v>
+        <v>-0.014982028229795937</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.11950798381433847</v>
+        <v>-0.18129151135003585</v>
       </c>
       <c r="N36" s="1">
-        <v>40.12658227848101</v>
+        <v>38.35443037974683</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>100</v>
       </c>
       <c r="P36" s="1">
-        <v>-2.48</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -3229,43 +3232,43 @@
         <v>63.29113924050633</v>
       </c>
       <c r="D37" s="1">
-        <v>0.598499061913696</v>
+        <v>0.6060037523452159</v>
       </c>
       <c r="E37" s="1">
         <v>0.52</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.004030313562553567</v>
+        <v>-0.04129399285351304</v>
       </c>
       <c r="G37" s="1">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H37" s="1">
-        <v>37.4</v>
+        <v>34.95</v>
       </c>
       <c r="I37" s="1">
-        <v>-22.29</v>
+        <v>-23.21</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.0018543394895870096</v>
+        <v>-0.0031632491880796624</v>
       </c>
       <c r="K37" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>-149</v>
+        <v>-200</v>
       </c>
       <c r="M37" s="1">
-        <v>0.03611419703840646</v>
+        <v>-0.00542760020708033</v>
       </c>
       <c r="N37" s="1">
-        <v>38.9873417721519</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.97</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -3285,37 +3288,37 @@
         <v>-0.1</v>
       </c>
       <c r="F38" s="3">
-        <v>0.2822612375138287</v>
+        <v>0.26342049006394885</v>
       </c>
       <c r="G38" s="3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H38" s="3">
-        <v>81.07</v>
+        <v>82.57</v>
       </c>
       <c r="I38" s="3">
-        <v>26.13</v>
+        <v>29.02</v>
       </c>
       <c r="J38" s="3">
-        <v>0.03887399062219226</v>
+        <v>0.03960451097304168</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="3">
-        <v>-22</v>
+        <v>-46</v>
       </c>
       <c r="M38" s="3">
-        <v>0.2928255824088182</v>
+        <v>0.27505283362495403</v>
       </c>
       <c r="N38" s="3">
-        <v>64.43037974683544</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>105</v>
       </c>
       <c r="P38" s="3">
-        <v>-1.32</v>
+        <v>-0.94</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3335,37 +3338,37 @@
         <v>-7.97</v>
       </c>
       <c r="F39" s="3">
-        <v>0.09296357322711366</v>
+        <v>0.06794935342768335</v>
       </c>
       <c r="G39" s="3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H39" s="3">
-        <v>50.52</v>
+        <v>48.15</v>
       </c>
       <c r="I39" s="3">
-        <v>8.69</v>
+        <v>7.47</v>
       </c>
       <c r="J39" s="3">
-        <v>0.01993512563304211</v>
+        <v>0.0170512546758961</v>
       </c>
       <c r="K39" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L39" s="3">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="M39" s="3">
-        <v>0.1246566079120821</v>
+        <v>0.09606085036677925</v>
       </c>
       <c r="N39" s="3">
-        <v>57.46835443037974</v>
+        <v>56.45569620253165</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>92</v>
       </c>
       <c r="P39" s="3">
-        <v>-2.53</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -3373,49 +3376,49 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>-4.08</v>
+        <v>-6.41</v>
       </c>
       <c r="C40" s="1">
-        <v>5.063291139240507</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>15.710784313725492</v>
+        <v>10.018720748829953</v>
       </c>
       <c r="E40" s="1">
         <v>12.27</v>
       </c>
       <c r="F40" s="1">
-        <v>0.23365240377663457</v>
+        <v>0.11310755946653876</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>47.21</v>
+        <v>40.05</v>
       </c>
       <c r="I40" s="1">
-        <v>-12.73</v>
+        <v>-21.05</v>
       </c>
       <c r="J40" s="1">
-        <v>0.022977603412417152</v>
+        <v>0.01748544935491823</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M40" s="1">
-        <v>0.1280089548267398</v>
+        <v>0.016171363124828808</v>
       </c>
       <c r="N40" s="1">
-        <v>44.68354430379747</v>
+        <v>37.34177215189874</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>107</v>
       </c>
       <c r="P40" s="1">
-        <v>-4.08</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3426,7 +3429,7 @@
         <v>-5.03</v>
       </c>
       <c r="C41" s="1">
-        <v>3.79746835443038</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="D41" s="1">
         <v>7.34990059642147</v>
@@ -3435,37 +3438,37 @@
         <v>-1.75</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.02375885219811577</v>
+        <v>-0.029972241879371517</v>
       </c>
       <c r="G41" s="1">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H41" s="1">
-        <v>74.52</v>
+        <v>67.11</v>
       </c>
       <c r="I41" s="1">
-        <v>-6.95</v>
+        <v>-10.02</v>
       </c>
       <c r="J41" s="1">
-        <v>0.01664603618337326</v>
+        <v>0.020311357402799175</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L41" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.012138072813627332</v>
+        <v>-0.01737053635494923</v>
       </c>
       <c r="N41" s="1">
-        <v>43.79746835443038</v>
+        <v>44.55696202531645</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>99</v>
       </c>
       <c r="P41" s="1">
-        <v>-2.09</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -3485,37 +3488,37 @@
         <v>-0.1</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.06845247200694075</v>
+        <v>-0.11210518309493923</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>38.68</v>
+        <v>32.57</v>
       </c>
       <c r="I42" s="1">
-        <v>-0.48</v>
+        <v>-2.68</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.006223033526343932</v>
+        <v>-0.00652169519913724</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.13606427933487342</v>
+        <v>-0.1741443487536336</v>
       </c>
       <c r="N42" s="1">
-        <v>43.41772151898734</v>
+        <v>41.64556962025316</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>103</v>
       </c>
       <c r="P42" s="1">
-        <v>1.23</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3535,37 +3538,37 @@
         <v>5.23</v>
       </c>
       <c r="F43" s="3">
-        <v>-0.09542337847727217</v>
+        <v>-0.05089839962555098</v>
       </c>
       <c r="G43" s="3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H43" s="3">
-        <v>42.64</v>
+        <v>50.34</v>
       </c>
       <c r="I43" s="3">
-        <v>-18.41</v>
+        <v>-13.72</v>
       </c>
       <c r="J43" s="3">
-        <v>-0.0014235899909965254</v>
+        <v>-0.0019450182993650366</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M43" s="3">
-        <v>-0.06689964726080055</v>
+        <v>-0.02569498857670638</v>
       </c>
       <c r="N43" s="3">
-        <v>50.379746835443036</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>108</v>
       </c>
       <c r="P43" s="3">
-        <v>-2.36</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -3579,43 +3582,43 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="1">
-        <v>26.862745098039216</v>
+        <v>26.91176470588235</v>
       </c>
       <c r="E44" s="1">
         <v>-1.51</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.4040123402536418</v>
+        <v>-0.37008009296786126</v>
       </c>
       <c r="G44" s="1">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="H44" s="1">
-        <v>33.61</v>
+        <v>37.06</v>
       </c>
       <c r="I44" s="1">
-        <v>-30.98</v>
+        <v>-28.9</v>
       </c>
       <c r="J44" s="1">
-        <v>-0.018336993673082717</v>
+        <v>-0.021500255259178976</v>
       </c>
       <c r="K44" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="1">
-        <v>-31</v>
+        <v>-88</v>
       </c>
       <c r="M44" s="1">
-        <v>-0.23603925642330914</v>
+        <v>-0.21789026471137662</v>
       </c>
       <c r="N44" s="1">
-        <v>38.73417721518987</v>
+        <v>39.99999999999999</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="P44" s="1">
-        <v>-0.44</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3629,43 +3632,43 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="3">
-        <v>0.818399044205496</v>
+        <v>0.821983273596177</v>
       </c>
       <c r="E45" s="3">
         <v>0.94</v>
       </c>
       <c r="F45" s="3">
-        <v>0.17378808482099742</v>
+        <v>0.1774315040334033</v>
       </c>
       <c r="G45" s="3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="3">
-        <v>62.91</v>
+        <v>58.56</v>
       </c>
       <c r="I45" s="3">
-        <v>16.56</v>
+        <v>15.14</v>
       </c>
       <c r="J45" s="3">
-        <v>0.025482681526180457</v>
+        <v>0.023648199835042998</v>
       </c>
       <c r="K45" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="M45" s="3">
-        <v>0.22238407133794902</v>
+        <v>0.2210527923871728</v>
       </c>
       <c r="N45" s="3">
-        <v>61.51898734177216</v>
+        <v>62.65822784810127</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P45" s="3">
-        <v>-2.73</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3685,37 +3688,37 @@
         <v>-0.94</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.25477861737604435</v>
+        <v>-0.26667139695523195</v>
       </c>
       <c r="G46" s="3">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H46" s="3">
-        <v>44.64</v>
+        <v>40.87</v>
       </c>
       <c r="I46" s="3">
-        <v>11.29</v>
+        <v>4.79</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.006220806887688156</v>
+        <v>-0.0066835997262821335</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.20090045841159798</v>
+        <v>-0.21917266074779407</v>
       </c>
       <c r="N46" s="3">
-        <v>51.77215189873418</v>
+        <v>50.12658227848101</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>95</v>
       </c>
       <c r="P46" s="3">
-        <v>-2.61</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3735,87 +3738,87 @@
         <v>-4.11</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.41131670566831885</v>
+        <v>-0.457975392465942</v>
       </c>
       <c r="G47" s="1">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H47" s="1">
-        <v>29.36</v>
+        <v>26.92</v>
       </c>
       <c r="I47" s="1">
-        <v>-18.79</v>
+        <v>-21.51</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.029771108480814303</v>
+        <v>-0.030394377303079353</v>
       </c>
       <c r="K47" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.3616642846618683</v>
+        <v>-0.4133847421487554</v>
       </c>
       <c r="N47" s="1">
-        <v>38.734177215189874</v>
+        <v>38.9873417721519</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>101</v>
       </c>
       <c r="P47" s="1">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="2">
         <v>3.98</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>54.43037974683544</v>
       </c>
-      <c r="D48" s="3">
-        <v>7.505025125628141</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="2">
+        <v>7.675879396984925</v>
+      </c>
+      <c r="E48" s="2">
         <v>-1.16</v>
       </c>
-      <c r="F48" s="3">
-        <v>0.3581561024532833</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="H48" s="3">
-        <v>72.08</v>
-      </c>
-      <c r="I48" s="3">
-        <v>86.27</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0.03910672973553605</v>
-      </c>
-      <c r="K48" s="3" t="b">
+      <c r="F48" s="2">
+        <v>0.36634599216298047</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2.11</v>
+      </c>
+      <c r="H48" s="2">
+        <v>68.87</v>
+      </c>
+      <c r="I48" s="2">
+        <v>82.63</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0.04172592781156484</v>
+      </c>
+      <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L48" s="3">
-        <v>276</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0.47436389629816755</v>
-      </c>
-      <c r="N48" s="3">
-        <v>69.87341772151898</v>
-      </c>
-      <c r="O48" s="3" t="s">
+      <c r="L48" s="2">
+        <v>267</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0.47394517010227855</v>
+      </c>
+      <c r="N48" s="2">
+        <v>71.13924050632912</v>
+      </c>
+      <c r="O48" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="P48" s="3">
-        <v>0.42</v>
+      <c r="P48" s="2">
+        <v>1.69</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -3829,43 +3832,43 @@
         <v>26.582278481012654</v>
       </c>
       <c r="D49" s="2">
-        <v>1710.0000000000002</v>
+        <v>1709.8333333333335</v>
       </c>
       <c r="E49" s="2">
         <v>2.02</v>
       </c>
       <c r="F49" s="2">
-        <v>0.7701396873881722</v>
+        <v>0.5966006262232061</v>
       </c>
       <c r="G49" s="2">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="H49" s="2">
-        <v>70.05</v>
+        <v>58.79</v>
       </c>
       <c r="I49" s="2">
-        <v>141.2</v>
+        <v>117.31</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06599801135342893</v>
+        <v>0.06785937393502986</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="M49" s="2">
-        <v>1.0659413444478776</v>
+        <v>0.8670526140165769</v>
       </c>
       <c r="N49" s="2">
-        <v>74.55696202531647</v>
+        <v>73.0379746835443</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>103</v>
       </c>
       <c r="P49" s="2">
-        <v>0.45</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3879,43 +3882,43 @@
         <v>25.31645569620253</v>
       </c>
       <c r="D50" s="1">
-        <v>385.61538461538464</v>
+        <v>300.1538461538462</v>
       </c>
       <c r="E50" s="1">
         <v>2.75</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.4456764354715913</v>
+        <v>-0.46770435480298933</v>
       </c>
       <c r="G50" s="1">
         <v>1.53</v>
       </c>
       <c r="H50" s="1">
-        <v>37.04</v>
+        <v>34.19</v>
       </c>
       <c r="I50" s="1">
-        <v>-24.92</v>
+        <v>-28.15</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.030562508889854904</v>
+        <v>-0.03248906040173917</v>
       </c>
       <c r="K50" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L50" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.38968540752814707</v>
+        <v>-0.416328170741883</v>
       </c>
       <c r="N50" s="1">
-        <v>38.607594936708864</v>
+        <v>38.22784810126583</v>
       </c>
       <c r="O50" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P50" s="1">
-        <v>0.25</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3935,37 +3938,37 @@
         <v>17.05</v>
       </c>
       <c r="F51" s="1">
-        <v>0.040237710631943646</v>
+        <v>0.02092920462188544</v>
       </c>
       <c r="G51" s="1">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="H51" s="1">
-        <v>55.1</v>
+        <v>53.42</v>
       </c>
       <c r="I51" s="1">
-        <v>32.39</v>
+        <v>29.59</v>
       </c>
       <c r="J51" s="1">
-        <v>0.03138057009107268</v>
+        <v>0.029607238639130482</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="M51" s="1">
-        <v>0.18496923569329948</v>
+        <v>0.1498543457563597</v>
       </c>
       <c r="N51" s="1">
-        <v>33.67088607594937</v>
+        <v>32.911392405063296</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>109</v>
       </c>
       <c r="P51" s="1">
-        <v>-2.49</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3985,37 +3988,37 @@
         <v>0.22</v>
       </c>
       <c r="F52" s="3">
-        <v>0.08932039831916402</v>
+        <v>0.01973553992918095</v>
       </c>
       <c r="G52" s="3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H52" s="3">
-        <v>65.8</v>
+        <v>57.13</v>
       </c>
       <c r="I52" s="3">
-        <v>63.69</v>
+        <v>55.01</v>
       </c>
       <c r="J52" s="3">
-        <v>0.027490398754253076</v>
+        <v>0.028614893221618865</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="3">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="M52" s="3">
-        <v>0.17700446094757671</v>
+        <v>0.10116194485621732</v>
       </c>
       <c r="N52" s="3">
-        <v>66.83544303797468</v>
+        <v>65.94936708860759</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P52" s="3">
-        <v>0.12</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -4035,37 +4038,37 @@
         <v>6.97</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.17683265907237794</v>
+        <v>-0.22656157373327646</v>
       </c>
       <c r="G53" s="1">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="H53" s="1">
-        <v>67.9</v>
+        <v>57.25</v>
       </c>
       <c r="I53" s="1">
-        <v>-15.18</v>
+        <v>-20.97</v>
       </c>
       <c r="J53" s="1">
-        <v>0.01939648830140087</v>
+        <v>0.02174484183900514</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.008859575242045281</v>
+        <v>-0.07146365958654055</v>
       </c>
       <c r="N53" s="1">
-        <v>48.481012658227854</v>
+        <v>47.46835443037975</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>90</v>
       </c>
       <c r="P53" s="1">
-        <v>-2.2</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -4085,37 +4088,37 @@
         <v>-0.44</v>
       </c>
       <c r="F54" s="3">
-        <v>0.018459313876989097</v>
+        <v>-0.05302157269131072</v>
       </c>
       <c r="G54" s="3">
         <v>1.46</v>
       </c>
       <c r="H54" s="3">
-        <v>70.31</v>
+        <v>63.63</v>
       </c>
       <c r="I54" s="3">
-        <v>13.43</v>
+        <v>9.72</v>
       </c>
       <c r="J54" s="3">
-        <v>0.03012053713667029</v>
+        <v>0.03241268225849441</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L54" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M54" s="3">
-        <v>0.0670553003939407</v>
+        <v>-0.008430922374124128</v>
       </c>
       <c r="N54" s="3">
-        <v>66.70886075949367</v>
+        <v>67.21518987341771</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>89</v>
       </c>
       <c r="P54" s="3">
-        <v>0.68</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -4135,31 +4138,31 @@
         <v>-0.7</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.18835995215135273</v>
+        <v>-0.1790060492823699</v>
       </c>
       <c r="G55" s="1">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H55" s="1">
-        <v>38.01</v>
+        <v>37.62</v>
       </c>
       <c r="I55" s="1">
-        <v>-3.39</v>
+        <v>-3.56</v>
       </c>
       <c r="J55" s="1">
-        <v>0.00004749291211385887</v>
+        <v>0.00042365856082820846</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>-9</v>
+        <v>-31</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.16723126236137376</v>
+        <v>-0.16058817197744502</v>
       </c>
       <c r="N55" s="1">
-        <v>46.9620253164557</v>
+        <v>46.962025316455694</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>110</v>
@@ -4185,37 +4188,37 @@
         <v>0.84</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.09444301673683857</v>
+        <v>-0.10471492447755065</v>
       </c>
       <c r="G56" s="1">
         <v>0.26</v>
       </c>
       <c r="H56" s="1">
-        <v>52.57</v>
+        <v>45.72</v>
       </c>
       <c r="I56" s="1">
-        <v>10.48</v>
+        <v>8.37</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.008805394590350426</v>
+        <v>-0.008041054038631564</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.1726191689597607</v>
+        <v>-0.17644770977041602</v>
       </c>
       <c r="N56" s="1">
-        <v>45.82278481012658</v>
+        <v>45.18987341772152</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="P56" s="1">
-        <v>-1.16</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -4229,43 +4232,43 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.31067044381492</v>
+        <v>2.355524079320113</v>
       </c>
       <c r="E57" s="2">
         <v>0.39</v>
       </c>
       <c r="F57" s="2">
-        <v>0.6525192474183457</v>
+        <v>0.5547443642327915</v>
       </c>
       <c r="G57" s="2">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="H57" s="2">
-        <v>75.62</v>
+        <v>66.28</v>
       </c>
       <c r="I57" s="2">
-        <v>155.2</v>
+        <v>135.95</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08442887501652538</v>
+        <v>0.08302087502985447</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L57" s="2">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="M57" s="2">
-        <v>0.7581626963682404</v>
+        <v>0.6526499225379185</v>
       </c>
       <c r="N57" s="2">
-        <v>81.26582278481013</v>
+        <v>80.63291139240506</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>112</v>
       </c>
       <c r="P57" s="2">
-        <v>-0.79</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4285,37 +4288,37 @@
         <v>-1.9</v>
       </c>
       <c r="F58" s="3">
-        <v>0.031653877808134584</v>
+        <v>-0.020395804242056392</v>
       </c>
       <c r="G58" s="3">
         <v>1.62</v>
       </c>
       <c r="H58" s="3">
-        <v>66.47</v>
+        <v>57.98</v>
       </c>
       <c r="I58" s="3">
-        <v>50.17</v>
+        <v>44.43</v>
       </c>
       <c r="J58" s="3">
-        <v>0.022503688978931072</v>
+        <v>0.023405428653427596</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="M58" s="3">
-        <v>0.09715281615706939</v>
+        <v>0.039704637489803796</v>
       </c>
       <c r="N58" s="3">
-        <v>65.44303797468355</v>
+        <v>64.43037974683544</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>101</v>
       </c>
       <c r="P58" s="3">
-        <v>0.51</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4335,37 +4338,37 @@
         <v>-2.43</v>
       </c>
       <c r="F59" s="3">
-        <v>0.19376945522803352</v>
+        <v>0.17904261223547482</v>
       </c>
       <c r="G59" s="3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="H59" s="3">
-        <v>58.84</v>
+        <v>51.69</v>
       </c>
       <c r="I59" s="3">
-        <v>49.42</v>
+        <v>43.37</v>
       </c>
       <c r="J59" s="3">
-        <v>0.021752375824627218</v>
+        <v>0.02317032186491351</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="3">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="M59" s="3">
-        <v>0.21912388297600827</v>
+        <v>0.200368575430651</v>
       </c>
       <c r="N59" s="3">
-        <v>60.37974683544304</v>
+        <v>59.74683544303797</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>90</v>
       </c>
       <c r="P59" s="3">
-        <v>0.24</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
@@ -4379,43 +4382,43 @@
         <v>68.35443037974683</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.1255886970172684</v>
+        <v>-0.13029827315541603</v>
       </c>
       <c r="E60" s="1">
         <v>-0.23</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.16171986417457856</v>
+        <v>-0.1489477353062037</v>
       </c>
       <c r="G60" s="1">
         <v>0.38</v>
       </c>
       <c r="H60" s="1">
-        <v>37.43</v>
+        <v>38.66</v>
       </c>
       <c r="I60" s="1">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="J60" s="1">
-        <v>-0.01014368855251062</v>
+        <v>-0.009984339530045553</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="M60" s="1">
-        <v>-0.22721880252351334</v>
+        <v>-0.2090481770380639</v>
       </c>
       <c r="N60" s="1">
-        <v>36.45569620253164</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>91</v>
       </c>
       <c r="P60" s="1">
-        <v>-1.63</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4435,31 +4438,31 @@
         <v>-0.38</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.15140793649880074</v>
+        <v>-0.17099099367816528</v>
       </c>
       <c r="G61" s="3">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H61" s="3">
-        <v>47.17</v>
+        <v>42.52</v>
       </c>
       <c r="I61" s="3">
-        <v>10.62</v>
+        <v>8.1</v>
       </c>
       <c r="J61" s="3">
-        <v>-0.007013080663460716</v>
+        <v>-0.006484471124865406</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.15563367445679654</v>
+        <v>-0.1758378034952508</v>
       </c>
       <c r="N61" s="3">
-        <v>53.164556962025316</v>
+        <v>53.16455696202532</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>113</v>
@@ -4485,37 +4488,37 @@
         <v>-8.63</v>
       </c>
       <c r="F62" s="2">
-        <v>0.6801710267948219</v>
+        <v>0.7870039611746505</v>
       </c>
       <c r="G62" s="2">
-        <v>4.76</v>
+        <v>4.63</v>
       </c>
       <c r="H62" s="2">
-        <v>64.4</v>
+        <v>65.5</v>
       </c>
       <c r="I62" s="2">
-        <v>233.09</v>
+        <v>233.6</v>
       </c>
       <c r="J62" s="2">
-        <v>0.10546988394515601</v>
+        <v>0.10154333708964342</v>
       </c>
       <c r="K62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="M62" s="2">
-        <v>1.0773903948464263</v>
+        <v>1.1388823538950577</v>
       </c>
       <c r="N62" s="2">
-        <v>81.89873417721519</v>
+        <v>83.29113924050633</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>101</v>
       </c>
       <c r="P62" s="2">
-        <v>-1.53</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -4535,19 +4538,19 @@
         <v>-4.36</v>
       </c>
       <c r="F63" s="2">
-        <v>0.641250149266834</v>
+        <v>0.659813799317615</v>
       </c>
       <c r="G63" s="2">
         <v>2.03</v>
       </c>
       <c r="H63" s="2">
-        <v>75.55</v>
+        <v>73.08</v>
       </c>
       <c r="I63" s="2">
-        <v>140.43</v>
+        <v>135.38</v>
       </c>
       <c r="J63" s="2">
-        <v>0.08667502892899964</v>
+        <v>0.08759541191729123</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
@@ -4556,16 +4559,16 @@
         <v>198</v>
       </c>
       <c r="M63" s="2">
-        <v>0.7500629016852256</v>
+        <v>0.7596580815495761</v>
       </c>
       <c r="N63" s="2">
-        <v>78.10126582278481</v>
+        <v>78.48101265822785</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>103</v>
       </c>
       <c r="P63" s="2">
-        <v>-0.53</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -4585,37 +4588,37 @@
         <v>-0.69</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.0749174419428013</v>
+        <v>-0.15173270683304146</v>
       </c>
       <c r="G64" s="1">
         <v>0.31</v>
       </c>
       <c r="H64" s="1">
-        <v>58.94</v>
+        <v>49.18</v>
       </c>
       <c r="I64" s="1">
-        <v>3.59</v>
+        <v>0.53</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.008835651650888173</v>
+        <v>-0.007675355116232243</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.1478114217182287</v>
+        <v>-0.2186186823088213</v>
       </c>
       <c r="N64" s="1">
-        <v>48.10126582278482</v>
+        <v>47.46835443037975</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>94</v>
       </c>
       <c r="P64" s="1">
-        <v>-0.12</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -4635,37 +4638,37 @@
         <v>-0.19</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.16793335414486013</v>
+        <v>-0.12564894128578813</v>
       </c>
       <c r="G65" s="1">
         <v>1.02</v>
       </c>
       <c r="H65" s="1">
-        <v>42.78</v>
+        <v>48.71</v>
       </c>
       <c r="I65" s="1">
-        <v>-33.81</v>
+        <v>-30.99</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.008093631679428235</v>
+        <v>-0.011724288133944402</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-159</v>
+        <v>-183</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.16582048516586223</v>
+        <v>-0.12371021735895393</v>
       </c>
       <c r="N65" s="1">
-        <v>40.63291139240506</v>
+        <v>39.87341772151898</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>92</v>
       </c>
       <c r="P65" s="1">
-        <v>-2.52</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
@@ -4679,43 +4682,43 @@
         <v>55.69620253164557</v>
       </c>
       <c r="D66" s="3">
-        <v>7.102244389027433</v>
+        <v>7.266832917705736</v>
       </c>
       <c r="E66" s="3">
         <v>-0.9</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.08351768096202683</v>
+        <v>-0.04838973089937444</v>
       </c>
       <c r="G66" s="3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H66" s="3">
-        <v>48.96</v>
+        <v>50.19</v>
       </c>
       <c r="I66" s="3">
-        <v>-11.63</v>
+        <v>-11.09</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.0004928700426987416</v>
+        <v>-0.0007620642574330307</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="3">
-        <v>-45</v>
+        <v>-66</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.06767116361954262</v>
+        <v>-0.034818663411535056</v>
       </c>
       <c r="N66" s="3">
-        <v>50.63291139240506</v>
+        <v>50.75949367088608</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>95</v>
       </c>
       <c r="P66" s="3">
-        <v>-0.74</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
@@ -4735,37 +4738,37 @@
         <v>0.3</v>
       </c>
       <c r="F67" s="3">
-        <v>-0.17570917181145368</v>
+        <v>-0.20663102503993735</v>
       </c>
       <c r="G67" s="3">
         <v>0.33</v>
       </c>
       <c r="H67" s="3">
-        <v>44.24</v>
+        <v>39.62</v>
       </c>
       <c r="I67" s="3">
-        <v>3.35</v>
+        <v>1.35</v>
       </c>
       <c r="J67" s="3">
-        <v>-0.010622393879639721</v>
+        <v>-0.011090693921459435</v>
       </c>
       <c r="K67" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="3">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="M67" s="3">
-        <v>-0.2464902826078832</v>
+        <v>-0.271578276588883</v>
       </c>
       <c r="N67" s="3">
-        <v>60.253164556962034</v>
+        <v>59.74683544303798</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>104</v>
       </c>
       <c r="P67" s="3">
-        <v>-1.12</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -4785,37 +4788,37 @@
         <v>-0.07</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.2737584211342412</v>
+        <v>-0.2874281543757484</v>
       </c>
       <c r="G68" s="1">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H68" s="1">
-        <v>36.06</v>
+        <v>33.52</v>
       </c>
       <c r="I68" s="1">
-        <v>-13.93</v>
+        <v>-15.25</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.014554167016053075</v>
+        <v>-0.015387484507357942</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>-23</v>
+        <v>-48</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2219931311487927</v>
+        <v>-0.2408987801317276</v>
       </c>
       <c r="N68" s="1">
-        <v>36.835443037974684</v>
+        <v>36.45569620253164</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P68" s="1">
-        <v>-1.79</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -4829,43 +4832,43 @@
         <v>93.67088607594937</v>
       </c>
       <c r="D69" s="1">
-        <v>-0.47663551401869164</v>
+        <v>-0.47608576140736675</v>
       </c>
       <c r="E69" s="1">
         <v>1.57</v>
       </c>
       <c r="F69" s="1">
-        <v>-0.2235064032776204</v>
+        <v>-0.22580565225190932</v>
       </c>
       <c r="G69" s="1">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H69" s="1">
-        <v>36.33</v>
+        <v>33.16</v>
       </c>
       <c r="I69" s="1">
-        <v>-14.98</v>
+        <v>-16.82</v>
       </c>
       <c r="J69" s="1">
-        <v>-0.012176986886437771</v>
+        <v>-0.013238691678533204</v>
       </c>
       <c r="K69" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L69" s="1">
-        <v>-36</v>
+        <v>-43</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.23724005164110673</v>
+        <v>-0.23937671973974872</v>
       </c>
       <c r="N69" s="1">
-        <v>38.48101265822785</v>
+        <v>37.848101265822784</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>99</v>
       </c>
       <c r="P69" s="1">
-        <v>-0.7</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -4885,37 +4888,37 @@
         <v>-0.78</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.44028916275093244</v>
+        <v>-0.45495617366977387</v>
       </c>
       <c r="G70" s="1">
         <v>1.11</v>
       </c>
       <c r="H70" s="1">
-        <v>30.64</v>
+        <v>30.09</v>
       </c>
       <c r="I70" s="1">
-        <v>-32.84</v>
+        <v>-32.88</v>
       </c>
       <c r="J70" s="1">
-        <v>-0.036951733464152266</v>
+        <v>-0.03576131515339131</v>
       </c>
       <c r="K70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>-68</v>
+        <v>-93</v>
       </c>
       <c r="M70" s="1">
-        <v>-0.428668383366444</v>
+        <v>-0.44429319207218576</v>
       </c>
       <c r="N70" s="1">
-        <v>35.696202531645575</v>
+        <v>36.075949367088604</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>114</v>
       </c>
       <c r="P70" s="1">
-        <v>-1.02</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
@@ -4935,37 +4938,37 @@
         <v>0.16</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.28634058494607356</v>
+        <v>-0.257648719824491</v>
       </c>
       <c r="G71" s="1">
         <v>1.01</v>
       </c>
       <c r="H71" s="1">
-        <v>47.79</v>
+        <v>50.11</v>
       </c>
       <c r="I71" s="1">
-        <v>-7.91</v>
+        <v>-7.21</v>
       </c>
       <c r="J71" s="1">
-        <v>-0.012108627386982845</v>
+        <v>-0.01041135545749011</v>
       </c>
       <c r="K71" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="1">
-        <v>-31</v>
+        <v>-54</v>
       </c>
       <c r="M71" s="1">
-        <v>-0.2852841504565746</v>
+        <v>-0.2566793578610739</v>
       </c>
       <c r="N71" s="1">
-        <v>39.873417721518976</v>
+        <v>42.9113924050633</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>93</v>
       </c>
       <c r="P71" s="1">
-        <v>-0.67</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
@@ -4985,37 +4988,37 @@
         <v>-1.31</v>
       </c>
       <c r="F72" s="1">
-        <v>-0.30139290482719244</v>
+        <v>-0.30773563356932304</v>
       </c>
       <c r="G72" s="1">
         <v>1.14</v>
       </c>
       <c r="H72" s="1">
-        <v>39.3</v>
+        <v>33.96</v>
       </c>
       <c r="I72" s="1">
-        <v>-9.3</v>
+        <v>-11.92</v>
       </c>
       <c r="J72" s="1">
-        <v>-0.013369079063163274</v>
+        <v>-0.012895102685770758</v>
       </c>
       <c r="K72" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L72" s="1">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="M72" s="1">
-        <v>-0.28660282197420717</v>
+        <v>-0.29416456608148367</v>
       </c>
       <c r="N72" s="1">
-        <v>39.24050632911392</v>
+        <v>38.35443037974683</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>103</v>
       </c>
       <c r="P72" s="1">
-        <v>0.61</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
@@ -5035,31 +5038,31 @@
         <v>0.1</v>
       </c>
       <c r="F73" s="3">
-        <v>0.24304275004610662</v>
+        <v>0.2260761832650745</v>
       </c>
       <c r="G73" s="3">
         <v>1.17</v>
       </c>
       <c r="H73" s="3">
-        <v>63.2</v>
+        <v>62.34</v>
       </c>
       <c r="I73" s="3">
-        <v>42.78</v>
+        <v>42.04</v>
       </c>
       <c r="J73" s="3">
-        <v>0.03311741649197117</v>
+        <v>0.03167383159955737</v>
       </c>
       <c r="K73" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M73" s="3">
-        <v>0.26100213636758873</v>
+        <v>0.2425553366431652</v>
       </c>
       <c r="N73" s="3">
-        <v>65.82278481012659</v>
+        <v>66.07594936708861</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>103</v>
@@ -5083,7 +5086,7 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="3">
-        <v>0.171791660070794</v>
+        <v>0.16119109676979138</v>
       </c>
       <c r="G74" s="3">
         <v>0.79</v>
@@ -5092,22 +5095,22 @@
         <v>82.84</v>
       </c>
       <c r="I74" s="3">
-        <v>32.17</v>
+        <v>31.87</v>
       </c>
       <c r="J74" s="3">
-        <v>0.02173636008250081</v>
+        <v>0.022037295034327584</v>
       </c>
       <c r="K74" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M74" s="3">
-        <v>0.1496065357913161</v>
+        <v>0.1408344955380323</v>
       </c>
       <c r="N74" s="3">
-        <v>64.81012658227847</v>
+        <v>65.56962025316456</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>117</v>
@@ -5131,31 +5134,31 @@
         <v>-0.71</v>
       </c>
       <c r="F75" s="3">
-        <v>0.09844585638263409</v>
+        <v>0.07659172329880896</v>
       </c>
       <c r="G75" s="3">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H75" s="3">
-        <v>62.95</v>
+        <v>59.46</v>
       </c>
       <c r="I75" s="3">
-        <v>16.76</v>
+        <v>14.74</v>
       </c>
       <c r="J75" s="3">
-        <v>0.005947979306673231</v>
+        <v>0.005399889390566219</v>
       </c>
       <c r="K75" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L75" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M75" s="3">
-        <v>0.09422011842463829</v>
+        <v>0.07368363740855766</v>
       </c>
       <c r="N75" s="3">
-        <v>58.734177215189874</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>103</v>
@@ -5163,52 +5166,52 @@
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="1">
         <v>2.05</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="1">
         <v>48.10126582278481</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="1">
         <v>0.7170731707317075</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="1">
         <v>2.63</v>
       </c>
-      <c r="F76" s="3">
-        <v>0.02756734714612362</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="F76" s="1">
+        <v>-0.035469744789771454</v>
+      </c>
+      <c r="G76" s="1">
         <v>0.72</v>
       </c>
-      <c r="H76" s="3">
-        <v>57.58</v>
-      </c>
-      <c r="I76" s="3">
-        <v>18.15</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0.018042502596555904</v>
-      </c>
-      <c r="K76" s="3" t="b">
+      <c r="H76" s="1">
+        <v>49.42</v>
+      </c>
+      <c r="I76" s="1">
+        <v>12.88</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0.017557388392607762</v>
+      </c>
+      <c r="K76" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L76" s="3">
-        <v>5</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-0.0020128185598469184</v>
-      </c>
-      <c r="N76" s="3">
-        <v>50.12658227848102</v>
-      </c>
-      <c r="O76" s="3" t="s">
+      <c r="L76" s="1">
+        <v>4</v>
+      </c>
+      <c r="M76" s="1">
+        <v>-0.06261187976545024</v>
+      </c>
+      <c r="N76" s="1">
+        <v>48.86075949367089</v>
+      </c>
+      <c r="O76" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P76" s="3"/>
+      <c r="P76" s="1"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
@@ -5227,31 +5230,31 @@
         <v>-0.34</v>
       </c>
       <c r="F77" s="3">
-        <v>0.0154903655561002</v>
+        <v>-0.004879866713475789</v>
       </c>
       <c r="G77" s="3">
         <v>0.98</v>
       </c>
       <c r="H77" s="3">
-        <v>66.8</v>
+        <v>58.35</v>
       </c>
       <c r="I77" s="3">
-        <v>11.55</v>
+        <v>9.21</v>
       </c>
       <c r="J77" s="3">
-        <v>0.008300076097574285</v>
+        <v>0.007734524845225627</v>
       </c>
       <c r="K77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M77" s="3">
-        <v>0.013377496577102299</v>
+        <v>-0.006818590640309985</v>
       </c>
       <c r="N77" s="3">
-        <v>62.78481012658227</v>
+        <v>61.64556962025317</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>88</v>
@@ -5269,43 +5272,43 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D78" s="3">
-        <v>-0.6414950419527079</v>
+        <v>-0.660564454614798</v>
       </c>
       <c r="E78" s="3">
         <v>0.57</v>
       </c>
       <c r="F78" s="3">
-        <v>0.13994188449510106</v>
+        <v>0.15335529684028812</v>
       </c>
       <c r="G78" s="3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H78" s="3">
-        <v>73.36</v>
+        <v>69.85</v>
       </c>
       <c r="I78" s="3">
-        <v>36.83</v>
+        <v>35.04</v>
       </c>
       <c r="J78" s="3">
-        <v>0.026968687612936203</v>
+        <v>0.02697399814603973</v>
       </c>
       <c r="K78" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="M78" s="3">
-        <v>0.1674091812220737</v>
+        <v>0.17758934592571562</v>
       </c>
       <c r="N78" s="3">
-        <v>60.50632911392405</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>102</v>
       </c>
       <c r="P78" s="3">
-        <v>-1.14</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
@@ -5319,43 +5322,43 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="3">
-        <v>2.420195439739414</v>
+        <v>2.6156351791530943</v>
       </c>
       <c r="E79" s="3">
         <v>0.82</v>
       </c>
       <c r="F79" s="3">
-        <v>0.4314015762005562</v>
+        <v>0.4334131898942318</v>
       </c>
       <c r="G79" s="3">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="H79" s="3">
-        <v>87.47</v>
+        <v>88.46</v>
       </c>
       <c r="I79" s="3">
-        <v>51.22</v>
+        <v>54.22</v>
       </c>
       <c r="J79" s="3">
-        <v>0.02780205335194993</v>
+        <v>0.032420325485079365</v>
       </c>
       <c r="K79" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L79" s="3">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="M79" s="3">
-        <v>0.4240065347740636</v>
+        <v>0.43050510400398045</v>
       </c>
       <c r="N79" s="3">
-        <v>64.55696202531645</v>
+        <v>66.07594936708861</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>109</v>
       </c>
       <c r="P79" s="3">
-        <v>2.91</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
@@ -5369,37 +5372,37 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="3">
-        <v>0.8119266055045871</v>
+        <v>0.8211009174311926</v>
       </c>
       <c r="E80" s="3">
         <v>5.52</v>
       </c>
       <c r="F80" s="3">
-        <v>1.0797669226250077</v>
+        <v>0.9500398162459049</v>
       </c>
       <c r="G80" s="3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H80" s="3">
-        <v>66.73</v>
+        <v>62.97</v>
       </c>
       <c r="I80" s="3">
-        <v>69.04</v>
+        <v>64.4</v>
       </c>
       <c r="J80" s="3">
-        <v>0.058703521846975554</v>
+        <v>0.05298790653590615</v>
       </c>
       <c r="K80" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M80" s="3">
-        <v>1.0808233571145067</v>
+        <v>0.9519785401727392</v>
       </c>
       <c r="N80" s="3">
-        <v>68.8607594936709</v>
+        <v>69.746835443038</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>96</v>
@@ -5422,7 +5425,7 @@
         <v>124</v>
       </c>
       <c r="B1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5430,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41.89873417721519</v>
+        <v>45.18987341772152</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5438,7 +5441,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>76.20253164556962</v>
+        <v>75.69620253164557</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5446,7 +5449,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>31.0126582278481</v>
+        <v>33.79746835443037</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5454,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>61.265822784810126</v>
+        <v>59.74683544303797</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5462,7 +5465,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>38.734177215189874</v>
+        <v>37.594936708860764</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5470,7 +5473,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>64.68354430379746</v>
+        <v>63.54430379746835</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5478,7 +5481,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>66.07594936708861</v>
+        <v>66.45569620253164</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5486,7 +5489,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>49.11392405063291</v>
+        <v>48.10126582278481</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5494,7 +5497,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.22784810126583</v>
+        <v>46.582278481012665</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5502,7 +5505,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>53.79746835443038</v>
+        <v>56.07594936708861</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5510,7 +5513,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>40.00000000000001</v>
+        <v>41.898734177215196</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5518,7 +5521,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>28.734177215189874</v>
+        <v>26.962025316455698</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -5526,7 +5529,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>53.79746835443038</v>
+        <v>55.569620253164565</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -5534,7 +5537,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>69.36708860759494</v>
+        <v>69.11392405063292</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5542,7 +5545,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>40</v>
+        <v>42.40506329113924</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5550,7 +5553,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>24.55696202531646</v>
+        <v>24.55696202531645</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5558,7 +5561,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>48.22784810126582</v>
+        <v>47.08860759493671</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5566,7 +5569,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>52.78481012658228</v>
+        <v>54.17721518987342</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5574,7 +5577,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37.59493670886076</v>
+        <v>37.21518987341772</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -5582,7 +5585,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>55.69620253164557</v>
+        <v>62.65822784810127</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -5590,7 +5593,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>41.265822784810126</v>
+        <v>40.50632911392404</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -5598,7 +5601,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>45.063291139240505</v>
+        <v>45.56962025316456</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -5606,7 +5609,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>31.012658227848103</v>
+        <v>28.9873417721519</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5614,7 +5617,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>27.9746835443038</v>
+        <v>27.341772151898734</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -5622,7 +5625,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>41.139240506329116</v>
+        <v>39.367088607594944</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -5638,7 +5641,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>34.30379746835443</v>
+        <v>33.67088607594936</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -5646,7 +5649,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>41.645569620253156</v>
+        <v>41.518987341772146</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5654,7 +5657,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>64.17721518987342</v>
+        <v>63.037974683544306</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -5662,7 +5665,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>68.9873417721519</v>
+        <v>68.48101265822785</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -5670,7 +5673,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>35.31645569620254</v>
+        <v>34.810126582278485</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -5678,7 +5681,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>50</v>
+        <v>52.65822784810126</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -5686,7 +5689,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>61.139240506329116</v>
+        <v>61.01265822784811</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -5694,7 +5697,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>32.911392405063296</v>
+        <v>33.037974683544306</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5702,7 +5705,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>40.12658227848101</v>
+        <v>38.35443037974683</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -5710,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>38.9873417721519</v>
+        <v>38.48101265822785</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -5718,7 +5721,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>64.43037974683544</v>
+        <v>64.81012658227849</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -5726,7 +5729,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>57.46835443037974</v>
+        <v>56.45569620253165</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -5734,7 +5737,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>44.68354430379747</v>
+        <v>37.34177215189874</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -5742,7 +5745,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>43.79746835443038</v>
+        <v>44.55696202531645</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -5750,7 +5753,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>43.41772151898734</v>
+        <v>41.64556962025316</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5758,7 +5761,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>50.379746835443036</v>
+        <v>53.67088607594937</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5766,7 +5769,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>38.73417721518987</v>
+        <v>39.99999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -5774,7 +5777,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>61.51898734177216</v>
+        <v>62.65822784810127</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -5782,7 +5785,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>51.77215189873418</v>
+        <v>50.12658227848101</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5790,7 +5793,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>38.734177215189874</v>
+        <v>38.9873417721519</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5798,7 +5801,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>69.87341772151898</v>
+        <v>71.13924050632912</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -5806,7 +5809,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>74.55696202531647</v>
+        <v>73.0379746835443</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -5814,7 +5817,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>38.607594936708864</v>
+        <v>38.22784810126583</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -5822,7 +5825,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>33.67088607594937</v>
+        <v>32.911392405063296</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5830,7 +5833,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>66.83544303797468</v>
+        <v>65.94936708860759</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5838,7 +5841,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>48.481012658227854</v>
+        <v>47.46835443037975</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -5846,7 +5849,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>66.70886075949367</v>
+        <v>67.21518987341771</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -5854,7 +5857,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>46.9620253164557</v>
+        <v>46.962025316455694</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -5862,7 +5865,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>45.82278481012658</v>
+        <v>45.18987341772152</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5870,7 +5873,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>81.26582278481013</v>
+        <v>80.63291139240506</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5881,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>65.44303797468355</v>
+        <v>64.43037974683544</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5886,7 +5889,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>60.37974683544304</v>
+        <v>59.74683544303797</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -5894,7 +5897,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>36.45569620253164</v>
+        <v>37.59493670886076</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -5902,7 +5905,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>53.164556962025316</v>
+        <v>53.16455696202532</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -5910,7 +5913,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>81.89873417721519</v>
+        <v>83.29113924050633</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -5918,7 +5921,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>78.10126582278481</v>
+        <v>78.48101265822785</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -5926,7 +5929,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>48.10126582278482</v>
+        <v>47.46835443037975</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -5934,7 +5937,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>40.63291139240506</v>
+        <v>39.87341772151898</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5942,7 +5945,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>50.63291139240506</v>
+        <v>50.75949367088608</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -5950,7 +5953,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>60.253164556962034</v>
+        <v>59.74683544303798</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -5958,7 +5961,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>36.835443037974684</v>
+        <v>36.45569620253164</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5966,7 +5969,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>38.48101265822785</v>
+        <v>37.848101265822784</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -5974,7 +5977,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>35.696202531645575</v>
+        <v>36.075949367088604</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -5982,7 +5985,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>39.873417721518976</v>
+        <v>42.9113924050633</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -5990,7 +5993,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>39.24050632911392</v>
+        <v>38.35443037974683</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -5998,7 +6001,7 @@
         <v>115</v>
       </c>
       <c r="B73">
-        <v>65.82278481012659</v>
+        <v>66.07594936708861</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -6006,7 +6009,7 @@
         <v>116</v>
       </c>
       <c r="B74">
-        <v>64.81012658227847</v>
+        <v>65.56962025316456</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -6014,7 +6017,7 @@
         <v>118</v>
       </c>
       <c r="B75">
-        <v>58.734177215189874</v>
+        <v>59.620253164556964</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -6022,7 +6025,7 @@
         <v>119</v>
       </c>
       <c r="B76">
-        <v>50.12658227848102</v>
+        <v>48.86075949367089</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -6030,7 +6033,7 @@
         <v>120</v>
       </c>
       <c r="B77">
-        <v>62.78481012658227</v>
+        <v>61.64556962025317</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -6038,7 +6041,7 @@
         <v>121</v>
       </c>
       <c r="B78">
-        <v>60.50632911392405</v>
+        <v>60.88607594936709</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -6046,7 +6049,7 @@
         <v>122</v>
       </c>
       <c r="B79">
-        <v>64.55696202531645</v>
+        <v>66.07594936708861</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -6054,7 +6057,7 @@
         <v>123</v>
       </c>
       <c r="B80">
-        <v>68.8607594936709</v>
+        <v>69.746835443038</v>
       </c>
     </row>
   </sheetData>
@@ -6073,10 +6076,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6084,7 +6087,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>107</v>
@@ -6095,10 +6098,10 @@
         <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6106,10 +6109,10 @@
         <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -6117,10 +6120,10 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -6128,82 +6131,82 @@
         <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -6222,15 +6225,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>107</v>
@@ -6238,98 +6241,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -6348,10 +6351,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6359,7 +6362,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>107</v>
@@ -6370,10 +6373,10 @@
         <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6381,90 +6384,90 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6483,10 +6486,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6494,7 +6497,7 @@
         <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
         <v>107</v>
@@ -6502,106 +6505,106 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6617,16 +6620,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6634,209 +6637,209 @@
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" t="s">
         <v>177</v>
-      </c>
-      <c r="B3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" t="s">
         <v>189</v>
       </c>
-      <c r="B8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" t="s">
-        <v>188</v>
-      </c>
       <c r="D8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="7" name="Nasdaq" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="SP_100" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Composite_Formula" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="SignalsTriggered" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="229">
   <si>
     <t>Ticker</t>
   </si>
@@ -240,13 +241,13 @@
     <t>EPS_TTM</t>
   </si>
   <si>
-    <t>EPS_Percentile_In_Universe</t>
-  </si>
-  <si>
-    <t>EPS_Fwd_Grwth_Trnd</t>
-  </si>
-  <si>
-    <t>Institutional_Accumulation_%</t>
+    <t>EPS_Percentile</t>
+  </si>
+  <si>
+    <t>EPS_Growth</t>
+  </si>
+  <si>
+    <t>Inst_Accumulation</t>
   </si>
   <si>
     <t>Alpha_63D</t>
@@ -258,24 +259,36 @@
     <t>RSI_14Day</t>
   </si>
   <si>
-    <t>SMA200_Dist_%</t>
+    <t>SMA200_Dist</t>
   </si>
   <si>
     <t>MA_Slope_50</t>
   </si>
   <si>
-    <t>Vol Expansion</t>
-  </si>
-  <si>
-    <t>LastQRtr_InstActivity</t>
+    <t>Volume_Expansion</t>
+  </si>
+  <si>
+    <t>Net_Inst</t>
   </si>
   <si>
     <t>RS_vs_SP100</t>
   </si>
   <si>
+    <t>Return_63D</t>
+  </si>
+  <si>
+    <t>RS_Rank</t>
+  </si>
+  <si>
+    <t>Drawdown_%</t>
+  </si>
+  <si>
     <t>Composite_Score</t>
   </si>
   <si>
+    <t>New_Composite_Score</t>
+  </si>
+  <si>
     <t>Earnings_Date</t>
   </si>
   <si>
@@ -294,7 +307,7 @@
     <t>2026-04-22</t>
   </si>
   <si>
-    <t>2026-04-16</t>
+    <t>2027-04-16</t>
   </si>
   <si>
     <t>2026-05-20</t>
@@ -396,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-15</t>
+    <t>2026-05-16</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -546,46 +559,64 @@
     <t>Source</t>
   </si>
   <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>Earnings quality vs peers</t>
+    <t>EPS Percentile</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Earnings strength vs peers</t>
   </si>
   <si>
     <t>Finviz</t>
   </si>
   <si>
-    <t>P(EPS_Fwd_Growth)</t>
-  </si>
-  <si>
-    <t>Earnings acceleration</t>
-  </si>
-  <si>
-    <t>P(MA_Slope_50)</t>
+    <t>EPS Growth Trend</t>
+  </si>
+  <si>
+    <t>Forward growth momentum</t>
+  </si>
+  <si>
+    <t>Return 63D</t>
   </si>
   <si>
     <t>20%</t>
   </si>
   <si>
-    <t>Medium-term price trend</t>
-  </si>
-  <si>
-    <t>Yahoo Finance prices</t>
-  </si>
-  <si>
-    <t>P(RSI_14)</t>
+    <t>Price momentum</t>
+  </si>
+  <si>
+    <t>Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Relative Strength</t>
   </si>
   <si>
     <t>10%</t>
   </si>
   <si>
-    <t>Short-term momentum strength</t>
-  </si>
-  <si>
-    <t>P(SMA200_Dist)</t>
-  </si>
-  <si>
-    <t>Long-term trend confirmation</t>
+    <t>Market outperformance</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
+    <t>MA Slope</t>
+  </si>
+  <si>
+    <t>Trend confirmation</t>
+  </si>
+  <si>
+    <t>Drawdown</t>
+  </si>
+  <si>
+    <t>-10%</t>
+  </si>
+  <si>
+    <t>Risk penalty</t>
+  </si>
+  <si>
+    <t>Price history</t>
   </si>
   <si>
     <t/>
@@ -594,7 +625,7 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>Composite = 0.30 × P(EPS_Univ) + 0.30 × P(Fwd_Growth) + 0.20 × P(MA_Slope_50) + 0.10 × P(RSI_14) + 0.10 × P(SMA200_Dist)</t>
+    <t>Composite = Growth + Momentum + Strength + Trend - Risk</t>
   </si>
   <si>
     <t>Score Range</t>
@@ -627,10 +658,55 @@
     <t>Consider reducing position</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>All P(x) values are percentile ranks within the current universe (0-100). Score is relative, not absolute.</t>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Triggers</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Multi-Day Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming</t>
   </si>
 </sst>
 </file>
@@ -660,17 +736,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1275,6 +1351,578 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <v>72.02531645569621</v>
+      </c>
+      <c r="C2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3">
+        <v>67.02531645569621</v>
+      </c>
+      <c r="C3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>66.89873417721519</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5">
+        <v>65.37974683544304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>65.31645569620254</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7">
+        <v>63.60759493670886</v>
+      </c>
+      <c r="C7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>62.594936708860764</v>
+      </c>
+      <c r="C8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>61.962025316455694</v>
+      </c>
+      <c r="C9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10">
+        <v>61.51898734177215</v>
+      </c>
+      <c r="C10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>60.9493670886076</v>
+      </c>
+      <c r="C11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12">
+        <v>59.24050632911393</v>
+      </c>
+      <c r="C12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13">
+        <v>57.40506329113924</v>
+      </c>
+      <c r="C13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>57.34177215189874</v>
+      </c>
+      <c r="C14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15">
+        <v>56.898734177215196</v>
+      </c>
+      <c r="C15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>55.25316455696202</v>
+      </c>
+      <c r="C16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>55.12658227848102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <v>54.68354430379747</v>
+      </c>
+      <c r="C18" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="C19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20">
+        <v>54.30379746835443</v>
+      </c>
+      <c r="C20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21">
+        <v>54.24050632911392</v>
+      </c>
+      <c r="C21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
+        <v>52.34177215189874</v>
+      </c>
+      <c r="C22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23">
+        <v>51.13924050632911</v>
+      </c>
+      <c r="C23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>50.949367088607595</v>
+      </c>
+      <c r="C24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25">
+        <v>50.50632911392405</v>
+      </c>
+      <c r="C25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26">
+        <v>47.34177215189873</v>
+      </c>
+      <c r="C26" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>47.21518987341773</v>
+      </c>
+      <c r="C27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28">
+        <v>46.582278481012665</v>
+      </c>
+      <c r="C28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>46.32911392405064</v>
+      </c>
+      <c r="C29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30">
+        <v>44.55696202531645</v>
+      </c>
+      <c r="C30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31">
+        <v>44.11392405063291</v>
+      </c>
+      <c r="C31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="C32" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="C33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="C34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35">
+        <v>41.39240506329114</v>
+      </c>
+      <c r="C35" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36">
+        <v>41.329113924050645</v>
+      </c>
+      <c r="C36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37">
+        <v>39.367088607594944</v>
+      </c>
+      <c r="C37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>37.84810126582279</v>
+      </c>
+      <c r="C38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>37.72151898734177</v>
+      </c>
+      <c r="C39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40">
+        <v>37.65822784810127</v>
+      </c>
+      <c r="C40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41">
+        <v>36.45569620253165</v>
+      </c>
+      <c r="C41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42">
+        <v>36.32911392405063</v>
+      </c>
+      <c r="C42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43">
+        <v>35.9493670886076</v>
+      </c>
+      <c r="C43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44">
+        <v>35.443037974683534</v>
+      </c>
+      <c r="C44" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>33.9873417721519</v>
+      </c>
+      <c r="C45" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46">
+        <v>33.924050632911396</v>
+      </c>
+      <c r="C46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47">
+        <v>33.22784810126582</v>
+      </c>
+      <c r="C47" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48">
+        <v>33.101265822784804</v>
+      </c>
+      <c r="C48" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49">
+        <v>32.278481012658226</v>
+      </c>
+      <c r="C49" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50">
+        <v>31.89873417721519</v>
+      </c>
+      <c r="C50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51">
+        <v>30.696202531645564</v>
+      </c>
+      <c r="C51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
@@ -1418,10 +2066,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1470,8 +2118,20 @@
       <c r="P1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S1" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1506,22 +2166,34 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M2" s="1">
         <v>-0.04389366407237705</v>
       </c>
       <c r="N2" s="1">
-        <v>45.18987341772152</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>87</v>
+        <v>6.3792532269333</v>
+      </c>
+      <c r="O2" s="1">
+        <v>53.16455696202531</v>
       </c>
       <c r="P2" s="1">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15.687871758897787</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>44.810126582278485</v>
+      </c>
+      <c r="R2" s="1">
+        <v>35.9493670886076</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T2" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1556,122 +2228,158 @@
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M3" s="2">
         <v>0.9379437048780217</v>
       </c>
       <c r="N3" s="2">
+        <v>104.56299012197317</v>
+      </c>
+      <c r="O3" s="2">
+        <v>96.20253164556962</v>
+      </c>
+      <c r="P3" s="2">
+        <v>26.467189489392297</v>
+      </c>
+      <c r="Q3" s="2">
         <v>75.69620253164557</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="P3" s="2">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="R3" s="2">
+        <v>65.31645569620254</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>-3.95</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>6.329113924050633</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="3">
         <v>9.865822784810128</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="3">
         <v>2.62</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>-0.2535364508958835</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="3">
         <v>1.1</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="3">
         <v>58.05</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="3">
         <v>-22.73</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="3">
         <v>-0.011052941902859758</v>
       </c>
-      <c r="K4" s="1" t="b">
+      <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L4" s="1">
-        <v>-72</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="L4" s="3">
+        <v>-88</v>
+      </c>
+      <c r="M4" s="3">
         <v>-0.24384283126171247</v>
       </c>
-      <c r="N4" s="1">
-        <v>33.79746835443037</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="1">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="N4" s="3">
+        <v>-13.615663492000246</v>
+      </c>
+      <c r="O4" s="3">
+        <v>16.455696202531644</v>
+      </c>
+      <c r="P4" s="3">
+        <v>48.360550359989794</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>33.417721518987335</v>
+      </c>
+      <c r="R4" s="3">
+        <v>15.126582278481017</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="1">
         <v>1.09</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>43.037974683544306</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>23.917431192660548</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="1">
         <v>0.63</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="1">
         <v>-0.1747058861985029</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="1">
         <v>1.81</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>57.96</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="1">
         <v>3.64</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="1">
         <v>0.009369255969228586</v>
       </c>
-      <c r="K5" s="3" t="b">
+      <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="3">
-        <v>-46</v>
-      </c>
-      <c r="M5" s="3">
+      <c r="L5" s="1">
+        <v>-81</v>
+      </c>
+      <c r="M5" s="1">
         <v>-0.09618756716171784</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="1">
+        <v>1.1498629179992155</v>
+      </c>
+      <c r="O5" s="1">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="P5" s="1">
+        <v>29.766948563835548</v>
+      </c>
+      <c r="Q5" s="1">
         <v>59.74683544303797</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R5" s="1">
+        <v>43.670886075949376</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T5" s="1">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1706,122 +2414,158 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="M6" s="1">
         <v>0.024354827904717435</v>
       </c>
       <c r="N6" s="1">
-        <v>37.594936708860764</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>91</v>
+        <v>13.204102424642736</v>
+      </c>
+      <c r="O6" s="1">
+        <v>63.29113924050633</v>
       </c>
       <c r="P6" s="1">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+        <v>20.72548824337846</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>37.21518987341772</v>
+      </c>
+      <c r="R6" s="1">
+        <v>41.39240506329114</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" s="1">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>4.9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>58.22784810126582</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>6.293877551020408</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>0.14</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>0.002710766112608426</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>2.26</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>64.66</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>21.16</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>0.023430570277173587</v>
       </c>
-      <c r="K7" s="3" t="b">
+      <c r="K7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>0.12485037350316297</v>
       </c>
-      <c r="N7" s="3">
-        <v>63.54430379746835</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="N7" s="2">
+        <v>23.2536569844873</v>
+      </c>
+      <c r="O7" s="2">
+        <v>73.41772151898735</v>
+      </c>
+      <c r="P7" s="2">
+        <v>15.539987609451147</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>63.16455696202531</v>
+      </c>
+      <c r="R7" s="2">
+        <v>55.12658227848102</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>13.24</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>86.07594936708861</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>-0.012084592145015116</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>0.43</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>0.2685989729401681</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>0.66</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>76.94</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>22.89</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>0.03334742657966023</v>
       </c>
-      <c r="K8" s="3" t="b">
+      <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L8" s="3">
-        <v>-191</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="L8" s="2">
+        <v>-211</v>
+      </c>
+      <c r="M8" s="2">
         <v>0.2356406661839867</v>
       </c>
-      <c r="N8" s="3">
-        <v>66.45569620253164</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P8" s="3">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>34.33268625256967</v>
+      </c>
+      <c r="O8" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="P8" s="2">
+        <v>27.294677507005353</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>66.07594936708861</v>
+      </c>
+      <c r="R8" s="2">
+        <v>55.25316455696202</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T8" s="2">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1856,22 +2600,34 @@
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="M9" s="1">
         <v>-0.08805297391453037</v>
       </c>
       <c r="N9" s="1">
+        <v>1.9633222427179662</v>
+      </c>
+      <c r="O9" s="1">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P9" s="1">
+        <v>34.04748479877408</v>
+      </c>
+      <c r="Q9" s="1">
         <v>48.10126582278481</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="P9" s="1">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R9" s="1">
+        <v>40.56962025316455</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T9" s="1">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1882,7 +2638,7 @@
         <v>67.08860759493672</v>
       </c>
       <c r="D10" s="1">
-        <v>0.4912</v>
+        <v>0.49919999999999987</v>
       </c>
       <c r="E10" s="1">
         <v>1.07</v>
@@ -1906,272 +2662,344 @@
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-128</v>
+        <v>-133</v>
       </c>
       <c r="M10" s="1">
         <v>-0.1335752035161627</v>
       </c>
       <c r="N10" s="1">
-        <v>46.582278481012665</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>95</v>
+        <v>-2.588900717445275</v>
+      </c>
+      <c r="O10" s="1">
+        <v>41.77215189873418</v>
       </c>
       <c r="P10" s="1">
-        <v>-3.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+        <v>20.24508080818123</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>46.20253164556962</v>
+      </c>
+      <c r="R10" s="1">
+        <v>37.59493670886076</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T10" s="1">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>-1.36</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>12.658227848101266</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="1">
         <v>31.911764705882348</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1">
         <v>8.3</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="1">
         <v>0.12533555255876536</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="1">
         <v>0.82</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="1">
         <v>66.24</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="1">
         <v>8.13</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="1">
         <v>0.020811267204622307</v>
       </c>
-      <c r="K11" s="3" t="b">
+      <c r="K11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L11" s="3">
-        <v>19</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="L11" s="1">
+        <v>24</v>
+      </c>
+      <c r="M11" s="1">
         <v>0.10788703721725756</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="1">
+        <v>21.55732335589675</v>
+      </c>
+      <c r="O11" s="1">
+        <v>70.88607594936708</v>
+      </c>
+      <c r="P11" s="1">
+        <v>23.11654999559394</v>
+      </c>
+      <c r="Q11" s="1">
         <v>56.07594936708861</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P11" s="3">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="R11" s="1">
+        <v>47.21518987341773</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>-0.34</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>20.253164556962027</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="3">
         <v>65.70588235294117</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="3">
         <v>-0.32</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="3">
         <v>-0.2905302085040573</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="3">
         <v>0.83</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="3">
         <v>52.17</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="3">
         <v>-34.67</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="3">
         <v>-0.011095628644533537</v>
       </c>
-      <c r="K12" s="1" t="b">
+      <c r="K12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
-        <v>-25</v>
-      </c>
-      <c r="M12" s="1">
+      <c r="L12" s="3">
+        <v>-44</v>
+      </c>
+      <c r="M12" s="3">
         <v>-0.307009361882148</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="3">
+        <v>-19.932316554043805</v>
+      </c>
+      <c r="O12" s="3">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="P12" s="3">
+        <v>49.40073075603063</v>
+      </c>
+      <c r="Q12" s="3">
         <v>41.898734177215196</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P12" s="1">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="R12" s="3">
+        <v>22.341772151898734</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>0.02</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>29.11392405063291</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>-1653.5</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>2.73</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>-0.24695705804821247</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>1.42</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <v>46.37</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <v>-1.23</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>-0.0006453714211657933</v>
       </c>
-      <c r="K13" s="4" t="b">
+      <c r="K13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13" s="3">
+        <v>12</v>
+      </c>
+      <c r="M13" s="3">
+        <v>-0.20624385558469427</v>
+      </c>
+      <c r="N13" s="3">
+        <v>-9.85576592429843</v>
+      </c>
+      <c r="O13" s="3">
+        <v>27.848101265822784</v>
+      </c>
+      <c r="P13" s="3">
+        <v>39.74359086324119</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>26.962025316455698</v>
+      </c>
+      <c r="R13" s="3">
+        <v>12.72151898734177</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T13" s="3">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="C14" s="1">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="D14" s="1">
+        <v>7.580152671755725</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-0.12133656204260415</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="H14" s="1">
+        <v>59.72</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-2.81</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.008497241964348224</v>
+      </c>
+      <c r="K14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>13</v>
+      </c>
+      <c r="M14" s="1">
+        <v>-0.15914167861587103</v>
+      </c>
+      <c r="N14" s="1">
+        <v>-5.145548227416105</v>
+      </c>
+      <c r="O14" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P14" s="1">
+        <v>33.10300785656511</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>55.18987341772152</v>
+      </c>
+      <c r="R14" s="1">
+        <v>36.45569620253165</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="T14" s="1">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="4">
-        <v>-0.20624385558469427</v>
-      </c>
-      <c r="N13" s="4">
-        <v>26.962025316455698</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P13" s="4">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3">
-        <v>1.31</v>
-      </c>
-      <c r="C14" s="3">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="D14" s="3">
-        <v>7.580152671755725</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-0.12133656204260415</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.61</v>
-      </c>
-      <c r="H14" s="3">
-        <v>59.72</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-2.81</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0.008497241964348224</v>
-      </c>
-      <c r="K14" s="3" t="b">
+      <c r="B15" s="2">
+        <v>-0.63</v>
+      </c>
+      <c r="C15" s="2">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="D15" s="2">
+        <v>62.85714285714286</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5.78</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1.098693544416193</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2.22</v>
+      </c>
+      <c r="H15" s="2">
+        <v>62.25</v>
+      </c>
+      <c r="I15" s="2">
+        <v>142.85</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.11891077311217498</v>
+      </c>
+      <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>13</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-0.15914167861587103</v>
-      </c>
-      <c r="N14" s="3">
-        <v>55.569620253164565</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P14" s="3">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3">
-        <v>-0.63</v>
-      </c>
-      <c r="C15" s="3">
-        <v>18.9873417721519</v>
-      </c>
-      <c r="D15" s="3">
-        <v>62.85714285714286</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5.78</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1.098693544416193</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2.22</v>
-      </c>
-      <c r="H15" s="3">
-        <v>62.25</v>
-      </c>
-      <c r="I15" s="3">
-        <v>142.85</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0.11891077311217498</v>
-      </c>
-      <c r="K15" s="3" t="b">
+      <c r="L15" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1.2169557039530792</v>
+      </c>
+      <c r="N15" s="2">
+        <v>132.4641900294789</v>
+      </c>
+      <c r="O15" s="2">
+        <v>100</v>
+      </c>
+      <c r="P15" s="2">
+        <v>24.171577948970977</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>69.11392405063292</v>
+      </c>
+      <c r="R15" s="2">
+        <v>61.962025316455694</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="3">
-        <v>188</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1.2169557039530792</v>
-      </c>
-      <c r="N15" s="3">
-        <v>69.11392405063292</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2206,172 +3034,220 @@
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M16" s="1">
         <v>0.04395661815610019</v>
       </c>
       <c r="N16" s="1">
-        <v>42.40506329113924</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>100</v>
+        <v>15.164281449781011</v>
+      </c>
+      <c r="O16" s="1">
+        <v>65.82278481012658</v>
       </c>
       <c r="P16" s="1">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+        <v>30.2515696939809</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>42.0253164556962</v>
+      </c>
+      <c r="R16" s="1">
+        <v>37.65822784810127</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T16" s="1">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>-6.21</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>3.79746835443038</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>4.355877616747182</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>4.89</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>-0.2643194481130663</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="3">
         <v>1.71</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="3">
         <v>40.67</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="3">
         <v>-13.46</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="3">
         <v>-0.014498611276431882</v>
       </c>
-      <c r="K17" s="4" t="b">
+      <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="4">
-        <v>19</v>
-      </c>
-      <c r="M17" s="4">
+      <c r="L17" s="3">
+        <v>22</v>
+      </c>
+      <c r="M17" s="3">
         <v>-0.19549474871045225</v>
       </c>
-      <c r="N17" s="4">
-        <v>24.55696202531645</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P17" s="4">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="N17" s="3">
+        <v>-8.780855236874228</v>
+      </c>
+      <c r="O17" s="3">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="P17" s="3">
+        <v>28.182703357372183</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>24.177215189873415</v>
+      </c>
+      <c r="R17" s="3">
+        <v>18.227848101265824</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T17" s="3">
+        <v>-4.94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>9.43</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="3">
         <v>-0.34700555328245314</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
         <v>1.19</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="3">
         <v>31.13</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="3">
         <v>-14.72</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="3">
         <v>-0.009012755161265349</v>
       </c>
-      <c r="K18" s="1" t="b">
+      <c r="K18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L18" s="1">
-        <v>32</v>
-      </c>
-      <c r="M18" s="1">
+      <c r="L18" s="3">
+        <v>36</v>
+      </c>
+      <c r="M18" s="3">
         <v>-0.32858767597752825</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="3">
+        <v>-22.09014796358183</v>
+      </c>
+      <c r="O18" s="3">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="P18" s="3">
+        <v>33.93532173431426</v>
+      </c>
+      <c r="Q18" s="3">
         <v>47.08860759493671</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P18" s="1">
-        <v>-6.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="R18" s="3">
+        <v>29.556962025316462</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>9.32</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="1">
         <v>77.21518987341773</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="1">
         <v>0.24463519313304713</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>-0.43</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="1">
         <v>-0.048303366108382144</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="1">
         <v>0.2</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="1">
         <v>53.64</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="1">
         <v>15.04</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="1">
         <v>0.004796651054090026</v>
       </c>
-      <c r="K19" s="3" t="b">
+      <c r="K19" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L19" s="3">
-        <v>76</v>
-      </c>
-      <c r="M19" s="3">
+      <c r="L19" s="1">
+        <v>85</v>
+      </c>
+      <c r="M19" s="1">
         <v>-0.1258523231817501</v>
       </c>
-      <c r="N19" s="3">
-        <v>54.17721518987342</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P19" s="3">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N19" s="1">
+        <v>-1.816612684004011</v>
+      </c>
+      <c r="O19" s="1">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="P19" s="1">
+        <v>14.335419717590279</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>53.79746835443038</v>
+      </c>
+      <c r="R19" s="1">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2406,72 +3282,96 @@
         <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="M20" s="1">
         <v>-0.142882637194632</v>
       </c>
       <c r="N20" s="1">
-        <v>37.21518987341772</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>101</v>
+        <v>-3.519644085292207</v>
+      </c>
+      <c r="O20" s="1">
+        <v>40.50632911392405</v>
       </c>
       <c r="P20" s="1">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+        <v>25.74193342123896</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>36.835443037974684</v>
+      </c>
+      <c r="R20" s="1">
+        <v>33.9873417721519</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="T20" s="1">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="1">
         <v>1.02</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="1">
         <v>41.77215189873418</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
         <v>14</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>5.19</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="1">
         <v>0.0735583537615512</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="1">
         <v>1.36</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="1">
         <v>79.77</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="1">
         <v>45.16</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="1">
         <v>0.002149483431858078</v>
       </c>
-      <c r="K21" s="3" t="b">
+      <c r="K21" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L21" s="3">
-        <v>37</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="L21" s="1">
+        <v>38</v>
+      </c>
+      <c r="M21" s="1">
         <v>0.10845538444456682</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="1">
+        <v>21.61415807862767</v>
+      </c>
+      <c r="O21" s="1">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="P21" s="1">
+        <v>39.63614933355383</v>
+      </c>
+      <c r="Q21" s="1">
         <v>62.65822784810127</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P21" s="3">
-        <v>12.93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R21" s="1">
+        <v>47.34177215189873</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T21" s="1">
+        <v>8.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -2506,22 +3406,34 @@
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M22" s="1">
         <v>-0.21510195516179886</v>
       </c>
       <c r="N22" s="1">
-        <v>40.50632911392404</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>93</v>
+        <v>-10.741575882008892</v>
+      </c>
+      <c r="O22" s="1">
+        <v>24.050632911392405</v>
       </c>
       <c r="P22" s="1">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>20.966620085005058</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>40.126582278481</v>
+      </c>
+      <c r="R22" s="1">
+        <v>30.18987341772152</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T22" s="1">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -2556,122 +3468,158 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M23" s="1">
         <v>-0.1476068526444433</v>
       </c>
       <c r="N23" s="1">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>102</v>
+        <v>-3.9920656302733297</v>
+      </c>
+      <c r="O23" s="1">
+        <v>39.24050632911392</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+        <v>28.794141696367475</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>45.189873417721515</v>
+      </c>
+      <c r="R23" s="1">
+        <v>35.443037974683534</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T23" s="1">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>-40.16</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>1.2658227848101267</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>-0.3107569721115539</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>9.38</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <v>-0.03159567105820904</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="3">
         <v>3.57</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="3">
         <v>54.4</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="3">
         <v>-18.62</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="3">
         <v>0.032115427199283675</v>
       </c>
-      <c r="K24" s="4" t="b">
+      <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="4">
-        <v>10</v>
-      </c>
-      <c r="M24" s="4">
+      <c r="L24" s="3">
+        <v>-11</v>
+      </c>
+      <c r="M24" s="3">
         <v>0.2175303535399855</v>
       </c>
-      <c r="N24" s="4">
-        <v>28.9873417721519</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="P24" s="4">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="N24" s="3">
+        <v>32.52165498816954</v>
+      </c>
+      <c r="O24" s="3">
+        <v>82.27848101265823</v>
+      </c>
+      <c r="P24" s="3">
+        <v>40.33904155950217</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>28.607594936708864</v>
+      </c>
+      <c r="R24" s="3">
+        <v>28.417721518987342</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>-2.28</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>11.39240506329114</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>0.8859649122807016</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>11.91</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>-0.441182512906166</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="3">
         <v>2.22</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="3">
         <v>45.21</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="3">
         <v>-52.93</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="3">
         <v>-0.0044881616010012575</v>
       </c>
-      <c r="K25" s="4" t="b">
+      <c r="K25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L25" s="4">
-        <v>52</v>
-      </c>
-      <c r="M25" s="4">
+      <c r="L25" s="3">
+        <v>42</v>
+      </c>
+      <c r="M25" s="3">
         <v>-0.3229203533692798</v>
       </c>
-      <c r="N25" s="4">
-        <v>27.341772151898734</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="P25" s="4">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N25" s="3">
+        <v>-21.523415702756985</v>
+      </c>
+      <c r="O25" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P25" s="3">
+        <v>55.620154465672535</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>26.962025316455698</v>
+      </c>
+      <c r="R25" s="3">
+        <v>9.177215189873419</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T25" s="3">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,472 +3654,592 @@
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-33</v>
+        <v>-24</v>
       </c>
       <c r="M26" s="1">
         <v>0.41532757772353834</v>
       </c>
       <c r="N26" s="1">
+        <v>52.30137740652482</v>
+      </c>
+      <c r="O26" s="1">
+        <v>88.60759493670885</v>
+      </c>
+      <c r="P26" s="1">
+        <v>50.63126652197354</v>
+      </c>
+      <c r="Q26" s="1">
         <v>39.367088607594944</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P26" s="1">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="R26" s="1">
+        <v>32.278481012658226</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T26" s="1">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="3">
         <v>-1.13</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="3">
         <v>13.924050632911392</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="3">
         <v>1.0176991150442478</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="3">
         <v>1.65</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="3">
         <v>-0.21825818230701438</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="3">
         <v>2.62</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="3">
         <v>56.69</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="3">
         <v>-21.3</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="3">
         <v>0.008056962376991866</v>
       </c>
-      <c r="K27" s="1" t="b">
+      <c r="K27" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L27" s="1">
-        <v>39</v>
-      </c>
-      <c r="M27" s="1">
+      <c r="L27" s="3">
+        <v>36</v>
+      </c>
+      <c r="M27" s="3">
         <v>-0.06122154423344428</v>
       </c>
-      <c r="N27" s="1">
-        <v>36.20253164556962</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P27" s="1">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="N27" s="3">
+        <v>4.646465210826574</v>
+      </c>
+      <c r="O27" s="3">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="P27" s="3">
+        <v>51.28834092723359</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>35.822784810126585</v>
+      </c>
+      <c r="R27" s="3">
+        <v>25.063291139240505</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="3">
         <v>-1.1</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="3">
         <v>15.18987341772152</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="3">
         <v>7.536363636363636</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="3">
         <v>-0.68</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="3">
         <v>-0.42051181481840655</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="3">
         <v>3.13</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="3">
         <v>49.44</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="3">
         <v>-25.71</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="3">
         <v>-0.009005059235791242</v>
       </c>
-      <c r="K28" s="1" t="b">
+      <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L28" s="1">
-        <v>10</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
         <v>-0.21403771661056437</v>
       </c>
-      <c r="N28" s="1">
-        <v>33.67088607594936</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P28" s="1">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="N28" s="3">
+        <v>-10.635152026885446</v>
+      </c>
+      <c r="O28" s="3">
+        <v>25.31645569620253</v>
+      </c>
+      <c r="P28" s="3">
+        <v>45.17203183430412</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>33.291139240506325</v>
+      </c>
+      <c r="R28" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T28" s="3">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="3">
         <v>0.44</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="3">
         <v>34.177215189873415</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="3">
         <v>77.04545454545456</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="3">
         <v>0.62</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="3">
         <v>-0.419262979032475</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="3">
         <v>2.11</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="3">
         <v>41.09</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="3">
         <v>-33.52</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="3">
         <v>-0.015715482245240393</v>
       </c>
-      <c r="K29" s="1" t="b">
+      <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L29" s="1">
-        <v>-45</v>
-      </c>
-      <c r="M29" s="1">
+      <c r="L29" s="3">
+        <v>-60</v>
+      </c>
+      <c r="M29" s="3">
         <v>-0.31166380109317693</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29" s="3">
+        <v>-20.397760475146693</v>
+      </c>
+      <c r="O29" s="3">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P29" s="3">
+        <v>48.25819923754261</v>
+      </c>
+      <c r="Q29" s="3">
         <v>41.518987341772146</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="R29" s="3">
+        <v>24.746835443037973</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="1">
         <v>1.95</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="1">
         <v>46.835443037974684</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="1">
         <v>2523.594871794872</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="1">
         <v>2.13</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="1">
         <v>-0.2195577976440304</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="1">
         <v>1.2</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="1">
         <v>44.58</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="1">
         <v>0.37</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="1">
         <v>0.0031873692550686795</v>
       </c>
-      <c r="K30" s="3" t="b">
+      <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="1">
         <v>21</v>
       </c>
-      <c r="M30" s="3">
+      <c r="M30" s="1">
         <v>-0.20017055837568842</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="1">
+        <v>-9.248436203397842</v>
+      </c>
+      <c r="O30" s="1">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="P30" s="1">
+        <v>24.961328061128594</v>
+      </c>
+      <c r="Q30" s="1">
         <v>63.037974683544306</v>
       </c>
-      <c r="O30" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P30" s="3">
-        <v>-4.63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="R30" s="1">
+        <v>46.32911392405064</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T30" s="1">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>5.13</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>59.49367088607595</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="2">
         <v>10.690058479532164</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>0.9</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>0.15822414412232277</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>1.43</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="2">
         <v>58.64</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="2">
         <v>22.59</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="2">
         <v>0.029369983533265455</v>
       </c>
-      <c r="K31" s="3" t="b">
+      <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L31" s="3">
-        <v>97</v>
-      </c>
-      <c r="M31" s="3">
+      <c r="L31" s="2">
+        <v>70</v>
+      </c>
+      <c r="M31" s="2">
         <v>0.19990670854925807</v>
       </c>
-      <c r="N31" s="3">
-        <v>68.48101265822785</v>
-      </c>
-      <c r="O31" s="3" t="s">
+      <c r="N31" s="2">
+        <v>30.759290489096795</v>
+      </c>
+      <c r="O31" s="2">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="P31" s="2">
+        <v>17.25839209766727</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>68.10126582278481</v>
+      </c>
+      <c r="R31" s="2">
+        <v>60.9493670886076</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3">
+        <v>-2.92</v>
+      </c>
+      <c r="C32" s="3">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.178082191780822</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-0.38807011843937855</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="H32" s="3">
+        <v>36.12</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-10.07</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-0.006325061572753529</v>
+      </c>
+      <c r="K32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>20</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-0.32990840063435256</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-22.222220429264258</v>
+      </c>
+      <c r="O32" s="3">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="P32" s="3">
+        <v>38.84187494148391</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>34.43037974683544</v>
+      </c>
+      <c r="R32" s="3">
+        <v>15.632911392405063</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="P31" s="3">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1">
-        <v>-2.92</v>
-      </c>
-      <c r="C32" s="1">
-        <v>10.126582278481013</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8.178082191780822</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="F32" s="1">
-        <v>-0.38807011843937855</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H32" s="1">
-        <v>36.12</v>
-      </c>
-      <c r="I32" s="1">
-        <v>-10.07</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-0.006325061572753529</v>
-      </c>
-      <c r="K32" s="1" t="b">
+      <c r="T32" s="3">
+        <v>-13.73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <v>16.79</v>
+      </c>
+      <c r="C33" s="1">
+        <v>88.60759493670885</v>
+      </c>
+      <c r="D33" s="1">
+        <v>-0.05896366885050616</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="F33" s="1">
+        <v>-0.06411046878691452</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="H33" s="1">
+        <v>57.9</v>
+      </c>
+      <c r="I33" s="1">
+        <v>-8.9</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.0023051794827069136</v>
+      </c>
+      <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <v>24</v>
-      </c>
-      <c r="M32" s="1">
-        <v>-0.32990840063435256</v>
-      </c>
-      <c r="N32" s="1">
-        <v>34.810126582278485</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P32" s="1">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3">
-        <v>16.79</v>
-      </c>
-      <c r="C33" s="3">
-        <v>88.60759493670885</v>
-      </c>
-      <c r="D33" s="3">
-        <v>-0.05777248362120303</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0.37</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-0.06411046878691452</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="H33" s="3">
-        <v>57.9</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-8.9</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.0023051794827069136</v>
-      </c>
-      <c r="K33" s="3" t="b">
+      <c r="L33" s="1">
+        <v>11</v>
+      </c>
+      <c r="M33" s="1">
+        <v>-0.056355573079577725</v>
+      </c>
+      <c r="N33" s="1">
+        <v>5.133062326213224</v>
+      </c>
+      <c r="O33" s="1">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P33" s="1">
+        <v>26.894390179645494</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>52.278481012658226</v>
+      </c>
+      <c r="R33" s="1">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T33" s="1">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>13.11</v>
+      </c>
+      <c r="C34" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="D34" s="2">
+        <v>-0.7025171624713958</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.58</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.16496462914942378</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1.26</v>
+      </c>
+      <c r="H34" s="2">
+        <v>70.23</v>
+      </c>
+      <c r="I34" s="2">
+        <v>36.21</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.02783748309324901</v>
+      </c>
+      <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L33" s="3">
-        <v>46</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-0.056355573079577725</v>
-      </c>
-      <c r="N33" s="3">
-        <v>52.65822784810126</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P33" s="3">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3">
-        <v>13.11</v>
-      </c>
-      <c r="C34" s="3">
-        <v>84.81012658227847</v>
-      </c>
-      <c r="D34" s="3">
-        <v>-0.6643783371472158</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0.58</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.16496462914942378</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1.26</v>
-      </c>
-      <c r="H34" s="3">
-        <v>70.23</v>
-      </c>
-      <c r="I34" s="3">
-        <v>36.21</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0.02783748309324901</v>
-      </c>
-      <c r="K34" s="3" t="b">
+      <c r="L34" s="2">
+        <v>37</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.19016804019826838</v>
+      </c>
+      <c r="N34" s="2">
+        <v>29.785423653997828</v>
+      </c>
+      <c r="O34" s="2">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P34" s="2">
+        <v>20.42247430615109</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>60.63291139240506</v>
+      </c>
+      <c r="R34" s="2">
+        <v>50.949367088607595</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T34" s="2">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3">
+        <v>17.37</v>
+      </c>
+      <c r="C35" s="3">
+        <v>91.13924050632912</v>
+      </c>
+      <c r="D35" s="3">
+        <v>-0.47898675877950486</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-0.96</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-0.3016835226741067</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="H35" s="3">
+        <v>26.06</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-25.51</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-0.02616499403082351</v>
+      </c>
+      <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L34" s="3">
-        <v>61</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0.19016804019826838</v>
-      </c>
-      <c r="N34" s="3">
-        <v>61.01265822784811</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P34" s="3">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <v>17.37</v>
-      </c>
-      <c r="C35" s="1">
-        <v>91.13924050632912</v>
-      </c>
-      <c r="D35" s="1">
-        <v>-0.47898675877950486</v>
-      </c>
-      <c r="E35" s="1">
-        <v>-0.96</v>
-      </c>
-      <c r="F35" s="1">
-        <v>-0.3016835226741067</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="H35" s="1">
-        <v>26.06</v>
-      </c>
-      <c r="I35" s="1">
-        <v>-25.51</v>
-      </c>
-      <c r="J35" s="1">
-        <v>-0.02616499403082351</v>
-      </c>
-      <c r="K35" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="L35" s="3">
         <v>22</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="3">
         <v>-0.3026528846375238</v>
       </c>
-      <c r="N35" s="1">
-        <v>33.037974683544306</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="P35" s="1">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N35" s="3">
+        <v>-19.49666882958139</v>
+      </c>
+      <c r="O35" s="3">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="P35" s="3">
+        <v>31.050134736892222</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>32.65822784810126</v>
+      </c>
+      <c r="R35" s="3">
+        <v>23.037974683544302</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -3206,22 +4274,34 @@
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>-37</v>
+        <v>-50</v>
       </c>
       <c r="M36" s="1">
         <v>-0.18129151135003585</v>
       </c>
       <c r="N36" s="1">
-        <v>38.35443037974683</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>100</v>
+        <v>-7.360531500832586</v>
+      </c>
+      <c r="O36" s="1">
+        <v>31.645569620253166</v>
       </c>
       <c r="P36" s="1">
-        <v>-4.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>32.54334537649318</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="R36" s="1">
+        <v>30.696202531645564</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T36" s="1">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -3256,122 +4336,158 @@
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>-200</v>
+        <v>-207</v>
       </c>
       <c r="M37" s="1">
         <v>-0.00542760020708033</v>
       </c>
       <c r="N37" s="1">
-        <v>38.48101265822785</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>88</v>
+        <v>10.225859613462955</v>
+      </c>
+      <c r="O37" s="1">
+        <v>60.75949367088608</v>
       </c>
       <c r="P37" s="1">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+        <v>35.0614795066832</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>38.10126582278481</v>
+      </c>
+      <c r="R37" s="1">
+        <v>37.84810126582279</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T37" s="1">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>-0.74</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <v>16.455696202531644</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="2">
         <v>36.648648648648646</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>-0.1</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>0.26342049006394885</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="2">
         <v>1.12</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="2">
         <v>82.57</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="2">
         <v>29.02</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="2">
         <v>0.03960451097304168</v>
       </c>
-      <c r="K38" s="3" t="b">
+      <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L38" s="3">
-        <v>-46</v>
-      </c>
-      <c r="M38" s="3">
+      <c r="L38" s="2">
+        <v>-41</v>
+      </c>
+      <c r="M38" s="2">
         <v>0.27505283362495403</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N38" s="2">
+        <v>38.27390299666639</v>
+      </c>
+      <c r="O38" s="2">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="P38" s="2">
+        <v>27.505487150580247</v>
+      </c>
+      <c r="Q38" s="2">
         <v>64.81012658227849</v>
       </c>
-      <c r="O38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P38" s="3">
-        <v>-0.94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="R38" s="2">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T38" s="2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="2">
         <v>-0.18</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <v>22.78481012658228</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="2">
         <v>100</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>-7.97</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>0.06794935342768335</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="2">
         <v>1.29</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="2">
         <v>48.15</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="2">
         <v>7.47</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="2">
         <v>0.0170512546758961</v>
       </c>
-      <c r="K39" s="3" t="b">
+      <c r="K39" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="2">
         <v>-4</v>
       </c>
-      <c r="M39" s="3">
+      <c r="M39" s="2">
         <v>0.09606085036677925</v>
       </c>
-      <c r="N39" s="3">
-        <v>56.45569620253165</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P39" s="3">
-        <v>-3.54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N39" s="2">
+        <v>20.37470467084891</v>
+      </c>
+      <c r="O39" s="2">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="P39" s="2">
+        <v>18.299999237060547</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>56.07594936708861</v>
+      </c>
+      <c r="R39" s="2">
+        <v>52.34177215189874</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T39" s="2">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -3406,22 +4522,34 @@
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M40" s="1">
         <v>0.016171363124828808</v>
       </c>
       <c r="N40" s="1">
-        <v>37.34177215189874</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>107</v>
+        <v>12.38575594665387</v>
+      </c>
+      <c r="O40" s="1">
+        <v>62.0253164556962</v>
       </c>
       <c r="P40" s="1">
-        <v>-11.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>45.29877115964868</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>36.9620253164557</v>
+      </c>
+      <c r="R40" s="1">
+        <v>33.101265822784804</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T40" s="1">
+        <v>-7.66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -3432,7 +4560,7 @@
         <v>5.063291139240507</v>
       </c>
       <c r="D41" s="1">
-        <v>7.34990059642147</v>
+        <v>7.415506958250497</v>
       </c>
       <c r="E41" s="1">
         <v>-1.75</v>
@@ -3456,22 +4584,34 @@
         <v>1</v>
       </c>
       <c r="L41" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" s="1">
         <v>-0.01737053635494923</v>
       </c>
       <c r="N41" s="1">
-        <v>44.55696202531645</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>99</v>
+        <v>9.031565998676063</v>
+      </c>
+      <c r="O41" s="1">
+        <v>56.9620253164557</v>
       </c>
       <c r="P41" s="1">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>46.4052282234621</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>44.17721518987342</v>
+      </c>
+      <c r="R41" s="1">
+        <v>30.44303797468355</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="T41" s="1">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -3506,272 +4646,344 @@
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M42" s="1">
         <v>-0.1741443487536336</v>
       </c>
       <c r="N42" s="1">
-        <v>41.64556962025316</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>103</v>
+        <v>-6.645815241192368</v>
+      </c>
+      <c r="O42" s="1">
+        <v>35.44303797468354</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+        <v>10.38279059078273</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>41.265822784810126</v>
+      </c>
+      <c r="R42" s="1">
+        <v>37.72151898734177</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T42" s="1">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="1">
         <v>-0.02</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="1">
         <v>27.848101265822784</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="1">
         <v>1214</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="1">
         <v>5.23</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="1">
         <v>-0.05089839962555098</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="1">
         <v>1.26</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="1">
         <v>50.34</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="1">
         <v>-13.72</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="1">
         <v>-0.0019450182993650366</v>
       </c>
-      <c r="K43" s="3" t="b">
+      <c r="K43" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L43" s="3">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="L43" s="1">
+        <v>8</v>
+      </c>
+      <c r="M43" s="1">
         <v>-0.02569498857670638</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="1">
+        <v>8.199120776500347</v>
+      </c>
+      <c r="O43" s="1">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P43" s="1">
+        <v>36.79958124823221</v>
+      </c>
+      <c r="Q43" s="1">
         <v>53.67088607594937</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="R43" s="1">
+        <v>44.55696202531645</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T43" s="1">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="3">
         <v>1.02</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="3">
         <v>41.77215189873418</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="3">
         <v>26.91176470588235</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="3">
         <v>-1.51</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="3">
         <v>-0.37008009296786126</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="3">
         <v>2.57</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44" s="3">
         <v>37.06</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I44" s="3">
         <v>-28.9</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="3">
         <v>-0.021500255259178976</v>
       </c>
-      <c r="K44" s="1" t="b">
+      <c r="K44" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L44" s="1">
-        <v>-88</v>
-      </c>
-      <c r="M44" s="1">
+      <c r="L44" s="3">
+        <v>-109</v>
+      </c>
+      <c r="M44" s="3">
         <v>-0.21789026471137662</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44" s="3">
+        <v>-11.020406836966671</v>
+      </c>
+      <c r="O44" s="3">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="P44" s="3">
+        <v>44.155007607957295</v>
+      </c>
+      <c r="Q44" s="3">
         <v>39.99999999999999</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="R44" s="3">
+        <v>29.177215189873415</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T44" s="3">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="2">
         <v>8.37</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <v>73.41772151898735</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="2">
         <v>0.821983273596177</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="2">
         <v>0.94</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>0.1774315040334033</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="2">
         <v>1.45</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="2">
         <v>58.56</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="2">
         <v>15.14</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="2">
         <v>0.023648199835042998</v>
       </c>
-      <c r="K45" s="3" t="b">
+      <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L45" s="3">
-        <v>64</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="L45" s="2">
+        <v>36</v>
+      </c>
+      <c r="M45" s="2">
         <v>0.2210527923871728</v>
       </c>
-      <c r="N45" s="3">
-        <v>62.65822784810127</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P45" s="3">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="N45" s="2">
+        <v>32.873898872888276</v>
+      </c>
+      <c r="O45" s="2">
+        <v>83.54430379746836</v>
+      </c>
+      <c r="P45" s="2">
+        <v>19.641850851970627</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>62.27848101265823</v>
+      </c>
+      <c r="R45" s="2">
+        <v>57.34177215189874</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T45" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="1">
         <v>-0.3</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="1">
         <v>21.518987341772153</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="1">
         <v>543.5000000000001</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="1">
         <v>-0.94</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="1">
         <v>-0.26667139695523195</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="1">
         <v>1.49</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="1">
         <v>40.87</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="1">
         <v>4.79</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="1">
         <v>-0.0066835997262821335</v>
       </c>
-      <c r="K46" s="3" t="b">
+      <c r="K46" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L46" s="3">
-        <v>25</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="L46" s="1">
+        <v>24</v>
+      </c>
+      <c r="M46" s="1">
         <v>-0.21917266074779407</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="1">
+        <v>-11.14864644060841</v>
+      </c>
+      <c r="O46" s="1">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="P46" s="1">
+        <v>40.6204924523832</v>
+      </c>
+      <c r="Q46" s="1">
         <v>50.12658227848101</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P46" s="3">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="R46" s="1">
+        <v>30.379746835443033</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T46" s="1">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="3">
         <v>10.62</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="3">
         <v>81.0126582278481</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="3">
         <v>0.8549905838041432</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="3">
         <v>-4.11</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="3">
         <v>-0.457975392465942</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="3">
         <v>1.46</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47" s="3">
         <v>26.92</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I47" s="3">
         <v>-21.51</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="3">
         <v>-0.030394377303079353</v>
       </c>
-      <c r="K47" s="1" t="b">
+      <c r="K47" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L47" s="1">
-        <v>4</v>
-      </c>
-      <c r="M47" s="1">
+      <c r="L47" s="3">
+        <v>13</v>
+      </c>
+      <c r="M47" s="3">
         <v>-0.4133847421487554</v>
       </c>
-      <c r="N47" s="1">
-        <v>38.9873417721519</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="P47" s="1">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N47" s="3">
+        <v>-30.569854580704554</v>
+      </c>
+      <c r="O47" s="3">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="P47" s="3">
+        <v>31.304415950527737</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>38.607594936708864</v>
+      </c>
+      <c r="R47" s="3">
+        <v>25.25316455696202</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T47" s="3">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
@@ -3806,22 +5018,34 @@
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="M48" s="2">
         <v>0.47394517010227855</v>
       </c>
       <c r="N48" s="2">
-        <v>71.13924050632912</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>90</v>
+        <v>58.16313664439884</v>
+      </c>
+      <c r="O48" s="2">
+        <v>91.13924050632912</v>
       </c>
       <c r="P48" s="2">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15.18684888660459</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>70.75949367088607</v>
+      </c>
+      <c r="R48" s="2">
+        <v>63.60759493670886</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T48" s="2">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
@@ -3856,72 +5080,96 @@
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M49" s="2">
         <v>0.8670526140165769</v>
       </c>
       <c r="N49" s="2">
+        <v>97.47388103582867</v>
+      </c>
+      <c r="O49" s="2">
+        <v>94.9367088607595</v>
+      </c>
+      <c r="P49" s="2">
+        <v>31.61869931071345</v>
+      </c>
+      <c r="Q49" s="2">
         <v>73.0379746835443</v>
       </c>
-      <c r="O49" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P49" s="2">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="R49" s="2">
+        <v>62.594936708860764</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T49" s="2">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="3">
         <v>-0.13</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="3">
         <v>25.31645569620253</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="3">
         <v>300.1538461538462</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="3">
         <v>2.75</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="3">
         <v>-0.46770435480298933</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" s="3">
         <v>1.53</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50" s="3">
         <v>34.19</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="3">
         <v>-28.15</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="3">
         <v>-0.03248906040173917</v>
       </c>
-      <c r="K50" s="1" t="b">
+      <c r="K50" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L50" s="1">
-        <v>1</v>
-      </c>
-      <c r="M50" s="1">
+      <c r="L50" s="3">
+        <v>-2</v>
+      </c>
+      <c r="M50" s="3">
         <v>-0.416328170741883</v>
       </c>
-      <c r="N50" s="1">
+      <c r="N50" s="3">
+        <v>-30.864197440017303</v>
+      </c>
+      <c r="O50" s="3">
+        <v>2.5316455696202533</v>
+      </c>
+      <c r="P50" s="3">
+        <v>47.64150593279924</v>
+      </c>
+      <c r="Q50" s="3">
         <v>38.22784810126583</v>
       </c>
-      <c r="O50" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P50" s="1">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R50" s="3">
+        <v>21.77215189873418</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -3932,7 +5180,7 @@
         <v>7.59493670886076</v>
       </c>
       <c r="D51" s="1">
-        <v>-6.131443298969073</v>
+        <v>13.440721649484537</v>
       </c>
       <c r="E51" s="1">
         <v>17.05</v>
@@ -3956,72 +5204,96 @@
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="M51" s="1">
         <v>0.1498543457563597</v>
       </c>
       <c r="N51" s="1">
-        <v>32.911392405063296</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>109</v>
+        <v>25.75405420980697</v>
+      </c>
+      <c r="O51" s="1">
+        <v>75.9493670886076</v>
       </c>
       <c r="P51" s="1">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+        <v>46.744012320672994</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>52.65822784810127</v>
+      </c>
+      <c r="R51" s="1">
+        <v>41.329113924050645</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T51" s="1">
+        <v>14.68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="2">
         <v>5.3</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="2">
         <v>62.0253164556962</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="2">
         <v>6.496226415094339</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="2">
         <v>0.22</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="2">
         <v>0.01973553992918095</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="2">
         <v>1.84</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="2">
         <v>57.13</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="2">
         <v>55.01</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="2">
         <v>0.028614893221618865</v>
       </c>
-      <c r="K52" s="3" t="b">
+      <c r="K52" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L52" s="3">
-        <v>292</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="L52" s="2">
+        <v>301</v>
+      </c>
+      <c r="M52" s="2">
         <v>0.10116194485621732</v>
       </c>
-      <c r="N52" s="3">
-        <v>65.94936708860759</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P52" s="3">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N52" s="2">
+        <v>20.884814119792736</v>
+      </c>
+      <c r="O52" s="2">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="P52" s="2">
+        <v>20.10180966623631</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>65.56962025316456</v>
+      </c>
+      <c r="R52" s="2">
+        <v>54.68354430379747</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T52" s="2">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -4056,72 +5328,96 @@
         <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="M53" s="1">
         <v>-0.07146365958654055</v>
       </c>
       <c r="N53" s="1">
-        <v>47.46835443037975</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>90</v>
+        <v>3.622253675516941</v>
+      </c>
+      <c r="O53" s="1">
+        <v>48.10126582278481</v>
       </c>
       <c r="P53" s="1">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+        <v>48.21894075039502</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>47.088607594936704</v>
+      </c>
+      <c r="R53" s="1">
+        <v>33.22784810126582</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="T53" s="1">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="2">
         <v>0.54</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="2">
         <v>35.44303797468354</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="2">
         <v>41.629629629629626</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="2">
         <v>-0.44</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="2">
         <v>-0.05302157269131072</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="2">
         <v>1.46</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="2">
         <v>63.63</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="2">
         <v>9.72</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="2">
         <v>0.03241268225849441</v>
       </c>
-      <c r="K54" s="3" t="b">
+      <c r="K54" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="L54" s="2">
+        <v>13</v>
+      </c>
+      <c r="M54" s="2">
         <v>-0.008430922374124128</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="2">
+        <v>9.925527396758586</v>
+      </c>
+      <c r="O54" s="2">
+        <v>58.22784810126582</v>
+      </c>
+      <c r="P54" s="2">
+        <v>25.062459708672506</v>
+      </c>
+      <c r="Q54" s="2">
         <v>67.21518987341771</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="P54" s="3">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R54" s="2">
+        <v>51.13924050632911</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T54" s="2">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -4156,22 +5452,34 @@
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>-31</v>
+        <v>-48</v>
       </c>
       <c r="M55" s="1">
         <v>-0.16058817197744502</v>
       </c>
       <c r="N55" s="1">
-        <v>46.962025316455694</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>110</v>
+        <v>-5.29019756357351</v>
+      </c>
+      <c r="O55" s="1">
+        <v>36.708860759493675</v>
       </c>
       <c r="P55" s="1">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18.39301096820415</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>46.582278481012665</v>
+      </c>
+      <c r="R55" s="1">
+        <v>38.67088607594937</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T55" s="1">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -4206,22 +5514,34 @@
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M56" s="1">
         <v>-0.17644770977041602</v>
       </c>
       <c r="N56" s="1">
-        <v>45.18987341772152</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>111</v>
+        <v>-6.876151342870604</v>
+      </c>
+      <c r="O56" s="1">
+        <v>32.91139240506329</v>
       </c>
       <c r="P56" s="1">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10.95912073621325</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>44.810126582278485</v>
+      </c>
+      <c r="R56" s="1">
+        <v>36.32911392405063</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="T56" s="1">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
@@ -4232,7 +5552,7 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.355524079320113</v>
+        <v>2.35505193578848</v>
       </c>
       <c r="E57" s="2">
         <v>0.39</v>
@@ -4256,122 +5576,158 @@
         <v>1</v>
       </c>
       <c r="L57" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="M57" s="2">
         <v>0.6526499225379185</v>
       </c>
       <c r="N57" s="2">
-        <v>80.63291139240506</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>112</v>
+        <v>76.03361188796285</v>
+      </c>
+      <c r="O57" s="2">
+        <v>92.40506329113924</v>
       </c>
       <c r="P57" s="2">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+        <v>30.30559414893712</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>80.25316455696203</v>
+      </c>
+      <c r="R57" s="2">
+        <v>66.89873417721519</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T57" s="2">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="2">
         <v>20.1</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="2">
         <v>94.9367088607595</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="2">
         <v>0.09701492537313429</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="2">
         <v>-1.9</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>-0.020395804242056392</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="2">
         <v>1.62</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="2">
         <v>57.98</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="2">
         <v>44.43</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="2">
         <v>0.023405428653427596</v>
       </c>
-      <c r="K58" s="3" t="b">
+      <c r="K58" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L58" s="3">
-        <v>291</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="L58" s="2">
+        <v>273</v>
+      </c>
+      <c r="M58" s="2">
         <v>0.039704637489803796</v>
       </c>
-      <c r="N58" s="3">
-        <v>64.43037974683544</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="P58" s="3">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="N58" s="2">
+        <v>14.73908338315138</v>
+      </c>
+      <c r="O58" s="2">
+        <v>64.55696202531645</v>
+      </c>
+      <c r="P58" s="2">
+        <v>13.880000945060484</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>64.0506329113924</v>
+      </c>
+      <c r="R58" s="2">
+        <v>54.24050632911392</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="T58" s="2">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="2">
         <v>34.32</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <v>100</v>
       </c>
-      <c r="D59" s="3">
-        <v>-1.435897435897436</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="2">
+        <v>-1.4889277389277389</v>
+      </c>
+      <c r="E59" s="2">
         <v>-2.43</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="2">
         <v>0.17904261223547482</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="2">
         <v>1.22</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="2">
         <v>51.69</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="2">
         <v>43.37</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="2">
         <v>0.02317032186491351</v>
       </c>
-      <c r="K59" s="3" t="b">
+      <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L59" s="3">
-        <v>365</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="L59" s="2">
+        <v>369</v>
+      </c>
+      <c r="M59" s="2">
         <v>0.200368575430651</v>
       </c>
-      <c r="N59" s="3">
-        <v>59.74683544303797</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P59" s="3">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N59" s="2">
+        <v>30.805477177236085</v>
+      </c>
+      <c r="O59" s="2">
+        <v>81.0126582278481</v>
+      </c>
+      <c r="P59" s="2">
+        <v>11.512523311327532</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>59.36708860759494</v>
+      </c>
+      <c r="R59" s="2">
+        <v>56.898734177215196</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
@@ -4406,122 +5762,158 @@
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M60" s="1">
         <v>-0.2090481770380639</v>
       </c>
       <c r="N60" s="1">
-        <v>37.59493670886076</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>91</v>
+        <v>-10.136198069635396</v>
+      </c>
+      <c r="O60" s="1">
+        <v>26.582278481012654</v>
       </c>
       <c r="P60" s="1">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+        <v>12.798408482128673</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>37.21518987341772</v>
+      </c>
+      <c r="R60" s="1">
+        <v>30.506329113924046</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T60" s="1">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="1">
         <v>17.74</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="1">
         <v>92.40506329113924</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="1">
         <v>0.6178128523111613</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="1">
         <v>-0.38</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="1">
         <v>-0.17099099367816528</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="1">
         <v>0.95</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="1">
         <v>42.52</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="1">
         <v>8.1</v>
       </c>
-      <c r="J61" s="3">
+      <c r="J61" s="1">
         <v>-0.006484471124865406</v>
       </c>
-      <c r="K61" s="3" t="b">
+      <c r="K61" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L61" s="3">
-        <v>166</v>
-      </c>
-      <c r="M61" s="3">
+      <c r="L61" s="1">
+        <v>178</v>
+      </c>
+      <c r="M61" s="1">
         <v>-0.1758378034952508</v>
       </c>
-      <c r="N61" s="3">
-        <v>53.16455696202532</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="P61" s="3">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="N61" s="1">
+        <v>-6.81516071535408</v>
+      </c>
+      <c r="O61" s="1">
+        <v>34.177215189873415</v>
+      </c>
+      <c r="P61" s="1">
+        <v>16.149676494964734</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>52.78481012658228</v>
+      </c>
+      <c r="R61" s="1">
+        <v>42.27848101265823</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T61" s="1">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="4">
         <v>28.77</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="4">
         <v>98.73417721518987</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="4">
         <v>4.831074035453597</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="4">
         <v>-8.63</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="4">
         <v>0.7870039611746505</v>
       </c>
-      <c r="G62" s="2">
+      <c r="G62" s="4">
         <v>4.63</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62" s="4">
         <v>65.5</v>
       </c>
-      <c r="I62" s="2">
+      <c r="I62" s="4">
         <v>233.6</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="4">
         <v>0.10154333708964342</v>
       </c>
-      <c r="K62" s="2" t="b">
+      <c r="K62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L62" s="2">
-        <v>461</v>
-      </c>
-      <c r="M62" s="2">
+      <c r="L62" s="4">
+        <v>472</v>
+      </c>
+      <c r="M62" s="4">
         <v>1.1388823538950577</v>
       </c>
-      <c r="N62" s="2">
-        <v>83.29113924050633</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="P62" s="2">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N62" s="4">
+        <v>124.65685502367674</v>
+      </c>
+      <c r="O62" s="4">
+        <v>98.73417721518987</v>
+      </c>
+      <c r="P62" s="4">
+        <v>25.85061584959845</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>82.91139240506328</v>
+      </c>
+      <c r="R62" s="4">
+        <v>72.02531645569621</v>
+      </c>
+      <c r="S62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="T62" s="4">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
@@ -4556,22 +5948,34 @@
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="M63" s="2">
         <v>0.7596580815495761</v>
       </c>
       <c r="N63" s="2">
-        <v>78.48101265822785</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>103</v>
+        <v>86.7344277891286</v>
+      </c>
+      <c r="O63" s="2">
+        <v>93.67088607594937</v>
       </c>
       <c r="P63" s="2">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>20.9978319173529</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>78.10126582278482</v>
+      </c>
+      <c r="R63" s="2">
+        <v>67.02531645569621</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T63" s="2">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
@@ -4582,7 +5986,7 @@
         <v>89.87341772151899</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.2691167753408418</v>
+        <v>-0.27504445761707175</v>
       </c>
       <c r="E64" s="1">
         <v>-0.69</v>
@@ -4606,22 +6010,34 @@
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M64" s="1">
         <v>-0.2186186823088213</v>
       </c>
       <c r="N64" s="1">
-        <v>47.46835443037975</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>94</v>
+        <v>-11.09324859671114</v>
+      </c>
+      <c r="O64" s="1">
+        <v>21.518987341772153</v>
       </c>
       <c r="P64" s="1">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15.211254913322609</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>47.08860759493671</v>
+      </c>
+      <c r="R64" s="1">
+        <v>33.924050632911396</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="T64" s="1">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
@@ -4656,518 +6072,656 @@
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-183</v>
+        <v>-191</v>
       </c>
       <c r="M65" s="1">
         <v>-0.12371021735895393</v>
       </c>
       <c r="N65" s="1">
-        <v>39.87341772151898</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>92</v>
+        <v>-1.602402101724396</v>
+      </c>
+      <c r="O65" s="1">
+        <v>44.303797468354425</v>
       </c>
       <c r="P65" s="1">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+        <v>48.12800106814908</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>39.49367088607595</v>
+      </c>
+      <c r="R65" s="1">
+        <v>31.89873417721519</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T65" s="1">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="1">
         <v>4.01</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="1">
         <v>55.69620253164557</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="1">
         <v>7.266832917705736</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="1">
         <v>-0.9</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="1">
         <v>-0.04838973089937444</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="1">
         <v>1.14</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="1">
         <v>50.19</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I66" s="1">
         <v>-11.09</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="1">
         <v>-0.0007620642574330307</v>
       </c>
-      <c r="K66" s="3" t="b">
+      <c r="K66" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L66" s="3">
-        <v>-66</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="L66" s="1">
+        <v>-73</v>
+      </c>
+      <c r="M66" s="1">
         <v>-0.034818663411535056</v>
       </c>
-      <c r="N66" s="3">
-        <v>50.75949367088608</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P66" s="3">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="N66" s="1">
+        <v>7.286753293017485</v>
+      </c>
+      <c r="O66" s="1">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="P66" s="1">
+        <v>21.01837744312229</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>50.37974683544304</v>
+      </c>
+      <c r="R66" s="1">
+        <v>44.43037974683545</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="1">
         <v>7.35</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="1">
         <v>69.62025316455697</v>
       </c>
-      <c r="D67" s="3">
-        <v>84.9795918367347</v>
-      </c>
-      <c r="E67" s="3">
+      <c r="D67" s="1">
+        <v>121.84625850340136</v>
+      </c>
+      <c r="E67" s="1">
         <v>0.3</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="1">
         <v>-0.20663102503993735</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="1">
         <v>0.33</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67" s="1">
         <v>39.62</v>
       </c>
-      <c r="I67" s="3">
+      <c r="I67" s="1">
         <v>1.35</v>
       </c>
-      <c r="J67" s="3">
+      <c r="J67" s="1">
         <v>-0.011090693921459435</v>
       </c>
-      <c r="K67" s="3" t="b">
+      <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="3">
-        <v>134</v>
-      </c>
-      <c r="M67" s="3">
+      <c r="L67" s="1">
+        <v>154</v>
+      </c>
+      <c r="M67" s="1">
         <v>-0.271578276588883</v>
       </c>
-      <c r="N67" s="3">
-        <v>59.74683544303798</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="P67" s="3">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="N67" s="1">
+        <v>-16.38920802471731</v>
+      </c>
+      <c r="O67" s="1">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="P67" s="1">
+        <v>18.003852697255347</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>60.12658227848101</v>
+      </c>
+      <c r="R67" s="1">
+        <v>44.11392405063291</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T67" s="1">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="3">
         <v>8.24</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="3">
         <v>72.15189873417721</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="3">
         <v>0.6286407766990291</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="3">
         <v>-0.07</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="3">
         <v>-0.2874281543757484</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" s="3">
         <v>1.48</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68" s="3">
         <v>33.52</v>
       </c>
-      <c r="I68" s="1">
+      <c r="I68" s="3">
         <v>-15.25</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="3">
         <v>-0.015387484507357942</v>
       </c>
-      <c r="K68" s="1" t="b">
+      <c r="K68" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L68" s="1">
-        <v>-48</v>
-      </c>
-      <c r="M68" s="1">
+      <c r="L68" s="3">
+        <v>-63</v>
+      </c>
+      <c r="M68" s="3">
         <v>-0.2408987801317276</v>
       </c>
-      <c r="N68" s="1">
-        <v>36.45569620253164</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P68" s="1">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="N68" s="3">
+        <v>-13.321258379001765</v>
+      </c>
+      <c r="O68" s="3">
+        <v>17.72151898734177</v>
+      </c>
+      <c r="P68" s="3">
+        <v>29.145649851223904</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>36.07594936708861</v>
+      </c>
+      <c r="R68" s="3">
+        <v>26.139240506329113</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T68" s="3">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="3">
         <v>18.19</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="3">
         <v>93.67088607594937</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="3">
         <v>-0.47608576140736675</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="3">
         <v>1.57</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="3">
         <v>-0.22580565225190932</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="3">
         <v>0.86</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69" s="3">
         <v>33.16</v>
       </c>
-      <c r="I69" s="1">
+      <c r="I69" s="3">
         <v>-16.82</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="3">
         <v>-0.013238691678533204</v>
       </c>
-      <c r="K69" s="1" t="b">
+      <c r="K69" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L69" s="1">
-        <v>-43</v>
-      </c>
-      <c r="M69" s="1">
+      <c r="L69" s="3">
+        <v>-52</v>
+      </c>
+      <c r="M69" s="3">
         <v>-0.23937671973974872</v>
       </c>
-      <c r="N69" s="1">
-        <v>37.848101265822784</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="P69" s="1">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="N69" s="3">
+        <v>-13.169052339803875</v>
+      </c>
+      <c r="O69" s="3">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P69" s="3">
+        <v>31.450467124868602</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>37.46835443037975</v>
+      </c>
+      <c r="R69" s="3">
+        <v>26.898734177215186</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T69" s="3">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="3">
         <v>1.52</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="3">
         <v>45.56962025316456</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="3">
         <v>13.532894736842104</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="3">
         <v>-0.78</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="3">
         <v>-0.45495617366977387</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" s="3">
         <v>1.11</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70" s="3">
         <v>30.09</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70" s="3">
         <v>-32.88</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="3">
         <v>-0.03576131515339131</v>
       </c>
-      <c r="K70" s="1" t="b">
+      <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L70" s="1">
-        <v>-93</v>
-      </c>
-      <c r="M70" s="1">
+      <c r="L70" s="3">
+        <v>-97</v>
+      </c>
+      <c r="M70" s="3">
         <v>-0.44429319207218576</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70" s="3">
+        <v>-33.66069957304759</v>
+      </c>
+      <c r="O70" s="3">
+        <v>1.2658227848101267</v>
+      </c>
+      <c r="P70" s="3">
+        <v>36.83258048205344</v>
+      </c>
+      <c r="Q70" s="3">
         <v>36.075949367088604</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P70" s="1">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="R70" s="3">
+        <v>22.151898734177216</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="3">
         <v>5.18</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="3">
         <v>60.75949367088608</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="3">
         <v>0.7837837837837839</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="3">
         <v>0.16</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="3">
         <v>-0.257648719824491</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="3">
         <v>1.01</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="3">
         <v>50.11</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I71" s="3">
         <v>-7.21</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="3">
         <v>-0.01041135545749011</v>
       </c>
-      <c r="K71" s="1" t="b">
+      <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L71" s="1">
-        <v>-54</v>
-      </c>
-      <c r="M71" s="1">
+      <c r="L71" s="3">
+        <v>-62</v>
+      </c>
+      <c r="M71" s="3">
         <v>-0.2566793578610739</v>
       </c>
-      <c r="N71" s="1">
-        <v>42.9113924050633</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="P71" s="1">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="N71" s="3">
+        <v>-14.899316151936398</v>
+      </c>
+      <c r="O71" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="P71" s="3">
+        <v>19.13407224404345</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>42.53164556962026</v>
+      </c>
+      <c r="R71" s="3">
+        <v>28.227848101265828</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="T71" s="3">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="3">
         <v>10.42</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="3">
         <v>78.48101265822784</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="3">
         <v>0.21305182341650677</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="3">
         <v>-1.31</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="3">
         <v>-0.30773563356932304</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="3">
         <v>1.14</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="3">
         <v>33.96</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I72" s="3">
         <v>-11.92</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="3">
         <v>-0.012895102685770758</v>
       </c>
-      <c r="K72" s="1" t="b">
+      <c r="K72" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L72" s="1">
-        <v>15</v>
-      </c>
-      <c r="M72" s="1">
+      <c r="L72" s="3">
+        <v>-1</v>
+      </c>
+      <c r="M72" s="3">
         <v>-0.29416456608148367</v>
       </c>
-      <c r="N72" s="1">
-        <v>38.35443037974683</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="P72" s="1">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="3">
+      <c r="N72" s="3">
+        <v>-18.647836973977373</v>
+      </c>
+      <c r="O72" s="3">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P72" s="3">
+        <v>19.4578633420253</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="R72" s="3">
+        <v>27.84810126582278</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="2">
         <v>0.61</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="2">
         <v>36.708860759493675</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="2">
         <v>22.40983606557377</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="2">
         <v>0.1</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="2">
         <v>0.2260761832650745</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="2">
         <v>1.17</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73" s="2">
         <v>62.34</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73" s="2">
         <v>42.04</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73" s="2">
         <v>0.03167383159955737</v>
       </c>
-      <c r="K73" s="3" t="b">
+      <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L73" s="3">
-        <v>14</v>
-      </c>
-      <c r="M73" s="3">
+      <c r="L73" s="2">
+        <v>25</v>
+      </c>
+      <c r="M73" s="2">
         <v>0.2425553366431652</v>
       </c>
-      <c r="N73" s="3">
+      <c r="N73" s="2">
+        <v>35.02415329848752</v>
+      </c>
+      <c r="O73" s="2">
+        <v>86.07594936708861</v>
+      </c>
+      <c r="P73" s="2">
+        <v>9.507882188735834</v>
+      </c>
+      <c r="Q73" s="2">
         <v>66.07594936708861</v>
       </c>
-      <c r="O73" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B74" s="3">
+      <c r="R73" s="2">
+        <v>61.51898734177215</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T73" s="2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B74" s="2">
         <v>0.96</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="2">
         <v>39.24050632911392</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="2">
         <v>14.25</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="2">
         <v>2.01</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="2">
         <v>0.16119109676979138</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="2">
         <v>0.79</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74" s="2">
         <v>82.84</v>
       </c>
-      <c r="I74" s="3">
+      <c r="I74" s="2">
         <v>31.87</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74" s="2">
         <v>0.022037295034327584</v>
       </c>
-      <c r="K74" s="3" t="b">
+      <c r="K74" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L74" s="3">
+      <c r="L74" s="2">
         <v>13</v>
       </c>
-      <c r="M74" s="3">
+      <c r="M74" s="2">
         <v>0.1408344955380323</v>
       </c>
-      <c r="N74" s="3">
+      <c r="N74" s="2">
+        <v>24.852069187974223</v>
+      </c>
+      <c r="O74" s="2">
+        <v>74.68354430379746</v>
+      </c>
+      <c r="P74" s="2">
+        <v>3.6747023875523213</v>
+      </c>
+      <c r="Q74" s="2">
         <v>65.56962025316456</v>
       </c>
-      <c r="O74" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="3">
+      <c r="R74" s="2">
+        <v>57.40506329113924</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T74" s="2">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="1">
         <v>0.44</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="1">
         <v>34.177215189873415</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="1">
         <v>29.204545454545453</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="1">
         <v>-0.71</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="1">
         <v>0.07659172329880896</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="1">
         <v>0.97</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75" s="1">
         <v>59.46</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I75" s="1">
         <v>14.74</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75" s="1">
         <v>0.005399889390566219</v>
       </c>
-      <c r="K75" s="3" t="b">
+      <c r="K75" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L75" s="3">
-        <v>9</v>
-      </c>
-      <c r="M75" s="3">
+      <c r="L75" s="1">
+        <v>20</v>
+      </c>
+      <c r="M75" s="1">
         <v>0.07368363740855766</v>
       </c>
-      <c r="N75" s="3">
+      <c r="N75" s="1">
+        <v>18.136983375026755</v>
+      </c>
+      <c r="O75" s="1">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P75" s="1">
+        <v>37.05001195108517</v>
+      </c>
+      <c r="Q75" s="1">
         <v>59.620253164556964</v>
       </c>
-      <c r="O75" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R75" s="1">
+        <v>46.582278481012665</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B76" s="1">
         <v>2.05</v>
@@ -5200,214 +6754,280 @@
         <v>0</v>
       </c>
       <c r="L76" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M76" s="1">
         <v>-0.06261187976545024</v>
       </c>
       <c r="N76" s="1">
-        <v>48.86075949367089</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P76" s="1"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B77" s="3">
+        <v>4.507431657625964</v>
+      </c>
+      <c r="O76" s="1">
+        <v>49.36708860759494</v>
+      </c>
+      <c r="P76" s="1">
+        <v>16.982798273104898</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>48.481012658227854</v>
+      </c>
+      <c r="R76" s="1">
+        <v>39.367088607594944</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="T76" s="1">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="2">
         <v>0.12</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="2">
         <v>31.645569620253166</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="2">
         <v>281.33333333333337</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="2">
         <v>-0.34</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="2">
         <v>-0.004879866713475789</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="2">
         <v>0.98</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77" s="2">
         <v>58.35</v>
       </c>
-      <c r="I77" s="3">
+      <c r="I77" s="2">
         <v>9.21</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77" s="2">
         <v>0.007734524845225627</v>
       </c>
-      <c r="K77" s="3" t="b">
+      <c r="K77" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L77" s="3">
+      <c r="L77" s="2">
+        <v>8</v>
+      </c>
+      <c r="M77" s="2">
+        <v>-0.006818590640309985</v>
+      </c>
+      <c r="N77" s="2">
+        <v>10.086760570140003</v>
+      </c>
+      <c r="O77" s="2">
+        <v>59.49367088607595</v>
+      </c>
+      <c r="P77" s="2">
+        <v>8.54788795515236</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>61.64556962025317</v>
+      </c>
+      <c r="R77" s="2">
+        <v>54.30379746835443</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T77" s="2">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="2">
+        <v>13.11</v>
+      </c>
+      <c r="C78" s="2">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="D78" s="2">
+        <v>-0.6994660564454616</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0.57</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0.15335529684028812</v>
+      </c>
+      <c r="G78" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="H78" s="2">
+        <v>69.85</v>
+      </c>
+      <c r="I78" s="2">
+        <v>35.04</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0.02697399814603973</v>
+      </c>
+      <c r="K78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2">
+        <v>64</v>
+      </c>
+      <c r="M78" s="2">
+        <v>0.17758934592571562</v>
+      </c>
+      <c r="N78" s="2">
+        <v>28.527554226742563</v>
+      </c>
+      <c r="O78" s="2">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="P78" s="2">
+        <v>20.806025084936465</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>60.506329113924046</v>
+      </c>
+      <c r="R78" s="2">
+        <v>50.50632911392405</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T78" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="2">
+        <v>3.07</v>
+      </c>
+      <c r="C79" s="2">
+        <v>50.63291139240506</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2.6156351791530943</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="F79" s="2">
+        <v>0.4334131898942318</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="H79" s="2">
+        <v>88.46</v>
+      </c>
+      <c r="I79" s="2">
+        <v>54.22</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.032420325485079365</v>
+      </c>
+      <c r="K79" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="M77" s="3">
-        <v>-0.006818590640309985</v>
-      </c>
-      <c r="N77" s="3">
-        <v>61.64556962025317</v>
-      </c>
-      <c r="O77" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B78" s="3">
-        <v>13.11</v>
-      </c>
-      <c r="C78" s="3">
-        <v>84.81012658227847</v>
-      </c>
-      <c r="D78" s="3">
-        <v>-0.660564454614798</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0.57</v>
-      </c>
-      <c r="F78" s="3">
-        <v>0.15335529684028812</v>
-      </c>
-      <c r="G78" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="H78" s="3">
-        <v>69.85</v>
-      </c>
-      <c r="I78" s="3">
-        <v>35.04</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0.02697399814603973</v>
-      </c>
-      <c r="K78" s="3" t="b">
+      <c r="L79" s="2">
+        <v>80</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0.43050510400398045</v>
+      </c>
+      <c r="N79" s="2">
+        <v>53.81913003456905</v>
+      </c>
+      <c r="O79" s="2">
+        <v>89.87341772151899</v>
+      </c>
+      <c r="P79" s="2">
+        <v>13.574555133673535</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>65.69620253164557</v>
+      </c>
+      <c r="R79" s="2">
+        <v>59.24050632911393</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="T79" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="2">
+        <v>8.72</v>
+      </c>
+      <c r="C80" s="2">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.8211009174311926</v>
+      </c>
+      <c r="E80" s="2">
+        <v>5.52</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0.9500398162459049</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="H80" s="2">
+        <v>62.97</v>
+      </c>
+      <c r="I80" s="2">
+        <v>64.4</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0.05298790653590615</v>
+      </c>
+      <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L78" s="3">
-        <v>68</v>
-      </c>
-      <c r="M78" s="3">
-        <v>0.17758934592571562</v>
-      </c>
-      <c r="N78" s="3">
-        <v>60.88607594936709</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="P78" s="3">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B79" s="3">
-        <v>3.07</v>
-      </c>
-      <c r="C79" s="3">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="D79" s="3">
-        <v>2.6156351791530943</v>
-      </c>
-      <c r="E79" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="F79" s="3">
-        <v>0.4334131898942318</v>
-      </c>
-      <c r="G79" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="H79" s="3">
-        <v>88.46</v>
-      </c>
-      <c r="I79" s="3">
-        <v>54.22</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0.032420325485079365</v>
-      </c>
-      <c r="K79" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L79" s="3">
-        <v>83</v>
-      </c>
-      <c r="M79" s="3">
-        <v>0.43050510400398045</v>
-      </c>
-      <c r="N79" s="3">
-        <v>66.07594936708861</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="P79" s="3">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B80" s="3">
-        <v>8.72</v>
-      </c>
-      <c r="C80" s="3">
-        <v>75.9493670886076</v>
-      </c>
-      <c r="D80" s="3">
-        <v>0.8211009174311926</v>
-      </c>
-      <c r="E80" s="3">
-        <v>5.52</v>
-      </c>
-      <c r="F80" s="3">
-        <v>0.9500398162459049</v>
-      </c>
-      <c r="G80" s="3">
-        <v>1.02</v>
-      </c>
-      <c r="H80" s="3">
-        <v>62.97</v>
-      </c>
-      <c r="I80" s="3">
-        <v>64.4</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0.05298790653590615</v>
-      </c>
-      <c r="K80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" s="3">
-        <v>147</v>
-      </c>
-      <c r="M80" s="3">
+      <c r="L80" s="2">
+        <v>141</v>
+      </c>
+      <c r="M80" s="2">
         <v>0.9519785401727392</v>
       </c>
-      <c r="N80" s="3">
-        <v>69.746835443038</v>
-      </c>
-      <c r="O80" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="P80" s="3"/>
+      <c r="N80" s="2">
+        <v>105.96647365144491</v>
+      </c>
+      <c r="O80" s="2">
+        <v>97.46835443037975</v>
+      </c>
+      <c r="P80" s="2">
+        <v>14.059118714058641</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>69.36708860759495</v>
+      </c>
+      <c r="R80" s="2">
+        <v>65.37974683544304</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T80" s="2">
+        <v>1.14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5422,10 +7042,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5433,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>45.18987341772152</v>
+        <v>35.9493670886076</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5441,7 +7061,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>75.69620253164557</v>
+        <v>65.31645569620254</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5449,7 +7069,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>33.79746835443037</v>
+        <v>15.126582278481017</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5457,7 +7077,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>59.74683544303797</v>
+        <v>43.670886075949376</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5465,7 +7085,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>37.594936708860764</v>
+        <v>41.39240506329114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5473,7 +7093,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>63.54430379746835</v>
+        <v>55.12658227848102</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5481,7 +7101,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>66.45569620253164</v>
+        <v>55.25316455696202</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5489,7 +7109,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>48.10126582278481</v>
+        <v>40.56962025316455</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5497,7 +7117,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>46.582278481012665</v>
+        <v>37.59493670886076</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5505,7 +7125,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>56.07594936708861</v>
+        <v>47.21518987341773</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5513,7 +7133,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>41.898734177215196</v>
+        <v>22.341772151898734</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5521,7 +7141,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>26.962025316455698</v>
+        <v>12.72151898734177</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -5529,7 +7149,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>55.569620253164565</v>
+        <v>36.45569620253165</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -5537,7 +7157,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>69.11392405063292</v>
+        <v>61.962025316455694</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5545,7 +7165,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>42.40506329113924</v>
+        <v>37.65822784810127</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5553,7 +7173,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>24.55696202531645</v>
+        <v>18.227848101265824</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5561,7 +7181,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>47.08860759493671</v>
+        <v>29.556962025316462</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5569,7 +7189,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>54.17721518987342</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5577,7 +7197,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37.21518987341772</v>
+        <v>33.9873417721519</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -5585,7 +7205,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>62.65822784810127</v>
+        <v>47.34177215189873</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -5593,7 +7213,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>40.50632911392404</v>
+        <v>30.18987341772152</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -5601,7 +7221,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>45.56962025316456</v>
+        <v>35.443037974683534</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -5609,7 +7229,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>28.9873417721519</v>
+        <v>28.417721518987342</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5617,7 +7237,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>27.341772151898734</v>
+        <v>9.177215189873419</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -5625,7 +7245,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>39.367088607594944</v>
+        <v>32.278481012658226</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -5633,7 +7253,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>36.20253164556962</v>
+        <v>25.063291139240505</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -5641,7 +7261,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>33.67088607594936</v>
+        <v>20.253164556962027</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -5649,7 +7269,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>41.518987341772146</v>
+        <v>24.746835443037973</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5657,7 +7277,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>63.037974683544306</v>
+        <v>46.32911392405064</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -5665,7 +7285,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>68.48101265822785</v>
+        <v>60.9493670886076</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -5673,7 +7293,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>34.810126582278485</v>
+        <v>15.632911392405063</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -5681,7 +7301,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>52.65822784810126</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -5689,7 +7309,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>61.01265822784811</v>
+        <v>50.949367088607595</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -5697,7 +7317,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>33.037974683544306</v>
+        <v>23.037974683544302</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5705,7 +7325,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>38.35443037974683</v>
+        <v>30.696202531645564</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -5713,7 +7333,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>38.48101265822785</v>
+        <v>37.84810126582279</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -5721,7 +7341,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>64.81012658227849</v>
+        <v>54.43037974683544</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -5729,7 +7349,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>56.45569620253165</v>
+        <v>52.34177215189874</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -5737,7 +7357,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>37.34177215189874</v>
+        <v>33.101265822784804</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -5745,7 +7365,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>44.55696202531645</v>
+        <v>30.44303797468355</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -5753,7 +7373,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>41.64556962025316</v>
+        <v>37.72151898734177</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5761,7 +7381,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>53.67088607594937</v>
+        <v>44.55696202531645</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5769,7 +7389,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>39.99999999999999</v>
+        <v>29.177215189873415</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -5777,7 +7397,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>62.65822784810127</v>
+        <v>57.34177215189874</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -5785,7 +7405,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>50.12658227848101</v>
+        <v>30.379746835443033</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5793,7 +7413,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>38.9873417721519</v>
+        <v>25.25316455696202</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5801,7 +7421,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>71.13924050632912</v>
+        <v>63.60759493670886</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -5809,7 +7429,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>73.0379746835443</v>
+        <v>62.594936708860764</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -5817,7 +7437,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>38.22784810126583</v>
+        <v>21.77215189873418</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -5825,7 +7445,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>32.911392405063296</v>
+        <v>41.329113924050645</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5833,7 +7453,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>65.94936708860759</v>
+        <v>54.68354430379747</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5841,7 +7461,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>47.46835443037975</v>
+        <v>33.22784810126582</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -5849,7 +7469,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>67.21518987341771</v>
+        <v>51.13924050632911</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -5857,7 +7477,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>46.962025316455694</v>
+        <v>38.67088607594937</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -5865,7 +7485,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>45.18987341772152</v>
+        <v>36.32911392405063</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5873,7 +7493,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>80.63291139240506</v>
+        <v>66.89873417721519</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -5881,7 +7501,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>64.43037974683544</v>
+        <v>54.24050632911392</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5889,7 +7509,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>59.74683544303797</v>
+        <v>56.898734177215196</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -5897,7 +7517,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>37.59493670886076</v>
+        <v>30.506329113924046</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -5905,7 +7525,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>53.16455696202532</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -5913,7 +7533,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>83.29113924050633</v>
+        <v>72.02531645569621</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -5921,7 +7541,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>78.48101265822785</v>
+        <v>67.02531645569621</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -5929,7 +7549,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>47.46835443037975</v>
+        <v>33.924050632911396</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -5937,7 +7557,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>39.87341772151898</v>
+        <v>31.89873417721519</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5945,7 +7565,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>50.75949367088608</v>
+        <v>44.43037974683545</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -5953,7 +7573,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>59.74683544303798</v>
+        <v>44.11392405063291</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -5961,7 +7581,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>36.45569620253164</v>
+        <v>26.139240506329113</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5969,7 +7589,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>37.848101265822784</v>
+        <v>26.898734177215186</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -5977,7 +7597,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>36.075949367088604</v>
+        <v>22.151898734177216</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -5985,7 +7605,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>42.9113924050633</v>
+        <v>28.227848101265828</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -5993,71 +7613,71 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>38.35443037974683</v>
+        <v>27.84810126582278</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B73">
-        <v>66.07594936708861</v>
+        <v>61.51898734177215</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B74">
-        <v>65.56962025316456</v>
+        <v>57.40506329113924</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B75">
-        <v>59.620253164556964</v>
+        <v>46.582278481012665</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B76">
-        <v>48.86075949367089</v>
+        <v>39.367088607594944</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B77">
-        <v>61.64556962025317</v>
+        <v>54.30379746835443</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B78">
-        <v>60.88607594936709</v>
+        <v>50.50632911392405</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B79">
-        <v>66.07594936708861</v>
+        <v>59.24050632911393</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B80">
-        <v>69.746835443038</v>
+        <v>65.37974683544304</v>
       </c>
     </row>
   </sheetData>
@@ -6076,137 +7696,137 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -6225,114 +7845,114 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -6351,10 +7971,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6362,112 +7982,112 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -6486,125 +8106,125 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -6615,231 +8235,217 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>189</v>
+      <c r="A11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>189</v>
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" t="s">
         <v>199</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>189</v>
+      <c r="D13" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>189</v>
+      <c r="A14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-16</t>
+    <t>2026-05-17</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -1394,7 +1394,7 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <v>66.89873417721519</v>
+        <v>66.77215189873418</v>
       </c>
       <c r="C4" t="s">
         <v>216</v>
@@ -1790,7 +1790,7 @@
         <v>15</v>
       </c>
       <c r="B40">
-        <v>37.65822784810127</v>
+        <v>37.53164556962025</v>
       </c>
       <c r="C40" t="s">
         <v>221</v>
@@ -2145,7 +2145,7 @@
         <v>-1.5446880269814502</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.05</v>
+        <v>0.4</v>
       </c>
       <c r="F2" s="1">
         <v>0.03656337889124221</v>
@@ -2207,7 +2207,7 @@
         <v>24.108196721311476</v>
       </c>
       <c r="E3" s="2">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="F3" s="2">
         <v>0.7993249441093764</v>
@@ -2269,7 +2269,7 @@
         <v>9.865822784810128</v>
       </c>
       <c r="E4" s="3">
-        <v>2.62</v>
+        <v>1.25</v>
       </c>
       <c r="F4" s="3">
         <v>-0.2535364508958835</v>
@@ -2331,7 +2331,7 @@
         <v>23.917431192660548</v>
       </c>
       <c r="E5" s="1">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="F5" s="1">
         <v>-0.1747058861985029</v>
@@ -2393,7 +2393,7 @@
         <v>1.4271844660194175</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.4</v>
+        <v>-0.11</v>
       </c>
       <c r="F6" s="1">
         <v>-0.025082632229554647</v>
@@ -2455,7 +2455,7 @@
         <v>6.293877551020408</v>
       </c>
       <c r="E7" s="2">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="F7" s="2">
         <v>0.002710766112608426</v>
@@ -2517,7 +2517,7 @@
         <v>-0.012084592145015116</v>
       </c>
       <c r="E8" s="2">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="F8" s="2">
         <v>0.2685989729401681</v>
@@ -2579,7 +2579,7 @@
         <v>46.2247191011236</v>
       </c>
       <c r="E9" s="1">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="F9" s="1">
         <v>-0.13555171012196826</v>
@@ -2641,7 +2641,7 @@
         <v>0.49919999999999987</v>
       </c>
       <c r="E10" s="1">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="F10" s="1">
         <v>-0.17331904401626377</v>
@@ -2703,7 +2703,7 @@
         <v>31.911764705882348</v>
       </c>
       <c r="E11" s="1">
-        <v>8.3</v>
+        <v>5.47</v>
       </c>
       <c r="F11" s="1">
         <v>0.12533555255876536</v>
@@ -2765,7 +2765,7 @@
         <v>65.70588235294117</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.32</v>
+        <v>5.82</v>
       </c>
       <c r="F12" s="3">
         <v>-0.2905302085040573</v>
@@ -2827,7 +2827,7 @@
         <v>-1653.5</v>
       </c>
       <c r="E13" s="3">
-        <v>2.73</v>
+        <v>1.61</v>
       </c>
       <c r="F13" s="3">
         <v>-0.24695705804821247</v>
@@ -2889,7 +2889,7 @@
         <v>7.580152671755725</v>
       </c>
       <c r="E14" s="1">
-        <v>0.33</v>
+        <v>-0.14</v>
       </c>
       <c r="F14" s="1">
         <v>-0.12133656204260415</v>
@@ -2951,7 +2951,7 @@
         <v>62.85714285714286</v>
       </c>
       <c r="E15" s="2">
-        <v>5.78</v>
+        <v>5.49</v>
       </c>
       <c r="F15" s="2">
         <v>1.098693544416193</v>
@@ -3013,7 +3013,7 @@
         <v>12.218130311614733</v>
       </c>
       <c r="E16" s="1">
-        <v>4.52</v>
+        <v>8.13</v>
       </c>
       <c r="F16" s="1">
         <v>-0.04425532051485587</v>
@@ -3052,13 +3052,13 @@
         <v>42.0253164556962</v>
       </c>
       <c r="R16" s="1">
-        <v>37.65822784810127</v>
+        <v>37.53164556962025</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="1">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3075,7 +3075,7 @@
         <v>4.355877616747182</v>
       </c>
       <c r="E17" s="3">
-        <v>4.89</v>
+        <v>4.24</v>
       </c>
       <c r="F17" s="3">
         <v>-0.2643194481130663</v>
@@ -3137,7 +3137,7 @@
         <v>1446.3333333333333</v>
       </c>
       <c r="E18" s="3">
-        <v>9.43</v>
+        <v>8.39</v>
       </c>
       <c r="F18" s="3">
         <v>-0.34700555328245314</v>
@@ -3199,7 +3199,7 @@
         <v>0.24463519313304713</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.43</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" s="1">
         <v>-0.048303366108382144</v>
@@ -3261,7 +3261,7 @@
         <v>0.728171334431631</v>
       </c>
       <c r="E20" s="1">
-        <v>-2.3</v>
+        <v>-3.42</v>
       </c>
       <c r="F20" s="1">
         <v>-0.1448213611214662</v>
@@ -3323,7 +3323,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="1">
-        <v>5.19</v>
+        <v>4.96</v>
       </c>
       <c r="F21" s="1">
         <v>0.0735583537615512</v>
@@ -3385,7 +3385,7 @@
         <v>0.6942046855733663</v>
       </c>
       <c r="E22" s="1">
-        <v>0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="F22" s="1">
         <v>-0.24902962388139738</v>
@@ -3447,7 +3447,7 @@
         <v>-0.7706288622319157</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="F23" s="1">
         <v>-0.16990217780303657</v>
@@ -3509,7 +3509,7 @@
         <v>-0.3107569721115539</v>
       </c>
       <c r="E24" s="3">
-        <v>9.38</v>
+        <v>13.86</v>
       </c>
       <c r="F24" s="3">
         <v>-0.03159567105820904</v>
@@ -3571,7 +3571,7 @@
         <v>0.8859649122807016</v>
       </c>
       <c r="E25" s="3">
-        <v>11.91</v>
+        <v>14.49</v>
       </c>
       <c r="F25" s="3">
         <v>-0.441182512906166</v>
@@ -3633,7 +3633,7 @@
         <v>-2571.7647058823527</v>
       </c>
       <c r="E26" s="1">
-        <v>4.67</v>
+        <v>3.56</v>
       </c>
       <c r="F26" s="1">
         <v>0.21466965129619875</v>
@@ -3695,7 +3695,7 @@
         <v>1.0176991150442478</v>
       </c>
       <c r="E27" s="3">
-        <v>1.65</v>
+        <v>5.04</v>
       </c>
       <c r="F27" s="3">
         <v>-0.21825818230701438</v>
@@ -3757,7 +3757,7 @@
         <v>7.536363636363636</v>
       </c>
       <c r="E28" s="3">
-        <v>-0.68</v>
+        <v>-1.13</v>
       </c>
       <c r="F28" s="3">
         <v>-0.42051181481840655</v>
@@ -3819,7 +3819,7 @@
         <v>77.04545454545456</v>
       </c>
       <c r="E29" s="3">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="F29" s="3">
         <v>-0.419262979032475</v>
@@ -3881,7 +3881,7 @@
         <v>2523.594871794872</v>
       </c>
       <c r="E30" s="1">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="F30" s="1">
         <v>-0.2195577976440304</v>
@@ -3943,7 +3943,7 @@
         <v>10.690058479532164</v>
       </c>
       <c r="E31" s="2">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="F31" s="2">
         <v>0.15822414412232277</v>
@@ -4005,7 +4005,7 @@
         <v>8.178082191780822</v>
       </c>
       <c r="E32" s="3">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="F32" s="3">
         <v>-0.38807011843937855</v>
@@ -4067,7 +4067,7 @@
         <v>-0.05896366885050616</v>
       </c>
       <c r="E33" s="1">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="F33" s="1">
         <v>-0.06411046878691452</v>
@@ -4129,7 +4129,7 @@
         <v>-0.7025171624713958</v>
       </c>
       <c r="E34" s="2">
-        <v>0.58</v>
+        <v>0.94</v>
       </c>
       <c r="F34" s="2">
         <v>0.16496462914942378</v>
@@ -4188,10 +4188,10 @@
         <v>91.13924050632912</v>
       </c>
       <c r="D35" s="3">
-        <v>-0.47898675877950486</v>
+        <v>-0.4801381692573403</v>
       </c>
       <c r="E35" s="3">
-        <v>-0.96</v>
+        <v>4.55</v>
       </c>
       <c r="F35" s="3">
         <v>-0.3016835226741067</v>
@@ -4224,19 +4224,19 @@
         <v>11.39240506329114</v>
       </c>
       <c r="P35" s="3">
-        <v>31.050134736892222</v>
+        <v>29.946003174037394</v>
       </c>
       <c r="Q35" s="3">
         <v>32.65822784810126</v>
       </c>
       <c r="R35" s="3">
-        <v>23.037974683544302</v>
+        <v>23.29113924050633</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>0.38488271068635965</v>
       </c>
       <c r="E36" s="1">
-        <v>-0.97</v>
+        <v>-1.05</v>
       </c>
       <c r="F36" s="1">
         <v>-0.19098513098420686</v>
@@ -4315,7 +4315,7 @@
         <v>0.6060037523452159</v>
       </c>
       <c r="E37" s="1">
-        <v>0.52</v>
+        <v>1.72</v>
       </c>
       <c r="F37" s="1">
         <v>-0.04129399285351304</v>
@@ -4348,7 +4348,7 @@
         <v>60.75949367088608</v>
       </c>
       <c r="P37" s="1">
-        <v>35.0614795066832</v>
+        <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
         <v>38.10126582278481</v>
@@ -4377,7 +4377,7 @@
         <v>36.648648648648646</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="F38" s="2">
         <v>0.26342049006394885</v>
@@ -4439,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="E39" s="2">
-        <v>-7.97</v>
+        <v>-6.6</v>
       </c>
       <c r="F39" s="2">
         <v>0.06794935342768335</v>
@@ -4501,7 +4501,7 @@
         <v>10.018720748829953</v>
       </c>
       <c r="E40" s="1">
-        <v>12.27</v>
+        <v>10.16</v>
       </c>
       <c r="F40" s="1">
         <v>0.11310755946653876</v>
@@ -4563,7 +4563,7 @@
         <v>7.415506958250497</v>
       </c>
       <c r="E41" s="1">
-        <v>-1.75</v>
+        <v>-1.71</v>
       </c>
       <c r="F41" s="1">
         <v>-0.029972241879371517</v>
@@ -4622,10 +4622,10 @@
         <v>53.16455696202531</v>
       </c>
       <c r="D42" s="1">
-        <v>1.0831024930747921</v>
+        <v>1.0775623268698062</v>
       </c>
       <c r="E42" s="1">
-        <v>-0.1</v>
+        <v>0.29</v>
       </c>
       <c r="F42" s="1">
         <v>-0.11210518309493923</v>
@@ -4687,7 +4687,7 @@
         <v>1214</v>
       </c>
       <c r="E43" s="1">
-        <v>5.23</v>
+        <v>6.54</v>
       </c>
       <c r="F43" s="1">
         <v>-0.05089839962555098</v>
@@ -4749,7 +4749,7 @@
         <v>26.91176470588235</v>
       </c>
       <c r="E44" s="3">
-        <v>-1.51</v>
+        <v>-1.94</v>
       </c>
       <c r="F44" s="3">
         <v>-0.37008009296786126</v>
@@ -4811,7 +4811,7 @@
         <v>0.821983273596177</v>
       </c>
       <c r="E45" s="2">
-        <v>0.94</v>
+        <v>1.15</v>
       </c>
       <c r="F45" s="2">
         <v>0.1774315040334033</v>
@@ -4873,7 +4873,7 @@
         <v>543.5000000000001</v>
       </c>
       <c r="E46" s="1">
-        <v>-0.94</v>
+        <v>-0.24</v>
       </c>
       <c r="F46" s="1">
         <v>-0.26667139695523195</v>
@@ -4935,7 +4935,7 @@
         <v>0.8549905838041432</v>
       </c>
       <c r="E47" s="3">
-        <v>-4.11</v>
+        <v>-3.9</v>
       </c>
       <c r="F47" s="3">
         <v>-0.457975392465942</v>
@@ -4997,7 +4997,7 @@
         <v>7.675879396984925</v>
       </c>
       <c r="E48" s="2">
-        <v>-1.16</v>
+        <v>-0.69</v>
       </c>
       <c r="F48" s="2">
         <v>0.36634599216298047</v>
@@ -5059,7 +5059,7 @@
         <v>1709.8333333333335</v>
       </c>
       <c r="E49" s="2">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="F49" s="2">
         <v>0.5966006262232061</v>
@@ -5121,7 +5121,7 @@
         <v>300.1538461538462</v>
       </c>
       <c r="E50" s="3">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="F50" s="3">
         <v>-0.46770435480298933</v>
@@ -5183,7 +5183,7 @@
         <v>13.440721649484537</v>
       </c>
       <c r="E51" s="1">
-        <v>17.05</v>
+        <v>16.72</v>
       </c>
       <c r="F51" s="1">
         <v>0.02092920462188544</v>
@@ -5245,7 +5245,7 @@
         <v>6.496226415094339</v>
       </c>
       <c r="E52" s="2">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="F52" s="2">
         <v>0.01973553992918095</v>
@@ -5307,7 +5307,7 @@
         <v>12.042253521126762</v>
       </c>
       <c r="E53" s="1">
-        <v>6.97</v>
+        <v>6.64</v>
       </c>
       <c r="F53" s="1">
         <v>-0.22656157373327646</v>
@@ -5369,7 +5369,7 @@
         <v>41.629629629629626</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="F54" s="2">
         <v>-0.05302157269131072</v>
@@ -5431,7 +5431,7 @@
         <v>2.2580645161290325</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="F55" s="1">
         <v>-0.1790060492823699</v>
@@ -5493,7 +5493,7 @@
         <v>0.1757225433526011</v>
       </c>
       <c r="E56" s="1">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="F56" s="1">
         <v>-0.10471492447755065</v>
@@ -5555,7 +5555,7 @@
         <v>2.35505193578848</v>
       </c>
       <c r="E57" s="2">
-        <v>0.39</v>
+        <v>0.11</v>
       </c>
       <c r="F57" s="2">
         <v>0.5547443642327915</v>
@@ -5594,13 +5594,13 @@
         <v>80.25316455696203</v>
       </c>
       <c r="R57" s="2">
-        <v>66.89873417721519</v>
+        <v>66.77215189873418</v>
       </c>
       <c r="S57" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T57" s="2">
-        <v>-0.44</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5617,7 +5617,7 @@
         <v>0.09701492537313429</v>
       </c>
       <c r="E58" s="2">
-        <v>-1.9</v>
+        <v>-1.46</v>
       </c>
       <c r="F58" s="2">
         <v>-0.020395804242056392</v>
@@ -5679,7 +5679,7 @@
         <v>-1.4889277389277389</v>
       </c>
       <c r="E59" s="2">
-        <v>-2.43</v>
+        <v>-2.31</v>
       </c>
       <c r="F59" s="2">
         <v>0.17904261223547482</v>
@@ -5741,7 +5741,7 @@
         <v>-0.13029827315541603</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.23</v>
+        <v>0.62</v>
       </c>
       <c r="F60" s="1">
         <v>-0.1489477353062037</v>
@@ -5803,7 +5803,7 @@
         <v>0.6178128523111613</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.38</v>
+        <v>-0.07</v>
       </c>
       <c r="F61" s="1">
         <v>-0.17099099367816528</v>
@@ -5865,7 +5865,7 @@
         <v>4.831074035453597</v>
       </c>
       <c r="E62" s="4">
-        <v>-8.63</v>
+        <v>-8.13</v>
       </c>
       <c r="F62" s="4">
         <v>0.7870039611746505</v>
@@ -5927,7 +5927,7 @@
         <v>6.3927893738140416</v>
       </c>
       <c r="E63" s="2">
-        <v>-4.36</v>
+        <v>-5.36</v>
       </c>
       <c r="F63" s="2">
         <v>0.659813799317615</v>
@@ -5989,7 +5989,7 @@
         <v>-0.27504445761707175</v>
       </c>
       <c r="E64" s="1">
-        <v>-0.69</v>
+        <v>-0.88</v>
       </c>
       <c r="F64" s="1">
         <v>-0.15173270683304146</v>
@@ -6051,7 +6051,7 @@
         <v>-0.10837118754055808</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="F65" s="1">
         <v>-0.12564894128578813</v>
@@ -6113,7 +6113,7 @@
         <v>7.266832917705736</v>
       </c>
       <c r="E66" s="1">
-        <v>-0.9</v>
+        <v>-1.48</v>
       </c>
       <c r="F66" s="1">
         <v>-0.04838973089937444</v>
@@ -6175,7 +6175,7 @@
         <v>121.84625850340136</v>
       </c>
       <c r="E67" s="1">
-        <v>0.3</v>
+        <v>-0.18</v>
       </c>
       <c r="F67" s="1">
         <v>-0.20663102503993735</v>
@@ -6237,7 +6237,7 @@
         <v>0.6286407766990291</v>
       </c>
       <c r="E68" s="3">
-        <v>-0.07</v>
+        <v>0.19</v>
       </c>
       <c r="F68" s="3">
         <v>-0.2874281543757484</v>
@@ -6299,7 +6299,7 @@
         <v>-0.47608576140736675</v>
       </c>
       <c r="E69" s="3">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="F69" s="3">
         <v>-0.22580565225190932</v>
@@ -6361,7 +6361,7 @@
         <v>13.532894736842104</v>
       </c>
       <c r="E70" s="3">
-        <v>-0.78</v>
+        <v>-1.56</v>
       </c>
       <c r="F70" s="3">
         <v>-0.45495617366977387</v>
@@ -6423,7 +6423,7 @@
         <v>0.7837837837837839</v>
       </c>
       <c r="E71" s="3">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="F71" s="3">
         <v>-0.257648719824491</v>
@@ -6485,7 +6485,7 @@
         <v>0.21305182341650677</v>
       </c>
       <c r="E72" s="3">
-        <v>-1.31</v>
+        <v>-1.49</v>
       </c>
       <c r="F72" s="3">
         <v>-0.30773563356932304</v>
@@ -6547,7 +6547,7 @@
         <v>22.40983606557377</v>
       </c>
       <c r="E73" s="2">
-        <v>0.1</v>
+        <v>-1.26</v>
       </c>
       <c r="F73" s="2">
         <v>0.2260761832650745</v>
@@ -6671,7 +6671,7 @@
         <v>29.204545454545453</v>
       </c>
       <c r="E75" s="1">
-        <v>-0.71</v>
+        <v>-2.27</v>
       </c>
       <c r="F75" s="1">
         <v>0.07659172329880896</v>
@@ -6733,7 +6733,7 @@
         <v>0.7170731707317075</v>
       </c>
       <c r="E76" s="1">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="F76" s="1">
         <v>-0.035469744789771454</v>
@@ -6795,7 +6795,7 @@
         <v>281.33333333333337</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="F77" s="2">
         <v>-0.004879866713475789</v>
@@ -6857,7 +6857,7 @@
         <v>-0.6994660564454616</v>
       </c>
       <c r="E78" s="2">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="F78" s="2">
         <v>0.15335529684028812</v>
@@ -6919,7 +6919,7 @@
         <v>2.6156351791530943</v>
       </c>
       <c r="E79" s="2">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="F79" s="2">
         <v>0.4334131898942318</v>
@@ -6981,7 +6981,7 @@
         <v>0.8211009174311926</v>
       </c>
       <c r="E80" s="2">
-        <v>5.52</v>
+        <v>4.67</v>
       </c>
       <c r="F80" s="2">
         <v>0.9500398162459049</v>
@@ -7165,7 +7165,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>37.65822784810127</v>
+        <v>37.53164556962025</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7317,7 +7317,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>23.037974683544302</v>
+        <v>23.29113924050633</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>66.89873417721519</v>
+        <v>66.77215189873418</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="228">
   <si>
     <t>Ticker</t>
   </si>
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-17</t>
+    <t>2026-05-18</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -679,34 +679,31 @@
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming</t>
+  </si>
+  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Momentum Breakout, Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1380,7 @@
         <v>62</v>
       </c>
       <c r="B3">
-        <v>67.02531645569621</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="C3" t="s">
         <v>215</v>
@@ -1402,32 +1399,32 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>65.37974683544304</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="B6">
         <v>65.31645569620254</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7">
-        <v>63.60759493670886</v>
+        <v>62.21518987341772</v>
       </c>
       <c r="C7" t="s">
         <v>215</v>
@@ -1435,13 +1432,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B8">
-        <v>62.594936708860764</v>
+        <v>62.151898734177216</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1457,13 +1454,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="B10">
-        <v>61.51898734177215</v>
+        <v>61.77215189873418</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1471,7 +1468,7 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>60.9493670886076</v>
+        <v>59.81012658227849</v>
       </c>
       <c r="C11" t="s">
         <v>218</v>
@@ -1482,7 +1479,7 @@
         <v>126</v>
       </c>
       <c r="B12">
-        <v>59.24050632911393</v>
+        <v>59.74683544303798</v>
       </c>
       <c r="C12" t="s">
         <v>216</v>
@@ -1493,7 +1490,7 @@
         <v>120</v>
       </c>
       <c r="B13">
-        <v>57.40506329113924</v>
+        <v>57.27848101265823</v>
       </c>
       <c r="C13" t="s">
         <v>218</v>
@@ -1504,7 +1501,7 @@
         <v>44</v>
       </c>
       <c r="B14">
-        <v>57.34177215189874</v>
+        <v>56.32911392405063</v>
       </c>
       <c r="C14" t="s">
         <v>218</v>
@@ -1512,109 +1509,109 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B15">
-        <v>56.898734177215196</v>
+        <v>55.44303797468355</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="B16">
-        <v>55.25316455696202</v>
+        <v>55.44303797468354</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B17">
-        <v>55.12658227848102</v>
+        <v>55.189873417721515</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B18">
-        <v>54.68354430379747</v>
+        <v>55.12658227848102</v>
       </c>
       <c r="C18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B19">
-        <v>54.43037974683544</v>
+        <v>55.12658227848101</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="B20">
-        <v>54.30379746835443</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B21">
-        <v>54.24050632911392</v>
+        <v>54.74683544303797</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B22">
-        <v>52.34177215189874</v>
+        <v>54.62025316455696</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>51.13924050632911</v>
+        <v>52.46835443037974</v>
       </c>
       <c r="C23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="B24">
-        <v>50.949367088607595</v>
+        <v>51.51898734177215</v>
       </c>
       <c r="C24" t="s">
         <v>218</v>
@@ -1622,10 +1619,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="B25">
-        <v>50.50632911392405</v>
+        <v>50.12658227848102</v>
       </c>
       <c r="C25" t="s">
         <v>218</v>
@@ -1633,24 +1630,24 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B26">
-        <v>47.34177215189873</v>
+        <v>49.11392405063291</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>47.21518987341773</v>
+        <v>48.60759493670886</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,10 +1655,10 @@
         <v>122</v>
       </c>
       <c r="B28">
-        <v>46.582278481012665</v>
+        <v>46.455696202531655</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,54 +1666,54 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>46.32911392405064</v>
+        <v>44.683544303797476</v>
       </c>
       <c r="C29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B30">
-        <v>44.55696202531645</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>44.11392405063291</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B32">
-        <v>42.27848101265823</v>
+        <v>43.734177215189874</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B33">
-        <v>42.27848101265823</v>
+        <v>42.911392405063296</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1724,87 +1721,87 @@
         <v>60</v>
       </c>
       <c r="B34">
-        <v>42.27848101265823</v>
+        <v>42.0253164556962</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>41.39240506329114</v>
+        <v>41.0126582278481</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B36">
-        <v>41.329113924050645</v>
+        <v>39.55696202531645</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="B37">
-        <v>39.367088607594944</v>
+        <v>39.050632911392405</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="B38">
-        <v>37.84810126582279</v>
+        <v>38.98734177215191</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B39">
-        <v>37.72151898734177</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>37.53164556962025</v>
+        <v>37.848101265822784</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B41">
-        <v>36.45569620253165</v>
+        <v>37.40506329113924</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1812,21 +1809,21 @@
         <v>55</v>
       </c>
       <c r="B42">
-        <v>36.32911392405063</v>
+        <v>37.21518987341772</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="B43">
-        <v>35.9493670886076</v>
+        <v>36.64556962025316</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1834,54 +1831,54 @@
         <v>22</v>
       </c>
       <c r="B44">
-        <v>35.443037974683534</v>
+        <v>34.810126582278485</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B45">
-        <v>33.9873417721519</v>
+        <v>33.924050632911396</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B46">
-        <v>33.924050632911396</v>
+        <v>33.481012658227854</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B47">
-        <v>33.22784810126582</v>
+        <v>32.974683544303794</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B48">
-        <v>33.101265822784804</v>
+        <v>32.594936708860764</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1892,29 +1889,29 @@
         <v>32.278481012658226</v>
       </c>
       <c r="C49" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B50">
         <v>31.89873417721519</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B51">
-        <v>30.696202531645564</v>
+        <v>31.582278481012654</v>
       </c>
       <c r="C51" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2148,49 +2145,49 @@
         <v>0.4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.03656337889124221</v>
+        <v>0.0703542356368584</v>
       </c>
       <c r="G2" s="1">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>59.38</v>
+        <v>62.55</v>
       </c>
       <c r="I2" s="1">
-        <v>21.6</v>
+        <v>23.35</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0004454689878052024</v>
+        <v>0.0020085720201510784</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.04389366407237705</v>
+        <v>-0.005785915926084906</v>
       </c>
       <c r="N2" s="1">
-        <v>6.3792532269333</v>
+        <v>9.781792744335805</v>
       </c>
       <c r="O2" s="1">
-        <v>53.16455696202531</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>44.810126582278485</v>
+        <v>46.70886075949367</v>
       </c>
       <c r="R2" s="1">
-        <v>35.9493670886076</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>3.1</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2204,55 +2201,55 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>24.108196721311476</v>
+        <v>24.104918032786884</v>
       </c>
       <c r="E3" s="2">
         <v>1.88</v>
       </c>
       <c r="F3" s="2">
-        <v>0.7993249441093764</v>
+        <v>0.8384975794067261</v>
       </c>
       <c r="G3" s="2">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="H3" s="2">
-        <v>67.29</v>
+        <v>66.23</v>
       </c>
       <c r="I3" s="2">
-        <v>89.17</v>
+        <v>86.76</v>
       </c>
       <c r="J3" s="2">
-        <v>0.09705513962480551</v>
+        <v>0.09281022506883387</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M3" s="2">
-        <v>0.9379437048780217</v>
+        <v>0.9694214985576408</v>
       </c>
       <c r="N3" s="2">
-        <v>104.56299012197317</v>
+        <v>107.3025341927084</v>
       </c>
       <c r="O3" s="2">
-        <v>96.20253164556962</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.69620253164557</v>
+        <v>75.82278481012658</v>
       </c>
       <c r="R3" s="2">
-        <v>65.31645569620254</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.38</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2272,19 +2269,19 @@
         <v>1.25</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.2535364508958835</v>
+        <v>-0.18550357082975716</v>
       </c>
       <c r="G4" s="3">
         <v>1.1</v>
       </c>
       <c r="H4" s="3">
-        <v>58.05</v>
+        <v>63.05</v>
       </c>
       <c r="I4" s="3">
-        <v>-22.73</v>
+        <v>-19.29</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.011052941902859758</v>
+        <v>-0.010990832169679707</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
@@ -2293,28 +2290,28 @@
         <v>-88</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.24384283126171247</v>
+        <v>-0.17621818649281284</v>
       </c>
       <c r="N4" s="3">
-        <v>-13.615663492000246</v>
+        <v>-7.261434312336975</v>
       </c>
       <c r="O4" s="3">
-        <v>16.455696202531644</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>33.417721518987335</v>
+        <v>35.56962025316456</v>
       </c>
       <c r="R4" s="3">
-        <v>15.126582278481017</v>
+        <v>19.430379746835445</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>0.32</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2334,19 +2331,19 @@
         <v>0.73</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.1747058861985029</v>
+        <v>-0.17851699600328538</v>
       </c>
       <c r="G5" s="1">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H5" s="1">
-        <v>57.96</v>
+        <v>52.68</v>
       </c>
       <c r="I5" s="1">
-        <v>3.64</v>
+        <v>0.51</v>
       </c>
       <c r="J5" s="1">
-        <v>0.009369255969228586</v>
+        <v>0.00782628272587361</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2355,28 +2352,28 @@
         <v>-81</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.09618756716171784</v>
+        <v>-0.10516245974142535</v>
       </c>
       <c r="N5" s="1">
-        <v>1.1498629179992155</v>
+        <v>-0.1558616371982243</v>
       </c>
       <c r="O5" s="1">
-        <v>45.56962025316456</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P5" s="1">
         <v>29.766948563835548</v>
       </c>
       <c r="Q5" s="1">
-        <v>59.74683544303797</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="R5" s="1">
-        <v>43.670886075949376</v>
+        <v>42.278481012658226</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.65</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2396,49 +2393,49 @@
         <v>-0.11</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.025082632229554647</v>
+        <v>0.0114693537470755</v>
       </c>
       <c r="G6" s="1">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>36.73</v>
+        <v>45.75</v>
       </c>
       <c r="I6" s="1">
-        <v>-15.16</v>
+        <v>-12.48</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.011352692562937442</v>
+        <v>-0.011080452397477165</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M6" s="1">
-        <v>0.024354827904717435</v>
+        <v>0.06068189073288033</v>
       </c>
       <c r="N6" s="1">
-        <v>13.204102424642736</v>
+        <v>16.428573410232346</v>
       </c>
       <c r="O6" s="1">
-        <v>63.29113924050633</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>37.21518987341772</v>
+        <v>39.36708860759493</v>
       </c>
       <c r="R6" s="1">
-        <v>41.39240506329114</v>
+        <v>42.911392405063296</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.7</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2452,25 +2449,25 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D7" s="2">
-        <v>6.293877551020408</v>
+        <v>6.297959183673469</v>
       </c>
       <c r="E7" s="2">
         <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>0.002710766112608426</v>
+        <v>-0.01774647948898561</v>
       </c>
       <c r="G7" s="2">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="H7" s="2">
-        <v>64.66</v>
+        <v>61.66</v>
       </c>
       <c r="I7" s="2">
-        <v>21.16</v>
+        <v>19.4</v>
       </c>
       <c r="J7" s="2">
-        <v>0.023430570277173587</v>
+        <v>0.02356356077928883</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2479,28 +2476,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.12485037350316297</v>
+        <v>0.09832082472281822</v>
       </c>
       <c r="N7" s="2">
-        <v>23.2536569844873</v>
+        <v>20.19246680922612</v>
       </c>
       <c r="O7" s="2">
-        <v>73.41772151898735</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>63.16455696202531</v>
+        <v>63.291139240506325</v>
       </c>
       <c r="R7" s="2">
-        <v>55.12658227848102</v>
+        <v>54.74683544303797</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2520,31 +2517,31 @@
         <v>0.19</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2685989729401681</v>
+        <v>0.28186469926579444</v>
       </c>
       <c r="G8" s="2">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>76.94</v>
+        <v>73.89</v>
       </c>
       <c r="I8" s="2">
-        <v>22.89</v>
+        <v>21.77</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03334742657966023</v>
+        <v>0.034017139234755404</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-211</v>
+        <v>-214</v>
       </c>
       <c r="M8" s="2">
-        <v>0.2356406661839867</v>
+        <v>0.24936585408648937</v>
       </c>
       <c r="N8" s="2">
-        <v>34.33268625256967</v>
+        <v>35.296969745593245</v>
       </c>
       <c r="O8" s="2">
         <v>84.81012658227847</v>
@@ -2553,16 +2550,16 @@
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>66.07594936708861</v>
+        <v>65.9493670886076</v>
       </c>
       <c r="R8" s="2">
-        <v>55.25316455696202</v>
+        <v>55.12658227848101</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.06</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2576,55 +2573,55 @@
         <v>37.9746835443038</v>
       </c>
       <c r="D9" s="1">
-        <v>46.2247191011236</v>
+        <v>46.0561797752809</v>
       </c>
       <c r="E9" s="1">
         <v>2.36</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.13555171012196826</v>
+        <v>-0.13409334925882924</v>
       </c>
       <c r="G9" s="1">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>43.48</v>
+        <v>45.02</v>
       </c>
       <c r="I9" s="1">
-        <v>-17.98</v>
+        <v>-17.21</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.008892293005765361</v>
+        <v>-0.011874267314837147</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.08805297391453037</v>
+        <v>-0.0876664275741077</v>
       </c>
       <c r="N9" s="1">
-        <v>1.9633222427179662</v>
+        <v>1.593741579533539</v>
       </c>
       <c r="O9" s="1">
-        <v>46.835443037974684</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P9" s="1">
         <v>34.04748479877408</v>
       </c>
       <c r="Q9" s="1">
-        <v>48.10126582278481</v>
+        <v>45.94936708860759</v>
       </c>
       <c r="R9" s="1">
-        <v>40.56962025316455</v>
+        <v>38.544303797468345</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.63</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2644,111 +2641,111 @@
         <v>1.48</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.17331904401626377</v>
+        <v>-0.15618452939247937</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>47.96</v>
+        <v>50.87</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.63</v>
+        <v>-4.47</v>
       </c>
       <c r="J10" s="1">
-        <v>0.000950680512234819</v>
+        <v>0.0016819570629001991</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-133</v>
+        <v>-132</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.1335752035161627</v>
+        <v>-0.1181144536110077</v>
       </c>
       <c r="N10" s="1">
-        <v>-2.588900717445275</v>
+        <v>-1.4510610241564685</v>
       </c>
       <c r="O10" s="1">
-        <v>41.77215189873418</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>46.20253164556962</v>
+        <v>47.08860759493671</v>
       </c>
       <c r="R10" s="1">
-        <v>37.59493670886076</v>
+        <v>37.21518987341773</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.2</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>-1.36</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>12.658227848101266</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>31.911764705882348</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>5.47</v>
       </c>
-      <c r="F11" s="1">
-        <v>0.12533555255876536</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="H11" s="1">
-        <v>66.24</v>
-      </c>
-      <c r="I11" s="1">
-        <v>8.13</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.020811267204622307</v>
-      </c>
-      <c r="K11" s="1" t="b">
+      <c r="F11" s="2">
+        <v>0.22299371633748066</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.81</v>
+      </c>
+      <c r="H11" s="2">
+        <v>70.02</v>
+      </c>
+      <c r="I11" s="2">
+        <v>12.52</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.020915555931008648</v>
+      </c>
+      <c r="K11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="2">
         <v>24</v>
       </c>
-      <c r="M11" s="1">
-        <v>0.10788703721725756</v>
-      </c>
-      <c r="N11" s="1">
-        <v>21.55732335589675</v>
-      </c>
-      <c r="O11" s="1">
-        <v>70.88607594936708</v>
-      </c>
-      <c r="P11" s="1">
+      <c r="M11" s="2">
+        <v>0.20535148609728648</v>
+      </c>
+      <c r="N11" s="2">
+        <v>30.895532946672947</v>
+      </c>
+      <c r="O11" s="2">
+        <v>81.0126582278481</v>
+      </c>
+      <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
-      <c r="Q11" s="1">
-        <v>56.07594936708861</v>
-      </c>
-      <c r="R11" s="1">
-        <v>47.21518987341773</v>
-      </c>
-      <c r="S11" s="1" t="s">
+      <c r="Q11" s="2">
+        <v>56.9620253164557</v>
+      </c>
+      <c r="R11" s="2">
+        <v>50.12658227848102</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T11" s="1">
-        <v>0.76</v>
+      <c r="T11" s="2">
+        <v>3.67</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2768,49 +2765,49 @@
         <v>5.82</v>
       </c>
       <c r="F12" s="3">
-        <v>-0.2905302085040573</v>
+        <v>-0.2049896933311422</v>
       </c>
       <c r="G12" s="3">
         <v>0.83</v>
       </c>
       <c r="H12" s="3">
-        <v>52.17</v>
+        <v>57.88</v>
       </c>
       <c r="I12" s="3">
-        <v>-34.67</v>
+        <v>-30.54</v>
       </c>
       <c r="J12" s="3">
-        <v>-0.011095628644533537</v>
+        <v>-0.010360775283759253</v>
       </c>
       <c r="K12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
-        <v>-44</v>
+        <v>-51</v>
       </c>
       <c r="M12" s="3">
-        <v>-0.307009361882148</v>
+        <v>-0.22077484670394754</v>
       </c>
       <c r="N12" s="3">
-        <v>-19.932316554043805</v>
+        <v>-11.717100333450444</v>
       </c>
       <c r="O12" s="3">
-        <v>10.126582278481013</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P12" s="3">
         <v>49.40073075603063</v>
       </c>
       <c r="Q12" s="3">
-        <v>41.898734177215196</v>
+        <v>44.05063291139242</v>
       </c>
       <c r="R12" s="3">
-        <v>22.341772151898734</v>
+        <v>26.0126582278481</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="3">
-        <v>1.65</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2830,49 +2827,49 @@
         <v>1.61</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.24695705804821247</v>
+        <v>-0.26024952328295353</v>
       </c>
       <c r="G13" s="3">
         <v>1.42</v>
       </c>
       <c r="H13" s="3">
-        <v>46.37</v>
+        <v>42.66</v>
       </c>
       <c r="I13" s="3">
-        <v>-1.23</v>
+        <v>-5.31</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.0006453714211657933</v>
+        <v>-0.0008064113307644788</v>
       </c>
       <c r="K13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3">
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.20624385558469427</v>
+        <v>-0.22125090906778744</v>
       </c>
       <c r="N13" s="3">
-        <v>-9.85576592429843</v>
+        <v>-11.76470656983444</v>
       </c>
       <c r="O13" s="3">
-        <v>27.848101265822784</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>26.962025316455698</v>
+        <v>25.063291139240505</v>
       </c>
       <c r="R13" s="3">
-        <v>12.72151898734177</v>
+        <v>10.696202531645572</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-3.16</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2892,49 +2889,49 @@
         <v>-0.14</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.12133656204260415</v>
+        <v>-0.01092020219065673</v>
       </c>
       <c r="G14" s="1">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="1">
-        <v>59.72</v>
+        <v>65.53</v>
       </c>
       <c r="I14" s="1">
-        <v>-2.81</v>
+        <v>2.27</v>
       </c>
       <c r="J14" s="1">
-        <v>0.008497241964348224</v>
+        <v>0.007725695028373236</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.15914167861587103</v>
+        <v>-0.048061739538433956</v>
       </c>
       <c r="N14" s="1">
-        <v>-5.145548227416105</v>
+        <v>5.5542103831009</v>
       </c>
       <c r="O14" s="1">
-        <v>37.9746835443038</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>55.18987341772152</v>
+        <v>56.45569620253164</v>
       </c>
       <c r="R14" s="1">
-        <v>36.45569620253165</v>
+        <v>39.55696202531645</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>1.27</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2948,37 +2945,37 @@
         <v>18.9873417721519</v>
       </c>
       <c r="D15" s="2">
-        <v>62.85714285714286</v>
+        <v>63.666666666666664</v>
       </c>
       <c r="E15" s="2">
         <v>5.49</v>
       </c>
       <c r="F15" s="2">
-        <v>1.098693544416193</v>
+        <v>1.127327487725272</v>
       </c>
       <c r="G15" s="2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H15" s="2">
-        <v>62.25</v>
+        <v>61.66</v>
       </c>
       <c r="I15" s="2">
-        <v>142.85</v>
+        <v>139.15</v>
       </c>
       <c r="J15" s="2">
-        <v>0.11891077311217498</v>
+        <v>0.1098033550304983</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="M15" s="2">
-        <v>1.2169557039530792</v>
+        <v>1.2387520997686037</v>
       </c>
       <c r="N15" s="2">
-        <v>132.4641900294789</v>
+        <v>134.23559431380468</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2987,7 +2984,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>69.11392405063292</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="R15" s="2">
         <v>61.962025316455694</v>
@@ -3016,49 +3013,49 @@
         <v>8.13</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.04425532051485587</v>
+        <v>-0.15149643627224202</v>
       </c>
       <c r="G16" s="1">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H16" s="1">
-        <v>48.96</v>
+        <v>43.14</v>
       </c>
       <c r="I16" s="1">
-        <v>3.5</v>
+        <v>-3.96</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0005051886203465474</v>
+        <v>-0.002538217697842285</v>
       </c>
       <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M16" s="1">
-        <v>0.04395661815610019</v>
+        <v>-0.06514236193865997</v>
       </c>
       <c r="N16" s="1">
-        <v>15.164281449781011</v>
+        <v>3.8461481430783033</v>
       </c>
       <c r="O16" s="1">
-        <v>65.82278481012658</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P16" s="1">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="1">
-        <v>42.0253164556962</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="R16" s="1">
-        <v>37.53164556962025</v>
+        <v>31.582278481012654</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="1">
-        <v>0.89</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3078,49 +3075,49 @@
         <v>4.24</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.2643194481130663</v>
+        <v>-0.25716158133857125</v>
       </c>
       <c r="G17" s="3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>40.67</v>
+        <v>41.08</v>
       </c>
       <c r="I17" s="3">
-        <v>-13.46</v>
+        <v>-13.13</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.014498611276431882</v>
+        <v>-0.015227695388811618</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.19549474871045225</v>
+        <v>-0.19030681411257222</v>
       </c>
       <c r="N17" s="3">
-        <v>-8.780855236874228</v>
+        <v>-8.670297074312918</v>
       </c>
       <c r="O17" s="3">
-        <v>30.37974683544304</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>24.177215189873415</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="R17" s="3">
-        <v>18.227848101265824</v>
+        <v>17.215189873417724</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.94</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3140,19 +3137,19 @@
         <v>8.39</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.34700555328245314</v>
+        <v>-0.33335657642902744</v>
       </c>
       <c r="G18" s="3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="H18" s="3">
-        <v>31.13</v>
+        <v>35.23</v>
       </c>
       <c r="I18" s="3">
-        <v>-14.72</v>
+        <v>-11.79</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.009012755161265349</v>
+        <v>-0.009136273670612718</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>1</v>
@@ -3161,10 +3158,10 @@
         <v>36</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.32858767597752825</v>
+        <v>-0.31292873088775</v>
       </c>
       <c r="N18" s="3">
-        <v>-22.09014796358183</v>
+        <v>-20.932488751830693</v>
       </c>
       <c r="O18" s="3">
         <v>6.329113924050633</v>
@@ -3173,16 +3170,16 @@
         <v>33.93532173431426</v>
       </c>
       <c r="Q18" s="3">
-        <v>47.08860759493671</v>
+        <v>47.21518987341772</v>
       </c>
       <c r="R18" s="3">
-        <v>29.556962025316462</v>
+        <v>29.430379746835445</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T18" s="3">
-        <v>-1.39</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3202,19 +3199,19 @@
         <v>-0.16</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.048303366108382144</v>
+        <v>-0.0482860664332288</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>53.64</v>
+        <v>52.51</v>
       </c>
       <c r="I19" s="1">
-        <v>15.04</v>
+        <v>14.21</v>
       </c>
       <c r="J19" s="1">
-        <v>0.004796651054090026</v>
+        <v>0.004892045477902574</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>1</v>
@@ -3223,28 +3220,28 @@
         <v>85</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.1258523231817501</v>
+        <v>-0.12256914112878325</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.816612684004011</v>
+        <v>-1.8965297759340138</v>
       </c>
       <c r="O19" s="1">
-        <v>43.037974683544306</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>53.79746835443038</v>
+        <v>53.29113924050634</v>
       </c>
       <c r="R19" s="1">
-        <v>42.27848101265823</v>
+        <v>41.0126582278481</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>1.39</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3264,49 +3261,49 @@
         <v>-3.42</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.1448213611214662</v>
+        <v>-0.04356525066034293</v>
       </c>
       <c r="G20" s="1">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H20" s="1">
-        <v>34.91</v>
+        <v>58.94</v>
       </c>
       <c r="I20" s="1">
-        <v>-15.3</v>
+        <v>-3.64</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.012981356034968689</v>
+        <v>-0.009626840755102025</v>
       </c>
       <c r="K20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.142882637194632</v>
+        <v>-0.03985109692556521</v>
       </c>
       <c r="N20" s="1">
-        <v>-3.519644085292207</v>
+        <v>6.375274644387787</v>
       </c>
       <c r="O20" s="1">
-        <v>40.50632911392405</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>36.835443037974684</v>
+        <v>46.32911392405064</v>
       </c>
       <c r="R20" s="1">
-        <v>33.9873417721519</v>
+        <v>39.050632911392405</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>6.58</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3326,19 +3323,19 @@
         <v>4.96</v>
       </c>
       <c r="F21" s="1">
-        <v>0.0735583537615512</v>
+        <v>-0.04643621647741378</v>
       </c>
       <c r="G21" s="1">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H21" s="1">
-        <v>79.77</v>
+        <v>70.71</v>
       </c>
       <c r="I21" s="1">
-        <v>45.16</v>
+        <v>36.05</v>
       </c>
       <c r="J21" s="1">
-        <v>0.002149483431858078</v>
+        <v>0.009664512828652428</v>
       </c>
       <c r="K21" s="1" t="b">
         <v>1</v>
@@ -3347,90 +3344,90 @@
         <v>38</v>
       </c>
       <c r="M21" s="1">
-        <v>0.10845538444456682</v>
+        <v>-0.014865909731803129</v>
       </c>
       <c r="N21" s="1">
-        <v>21.61415807862767</v>
+        <v>8.873793363763987</v>
       </c>
       <c r="O21" s="1">
-        <v>72.15189873417721</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P21" s="1">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="1">
-        <v>62.65822784810127</v>
+        <v>64.17721518987341</v>
       </c>
       <c r="R21" s="1">
-        <v>47.34177215189873</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="1">
-        <v>8.54</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="3">
         <v>8.11</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>70.88607594936708</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="3">
         <v>0.6942046855733663</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="3">
         <v>-0.12</v>
       </c>
-      <c r="F22" s="1">
-        <v>-0.24902962388139738</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.35</v>
-      </c>
-      <c r="H22" s="1">
-        <v>42.03</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-6.03</v>
-      </c>
-      <c r="J22" s="1">
-        <v>-0.014815021759235719</v>
-      </c>
-      <c r="K22" s="1" t="b">
+      <c r="F22" s="3">
+        <v>-0.2626579789231705</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1.36</v>
+      </c>
+      <c r="H22" s="3">
+        <v>45.13</v>
+      </c>
+      <c r="I22" s="3">
+        <v>-4.57</v>
+      </c>
+      <c r="J22" s="3">
+        <v>-0.014564777696410366</v>
+      </c>
+      <c r="K22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L22" s="1">
-        <v>62</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.21510195516179886</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-10.741575882008892</v>
-      </c>
-      <c r="O22" s="1">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="L22" s="3">
+        <v>61</v>
+      </c>
+      <c r="M22" s="3">
+        <v>-0.22923059531017098</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-12.562675194072789</v>
+      </c>
+      <c r="O22" s="3">
+        <v>17.72151898734177</v>
+      </c>
+      <c r="P22" s="3">
         <v>20.966620085005058</v>
       </c>
-      <c r="Q22" s="1">
-        <v>40.126582278481</v>
-      </c>
-      <c r="R22" s="1">
-        <v>30.18987341772152</v>
-      </c>
-      <c r="S22" s="1" t="s">
+      <c r="Q22" s="3">
+        <v>41.0126582278481</v>
+      </c>
+      <c r="R22" s="3">
+        <v>28.417721518987342</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T22" s="1">
-        <v>-0.06</v>
+      <c r="T22" s="3">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3444,55 +3441,55 @@
         <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.7706288622319157</v>
+        <v>-0.7731733914940022</v>
       </c>
       <c r="E23" s="1">
         <v>-0.36</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.16990217780303657</v>
+        <v>-0.16981242643259645</v>
       </c>
       <c r="G23" s="1">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>45.59</v>
+        <v>44.5</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.79</v>
+        <v>-9.13</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.0074685167164958485</v>
+        <v>-0.00697930373215041</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.1476068526444433</v>
+        <v>-0.1475275040239301</v>
       </c>
       <c r="N23" s="1">
-        <v>-3.9920656302733297</v>
+        <v>-4.392366065448701</v>
       </c>
       <c r="O23" s="1">
-        <v>39.24050632911392</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>45.189873417721515</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="R23" s="1">
-        <v>35.443037974683534</v>
+        <v>34.810126582278485</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>3.48</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3506,25 +3503,25 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="3">
-        <v>-0.3107569721115539</v>
+        <v>-0.1750498007968128</v>
       </c>
       <c r="E24" s="3">
         <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.03159567105820904</v>
+        <v>-0.04721990067610321</v>
       </c>
       <c r="G24" s="3">
         <v>3.57</v>
       </c>
       <c r="H24" s="3">
-        <v>54.4</v>
+        <v>48.42</v>
       </c>
       <c r="I24" s="3">
-        <v>-18.62</v>
+        <v>-23.15</v>
       </c>
       <c r="J24" s="3">
-        <v>0.032115427199283675</v>
+        <v>0.027345354150105805</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
@@ -3533,28 +3530,28 @@
         <v>-11</v>
       </c>
       <c r="M24" s="3">
-        <v>0.2175303535399855</v>
+        <v>0.19141447678336543</v>
       </c>
       <c r="N24" s="3">
-        <v>32.52165498816954</v>
+        <v>29.501832015280847</v>
       </c>
       <c r="O24" s="3">
-        <v>82.27848101265823</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>28.607594936708864</v>
+        <v>25.56962025316456</v>
       </c>
       <c r="R24" s="3">
-        <v>28.417721518987342</v>
+        <v>27.088607594936708</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-2.59</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3574,49 +3571,49 @@
         <v>14.49</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.441182512906166</v>
+        <v>-0.48340627771798417</v>
       </c>
       <c r="G25" s="3">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="H25" s="3">
-        <v>45.21</v>
+        <v>41.46</v>
       </c>
       <c r="I25" s="3">
-        <v>-52.93</v>
+        <v>-55.71</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.0044881616010012575</v>
+        <v>-0.007285600179980536</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.3229203533692798</v>
+        <v>-0.3691960503735692</v>
       </c>
       <c r="N25" s="3">
-        <v>-21.523415702756985</v>
+        <v>-26.55922070041261</v>
       </c>
       <c r="O25" s="3">
-        <v>7.59493670886076</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>26.962025316455698</v>
+        <v>24.55696202531646</v>
       </c>
       <c r="R25" s="3">
-        <v>9.177215189873419</v>
+        <v>7.784810126582279</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-2.78</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3630,37 +3627,37 @@
         <v>24.050632911392405</v>
       </c>
       <c r="D26" s="1">
-        <v>-2571.7647058823527</v>
+        <v>-2569.235294117647</v>
       </c>
       <c r="E26" s="1">
         <v>3.56</v>
       </c>
       <c r="F26" s="1">
-        <v>0.21466965129619875</v>
+        <v>0.1921820320860143</v>
       </c>
       <c r="G26" s="1">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="H26" s="1">
-        <v>58.58</v>
+        <v>54.12</v>
       </c>
       <c r="I26" s="1">
-        <v>10.58</v>
+        <v>4.86</v>
       </c>
       <c r="J26" s="1">
-        <v>0.04870818061008482</v>
+        <v>0.045595959814655786</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-24</v>
+        <v>-30</v>
       </c>
       <c r="M26" s="1">
-        <v>0.41532757772353834</v>
+        <v>0.38253241099337254</v>
       </c>
       <c r="N26" s="1">
-        <v>52.30137740652482</v>
+        <v>48.613625436281566</v>
       </c>
       <c r="O26" s="1">
         <v>88.60759493670885</v>
@@ -3669,7 +3666,7 @@
         <v>50.63126652197354</v>
       </c>
       <c r="Q26" s="1">
-        <v>39.367088607594944</v>
+        <v>37.721518987341774</v>
       </c>
       <c r="R26" s="1">
         <v>32.278481012658226</v>
@@ -3698,49 +3695,49 @@
         <v>5.04</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.21825818230701438</v>
+        <v>-0.2179909716700258</v>
       </c>
       <c r="G27" s="3">
         <v>2.62</v>
       </c>
       <c r="H27" s="3">
-        <v>56.69</v>
+        <v>56.58</v>
       </c>
       <c r="I27" s="3">
-        <v>-21.3</v>
+        <v>-21.18</v>
       </c>
       <c r="J27" s="3">
-        <v>0.008056962376991866</v>
+        <v>0.008305972203884657</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.06122154423344428</v>
+        <v>-0.06756774541152799</v>
       </c>
       <c r="N27" s="3">
-        <v>4.646465210826574</v>
+        <v>3.6036097957914994</v>
       </c>
       <c r="O27" s="3">
-        <v>50.63291139240506</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>35.822784810126585</v>
+        <v>36.962025316455694</v>
       </c>
       <c r="R27" s="3">
-        <v>25.063291139240505</v>
+        <v>23.67088607594937</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>-1.33</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3754,55 +3751,55 @@
         <v>15.18987341772152</v>
       </c>
       <c r="D28" s="3">
-        <v>7.536363636363636</v>
+        <v>7.899999999999999</v>
       </c>
       <c r="E28" s="3">
         <v>-1.13</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.42051181481840655</v>
+        <v>-0.43334734979242256</v>
       </c>
       <c r="G28" s="3">
         <v>3.13</v>
       </c>
       <c r="H28" s="3">
-        <v>49.44</v>
+        <v>46.78</v>
       </c>
       <c r="I28" s="3">
-        <v>-25.71</v>
+        <v>-27.12</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.009005059235791242</v>
+        <v>-0.008211679821581552</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.21403771661056437</v>
+        <v>-0.23556866341550886</v>
       </c>
       <c r="N28" s="3">
-        <v>-10.635152026885446</v>
+        <v>-13.196482004606583</v>
       </c>
       <c r="O28" s="3">
-        <v>25.31645569620253</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>33.291139240506325</v>
+        <v>33.54430379746835</v>
       </c>
       <c r="R28" s="3">
-        <v>20.253164556962027</v>
+        <v>18.35443037974684</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-1.65</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3822,49 +3819,49 @@
         <v>0.88</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.419262979032475</v>
+        <v>-0.4023720672745934</v>
       </c>
       <c r="G29" s="3">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>41.09</v>
+        <v>42.02</v>
       </c>
       <c r="I29" s="3">
-        <v>-33.52</v>
+        <v>-33</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.015715482245240393</v>
+        <v>-0.017697579687506945</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.31166380109317693</v>
+        <v>-0.2983757627008171</v>
       </c>
       <c r="N29" s="3">
-        <v>-20.397760475146693</v>
+        <v>-19.477191933137412</v>
       </c>
       <c r="O29" s="3">
-        <v>8.860759493670885</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.518987341772146</v>
+        <v>41.0126582278481</v>
       </c>
       <c r="R29" s="3">
-        <v>24.746835443037973</v>
+        <v>24.36708860759493</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3884,49 +3881,49 @@
         <v>2.51</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.2195577976440304</v>
+        <v>-0.2181834356803246</v>
       </c>
       <c r="G30" s="1">
         <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>44.58</v>
+        <v>44.69</v>
       </c>
       <c r="I30" s="1">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="J30" s="1">
-        <v>0.0031873692550686795</v>
+        <v>0.0012361694659760135</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.20017055837568842</v>
+        <v>-0.19961266700643598</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.248436203397842</v>
+        <v>-9.600882363699286</v>
       </c>
       <c r="O30" s="1">
-        <v>29.11392405063291</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>63.037974683544306</v>
+        <v>62.151898734177216</v>
       </c>
       <c r="R30" s="1">
-        <v>46.32911392405064</v>
+        <v>44.683544303797476</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-1.2</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3940,55 +3937,55 @@
         <v>59.49367088607595</v>
       </c>
       <c r="D31" s="2">
-        <v>10.690058479532164</v>
+        <v>10.729044834307992</v>
       </c>
       <c r="E31" s="2">
         <v>0.99</v>
       </c>
       <c r="F31" s="2">
-        <v>0.15822414412232277</v>
+        <v>0.12160998144169308</v>
       </c>
       <c r="G31" s="2">
         <v>1.43</v>
       </c>
       <c r="H31" s="2">
-        <v>58.64</v>
+        <v>56.52</v>
       </c>
       <c r="I31" s="2">
-        <v>22.59</v>
+        <v>21.08</v>
       </c>
       <c r="J31" s="2">
-        <v>0.029369983533265455</v>
+        <v>0.02815971364510794</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M31" s="2">
-        <v>0.19990670854925807</v>
+        <v>0.1615371340905536</v>
       </c>
       <c r="N31" s="2">
-        <v>30.759290489096795</v>
+        <v>26.51409774599967</v>
       </c>
       <c r="O31" s="2">
-        <v>79.74683544303798</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>68.10126582278481</v>
+        <v>67.46835443037975</v>
       </c>
       <c r="R31" s="2">
-        <v>60.9493670886076</v>
+        <v>59.81012658227849</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>0.13</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4008,49 +4005,49 @@
         <v>1.51</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.38807011843937855</v>
+        <v>-0.3506085062803344</v>
       </c>
       <c r="G32" s="3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H32" s="3">
-        <v>36.12</v>
+        <v>33.07</v>
       </c>
       <c r="I32" s="3">
-        <v>-10.07</v>
+        <v>-12.95</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.006325061572753529</v>
+        <v>-0.007322670909482875</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.32990840063435256</v>
+        <v>-0.2930391233912797</v>
       </c>
       <c r="N32" s="3">
-        <v>-22.222220429264258</v>
+        <v>-18.943528002183665</v>
       </c>
       <c r="O32" s="3">
-        <v>5.063291139240507</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P32" s="3">
-        <v>38.84187494148391</v>
+        <v>40.53452147980343</v>
       </c>
       <c r="Q32" s="3">
-        <v>34.43037974683544</v>
+        <v>31.139240506329113</v>
       </c>
       <c r="R32" s="3">
-        <v>15.632911392405063</v>
+        <v>15.759493670886073</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-13.73</v>
+        <v>-13.61</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4070,49 +4067,49 @@
         <v>0.66</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.06411046878691452</v>
+        <v>-0.04473289060781967</v>
       </c>
       <c r="G33" s="1">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>57.9</v>
+        <v>58.77</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.9</v>
+        <v>-8.44</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0023051794827069136</v>
+        <v>0.0020349008366425656</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.056355573079577725</v>
+        <v>-0.03637604470456979</v>
       </c>
       <c r="N33" s="1">
-        <v>5.133062326213224</v>
+        <v>6.72277986648732</v>
       </c>
       <c r="O33" s="1">
-        <v>51.89873417721519</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P33" s="1">
         <v>26.894390179645494</v>
       </c>
       <c r="Q33" s="1">
-        <v>52.278481012658226</v>
+        <v>53.037974683544306</v>
       </c>
       <c r="R33" s="1">
-        <v>42.27848101265823</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>2.34</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4126,55 +4123,55 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.7025171624713958</v>
+        <v>-0.7185354691075515</v>
       </c>
       <c r="E34" s="2">
         <v>0.94</v>
       </c>
       <c r="F34" s="2">
-        <v>0.16496462914942378</v>
+        <v>0.18653803551012116</v>
       </c>
       <c r="G34" s="2">
         <v>1.26</v>
       </c>
       <c r="H34" s="2">
-        <v>70.23</v>
+        <v>70.3</v>
       </c>
       <c r="I34" s="2">
-        <v>36.21</v>
+        <v>35.78</v>
       </c>
       <c r="J34" s="2">
-        <v>0.02783748309324901</v>
+        <v>0.029030342290056157</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M34" s="2">
-        <v>0.19016804019826838</v>
+        <v>0.21068003478617636</v>
       </c>
       <c r="N34" s="2">
-        <v>29.785423653997828</v>
+        <v>31.42838781556194</v>
       </c>
       <c r="O34" s="2">
-        <v>78.48101265822784</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>60.63291139240506</v>
+        <v>61.518987341772146</v>
       </c>
       <c r="R34" s="2">
-        <v>50.949367088607595</v>
+        <v>52.46835443037974</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="2">
-        <v>-0.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4194,31 +4191,31 @@
         <v>4.55</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.3016835226741067</v>
+        <v>-0.27897198259300393</v>
       </c>
       <c r="G35" s="3">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>26.06</v>
+        <v>31.37</v>
       </c>
       <c r="I35" s="3">
-        <v>-25.51</v>
+        <v>-23.96</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.02616499403082351</v>
+        <v>-0.026896848291015418</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.3026528846375238</v>
+        <v>-0.27897198259300393</v>
       </c>
       <c r="N35" s="3">
-        <v>-19.49666882958139</v>
+        <v>-17.53681392235609</v>
       </c>
       <c r="O35" s="3">
         <v>11.39240506329114</v>
@@ -4227,7 +4224,7 @@
         <v>29.946003174037394</v>
       </c>
       <c r="Q35" s="3">
-        <v>32.65822784810126</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="R35" s="3">
         <v>23.29113924050633</v>
@@ -4240,65 +4237,65 @@
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="3">
         <v>11.51</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="3">
         <v>82.27848101265823</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="3">
         <v>0.38488271068635965</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="3">
         <v>-1.05</v>
       </c>
-      <c r="F36" s="1">
-        <v>-0.19098513098420686</v>
-      </c>
-      <c r="G36" s="1">
-        <v>1.1</v>
-      </c>
-      <c r="H36" s="1">
-        <v>35.18</v>
-      </c>
-      <c r="I36" s="1">
-        <v>-17.99</v>
-      </c>
-      <c r="J36" s="1">
-        <v>-0.014982028229795937</v>
-      </c>
-      <c r="K36" s="1" t="b">
+      <c r="F36" s="3">
+        <v>-0.2500884003591458</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H36" s="3">
+        <v>33.41</v>
+      </c>
+      <c r="I36" s="3">
+        <v>-19.48</v>
+      </c>
+      <c r="J36" s="3">
+        <v>-0.016795387598225176</v>
+      </c>
+      <c r="K36" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L36" s="1">
-        <v>-50</v>
-      </c>
-      <c r="M36" s="1">
-        <v>-0.18129151135003585</v>
-      </c>
-      <c r="N36" s="1">
-        <v>-7.360531500832586</v>
-      </c>
-      <c r="O36" s="1">
-        <v>31.645569620253166</v>
-      </c>
-      <c r="P36" s="1">
+      <c r="L36" s="3">
+        <v>-51</v>
+      </c>
+      <c r="M36" s="3">
+        <v>-0.23894593915481266</v>
+      </c>
+      <c r="N36" s="3">
+        <v>-13.53420957853696</v>
+      </c>
+      <c r="O36" s="3">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="P36" s="3">
         <v>32.54334537649318</v>
       </c>
-      <c r="Q36" s="1">
-        <v>37.9746835443038</v>
-      </c>
-      <c r="R36" s="1">
-        <v>30.696202531645564</v>
-      </c>
-      <c r="S36" s="1" t="s">
+      <c r="Q36" s="3">
+        <v>36.582278481012665</v>
+      </c>
+      <c r="R36" s="3">
+        <v>25.632911392405067</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="1">
-        <v>-3.61</v>
+      <c r="T36" s="3">
+        <v>-8.67</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4318,49 +4315,49 @@
         <v>1.72</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.04129399285351304</v>
+        <v>-0.051287303410220586</v>
       </c>
       <c r="G37" s="1">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H37" s="1">
-        <v>34.95</v>
+        <v>34.85</v>
       </c>
       <c r="I37" s="1">
-        <v>-23.21</v>
+        <v>-23.09</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.0031632491880796624</v>
+        <v>-0.003781111725511868</v>
       </c>
       <c r="K37" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-207</v>
+        <v>-205</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.00542760020708033</v>
+        <v>-0.01600284292983223</v>
       </c>
       <c r="N37" s="1">
-        <v>10.225859613462955</v>
+        <v>8.76010004396109</v>
       </c>
       <c r="O37" s="1">
-        <v>60.75949367088608</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P37" s="1">
         <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
-        <v>38.10126582278481</v>
+        <v>37.84810126582279</v>
       </c>
       <c r="R37" s="1">
-        <v>37.84810126582279</v>
+        <v>37.21518987341772</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>-0.95</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4380,49 +4377,49 @@
         <v>-0.05</v>
       </c>
       <c r="F38" s="2">
-        <v>0.26342049006394885</v>
+        <v>0.38084096194479583</v>
       </c>
       <c r="G38" s="2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="H38" s="2">
-        <v>82.57</v>
+        <v>84.82</v>
       </c>
       <c r="I38" s="2">
-        <v>29.02</v>
+        <v>34.15</v>
       </c>
       <c r="J38" s="2">
-        <v>0.03960451097304168</v>
+        <v>0.040201883985519334</v>
       </c>
       <c r="K38" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>-41</v>
+        <v>-44</v>
       </c>
       <c r="M38" s="2">
-        <v>0.27505283362495403</v>
+        <v>0.39012634628174014</v>
       </c>
       <c r="N38" s="2">
-        <v>38.27390299666639</v>
+        <v>49.37301896511831</v>
       </c>
       <c r="O38" s="2">
-        <v>87.34177215189874</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P38" s="2">
         <v>27.505487150580247</v>
       </c>
       <c r="Q38" s="2">
-        <v>64.81012658227849</v>
+        <v>65.18987341772153</v>
       </c>
       <c r="R38" s="2">
-        <v>54.43037974683544</v>
+        <v>55.189873417721515</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4442,49 +4439,49 @@
         <v>-6.6</v>
       </c>
       <c r="F39" s="2">
-        <v>0.06794935342768335</v>
+        <v>0.13925187422803692</v>
       </c>
       <c r="G39" s="2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H39" s="2">
-        <v>48.15</v>
+        <v>58.74</v>
       </c>
       <c r="I39" s="2">
-        <v>7.47</v>
+        <v>13.84</v>
       </c>
       <c r="J39" s="2">
-        <v>0.0170512546758961</v>
+        <v>0.016446432492736814</v>
       </c>
       <c r="K39" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2">
         <v>-4</v>
       </c>
       <c r="M39" s="2">
-        <v>0.09606085036677925</v>
+        <v>0.16710802723886986</v>
       </c>
       <c r="N39" s="2">
-        <v>20.37470467084891</v>
+        <v>27.071187060831292</v>
       </c>
       <c r="O39" s="2">
-        <v>68.35443037974683</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P39" s="2">
         <v>18.299999237060547</v>
       </c>
       <c r="Q39" s="2">
-        <v>56.07594936708861</v>
+        <v>60.12658227848102</v>
       </c>
       <c r="R39" s="2">
-        <v>52.34177215189874</v>
+        <v>55.12658227848102</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="2">
-        <v>-1.08</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4504,31 +4501,31 @@
         <v>10.16</v>
       </c>
       <c r="F40" s="1">
-        <v>0.11310755946653876</v>
+        <v>0.10050004291534424</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>40.05</v>
+        <v>39.88</v>
       </c>
       <c r="I40" s="1">
-        <v>-21.05</v>
+        <v>-21.18</v>
       </c>
       <c r="J40" s="1">
-        <v>0.01748544935491823</v>
+        <v>0.011139004953147463</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M40" s="1">
-        <v>0.016171363124828808</v>
+        <v>0.007646199545901178</v>
       </c>
       <c r="N40" s="1">
-        <v>12.38575594665387</v>
+        <v>11.125004291534424</v>
       </c>
       <c r="O40" s="1">
         <v>62.0253164556962</v>
@@ -4537,78 +4534,78 @@
         <v>45.29877115964868</v>
       </c>
       <c r="Q40" s="1">
-        <v>36.9620253164557</v>
+        <v>36.32911392405063</v>
       </c>
       <c r="R40" s="1">
-        <v>33.101265822784804</v>
+        <v>32.974683544303794</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-7.66</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="3">
         <v>-5.03</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="3">
         <v>5.063291139240507</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="3">
         <v>7.415506958250497</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="3">
         <v>-1.71</v>
       </c>
-      <c r="F41" s="1">
-        <v>-0.029972241879371517</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.13</v>
-      </c>
-      <c r="H41" s="1">
-        <v>67.11</v>
-      </c>
-      <c r="I41" s="1">
-        <v>-10.02</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0.020311357402799175</v>
-      </c>
-      <c r="K41" s="1" t="b">
+      <c r="F41" s="3">
+        <v>-0.10456658819425821</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="H41" s="3">
+        <v>55.81</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-15.94</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0.02165646919454138</v>
+      </c>
+      <c r="K41" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L41" s="1">
-        <v>3</v>
-      </c>
-      <c r="M41" s="1">
-        <v>-0.01737053635494923</v>
-      </c>
-      <c r="N41" s="1">
-        <v>9.031565998676063</v>
-      </c>
-      <c r="O41" s="1">
-        <v>56.9620253164557</v>
-      </c>
-      <c r="P41" s="1">
+      <c r="L41" s="3">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3">
+        <v>-0.09713828072470276</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0.6465562644740378</v>
+      </c>
+      <c r="O41" s="3">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="P41" s="3">
         <v>46.4052282234621</v>
       </c>
-      <c r="Q41" s="1">
-        <v>44.17721518987342</v>
-      </c>
-      <c r="R41" s="1">
-        <v>30.44303797468355</v>
-      </c>
-      <c r="S41" s="1" t="s">
+      <c r="Q41" s="3">
+        <v>41.39240506329114</v>
+      </c>
+      <c r="R41" s="3">
+        <v>26.64556962025317</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T41" s="1">
-        <v>0.38</v>
+      <c r="T41" s="3">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4622,25 +4619,25 @@
         <v>53.16455696202531</v>
       </c>
       <c r="D42" s="1">
-        <v>1.0775623268698062</v>
+        <v>1.0692520775623269</v>
       </c>
       <c r="E42" s="1">
         <v>0.29</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.11210518309493923</v>
+        <v>-0.09559773625677426</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>32.57</v>
+        <v>35.87</v>
       </c>
       <c r="I42" s="1">
-        <v>-2.68</v>
+        <v>-2</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.00652169519913724</v>
+        <v>-0.006569076692434285</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4649,10 +4646,10 @@
         <v>20</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.1741443487536336</v>
+        <v>-0.15502419601321782</v>
       </c>
       <c r="N42" s="1">
-        <v>-6.645815241192368</v>
+        <v>-5.142035264377481</v>
       </c>
       <c r="O42" s="1">
         <v>35.44303797468354</v>
@@ -4661,16 +4658,16 @@
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>41.265822784810126</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="R42" s="1">
-        <v>37.72151898734177</v>
+        <v>37.848101265822784</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4690,19 +4687,19 @@
         <v>6.54</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.05089839962555098</v>
+        <v>0.04050414428282115</v>
       </c>
       <c r="G43" s="1">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="H43" s="1">
-        <v>50.34</v>
+        <v>54.72</v>
       </c>
       <c r="I43" s="1">
-        <v>-13.72</v>
+        <v>-10.56</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.0019450182993650366</v>
+        <v>-0.0051556829918994705</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
@@ -4711,28 +4708,28 @@
         <v>8</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.02569498857670638</v>
+        <v>0.06650322042626522</v>
       </c>
       <c r="N43" s="1">
-        <v>8.199120776500347</v>
+        <v>17.010706379570838</v>
       </c>
       <c r="O43" s="1">
-        <v>55.69620253164557</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P43" s="1">
         <v>36.79958124823221</v>
       </c>
       <c r="Q43" s="1">
-        <v>53.67088607594937</v>
+        <v>54.93670886075949</v>
       </c>
       <c r="R43" s="1">
-        <v>44.55696202531645</v>
+        <v>48.60759493670886</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>2.41</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4752,49 +4749,49 @@
         <v>-1.94</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.37008009296786126</v>
+        <v>-0.3513018202198858</v>
       </c>
       <c r="G44" s="3">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="H44" s="3">
-        <v>37.06</v>
+        <v>39.55</v>
       </c>
       <c r="I44" s="3">
-        <v>-28.9</v>
+        <v>-27.35</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.021500255259178976</v>
+        <v>-0.02314899278559156</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="3">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.21789026471137662</v>
+        <v>-0.20180713239508252</v>
       </c>
       <c r="N44" s="3">
-        <v>-11.020406836966671</v>
+        <v>-9.82032890256395</v>
       </c>
       <c r="O44" s="3">
-        <v>22.78481012658228</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P44" s="3">
         <v>44.155007607957295</v>
       </c>
       <c r="Q44" s="3">
-        <v>39.99999999999999</v>
+        <v>39.87341772151898</v>
       </c>
       <c r="R44" s="3">
-        <v>29.177215189873415</v>
+        <v>29.55696202531646</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>2.66</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4808,37 +4805,37 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.821983273596177</v>
+        <v>0.7407407407407409</v>
       </c>
       <c r="E45" s="2">
         <v>1.15</v>
       </c>
       <c r="F45" s="2">
-        <v>0.1774315040334033</v>
+        <v>0.17041216515705926</v>
       </c>
       <c r="G45" s="2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>58.56</v>
+        <v>59.27</v>
       </c>
       <c r="I45" s="2">
-        <v>15.14</v>
+        <v>15.37</v>
       </c>
       <c r="J45" s="2">
-        <v>0.023648199835042998</v>
+        <v>0.02289653980282876</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M45" s="2">
-        <v>0.2210527923871728</v>
+        <v>0.2131249331070031</v>
       </c>
       <c r="N45" s="2">
-        <v>32.873898872888276</v>
+        <v>31.672877647644626</v>
       </c>
       <c r="O45" s="2">
         <v>83.54430379746836</v>
@@ -4847,78 +4844,78 @@
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>62.27848101265823</v>
+        <v>61.26582278481012</v>
       </c>
       <c r="R45" s="2">
-        <v>57.34177215189874</v>
+        <v>56.32911392405063</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>0.38</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="3">
         <v>-0.3</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="3">
         <v>21.518987341772153</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="3">
         <v>543.5000000000001</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="3">
         <v>-0.24</v>
       </c>
-      <c r="F46" s="1">
-        <v>-0.26667139695523195</v>
-      </c>
-      <c r="G46" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H46" s="1">
-        <v>40.87</v>
-      </c>
-      <c r="I46" s="1">
-        <v>4.79</v>
-      </c>
-      <c r="J46" s="1">
-        <v>-0.0066835997262821335</v>
-      </c>
-      <c r="K46" s="1" t="b">
+      <c r="F46" s="3">
+        <v>-0.3050672336445899</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="H46" s="3">
+        <v>37.7</v>
+      </c>
+      <c r="I46" s="3">
+        <v>-1.19</v>
+      </c>
+      <c r="J46" s="3">
+        <v>-0.009046035595179662</v>
+      </c>
+      <c r="K46" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L46" s="1">
-        <v>24</v>
-      </c>
-      <c r="M46" s="1">
-        <v>-0.21917266074779407</v>
-      </c>
-      <c r="N46" s="1">
-        <v>-11.14864644060841</v>
-      </c>
-      <c r="O46" s="1">
-        <v>20.253164556962027</v>
-      </c>
-      <c r="P46" s="1">
+      <c r="L46" s="3">
+        <v>25</v>
+      </c>
+      <c r="M46" s="3">
+        <v>-0.2577117735261739</v>
+      </c>
+      <c r="N46" s="3">
+        <v>-15.410793015673082</v>
+      </c>
+      <c r="O46" s="3">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="P46" s="3">
         <v>40.6204924523832</v>
       </c>
-      <c r="Q46" s="1">
-        <v>50.12658227848101</v>
-      </c>
-      <c r="R46" s="1">
-        <v>30.379746835443033</v>
-      </c>
-      <c r="S46" s="1" t="s">
+      <c r="Q46" s="3">
+        <v>46.708860759493675</v>
+      </c>
+      <c r="R46" s="3">
+        <v>27.721518987341764</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T46" s="1">
-        <v>-1.01</v>
+      <c r="T46" s="3">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4938,31 +4935,31 @@
         <v>-3.9</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.457975392465942</v>
+        <v>-0.4271698360842434</v>
       </c>
       <c r="G47" s="3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H47" s="3">
-        <v>26.92</v>
+        <v>29.38</v>
       </c>
       <c r="I47" s="3">
-        <v>-21.51</v>
+        <v>-20.47</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030394377303079353</v>
+        <v>-0.030347190060011527</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.4133847421487554</v>
+        <v>-0.38352852970060514</v>
       </c>
       <c r="N47" s="3">
-        <v>-30.569854580704554</v>
+        <v>-27.992468633116207</v>
       </c>
       <c r="O47" s="3">
         <v>3.79746835443038</v>
@@ -4971,7 +4968,7 @@
         <v>31.304415950527737</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.607594936708864</v>
+        <v>38.860759493670884</v>
       </c>
       <c r="R47" s="3">
         <v>25.25316455696202</v>
@@ -4994,55 +4991,55 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D48" s="2">
-        <v>7.675879396984925</v>
+        <v>7.673366834170855</v>
       </c>
       <c r="E48" s="2">
         <v>-0.69</v>
       </c>
       <c r="F48" s="2">
-        <v>0.36634599216298047</v>
+        <v>0.18928018145665992</v>
       </c>
       <c r="G48" s="2">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H48" s="2">
-        <v>68.87</v>
+        <v>53.69</v>
       </c>
       <c r="I48" s="2">
-        <v>82.63</v>
+        <v>66.47</v>
       </c>
       <c r="J48" s="2">
-        <v>0.04172592781156484</v>
+        <v>0.04034650925906881</v>
       </c>
       <c r="K48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M48" s="2">
-        <v>0.47394517010227855</v>
+        <v>0.2914194091630473</v>
       </c>
       <c r="N48" s="2">
-        <v>58.16313664439884</v>
+        <v>39.50232525324903</v>
       </c>
       <c r="O48" s="2">
-        <v>91.13924050632912</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P48" s="2">
         <v>15.18684888660459</v>
       </c>
       <c r="Q48" s="2">
-        <v>70.75949367088607</v>
+        <v>67.21518987341771</v>
       </c>
       <c r="R48" s="2">
-        <v>63.60759493670886</v>
+        <v>61.77215189873418</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T48" s="2">
-        <v>0.57</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5062,49 +5059,49 @@
         <v>3.55</v>
       </c>
       <c r="F49" s="2">
-        <v>0.5966006262232061</v>
+        <v>0.4166832538248919</v>
       </c>
       <c r="G49" s="2">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="H49" s="2">
-        <v>58.79</v>
+        <v>53.03</v>
       </c>
       <c r="I49" s="2">
-        <v>117.31</v>
+        <v>101.97</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06785937393502986</v>
+        <v>0.06644165588838259</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M49" s="2">
-        <v>0.8670526140165769</v>
+        <v>0.6766740152593325</v>
       </c>
       <c r="N49" s="2">
-        <v>97.47388103582867</v>
+        <v>78.02778586287755</v>
       </c>
       <c r="O49" s="2">
-        <v>94.9367088607595</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="P49" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q49" s="2">
-        <v>73.0379746835443</v>
+        <v>71.39240506329114</v>
       </c>
       <c r="R49" s="2">
-        <v>62.594936708860764</v>
+        <v>62.21518987341772</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.95</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5124,49 +5121,49 @@
         <v>2.59</v>
       </c>
       <c r="F50" s="3">
-        <v>-0.46770435480298933</v>
+        <v>-0.4456703998039746</v>
       </c>
       <c r="G50" s="3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H50" s="3">
-        <v>34.19</v>
+        <v>36.3</v>
       </c>
       <c r="I50" s="3">
-        <v>-28.15</v>
+        <v>-26.9</v>
       </c>
       <c r="J50" s="3">
-        <v>-0.03248906040173917</v>
+        <v>-0.036499267452008585</v>
       </c>
       <c r="K50" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3">
         <v>-2</v>
       </c>
       <c r="M50" s="3">
-        <v>-0.416328170741883</v>
+        <v>-0.3955293243844753</v>
       </c>
       <c r="N50" s="3">
-        <v>-30.864197440017303</v>
+        <v>-29.19254810150323</v>
       </c>
       <c r="O50" s="3">
         <v>2.5316455696202533</v>
       </c>
       <c r="P50" s="3">
-        <v>47.64150593279924</v>
+        <v>46.88994928756761</v>
       </c>
       <c r="Q50" s="3">
-        <v>38.22784810126583</v>
+        <v>38.22784810126582</v>
       </c>
       <c r="R50" s="3">
-        <v>21.77215189873418</v>
+        <v>21.645569620253163</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T50" s="3">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5186,49 +5183,49 @@
         <v>16.72</v>
       </c>
       <c r="F51" s="1">
-        <v>0.02092920462188544</v>
+        <v>-0.11225424461657726</v>
       </c>
       <c r="G51" s="1">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="H51" s="1">
-        <v>53.42</v>
+        <v>43.33</v>
       </c>
       <c r="I51" s="1">
-        <v>29.59</v>
+        <v>12.78</v>
       </c>
       <c r="J51" s="1">
-        <v>0.029607238639130482</v>
+        <v>0.025800525067663532</v>
       </c>
       <c r="K51" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M51" s="1">
-        <v>0.1498543457563597</v>
+        <v>0.014955520799559752</v>
       </c>
       <c r="N51" s="1">
-        <v>25.75405420980697</v>
+        <v>11.855936416900272</v>
       </c>
       <c r="O51" s="1">
-        <v>75.9493670886076</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P51" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q51" s="1">
-        <v>52.65822784810127</v>
+        <v>47.72151898734178</v>
       </c>
       <c r="R51" s="1">
-        <v>41.329113924050645</v>
+        <v>37.40506329113924</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T51" s="1">
-        <v>14.68</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5242,55 +5239,55 @@
         <v>62.0253164556962</v>
       </c>
       <c r="D52" s="2">
-        <v>6.496226415094339</v>
+        <v>6.507547169811321</v>
       </c>
       <c r="E52" s="2">
         <v>0.25</v>
       </c>
       <c r="F52" s="2">
-        <v>0.01973553992918095</v>
+        <v>-0.000776152966117688</v>
       </c>
       <c r="G52" s="2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H52" s="2">
-        <v>57.13</v>
+        <v>53.56</v>
       </c>
       <c r="I52" s="2">
-        <v>55.01</v>
+        <v>50.58</v>
       </c>
       <c r="J52" s="2">
-        <v>0.028614893221618865</v>
+        <v>0.02982796949308086</v>
       </c>
       <c r="K52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L52" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M52" s="2">
-        <v>0.10116194485621732</v>
+        <v>0.07629253703052008</v>
       </c>
       <c r="N52" s="2">
-        <v>20.884814119792736</v>
+        <v>17.98963803999632</v>
       </c>
       <c r="O52" s="2">
-        <v>69.62025316455697</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P52" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q52" s="2">
-        <v>65.56962025316456</v>
+        <v>65.9493670886076</v>
       </c>
       <c r="R52" s="2">
-        <v>54.68354430379747</v>
+        <v>55.44303797468355</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T52" s="2">
-        <v>-2.09</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5310,111 +5307,111 @@
         <v>6.64</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.22656157373327646</v>
+        <v>-0.19892397531012102</v>
       </c>
       <c r="G53" s="1">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H53" s="1">
-        <v>57.25</v>
+        <v>50.85</v>
       </c>
       <c r="I53" s="1">
-        <v>-20.97</v>
+        <v>-25.28</v>
       </c>
       <c r="J53" s="1">
-        <v>0.02174484183900514</v>
+        <v>0.02100547168695652</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L53" s="1">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.07146365958654055</v>
+        <v>-0.05221490278640095</v>
       </c>
       <c r="N53" s="1">
-        <v>3.622253675516941</v>
+        <v>5.1388940583042055</v>
       </c>
       <c r="O53" s="1">
-        <v>48.10126582278481</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P53" s="1">
         <v>48.21894075039502</v>
       </c>
       <c r="Q53" s="1">
-        <v>47.088607594936704</v>
+        <v>44.810126582278485</v>
       </c>
       <c r="R53" s="1">
-        <v>33.22784810126582</v>
+        <v>33.481012658227854</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T53" s="1">
-        <v>-1.9</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>0.54</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="1">
         <v>35.44303797468354</v>
       </c>
-      <c r="D54" s="2">
-        <v>41.629629629629626</v>
-      </c>
-      <c r="E54" s="2">
+      <c r="D54" s="1">
+        <v>40.407407407407405</v>
+      </c>
+      <c r="E54" s="1">
         <v>-0.43</v>
       </c>
-      <c r="F54" s="2">
-        <v>-0.05302157269131072</v>
-      </c>
-      <c r="G54" s="2">
-        <v>1.46</v>
-      </c>
-      <c r="H54" s="2">
-        <v>63.63</v>
-      </c>
-      <c r="I54" s="2">
-        <v>9.72</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0.03241268225849441</v>
-      </c>
-      <c r="K54" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" s="2">
+      <c r="F54" s="1">
+        <v>-0.08513223155526206</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H54" s="1">
+        <v>54.83</v>
+      </c>
+      <c r="I54" s="1">
+        <v>4.04</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.030077081491101127</v>
+      </c>
+      <c r="K54" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
         <v>13</v>
       </c>
-      <c r="M54" s="2">
-        <v>-0.008430922374124128</v>
-      </c>
-      <c r="N54" s="2">
-        <v>9.925527396758586</v>
-      </c>
-      <c r="O54" s="2">
-        <v>58.22784810126582</v>
-      </c>
-      <c r="P54" s="2">
+      <c r="M54" s="1">
+        <v>-0.04334800203901268</v>
+      </c>
+      <c r="N54" s="1">
+        <v>6.025584133043034</v>
+      </c>
+      <c r="O54" s="1">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P54" s="1">
         <v>25.062459708672506</v>
       </c>
-      <c r="Q54" s="2">
-        <v>67.21518987341771</v>
-      </c>
-      <c r="R54" s="2">
-        <v>51.13924050632911</v>
-      </c>
-      <c r="S54" s="2" t="s">
+      <c r="Q54" s="1">
+        <v>64.43037974683544</v>
+      </c>
+      <c r="R54" s="1">
+        <v>49.11392405063291</v>
+      </c>
+      <c r="S54" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T54" s="2">
-        <v>-1.52</v>
+      <c r="T54" s="1">
+        <v>-3.54</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5434,49 +5431,49 @@
         <v>-0.26</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.1790060492823699</v>
+        <v>-0.16197313505260122</v>
       </c>
       <c r="G55" s="1">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H55" s="1">
-        <v>37.62</v>
+        <v>44.69</v>
       </c>
       <c r="I55" s="1">
-        <v>-3.56</v>
+        <v>-1.81</v>
       </c>
       <c r="J55" s="1">
-        <v>0.00042365856082820846</v>
+        <v>0.0009499959979441232</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>-48</v>
+        <v>-57</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.16058817197744502</v>
+        <v>-0.14247382794501817</v>
       </c>
       <c r="N55" s="1">
-        <v>-5.29019756357351</v>
+        <v>-3.886998457557516</v>
       </c>
       <c r="O55" s="1">
-        <v>36.708860759493675</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P55" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q55" s="1">
-        <v>46.582278481012665</v>
+        <v>48.227848101265835</v>
       </c>
       <c r="R55" s="1">
-        <v>38.67088607594937</v>
+        <v>39.0506329113924</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T55" s="1">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5496,49 +5493,49 @@
         <v>0.81</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.10471492447755065</v>
+        <v>-0.09411200319531839</v>
       </c>
       <c r="G56" s="1">
         <v>0.26</v>
       </c>
       <c r="H56" s="1">
-        <v>45.72</v>
+        <v>49.54</v>
       </c>
       <c r="I56" s="1">
-        <v>8.37</v>
+        <v>9.26</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.008041054038631564</v>
+        <v>-0.006743493601277909</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.17644770977041602</v>
+        <v>-0.16282384728870625</v>
       </c>
       <c r="N56" s="1">
-        <v>-6.876151342870604</v>
+        <v>-5.922000391926318</v>
       </c>
       <c r="O56" s="1">
-        <v>32.91139240506329</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P56" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q56" s="1">
-        <v>44.810126582278485</v>
+        <v>46.58227848101266</v>
       </c>
       <c r="R56" s="1">
-        <v>36.32911392405063</v>
+        <v>37.21518987341772</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T56" s="1">
-        <v>2.34</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5552,37 +5549,37 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D57" s="2">
-        <v>2.35505193578848</v>
+        <v>2.3866855524079322</v>
       </c>
       <c r="E57" s="2">
         <v>0.11</v>
       </c>
       <c r="F57" s="2">
-        <v>0.5547443642327915</v>
+        <v>0.5120440504377429</v>
       </c>
       <c r="G57" s="2">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="H57" s="2">
-        <v>66.28</v>
+        <v>59.62</v>
       </c>
       <c r="I57" s="2">
-        <v>135.95</v>
+        <v>119.86</v>
       </c>
       <c r="J57" s="2">
-        <v>0.08302087502985447</v>
+        <v>0.07848699843097959</v>
       </c>
       <c r="K57" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L57" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="M57" s="2">
-        <v>0.6526499225379185</v>
+        <v>0.6011837400724083</v>
       </c>
       <c r="N57" s="2">
-        <v>76.03361188796285</v>
+        <v>70.47875834418512</v>
       </c>
       <c r="O57" s="2">
         <v>92.40506329113924</v>
@@ -5591,7 +5588,7 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q57" s="2">
-        <v>80.25316455696203</v>
+        <v>79.11392405063292</v>
       </c>
       <c r="R57" s="2">
         <v>66.77215189873418</v>
@@ -5620,49 +5617,49 @@
         <v>-1.46</v>
       </c>
       <c r="F58" s="2">
-        <v>-0.020395804242056392</v>
+        <v>-0.03147240354967856</v>
       </c>
       <c r="G58" s="2">
         <v>1.62</v>
       </c>
       <c r="H58" s="2">
-        <v>57.98</v>
+        <v>52.48</v>
       </c>
       <c r="I58" s="2">
-        <v>44.43</v>
+        <v>39.99</v>
       </c>
       <c r="J58" s="2">
-        <v>0.023405428653427596</v>
+        <v>0.02326959230595297</v>
       </c>
       <c r="K58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M58" s="2">
-        <v>0.039704637489803796</v>
+        <v>0.02609697933937616</v>
       </c>
       <c r="N58" s="2">
-        <v>14.73908338315138</v>
+        <v>12.97008227088193</v>
       </c>
       <c r="O58" s="2">
-        <v>64.55696202531645</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P58" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q58" s="2">
-        <v>64.0506329113924</v>
+        <v>62.78481012658228</v>
       </c>
       <c r="R58" s="2">
-        <v>54.24050632911392</v>
+        <v>54.62025316455696</v>
       </c>
       <c r="S58" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T58" s="2">
-        <v>-1.08</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5682,49 +5679,49 @@
         <v>-2.31</v>
       </c>
       <c r="F59" s="2">
-        <v>0.17904261223547482</v>
+        <v>0.10891482034506436</v>
       </c>
       <c r="G59" s="2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="H59" s="2">
-        <v>51.69</v>
+        <v>46.28</v>
       </c>
       <c r="I59" s="2">
-        <v>43.37</v>
+        <v>37.99</v>
       </c>
       <c r="J59" s="2">
-        <v>0.02317032186491351</v>
+        <v>0.023569189817422096</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M59" s="2">
-        <v>0.200368575430651</v>
+        <v>0.13212828118742515</v>
       </c>
       <c r="N59" s="2">
-        <v>30.805477177236085</v>
+        <v>23.573212455686832</v>
       </c>
       <c r="O59" s="2">
-        <v>81.0126582278481</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P59" s="2">
-        <v>11.512523311327532</v>
+        <v>11.942274303251052</v>
       </c>
       <c r="Q59" s="2">
-        <v>59.36708860759494</v>
+        <v>58.86075949367089</v>
       </c>
       <c r="R59" s="2">
-        <v>56.898734177215196</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T59" s="2">
-        <v>0.32</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5744,49 +5741,49 @@
         <v>0.62</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.1489477353062037</v>
+        <v>-0.12638494034057418</v>
       </c>
       <c r="G60" s="1">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H60" s="1">
-        <v>38.66</v>
+        <v>38.55</v>
       </c>
       <c r="I60" s="1">
-        <v>-0.85</v>
+        <v>-0.92</v>
       </c>
       <c r="J60" s="1">
-        <v>-0.009984339530045553</v>
+        <v>-0.008735830250640496</v>
       </c>
       <c r="K60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M60" s="1">
-        <v>-0.2090481770380639</v>
+        <v>-0.18302578479593445</v>
       </c>
       <c r="N60" s="1">
-        <v>-10.136198069635396</v>
+        <v>-7.942194142649135</v>
       </c>
       <c r="O60" s="1">
-        <v>26.582278481012654</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P60" s="1">
         <v>12.798408482128673</v>
       </c>
       <c r="Q60" s="1">
-        <v>37.21518987341772</v>
+        <v>37.34177215189873</v>
       </c>
       <c r="R60" s="1">
-        <v>30.506329113924046</v>
+        <v>31.89873417721519</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T60" s="1">
-        <v>1.71</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5806,49 +5803,49 @@
         <v>-0.07</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.17099099367816528</v>
+        <v>-0.16038838312440135</v>
       </c>
       <c r="G61" s="1">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="H61" s="1">
-        <v>42.52</v>
+        <v>43.76</v>
       </c>
       <c r="I61" s="1">
-        <v>8.1</v>
+        <v>8.57</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.006484471124865406</v>
+        <v>-0.005955899128925325</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.1758378034952508</v>
+        <v>-0.16410253685917908</v>
       </c>
       <c r="N61" s="1">
-        <v>-6.81516071535408</v>
+        <v>-6.0498693489736</v>
       </c>
       <c r="O61" s="1">
-        <v>34.177215189873415</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P61" s="1">
         <v>16.149676494964734</v>
       </c>
       <c r="Q61" s="1">
-        <v>52.78481012658228</v>
+        <v>53.03797468354429</v>
       </c>
       <c r="R61" s="1">
-        <v>42.27848101265823</v>
+        <v>42.0253164556962</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T61" s="1">
-        <v>-0.57</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5862,37 +5859,37 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D62" s="4">
-        <v>4.831074035453597</v>
+        <v>4.924921793534932</v>
       </c>
       <c r="E62" s="4">
         <v>-8.13</v>
       </c>
       <c r="F62" s="4">
-        <v>0.7870039611746505</v>
+        <v>0.803418982178189</v>
       </c>
       <c r="G62" s="4">
-        <v>4.63</v>
+        <v>4.77</v>
       </c>
       <c r="H62" s="4">
-        <v>65.5</v>
+        <v>59.54</v>
       </c>
       <c r="I62" s="4">
-        <v>233.6</v>
+        <v>211.16</v>
       </c>
       <c r="J62" s="4">
-        <v>0.10154333708964342</v>
+        <v>0.09688950559761088</v>
       </c>
       <c r="K62" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="4">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="M62" s="4">
-        <v>1.1388823538950577</v>
+        <v>1.1534779716809893</v>
       </c>
       <c r="N62" s="4">
-        <v>124.65685502367674</v>
+        <v>125.70818150504324</v>
       </c>
       <c r="O62" s="4">
         <v>98.73417721518987</v>
@@ -5901,7 +5898,7 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q62" s="4">
-        <v>82.91139240506328</v>
+        <v>81.89873417721519</v>
       </c>
       <c r="R62" s="4">
         <v>72.02531645569621</v>
@@ -5930,49 +5927,49 @@
         <v>-5.36</v>
       </c>
       <c r="F63" s="2">
-        <v>0.659813799317615</v>
+        <v>0.582807567756483</v>
       </c>
       <c r="G63" s="2">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="H63" s="2">
-        <v>73.08</v>
+        <v>60.53</v>
       </c>
       <c r="I63" s="2">
-        <v>135.38</v>
+        <v>117.34</v>
       </c>
       <c r="J63" s="2">
-        <v>0.08759541191729123</v>
+        <v>0.0846049925147908</v>
       </c>
       <c r="K63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M63" s="2">
-        <v>0.7596580815495761</v>
+        <v>0.6775184879933149</v>
       </c>
       <c r="N63" s="2">
-        <v>86.7344277891286</v>
+        <v>78.1122331362758</v>
       </c>
       <c r="O63" s="2">
-        <v>93.67088607594937</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P63" s="2">
         <v>20.9978319173529</v>
       </c>
       <c r="Q63" s="2">
-        <v>78.10126582278482</v>
+        <v>76.58227848101265</v>
       </c>
       <c r="R63" s="2">
-        <v>67.02531645569621</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T63" s="2">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5992,49 +5989,49 @@
         <v>-0.88</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.15173270683304146</v>
+        <v>-0.12395774130970882</v>
       </c>
       <c r="G64" s="1">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H64" s="1">
-        <v>49.18</v>
+        <v>48.94</v>
       </c>
       <c r="I64" s="1">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.007675355116232243</v>
+        <v>-0.0058368555469811645</v>
       </c>
       <c r="K64" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M64" s="1">
-        <v>-0.2186186823088213</v>
+        <v>-0.18895543166831896</v>
       </c>
       <c r="N64" s="1">
-        <v>-11.09324859671114</v>
+        <v>-8.535158829887585</v>
       </c>
       <c r="O64" s="1">
-        <v>21.518987341772153</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P64" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q64" s="1">
-        <v>47.08860759493671</v>
+        <v>48.22784810126583</v>
       </c>
       <c r="R64" s="1">
-        <v>33.924050632911396</v>
+        <v>36.64556962025316</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T64" s="1">
-        <v>-3.48</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6054,49 +6051,49 @@
         <v>-0.2</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.12564894128578813</v>
+        <v>-0.04404825164755059</v>
       </c>
       <c r="G65" s="1">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H65" s="1">
-        <v>48.71</v>
+        <v>52.39</v>
       </c>
       <c r="I65" s="1">
-        <v>-30.99</v>
+        <v>-28.96</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.011724288133944402</v>
+        <v>-0.014723341169018873</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-191</v>
+        <v>-188</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.12371021735895393</v>
+        <v>-0.04033409791277287</v>
       </c>
       <c r="N65" s="1">
-        <v>-1.602402101724396</v>
+        <v>6.326974545667026</v>
       </c>
       <c r="O65" s="1">
-        <v>44.303797468354425</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P65" s="1">
         <v>48.12800106814908</v>
       </c>
       <c r="Q65" s="1">
-        <v>39.49367088607595</v>
+        <v>39.11392405063291</v>
       </c>
       <c r="R65" s="1">
-        <v>31.89873417721519</v>
+        <v>33.924050632911396</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T65" s="1">
-        <v>2.85</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6116,49 +6113,49 @@
         <v>-1.48</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.04838973089937444</v>
+        <v>-0.05302032012287701</v>
       </c>
       <c r="G66" s="1">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H66" s="1">
-        <v>50.19</v>
+        <v>50.15</v>
       </c>
       <c r="I66" s="1">
-        <v>-11.09</v>
+        <v>-11.04</v>
       </c>
       <c r="J66" s="1">
-        <v>-0.0007620642574330307</v>
+        <v>-0.0009719116505956617</v>
       </c>
       <c r="K66" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="1">
-        <v>-73</v>
+        <v>-71</v>
       </c>
       <c r="M66" s="1">
-        <v>-0.034818663411535056</v>
+        <v>-0.039092243617460554</v>
       </c>
       <c r="N66" s="1">
-        <v>7.286753293017485</v>
+        <v>6.451159975198248</v>
       </c>
       <c r="O66" s="1">
-        <v>54.43037974683544</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P66" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q66" s="1">
-        <v>50.37974683544304</v>
+        <v>50.25316455696203</v>
       </c>
       <c r="R66" s="1">
-        <v>44.43037974683545</v>
+        <v>44.936708860759495</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T66" s="1">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6172,55 +6169,55 @@
         <v>69.62025316455697</v>
       </c>
       <c r="D67" s="1">
-        <v>121.84625850340136</v>
+        <v>200.22857142857146</v>
       </c>
       <c r="E67" s="1">
         <v>-0.18</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.20663102503993735</v>
+        <v>-0.20626589337855733</v>
       </c>
       <c r="G67" s="1">
         <v>0.33</v>
       </c>
       <c r="H67" s="1">
-        <v>39.62</v>
+        <v>39.87</v>
       </c>
       <c r="I67" s="1">
         <v>1.35</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.011090693921459435</v>
+        <v>-0.010946538905365932</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.271578276588883</v>
+        <v>-0.2684779684360842</v>
       </c>
       <c r="N67" s="1">
-        <v>-16.38920802471731</v>
+        <v>-16.48741250666411</v>
       </c>
       <c r="O67" s="1">
-        <v>13.924050632911392</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P67" s="1">
         <v>18.003852697255347</v>
       </c>
       <c r="Q67" s="1">
-        <v>60.12658227848101</v>
+        <v>60</v>
       </c>
       <c r="R67" s="1">
-        <v>44.11392405063291</v>
+        <v>43.734177215189874</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T67" s="1">
-        <v>-0.82</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6240,49 +6237,49 @@
         <v>0.19</v>
       </c>
       <c r="F68" s="3">
-        <v>-0.2874281543757484</v>
+        <v>-0.25740260569165335</v>
       </c>
       <c r="G68" s="3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H68" s="3">
-        <v>33.52</v>
+        <v>44.83</v>
       </c>
       <c r="I68" s="3">
-        <v>-15.25</v>
+        <v>-11.43</v>
       </c>
       <c r="J68" s="3">
-        <v>-0.015387484507357942</v>
+        <v>-0.014024373117659573</v>
       </c>
       <c r="K68" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="3">
-        <v>-63</v>
+        <v>-61</v>
       </c>
       <c r="M68" s="3">
-        <v>-0.2408987801317276</v>
+        <v>-0.21190422244062623</v>
       </c>
       <c r="N68" s="3">
-        <v>-13.321258379001765</v>
+        <v>-10.830037907118312</v>
       </c>
       <c r="O68" s="3">
-        <v>17.72151898734177</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P68" s="3">
         <v>29.145649851223904</v>
       </c>
       <c r="Q68" s="3">
-        <v>36.07594936708861</v>
+        <v>40.12658227848101</v>
       </c>
       <c r="R68" s="3">
-        <v>26.139240506329113</v>
+        <v>28.164556962025312</v>
       </c>
       <c r="S68" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T68" s="3">
-        <v>-1.58</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6302,31 +6299,31 @@
         <v>1.82</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.22580565225190932</v>
+        <v>-0.21033504627324695</v>
       </c>
       <c r="G69" s="3">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H69" s="3">
-        <v>33.16</v>
+        <v>35.41</v>
       </c>
       <c r="I69" s="3">
-        <v>-16.82</v>
+        <v>-16.11</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.013238691678533204</v>
+        <v>-0.012926741798049627</v>
       </c>
       <c r="K69" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.23937671973974872</v>
+        <v>-0.22240604591127455</v>
       </c>
       <c r="N69" s="3">
-        <v>-13.169052339803875</v>
+        <v>-11.880220254183154</v>
       </c>
       <c r="O69" s="3">
         <v>18.9873417721519</v>
@@ -6335,16 +6332,16 @@
         <v>31.450467124868602</v>
       </c>
       <c r="Q69" s="3">
-        <v>37.46835443037975</v>
+        <v>37.84810126582279</v>
       </c>
       <c r="R69" s="3">
-        <v>26.898734177215186</v>
+        <v>27.025316455696203</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.82</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6364,31 +6361,31 @@
         <v>-1.56</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.45495617366977387</v>
+        <v>-0.45800455981527743</v>
       </c>
       <c r="G70" s="3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H70" s="3">
-        <v>30.09</v>
+        <v>36.17</v>
       </c>
       <c r="I70" s="3">
-        <v>-32.88</v>
+        <v>-31.6</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.03576131515339131</v>
+        <v>-0.03386514245475491</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-97</v>
+        <v>-100</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.44429319207218576</v>
+        <v>-0.4468620986109443</v>
       </c>
       <c r="N70" s="3">
-        <v>-33.66069957304759</v>
+        <v>-34.32582552415012</v>
       </c>
       <c r="O70" s="3">
         <v>1.2658227848101267</v>
@@ -6397,78 +6394,78 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q70" s="3">
-        <v>36.075949367088604</v>
+        <v>36.962025316455694</v>
       </c>
       <c r="R70" s="3">
-        <v>22.151898734177216</v>
+        <v>22.27848101265823</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T70" s="3">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="1">
         <v>5.18</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="1">
         <v>60.75949367088608</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="1">
         <v>0.7837837837837839</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="1">
         <v>-0.2</v>
       </c>
-      <c r="F71" s="3">
-        <v>-0.257648719824491</v>
-      </c>
-      <c r="G71" s="3">
+      <c r="F71" s="1">
+        <v>-0.19455741925371617</v>
+      </c>
+      <c r="G71" s="1">
         <v>1.01</v>
       </c>
-      <c r="H71" s="3">
-        <v>50.11</v>
-      </c>
-      <c r="I71" s="3">
-        <v>-7.21</v>
-      </c>
-      <c r="J71" s="3">
-        <v>-0.01041135545749011</v>
-      </c>
-      <c r="K71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3">
-        <v>-62</v>
-      </c>
-      <c r="M71" s="3">
-        <v>-0.2566793578610739</v>
-      </c>
-      <c r="N71" s="3">
-        <v>-14.899316151936398</v>
-      </c>
-      <c r="O71" s="3">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="P71" s="3">
+      <c r="H71" s="1">
+        <v>60.86</v>
+      </c>
+      <c r="I71" s="1">
+        <v>-3.21</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-0.007594479396489348</v>
+      </c>
+      <c r="K71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1">
+        <v>-64</v>
+      </c>
+      <c r="M71" s="1">
+        <v>-0.19362888082002172</v>
+      </c>
+      <c r="N71" s="1">
+        <v>-9.002503745057872</v>
+      </c>
+      <c r="O71" s="1">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="P71" s="1">
         <v>19.13407224404345</v>
       </c>
-      <c r="Q71" s="3">
-        <v>42.53164556962026</v>
-      </c>
-      <c r="R71" s="3">
-        <v>28.227848101265828</v>
-      </c>
-      <c r="S71" s="3" t="s">
+      <c r="Q71" s="1">
+        <v>47.8481012658228</v>
+      </c>
+      <c r="R71" s="1">
+        <v>32.594936708860764</v>
+      </c>
+      <c r="S71" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T71" s="3">
-        <v>2.03</v>
+      <c r="T71" s="1">
+        <v>6.39</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6482,55 +6479,55 @@
         <v>78.48101265822784</v>
       </c>
       <c r="D72" s="3">
-        <v>0.21305182341650677</v>
+        <v>0.21976967370441466</v>
       </c>
       <c r="E72" s="3">
         <v>-1.49</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.30773563356932304</v>
+        <v>-0.293697481647043</v>
       </c>
       <c r="G72" s="3">
         <v>1.14</v>
       </c>
       <c r="H72" s="3">
-        <v>33.96</v>
+        <v>36.7</v>
       </c>
       <c r="I72" s="3">
-        <v>-11.92</v>
+        <v>-11.1</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.012895102685770758</v>
+        <v>-0.011535808425502841</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L72" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.29416456608148367</v>
+        <v>-0.28069794357532096</v>
       </c>
       <c r="N72" s="3">
-        <v>-18.647836973977373</v>
+        <v>-17.709410020587796</v>
       </c>
       <c r="O72" s="3">
-        <v>12.658227848101266</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P72" s="3">
         <v>19.4578633420253</v>
       </c>
       <c r="Q72" s="3">
-        <v>37.9746835443038</v>
+        <v>38.60759493670885</v>
       </c>
       <c r="R72" s="3">
-        <v>27.84810126582278</v>
+        <v>27.21518987341772</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T72" s="3">
-        <v>0.38</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6550,49 +6547,49 @@
         <v>-1.26</v>
       </c>
       <c r="F73" s="2">
-        <v>0.2260761832650745</v>
+        <v>0.2824056985654553</v>
       </c>
       <c r="G73" s="2">
         <v>1.17</v>
       </c>
       <c r="H73" s="2">
-        <v>62.34</v>
+        <v>63.48</v>
       </c>
       <c r="I73" s="2">
-        <v>42.04</v>
+        <v>42.55</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03167383159955737</v>
+        <v>0.03052633467924307</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M73" s="2">
-        <v>0.2425553366431652</v>
+        <v>0.29819085193826056</v>
       </c>
       <c r="N73" s="2">
-        <v>35.02415329848752</v>
+        <v>40.179469530770355</v>
       </c>
       <c r="O73" s="2">
-        <v>86.07594936708861</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>66.07594936708861</v>
+        <v>67.72151898734177</v>
       </c>
       <c r="R73" s="2">
-        <v>61.51898734177215</v>
+        <v>62.151898734177216</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>0.51</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6612,7 +6609,7 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="2">
-        <v>0.16119109676979138</v>
+        <v>0.1627766418008498</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
@@ -6621,22 +6618,22 @@
         <v>82.84</v>
       </c>
       <c r="I74" s="2">
-        <v>31.87</v>
+        <v>31.56</v>
       </c>
       <c r="J74" s="2">
-        <v>0.022037295034327584</v>
+        <v>0.02106929882863832</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M74" s="2">
-        <v>0.1408344955380323</v>
+        <v>0.14327733469326676</v>
       </c>
       <c r="N74" s="2">
-        <v>24.852069187974223</v>
+        <v>24.68811780627098</v>
       </c>
       <c r="O74" s="2">
         <v>74.68354430379746</v>
@@ -6645,16 +6642,16 @@
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>65.56962025316456</v>
+        <v>65.0632911392405</v>
       </c>
       <c r="R74" s="2">
-        <v>57.40506329113924</v>
+        <v>57.27848101265823</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6674,19 +6671,19 @@
         <v>-2.27</v>
       </c>
       <c r="F75" s="1">
-        <v>0.07659172329880896</v>
+        <v>0.05665305738230157</v>
       </c>
       <c r="G75" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H75" s="1">
-        <v>59.46</v>
+        <v>59.82</v>
       </c>
       <c r="I75" s="1">
-        <v>14.74</v>
+        <v>14.82</v>
       </c>
       <c r="J75" s="1">
-        <v>0.005399889390566219</v>
+        <v>0.005244941446567493</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6695,10 +6692,10 @@
         <v>20</v>
       </c>
       <c r="M75" s="1">
-        <v>0.07368363740855766</v>
+        <v>0.05293890364752385</v>
       </c>
       <c r="N75" s="1">
-        <v>18.136983375026755</v>
+        <v>15.654274701696687</v>
       </c>
       <c r="O75" s="1">
         <v>67.08860759493672</v>
@@ -6707,16 +6704,16 @@
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>59.620253164556964</v>
+        <v>59.74683544303797</v>
       </c>
       <c r="R75" s="1">
-        <v>46.582278481012665</v>
+        <v>46.455696202531655</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6736,49 +6733,49 @@
         <v>3.5</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.035469744789771454</v>
+        <v>-0.03383881081005641</v>
       </c>
       <c r="G76" s="1">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H76" s="1">
-        <v>49.42</v>
+        <v>50.56</v>
       </c>
       <c r="I76" s="1">
-        <v>12.88</v>
+        <v>13.34</v>
       </c>
       <c r="J76" s="1">
-        <v>0.017557388392607762</v>
+        <v>0.016908958766601135</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L76" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.06261187976545024</v>
+        <v>-0.0607664253871949</v>
       </c>
       <c r="N76" s="1">
-        <v>4.507431657625964</v>
+        <v>4.283741798224821</v>
       </c>
       <c r="O76" s="1">
-        <v>49.36708860759494</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>48.481012658227854</v>
+        <v>48.607594936708864</v>
       </c>
       <c r="R76" s="1">
-        <v>39.367088607594944</v>
+        <v>38.98734177215191</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>-2.85</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6798,19 +6795,19 @@
         <v>-0.19</v>
       </c>
       <c r="F77" s="2">
-        <v>-0.004879866713475789</v>
+        <v>0.011743538489930455</v>
       </c>
       <c r="G77" s="2">
         <v>0.98</v>
       </c>
       <c r="H77" s="2">
-        <v>58.35</v>
+        <v>64.16</v>
       </c>
       <c r="I77" s="2">
-        <v>9.21</v>
+        <v>11.8</v>
       </c>
       <c r="J77" s="2">
-        <v>0.007734524845225627</v>
+        <v>0.0077817686474400335</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6819,28 +6816,28 @@
         <v>8</v>
       </c>
       <c r="M77" s="2">
-        <v>-0.006818590640309985</v>
+        <v>0.009886461622541587</v>
       </c>
       <c r="N77" s="2">
-        <v>10.086760570140003</v>
+        <v>11.349030499198465</v>
       </c>
       <c r="O77" s="2">
-        <v>59.49367088607595</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>61.64556962025317</v>
+        <v>63.67088607594937</v>
       </c>
       <c r="R77" s="2">
-        <v>54.30379746835443</v>
+        <v>55.44303797468354</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>-0.13</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6854,25 +6851,25 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D78" s="2">
-        <v>-0.6994660564454616</v>
+        <v>-0.7162471395881006</v>
       </c>
       <c r="E78" s="2">
         <v>0.93</v>
       </c>
       <c r="F78" s="2">
-        <v>0.15335529684028812</v>
+        <v>0.1704180033472582</v>
       </c>
       <c r="G78" s="2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H78" s="2">
-        <v>69.85</v>
+        <v>69.65</v>
       </c>
       <c r="I78" s="2">
-        <v>35.04</v>
+        <v>34.51</v>
       </c>
       <c r="J78" s="2">
-        <v>0.02697399814603973</v>
+        <v>0.028051727554599237</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6881,28 +6878,28 @@
         <v>64</v>
       </c>
       <c r="M78" s="2">
-        <v>0.17758934592571562</v>
+        <v>0.1945600026233134</v>
       </c>
       <c r="N78" s="2">
-        <v>28.527554226742563</v>
+        <v>29.816384599275647</v>
       </c>
       <c r="O78" s="2">
-        <v>77.21518987341773</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P78" s="2">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="2">
-        <v>60.506329113924046</v>
+        <v>61.0126582278481</v>
       </c>
       <c r="R78" s="2">
-        <v>50.50632911392405</v>
+        <v>51.51898734177215</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>0.82</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6916,25 +6913,25 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="2">
-        <v>2.6156351791530943</v>
+        <v>2.7622149837133554</v>
       </c>
       <c r="E79" s="2">
         <v>0.99</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4334131898942318</v>
+        <v>0.4479484078597269</v>
       </c>
       <c r="G79" s="2">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="H79" s="2">
-        <v>88.46</v>
+        <v>88.71</v>
       </c>
       <c r="I79" s="2">
-        <v>54.22</v>
+        <v>54.58</v>
       </c>
       <c r="J79" s="2">
-        <v>0.032420325485079365</v>
+        <v>0.03728981357789821</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
@@ -6943,28 +6940,28 @@
         <v>80</v>
       </c>
       <c r="M79" s="2">
-        <v>0.43050510400398045</v>
+        <v>0.44330571569125476</v>
       </c>
       <c r="N79" s="2">
-        <v>53.81913003456905</v>
+        <v>54.690955906069796</v>
       </c>
       <c r="O79" s="2">
-        <v>89.87341772151899</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>65.69620253164557</v>
+        <v>66.0759493670886</v>
       </c>
       <c r="R79" s="2">
-        <v>59.24050632911393</v>
+        <v>59.74683544303798</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6978,55 +6975,55 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8211009174311926</v>
+        <v>0.8371559633027521</v>
       </c>
       <c r="E80" s="2">
         <v>4.67</v>
       </c>
       <c r="F80" s="2">
-        <v>0.9500398162459049</v>
+        <v>0.9467881480859501</v>
       </c>
       <c r="G80" s="2">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2">
-        <v>62.97</v>
+        <v>60.51</v>
       </c>
       <c r="I80" s="2">
-        <v>64.4</v>
+        <v>61.14</v>
       </c>
       <c r="J80" s="2">
-        <v>0.05298790653590615</v>
+        <v>0.051604147781813624</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M80" s="2">
-        <v>0.9519785401727392</v>
+        <v>0.9467881480859501</v>
       </c>
       <c r="N80" s="2">
-        <v>105.96647365144491</v>
+        <v>105.03919914553934</v>
       </c>
       <c r="O80" s="2">
-        <v>97.46835443037975</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P80" s="2">
         <v>14.059118714058641</v>
       </c>
       <c r="Q80" s="2">
-        <v>69.36708860759495</v>
+        <v>69.49367088607596</v>
       </c>
       <c r="R80" s="2">
-        <v>65.37974683544304</v>
+        <v>65.31645569620254</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>
@@ -7053,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>35.9493670886076</v>
+        <v>38.48101265822785</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7061,7 +7058,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65.31645569620254</v>
+        <v>65.69620253164557</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7069,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>15.126582278481017</v>
+        <v>19.430379746835445</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7077,7 +7074,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>43.670886075949376</v>
+        <v>42.278481012658226</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7085,7 +7082,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>41.39240506329114</v>
+        <v>42.911392405063296</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7093,7 +7090,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.12658227848102</v>
+        <v>54.74683544303797</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7101,7 +7098,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.25316455696202</v>
+        <v>55.12658227848101</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7109,7 +7106,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40.56962025316455</v>
+        <v>38.544303797468345</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7117,7 +7114,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.59493670886076</v>
+        <v>37.21518987341773</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7125,7 +7122,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>47.21518987341773</v>
+        <v>50.12658227848102</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7133,7 +7130,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>22.341772151898734</v>
+        <v>26.0126582278481</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7141,7 +7138,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>12.72151898734177</v>
+        <v>10.696202531645572</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7149,7 +7146,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>36.45569620253165</v>
+        <v>39.55696202531645</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7165,7 +7162,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>37.53164556962025</v>
+        <v>31.582278481012654</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7173,7 +7170,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18.227848101265824</v>
+        <v>17.215189873417724</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7181,7 +7178,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>29.556962025316462</v>
+        <v>29.430379746835445</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7189,7 +7186,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>42.27848101265823</v>
+        <v>41.0126582278481</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7197,7 +7194,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>33.9873417721519</v>
+        <v>39.050632911392405</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7205,7 +7202,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>47.34177215189873</v>
+        <v>44.68354430379747</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7213,7 +7210,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.18987341772152</v>
+        <v>28.417721518987342</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7221,7 +7218,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>35.443037974683534</v>
+        <v>34.810126582278485</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7229,7 +7226,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>28.417721518987342</v>
+        <v>27.088607594936708</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7237,7 +7234,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.177215189873419</v>
+        <v>7.784810126582279</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7253,7 +7250,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>25.063291139240505</v>
+        <v>23.67088607594937</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7261,7 +7258,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>20.253164556962027</v>
+        <v>18.35443037974684</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7269,7 +7266,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>24.746835443037973</v>
+        <v>24.36708860759493</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7277,7 +7274,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>46.32911392405064</v>
+        <v>44.683544303797476</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7285,7 +7282,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>60.9493670886076</v>
+        <v>59.81012658227849</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7293,7 +7290,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>15.632911392405063</v>
+        <v>15.759493670886073</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7301,7 +7298,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>42.27848101265823</v>
+        <v>43.79746835443038</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7309,7 +7306,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>50.949367088607595</v>
+        <v>52.46835443037974</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7325,7 +7322,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>30.696202531645564</v>
+        <v>25.632911392405067</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7333,7 +7330,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>37.84810126582279</v>
+        <v>37.21518987341772</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7341,7 +7338,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>54.43037974683544</v>
+        <v>55.189873417721515</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7349,7 +7346,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>52.34177215189874</v>
+        <v>55.12658227848102</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7357,7 +7354,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>33.101265822784804</v>
+        <v>32.974683544303794</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7365,7 +7362,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>30.44303797468355</v>
+        <v>26.64556962025317</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7373,7 +7370,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>37.72151898734177</v>
+        <v>37.848101265822784</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7381,7 +7378,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>44.55696202531645</v>
+        <v>48.60759493670886</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7389,7 +7386,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>29.177215189873415</v>
+        <v>29.55696202531646</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7397,7 +7394,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>57.34177215189874</v>
+        <v>56.32911392405063</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7405,7 +7402,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>30.379746835443033</v>
+        <v>27.721518987341764</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7421,7 +7418,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>63.60759493670886</v>
+        <v>61.77215189873418</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7429,7 +7426,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>62.594936708860764</v>
+        <v>62.21518987341772</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7437,7 +7434,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>21.77215189873418</v>
+        <v>21.645569620253163</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7445,7 +7442,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>41.329113924050645</v>
+        <v>37.40506329113924</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7453,7 +7450,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>54.68354430379747</v>
+        <v>55.44303797468355</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7461,7 +7458,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>33.22784810126582</v>
+        <v>33.481012658227854</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7469,7 +7466,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>51.13924050632911</v>
+        <v>49.11392405063291</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7477,7 +7474,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>38.67088607594937</v>
+        <v>39.0506329113924</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7485,7 +7482,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>36.32911392405063</v>
+        <v>37.21518987341772</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7501,7 +7498,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>54.24050632911392</v>
+        <v>54.62025316455696</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7509,7 +7506,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>56.898734177215196</v>
+        <v>55.00000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7517,7 +7514,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>30.506329113924046</v>
+        <v>31.89873417721519</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7525,7 +7522,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>42.27848101265823</v>
+        <v>42.0253164556962</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7541,7 +7538,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>67.02531645569621</v>
+        <v>67.40506329113924</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7549,7 +7546,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>33.924050632911396</v>
+        <v>36.64556962025316</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7557,7 +7554,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>31.89873417721519</v>
+        <v>33.924050632911396</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7565,7 +7562,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>44.43037974683545</v>
+        <v>44.936708860759495</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7573,7 +7570,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>44.11392405063291</v>
+        <v>43.734177215189874</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7581,7 +7578,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>26.139240506329113</v>
+        <v>28.164556962025312</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7589,7 +7586,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>26.898734177215186</v>
+        <v>27.025316455696203</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7597,7 +7594,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>22.151898734177216</v>
+        <v>22.27848101265823</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7605,7 +7602,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>28.227848101265828</v>
+        <v>32.594936708860764</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7613,7 +7610,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>27.84810126582278</v>
+        <v>27.21518987341772</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7621,7 +7618,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>61.51898734177215</v>
+        <v>62.151898734177216</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7629,7 +7626,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>57.40506329113924</v>
+        <v>57.27848101265823</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7637,7 +7634,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>46.582278481012665</v>
+        <v>46.455696202531655</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7645,7 +7642,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>39.367088607594944</v>
+        <v>38.98734177215191</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7653,7 +7650,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>54.30379746835443</v>
+        <v>55.44303797468354</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7661,7 +7658,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>50.50632911392405</v>
+        <v>51.51898734177215</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7669,7 +7666,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>59.24050632911393</v>
+        <v>59.74683544303798</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7677,7 +7674,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>65.37974683544304</v>
+        <v>65.31645569620254</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="228">
   <si>
     <t>Ticker</t>
   </si>
@@ -163,12 +163,18 @@
     <t>IDCC</t>
   </si>
   <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
     <t>VRT</t>
   </si>
   <si>
-    <t>BE</t>
-  </si>
-  <si>
     <t>SMRT</t>
   </si>
   <si>
@@ -193,9 +199,6 @@
     <t>MU</t>
   </si>
   <si>
-    <t>CAT</t>
-  </si>
-  <si>
     <t>GEV</t>
   </si>
   <si>
@@ -232,9 +235,6 @@
     <t>NKE</t>
   </si>
   <si>
-    <t>MMM</t>
-  </si>
-  <si>
     <t>SHW</t>
   </si>
   <si>
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-18</t>
+    <t>2026-05-19</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2">
         <v>72.02531645569621</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>67.40506329113924</v>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4">
         <v>66.77215189873418</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>62.21518987341772</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>61.77215189873418</v>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>55.44303797468355</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20">
         <v>55.00000000000001</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>54.62025316455696</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26">
         <v>49.11392405063291</v>
@@ -1677,7 +1677,7 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>44.68354430379747</v>
+        <v>44.55696202531646</v>
       </c>
       <c r="C30" t="s">
         <v>220</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32">
         <v>43.734177215189874</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B34">
         <v>42.0253164556962</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B41">
-        <v>37.40506329113924</v>
+        <v>37.278481012658226</v>
       </c>
       <c r="C41" t="s">
         <v>219</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B42">
         <v>37.21518987341772</v>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B43">
         <v>36.64556962025316</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <v>33.924050632911396</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>33.481012658227854</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>32.594936708860764</v>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>31.89873417721519</v>
@@ -1922,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1992,66 +1992,76 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2201,7 +2211,7 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>24.104918032786884</v>
+        <v>24.085245901639347</v>
       </c>
       <c r="E3" s="2">
         <v>1.88</v>
@@ -2225,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M3" s="2">
         <v>0.9694214985576408</v>
@@ -2263,7 +2273,7 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D4" s="3">
-        <v>9.865822784810128</v>
+        <v>9.863291139240506</v>
       </c>
       <c r="E4" s="3">
         <v>1.25</v>
@@ -2349,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="M5" s="1">
         <v>-0.10516245974142535</v>
@@ -2367,13 +2377,13 @@
         <v>58.22784810126582</v>
       </c>
       <c r="R5" s="1">
-        <v>42.278481012658226</v>
+        <v>42.151898734177216</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-3.04</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2449,7 +2459,7 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D7" s="2">
-        <v>6.297959183673469</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="E7" s="2">
         <v>0.36</v>
@@ -2535,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-214</v>
+        <v>-213</v>
       </c>
       <c r="M8" s="2">
         <v>0.24936585408648937</v>
@@ -2597,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="M9" s="1">
         <v>-0.0876664275741077</v>
@@ -2783,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3">
-        <v>-51</v>
+        <v>-50</v>
       </c>
       <c r="M12" s="3">
         <v>-0.22077484670394754</v>
@@ -2863,13 +2873,13 @@
         <v>25.063291139240505</v>
       </c>
       <c r="R13" s="3">
-        <v>10.696202531645572</v>
+        <v>10.569620253164558</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-5.19</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2907,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M14" s="1">
         <v>-0.048061739538433956</v>
@@ -2945,7 +2955,7 @@
         <v>18.9873417721519</v>
       </c>
       <c r="D15" s="2">
-        <v>63.666666666666664</v>
+        <v>63.57142857142858</v>
       </c>
       <c r="E15" s="2">
         <v>5.49</v>
@@ -2969,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M15" s="2">
         <v>1.2387520997686037</v>
@@ -3031,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M16" s="1">
         <v>-0.06514236193865997</v>
@@ -3155,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M18" s="3">
         <v>-0.31292873088775</v>
@@ -3217,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M19" s="1">
         <v>-0.12256914112878325</v>
@@ -3341,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M21" s="1">
         <v>-0.014865909731803129</v>
@@ -3359,13 +3369,13 @@
         <v>64.17721518987341</v>
       </c>
       <c r="R21" s="1">
-        <v>44.68354430379747</v>
+        <v>44.55696202531646</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="1">
-        <v>5.89</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3403,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M22" s="3">
         <v>-0.22923059531017098</v>
@@ -3465,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M23" s="1">
         <v>-0.1475275040239301</v>
@@ -3545,13 +3555,13 @@
         <v>25.56962025316456</v>
       </c>
       <c r="R24" s="3">
-        <v>27.088607594936708</v>
+        <v>26.962025316455694</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-3.92</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3651,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="M26" s="1">
         <v>0.38253241099337254</v>
@@ -3713,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M27" s="3">
         <v>-0.06756774541152799</v>
@@ -3875,7 +3885,7 @@
         <v>46.835443037974684</v>
       </c>
       <c r="D30" s="1">
-        <v>2523.594871794872</v>
+        <v>2783.0820512820515</v>
       </c>
       <c r="E30" s="1">
         <v>2.51</v>
@@ -3937,7 +3947,7 @@
         <v>59.49367088607595</v>
       </c>
       <c r="D31" s="2">
-        <v>10.729044834307992</v>
+        <v>10.775828460038985</v>
       </c>
       <c r="E31" s="2">
         <v>0.99</v>
@@ -3961,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M31" s="2">
         <v>0.1615371340905536</v>
@@ -4023,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M32" s="3">
         <v>-0.2930391233912797</v>
@@ -4035,19 +4045,19 @@
         <v>8.860759493670885</v>
       </c>
       <c r="P32" s="3">
-        <v>40.53452147980343</v>
+        <v>38.62068790128861</v>
       </c>
       <c r="Q32" s="3">
         <v>31.139240506329113</v>
       </c>
       <c r="R32" s="3">
-        <v>15.759493670886073</v>
+        <v>16.13924050632911</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-13.61</v>
+        <v>-13.23</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4085,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M33" s="1">
         <v>-0.03637604470456979</v>
@@ -4147,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M34" s="2">
         <v>0.21068003478617636</v>
@@ -4209,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M35" s="3">
         <v>-0.27897198259300393</v>
@@ -4221,19 +4231,19 @@
         <v>11.39240506329114</v>
       </c>
       <c r="P35" s="3">
-        <v>29.946003174037394</v>
+        <v>29.3533388963776</v>
       </c>
       <c r="Q35" s="3">
         <v>32.91139240506329</v>
       </c>
       <c r="R35" s="3">
-        <v>23.29113924050633</v>
+        <v>23.417721518987342</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4271,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="L36" s="3">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="M36" s="3">
         <v>-0.23894593915481266</v>
@@ -4395,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>-44</v>
+        <v>-42</v>
       </c>
       <c r="M38" s="2">
         <v>0.39012634628174014</v>
@@ -4519,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M40" s="1">
         <v>0.007646199545901178</v>
@@ -4581,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="3">
         <v>-0.09713828072470276</v>
@@ -4599,13 +4609,13 @@
         <v>41.39240506329114</v>
       </c>
       <c r="R41" s="3">
-        <v>26.64556962025317</v>
+        <v>26.51898734177216</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="3">
-        <v>-3.42</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4767,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="3">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="M44" s="3">
         <v>-0.20180713239508252</v>
@@ -4829,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M45" s="2">
         <v>0.2131249331070031</v>
@@ -4953,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>-0.38352852970060514</v>
@@ -4981,65 +4991,65 @@
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2">
-        <v>3.98</v>
-      </c>
-      <c r="C48" s="2">
-        <v>54.43037974683544</v>
-      </c>
-      <c r="D48" s="2">
-        <v>7.673366834170855</v>
-      </c>
-      <c r="E48" s="2">
-        <v>-0.69</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0.18928018145665992</v>
-      </c>
-      <c r="G48" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="H48" s="2">
-        <v>53.69</v>
-      </c>
-      <c r="I48" s="2">
-        <v>66.47</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0.04034650925906881</v>
-      </c>
-      <c r="K48" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>249</v>
-      </c>
-      <c r="M48" s="2">
-        <v>0.2914194091630473</v>
-      </c>
-      <c r="N48" s="2">
-        <v>39.50232525324903</v>
-      </c>
-      <c r="O48" s="2">
-        <v>86.07594936708861</v>
-      </c>
-      <c r="P48" s="2">
-        <v>15.18684888660459</v>
-      </c>
-      <c r="Q48" s="2">
-        <v>67.21518987341771</v>
-      </c>
-      <c r="R48" s="2">
-        <v>61.77215189873418</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T48" s="2">
-        <v>-1.27</v>
+      <c r="B48" s="1">
+        <v>5.18</v>
+      </c>
+      <c r="C48" s="1">
+        <v>60.75949367088608</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.7837837837837839</v>
+      </c>
+      <c r="E48" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="F48" s="1">
+        <v>-0.19455741925371617</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="H48" s="1">
+        <v>60.86</v>
+      </c>
+      <c r="I48" s="1">
+        <v>-3.21</v>
+      </c>
+      <c r="J48" s="1">
+        <v>-0.007594479396489348</v>
+      </c>
+      <c r="K48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>-65</v>
+      </c>
+      <c r="M48" s="1">
+        <v>-0.19362888082002172</v>
+      </c>
+      <c r="N48" s="1">
+        <v>-9.002503745057872</v>
+      </c>
+      <c r="O48" s="1">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="P48" s="1">
+        <v>19.13407224404345</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>47.8481012658228</v>
+      </c>
+      <c r="R48" s="1">
+        <v>32.594936708860764</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T48" s="1">
+        <v>6.39</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5047,247 +5057,247 @@
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>-0.06</v>
+        <v>20.1</v>
       </c>
       <c r="C49" s="2">
-        <v>26.582278481012654</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="D49" s="2">
-        <v>1709.8333333333335</v>
+        <v>0.09701492537313429</v>
       </c>
       <c r="E49" s="2">
-        <v>3.55</v>
+        <v>-1.46</v>
       </c>
       <c r="F49" s="2">
-        <v>0.4166832538248919</v>
+        <v>-0.03147240354967856</v>
       </c>
       <c r="G49" s="2">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="H49" s="2">
-        <v>53.03</v>
+        <v>52.48</v>
       </c>
       <c r="I49" s="2">
-        <v>101.97</v>
+        <v>39.99</v>
       </c>
       <c r="J49" s="2">
-        <v>0.06644165588838259</v>
+        <v>0.02326959230595297</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="M49" s="2">
+        <v>0.02609697933937616</v>
+      </c>
+      <c r="N49" s="2">
+        <v>12.97008227088193</v>
+      </c>
+      <c r="O49" s="2">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P49" s="2">
+        <v>13.880000945060484</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>62.78481012658228</v>
+      </c>
+      <c r="R49" s="2">
+        <v>54.62025316455696</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="T49" s="2">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="C50" s="2">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1709.8333333333335</v>
+      </c>
+      <c r="E50" s="2">
+        <v>3.55</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.4166832538248919</v>
+      </c>
+      <c r="G50" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="H50" s="2">
+        <v>53.03</v>
+      </c>
+      <c r="I50" s="2">
+        <v>101.97</v>
+      </c>
+      <c r="J50" s="2">
+        <v>0.06644165588838259</v>
+      </c>
+      <c r="K50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>210</v>
+      </c>
+      <c r="M50" s="2">
         <v>0.6766740152593325</v>
       </c>
-      <c r="N49" s="2">
+      <c r="N50" s="2">
         <v>78.02778586287755</v>
       </c>
-      <c r="O49" s="2">
+      <c r="O50" s="2">
         <v>93.67088607594937</v>
       </c>
-      <c r="P49" s="2">
+      <c r="P50" s="2">
         <v>31.61869931071345</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q50" s="2">
         <v>71.39240506329114</v>
       </c>
-      <c r="R49" s="2">
+      <c r="R50" s="2">
         <v>62.21518987341772</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T49" s="2">
+      <c r="T50" s="2">
         <v>-1.33</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3.98</v>
+      </c>
+      <c r="C51" s="2">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="D51" s="2">
+        <v>7.673366834170855</v>
+      </c>
+      <c r="E51" s="2">
+        <v>-0.69</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0.18928018145665992</v>
+      </c>
+      <c r="G51" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="H51" s="2">
+        <v>53.69</v>
+      </c>
+      <c r="I51" s="2">
+        <v>66.47</v>
+      </c>
+      <c r="J51" s="2">
+        <v>0.04034650925906881</v>
+      </c>
+      <c r="K51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2">
+        <v>251</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0.2914194091630473</v>
+      </c>
+      <c r="N51" s="2">
+        <v>39.50232525324903</v>
+      </c>
+      <c r="O51" s="2">
+        <v>86.07594936708861</v>
+      </c>
+      <c r="P51" s="2">
+        <v>15.18684888660459</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>67.21518987341771</v>
+      </c>
+      <c r="R51" s="2">
+        <v>61.77215189873418</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T51" s="2">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3">
         <v>-0.13</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C52" s="3">
         <v>25.31645569620253</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D52" s="3">
         <v>300.1538461538462</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E52" s="3">
         <v>2.59</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F52" s="3">
         <v>-0.4456703998039746</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G52" s="3">
         <v>1.54</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H52" s="3">
         <v>36.3</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I52" s="3">
         <v>-26.9</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J52" s="3">
         <v>-0.036499267452008585</v>
       </c>
-      <c r="K50" s="3" t="b">
+      <c r="K52" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L50" s="3">
+      <c r="L52" s="3">
         <v>-2</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M52" s="3">
         <v>-0.3955293243844753</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N52" s="3">
         <v>-29.19254810150323</v>
       </c>
-      <c r="O50" s="3">
+      <c r="O52" s="3">
         <v>2.5316455696202533</v>
       </c>
-      <c r="P50" s="3">
-        <v>46.88994928756761</v>
-      </c>
-      <c r="Q50" s="3">
+      <c r="P52" s="3">
+        <v>46.37680917379436</v>
+      </c>
+      <c r="Q52" s="3">
         <v>38.22784810126582</v>
       </c>
-      <c r="R50" s="3">
-        <v>21.645569620253163</v>
-      </c>
-      <c r="S50" s="3" t="s">
+      <c r="R52" s="3">
+        <v>21.89873417721519</v>
+      </c>
+      <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T50" s="3">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <v>-3.88</v>
-      </c>
-      <c r="C51" s="1">
-        <v>7.59493670886076</v>
-      </c>
-      <c r="D51" s="1">
-        <v>13.440721649484537</v>
-      </c>
-      <c r="E51" s="1">
-        <v>16.72</v>
-      </c>
-      <c r="F51" s="1">
-        <v>-0.11225424461657726</v>
-      </c>
-      <c r="G51" s="1">
-        <v>2.37</v>
-      </c>
-      <c r="H51" s="1">
-        <v>43.33</v>
-      </c>
-      <c r="I51" s="1">
-        <v>12.78</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0.025800525067663532</v>
-      </c>
-      <c r="K51" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>93</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0.014955520799559752</v>
-      </c>
-      <c r="N51" s="1">
-        <v>11.855936416900272</v>
-      </c>
-      <c r="O51" s="1">
-        <v>64.55696202531645</v>
-      </c>
-      <c r="P51" s="1">
-        <v>46.744012320672994</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>47.72151898734178</v>
-      </c>
-      <c r="R51" s="1">
-        <v>37.40506329113924</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T51" s="1">
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2">
-        <v>5.3</v>
-      </c>
-      <c r="C52" s="2">
-        <v>62.0253164556962</v>
-      </c>
-      <c r="D52" s="2">
-        <v>6.507547169811321</v>
-      </c>
-      <c r="E52" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F52" s="2">
-        <v>-0.000776152966117688</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1.83</v>
-      </c>
-      <c r="H52" s="2">
-        <v>53.56</v>
-      </c>
-      <c r="I52" s="2">
-        <v>50.58</v>
-      </c>
-      <c r="J52" s="2">
-        <v>0.02982796949308086</v>
-      </c>
-      <c r="K52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2">
-        <v>303</v>
-      </c>
-      <c r="M52" s="2">
-        <v>0.07629253703052008</v>
-      </c>
-      <c r="N52" s="2">
-        <v>17.98963803999632</v>
-      </c>
-      <c r="O52" s="2">
-        <v>70.88607594936708</v>
-      </c>
-      <c r="P52" s="2">
-        <v>20.10180966623631</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>65.9493670886076</v>
-      </c>
-      <c r="R52" s="2">
-        <v>55.44303797468355</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T52" s="2">
-        <v>-1.33</v>
+      <c r="T52" s="3">
+        <v>0.13</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5295,123 +5305,123 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>-0.71</v>
+        <v>-3.88</v>
       </c>
       <c r="C53" s="1">
-        <v>17.72151898734177</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="D53" s="1">
-        <v>12.042253521126762</v>
+        <v>13.440721649484537</v>
       </c>
       <c r="E53" s="1">
-        <v>6.64</v>
+        <v>16.72</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.19892397531012102</v>
+        <v>-0.11225424461657726</v>
       </c>
       <c r="G53" s="1">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="H53" s="1">
-        <v>50.85</v>
+        <v>43.33</v>
       </c>
       <c r="I53" s="1">
-        <v>-25.28</v>
+        <v>12.78</v>
       </c>
       <c r="J53" s="1">
-        <v>0.02100547168695652</v>
+        <v>0.025800525067663532</v>
       </c>
       <c r="K53" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>-16</v>
+        <v>93</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.05221490278640095</v>
+        <v>0.014955520799559752</v>
       </c>
       <c r="N53" s="1">
-        <v>5.1388940583042055</v>
+        <v>11.855936416900272</v>
       </c>
       <c r="O53" s="1">
-        <v>49.36708860759494</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P53" s="1">
-        <v>48.21894075039502</v>
+        <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>44.810126582278485</v>
+        <v>47.72151898734178</v>
       </c>
       <c r="R53" s="1">
-        <v>33.481012658227854</v>
+        <v>37.278481012658226</v>
       </c>
       <c r="S53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T53" s="1">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="C54" s="2">
+        <v>62.0253164556962</v>
+      </c>
+      <c r="D54" s="2">
+        <v>6.507547169811321</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="F54" s="2">
+        <v>-0.000776152966117688</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1.83</v>
+      </c>
+      <c r="H54" s="2">
+        <v>53.56</v>
+      </c>
+      <c r="I54" s="2">
+        <v>50.58</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.02982796949308086</v>
+      </c>
+      <c r="K54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2">
+        <v>300</v>
+      </c>
+      <c r="M54" s="2">
+        <v>0.07629253703052008</v>
+      </c>
+      <c r="N54" s="2">
+        <v>17.98963803999632</v>
+      </c>
+      <c r="O54" s="2">
+        <v>70.88607594936708</v>
+      </c>
+      <c r="P54" s="2">
+        <v>20.10180966623631</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>65.9493670886076</v>
+      </c>
+      <c r="R54" s="2">
+        <v>55.44303797468355</v>
+      </c>
+      <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="T53" s="1">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="C54" s="1">
-        <v>35.44303797468354</v>
-      </c>
-      <c r="D54" s="1">
-        <v>40.407407407407405</v>
-      </c>
-      <c r="E54" s="1">
-        <v>-0.43</v>
-      </c>
-      <c r="F54" s="1">
-        <v>-0.08513223155526206</v>
-      </c>
-      <c r="G54" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H54" s="1">
-        <v>54.83</v>
-      </c>
-      <c r="I54" s="1">
-        <v>4.04</v>
-      </c>
-      <c r="J54" s="1">
-        <v>0.030077081491101127</v>
-      </c>
-      <c r="K54" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" s="1">
-        <v>13</v>
-      </c>
-      <c r="M54" s="1">
-        <v>-0.04334800203901268</v>
-      </c>
-      <c r="N54" s="1">
-        <v>6.025584133043034</v>
-      </c>
-      <c r="O54" s="1">
-        <v>51.89873417721519</v>
-      </c>
-      <c r="P54" s="1">
-        <v>25.062459708672506</v>
-      </c>
-      <c r="Q54" s="1">
-        <v>64.43037974683544</v>
-      </c>
-      <c r="R54" s="1">
-        <v>49.11392405063291</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="T54" s="1">
-        <v>-3.54</v>
+      <c r="T54" s="2">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5419,61 +5429,61 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>4.03</v>
+        <v>-0.71</v>
       </c>
       <c r="C55" s="1">
-        <v>56.9620253164557</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="D55" s="1">
-        <v>2.2580645161290325</v>
+        <v>12.042253521126762</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.26</v>
+        <v>6.64</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.16197313505260122</v>
+        <v>-0.19892397531012102</v>
       </c>
       <c r="G55" s="1">
-        <v>1.21</v>
+        <v>2.58</v>
       </c>
       <c r="H55" s="1">
-        <v>44.69</v>
+        <v>50.85</v>
       </c>
       <c r="I55" s="1">
-        <v>-1.81</v>
+        <v>-25.28</v>
       </c>
       <c r="J55" s="1">
-        <v>0.0009499959979441232</v>
+        <v>0.02100547168695652</v>
       </c>
       <c r="K55" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="1">
-        <v>-57</v>
+        <v>-15</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.14247382794501817</v>
+        <v>-0.05221490278640095</v>
       </c>
       <c r="N55" s="1">
-        <v>-3.886998457557516</v>
+        <v>5.1388940583042055</v>
       </c>
       <c r="O55" s="1">
-        <v>37.9746835443038</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P55" s="1">
-        <v>18.39301096820415</v>
+        <v>48.21894075039502</v>
       </c>
       <c r="Q55" s="1">
-        <v>48.227848101265835</v>
+        <v>44.810126582278485</v>
       </c>
       <c r="R55" s="1">
-        <v>39.0506329113924</v>
+        <v>33.481012658227854</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>2.47</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5481,185 +5491,185 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>8.65</v>
+        <v>0.54</v>
       </c>
       <c r="C56" s="1">
-        <v>74.68354430379746</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="D56" s="1">
-        <v>0.1757225433526011</v>
+        <v>40.407407407407405</v>
       </c>
       <c r="E56" s="1">
-        <v>0.81</v>
+        <v>-0.43</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.09411200319531839</v>
+        <v>-0.08513223155526206</v>
       </c>
       <c r="G56" s="1">
-        <v>0.26</v>
+        <v>1.45</v>
       </c>
       <c r="H56" s="1">
-        <v>49.54</v>
+        <v>54.83</v>
       </c>
       <c r="I56" s="1">
-        <v>9.26</v>
+        <v>4.04</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.006743493601277909</v>
+        <v>0.030077081491101127</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="M56" s="1">
+        <v>-0.04334800203901268</v>
+      </c>
+      <c r="N56" s="1">
+        <v>6.025584133043034</v>
+      </c>
+      <c r="O56" s="1">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P56" s="1">
+        <v>25.062459708672506</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>64.43037974683544</v>
+      </c>
+      <c r="R56" s="1">
+        <v>49.11392405063291</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T56" s="1">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4.03</v>
+      </c>
+      <c r="C57" s="1">
+        <v>56.9620253164557</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2.2580645161290325</v>
+      </c>
+      <c r="E57" s="1">
+        <v>-0.26</v>
+      </c>
+      <c r="F57" s="1">
+        <v>-0.16197313505260122</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="H57" s="1">
+        <v>44.69</v>
+      </c>
+      <c r="I57" s="1">
+        <v>-1.81</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.0009499959979441232</v>
+      </c>
+      <c r="K57" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>-58</v>
+      </c>
+      <c r="M57" s="1">
+        <v>-0.14247382794501817</v>
+      </c>
+      <c r="N57" s="1">
+        <v>-3.886998457557516</v>
+      </c>
+      <c r="O57" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P57" s="1">
+        <v>18.39301096820415</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>48.227848101265835</v>
+      </c>
+      <c r="R57" s="1">
+        <v>39.0506329113924</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T57" s="1">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <v>8.65</v>
+      </c>
+      <c r="C58" s="1">
+        <v>74.68354430379746</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.1757225433526011</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="F58" s="1">
+        <v>-0.09411200319531839</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="H58" s="1">
+        <v>49.54</v>
+      </c>
+      <c r="I58" s="1">
+        <v>9.26</v>
+      </c>
+      <c r="J58" s="1">
+        <v>-0.006743493601277909</v>
+      </c>
+      <c r="K58" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>162</v>
+      </c>
+      <c r="M58" s="1">
         <v>-0.16282384728870625</v>
       </c>
-      <c r="N56" s="1">
+      <c r="N58" s="1">
         <v>-5.922000391926318</v>
       </c>
-      <c r="O56" s="1">
+      <c r="O58" s="1">
         <v>34.177215189873415</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
-      <c r="Q56" s="1">
+      <c r="Q58" s="1">
         <v>46.58227848101266</v>
       </c>
-      <c r="R56" s="1">
+      <c r="R58" s="1">
         <v>37.21518987341772</v>
       </c>
-      <c r="S56" s="1" t="s">
+      <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="T56" s="1">
+      <c r="T58" s="1">
         <v>3.23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2">
-        <v>21.18</v>
-      </c>
-      <c r="C57" s="2">
-        <v>96.20253164556962</v>
-      </c>
-      <c r="D57" s="2">
-        <v>2.3866855524079322</v>
-      </c>
-      <c r="E57" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0.5120440504377429</v>
-      </c>
-      <c r="G57" s="2">
-        <v>1.96</v>
-      </c>
-      <c r="H57" s="2">
-        <v>59.62</v>
-      </c>
-      <c r="I57" s="2">
-        <v>119.86</v>
-      </c>
-      <c r="J57" s="2">
-        <v>0.07848699843097959</v>
-      </c>
-      <c r="K57" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" s="2">
-        <v>368</v>
-      </c>
-      <c r="M57" s="2">
-        <v>0.6011837400724083</v>
-      </c>
-      <c r="N57" s="2">
-        <v>70.47875834418512</v>
-      </c>
-      <c r="O57" s="2">
-        <v>92.40506329113924</v>
-      </c>
-      <c r="P57" s="2">
-        <v>30.30559414893712</v>
-      </c>
-      <c r="Q57" s="2">
-        <v>79.11392405063292</v>
-      </c>
-      <c r="R57" s="2">
-        <v>66.77215189873418</v>
-      </c>
-      <c r="S57" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="T57" s="2">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2">
-        <v>20.1</v>
-      </c>
-      <c r="C58" s="2">
-        <v>94.9367088607595</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0.09701492537313429</v>
-      </c>
-      <c r="E58" s="2">
-        <v>-1.46</v>
-      </c>
-      <c r="F58" s="2">
-        <v>-0.03147240354967856</v>
-      </c>
-      <c r="G58" s="2">
-        <v>1.62</v>
-      </c>
-      <c r="H58" s="2">
-        <v>52.48</v>
-      </c>
-      <c r="I58" s="2">
-        <v>39.99</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0.02326959230595297</v>
-      </c>
-      <c r="K58" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" s="2">
-        <v>270</v>
-      </c>
-      <c r="M58" s="2">
-        <v>0.02609697933937616</v>
-      </c>
-      <c r="N58" s="2">
-        <v>12.97008227088193</v>
-      </c>
-      <c r="O58" s="2">
-        <v>65.82278481012658</v>
-      </c>
-      <c r="P58" s="2">
-        <v>13.880000945060484</v>
-      </c>
-      <c r="Q58" s="2">
-        <v>62.78481012658228</v>
-      </c>
-      <c r="R58" s="2">
-        <v>54.62025316455696</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="T58" s="2">
-        <v>-0.7</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5667,123 +5677,123 @@
         <v>58</v>
       </c>
       <c r="B59" s="2">
+        <v>21.18</v>
+      </c>
+      <c r="C59" s="2">
+        <v>96.20253164556962</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2.3866855524079322</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0.5120440504377429</v>
+      </c>
+      <c r="G59" s="2">
+        <v>1.96</v>
+      </c>
+      <c r="H59" s="2">
+        <v>59.62</v>
+      </c>
+      <c r="I59" s="2">
+        <v>119.86</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0.07848699843097959</v>
+      </c>
+      <c r="K59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2">
+        <v>369</v>
+      </c>
+      <c r="M59" s="2">
+        <v>0.6011837400724083</v>
+      </c>
+      <c r="N59" s="2">
+        <v>70.47875834418512</v>
+      </c>
+      <c r="O59" s="2">
+        <v>92.40506329113924</v>
+      </c>
+      <c r="P59" s="2">
+        <v>30.30559414893712</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>79.11392405063292</v>
+      </c>
+      <c r="R59" s="2">
+        <v>66.77215189873418</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T59" s="2">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
         <v>34.32</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C60" s="2">
         <v>100</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D60" s="2">
         <v>-1.4889277389277389</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E60" s="2">
         <v>-2.31</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F60" s="2">
         <v>0.10891482034506436</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G60" s="2">
         <v>1.25</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H60" s="2">
         <v>46.28</v>
       </c>
-      <c r="I59" s="2">
+      <c r="I60" s="2">
         <v>37.99</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J60" s="2">
         <v>0.023569189817422096</v>
       </c>
-      <c r="K59" s="2" t="b">
+      <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L60" s="2">
         <v>368</v>
       </c>
-      <c r="M59" s="2">
+      <c r="M60" s="2">
         <v>0.13212828118742515</v>
       </c>
-      <c r="N59" s="2">
+      <c r="N60" s="2">
         <v>23.573212455686832</v>
       </c>
-      <c r="O59" s="2">
+      <c r="O60" s="2">
         <v>73.41772151898735</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P60" s="2">
         <v>11.942274303251052</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q60" s="2">
         <v>58.86075949367089</v>
       </c>
-      <c r="R59" s="2">
+      <c r="R60" s="2">
         <v>55.00000000000001</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T60" s="2">
         <v>-1.58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1">
-        <v>6.37</v>
-      </c>
-      <c r="C60" s="1">
-        <v>68.35443037974683</v>
-      </c>
-      <c r="D60" s="1">
-        <v>-0.13029827315541603</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="F60" s="1">
-        <v>-0.12638494034057418</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="H60" s="1">
-        <v>38.55</v>
-      </c>
-      <c r="I60" s="1">
-        <v>-0.92</v>
-      </c>
-      <c r="J60" s="1">
-        <v>-0.008735830250640496</v>
-      </c>
-      <c r="K60" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <v>104</v>
-      </c>
-      <c r="M60" s="1">
-        <v>-0.18302578479593445</v>
-      </c>
-      <c r="N60" s="1">
-        <v>-7.942194142649135</v>
-      </c>
-      <c r="O60" s="1">
-        <v>30.37974683544304</v>
-      </c>
-      <c r="P60" s="1">
-        <v>12.798408482128673</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>37.34177215189873</v>
-      </c>
-      <c r="R60" s="1">
-        <v>31.89873417721519</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="T60" s="1">
-        <v>3.1</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5791,247 +5801,247 @@
         <v>60</v>
       </c>
       <c r="B61" s="1">
-        <v>17.74</v>
+        <v>6.37</v>
       </c>
       <c r="C61" s="1">
-        <v>92.40506329113924</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="D61" s="1">
-        <v>0.6178128523111613</v>
+        <v>-0.13029827315541603</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.07</v>
+        <v>0.62</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.16038838312440135</v>
+        <v>-0.12638494034057418</v>
       </c>
       <c r="G61" s="1">
-        <v>0.96</v>
+        <v>0.39</v>
       </c>
       <c r="H61" s="1">
-        <v>43.76</v>
+        <v>38.55</v>
       </c>
       <c r="I61" s="1">
-        <v>8.57</v>
+        <v>-0.92</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.005955899128925325</v>
+        <v>-0.008735830250640496</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="1">
+        <v>104</v>
+      </c>
+      <c r="M61" s="1">
+        <v>-0.18302578479593445</v>
+      </c>
+      <c r="N61" s="1">
+        <v>-7.942194142649135</v>
+      </c>
+      <c r="O61" s="1">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="P61" s="1">
+        <v>12.798408482128673</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>37.34177215189873</v>
+      </c>
+      <c r="R61" s="1">
+        <v>31.89873417721519</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T61" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <v>17.74</v>
+      </c>
+      <c r="C62" s="1">
+        <v>92.40506329113924</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.6178128523111613</v>
+      </c>
+      <c r="E62" s="1">
+        <v>-0.07</v>
+      </c>
+      <c r="F62" s="1">
+        <v>-0.16038838312440135</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="H62" s="1">
+        <v>43.76</v>
+      </c>
+      <c r="I62" s="1">
+        <v>8.57</v>
+      </c>
+      <c r="J62" s="1">
+        <v>-0.005955899128925325</v>
+      </c>
+      <c r="K62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
         <v>175</v>
       </c>
-      <c r="M61" s="1">
+      <c r="M62" s="1">
         <v>-0.16410253685917908</v>
       </c>
-      <c r="N61" s="1">
+      <c r="N62" s="1">
         <v>-6.0498693489736</v>
       </c>
-      <c r="O61" s="1">
+      <c r="O62" s="1">
         <v>32.91139240506329</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P62" s="1">
         <v>16.149676494964734</v>
       </c>
-      <c r="Q61" s="1">
+      <c r="Q62" s="1">
         <v>53.03797468354429</v>
       </c>
-      <c r="R61" s="1">
+      <c r="R62" s="1">
         <v>42.0253164556962</v>
       </c>
-      <c r="S61" s="1" t="s">
+      <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="T61" s="1">
+      <c r="T62" s="1">
         <v>-0.82</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="4">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4">
         <v>28.77</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C63" s="4">
         <v>98.73417721518987</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D63" s="4">
         <v>4.924921793534932</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E63" s="4">
         <v>-8.13</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F63" s="4">
         <v>0.803418982178189</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G63" s="4">
         <v>4.77</v>
       </c>
-      <c r="H62" s="4">
+      <c r="H63" s="4">
         <v>59.54</v>
       </c>
-      <c r="I62" s="4">
+      <c r="I63" s="4">
         <v>211.16</v>
       </c>
-      <c r="J62" s="4">
+      <c r="J63" s="4">
         <v>0.09688950559761088</v>
       </c>
-      <c r="K62" s="4" t="b">
+      <c r="K63" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="L62" s="4">
-        <v>478</v>
-      </c>
-      <c r="M62" s="4">
+      <c r="L63" s="4">
+        <v>479</v>
+      </c>
+      <c r="M63" s="4">
         <v>1.1534779716809893</v>
       </c>
-      <c r="N62" s="4">
+      <c r="N63" s="4">
         <v>125.70818150504324</v>
       </c>
-      <c r="O62" s="4">
+      <c r="O63" s="4">
         <v>98.73417721518987</v>
       </c>
-      <c r="P62" s="4">
+      <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
-      <c r="Q62" s="4">
+      <c r="Q63" s="4">
         <v>81.89873417721519</v>
       </c>
-      <c r="R62" s="4">
+      <c r="R63" s="4">
         <v>72.02531645569621</v>
       </c>
-      <c r="S62" s="4" t="s">
+      <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="T62" s="4">
+      <c r="T63" s="4">
         <v>-0.32</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
         <v>10.54</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C64" s="2">
         <v>79.74683544303798</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D64" s="2">
         <v>6.3927893738140416</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E64" s="2">
         <v>-5.36</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F64" s="2">
         <v>0.582807567756483</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G64" s="2">
         <v>2.02</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H64" s="2">
         <v>60.53</v>
       </c>
-      <c r="I63" s="2">
+      <c r="I64" s="2">
         <v>117.34</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J64" s="2">
         <v>0.0846049925147908</v>
       </c>
-      <c r="K63" s="2" t="b">
+      <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L63" s="2">
-        <v>201</v>
-      </c>
-      <c r="M63" s="2">
+      <c r="L64" s="2">
+        <v>203</v>
+      </c>
+      <c r="M64" s="2">
         <v>0.6775184879933149</v>
       </c>
-      <c r="N63" s="2">
+      <c r="N64" s="2">
         <v>78.1122331362758</v>
       </c>
-      <c r="O63" s="2">
+      <c r="O64" s="2">
         <v>94.9367088607595</v>
       </c>
-      <c r="P63" s="2">
+      <c r="P64" s="2">
         <v>20.9978319173529</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q64" s="2">
         <v>76.58227848101265</v>
       </c>
-      <c r="R63" s="2">
+      <c r="R64" s="2">
         <v>67.40506329113924</v>
       </c>
-      <c r="S63" s="2" t="s">
+      <c r="S64" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T63" s="2">
+      <c r="T64" s="2">
         <v>0.44</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <v>16.87</v>
-      </c>
-      <c r="C64" s="1">
-        <v>89.87341772151899</v>
-      </c>
-      <c r="D64" s="1">
-        <v>-0.27504445761707175</v>
-      </c>
-      <c r="E64" s="1">
-        <v>-0.88</v>
-      </c>
-      <c r="F64" s="1">
-        <v>-0.12395774130970882</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H64" s="1">
-        <v>48.94</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="J64" s="1">
-        <v>-0.0058368555469811645</v>
-      </c>
-      <c r="K64" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>57</v>
-      </c>
-      <c r="M64" s="1">
-        <v>-0.18895543166831896</v>
-      </c>
-      <c r="N64" s="1">
-        <v>-8.535158829887585</v>
-      </c>
-      <c r="O64" s="1">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="P64" s="1">
-        <v>15.211254913322609</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>48.22784810126583</v>
-      </c>
-      <c r="R64" s="1">
-        <v>36.64556962025316</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T64" s="1">
-        <v>-0.76</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6039,61 +6049,61 @@
         <v>64</v>
       </c>
       <c r="B65" s="1">
-        <v>15.41</v>
+        <v>16.87</v>
       </c>
       <c r="C65" s="1">
-        <v>87.34177215189874</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.10837118754055808</v>
+        <v>-0.27504445761707175</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.2</v>
+        <v>-0.88</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.04404825164755059</v>
+        <v>-0.12395774130970882</v>
       </c>
       <c r="G65" s="1">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>52.39</v>
+        <v>48.94</v>
       </c>
       <c r="I65" s="1">
-        <v>-28.96</v>
+        <v>0.47</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.014723341169018873</v>
+        <v>-0.0058368555469811645</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>-188</v>
+        <v>57</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.04033409791277287</v>
+        <v>-0.18895543166831896</v>
       </c>
       <c r="N65" s="1">
-        <v>6.326974545667026</v>
+        <v>-8.535158829887585</v>
       </c>
       <c r="O65" s="1">
-        <v>53.16455696202531</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P65" s="1">
-        <v>48.12800106814908</v>
+        <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>39.11392405063291</v>
+        <v>48.22784810126583</v>
       </c>
       <c r="R65" s="1">
-        <v>33.924050632911396</v>
+        <v>36.64556962025316</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>4.87</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6101,61 +6111,61 @@
         <v>65</v>
       </c>
       <c r="B66" s="1">
-        <v>4.01</v>
+        <v>15.41</v>
       </c>
       <c r="C66" s="1">
-        <v>55.69620253164557</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="D66" s="1">
-        <v>7.266832917705736</v>
+        <v>-0.10837118754055808</v>
       </c>
       <c r="E66" s="1">
-        <v>-1.48</v>
+        <v>-0.2</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.05302032012287701</v>
+        <v>-0.04404825164755059</v>
       </c>
       <c r="G66" s="1">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H66" s="1">
-        <v>50.15</v>
+        <v>52.39</v>
       </c>
       <c r="I66" s="1">
-        <v>-11.04</v>
+        <v>-28.96</v>
       </c>
       <c r="J66" s="1">
-        <v>-0.0009719116505956617</v>
+        <v>-0.014723341169018873</v>
       </c>
       <c r="K66" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="1">
-        <v>-71</v>
+        <v>-186</v>
       </c>
       <c r="M66" s="1">
-        <v>-0.039092243617460554</v>
+        <v>-0.04033409791277287</v>
       </c>
       <c r="N66" s="1">
-        <v>6.451159975198248</v>
+        <v>6.326974545667026</v>
       </c>
       <c r="O66" s="1">
-        <v>55.69620253164557</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P66" s="1">
-        <v>21.01837744312229</v>
+        <v>48.12800106814908</v>
       </c>
       <c r="Q66" s="1">
-        <v>50.25316455696203</v>
+        <v>39.11392405063291</v>
       </c>
       <c r="R66" s="1">
-        <v>44.936708860759495</v>
+        <v>33.924050632911396</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="T66" s="1">
-        <v>0.82</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6163,123 +6173,123 @@
         <v>66</v>
       </c>
       <c r="B67" s="1">
-        <v>7.35</v>
+        <v>4.01</v>
       </c>
       <c r="C67" s="1">
-        <v>69.62025316455697</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="D67" s="1">
-        <v>200.22857142857146</v>
+        <v>7.266832917705736</v>
       </c>
       <c r="E67" s="1">
-        <v>-0.18</v>
+        <v>-1.48</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.20626589337855733</v>
+        <v>-0.05302032012287701</v>
       </c>
       <c r="G67" s="1">
-        <v>0.33</v>
+        <v>1.15</v>
       </c>
       <c r="H67" s="1">
-        <v>39.87</v>
+        <v>50.15</v>
       </c>
       <c r="I67" s="1">
-        <v>1.35</v>
+        <v>-11.04</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.010946538905365932</v>
+        <v>-0.0009719116505956617</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>150</v>
+        <v>-71</v>
       </c>
       <c r="M67" s="1">
+        <v>-0.039092243617460554</v>
+      </c>
+      <c r="N67" s="1">
+        <v>6.451159975198248</v>
+      </c>
+      <c r="O67" s="1">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P67" s="1">
+        <v>21.01837744312229</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>50.25316455696203</v>
+      </c>
+      <c r="R67" s="1">
+        <v>44.936708860759495</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <v>7.35</v>
+      </c>
+      <c r="C68" s="1">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="D68" s="1">
+        <v>200.22857142857146</v>
+      </c>
+      <c r="E68" s="1">
+        <v>-0.18</v>
+      </c>
+      <c r="F68" s="1">
+        <v>-0.20626589337855733</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="H68" s="1">
+        <v>39.87</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-0.010946538905365932</v>
+      </c>
+      <c r="K68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>149</v>
+      </c>
+      <c r="M68" s="1">
         <v>-0.2684779684360842</v>
       </c>
-      <c r="N67" s="1">
+      <c r="N68" s="1">
         <v>-16.48741250666411</v>
       </c>
-      <c r="O67" s="1">
+      <c r="O68" s="1">
         <v>12.658227848101266</v>
       </c>
-      <c r="P67" s="1">
+      <c r="P68" s="1">
         <v>18.003852697255347</v>
       </c>
-      <c r="Q67" s="1">
+      <c r="Q68" s="1">
         <v>60</v>
       </c>
-      <c r="R67" s="1">
+      <c r="R68" s="1">
         <v>43.734177215189874</v>
       </c>
-      <c r="S67" s="1" t="s">
+      <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="T67" s="1">
+      <c r="T68" s="1">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3">
-        <v>8.24</v>
-      </c>
-      <c r="C68" s="3">
-        <v>72.15189873417721</v>
-      </c>
-      <c r="D68" s="3">
-        <v>0.6286407766990291</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="F68" s="3">
-        <v>-0.25740260569165335</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1.49</v>
-      </c>
-      <c r="H68" s="3">
-        <v>44.83</v>
-      </c>
-      <c r="I68" s="3">
-        <v>-11.43</v>
-      </c>
-      <c r="J68" s="3">
-        <v>-0.014024373117659573</v>
-      </c>
-      <c r="K68" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3">
-        <v>-61</v>
-      </c>
-      <c r="M68" s="3">
-        <v>-0.21190422244062623</v>
-      </c>
-      <c r="N68" s="3">
-        <v>-10.830037907118312</v>
-      </c>
-      <c r="O68" s="3">
-        <v>22.78481012658228</v>
-      </c>
-      <c r="P68" s="3">
-        <v>29.145649851223904</v>
-      </c>
-      <c r="Q68" s="3">
-        <v>40.12658227848101</v>
-      </c>
-      <c r="R68" s="3">
-        <v>28.164556962025312</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T68" s="3">
-        <v>0.44</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6287,61 +6297,61 @@
         <v>68</v>
       </c>
       <c r="B69" s="3">
-        <v>18.19</v>
+        <v>8.24</v>
       </c>
       <c r="C69" s="3">
-        <v>93.67088607594937</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="D69" s="3">
-        <v>-0.47608576140736675</v>
+        <v>0.6286407766990291</v>
       </c>
       <c r="E69" s="3">
-        <v>1.82</v>
+        <v>0.19</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.21033504627324695</v>
+        <v>-0.25740260569165335</v>
       </c>
       <c r="G69" s="3">
-        <v>0.87</v>
+        <v>1.49</v>
       </c>
       <c r="H69" s="3">
-        <v>35.41</v>
+        <v>44.83</v>
       </c>
       <c r="I69" s="3">
-        <v>-16.11</v>
+        <v>-11.43</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.012926741798049627</v>
+        <v>-0.014024373117659573</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-55</v>
+        <v>-62</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.22240604591127455</v>
+        <v>-0.21190422244062623</v>
       </c>
       <c r="N69" s="3">
-        <v>-11.880220254183154</v>
+        <v>-10.830037907118312</v>
       </c>
       <c r="O69" s="3">
-        <v>18.9873417721519</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P69" s="3">
-        <v>31.450467124868602</v>
+        <v>29.145649851223904</v>
       </c>
       <c r="Q69" s="3">
-        <v>37.84810126582279</v>
+        <v>40.12658227848101</v>
       </c>
       <c r="R69" s="3">
-        <v>27.025316455696203</v>
+        <v>28.164556962025312</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6349,123 +6359,123 @@
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>1.52</v>
+        <v>18.19</v>
       </c>
       <c r="C70" s="3">
-        <v>45.56962025316456</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="D70" s="3">
-        <v>13.532894736842104</v>
+        <v>-0.47608576140736675</v>
       </c>
       <c r="E70" s="3">
-        <v>-1.56</v>
+        <v>1.82</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.45800455981527743</v>
+        <v>-0.21033504627324695</v>
       </c>
       <c r="G70" s="3">
-        <v>1.12</v>
+        <v>0.87</v>
       </c>
       <c r="H70" s="3">
-        <v>36.17</v>
+        <v>35.41</v>
       </c>
       <c r="I70" s="3">
-        <v>-31.6</v>
+        <v>-16.11</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.03386514245475491</v>
+        <v>-0.012926741798049627</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-100</v>
+        <v>-56</v>
       </c>
       <c r="M70" s="3">
+        <v>-0.22240604591127455</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-11.880220254183154</v>
+      </c>
+      <c r="O70" s="3">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P70" s="3">
+        <v>31.450467124868602</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>37.84810126582279</v>
+      </c>
+      <c r="R70" s="3">
+        <v>27.025316455696203</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T70" s="3">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="C71" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="D71" s="3">
+        <v>13.532894736842104</v>
+      </c>
+      <c r="E71" s="3">
+        <v>-1.56</v>
+      </c>
+      <c r="F71" s="3">
+        <v>-0.45800455981527743</v>
+      </c>
+      <c r="G71" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H71" s="3">
+        <v>36.17</v>
+      </c>
+      <c r="I71" s="3">
+        <v>-31.6</v>
+      </c>
+      <c r="J71" s="3">
+        <v>-0.03386514245475491</v>
+      </c>
+      <c r="K71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>-98</v>
+      </c>
+      <c r="M71" s="3">
         <v>-0.4468620986109443</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N71" s="3">
         <v>-34.32582552415012</v>
       </c>
-      <c r="O70" s="3">
+      <c r="O71" s="3">
         <v>1.2658227848101267</v>
       </c>
-      <c r="P70" s="3">
+      <c r="P71" s="3">
         <v>36.83258048205344</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q71" s="3">
         <v>36.962025316455694</v>
       </c>
-      <c r="R70" s="3">
+      <c r="R71" s="3">
         <v>22.27848101265823</v>
       </c>
-      <c r="S70" s="3" t="s">
+      <c r="S71" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="T70" s="3">
+      <c r="T71" s="3">
         <v>0.44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <v>5.18</v>
-      </c>
-      <c r="C71" s="1">
-        <v>60.75949367088608</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0.7837837837837839</v>
-      </c>
-      <c r="E71" s="1">
-        <v>-0.2</v>
-      </c>
-      <c r="F71" s="1">
-        <v>-0.19455741925371617</v>
-      </c>
-      <c r="G71" s="1">
-        <v>1.01</v>
-      </c>
-      <c r="H71" s="1">
-        <v>60.86</v>
-      </c>
-      <c r="I71" s="1">
-        <v>-3.21</v>
-      </c>
-      <c r="J71" s="1">
-        <v>-0.007594479396489348</v>
-      </c>
-      <c r="K71" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L71" s="1">
-        <v>-64</v>
-      </c>
-      <c r="M71" s="1">
-        <v>-0.19362888082002172</v>
-      </c>
-      <c r="N71" s="1">
-        <v>-9.002503745057872</v>
-      </c>
-      <c r="O71" s="1">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="P71" s="1">
-        <v>19.13407224404345</v>
-      </c>
-      <c r="Q71" s="1">
-        <v>47.8481012658228</v>
-      </c>
-      <c r="R71" s="1">
-        <v>32.594936708860764</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T71" s="1">
-        <v>6.39</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6503,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="L72" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M72" s="3">
         <v>-0.28069794357532096</v>
@@ -6875,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M78" s="2">
         <v>0.1945600026233134</v>
@@ -6937,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="L79" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M79" s="2">
         <v>0.44330571569125476</v>
@@ -7074,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>42.278481012658226</v>
+        <v>42.151898734177216</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7138,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>10.696202531645572</v>
+        <v>10.569620253164558</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7202,7 +7212,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>44.68354430379747</v>
+        <v>44.55696202531646</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7226,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>27.088607594936708</v>
+        <v>26.962025316455694</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7290,7 +7300,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>15.759493670886073</v>
+        <v>16.13924050632911</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7314,7 +7324,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>23.29113924050633</v>
+        <v>23.417721518987342</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7362,7 +7372,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>26.64556962025317</v>
+        <v>26.51898734177216</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7418,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>61.77215189873418</v>
+        <v>32.594936708860764</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7426,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>62.21518987341772</v>
+        <v>54.62025316455696</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7434,7 +7444,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>21.645569620253163</v>
+        <v>62.21518987341772</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7442,7 +7452,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>37.40506329113924</v>
+        <v>61.77215189873418</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7450,7 +7460,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>55.44303797468355</v>
+        <v>21.89873417721519</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7458,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>33.481012658227854</v>
+        <v>37.278481012658226</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7466,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>49.11392405063291</v>
+        <v>55.44303797468355</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7474,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>39.0506329113924</v>
+        <v>33.481012658227854</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7482,7 +7492,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>37.21518987341772</v>
+        <v>49.11392405063291</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7490,7 +7500,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>66.77215189873418</v>
+        <v>39.0506329113924</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7498,7 +7508,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>54.62025316455696</v>
+        <v>37.21518987341772</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7506,7 +7516,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>55.00000000000001</v>
+        <v>66.77215189873418</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7514,7 +7524,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>31.89873417721519</v>
+        <v>55.00000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7522,7 +7532,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>42.0253164556962</v>
+        <v>31.89873417721519</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7530,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>72.02531645569621</v>
+        <v>42.0253164556962</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7538,7 +7548,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>67.40506329113924</v>
+        <v>72.02531645569621</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7546,7 +7556,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>36.64556962025316</v>
+        <v>67.40506329113924</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7554,7 +7564,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>33.924050632911396</v>
+        <v>36.64556962025316</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7562,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>44.936708860759495</v>
+        <v>33.924050632911396</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7570,7 +7580,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>43.734177215189874</v>
+        <v>44.936708860759495</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7588,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>28.164556962025312</v>
+        <v>43.734177215189874</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7586,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.025316455696203</v>
+        <v>28.164556962025312</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7594,7 +7604,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>22.27848101265823</v>
+        <v>27.025316455696203</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,7 +7612,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>32.594936708860764</v>
+        <v>22.27848101265823</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -325,7 +325,7 @@
     <t>2026-05-28</t>
   </si>
   <si>
-    <t>2027-03-03</t>
+    <t>2026-06-02</t>
   </si>
   <si>
     <t>2027-03-10</t>
@@ -670,40 +670,40 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Institutional Buying</t>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Institutional Buying</t>
   </si>
   <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
   <si>
-    <t>Momentum Breakout, Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming, Volume Spike</t>
   </si>
   <si>
     <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
-    <t>Earnings Upcoming</t>
-  </si>
-  <si>
     <t>Volume Spike</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1394,7 @@
         <v>66.77215189873418</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>65.31645569620254</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1438,7 +1438,7 @@
         <v>62.151898734177216</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1457,10 +1457,10 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>61.77215189873418</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1468,10 +1468,10 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>59.81012658227849</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1479,10 +1479,10 @@
         <v>126</v>
       </c>
       <c r="B12">
-        <v>59.74683544303798</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="C12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1490,43 +1490,43 @@
         <v>120</v>
       </c>
       <c r="B13">
-        <v>57.27848101265823</v>
+        <v>58.670886075949376</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="B14">
-        <v>56.32911392405063</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B15">
-        <v>55.44303797468355</v>
+        <v>55.75949367088608</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="B16">
-        <v>55.44303797468354</v>
+        <v>55.63291139240508</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1534,65 +1534,65 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>55.189873417721515</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B18">
-        <v>55.12658227848102</v>
+        <v>55.18987341772152</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19">
-        <v>55.12658227848101</v>
+        <v>54.87341772151898</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B20">
-        <v>55.00000000000001</v>
+        <v>54.68354430379747</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="B21">
-        <v>54.74683544303797</v>
+        <v>54.43037974683545</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>54.62025316455696</v>
+        <v>54.11392405063292</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1600,32 +1600,32 @@
         <v>33</v>
       </c>
       <c r="B23">
-        <v>52.46835443037974</v>
+        <v>52.21518987341772</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="B24">
-        <v>51.51898734177215</v>
+        <v>51.26582278481013</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="B25">
-        <v>50.12658227848102</v>
+        <v>50.88607594936709</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1633,10 +1633,10 @@
         <v>55</v>
       </c>
       <c r="B26">
-        <v>49.11392405063291</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1644,10 +1644,10 @@
         <v>42</v>
       </c>
       <c r="B27">
-        <v>48.60759493670886</v>
+        <v>47.34177215189873</v>
       </c>
       <c r="C27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1655,10 +1655,10 @@
         <v>122</v>
       </c>
       <c r="B28">
-        <v>46.455696202531655</v>
+        <v>45.69620253164557</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1666,7 +1666,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>44.683544303797476</v>
+        <v>44.9367088607595</v>
       </c>
       <c r="C29" t="s">
         <v>220</v>
@@ -1674,134 +1674,134 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B30">
-        <v>44.55696202531646</v>
+        <v>44.87341772151899</v>
       </c>
       <c r="C30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B31">
-        <v>43.79746835443038</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>43.734177215189874</v>
+        <v>42.59493670886076</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B33">
-        <v>42.911392405063296</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="B34">
-        <v>42.0253164556962</v>
+        <v>41.64556962025317</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="B35">
-        <v>41.0126582278481</v>
+        <v>41.39240506329114</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>39.55696202531645</v>
+        <v>41.13924050632911</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B37">
-        <v>39.050632911392405</v>
+        <v>40.31645569620253</v>
       </c>
       <c r="C37" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="B38">
-        <v>38.98734177215191</v>
+        <v>39.81012658227848</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>38.48101265822785</v>
+        <v>39.11392405063291</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B40">
-        <v>37.848101265822784</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B41">
-        <v>37.278481012658226</v>
+        <v>37.151898734177216</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1809,87 +1809,87 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>37.21518987341772</v>
+        <v>37.088607594936704</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B43">
-        <v>36.64556962025316</v>
+        <v>36.01265822784811</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>34.810126582278485</v>
+        <v>33.86075949367089</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B45">
-        <v>33.924050632911396</v>
+        <v>33.60759493670885</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>33.481012658227854</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B47">
-        <v>32.974683544303794</v>
+        <v>32.72151898734177</v>
       </c>
       <c r="C47" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>32.594936708860764</v>
+        <v>32.278481012658226</v>
       </c>
       <c r="C48" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B49">
-        <v>32.278481012658226</v>
+        <v>32.08860759493672</v>
       </c>
       <c r="C49" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1897,21 +1897,21 @@
         <v>60</v>
       </c>
       <c r="B50">
-        <v>31.89873417721519</v>
+        <v>31.202531645569614</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B51">
-        <v>31.582278481012654</v>
+        <v>30.189873417721518</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2155,31 +2155,31 @@
         <v>0.4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.0703542356368584</v>
+        <v>0.05289625432642264</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H2" s="1">
-        <v>62.55</v>
+        <v>64.9</v>
       </c>
       <c r="I2" s="1">
-        <v>23.35</v>
+        <v>24.68</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0020085720201510784</v>
+        <v>0.004038391202591925</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.005785915926084906</v>
+        <v>-0.011605464699858903</v>
       </c>
       <c r="N2" s="1">
-        <v>9.781792744335805</v>
+        <v>7.877628718443935</v>
       </c>
       <c r="O2" s="1">
         <v>60.75949367088608</v>
@@ -2188,16 +2188,16 @@
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>46.70886075949367</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="R2" s="1">
-        <v>38.48101265822785</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>5.63</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2217,19 +2217,19 @@
         <v>1.88</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8384975794067261</v>
+        <v>0.8663460622859935</v>
       </c>
       <c r="G3" s="2">
         <v>2.41</v>
       </c>
       <c r="H3" s="2">
-        <v>66.23</v>
+        <v>63.81</v>
       </c>
       <c r="I3" s="2">
-        <v>86.76</v>
+        <v>82.7</v>
       </c>
       <c r="J3" s="2">
-        <v>0.09281022506883387</v>
+        <v>0.08816515348208924</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -2238,10 +2238,10 @@
         <v>107</v>
       </c>
       <c r="M3" s="2">
-        <v>0.9694214985576408</v>
+        <v>0.978626832442854</v>
       </c>
       <c r="N3" s="2">
-        <v>107.3025341927084</v>
+        <v>106.90085843271524</v>
       </c>
       <c r="O3" s="2">
         <v>97.46835443037975</v>
@@ -2279,49 +2279,49 @@
         <v>1.25</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.18550357082975716</v>
+        <v>-0.1362266529933853</v>
       </c>
       <c r="G4" s="3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H4" s="3">
-        <v>63.05</v>
+        <v>66.43</v>
       </c>
       <c r="I4" s="3">
-        <v>-19.29</v>
+        <v>-16.61</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.010990832169679707</v>
+        <v>-0.01036475455799528</v>
       </c>
       <c r="K4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
         <v>-88</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.17621818649281284</v>
+        <v>-0.1274671602861125</v>
       </c>
       <c r="N4" s="3">
-        <v>-7.261434312336975</v>
+        <v>-3.7085408401814313</v>
       </c>
       <c r="O4" s="3">
-        <v>31.645569620253166</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>35.56962025316456</v>
+        <v>36.835443037974684</v>
       </c>
       <c r="R4" s="3">
-        <v>19.430379746835445</v>
+        <v>21.835443037974684</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>4.62</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2341,19 +2341,19 @@
         <v>0.73</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.17851699600328538</v>
+        <v>-0.17081982022636585</v>
       </c>
       <c r="G5" s="1">
         <v>1.79</v>
       </c>
       <c r="H5" s="1">
-        <v>52.68</v>
+        <v>50.3</v>
       </c>
       <c r="I5" s="1">
-        <v>0.51</v>
+        <v>-1.05</v>
       </c>
       <c r="J5" s="1">
-        <v>0.00782628272587361</v>
+        <v>0.006529709234932777</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2362,28 +2362,28 @@
         <v>-82</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.10516245974142535</v>
+        <v>-0.10791073623777026</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.1558616371982243</v>
+        <v>-1.7528984353472075</v>
       </c>
       <c r="O5" s="1">
-        <v>41.77215189873418</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P5" s="1">
         <v>29.766948563835548</v>
       </c>
       <c r="Q5" s="1">
-        <v>58.22784810126582</v>
+        <v>56.835443037974684</v>
       </c>
       <c r="R5" s="1">
-        <v>42.151898734177216</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-3.16</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2403,19 +2403,19 @@
         <v>-0.11</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0114693537470755</v>
+        <v>0.012816731296728168</v>
       </c>
       <c r="G6" s="1">
         <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>45.75</v>
+        <v>44.91</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.48</v>
+        <v>-12.68</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.011080452397477165</v>
+        <v>-0.01100991781032459</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
@@ -2424,28 +2424,28 @@
         <v>124</v>
       </c>
       <c r="M6" s="1">
-        <v>0.06068189073288033</v>
+        <v>0.05502155979540624</v>
       </c>
       <c r="N6" s="1">
-        <v>16.428573410232346</v>
+        <v>14.540331167970432</v>
       </c>
       <c r="O6" s="1">
-        <v>68.35443037974683</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>39.36708860759493</v>
+        <v>39.1139240506329</v>
       </c>
       <c r="R6" s="1">
-        <v>42.911392405063296</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2459,25 +2459,25 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D7" s="2">
-        <v>6.300000000000001</v>
+        <v>6.2693877551020405</v>
       </c>
       <c r="E7" s="2">
         <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.01774647948898561</v>
+        <v>-0.01633911583033909</v>
       </c>
       <c r="G7" s="2">
         <v>2.25</v>
       </c>
       <c r="H7" s="2">
-        <v>61.66</v>
+        <v>59.95</v>
       </c>
       <c r="I7" s="2">
-        <v>19.4</v>
+        <v>18.33</v>
       </c>
       <c r="J7" s="2">
-        <v>0.02356356077928883</v>
+        <v>0.02343295342828491</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.09832082472281822</v>
+        <v>0.08320057402503367</v>
       </c>
       <c r="N7" s="2">
-        <v>20.19246680922612</v>
+        <v>17.358232590933188</v>
       </c>
       <c r="O7" s="2">
         <v>72.15189873417721</v>
@@ -2498,16 +2498,16 @@
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>63.291139240506325</v>
+        <v>63.164556962025316</v>
       </c>
       <c r="R7" s="2">
-        <v>54.74683544303797</v>
+        <v>54.87341772151898</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2527,49 +2527,49 @@
         <v>0.19</v>
       </c>
       <c r="F8" s="2">
-        <v>0.28186469926579444</v>
+        <v>0.28807913833170645</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>73.89</v>
+        <v>71.77</v>
       </c>
       <c r="I8" s="2">
-        <v>21.77</v>
+        <v>20.9</v>
       </c>
       <c r="J8" s="2">
-        <v>0.034017139234755404</v>
+        <v>0.03396351038451503</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-213</v>
+        <v>-212</v>
       </c>
       <c r="M8" s="2">
-        <v>0.24936585408648937</v>
+        <v>0.2602080251722021</v>
       </c>
       <c r="N8" s="2">
-        <v>35.296969745593245</v>
+        <v>35.05897770565003</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>65.9493670886076</v>
+        <v>65.56962025316456</v>
       </c>
       <c r="R8" s="2">
-        <v>55.12658227848101</v>
+        <v>55.18987341772152</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.19</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2589,19 +2589,19 @@
         <v>2.36</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.13409334925882924</v>
+        <v>-0.1310840982921593</v>
       </c>
       <c r="G9" s="1">
         <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>45.02</v>
+        <v>45.18</v>
       </c>
       <c r="I9" s="1">
-        <v>-17.21</v>
+        <v>-17.09</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.011874267314837147</v>
+        <v>-0.013538607039830019</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
@@ -2610,28 +2610,28 @@
         <v>-14</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.0876664275741077</v>
+        <v>-0.0912682223500102</v>
       </c>
       <c r="N9" s="1">
-        <v>1.593741579533539</v>
+        <v>-0.08864704657120212</v>
       </c>
       <c r="O9" s="1">
-        <v>44.303797468354425</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P9" s="1">
         <v>34.04748479877408</v>
       </c>
       <c r="Q9" s="1">
-        <v>45.94936708860759</v>
+        <v>45.44303797468355</v>
       </c>
       <c r="R9" s="1">
-        <v>38.544303797468345</v>
+        <v>38.67088607594936</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-2.66</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2645,55 +2645,55 @@
         <v>67.08860759493672</v>
       </c>
       <c r="D10" s="1">
-        <v>0.49919999999999987</v>
+        <v>0.5536000000000001</v>
       </c>
       <c r="E10" s="1">
         <v>1.48</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.15618452939247937</v>
+        <v>-0.1679420458536197</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>50.87</v>
+        <v>47.02</v>
       </c>
       <c r="I10" s="1">
-        <v>-4.47</v>
+        <v>-5.9</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0016819570629001991</v>
+        <v>0.001443700246548156</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.1181144536110077</v>
+        <v>-0.13529302758105743</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.4510610241564685</v>
+        <v>-4.491127569675927</v>
       </c>
       <c r="O10" s="1">
-        <v>40.50632911392405</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>47.08860759493671</v>
+        <v>46.32911392405064</v>
       </c>
       <c r="R10" s="1">
-        <v>37.21518987341773</v>
+        <v>35.9493670886076</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.58</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2707,25 +2707,25 @@
         <v>12.658227848101266</v>
       </c>
       <c r="D11" s="2">
-        <v>31.911764705882348</v>
+        <v>31.867647058823525</v>
       </c>
       <c r="E11" s="2">
         <v>5.47</v>
       </c>
       <c r="F11" s="2">
-        <v>0.22299371633748066</v>
+        <v>0.2467983561729473</v>
       </c>
       <c r="G11" s="2">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="H11" s="2">
-        <v>70.02</v>
+        <v>70.65</v>
       </c>
       <c r="I11" s="2">
-        <v>12.52</v>
+        <v>13.3</v>
       </c>
       <c r="J11" s="2">
-        <v>0.020915555931008648</v>
+        <v>0.02183170715604227</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2734,28 +2734,28 @@
         <v>24</v>
       </c>
       <c r="M11" s="2">
-        <v>0.20535148609728648</v>
+        <v>0.2324646408337736</v>
       </c>
       <c r="N11" s="2">
-        <v>30.895532946672947</v>
+        <v>32.28463927180717</v>
       </c>
       <c r="O11" s="2">
-        <v>81.0126582278481</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>56.9620253164557</v>
+        <v>58.481012658227854</v>
       </c>
       <c r="R11" s="2">
-        <v>50.12658227848102</v>
+        <v>51.26582278481013</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>3.67</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2775,19 +2775,19 @@
         <v>5.82</v>
       </c>
       <c r="F12" s="3">
-        <v>-0.2049896933311422</v>
+        <v>-0.1991037672820881</v>
       </c>
       <c r="G12" s="3">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H12" s="3">
-        <v>57.88</v>
+        <v>59.24</v>
       </c>
       <c r="I12" s="3">
-        <v>-30.54</v>
+        <v>-29.36</v>
       </c>
       <c r="J12" s="3">
-        <v>-0.010360775283759253</v>
+        <v>-0.006858348084406471</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>0</v>
@@ -2796,10 +2796,10 @@
         <v>-50</v>
       </c>
       <c r="M12" s="3">
-        <v>-0.22077484670394754</v>
+        <v>-0.2118448475835758</v>
       </c>
       <c r="N12" s="3">
-        <v>-11.717100333450444</v>
+        <v>-12.146309569927759</v>
       </c>
       <c r="O12" s="3">
         <v>21.518987341772153</v>
@@ -2808,16 +2808,16 @@
         <v>49.40073075603063</v>
       </c>
       <c r="Q12" s="3">
-        <v>44.05063291139242</v>
+        <v>46.07594936708862</v>
       </c>
       <c r="R12" s="3">
-        <v>26.0126582278481</v>
+        <v>26.645569620253163</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="3">
-        <v>5.32</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2837,19 +2837,19 @@
         <v>1.61</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.26024952328295353</v>
+        <v>-0.3009153370465708</v>
       </c>
       <c r="G13" s="3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H13" s="3">
-        <v>42.66</v>
+        <v>38.66</v>
       </c>
       <c r="I13" s="3">
-        <v>-5.31</v>
+        <v>-10.15</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.0008064113307644788</v>
+        <v>-0.0013989788988333187</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
@@ -2858,28 +2858,28 @@
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.22125090906778744</v>
+        <v>-0.2682663187740085</v>
       </c>
       <c r="N13" s="3">
-        <v>-11.76470656983444</v>
+        <v>-17.78845668897103</v>
       </c>
       <c r="O13" s="3">
-        <v>20.253164556962027</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>25.063291139240505</v>
+        <v>23.544303797468356</v>
       </c>
       <c r="R13" s="3">
-        <v>10.569620253164558</v>
+        <v>8.670886075949369</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-5.32</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2899,49 +2899,49 @@
         <v>-0.14</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.01092020219065673</v>
+        <v>-0.025923745197437856</v>
       </c>
       <c r="G14" s="1">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H14" s="1">
-        <v>65.53</v>
+        <v>62.48</v>
       </c>
       <c r="I14" s="1">
-        <v>2.27</v>
+        <v>0.75</v>
       </c>
       <c r="J14" s="1">
-        <v>0.007725695028373236</v>
+        <v>0.007950643838121526</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.048061739538433956</v>
+        <v>-0.05698012843231415</v>
       </c>
       <c r="N14" s="1">
-        <v>5.5542103831009</v>
+        <v>3.340162345198408</v>
       </c>
       <c r="O14" s="1">
-        <v>50.63291139240506</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>56.45569620253164</v>
+        <v>56.835443037974684</v>
       </c>
       <c r="R14" s="1">
-        <v>39.55696202531645</v>
+        <v>40.31645569620253</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>4.37</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2961,31 +2961,31 @@
         <v>5.49</v>
       </c>
       <c r="F15" s="2">
-        <v>1.127327487725272</v>
+        <v>1.2513677851677776</v>
       </c>
       <c r="G15" s="2">
         <v>2.2</v>
       </c>
       <c r="H15" s="2">
-        <v>61.66</v>
+        <v>63.31</v>
       </c>
       <c r="I15" s="2">
-        <v>139.15</v>
+        <v>142.52</v>
       </c>
       <c r="J15" s="2">
-        <v>0.1098033550304983</v>
+        <v>0.10424764751513516</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M15" s="2">
-        <v>1.2387520997686037</v>
+        <v>1.3469258874289354</v>
       </c>
       <c r="N15" s="2">
-        <v>134.23559431380468</v>
+        <v>143.73076393132337</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2994,7 +2994,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>69.62025316455697</v>
+        <v>70.12658227848101</v>
       </c>
       <c r="R15" s="2">
         <v>61.962025316455694</v>
@@ -3007,65 +3007,65 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>-3.53</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="3">
         <v>8.860759493670885</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="3">
         <v>12.218130311614733</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="3">
         <v>8.13</v>
       </c>
-      <c r="F16" s="1">
-        <v>-0.15149643627224202</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.93</v>
-      </c>
-      <c r="H16" s="1">
-        <v>43.14</v>
-      </c>
-      <c r="I16" s="1">
-        <v>-3.96</v>
-      </c>
-      <c r="J16" s="1">
-        <v>-0.002538217697842285</v>
-      </c>
-      <c r="K16" s="1" t="b">
+      <c r="F16" s="3">
+        <v>-0.2069121929175408</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.92</v>
+      </c>
+      <c r="H16" s="3">
+        <v>39.3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>-9.65</v>
+      </c>
+      <c r="J16" s="3">
+        <v>-0.003276645157127991</v>
+      </c>
+      <c r="K16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="3">
         <v>16</v>
       </c>
-      <c r="M16" s="1">
-        <v>-0.06514236193865997</v>
-      </c>
-      <c r="N16" s="1">
-        <v>3.8461481430783033</v>
-      </c>
-      <c r="O16" s="1">
-        <v>46.835443037974684</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="M16" s="3">
+        <v>-0.13365098118398644</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-4.326922929968819</v>
+      </c>
+      <c r="O16" s="3">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
-      <c r="Q16" s="1">
-        <v>38.734177215189874</v>
-      </c>
-      <c r="R16" s="1">
-        <v>31.582278481012654</v>
-      </c>
-      <c r="S16" s="1" t="s">
+      <c r="Q16" s="3">
+        <v>37.848101265822784</v>
+      </c>
+      <c r="R16" s="3">
+        <v>28.924050632911392</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="1">
-        <v>-5.06</v>
+      <c r="T16" s="3">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3085,19 +3085,19 @@
         <v>4.24</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.25716158133857125</v>
+        <v>-0.2585163190417348</v>
       </c>
       <c r="G17" s="3">
         <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>41.08</v>
+        <v>39.18</v>
       </c>
       <c r="I17" s="3">
-        <v>-13.13</v>
+        <v>-14.8</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.015227695388811618</v>
+        <v>-0.01652593355853355</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3106,13 +3106,13 @@
         <v>21</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.19030681411257222</v>
+        <v>-0.20118145768504003</v>
       </c>
       <c r="N17" s="3">
-        <v>-8.670297074312918</v>
+        <v>-11.07997058007418</v>
       </c>
       <c r="O17" s="3">
-        <v>27.848101265822784</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
@@ -3121,75 +3121,75 @@
         <v>22.78481012658228</v>
       </c>
       <c r="R17" s="3">
-        <v>17.215189873417724</v>
+        <v>16.582278481012658</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-5.95</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>8.39</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.33335657642902744</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F18" s="1">
+        <v>-0.3102410382358625</v>
+      </c>
+      <c r="G18" s="1">
         <v>1.22</v>
       </c>
-      <c r="H18" s="3">
-        <v>35.23</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-11.79</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.009136273670612718</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="H18" s="1">
+        <v>35.82</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-11.44</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.009763830748729873</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>37</v>
       </c>
-      <c r="M18" s="3">
-        <v>-0.31292873088775</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-20.932488751830693</v>
-      </c>
-      <c r="O18" s="3">
-        <v>6.329113924050633</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="M18" s="1">
+        <v>-0.2927220528213169</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-20.234030093701872</v>
+      </c>
+      <c r="O18" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P18" s="1">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="3">
-        <v>47.21518987341772</v>
-      </c>
-      <c r="R18" s="3">
-        <v>29.430379746835445</v>
-      </c>
-      <c r="S18" s="3" t="s">
+      <c r="Q18" s="1">
+        <v>47.84810126582279</v>
+      </c>
+      <c r="R18" s="1">
+        <v>30.189873417721518</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="3">
-        <v>-1.52</v>
+      <c r="T18" s="1">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,19 +3209,19 @@
         <v>-0.16</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.0482860664332288</v>
+        <v>-0.04506612647753924</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>52.51</v>
+        <v>51.01</v>
       </c>
       <c r="I19" s="1">
-        <v>14.21</v>
+        <v>13.2</v>
       </c>
       <c r="J19" s="1">
-        <v>0.004892045477902574</v>
+        <v>0.003913390669480092</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>1</v>
@@ -3230,28 +3230,28 @@
         <v>83</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.12256914112878325</v>
+        <v>-0.1087715279849778</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.8965297759340138</v>
+        <v>-1.8389776100679551</v>
       </c>
       <c r="O19" s="1">
-        <v>39.24050632911392</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>53.29113924050634</v>
+        <v>52.65822784810127</v>
       </c>
       <c r="R19" s="1">
-        <v>41.0126582278481</v>
+        <v>41.64556962025317</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>0.13</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3271,19 +3271,19 @@
         <v>-3.42</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.04356525066034293</v>
+        <v>-0.05681047219559868</v>
       </c>
       <c r="G20" s="1">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H20" s="1">
-        <v>58.94</v>
+        <v>58.42</v>
       </c>
       <c r="I20" s="1">
-        <v>-3.64</v>
+        <v>-3.89</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.009626840755102025</v>
+        <v>-0.006193482756174904</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>1</v>
@@ -3292,28 +3292,28 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.03985109692556521</v>
+        <v>-0.05203256708254078</v>
       </c>
       <c r="N20" s="1">
-        <v>6.375274644387787</v>
+        <v>3.834918480175752</v>
       </c>
       <c r="O20" s="1">
-        <v>54.43037974683544</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>46.32911392405064</v>
+        <v>48.86075949367089</v>
       </c>
       <c r="R20" s="1">
-        <v>39.050632911392405</v>
+        <v>39.81012658227848</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>11.65</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3333,19 +3333,19 @@
         <v>4.96</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.04643621647741378</v>
+        <v>-0.1002253939883951</v>
       </c>
       <c r="G21" s="1">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H21" s="1">
-        <v>70.71</v>
+        <v>63.59</v>
       </c>
       <c r="I21" s="1">
-        <v>36.05</v>
+        <v>27.76</v>
       </c>
       <c r="J21" s="1">
-        <v>0.009664512828652428</v>
+        <v>0.016732073833929544</v>
       </c>
       <c r="K21" s="1" t="b">
         <v>1</v>
@@ -3354,28 +3354,28 @@
         <v>37</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.014865909731803129</v>
+        <v>-0.07474323338541966</v>
       </c>
       <c r="N21" s="1">
-        <v>8.873793363763987</v>
+        <v>1.5638518498878544</v>
       </c>
       <c r="O21" s="1">
-        <v>59.49367088607595</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P21" s="1">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="1">
-        <v>64.17721518987341</v>
+        <v>63.54430379746835</v>
       </c>
       <c r="R21" s="1">
-        <v>44.55696202531646</v>
+        <v>41.13924050632911</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="1">
-        <v>5.76</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3395,19 +3395,19 @@
         <v>-0.12</v>
       </c>
       <c r="F22" s="3">
-        <v>-0.2626579789231705</v>
+        <v>-0.253462646965331</v>
       </c>
       <c r="G22" s="3">
         <v>1.36</v>
       </c>
       <c r="H22" s="3">
-        <v>45.13</v>
+        <v>44.72</v>
       </c>
       <c r="I22" s="3">
-        <v>-4.57</v>
+        <v>-4.83</v>
       </c>
       <c r="J22" s="3">
-        <v>-0.014564777696410366</v>
+        <v>-0.013833642849341365</v>
       </c>
       <c r="K22" s="3" t="b">
         <v>0</v>
@@ -3416,28 +3416,28 @@
         <v>59</v>
       </c>
       <c r="M22" s="3">
-        <v>-0.22923059531017098</v>
+        <v>-0.22479521628698362</v>
       </c>
       <c r="N22" s="3">
-        <v>-12.562675194072789</v>
+        <v>-13.441346440268537</v>
       </c>
       <c r="O22" s="3">
-        <v>17.72151898734177</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P22" s="3">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="3">
-        <v>41.0126582278481</v>
+        <v>41.13924050632911</v>
       </c>
       <c r="R22" s="3">
-        <v>28.417721518987342</v>
+        <v>28.79746835443038</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="3">
-        <v>-1.84</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3457,49 +3457,49 @@
         <v>-0.36</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.16981242643259645</v>
+        <v>-0.17262882708177096</v>
       </c>
       <c r="G23" s="1">
         <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>44.5</v>
+        <v>41.46</v>
       </c>
       <c r="I23" s="1">
-        <v>-9.13</v>
+        <v>-10.31</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.00697930373215041</v>
+        <v>-0.006805512295149884</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.1475275040239301</v>
+        <v>-0.15351720662953938</v>
       </c>
       <c r="N23" s="1">
-        <v>-4.392366065448701</v>
+        <v>-6.313545474524116</v>
       </c>
       <c r="O23" s="1">
-        <v>36.708860759493675</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>44.68354430379747</v>
+        <v>43.41772151898734</v>
       </c>
       <c r="R23" s="1">
-        <v>34.810126582278485</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>2.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3513,55 +3513,55 @@
         <v>1.2658227848101267</v>
       </c>
       <c r="D24" s="3">
-        <v>-0.1750498007968128</v>
+        <v>-0.009462151394422375</v>
       </c>
       <c r="E24" s="3">
         <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.04721990067610321</v>
+        <v>0.01990081906122826</v>
       </c>
       <c r="G24" s="3">
         <v>3.57</v>
       </c>
       <c r="H24" s="3">
-        <v>48.42</v>
+        <v>47.38</v>
       </c>
       <c r="I24" s="3">
-        <v>-23.15</v>
+        <v>-23.72</v>
       </c>
       <c r="J24" s="3">
-        <v>0.027345354150105805</v>
+        <v>0.02435625297783154</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="M24" s="3">
-        <v>0.19141447678336543</v>
+        <v>0.2245544214038746</v>
       </c>
       <c r="N24" s="3">
-        <v>29.501832015280847</v>
+        <v>31.493617328817287</v>
       </c>
       <c r="O24" s="3">
-        <v>78.48101265822784</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>25.56962025316456</v>
+        <v>27.468354430379748</v>
       </c>
       <c r="R24" s="3">
-        <v>26.962025316455694</v>
+        <v>29.49367088607595</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-4.05</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3581,19 +3581,19 @@
         <v>14.49</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.48340627771798417</v>
+        <v>-0.47908174589138464</v>
       </c>
       <c r="G25" s="3">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H25" s="3">
-        <v>41.46</v>
+        <v>39.49</v>
       </c>
       <c r="I25" s="3">
-        <v>-55.71</v>
+        <v>-57.17</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.007285600179980536</v>
+        <v>-0.009106245229165899</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3602,28 +3602,28 @@
         <v>39</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.3691960503735692</v>
+        <v>-0.3819310085925408</v>
       </c>
       <c r="N25" s="3">
-        <v>-26.55922070041261</v>
+        <v>-29.154925670824262</v>
       </c>
       <c r="O25" s="3">
-        <v>5.063291139240507</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>24.55696202531646</v>
+        <v>23.16455696202532</v>
       </c>
       <c r="R25" s="3">
-        <v>7.784810126582279</v>
+        <v>6.7721518987341796</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-4.18</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3643,31 +3643,31 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="1">
-        <v>0.1921820320860143</v>
+        <v>0.2000788445480564</v>
       </c>
       <c r="G26" s="1">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H26" s="1">
-        <v>54.12</v>
+        <v>52.69</v>
       </c>
       <c r="I26" s="1">
-        <v>4.86</v>
+        <v>2.9</v>
       </c>
       <c r="J26" s="1">
-        <v>0.045595959814655786</v>
+        <v>0.04255622403041103</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="M26" s="1">
-        <v>0.38253241099337254</v>
+        <v>0.36252761839202474</v>
       </c>
       <c r="N26" s="1">
-        <v>48.613625436281566</v>
+        <v>45.2909370276323</v>
       </c>
       <c r="O26" s="1">
         <v>88.60759493670885</v>
@@ -3676,7 +3676,7 @@
         <v>50.63126652197354</v>
       </c>
       <c r="Q26" s="1">
-        <v>37.721518987341774</v>
+        <v>37.84810126582279</v>
       </c>
       <c r="R26" s="1">
         <v>32.278481012658226</v>
@@ -3705,19 +3705,19 @@
         <v>5.04</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.2179909716700258</v>
+        <v>-0.22830492742217814</v>
       </c>
       <c r="G27" s="3">
         <v>2.62</v>
       </c>
       <c r="H27" s="3">
-        <v>56.58</v>
+        <v>52.61</v>
       </c>
       <c r="I27" s="3">
-        <v>-21.18</v>
+        <v>-23.64</v>
       </c>
       <c r="J27" s="3">
-        <v>0.008305972203884657</v>
+        <v>0.007736944793131371</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3726,28 +3726,28 @@
         <v>40</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.06756774541152799</v>
+        <v>-0.09930148936961503</v>
       </c>
       <c r="N27" s="3">
-        <v>3.6036097957914994</v>
+        <v>-0.8919737485316819</v>
       </c>
       <c r="O27" s="3">
-        <v>45.56962025316456</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>36.962025316455694</v>
+        <v>35.822784810126585</v>
       </c>
       <c r="R27" s="3">
-        <v>23.67088607594937</v>
+        <v>23.164556962025316</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>-2.72</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3767,31 +3767,31 @@
         <v>-1.13</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.43334734979242256</v>
+        <v>-0.41128140658019646</v>
       </c>
       <c r="G28" s="3">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="H28" s="3">
-        <v>46.78</v>
+        <v>46.57</v>
       </c>
       <c r="I28" s="3">
-        <v>-27.12</v>
+        <v>-27.08</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.008211679821581552</v>
+        <v>-0.006479189644248075</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.23556866341550886</v>
+        <v>-0.24246209258548423</v>
       </c>
       <c r="N28" s="3">
-        <v>-13.196482004606583</v>
+        <v>-15.208034070118599</v>
       </c>
       <c r="O28" s="3">
         <v>16.455696202531644</v>
@@ -3800,16 +3800,16 @@
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>33.54430379746835</v>
+        <v>34.43037974683544</v>
       </c>
       <c r="R28" s="3">
-        <v>18.35443037974684</v>
+        <v>18.734177215189877</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-3.54</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3823,25 +3823,25 @@
         <v>34.177215189873415</v>
       </c>
       <c r="D29" s="3">
-        <v>77.04545454545456</v>
+        <v>77.20454545454545</v>
       </c>
       <c r="E29" s="3">
         <v>0.88</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.4023720672745934</v>
+        <v>-0.40014255715490565</v>
       </c>
       <c r="G29" s="3">
         <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>42.02</v>
+        <v>38.85</v>
       </c>
       <c r="I29" s="3">
-        <v>-33</v>
+        <v>-34.96</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.017697579687506945</v>
+        <v>-0.018989950140114696</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
@@ -3850,10 +3850,10 @@
         <v>-63</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.2983757627008171</v>
+        <v>-0.31095499504449164</v>
       </c>
       <c r="N29" s="3">
-        <v>-19.477191933137412</v>
+        <v>-22.057324316019347</v>
       </c>
       <c r="O29" s="3">
         <v>7.59493670886076</v>
@@ -3862,7 +3862,7 @@
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.0126582278481</v>
+        <v>40.25316455696202</v>
       </c>
       <c r="R29" s="3">
         <v>24.36708860759493</v>
@@ -3891,19 +3891,19 @@
         <v>2.51</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.2181834356803246</v>
+        <v>-0.20642110147513193</v>
       </c>
       <c r="G30" s="1">
         <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>44.69</v>
+        <v>40.52</v>
       </c>
       <c r="I30" s="1">
-        <v>0.43</v>
+        <v>-2.1</v>
       </c>
       <c r="J30" s="1">
-        <v>0.0012361694659760135</v>
+        <v>-0.00033825062740763616</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
@@ -3912,28 +3912,28 @@
         <v>23</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.19961266700643598</v>
+        <v>-0.1904947510982723</v>
       </c>
       <c r="N30" s="1">
-        <v>-9.600882363699286</v>
+        <v>-10.011299921397404</v>
       </c>
       <c r="O30" s="1">
-        <v>25.31645569620253</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>62.151898734177216</v>
+        <v>60.63291139240506</v>
       </c>
       <c r="R30" s="1">
-        <v>44.683544303797476</v>
+        <v>44.9367088607595</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-2.85</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3953,49 +3953,49 @@
         <v>0.99</v>
       </c>
       <c r="F31" s="2">
-        <v>0.12160998144169308</v>
+        <v>0.10793332560072785</v>
       </c>
       <c r="G31" s="2">
         <v>1.43</v>
       </c>
       <c r="H31" s="2">
-        <v>56.52</v>
+        <v>52.17</v>
       </c>
       <c r="I31" s="2">
-        <v>21.08</v>
+        <v>18.1</v>
       </c>
       <c r="J31" s="2">
-        <v>0.02815971364510794</v>
+        <v>0.026066919833058855</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M31" s="2">
-        <v>0.1615371340905536</v>
+        <v>0.14217497891097608</v>
       </c>
       <c r="N31" s="2">
-        <v>26.51409774599967</v>
+        <v>23.255673079527426</v>
       </c>
       <c r="O31" s="2">
-        <v>75.9493670886076</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>67.46835443037975</v>
+        <v>66.83544303797468</v>
       </c>
       <c r="R31" s="2">
-        <v>59.81012658227849</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-1.01</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4015,19 +4015,19 @@
         <v>1.51</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.3506085062803344</v>
+        <v>-0.3401955153799341</v>
       </c>
       <c r="G32" s="3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H32" s="3">
-        <v>33.07</v>
+        <v>30.26</v>
       </c>
       <c r="I32" s="3">
-        <v>-12.95</v>
+        <v>-15.9</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.007322670909482875</v>
+        <v>-0.009785412990941067</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
@@ -4036,28 +4036,28 @@
         <v>21</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.2930391233912797</v>
+        <v>-0.2916201467305122</v>
       </c>
       <c r="N32" s="3">
-        <v>-18.943528002183665</v>
+        <v>-20.123839484621396</v>
       </c>
       <c r="O32" s="3">
-        <v>8.860759493670885</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P32" s="3">
-        <v>38.62068790128861</v>
+        <v>40.689656926297594</v>
       </c>
       <c r="Q32" s="3">
-        <v>31.139240506329113</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="R32" s="3">
-        <v>16.13924050632911</v>
+        <v>15.379746835443036</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-13.23</v>
+        <v>-13.99</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4077,49 +4077,49 @@
         <v>0.66</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.04473289060781967</v>
+        <v>-0.05295399731155552</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>58.77</v>
+        <v>54.17</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.44</v>
+        <v>-9.66</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0020349008366425656</v>
+        <v>0.001973267457559314</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.03637604470456979</v>
+        <v>-0.04578713964196868</v>
       </c>
       <c r="N33" s="1">
-        <v>6.72277986648732</v>
+        <v>4.4594612242329426</v>
       </c>
       <c r="O33" s="1">
-        <v>56.9620253164557</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P33" s="1">
         <v>26.894390179645494</v>
       </c>
       <c r="Q33" s="1">
-        <v>53.037974683544306</v>
+        <v>52.15189873417721</v>
       </c>
       <c r="R33" s="1">
-        <v>43.79746835443038</v>
+        <v>42.59493670886076</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>3.86</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4139,49 +4139,49 @@
         <v>0.94</v>
       </c>
       <c r="F34" s="2">
-        <v>0.18653803551012116</v>
+        <v>0.1669281053839797</v>
       </c>
       <c r="G34" s="2">
         <v>1.26</v>
       </c>
       <c r="H34" s="2">
-        <v>70.3</v>
+        <v>62.07</v>
       </c>
       <c r="I34" s="2">
-        <v>35.78</v>
+        <v>32.16</v>
       </c>
       <c r="J34" s="2">
-        <v>0.029030342290056157</v>
+        <v>0.02891552930206472</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M34" s="2">
-        <v>0.21068003478617636</v>
+        <v>0.18763236087389723</v>
       </c>
       <c r="N34" s="2">
-        <v>31.42838781556194</v>
+        <v>27.801411275819536</v>
       </c>
       <c r="O34" s="2">
-        <v>82.27848101265823</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>61.518987341772146</v>
+        <v>60.75949367088609</v>
       </c>
       <c r="R34" s="2">
-        <v>52.46835443037974</v>
+        <v>52.21518987341772</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="2">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4201,31 +4201,31 @@
         <v>4.55</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.27897198259300393</v>
+        <v>-0.2745770929426098</v>
       </c>
       <c r="G35" s="3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H35" s="3">
-        <v>31.37</v>
+        <v>35.51</v>
       </c>
       <c r="I35" s="3">
-        <v>-23.96</v>
+        <v>-22.64</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.026896848291015418</v>
+        <v>-0.027677007413035547</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.27897198259300393</v>
+        <v>-0.2737807754237668</v>
       </c>
       <c r="N35" s="3">
-        <v>-17.53681392235609</v>
+        <v>-18.33990235394686</v>
       </c>
       <c r="O35" s="3">
         <v>11.39240506329114</v>
@@ -4234,7 +4234,7 @@
         <v>29.3533388963776</v>
       </c>
       <c r="Q35" s="3">
-        <v>32.91139240506329</v>
+        <v>34.0506329113924</v>
       </c>
       <c r="R35" s="3">
         <v>23.417721518987342</v>
@@ -4263,49 +4263,49 @@
         <v>-1.05</v>
       </c>
       <c r="F36" s="3">
-        <v>-0.2500884003591458</v>
+        <v>-0.21345558880979326</v>
       </c>
       <c r="G36" s="3">
         <v>1.12</v>
       </c>
       <c r="H36" s="3">
-        <v>33.41</v>
+        <v>32.96</v>
       </c>
       <c r="I36" s="3">
-        <v>-19.48</v>
+        <v>-19.79</v>
       </c>
       <c r="J36" s="3">
-        <v>-0.016795387598225176</v>
+        <v>-0.018745918141179544</v>
       </c>
       <c r="K36" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L36" s="3">
-        <v>-52</v>
+        <v>-51</v>
       </c>
       <c r="M36" s="3">
-        <v>-0.23894593915481266</v>
+        <v>-0.20389977858367747</v>
       </c>
       <c r="N36" s="3">
-        <v>-13.53420957853696</v>
+        <v>-11.351802669937927</v>
       </c>
       <c r="O36" s="3">
-        <v>15.18987341772152</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P36" s="3">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="3">
-        <v>36.582278481012665</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="R36" s="3">
-        <v>25.632911392405067</v>
+        <v>28.29113924050633</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="3">
-        <v>-8.67</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4325,31 +4325,31 @@
         <v>1.72</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.051287303410220586</v>
+        <v>-0.0632232162901188</v>
       </c>
       <c r="G37" s="1">
         <v>1.38</v>
       </c>
       <c r="H37" s="1">
-        <v>34.85</v>
+        <v>32.67</v>
       </c>
       <c r="I37" s="1">
-        <v>-23.09</v>
+        <v>-23.9</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.003781111725511868</v>
+        <v>-0.004694245373217974</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-205</v>
+        <v>-206</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.01600284292983223</v>
+        <v>-0.0329631505740855</v>
       </c>
       <c r="N37" s="1">
-        <v>8.76010004396109</v>
+        <v>5.741860131021274</v>
       </c>
       <c r="O37" s="1">
         <v>58.22784810126582</v>
@@ -4358,7 +4358,7 @@
         <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
-        <v>37.84810126582279</v>
+        <v>37.34177215189874</v>
       </c>
       <c r="R37" s="1">
         <v>37.21518987341772</v>
@@ -4387,19 +4387,19 @@
         <v>-0.05</v>
       </c>
       <c r="F38" s="2">
-        <v>0.38084096194479583</v>
+        <v>0.38459935188995253</v>
       </c>
       <c r="G38" s="2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H38" s="2">
-        <v>84.82</v>
+        <v>83.9</v>
       </c>
       <c r="I38" s="2">
-        <v>34.15</v>
+        <v>33.48</v>
       </c>
       <c r="J38" s="2">
-        <v>0.040201883985519334</v>
+        <v>0.040893267337176645</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
@@ -4408,28 +4408,28 @@
         <v>-42</v>
       </c>
       <c r="M38" s="2">
-        <v>0.39012634628174014</v>
+        <v>0.39335884459722537</v>
       </c>
       <c r="N38" s="2">
-        <v>49.37301896511831</v>
+        <v>48.374059648152354</v>
       </c>
       <c r="O38" s="2">
-        <v>89.87341772151899</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P38" s="2">
         <v>27.505487150580247</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.18987341772153</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="R38" s="2">
-        <v>55.189873417721515</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4449,49 +4449,49 @@
         <v>-6.6</v>
       </c>
       <c r="F39" s="2">
-        <v>0.13925187422803692</v>
+        <v>0.08786365801448949</v>
       </c>
       <c r="G39" s="2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H39" s="2">
-        <v>58.74</v>
+        <v>54.42</v>
       </c>
       <c r="I39" s="2">
-        <v>13.84</v>
+        <v>11.54</v>
       </c>
       <c r="J39" s="2">
-        <v>0.016446432492736814</v>
+        <v>0.017164162547676932</v>
       </c>
       <c r="K39" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2">
         <v>-4</v>
       </c>
       <c r="M39" s="2">
-        <v>0.16710802723886986</v>
+        <v>0.11254950109862194</v>
       </c>
       <c r="N39" s="2">
-        <v>27.071187060831292</v>
+        <v>20.29312529829202</v>
       </c>
       <c r="O39" s="2">
-        <v>77.21518987341773</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P39" s="2">
         <v>18.299999237060547</v>
       </c>
       <c r="Q39" s="2">
-        <v>60.12658227848102</v>
+        <v>60</v>
       </c>
       <c r="R39" s="2">
-        <v>55.12658227848102</v>
+        <v>54.11392405063292</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="2">
-        <v>1.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4511,19 +4511,19 @@
         <v>10.16</v>
       </c>
       <c r="F40" s="1">
-        <v>0.10050004291534424</v>
+        <v>0.12676959523726963</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>39.88</v>
+        <v>41.68</v>
       </c>
       <c r="I40" s="1">
-        <v>-21.18</v>
+        <v>-19.62</v>
       </c>
       <c r="J40" s="1">
-        <v>0.011139004953147463</v>
+        <v>0.00654322177489611</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
@@ -4532,13 +4532,13 @@
         <v>52</v>
       </c>
       <c r="M40" s="1">
-        <v>0.007646199545901178</v>
+        <v>0.04713784335297144</v>
       </c>
       <c r="N40" s="1">
-        <v>11.125004291534424</v>
+        <v>13.751959523726967</v>
       </c>
       <c r="O40" s="1">
-        <v>62.0253164556962</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P40" s="1">
         <v>45.29877115964868</v>
@@ -4547,75 +4547,75 @@
         <v>36.32911392405063</v>
       </c>
       <c r="R40" s="1">
-        <v>32.974683544303794</v>
+        <v>33.60759493670885</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-7.78</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="1">
         <v>-5.03</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="1">
         <v>5.063291139240507</v>
       </c>
-      <c r="D41" s="3">
-        <v>7.415506958250497</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="1">
+        <v>7.405566600397614</v>
+      </c>
+      <c r="E41" s="1">
         <v>-1.71</v>
       </c>
-      <c r="F41" s="3">
-        <v>-0.10456658819425821</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="H41" s="3">
-        <v>55.81</v>
-      </c>
-      <c r="I41" s="3">
-        <v>-15.94</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0.02165646919454138</v>
-      </c>
-      <c r="K41" s="3" t="b">
+      <c r="F41" s="1">
+        <v>-0.03441757424506209</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="H41" s="1">
+        <v>59.29</v>
+      </c>
+      <c r="I41" s="1">
+        <v>-12.89</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.023441624569661992</v>
+      </c>
+      <c r="K41" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="1">
         <v>2</v>
       </c>
-      <c r="M41" s="3">
-        <v>-0.09713828072470276</v>
-      </c>
-      <c r="N41" s="3">
-        <v>0.6465562644740378</v>
-      </c>
-      <c r="O41" s="3">
-        <v>43.037974683544306</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="M41" s="1">
+        <v>-0.028843351613161206</v>
+      </c>
+      <c r="N41" s="1">
+        <v>6.153840027113693</v>
+      </c>
+      <c r="O41" s="1">
+        <v>59.49367088607595</v>
+      </c>
+      <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
-      <c r="Q41" s="3">
-        <v>41.39240506329114</v>
-      </c>
-      <c r="R41" s="3">
-        <v>26.51898734177216</v>
-      </c>
-      <c r="S41" s="3" t="s">
+      <c r="Q41" s="1">
+        <v>44.17721518987343</v>
+      </c>
+      <c r="R41" s="1">
+        <v>32.08860759493672</v>
+      </c>
+      <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T41" s="3">
-        <v>-3.54</v>
+      <c r="T41" s="1">
+        <v>2.03</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4635,19 +4635,19 @@
         <v>0.29</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.09559773625677426</v>
+        <v>-0.0633823226651774</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>35.87</v>
+        <v>43.1</v>
       </c>
       <c r="I42" s="1">
-        <v>-2</v>
+        <v>-0.39</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.006569076692434285</v>
+        <v>-0.006358096147361646</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4656,28 +4656,28 @@
         <v>20</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.15502419601321782</v>
+        <v>-0.11434664387112825</v>
       </c>
       <c r="N42" s="1">
-        <v>-5.142035264377481</v>
+        <v>-2.396489198683003</v>
       </c>
       <c r="O42" s="1">
-        <v>35.44303797468354</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>41.89873417721519</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="R42" s="1">
-        <v>37.848101265822784</v>
+        <v>39.11392405063291</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.7</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4697,49 +4697,49 @@
         <v>6.54</v>
       </c>
       <c r="F43" s="1">
-        <v>0.04050414428282115</v>
+        <v>0.029859632219619917</v>
       </c>
       <c r="G43" s="1">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>54.72</v>
+        <v>55.45</v>
       </c>
       <c r="I43" s="1">
-        <v>-10.56</v>
+        <v>-9.96</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.0051556829918994705</v>
+        <v>-0.006700277013963392</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M43" s="1">
-        <v>0.06650322042626522</v>
+        <v>0.05295284026606639</v>
       </c>
       <c r="N43" s="1">
-        <v>17.010706379570838</v>
+        <v>14.33345921503645</v>
       </c>
       <c r="O43" s="1">
-        <v>69.62025316455697</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P43" s="1">
         <v>36.79958124823221</v>
       </c>
       <c r="Q43" s="1">
-        <v>54.93670886075949</v>
+        <v>54.30379746835443</v>
       </c>
       <c r="R43" s="1">
-        <v>48.60759493670886</v>
+        <v>47.34177215189873</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>6.46</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4753,25 +4753,25 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="3">
-        <v>26.91176470588235</v>
+        <v>26.784313725490197</v>
       </c>
       <c r="E44" s="3">
         <v>-1.94</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.3513018202198858</v>
+        <v>-0.3889839843871479</v>
       </c>
       <c r="G44" s="3">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H44" s="3">
-        <v>39.55</v>
+        <v>38.48</v>
       </c>
       <c r="I44" s="3">
-        <v>-27.35</v>
+        <v>-28.29</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.02314899278559156</v>
+        <v>-0.02536336424811085</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>1</v>
@@ -4780,28 +4780,28 @@
         <v>-109</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.20180713239508252</v>
+        <v>-0.2599805463345848</v>
       </c>
       <c r="N44" s="3">
-        <v>-9.82032890256395</v>
+        <v>-16.959879445028655</v>
       </c>
       <c r="O44" s="3">
-        <v>24.050632911392405</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P44" s="3">
         <v>44.155007607957295</v>
       </c>
       <c r="Q44" s="3">
-        <v>39.87341772151898</v>
+        <v>39.49367088607594</v>
       </c>
       <c r="R44" s="3">
-        <v>29.55696202531646</v>
+        <v>26.89873417721519</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>3.04</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4815,55 +4815,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.7407407407407409</v>
+        <v>0.731182795698925</v>
       </c>
       <c r="E45" s="2">
         <v>1.15</v>
       </c>
       <c r="F45" s="2">
-        <v>0.17041216515705926</v>
+        <v>0.13935809412711037</v>
       </c>
       <c r="G45" s="2">
         <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>59.27</v>
+        <v>51.93</v>
       </c>
       <c r="I45" s="2">
-        <v>15.37</v>
+        <v>12.86</v>
       </c>
       <c r="J45" s="2">
-        <v>0.02289653980282876</v>
+        <v>0.02179236752245355</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M45" s="2">
-        <v>0.2131249331070031</v>
+        <v>0.17598869999388755</v>
       </c>
       <c r="N45" s="2">
-        <v>31.672877647644626</v>
+        <v>26.63704518781857</v>
       </c>
       <c r="O45" s="2">
-        <v>83.54430379746836</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>61.26582278481012</v>
+        <v>58.734177215189874</v>
       </c>
       <c r="R45" s="2">
-        <v>56.32911392405063</v>
+        <v>54.68354430379747</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-0.63</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4883,19 +4883,19 @@
         <v>-0.24</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3050672336445899</v>
+        <v>-0.3719970566229067</v>
       </c>
       <c r="G46" s="3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H46" s="3">
-        <v>37.7</v>
+        <v>34.24</v>
       </c>
       <c r="I46" s="3">
-        <v>-1.19</v>
+        <v>-8.31</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.009046035595179662</v>
+        <v>-0.010350607901697213</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4904,28 +4904,28 @@
         <v>25</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2577117735261739</v>
+        <v>-0.33218118068075764</v>
       </c>
       <c r="N46" s="3">
-        <v>-15.410793015673082</v>
+        <v>-24.179942879645942</v>
       </c>
       <c r="O46" s="3">
-        <v>13.924050632911392</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P46" s="3">
-        <v>40.6204924523832</v>
+        <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>46.708860759493675</v>
+        <v>44.30379746835443</v>
       </c>
       <c r="R46" s="3">
-        <v>27.721518987341764</v>
+        <v>25.0632911392405</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-3.67</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4945,19 +4945,19 @@
         <v>-3.9</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.4271698360842434</v>
+        <v>-0.3955556422473674</v>
       </c>
       <c r="G47" s="3">
         <v>1.47</v>
       </c>
       <c r="H47" s="3">
-        <v>29.38</v>
+        <v>30.06</v>
       </c>
       <c r="I47" s="3">
-        <v>-20.47</v>
+        <v>-20.2</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030347190060011527</v>
+        <v>-0.02994474249710443</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4966,28 +4966,28 @@
         <v>8</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.38352852970060514</v>
+        <v>-0.35812871886174724</v>
       </c>
       <c r="N47" s="3">
-        <v>-27.992468633116207</v>
+        <v>-26.774696697744897</v>
       </c>
       <c r="O47" s="3">
-        <v>3.79746835443038</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P47" s="3">
         <v>31.304415950527737</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.860759493670884</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="R47" s="3">
-        <v>25.25316455696202</v>
+        <v>25.632911392405056</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5007,19 +5007,19 @@
         <v>-0.2</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.19455741925371617</v>
+        <v>-0.18218573932361465</v>
       </c>
       <c r="G48" s="1">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>60.86</v>
+        <v>54.5</v>
       </c>
       <c r="I48" s="1">
-        <v>-3.21</v>
+        <v>-5.24</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.007594479396489348</v>
+        <v>-0.005451166591159077</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>1</v>
@@ -5028,28 +5028,28 @@
         <v>-65</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.19362888082002172</v>
+        <v>-0.18059310428592867</v>
       </c>
       <c r="N48" s="1">
-        <v>-9.002503745057872</v>
+        <v>-9.021135240163044</v>
       </c>
       <c r="O48" s="1">
-        <v>26.582278481012654</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>47.8481012658228</v>
+        <v>48.35443037974684</v>
       </c>
       <c r="R48" s="1">
-        <v>32.594936708860764</v>
+        <v>33.86075949367089</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>6.39</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5069,49 +5069,49 @@
         <v>-1.46</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.03147240354967856</v>
+        <v>0.004905078657271966</v>
       </c>
       <c r="G49" s="2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>52.48</v>
+        <v>51.65</v>
       </c>
       <c r="I49" s="2">
-        <v>39.99</v>
+        <v>38.88</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02326959230595297</v>
+        <v>0.023056684405063557</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M49" s="2">
-        <v>0.02609697933937616</v>
+        <v>0.05348044730669388</v>
       </c>
       <c r="N49" s="2">
-        <v>12.97008227088193</v>
+        <v>14.386219919099217</v>
       </c>
       <c r="O49" s="2">
-        <v>65.82278481012658</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>62.78481012658228</v>
+        <v>63.164556962025316</v>
       </c>
       <c r="R49" s="2">
-        <v>54.62025316455696</v>
+        <v>55.75949367088608</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5131,19 +5131,19 @@
         <v>3.55</v>
       </c>
       <c r="F50" s="2">
-        <v>0.4166832538248919</v>
+        <v>0.3491738299917643</v>
       </c>
       <c r="G50" s="2">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="H50" s="2">
-        <v>53.03</v>
+        <v>53.77</v>
       </c>
       <c r="I50" s="2">
-        <v>101.97</v>
+        <v>102.25</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06644165588838259</v>
+        <v>0.06516006028912798</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
@@ -5152,10 +5152,10 @@
         <v>210</v>
       </c>
       <c r="M50" s="2">
-        <v>0.6766740152593325</v>
+        <v>0.5713464177489562</v>
       </c>
       <c r="N50" s="2">
-        <v>78.02778586287755</v>
+        <v>66.17281696332545</v>
       </c>
       <c r="O50" s="2">
         <v>93.67088607594937</v>
@@ -5164,7 +5164,7 @@
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>71.39240506329114</v>
+        <v>72.27848101265823</v>
       </c>
       <c r="R50" s="2">
         <v>62.21518987341772</v>
@@ -5193,49 +5193,49 @@
         <v>-0.69</v>
       </c>
       <c r="F51" s="2">
-        <v>0.18928018145665992</v>
+        <v>0.1493686948363873</v>
       </c>
       <c r="G51" s="2">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H51" s="2">
-        <v>53.69</v>
+        <v>47.52</v>
       </c>
       <c r="I51" s="2">
-        <v>66.47</v>
+        <v>57.39</v>
       </c>
       <c r="J51" s="2">
-        <v>0.04034650925906881</v>
+        <v>0.03650757721219353</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M51" s="2">
-        <v>0.2914194091630473</v>
+        <v>0.23616730439027234</v>
       </c>
       <c r="N51" s="2">
-        <v>39.50232525324903</v>
+        <v>32.65490562745706</v>
       </c>
       <c r="O51" s="2">
-        <v>86.07594936708861</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P51" s="2">
         <v>15.18684888660459</v>
       </c>
       <c r="Q51" s="2">
-        <v>67.21518987341771</v>
+        <v>65.56962025316456</v>
       </c>
       <c r="R51" s="2">
-        <v>61.77215189873418</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-1.27</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5255,31 +5255,31 @@
         <v>2.59</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.4456703998039746</v>
+        <v>-0.4447601399912655</v>
       </c>
       <c r="G52" s="3">
         <v>1.54</v>
       </c>
       <c r="H52" s="3">
-        <v>36.3</v>
+        <v>37.38</v>
       </c>
       <c r="I52" s="3">
-        <v>-26.9</v>
+        <v>-26.3</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.036499267452008585</v>
+        <v>-0.0393890667011606</v>
       </c>
       <c r="K52" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3">
         <v>-2</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.3955293243844753</v>
+        <v>-0.4017589939737445</v>
       </c>
       <c r="N52" s="3">
-        <v>-29.19254810150323</v>
+        <v>-31.137724208944622</v>
       </c>
       <c r="O52" s="3">
         <v>2.5316455696202533</v>
@@ -5288,7 +5288,7 @@
         <v>46.37680917379436</v>
       </c>
       <c r="Q52" s="3">
-        <v>38.22784810126582</v>
+        <v>38.35443037974684</v>
       </c>
       <c r="R52" s="3">
         <v>21.89873417721519</v>
@@ -5317,19 +5317,19 @@
         <v>16.72</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.11225424461657726</v>
+        <v>-0.10090663255117185</v>
       </c>
       <c r="G53" s="1">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="H53" s="1">
-        <v>43.33</v>
+        <v>39.92</v>
       </c>
       <c r="I53" s="1">
-        <v>12.78</v>
+        <v>5.67</v>
       </c>
       <c r="J53" s="1">
-        <v>0.025800525067663532</v>
+        <v>0.022259614660490392</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
@@ -5338,28 +5338,28 @@
         <v>93</v>
       </c>
       <c r="M53" s="1">
-        <v>0.014955520799559752</v>
+        <v>0.006596232492630749</v>
       </c>
       <c r="N53" s="1">
-        <v>11.855936416900272</v>
+        <v>9.697798437692896</v>
       </c>
       <c r="O53" s="1">
-        <v>64.55696202531645</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>47.72151898734178</v>
+        <v>45.69620253164557</v>
       </c>
       <c r="R53" s="1">
-        <v>37.278481012658226</v>
+        <v>36.01265822784811</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>10.63</v>
+        <v>9.37</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5379,19 +5379,19 @@
         <v>0.25</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.000776152966117688</v>
+        <v>-0.017023413517112118</v>
       </c>
       <c r="G54" s="2">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H54" s="2">
-        <v>53.56</v>
+        <v>51.23</v>
       </c>
       <c r="I54" s="2">
-        <v>50.58</v>
+        <v>47.39</v>
       </c>
       <c r="J54" s="2">
-        <v>0.02982796949308086</v>
+        <v>0.030013098625128666</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
@@ -5400,28 +5400,28 @@
         <v>300</v>
       </c>
       <c r="M54" s="2">
-        <v>0.07629253703052008</v>
+        <v>0.04827462302801244</v>
       </c>
       <c r="N54" s="2">
-        <v>17.98963803999632</v>
+        <v>13.865637491231073</v>
       </c>
       <c r="O54" s="2">
-        <v>70.88607594936708</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>65.9493670886076</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="R54" s="2">
-        <v>55.44303797468355</v>
+        <v>54.43037974683545</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>-1.33</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5435,37 +5435,37 @@
         <v>17.72151898734177</v>
       </c>
       <c r="D55" s="1">
-        <v>12.042253521126762</v>
+        <v>10.605633802816902</v>
       </c>
       <c r="E55" s="1">
         <v>6.64</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.19892397531012102</v>
+        <v>-0.19442456830534355</v>
       </c>
       <c r="G55" s="1">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="H55" s="1">
-        <v>50.85</v>
+        <v>47.35</v>
       </c>
       <c r="I55" s="1">
-        <v>-25.28</v>
+        <v>-27.91</v>
       </c>
       <c r="J55" s="1">
-        <v>0.02100547168695652</v>
+        <v>0.0179290384271083</v>
       </c>
       <c r="K55" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="1">
         <v>-15</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.05221490278640095</v>
+        <v>-0.06940271784699537</v>
       </c>
       <c r="N55" s="1">
-        <v>5.1388940583042055</v>
+        <v>2.0979034037302804</v>
       </c>
       <c r="O55" s="1">
         <v>49.36708860759494</v>
@@ -5474,78 +5474,78 @@
         <v>48.21894075039502</v>
       </c>
       <c r="Q55" s="1">
-        <v>44.810126582278485</v>
+        <v>43.54430379746835</v>
       </c>
       <c r="R55" s="1">
-        <v>33.481012658227854</v>
+        <v>33.0379746835443</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>-1.65</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>0.54</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>35.44303797468354</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>40.407407407407405</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>-0.43</v>
       </c>
-      <c r="F56" s="1">
-        <v>-0.08513223155526206</v>
-      </c>
-      <c r="G56" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H56" s="1">
-        <v>54.83</v>
-      </c>
-      <c r="I56" s="1">
-        <v>4.04</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.030077081491101127</v>
-      </c>
-      <c r="K56" s="1" t="b">
+      <c r="F56" s="2">
+        <v>-0.07817453845352429</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1.44</v>
+      </c>
+      <c r="H56" s="2">
+        <v>52.84</v>
+      </c>
+      <c r="I56" s="2">
+        <v>2.49</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.028515566693884147</v>
+      </c>
+      <c r="K56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L56" s="1">
+      <c r="L56" s="2">
         <v>14</v>
       </c>
-      <c r="M56" s="1">
-        <v>-0.04334800203901268</v>
-      </c>
-      <c r="N56" s="1">
-        <v>6.025584133043034</v>
-      </c>
-      <c r="O56" s="1">
-        <v>51.89873417721519</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="M56" s="2">
+        <v>-0.043136567624433075</v>
+      </c>
+      <c r="N56" s="2">
+        <v>4.724518425986517</v>
+      </c>
+      <c r="O56" s="2">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
-      <c r="Q56" s="1">
-        <v>64.43037974683544</v>
-      </c>
-      <c r="R56" s="1">
-        <v>49.11392405063291</v>
-      </c>
-      <c r="S56" s="1" t="s">
+      <c r="Q56" s="2">
+        <v>63.924050632911396</v>
+      </c>
+      <c r="R56" s="2">
+        <v>50</v>
+      </c>
+      <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T56" s="1">
-        <v>-3.54</v>
+      <c r="T56" s="2">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5565,49 +5565,49 @@
         <v>-0.26</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.16197313505260122</v>
+        <v>-0.15695449131272274</v>
       </c>
       <c r="G57" s="1">
         <v>1.21</v>
       </c>
       <c r="H57" s="1">
-        <v>44.69</v>
+        <v>44.77</v>
       </c>
       <c r="I57" s="1">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0009499959979441232</v>
+        <v>0.0016737278743720902</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>-58</v>
+        <v>-56</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.14247382794501817</v>
+        <v>-0.14023182341702012</v>
       </c>
       <c r="N57" s="1">
-        <v>-3.886998457557516</v>
+        <v>-4.98500715327219</v>
       </c>
       <c r="O57" s="1">
-        <v>37.9746835443038</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>48.227848101265835</v>
+        <v>48.98734177215191</v>
       </c>
       <c r="R57" s="1">
-        <v>39.0506329113924</v>
+        <v>38.54430379746836</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>2.47</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5627,49 +5627,49 @@
         <v>0.81</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.09411200319531839</v>
+        <v>-0.09264044740411104</v>
       </c>
       <c r="G58" s="1">
         <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>49.54</v>
+        <v>51.35</v>
       </c>
       <c r="I58" s="1">
-        <v>9.26</v>
+        <v>9.61</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.006743493601277909</v>
+        <v>-0.005762453981182471</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.16282384728870625</v>
+        <v>-0.1515679437984917</v>
       </c>
       <c r="N58" s="1">
-        <v>-5.922000391926318</v>
+        <v>-6.118619191419353</v>
       </c>
       <c r="O58" s="1">
-        <v>34.177215189873415</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>46.58227848101266</v>
+        <v>48.22784810126582</v>
       </c>
       <c r="R58" s="1">
-        <v>37.21518987341772</v>
+        <v>37.088607594936704</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5689,31 +5689,31 @@
         <v>0.11</v>
       </c>
       <c r="F59" s="2">
-        <v>0.5120440504377429</v>
+        <v>0.49388011606644744</v>
       </c>
       <c r="G59" s="2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H59" s="2">
-        <v>59.62</v>
+        <v>61.29</v>
       </c>
       <c r="I59" s="2">
-        <v>119.86</v>
+        <v>123.27</v>
       </c>
       <c r="J59" s="2">
-        <v>0.07848699843097959</v>
+        <v>0.07537002172374156</v>
       </c>
       <c r="K59" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2">
         <v>369</v>
       </c>
       <c r="M59" s="2">
-        <v>0.6011837400724083</v>
+        <v>0.5695302803565307</v>
       </c>
       <c r="N59" s="2">
-        <v>70.47875834418512</v>
+        <v>65.9912032240829</v>
       </c>
       <c r="O59" s="2">
         <v>92.40506329113924</v>
@@ -5722,7 +5722,7 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>79.11392405063292</v>
+        <v>79.62025316455697</v>
       </c>
       <c r="R59" s="2">
         <v>66.77215189873418</v>
@@ -5751,49 +5751,49 @@
         <v>-2.31</v>
       </c>
       <c r="F60" s="2">
-        <v>0.10891482034506436</v>
+        <v>0.12810677799114745</v>
       </c>
       <c r="G60" s="2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H60" s="2">
-        <v>46.28</v>
+        <v>46.21</v>
       </c>
       <c r="I60" s="2">
-        <v>37.99</v>
+        <v>37.59</v>
       </c>
       <c r="J60" s="2">
-        <v>0.023569189817422096</v>
+        <v>0.023283659555353383</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M60" s="2">
-        <v>0.13212828118742515</v>
+        <v>0.14721839844337903</v>
       </c>
       <c r="N60" s="2">
-        <v>23.573212455686832</v>
+        <v>23.760015032767715</v>
       </c>
       <c r="O60" s="2">
-        <v>73.41772151898735</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P60" s="2">
-        <v>11.942274303251052</v>
+        <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>58.86075949367089</v>
+        <v>58.60759493670886</v>
       </c>
       <c r="R60" s="2">
-        <v>55.00000000000001</v>
+        <v>55.63291139240508</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-1.58</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5813,49 +5813,49 @@
         <v>0.62</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.12638494034057418</v>
+        <v>-0.12709140254575158</v>
       </c>
       <c r="G61" s="1">
         <v>0.39</v>
       </c>
       <c r="H61" s="1">
-        <v>38.55</v>
+        <v>42.34</v>
       </c>
       <c r="I61" s="1">
-        <v>-0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.008735830250640496</v>
+        <v>-0.00820564370970525</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.18302578479593445</v>
+        <v>-0.1756667711951735</v>
       </c>
       <c r="N61" s="1">
-        <v>-7.942194142649135</v>
+        <v>-8.528501931087524</v>
       </c>
       <c r="O61" s="1">
-        <v>30.37974683544304</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P61" s="1">
         <v>12.798408482128673</v>
       </c>
       <c r="Q61" s="1">
-        <v>37.34177215189873</v>
+        <v>38.607594936708864</v>
       </c>
       <c r="R61" s="1">
-        <v>31.89873417721519</v>
+        <v>31.202531645569614</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T61" s="1">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5875,49 +5875,49 @@
         <v>-0.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.16038838312440135</v>
+        <v>-0.14652867633789168</v>
       </c>
       <c r="G62" s="1">
         <v>0.96</v>
       </c>
       <c r="H62" s="1">
-        <v>43.76</v>
+        <v>41.43</v>
       </c>
       <c r="I62" s="1">
-        <v>8.57</v>
+        <v>7.28</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.005955899128925325</v>
+        <v>-0.005954810300976654</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.16410253685917908</v>
+        <v>-0.14971394641326363</v>
       </c>
       <c r="N62" s="1">
-        <v>-6.0498693489736</v>
+        <v>-5.933219452896544</v>
       </c>
       <c r="O62" s="1">
-        <v>32.91139240506329</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P62" s="1">
         <v>16.149676494964734</v>
       </c>
       <c r="Q62" s="1">
-        <v>53.03797468354429</v>
+        <v>52.53164556962025</v>
       </c>
       <c r="R62" s="1">
-        <v>42.0253164556962</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-0.82</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5931,25 +5931,25 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D63" s="4">
-        <v>4.924921793534932</v>
+        <v>4.982273201251304</v>
       </c>
       <c r="E63" s="4">
         <v>-8.13</v>
       </c>
       <c r="F63" s="4">
-        <v>0.803418982178189</v>
+        <v>0.9157428358648717</v>
       </c>
       <c r="G63" s="4">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="H63" s="4">
-        <v>59.54</v>
+        <v>62.05</v>
       </c>
       <c r="I63" s="4">
-        <v>211.16</v>
+        <v>217.92</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09688950559761088</v>
+        <v>0.09415981916637181</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
@@ -5958,10 +5958,10 @@
         <v>479</v>
       </c>
       <c r="M63" s="4">
-        <v>1.1534779716809893</v>
+        <v>1.213565587912147</v>
       </c>
       <c r="N63" s="4">
-        <v>125.70818150504324</v>
+        <v>130.3947339796445</v>
       </c>
       <c r="O63" s="4">
         <v>98.73417721518987</v>
@@ -5970,7 +5970,7 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>81.89873417721519</v>
+        <v>82.78481012658227</v>
       </c>
       <c r="R63" s="4">
         <v>72.02531645569621</v>
@@ -5999,31 +5999,31 @@
         <v>-5.36</v>
       </c>
       <c r="F64" s="2">
-        <v>0.582807567756483</v>
+        <v>0.5582182125183286</v>
       </c>
       <c r="G64" s="2">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="H64" s="2">
-        <v>60.53</v>
+        <v>59.04</v>
       </c>
       <c r="I64" s="2">
-        <v>117.34</v>
+        <v>113.33</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0846049925147908</v>
+        <v>0.0804520211397876</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M64" s="2">
-        <v>0.6775184879933149</v>
+        <v>0.6386462819214698</v>
       </c>
       <c r="N64" s="2">
-        <v>78.1122331362758</v>
+        <v>72.9028033805768</v>
       </c>
       <c r="O64" s="2">
         <v>94.9367088607595</v>
@@ -6032,7 +6032,7 @@
         <v>20.9978319173529</v>
       </c>
       <c r="Q64" s="2">
-        <v>76.58227848101265</v>
+        <v>76.07594936708861</v>
       </c>
       <c r="R64" s="2">
         <v>67.40506329113924</v>
@@ -6061,19 +6061,19 @@
         <v>-0.88</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.12395774130970882</v>
+        <v>-0.11118478334606827</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>48.94</v>
+        <v>47.41</v>
       </c>
       <c r="I65" s="1">
-        <v>0.47</v>
+        <v>-0.02</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.0058368555469811645</v>
+        <v>-0.005345493843639389</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>0</v>
@@ -6082,28 +6082,28 @@
         <v>57</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.18895543166831896</v>
+        <v>-0.166927009665077</v>
       </c>
       <c r="N65" s="1">
-        <v>-8.535158829887585</v>
+        <v>-7.654525778077878</v>
       </c>
       <c r="O65" s="1">
-        <v>29.11392405063291</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>48.22784810126583</v>
+        <v>48.98734177215189</v>
       </c>
       <c r="R65" s="1">
-        <v>36.64556962025316</v>
+        <v>37.151898734177216</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6123,49 +6123,49 @@
         <v>-0.2</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.04404825164755059</v>
+        <v>-0.067538364875655</v>
       </c>
       <c r="G66" s="1">
         <v>1.04</v>
       </c>
       <c r="H66" s="1">
-        <v>52.39</v>
+        <v>51.05</v>
       </c>
       <c r="I66" s="1">
-        <v>-28.96</v>
+        <v>-29.34</v>
       </c>
       <c r="J66" s="1">
-        <v>-0.014723341169018873</v>
+        <v>-0.0167961655692444</v>
       </c>
       <c r="K66" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L66" s="1">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="M66" s="1">
-        <v>-0.04033409791277287</v>
+        <v>-0.06435309480028306</v>
       </c>
       <c r="N66" s="1">
-        <v>6.326974545667026</v>
+        <v>2.6028657084015188</v>
       </c>
       <c r="O66" s="1">
-        <v>53.16455696202531</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P66" s="1">
         <v>48.12800106814908</v>
       </c>
       <c r="Q66" s="1">
-        <v>39.11392405063291</v>
+        <v>38.607594936708864</v>
       </c>
       <c r="R66" s="1">
-        <v>33.924050632911396</v>
+        <v>32.72151898734177</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="1">
-        <v>4.87</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6185,49 +6185,49 @@
         <v>-1.48</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.05302032012287701</v>
+        <v>-0.0841871748879574</v>
       </c>
       <c r="G67" s="1">
         <v>1.15</v>
       </c>
       <c r="H67" s="1">
-        <v>50.15</v>
+        <v>46.91</v>
       </c>
       <c r="I67" s="1">
-        <v>-11.04</v>
+        <v>-12.15</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.0009719116505956617</v>
+        <v>-0.0010148770194261503</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-71</v>
+        <v>-73</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.039092243617460554</v>
+        <v>-0.07224241210531268</v>
       </c>
       <c r="N67" s="1">
-        <v>6.451159975198248</v>
+        <v>1.813933977898554</v>
       </c>
       <c r="O67" s="1">
-        <v>55.69620253164557</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>50.25316455696203</v>
+        <v>49.74683544303797</v>
       </c>
       <c r="R67" s="1">
-        <v>44.936708860759495</v>
+        <v>42.784810126582286</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>0.82</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6247,49 +6247,49 @@
         <v>-0.18</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.20626589337855733</v>
+        <v>-0.18263542255890908</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>39.87</v>
+        <v>42.2</v>
       </c>
       <c r="I68" s="1">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.010946538905365932</v>
+        <v>-0.011120849696270613</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2684779684360842</v>
+        <v>-0.23598869632138886</v>
       </c>
       <c r="N68" s="1">
-        <v>-16.48741250666411</v>
+        <v>-14.560694443709066</v>
       </c>
       <c r="O68" s="1">
-        <v>12.658227848101266</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P68" s="1">
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>60</v>
+        <v>60.37974683544303</v>
       </c>
       <c r="R68" s="1">
-        <v>43.734177215189874</v>
+        <v>44.87341772151899</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>-1.2</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6309,31 +6309,31 @@
         <v>0.19</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.25740260569165335</v>
+        <v>-0.24837803768197456</v>
       </c>
       <c r="G69" s="3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H69" s="3">
-        <v>44.83</v>
+        <v>45.71</v>
       </c>
       <c r="I69" s="3">
-        <v>-11.43</v>
+        <v>-11.06</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.014024373117659573</v>
+        <v>-0.013532139114412724</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.21190422244062623</v>
+        <v>-0.20856216173982545</v>
       </c>
       <c r="N69" s="3">
-        <v>-10.830037907118312</v>
+        <v>-11.818040985552722</v>
       </c>
       <c r="O69" s="3">
         <v>22.78481012658228</v>
@@ -6342,16 +6342,16 @@
         <v>29.145649851223904</v>
       </c>
       <c r="Q69" s="3">
-        <v>40.12658227848101</v>
+        <v>41.0126582278481</v>
       </c>
       <c r="R69" s="3">
-        <v>28.164556962025312</v>
+        <v>28.29113924050633</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6371,49 +6371,49 @@
         <v>1.82</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.21033504627324695</v>
+        <v>-0.20805750853954208</v>
       </c>
       <c r="G70" s="3">
         <v>0.87</v>
       </c>
       <c r="H70" s="3">
-        <v>35.41</v>
+        <v>38.93</v>
       </c>
       <c r="I70" s="3">
-        <v>-16.11</v>
+        <v>-14.99</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.012926741798049627</v>
+        <v>-0.013480278978388126</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.22240604591127455</v>
+        <v>-0.21840963628450083</v>
       </c>
       <c r="N70" s="3">
-        <v>-11.880220254183154</v>
+        <v>-12.802788440020265</v>
       </c>
       <c r="O70" s="3">
-        <v>18.9873417721519</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>37.84810126582279</v>
+        <v>39.11392405063292</v>
       </c>
       <c r="R70" s="3">
-        <v>27.025316455696203</v>
+        <v>27.531645569620256</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>-0.7</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6433,31 +6433,31 @@
         <v>-1.56</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.45800455981527743</v>
+        <v>-0.452798032071784</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>36.17</v>
+        <v>35.45</v>
       </c>
       <c r="I71" s="3">
-        <v>-31.6</v>
+        <v>-31.66</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.03386514245475491</v>
+        <v>-0.03225248689308389</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-98</v>
+        <v>-97</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.4468620986109443</v>
+        <v>-0.4432422218456682</v>
       </c>
       <c r="N71" s="3">
-        <v>-34.32582552415012</v>
+        <v>-35.286046996137</v>
       </c>
       <c r="O71" s="3">
         <v>1.2658227848101267</v>
@@ -6466,7 +6466,7 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>36.962025316455694</v>
+        <v>36.70886075949367</v>
       </c>
       <c r="R71" s="3">
         <v>22.27848101265823</v>
@@ -6495,19 +6495,19 @@
         <v>-1.49</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.293697481647043</v>
+        <v>-0.2847139277015262</v>
       </c>
       <c r="G72" s="3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="H72" s="3">
-        <v>36.7</v>
+        <v>34.55</v>
       </c>
       <c r="I72" s="3">
-        <v>-11.1</v>
+        <v>-12.14</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.011535808425502841</v>
+        <v>-0.010941501290329845</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>1</v>
@@ -6516,28 +6516,28 @@
         <v>3</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.28069794357532096</v>
+        <v>-0.2727691649188815</v>
       </c>
       <c r="N72" s="3">
-        <v>-17.709410020587796</v>
+        <v>-18.238741303458326</v>
       </c>
       <c r="O72" s="3">
-        <v>10.126582278481013</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P72" s="3">
-        <v>19.4578633420253</v>
+        <v>19.739671794345924</v>
       </c>
       <c r="Q72" s="3">
-        <v>38.60759493670885</v>
+        <v>38.35443037974683</v>
       </c>
       <c r="R72" s="3">
-        <v>27.21518987341772</v>
+        <v>28.10126582278481</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T72" s="3">
-        <v>-0.25</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6557,19 +6557,19 @@
         <v>-1.26</v>
       </c>
       <c r="F73" s="2">
-        <v>0.2824056985654553</v>
+        <v>0.31362469015228267</v>
       </c>
       <c r="G73" s="2">
         <v>1.17</v>
       </c>
       <c r="H73" s="2">
-        <v>63.48</v>
+        <v>64.55</v>
       </c>
       <c r="I73" s="2">
-        <v>42.55</v>
+        <v>42.98</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03052633467924307</v>
+        <v>0.030617865994081703</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
@@ -6578,10 +6578,10 @@
         <v>26</v>
       </c>
       <c r="M73" s="2">
-        <v>0.29819085193826056</v>
+        <v>0.32716208797261337</v>
       </c>
       <c r="N73" s="2">
-        <v>40.179469530770355</v>
+        <v>41.754383985691156</v>
       </c>
       <c r="O73" s="2">
         <v>87.34177215189874</v>
@@ -6590,7 +6590,7 @@
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.72151898734177</v>
+        <v>68.22784810126582</v>
       </c>
       <c r="R73" s="2">
         <v>62.151898734177216</v>
@@ -6619,34 +6619,34 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="2">
-        <v>0.1627766418008498</v>
+        <v>0.20378191439857105</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
       </c>
       <c r="H74" s="2">
-        <v>82.84</v>
+        <v>80.13</v>
       </c>
       <c r="I74" s="2">
-        <v>31.56</v>
+        <v>31.09</v>
       </c>
       <c r="J74" s="2">
-        <v>0.02106929882863832</v>
+        <v>0.019894183659761838</v>
       </c>
       <c r="K74" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2">
         <v>12</v>
       </c>
       <c r="M74" s="2">
-        <v>0.14327733469326676</v>
+        <v>0.18705924650286843</v>
       </c>
       <c r="N74" s="2">
-        <v>24.68811780627098</v>
+        <v>27.744099838716657</v>
       </c>
       <c r="O74" s="2">
-        <v>74.68354430379746</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
@@ -6655,13 +6655,13 @@
         <v>65.0632911392405</v>
       </c>
       <c r="R74" s="2">
-        <v>57.27848101265823</v>
+        <v>58.670886075949376</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>0.95</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6681,19 +6681,19 @@
         <v>-2.27</v>
       </c>
       <c r="F75" s="1">
-        <v>0.05665305738230157</v>
+        <v>0.047742627284892966</v>
       </c>
       <c r="G75" s="1">
         <v>0.96</v>
       </c>
       <c r="H75" s="1">
-        <v>59.82</v>
+        <v>61.96</v>
       </c>
       <c r="I75" s="1">
-        <v>14.82</v>
+        <v>16.2</v>
       </c>
       <c r="J75" s="1">
-        <v>0.005244941446567493</v>
+        <v>0.006054596459029677</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6702,28 +6702,28 @@
         <v>20</v>
       </c>
       <c r="M75" s="1">
-        <v>0.05293890364752385</v>
+        <v>0.04455735720952103</v>
       </c>
       <c r="N75" s="1">
-        <v>15.654274701696687</v>
+        <v>13.493910909381924</v>
       </c>
       <c r="O75" s="1">
-        <v>67.08860759493672</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>59.74683544303797</v>
+        <v>60.379746835443036</v>
       </c>
       <c r="R75" s="1">
-        <v>46.455696202531655</v>
+        <v>45.69620253164557</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6743,19 +6743,19 @@
         <v>3.5</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.03383881081005641</v>
+        <v>-0.019951222580168418</v>
       </c>
       <c r="G76" s="1">
         <v>0.71</v>
       </c>
       <c r="H76" s="1">
-        <v>50.56</v>
+        <v>53.36</v>
       </c>
       <c r="I76" s="1">
-        <v>13.34</v>
+        <v>14.87</v>
       </c>
       <c r="J76" s="1">
-        <v>0.016908958766601135</v>
+        <v>0.015723621144014217</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6764,28 +6764,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.0607664253871949</v>
+        <v>-0.043044430626614893</v>
       </c>
       <c r="N76" s="1">
-        <v>4.283741798224821</v>
+        <v>4.7337321257683325</v>
       </c>
       <c r="O76" s="1">
-        <v>48.10126582278481</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>48.607594936708864</v>
+        <v>50.12658227848101</v>
       </c>
       <c r="R76" s="1">
-        <v>38.98734177215191</v>
+        <v>41.39240506329114</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>-3.23</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6805,19 +6805,19 @@
         <v>-0.19</v>
       </c>
       <c r="F77" s="2">
-        <v>0.011743538489930455</v>
+        <v>0.021243186683114132</v>
       </c>
       <c r="G77" s="2">
         <v>0.98</v>
       </c>
       <c r="H77" s="2">
-        <v>64.16</v>
+        <v>60.18</v>
       </c>
       <c r="I77" s="2">
-        <v>11.8</v>
+        <v>10.52</v>
       </c>
       <c r="J77" s="2">
-        <v>0.0077817686474400335</v>
+        <v>0.008170585819772246</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6826,10 +6826,10 @@
         <v>8</v>
       </c>
       <c r="M77" s="2">
-        <v>0.009886461622541587</v>
+        <v>0.01965055164542817</v>
       </c>
       <c r="N77" s="2">
-        <v>11.349030499198465</v>
+        <v>11.003230352972645</v>
       </c>
       <c r="O77" s="2">
         <v>63.29113924050633</v>
@@ -6841,13 +6841,13 @@
         <v>63.67088607594937</v>
       </c>
       <c r="R77" s="2">
-        <v>55.44303797468354</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6867,19 +6867,19 @@
         <v>0.93</v>
       </c>
       <c r="F78" s="2">
-        <v>0.1704180033472582</v>
+        <v>0.1552823245490744</v>
       </c>
       <c r="G78" s="2">
         <v>1.26</v>
       </c>
       <c r="H78" s="2">
-        <v>69.65</v>
+        <v>62.3</v>
       </c>
       <c r="I78" s="2">
-        <v>34.51</v>
+        <v>31.26</v>
       </c>
       <c r="J78" s="2">
-        <v>0.028051727554599237</v>
+        <v>0.028006030363875126</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
@@ -6888,28 +6888,28 @@
         <v>61</v>
       </c>
       <c r="M78" s="2">
-        <v>0.1945600026233134</v>
+        <v>0.17598658003899192</v>
       </c>
       <c r="N78" s="2">
-        <v>29.816384599275647</v>
+        <v>26.636833192329018</v>
       </c>
       <c r="O78" s="2">
-        <v>79.74683544303798</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P78" s="2">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="2">
-        <v>61.0126582278481</v>
+        <v>60.63291139240506</v>
       </c>
       <c r="R78" s="2">
-        <v>51.51898734177215</v>
+        <v>50.88607594936709</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6923,55 +6923,55 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="2">
-        <v>2.7622149837133554</v>
+        <v>2.775244299674267</v>
       </c>
       <c r="E79" s="2">
         <v>0.99</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4479484078597269</v>
+        <v>0.38942481400400625</v>
       </c>
       <c r="G79" s="2">
         <v>0.95</v>
       </c>
       <c r="H79" s="2">
-        <v>88.71</v>
+        <v>79.38</v>
       </c>
       <c r="I79" s="2">
-        <v>54.58</v>
+        <v>49.56</v>
       </c>
       <c r="J79" s="2">
-        <v>0.03728981357789821</v>
+        <v>0.04170852902060031</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L79" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M79" s="2">
-        <v>0.44330571569125476</v>
+        <v>0.38544322640979134</v>
       </c>
       <c r="N79" s="2">
-        <v>54.690955906069796</v>
+        <v>47.582497829408965</v>
       </c>
       <c r="O79" s="2">
-        <v>91.13924050632912</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>66.0759493670886</v>
+        <v>66.32911392405063</v>
       </c>
       <c r="R79" s="2">
-        <v>59.74683544303798</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6991,31 +6991,31 @@
         <v>4.67</v>
       </c>
       <c r="F80" s="2">
-        <v>0.9467881480859501</v>
+        <v>0.9241755093420445</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
       </c>
       <c r="H80" s="2">
-        <v>60.51</v>
+        <v>58.78</v>
       </c>
       <c r="I80" s="2">
-        <v>61.14</v>
+        <v>58.68</v>
       </c>
       <c r="J80" s="2">
-        <v>0.051604147781813624</v>
+        <v>0.05149076759945039</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M80" s="2">
-        <v>0.9467881480859501</v>
+        <v>0.9241755093420445</v>
       </c>
       <c r="N80" s="2">
-        <v>105.03919914553934</v>
+        <v>101.45572612263425</v>
       </c>
       <c r="O80" s="2">
         <v>96.20253164556962</v>
@@ -7024,7 +7024,7 @@
         <v>14.059118714058641</v>
       </c>
       <c r="Q80" s="2">
-        <v>69.49367088607596</v>
+        <v>69.11392405063292</v>
       </c>
       <c r="R80" s="2">
         <v>65.31645569620254</v>
@@ -7060,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38.48101265822785</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19.430379746835445</v>
+        <v>21.835443037974684</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>42.151898734177216</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42.911392405063296</v>
+        <v>43.67088607594937</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.74683544303797</v>
+        <v>54.87341772151898</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.12658227848101</v>
+        <v>55.18987341772152</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.544303797468345</v>
+        <v>38.67088607594936</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.21518987341773</v>
+        <v>35.9493670886076</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50.12658227848102</v>
+        <v>51.26582278481013</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>26.0126582278481</v>
+        <v>26.645569620253163</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>10.569620253164558</v>
+        <v>8.670886075949369</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>39.55696202531645</v>
+        <v>40.31645569620253</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7172,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>31.582278481012654</v>
+        <v>28.924050632911392</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>17.215189873417724</v>
+        <v>16.582278481012658</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>29.430379746835445</v>
+        <v>30.189873417721518</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>41.0126582278481</v>
+        <v>41.64556962025317</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39.050632911392405</v>
+        <v>39.81012658227848</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7212,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>44.55696202531646</v>
+        <v>41.13924050632911</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>28.417721518987342</v>
+        <v>28.79746835443038</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34.810126582278485</v>
+        <v>32.91139240506329</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>26.962025316455694</v>
+        <v>29.49367088607595</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7244,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>7.784810126582279</v>
+        <v>6.7721518987341796</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>23.67088607594937</v>
+        <v>23.164556962025316</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>18.35443037974684</v>
+        <v>18.734177215189877</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7284,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>44.683544303797476</v>
+        <v>44.9367088607595</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>59.81012658227849</v>
+        <v>59.620253164556964</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>16.13924050632911</v>
+        <v>15.379746835443036</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>43.79746835443038</v>
+        <v>42.59493670886076</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7316,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>52.46835443037974</v>
+        <v>52.21518987341772</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>25.632911392405067</v>
+        <v>28.29113924050633</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>55.189873417721515</v>
+        <v>55.56962025316456</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7356,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>55.12658227848102</v>
+        <v>54.11392405063292</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7364,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>32.974683544303794</v>
+        <v>33.60759493670885</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7372,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>26.51898734177216</v>
+        <v>32.08860759493672</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>37.848101265822784</v>
+        <v>39.11392405063291</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>48.60759493670886</v>
+        <v>47.34177215189873</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7396,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>29.55696202531646</v>
+        <v>26.89873417721519</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7404,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>56.32911392405063</v>
+        <v>54.68354430379747</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>27.721518987341764</v>
+        <v>25.0632911392405</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.25316455696202</v>
+        <v>25.632911392405056</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>32.594936708860764</v>
+        <v>33.86075949367089</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.62025316455696</v>
+        <v>55.75949367088608</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>61.77215189873418</v>
+        <v>61.13924050632911</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>37.278481012658226</v>
+        <v>36.01265822784811</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>55.44303797468355</v>
+        <v>54.43037974683545</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>33.481012658227854</v>
+        <v>33.0379746835443</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7492,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>49.11392405063291</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>39.0506329113924</v>
+        <v>38.54430379746836</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>37.21518987341772</v>
+        <v>37.088607594936704</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7524,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>55.00000000000001</v>
+        <v>55.63291139240508</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7532,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>31.89873417721519</v>
+        <v>31.202531645569614</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>42.0253164556962</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>36.64556962025316</v>
+        <v>37.151898734177216</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>33.924050632911396</v>
+        <v>32.72151898734177</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>44.936708860759495</v>
+        <v>42.784810126582286</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>43.734177215189874</v>
+        <v>44.87341772151899</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>28.164556962025312</v>
+        <v>28.29113924050633</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7604,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>27.025316455696203</v>
+        <v>27.531645569620256</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>27.21518987341772</v>
+        <v>28.10126582278481</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7636,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>57.27848101265823</v>
+        <v>58.670886075949376</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7644,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>46.455696202531655</v>
+        <v>45.69620253164557</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>38.98734177215191</v>
+        <v>41.39240506329114</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7660,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>55.44303797468354</v>
+        <v>55.822784810126585</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>51.51898734177215</v>
+        <v>50.88607594936709</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7676,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>59.74683544303798</v>
+        <v>59.620253164556964</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="226">
   <si>
     <t>Ticker</t>
   </si>
@@ -409,9 +409,6 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -679,31 +676,28 @@
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+    <t>Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Earnings Upcoming, Volume Spike</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1358,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" t="s">
         <v>212</v>
-      </c>
-      <c r="C1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1372,7 +1366,7 @@
         <v>72.02531645569621</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,7 +1377,7 @@
         <v>67.40506329113924</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1394,7 +1388,7 @@
         <v>66.77215189873418</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1402,10 +1396,10 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>65.69620253164557</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1416,15 +1410,15 @@
         <v>65.31645569620254</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B7">
-        <v>62.21518987341772</v>
+        <v>62.65822784810127</v>
       </c>
       <c r="C7" t="s">
         <v>215</v>
@@ -1432,13 +1426,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B8">
-        <v>62.151898734177216</v>
+        <v>62.21518987341772</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1449,7 +1443,7 @@
         <v>61.962025316455694</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1457,10 +1451,10 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>61.13924050632911</v>
+        <v>60.12658227848101</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1468,10 +1462,10 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>59.620253164556964</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1479,10 +1473,10 @@
         <v>126</v>
       </c>
       <c r="B12">
-        <v>59.620253164556964</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1490,161 +1484,161 @@
         <v>120</v>
       </c>
       <c r="B13">
-        <v>58.670886075949376</v>
+        <v>58.29113924050633</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="B14">
-        <v>55.822784810126585</v>
+        <v>56.708860759493675</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15">
-        <v>55.75949367088608</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>55.63291139240508</v>
+        <v>55.31645569620253</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>55.56962025316456</v>
+        <v>55.25316455696202</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B18">
-        <v>55.18987341772152</v>
+        <v>54.873417721519</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="B19">
-        <v>54.87341772151898</v>
+        <v>54.74683544303799</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>54.68354430379747</v>
+        <v>54.62025316455696</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>54.43037974683545</v>
+        <v>52.784810126582286</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B22">
-        <v>54.11392405063292</v>
+        <v>52.21518987341772</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="B23">
-        <v>52.21518987341772</v>
+        <v>51.0126582278481</v>
       </c>
       <c r="C23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="B24">
-        <v>51.26582278481013</v>
+        <v>49.493670886075954</v>
       </c>
       <c r="C24" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="B25">
-        <v>50.88607594936709</v>
+        <v>49.49367088607595</v>
       </c>
       <c r="C25" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>50</v>
+        <v>47.34177215189874</v>
       </c>
       <c r="C26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B27">
-        <v>47.34177215189873</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="C27" t="s">
         <v>221</v>
@@ -1652,10 +1646,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>45.69620253164557</v>
+        <v>45.82278481012658</v>
       </c>
       <c r="C28" t="s">
         <v>221</v>
@@ -1663,21 +1657,21 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B29">
-        <v>44.9367088607595</v>
+        <v>45.75949367088607</v>
       </c>
       <c r="C29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="B30">
-        <v>44.87341772151899</v>
+        <v>45.37974683544304</v>
       </c>
       <c r="C30" t="s">
         <v>221</v>
@@ -1685,18 +1679,18 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>43.67088607594937</v>
+        <v>45.12658227848101</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>42.59493670886076</v>
@@ -1707,68 +1701,68 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B33">
         <v>42.27848101265823</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>41.64556962025317</v>
+        <v>41.9620253164557</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>41.39240506329114</v>
+        <v>40.8860759493671</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B36">
-        <v>41.13924050632911</v>
+        <v>40.18987341772152</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B37">
-        <v>40.31645569620253</v>
+        <v>39.936708860759495</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>39.81012658227848</v>
+        <v>38.54430379746835</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1776,7 +1770,7 @@
         <v>41</v>
       </c>
       <c r="B39">
-        <v>39.11392405063291</v>
+        <v>38.101265822784804</v>
       </c>
       <c r="C39" t="s">
         <v>221</v>
@@ -1784,21 +1778,21 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="B40">
-        <v>38.734177215189874</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B41">
-        <v>37.151898734177216</v>
+        <v>36.075949367088604</v>
       </c>
       <c r="C41" t="s">
         <v>221</v>
@@ -1809,7 +1803,7 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>37.088607594936704</v>
+        <v>35.949367088607595</v>
       </c>
       <c r="C42" t="s">
         <v>221</v>
@@ -1817,46 +1811,46 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B43">
-        <v>36.01265822784811</v>
+        <v>35.50632911392405</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>33.86075949367089</v>
+        <v>33.544303797468345</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B45">
-        <v>33.60759493670885</v>
+        <v>32.78481012658228</v>
       </c>
       <c r="C45" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B46">
-        <v>32.91139240506329</v>
+        <v>31.835443037974677</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1864,7 +1858,7 @@
         <v>65</v>
       </c>
       <c r="B47">
-        <v>32.72151898734177</v>
+        <v>31.20253164556962</v>
       </c>
       <c r="C47" t="s">
         <v>224</v>
@@ -1872,13 +1866,13 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B48">
-        <v>32.278481012658226</v>
+        <v>30.506329113924053</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1886,10 +1880,10 @@
         <v>40</v>
       </c>
       <c r="B49">
-        <v>32.08860759493672</v>
+        <v>30.44303797468355</v>
       </c>
       <c r="C49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1897,18 +1891,18 @@
         <v>60</v>
       </c>
       <c r="B50">
-        <v>31.202531645569614</v>
+        <v>30.063291139240505</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B51">
-        <v>30.189873417721518</v>
+        <v>29.746835443037973</v>
       </c>
       <c r="C51" t="s">
         <v>220</v>
@@ -2155,19 +2149,19 @@
         <v>0.4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.05289625432642264</v>
+        <v>0.006404755019511793</v>
       </c>
       <c r="G2" s="1">
         <v>0.19</v>
       </c>
       <c r="H2" s="1">
-        <v>64.9</v>
+        <v>53.8</v>
       </c>
       <c r="I2" s="1">
-        <v>24.68</v>
+        <v>19.64</v>
       </c>
       <c r="J2" s="1">
-        <v>0.004038391202591925</v>
+        <v>0.005125373750331907</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -2176,28 +2170,28 @@
         <v>296</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.011605464699858903</v>
+        <v>-0.0704078833155315</v>
       </c>
       <c r="N2" s="1">
-        <v>7.877628718443935</v>
+        <v>3.517253438205291</v>
       </c>
       <c r="O2" s="1">
-        <v>60.75949367088608</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>48.10126582278481</v>
+        <v>44.68354430379747</v>
       </c>
       <c r="R2" s="1">
-        <v>38.734177215189874</v>
+        <v>36.075949367088604</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>5.89</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2211,37 +2205,37 @@
         <v>49.36708860759494</v>
       </c>
       <c r="D3" s="2">
-        <v>24.085245901639347</v>
+        <v>23.93770491803279</v>
       </c>
       <c r="E3" s="2">
         <v>1.88</v>
       </c>
       <c r="F3" s="2">
-        <v>0.8663460622859935</v>
+        <v>0.962473230590845</v>
       </c>
       <c r="G3" s="2">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="H3" s="2">
-        <v>63.81</v>
+        <v>69.59</v>
       </c>
       <c r="I3" s="2">
-        <v>82.7</v>
+        <v>96.33</v>
       </c>
       <c r="J3" s="2">
-        <v>0.08816515348208924</v>
+        <v>0.08574510564501076</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M3" s="2">
-        <v>0.978626832442854</v>
+        <v>1.095235815367463</v>
       </c>
       <c r="N3" s="2">
-        <v>106.90085843271524</v>
+        <v>120.08162330650471</v>
       </c>
       <c r="O3" s="2">
         <v>97.46835443037975</v>
@@ -2253,13 +2247,13 @@
         <v>75.82278481012658</v>
       </c>
       <c r="R3" s="2">
-        <v>65.69620253164557</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2273,55 +2267,55 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D4" s="3">
-        <v>9.863291139240506</v>
+        <v>9.868354430379748</v>
       </c>
       <c r="E4" s="3">
         <v>1.25</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.1362266529933853</v>
+        <v>-0.18331120464487982</v>
       </c>
       <c r="G4" s="3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H4" s="3">
-        <v>66.43</v>
+        <v>63.4</v>
       </c>
       <c r="I4" s="3">
-        <v>-16.61</v>
+        <v>-17.79</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.01036475455799528</v>
+        <v>-0.009728224775035507</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>-88</v>
+        <v>-93</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.1274671602861125</v>
+        <v>-0.17382816287512137</v>
       </c>
       <c r="N4" s="3">
-        <v>-3.7085408401814313</v>
+        <v>-6.8247745177537125</v>
       </c>
       <c r="O4" s="3">
-        <v>39.24050632911392</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>36.835443037974684</v>
+        <v>36.45569620253164</v>
       </c>
       <c r="R4" s="3">
-        <v>21.835443037974684</v>
+        <v>20.06329113924051</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>7.03</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2335,25 +2329,25 @@
         <v>43.037974683544306</v>
       </c>
       <c r="D5" s="1">
-        <v>23.917431192660548</v>
+        <v>25.247706422018346</v>
       </c>
       <c r="E5" s="1">
         <v>0.73</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.17081982022636585</v>
+        <v>-0.16701604053351085</v>
       </c>
       <c r="G5" s="1">
         <v>1.79</v>
       </c>
       <c r="H5" s="1">
-        <v>50.3</v>
+        <v>55.17</v>
       </c>
       <c r="I5" s="1">
-        <v>-1.05</v>
+        <v>2.03</v>
       </c>
       <c r="J5" s="1">
-        <v>0.006529709234932777</v>
+        <v>0.004706264373024448</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2362,28 +2356,28 @@
         <v>-82</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.10791073623777026</v>
+        <v>-0.09210001055241923</v>
       </c>
       <c r="N5" s="1">
-        <v>-1.7528984353472075</v>
+        <v>1.3480407145165045</v>
       </c>
       <c r="O5" s="1">
-        <v>43.037974683544306</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P5" s="1">
         <v>29.766948563835548</v>
       </c>
       <c r="Q5" s="1">
-        <v>56.835443037974684</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="R5" s="1">
-        <v>42.27848101265823</v>
+        <v>43.60759493670886</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-3.04</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2397,55 +2391,55 @@
         <v>51.89873417721519</v>
       </c>
       <c r="D6" s="1">
-        <v>1.4271844660194175</v>
+        <v>1.5210355987055018</v>
       </c>
       <c r="E6" s="1">
         <v>-0.11</v>
       </c>
       <c r="F6" s="1">
-        <v>0.012816731296728168</v>
+        <v>-0.012762916788167739</v>
       </c>
       <c r="G6" s="1">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H6" s="1">
-        <v>44.91</v>
+        <v>41.72</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.68</v>
+        <v>-13.77</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.01100991781032459</v>
+        <v>-0.010761659579127787</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M6" s="1">
-        <v>0.05502155979540624</v>
+        <v>0.038445508768527814</v>
       </c>
       <c r="N6" s="1">
-        <v>14.540331167970432</v>
+        <v>14.4025926466112</v>
       </c>
       <c r="O6" s="1">
-        <v>70.88607594936708</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>39.1139240506329</v>
+        <v>37.721518987341774</v>
       </c>
       <c r="R6" s="1">
-        <v>43.67088607594937</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>1.58</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2465,19 +2459,19 @@
         <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.01633911583033909</v>
+        <v>-0.034815574041854425</v>
       </c>
       <c r="G7" s="2">
         <v>2.25</v>
       </c>
       <c r="H7" s="2">
-        <v>59.95</v>
+        <v>61.85</v>
       </c>
       <c r="I7" s="2">
-        <v>18.33</v>
+        <v>19.73</v>
       </c>
       <c r="J7" s="2">
-        <v>0.02343295342828491</v>
+        <v>0.022580054089422926</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2486,28 +2480,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.08320057402503367</v>
+        <v>0.08372244808012597</v>
       </c>
       <c r="N7" s="2">
-        <v>17.358232590933188</v>
+        <v>18.93028657777102</v>
       </c>
       <c r="O7" s="2">
-        <v>72.15189873417721</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>63.164556962025316</v>
+        <v>63.417721518987335</v>
       </c>
       <c r="R7" s="2">
-        <v>54.87341772151898</v>
+        <v>54.367088607594944</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>0.32</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2521,55 +2515,55 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>-0.012084592145015116</v>
+        <v>-0.003776435045317274</v>
       </c>
       <c r="E8" s="2">
         <v>0.19</v>
       </c>
       <c r="F8" s="2">
-        <v>0.28807913833170645</v>
+        <v>0.2496534716100896</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>71.77</v>
+        <v>65.4</v>
       </c>
       <c r="I8" s="2">
-        <v>20.9</v>
+        <v>18.79</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03396351038451503</v>
+        <v>0.03302739540391629</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="M8" s="2">
-        <v>0.2602080251722021</v>
+        <v>0.2164628254159351</v>
       </c>
       <c r="N8" s="2">
-        <v>35.05897770565003</v>
+        <v>32.20432431135193</v>
       </c>
       <c r="O8" s="2">
-        <v>86.07594936708861</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>65.56962025316456</v>
+        <v>64.9367088607595</v>
       </c>
       <c r="R8" s="2">
-        <v>55.18987341772152</v>
+        <v>55.25316455696202</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2583,25 +2577,25 @@
         <v>37.9746835443038</v>
       </c>
       <c r="D9" s="1">
-        <v>46.0561797752809</v>
+        <v>46.831460674157306</v>
       </c>
       <c r="E9" s="1">
         <v>2.36</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.1310840982921593</v>
+        <v>-0.1371895789028914</v>
       </c>
       <c r="G9" s="1">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H9" s="1">
-        <v>45.18</v>
+        <v>47.87</v>
       </c>
       <c r="I9" s="1">
-        <v>-17.09</v>
+        <v>-15.87</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.013538607039830019</v>
+        <v>-0.01313251653666682</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
@@ -2610,28 +2604,28 @@
         <v>-14</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.0912682223500102</v>
+        <v>-0.08882606587712338</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.08864704657120212</v>
+        <v>1.6754351820460984</v>
       </c>
       <c r="O9" s="1">
-        <v>45.56962025316456</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P9" s="1">
         <v>34.04748479877408</v>
       </c>
       <c r="Q9" s="1">
-        <v>45.44303797468355</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="R9" s="1">
-        <v>38.67088607594936</v>
+        <v>39.430379746835435</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-2.53</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2645,25 +2639,25 @@
         <v>67.08860759493672</v>
       </c>
       <c r="D10" s="1">
-        <v>0.5536000000000001</v>
+        <v>0.5663999999999999</v>
       </c>
       <c r="E10" s="1">
         <v>1.48</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.1679420458536197</v>
+        <v>-0.1625740792266629</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>47.02</v>
+        <v>51.4</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.9</v>
+        <v>-4.18</v>
       </c>
       <c r="J10" s="1">
-        <v>0.001443700246548156</v>
+        <v>0.001672895700534598</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2672,28 +2666,28 @@
         <v>-131</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.13529302758105743</v>
+        <v>-0.12369360797065332</v>
       </c>
       <c r="N10" s="1">
-        <v>-4.491127569675927</v>
+        <v>-1.8113190273068986</v>
       </c>
       <c r="O10" s="1">
-        <v>36.708860759493675</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>46.32911392405064</v>
+        <v>47.72151898734178</v>
       </c>
       <c r="R10" s="1">
-        <v>35.9493670886076</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-2.85</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2707,25 +2701,25 @@
         <v>12.658227848101266</v>
       </c>
       <c r="D11" s="2">
-        <v>31.867647058823525</v>
+        <v>31.88970588235294</v>
       </c>
       <c r="E11" s="2">
         <v>5.47</v>
       </c>
       <c r="F11" s="2">
-        <v>0.2467983561729473</v>
+        <v>0.23765850895622276</v>
       </c>
       <c r="G11" s="2">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="H11" s="2">
-        <v>70.65</v>
+        <v>72.26</v>
       </c>
       <c r="I11" s="2">
-        <v>13.3</v>
+        <v>15.31</v>
       </c>
       <c r="J11" s="2">
-        <v>0.02183170715604227</v>
+        <v>0.02318709521283926</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2734,90 +2728,90 @@
         <v>24</v>
       </c>
       <c r="M11" s="2">
-        <v>0.2324646408337736</v>
+        <v>0.21964072959368175</v>
       </c>
       <c r="N11" s="2">
-        <v>32.28463927180717</v>
+        <v>32.52211472912661</v>
       </c>
       <c r="O11" s="2">
-        <v>83.54430379746836</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>58.481012658227854</v>
+        <v>60.126582278481024</v>
       </c>
       <c r="R11" s="2">
-        <v>51.26582278481013</v>
+        <v>52.784810126582286</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>4.81</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>-0.34</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>20.253164556962027</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="1">
         <v>65.70588235294117</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>5.82</v>
       </c>
-      <c r="F12" s="3">
-        <v>-0.1991037672820881</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="1">
+        <v>-0.16138872777707075</v>
+      </c>
+      <c r="G12" s="1">
         <v>0.84</v>
       </c>
-      <c r="H12" s="3">
-        <v>59.24</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-29.36</v>
-      </c>
-      <c r="J12" s="3">
-        <v>-0.006858348084406471</v>
-      </c>
-      <c r="K12" s="3" t="b">
+      <c r="H12" s="1">
+        <v>63.48</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-25.74</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.00036432772497650137</v>
+      </c>
+      <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="3">
-        <v>-50</v>
-      </c>
-      <c r="M12" s="3">
-        <v>-0.2118448475835758</v>
-      </c>
-      <c r="N12" s="3">
-        <v>-12.146309569927759</v>
-      </c>
-      <c r="O12" s="3">
-        <v>21.518987341772153</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="L12" s="1">
+        <v>-51</v>
+      </c>
+      <c r="M12" s="1">
+        <v>-0.17656159460868426</v>
+      </c>
+      <c r="N12" s="1">
+        <v>-7.098117691109997</v>
+      </c>
+      <c r="O12" s="1">
+        <v>30.37974683544304</v>
+      </c>
+      <c r="P12" s="1">
         <v>49.40073075603063</v>
       </c>
-      <c r="Q12" s="3">
-        <v>46.07594936708862</v>
-      </c>
-      <c r="R12" s="3">
-        <v>26.645569620253163</v>
-      </c>
-      <c r="S12" s="3" t="s">
+      <c r="Q12" s="1">
+        <v>50.75949367088608</v>
+      </c>
+      <c r="R12" s="1">
+        <v>31.07594936708861</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="T12" s="3">
-        <v>5.95</v>
+      <c r="T12" s="1">
+        <v>10.38</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2837,19 +2831,19 @@
         <v>1.61</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.3009153370465708</v>
+        <v>-0.3378974859954296</v>
       </c>
       <c r="G13" s="3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H13" s="3">
-        <v>38.66</v>
+        <v>39.34</v>
       </c>
       <c r="I13" s="3">
-        <v>-10.15</v>
+        <v>-9.73</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.0013989788988333187</v>
+        <v>-0.0038188457370752706</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
@@ -2858,28 +2852,28 @@
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.2682663187740085</v>
+        <v>-0.2980687105624442</v>
       </c>
       <c r="N13" s="3">
-        <v>-17.78845668897103</v>
+        <v>-19.24882928648599</v>
       </c>
       <c r="O13" s="3">
-        <v>13.924050632911392</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>23.544303797468356</v>
+        <v>22.27848101265823</v>
       </c>
       <c r="R13" s="3">
-        <v>8.670886075949369</v>
+        <v>7.278481012658229</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-7.22</v>
+        <v>-8.61</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2899,49 +2893,49 @@
         <v>-0.14</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.025923745197437856</v>
+        <v>0.0208602774213386</v>
       </c>
       <c r="G14" s="1">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="1">
-        <v>62.48</v>
+        <v>66.65</v>
       </c>
       <c r="I14" s="1">
-        <v>0.75</v>
+        <v>4.73</v>
       </c>
       <c r="J14" s="1">
-        <v>0.007950643838121526</v>
+        <v>0.008917514457697458</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.05698012843231415</v>
+        <v>-0.017071889657695127</v>
       </c>
       <c r="N14" s="1">
-        <v>3.340162345198408</v>
+        <v>8.850852803988923</v>
       </c>
       <c r="O14" s="1">
-        <v>51.89873417721519</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>56.835443037974684</v>
+        <v>57.46835443037975</v>
       </c>
       <c r="R14" s="1">
-        <v>40.31645569620253</v>
+        <v>42.59493670886076</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>5.13</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2961,31 +2955,31 @@
         <v>5.49</v>
       </c>
       <c r="F15" s="2">
-        <v>1.2513677851677776</v>
+        <v>1.4466921517094573</v>
       </c>
       <c r="G15" s="2">
         <v>2.2</v>
       </c>
       <c r="H15" s="2">
-        <v>63.31</v>
+        <v>67.94</v>
       </c>
       <c r="I15" s="2">
-        <v>142.52</v>
+        <v>157.57</v>
       </c>
       <c r="J15" s="2">
-        <v>0.10424764751513516</v>
+        <v>0.10034053155023638</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M15" s="2">
-        <v>1.3469258874289354</v>
+        <v>1.5604886529465585</v>
       </c>
       <c r="N15" s="2">
-        <v>143.73076393132337</v>
+        <v>166.6069070644143</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2994,7 +2988,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>70.12658227848101</v>
+        <v>70.63291139240506</v>
       </c>
       <c r="R15" s="2">
         <v>61.962025316455694</v>
@@ -3023,49 +3017,49 @@
         <v>8.13</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2069121929175408</v>
+        <v>-0.2526403325969223</v>
       </c>
       <c r="G16" s="3">
         <v>1.92</v>
       </c>
       <c r="H16" s="3">
-        <v>39.3</v>
+        <v>41.69</v>
       </c>
       <c r="I16" s="3">
-        <v>-9.65</v>
+        <v>-7.24</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.003276645157127991</v>
+        <v>-0.0060341985187148395</v>
       </c>
       <c r="K16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3">
         <v>16</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.13365098118398644</v>
+        <v>-0.16539634831514471</v>
       </c>
       <c r="N16" s="3">
-        <v>-4.326922929968819</v>
+        <v>-5.981593061756044</v>
       </c>
       <c r="O16" s="3">
-        <v>37.9746835443038</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="3">
-        <v>37.848101265822784</v>
+        <v>35.56962025316456</v>
       </c>
       <c r="R16" s="3">
-        <v>28.924050632911392</v>
+        <v>26.898734177215186</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="3">
-        <v>-7.72</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3085,34 +3079,34 @@
         <v>4.24</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.2585163190417348</v>
+        <v>-0.28626343485356553</v>
       </c>
       <c r="G17" s="3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H17" s="3">
-        <v>39.18</v>
+        <v>42.03</v>
       </c>
       <c r="I17" s="3">
-        <v>-14.8</v>
+        <v>-12.99</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.01652593355853355</v>
+        <v>-0.016150723998906397</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.20118145768504003</v>
+        <v>-0.21703722993432895</v>
       </c>
       <c r="N17" s="3">
-        <v>-11.07997058007418</v>
+        <v>-11.145681223674469</v>
       </c>
       <c r="O17" s="3">
-        <v>25.31645569620253</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
@@ -3121,75 +3115,75 @@
         <v>22.78481012658228</v>
       </c>
       <c r="R17" s="3">
-        <v>16.582278481012658</v>
+        <v>15.443037974683545</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-6.58</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>8.39</v>
       </c>
-      <c r="F18" s="1">
-        <v>-0.3102410382358625</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="H18" s="1">
-        <v>35.82</v>
-      </c>
-      <c r="I18" s="1">
-        <v>-11.44</v>
-      </c>
-      <c r="J18" s="1">
-        <v>-0.009763830748729873</v>
-      </c>
-      <c r="K18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="F18" s="3">
+        <v>-0.32891554685912827</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1.24</v>
+      </c>
+      <c r="H18" s="3">
+        <v>38.13</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-9.89</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-0.011080273503358553</v>
+      </c>
+      <c r="K18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>37</v>
       </c>
-      <c r="M18" s="1">
-        <v>-0.2927220528213169</v>
-      </c>
-      <c r="N18" s="1">
-        <v>-20.234030093701872</v>
-      </c>
-      <c r="O18" s="1">
-        <v>8.860759493670885</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="M18" s="3">
+        <v>-0.30615624661170804</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-20.057582891412373</v>
+      </c>
+      <c r="O18" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P18" s="3">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="1">
-        <v>47.84810126582279</v>
-      </c>
-      <c r="R18" s="1">
-        <v>30.189873417721518</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="Q18" s="3">
+        <v>46.582278481012665</v>
+      </c>
+      <c r="R18" s="3">
+        <v>29.43037974683544</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="1">
-        <v>-0.76</v>
+      <c r="T18" s="3">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,49 +3203,49 @@
         <v>-0.16</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.04506612647753924</v>
+        <v>-0.05199845931261464</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>51.01</v>
+        <v>47.99</v>
       </c>
       <c r="I19" s="1">
-        <v>13.2</v>
+        <v>11.38</v>
       </c>
       <c r="J19" s="1">
-        <v>0.003913390669480092</v>
+        <v>0.001624719483051169</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.1087715279849778</v>
+        <v>-0.12786279347068208</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.8389776100679551</v>
+        <v>-2.2282375773097804</v>
       </c>
       <c r="O19" s="1">
-        <v>41.77215189873418</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>52.65822784810127</v>
+        <v>50.379746835443036</v>
       </c>
       <c r="R19" s="1">
-        <v>41.64556962025317</v>
+        <v>40.8860759493671</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>0.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3265,25 +3259,25 @@
         <v>65.82278481012658</v>
       </c>
       <c r="D20" s="1">
-        <v>0.728171334431631</v>
+        <v>0.6392092257001646</v>
       </c>
       <c r="E20" s="1">
         <v>-3.42</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.05681047219559868</v>
+        <v>-0.052572222114560974</v>
       </c>
       <c r="G20" s="1">
         <v>1.06</v>
       </c>
       <c r="H20" s="1">
-        <v>58.42</v>
+        <v>61.66</v>
       </c>
       <c r="I20" s="1">
-        <v>-3.89</v>
+        <v>-1.58</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.006193482756174904</v>
+        <v>-0.00206880999129</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>1</v>
@@ -3292,10 +3286,10 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.05203256708254078</v>
+        <v>-0.046882397052705915</v>
       </c>
       <c r="N20" s="1">
-        <v>3.834918480175752</v>
+        <v>5.869802064487831</v>
       </c>
       <c r="O20" s="1">
         <v>53.16455696202531</v>
@@ -3304,16 +3298,16 @@
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>48.86075949367089</v>
+        <v>50</v>
       </c>
       <c r="R20" s="1">
-        <v>39.81012658227848</v>
+        <v>39.936708860759495</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>12.41</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3327,117 +3321,117 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D21" s="1">
-        <v>14</v>
+        <v>14.009803921568627</v>
       </c>
       <c r="E21" s="1">
         <v>4.96</v>
       </c>
       <c r="F21" s="1">
-        <v>-0.1002253939883951</v>
+        <v>0.06804873915608012</v>
       </c>
       <c r="G21" s="1">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="H21" s="1">
-        <v>63.59</v>
+        <v>70.56</v>
       </c>
       <c r="I21" s="1">
-        <v>27.76</v>
+        <v>44.8</v>
       </c>
       <c r="J21" s="1">
-        <v>0.016732073833929544</v>
+        <v>0.022507725535026318</v>
       </c>
       <c r="K21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M21" s="1">
-        <v>-0.07474323338541966</v>
+        <v>0.09554956028837958</v>
       </c>
       <c r="N21" s="1">
-        <v>1.5638518498878544</v>
+        <v>20.1129977985964</v>
       </c>
       <c r="O21" s="1">
-        <v>46.835443037974684</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P21" s="1">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="1">
-        <v>63.54430379746835</v>
+        <v>67.34177215189874</v>
       </c>
       <c r="R21" s="1">
-        <v>41.13924050632911</v>
+        <v>49.49367088607595</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="1">
-        <v>2.34</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="1">
         <v>8.11</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="1">
         <v>70.88607594936708</v>
       </c>
-      <c r="D22" s="3">
-        <v>0.6942046855733663</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="1">
+        <v>0.6954377311960543</v>
+      </c>
+      <c r="E22" s="1">
         <v>-0.12</v>
       </c>
-      <c r="F22" s="3">
-        <v>-0.253462646965331</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="1">
+        <v>-0.24299348474188467</v>
+      </c>
+      <c r="G22" s="1">
         <v>1.36</v>
       </c>
-      <c r="H22" s="3">
-        <v>44.72</v>
-      </c>
-      <c r="I22" s="3">
-        <v>-4.83</v>
-      </c>
-      <c r="J22" s="3">
-        <v>-0.013833642849341365</v>
-      </c>
-      <c r="K22" s="3" t="b">
+      <c r="H22" s="1">
+        <v>54.12</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-0.012993468467941877</v>
+      </c>
+      <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="1">
         <v>59</v>
       </c>
-      <c r="M22" s="3">
-        <v>-0.22479521628698362</v>
-      </c>
-      <c r="N22" s="3">
-        <v>-13.441346440268537</v>
-      </c>
-      <c r="O22" s="3">
-        <v>18.9873417721519</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="M22" s="1">
+        <v>-0.2088545343707543</v>
+      </c>
+      <c r="N22" s="1">
+        <v>-10.327411667317</v>
+      </c>
+      <c r="O22" s="1">
+        <v>22.78481012658228</v>
+      </c>
+      <c r="P22" s="1">
         <v>20.966620085005058</v>
       </c>
-      <c r="Q22" s="3">
-        <v>41.13924050632911</v>
-      </c>
-      <c r="R22" s="3">
-        <v>28.79746835443038</v>
-      </c>
-      <c r="S22" s="3" t="s">
+      <c r="Q22" s="1">
+        <v>45.189873417721515</v>
+      </c>
+      <c r="R22" s="1">
+        <v>30.506329113924053</v>
+      </c>
+      <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="T22" s="3">
-        <v>-1.46</v>
+      <c r="T22" s="1">
+        <v>0.25</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3451,55 +3445,55 @@
         <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.7731733914940022</v>
+        <v>-0.7695383496910214</v>
       </c>
       <c r="E23" s="1">
         <v>-0.36</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.17262882708177096</v>
+        <v>-0.18994217139195058</v>
       </c>
       <c r="G23" s="1">
         <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>41.46</v>
+        <v>42.66</v>
       </c>
       <c r="I23" s="1">
-        <v>-10.31</v>
+        <v>-9.83</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.006805512295149884</v>
+        <v>-0.007152481007156544</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.15351720662953938</v>
+        <v>-0.16718287114453034</v>
       </c>
       <c r="N23" s="1">
-        <v>-6.313545474524116</v>
+        <v>-6.160245344694604</v>
       </c>
       <c r="O23" s="1">
-        <v>31.645569620253166</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>43.41772151898734</v>
+        <v>43.291139240506325</v>
       </c>
       <c r="R23" s="1">
-        <v>32.91139240506329</v>
+        <v>33.544303797468345</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>0.95</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3519,49 +3513,49 @@
         <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>0.01990081906122826</v>
+        <v>-0.06841393094452197</v>
       </c>
       <c r="G24" s="3">
         <v>3.57</v>
       </c>
       <c r="H24" s="3">
-        <v>47.38</v>
+        <v>48.09</v>
       </c>
       <c r="I24" s="3">
-        <v>-23.72</v>
+        <v>-22.77</v>
       </c>
       <c r="J24" s="3">
-        <v>0.02435625297783154</v>
+        <v>0.021818737762920145</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="M24" s="3">
-        <v>0.2245544214038746</v>
+        <v>0.1753002425382697</v>
       </c>
       <c r="N24" s="3">
-        <v>31.493617328817287</v>
+        <v>28.088066023585405</v>
       </c>
       <c r="O24" s="3">
-        <v>82.27848101265823</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>27.468354430379748</v>
+        <v>25.06329113924051</v>
       </c>
       <c r="R24" s="3">
-        <v>29.49367088607595</v>
+        <v>27.658227848101266</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-1.52</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3581,49 +3575,49 @@
         <v>14.49</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.47908174589138464</v>
+        <v>-0.5125223711058603</v>
       </c>
       <c r="G25" s="3">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="H25" s="3">
-        <v>39.49</v>
+        <v>41.83</v>
       </c>
       <c r="I25" s="3">
-        <v>-57.17</v>
+        <v>-55.45</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.009106245229165899</v>
+        <v>-0.010958903546823775</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.3819310085925408</v>
+        <v>-0.3958809573378316</v>
       </c>
       <c r="N25" s="3">
-        <v>-29.154925670824262</v>
+        <v>-29.03005396402472</v>
       </c>
       <c r="O25" s="3">
-        <v>3.79746835443038</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>23.16455696202532</v>
+        <v>22.025316455696203</v>
       </c>
       <c r="R25" s="3">
-        <v>6.7721518987341796</v>
+        <v>6.0126582278481</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-5.19</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3643,49 +3637,49 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="1">
-        <v>0.2000788445480564</v>
+        <v>0.2705138622877369</v>
       </c>
       <c r="G26" s="1">
         <v>3.04</v>
       </c>
       <c r="H26" s="1">
-        <v>52.69</v>
+        <v>58.19</v>
       </c>
       <c r="I26" s="1">
-        <v>2.9</v>
+        <v>11.31</v>
       </c>
       <c r="J26" s="1">
-        <v>0.04255622403041103</v>
+        <v>0.041701520339968344</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="M26" s="1">
-        <v>0.36252761839202474</v>
+        <v>0.46396791439080887</v>
       </c>
       <c r="N26" s="1">
-        <v>45.2909370276323</v>
+        <v>56.954833208839325</v>
       </c>
       <c r="O26" s="1">
-        <v>88.60759493670885</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P26" s="1">
         <v>50.63126652197354</v>
       </c>
       <c r="Q26" s="1">
-        <v>37.84810126582279</v>
+        <v>38.48101265822785</v>
       </c>
       <c r="R26" s="1">
-        <v>32.278481012658226</v>
+        <v>32.78481012658228</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3705,49 +3699,49 @@
         <v>5.04</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.22830492742217814</v>
+        <v>-0.27581839557369814</v>
       </c>
       <c r="G27" s="3">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="H27" s="3">
-        <v>52.61</v>
+        <v>53.31</v>
       </c>
       <c r="I27" s="3">
-        <v>-23.64</v>
+        <v>-22.8</v>
       </c>
       <c r="J27" s="3">
-        <v>0.007736944793131371</v>
+        <v>0.005309580651560144</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.09930148936961503</v>
+        <v>-0.1231414230805874</v>
       </c>
       <c r="N27" s="3">
-        <v>-0.8919737485316819</v>
+        <v>-1.756100538300305</v>
       </c>
       <c r="O27" s="3">
-        <v>44.303797468354425</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>35.822784810126585</v>
+        <v>34.683544303797476</v>
       </c>
       <c r="R27" s="3">
-        <v>23.164556962025316</v>
+        <v>22.658227848101262</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>-3.23</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3767,49 +3761,49 @@
         <v>-1.13</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.41128140658019646</v>
+        <v>-0.5081224308291079</v>
       </c>
       <c r="G28" s="3">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H28" s="3">
-        <v>46.57</v>
+        <v>43.84</v>
       </c>
       <c r="I28" s="3">
-        <v>-27.08</v>
+        <v>-28.47</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.006479189644248075</v>
+        <v>-0.007637735377120385</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.24246209258548423</v>
+        <v>-0.30613364113325336</v>
       </c>
       <c r="N28" s="3">
-        <v>-15.208034070118599</v>
+        <v>-20.05532234356691</v>
       </c>
       <c r="O28" s="3">
-        <v>16.455696202531644</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>34.43037974683544</v>
+        <v>32.151898734177216</v>
       </c>
       <c r="R28" s="3">
-        <v>18.734177215189877</v>
+        <v>16.07594936708861</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-3.16</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3829,49 +3823,49 @@
         <v>0.88</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.40014255715490565</v>
+        <v>-0.3997854114255175</v>
       </c>
       <c r="G29" s="3">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="H29" s="3">
-        <v>38.85</v>
+        <v>43.27</v>
       </c>
       <c r="I29" s="3">
-        <v>-34.96</v>
+        <v>-32.91</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.018989950140114696</v>
+        <v>-0.01824777471718841</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-63</v>
+        <v>-70</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.31095499504449164</v>
+        <v>-0.2926270394272472</v>
       </c>
       <c r="N29" s="3">
-        <v>-22.057324316019347</v>
+        <v>-18.704662172966287</v>
       </c>
       <c r="O29" s="3">
-        <v>7.59493670886076</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>40.25316455696202</v>
+        <v>41.13924050632911</v>
       </c>
       <c r="R29" s="3">
-        <v>24.36708860759493</v>
+        <v>25.506329113924046</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3891,49 +3885,49 @@
         <v>2.51</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.20642110147513193</v>
+        <v>-0.17379561096699297</v>
       </c>
       <c r="G30" s="1">
         <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>40.52</v>
+        <v>47.32</v>
       </c>
       <c r="I30" s="1">
-        <v>-2.1</v>
+        <v>1.17</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.00033825062740763616</v>
+        <v>-0.001442740576152576</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.1904947510982723</v>
+        <v>-0.15482952742747613</v>
       </c>
       <c r="N30" s="1">
-        <v>-10.011299921397404</v>
+        <v>-4.924910972989183</v>
       </c>
       <c r="O30" s="1">
-        <v>26.582278481012654</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>60.63291139240506</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="R30" s="1">
-        <v>44.9367088607595</v>
+        <v>47.34177215189874</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-2.59</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3947,55 +3941,55 @@
         <v>59.49367088607595</v>
       </c>
       <c r="D31" s="2">
-        <v>10.775828460038985</v>
+        <v>10.83625730994152</v>
       </c>
       <c r="E31" s="2">
         <v>0.99</v>
       </c>
       <c r="F31" s="2">
-        <v>0.10793332560072785</v>
+        <v>0.10445846119607602</v>
       </c>
       <c r="G31" s="2">
         <v>1.43</v>
       </c>
       <c r="H31" s="2">
-        <v>52.17</v>
+        <v>54.77</v>
       </c>
       <c r="I31" s="2">
-        <v>18.1</v>
+        <v>19.81</v>
       </c>
       <c r="J31" s="2">
-        <v>0.026066919833058855</v>
+        <v>0.02439872967559199</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M31" s="2">
-        <v>0.14217497891097608</v>
+        <v>0.1452355408060373</v>
       </c>
       <c r="N31" s="2">
-        <v>23.255673079527426</v>
+        <v>25.081595850362167</v>
       </c>
       <c r="O31" s="2">
-        <v>74.68354430379746</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>66.83544303797468</v>
+        <v>67.46835443037975</v>
       </c>
       <c r="R31" s="2">
-        <v>59.620253164556964</v>
+        <v>60</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-1.2</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4015,49 +4009,49 @@
         <v>1.51</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.3401955153799341</v>
+        <v>-0.2846308670655817</v>
       </c>
       <c r="G32" s="3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H32" s="3">
-        <v>30.26</v>
+        <v>40.34</v>
       </c>
       <c r="I32" s="3">
-        <v>-15.9</v>
+        <v>-10.53</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.009785412990941067</v>
+        <v>-0.012341235670792932</v>
       </c>
       <c r="K32" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.2916201467305122</v>
+        <v>-0.22488770391610358</v>
       </c>
       <c r="N32" s="3">
-        <v>-20.123839484621396</v>
+        <v>-11.930728621851927</v>
       </c>
       <c r="O32" s="3">
-        <v>10.126582278481013</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P32" s="3">
         <v>40.689656926297594</v>
       </c>
       <c r="Q32" s="3">
-        <v>29.11392405063291</v>
+        <v>29.620253164556956</v>
       </c>
       <c r="R32" s="3">
-        <v>15.379746835443036</v>
+        <v>17.91139240506329</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-13.99</v>
+        <v>-11.46</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4071,55 +4065,55 @@
         <v>88.60759493670885</v>
       </c>
       <c r="D33" s="1">
-        <v>-0.05896366885050616</v>
+        <v>-0.0601548540798094</v>
       </c>
       <c r="E33" s="1">
         <v>0.66</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.05295399731155552</v>
+        <v>-0.05739677304831063</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>54.17</v>
+        <v>56.36</v>
       </c>
       <c r="I33" s="1">
-        <v>-9.66</v>
+        <v>-8.76</v>
       </c>
       <c r="J33" s="1">
-        <v>0.001973267457559314</v>
+        <v>0.0026763281941871143</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.04578713964196868</v>
+        <v>-0.04886203545552803</v>
       </c>
       <c r="N33" s="1">
-        <v>4.4594612242329426</v>
+        <v>5.671838224205635</v>
       </c>
       <c r="O33" s="1">
-        <v>54.43037974683544</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P33" s="1">
         <v>26.894390179645494</v>
       </c>
       <c r="Q33" s="1">
-        <v>52.15189873417721</v>
+        <v>52.40506329113923</v>
       </c>
       <c r="R33" s="1">
-        <v>42.59493670886076</v>
+        <v>41.9620253164557</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>2.66</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4133,37 +4127,37 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.7185354691075515</v>
+        <v>-0.7170099160945842</v>
       </c>
       <c r="E34" s="2">
         <v>0.94</v>
       </c>
       <c r="F34" s="2">
-        <v>0.1669281053839797</v>
+        <v>0.15393073932486953</v>
       </c>
       <c r="G34" s="2">
         <v>1.26</v>
       </c>
       <c r="H34" s="2">
-        <v>62.07</v>
+        <v>62.7</v>
       </c>
       <c r="I34" s="2">
-        <v>32.16</v>
+        <v>32.15</v>
       </c>
       <c r="J34" s="2">
-        <v>0.02891552930206472</v>
+        <v>0.027697165010491343</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M34" s="2">
-        <v>0.18763236087389723</v>
+        <v>0.17858664792624146</v>
       </c>
       <c r="N34" s="2">
-        <v>27.801411275819536</v>
+        <v>28.416706562382576</v>
       </c>
       <c r="O34" s="2">
         <v>81.0126582278481</v>
@@ -4172,7 +4166,7 @@
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>60.75949367088609</v>
+        <v>60.37974683544304</v>
       </c>
       <c r="R34" s="2">
         <v>52.21518987341772</v>
@@ -4201,111 +4195,111 @@
         <v>4.55</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.2745770929426098</v>
+        <v>-0.286104456782967</v>
       </c>
       <c r="G35" s="3">
         <v>1.01</v>
       </c>
       <c r="H35" s="3">
-        <v>35.51</v>
+        <v>38.24</v>
       </c>
       <c r="I35" s="3">
-        <v>-22.64</v>
+        <v>-21.69</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.027677007413035547</v>
+        <v>-0.026985346199492784</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.2737807754237668</v>
+        <v>-0.28515615260599114</v>
       </c>
       <c r="N35" s="3">
-        <v>-18.33990235394686</v>
+        <v>-17.957573490840687</v>
       </c>
       <c r="O35" s="3">
-        <v>11.39240506329114</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P35" s="3">
         <v>29.3533388963776</v>
       </c>
       <c r="Q35" s="3">
-        <v>34.0506329113924</v>
+        <v>33.67088607594936</v>
       </c>
       <c r="R35" s="3">
-        <v>23.417721518987342</v>
+        <v>23.79746835443038</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="1">
         <v>11.51</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="1">
         <v>82.27848101265823</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="1">
         <v>0.38488271068635965</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="1">
         <v>-1.05</v>
       </c>
-      <c r="F36" s="3">
-        <v>-0.21345558880979326</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1.12</v>
-      </c>
-      <c r="H36" s="3">
-        <v>32.96</v>
-      </c>
-      <c r="I36" s="3">
-        <v>-19.79</v>
-      </c>
-      <c r="J36" s="3">
-        <v>-0.018745918141179544</v>
-      </c>
-      <c r="K36" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="3">
-        <v>-51</v>
-      </c>
-      <c r="M36" s="3">
-        <v>-0.20389977858367747</v>
-      </c>
-      <c r="N36" s="3">
-        <v>-11.351802669937927</v>
-      </c>
-      <c r="O36" s="3">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="P36" s="3">
+      <c r="F36" s="1">
+        <v>-0.1545146126968847</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H36" s="1">
+        <v>45.39</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-13.36</v>
+      </c>
+      <c r="J36" s="1">
+        <v>-0.017864087744349548</v>
+      </c>
+      <c r="K36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>-56</v>
+      </c>
+      <c r="M36" s="1">
+        <v>-0.14123835421922293</v>
+      </c>
+      <c r="N36" s="1">
+        <v>-3.5657936521638587</v>
+      </c>
+      <c r="O36" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
-      <c r="Q36" s="3">
-        <v>36.45569620253165</v>
-      </c>
-      <c r="R36" s="3">
-        <v>28.29113924050633</v>
-      </c>
-      <c r="S36" s="3" t="s">
+      <c r="Q36" s="1">
+        <v>40.12658227848101</v>
+      </c>
+      <c r="R36" s="1">
+        <v>32.46835443037974</v>
+      </c>
+      <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="3">
-        <v>-6.01</v>
+      <c r="T36" s="1">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4319,55 +4313,55 @@
         <v>63.29113924050633</v>
       </c>
       <c r="D37" s="1">
-        <v>0.6060037523452159</v>
+        <v>0.6022514071294557</v>
       </c>
       <c r="E37" s="1">
         <v>1.72</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.0632232162901188</v>
+        <v>-0.07918061209309032</v>
       </c>
       <c r="G37" s="1">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H37" s="1">
-        <v>32.67</v>
+        <v>36.85</v>
       </c>
       <c r="I37" s="1">
-        <v>-23.9</v>
+        <v>-22.79</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.004694245373217974</v>
+        <v>-0.004481032438917695</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-206</v>
+        <v>-208</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.0329631505740855</v>
+        <v>-0.042196749191032445</v>
       </c>
       <c r="N37" s="1">
-        <v>5.741860131021274</v>
+        <v>6.338366850655194</v>
       </c>
       <c r="O37" s="1">
-        <v>58.22784810126582</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P37" s="1">
         <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
-        <v>37.34177215189874</v>
+        <v>37.08860759493671</v>
       </c>
       <c r="R37" s="1">
-        <v>37.21518987341772</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>-1.58</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4387,111 +4381,111 @@
         <v>-0.05</v>
       </c>
       <c r="F38" s="2">
-        <v>0.38459935188995253</v>
+        <v>0.42591886847537525</v>
       </c>
       <c r="G38" s="2">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="H38" s="2">
-        <v>83.9</v>
+        <v>86.58</v>
       </c>
       <c r="I38" s="2">
-        <v>33.48</v>
+        <v>40.38</v>
       </c>
       <c r="J38" s="2">
-        <v>0.040893267337176645</v>
+        <v>0.04252872102580373</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="M38" s="2">
-        <v>0.39335884459722537</v>
+        <v>0.43445360606815786</v>
       </c>
       <c r="N38" s="2">
-        <v>48.374059648152354</v>
+        <v>54.00340237657421</v>
       </c>
       <c r="O38" s="2">
-        <v>91.13924050632912</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P38" s="2">
         <v>27.505487150580247</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.69620253164557</v>
+        <v>65.94936708860759</v>
       </c>
       <c r="R38" s="2">
-        <v>55.56962025316456</v>
+        <v>55.31645569620253</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>-0.18</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>22.78481012658228</v>
       </c>
-      <c r="D39" s="2">
-        <v>100</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="D39" s="1">
+        <v>79.72222222222223</v>
+      </c>
+      <c r="E39" s="1">
         <v>-6.6</v>
       </c>
-      <c r="F39" s="2">
-        <v>0.08786365801448949</v>
-      </c>
-      <c r="G39" s="2">
+      <c r="F39" s="1">
+        <v>-0.1448679734272538</v>
+      </c>
+      <c r="G39" s="1">
         <v>1.31</v>
       </c>
-      <c r="H39" s="2">
-        <v>54.42</v>
-      </c>
-      <c r="I39" s="2">
-        <v>11.54</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0.017164162547676932</v>
-      </c>
-      <c r="K39" s="2" t="b">
+      <c r="H39" s="1">
+        <v>34.08</v>
+      </c>
+      <c r="I39" s="1">
+        <v>-5.73</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.014175230667651575</v>
+      </c>
+      <c r="K39" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39" s="1">
         <v>-4</v>
       </c>
-      <c r="M39" s="2">
-        <v>0.11254950109862194</v>
-      </c>
-      <c r="N39" s="2">
-        <v>20.29312529829202</v>
-      </c>
-      <c r="O39" s="2">
-        <v>73.41772151898735</v>
-      </c>
-      <c r="P39" s="2">
-        <v>18.299999237060547</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>60</v>
-      </c>
-      <c r="R39" s="2">
-        <v>54.11392405063292</v>
-      </c>
-      <c r="S39" s="2" t="s">
+      <c r="M39" s="1">
+        <v>-0.11547054394100265</v>
+      </c>
+      <c r="N39" s="1">
+        <v>-0.9890126243418337</v>
+      </c>
+      <c r="O39" s="1">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="P39" s="1">
+        <v>18.53526322746658</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>50.88607594936709</v>
+      </c>
+      <c r="R39" s="1">
+        <v>45.12658227848101</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T39" s="2">
-        <v>0.7</v>
+      <c r="T39" s="1">
+        <v>-8.29</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4505,25 +4499,25 @@
         <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>10.018720748829953</v>
+        <v>10.126365054602184</v>
       </c>
       <c r="E40" s="1">
         <v>10.16</v>
       </c>
       <c r="F40" s="1">
-        <v>0.12676959523726963</v>
+        <v>0.13135696449196702</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>41.68</v>
+        <v>43.69</v>
       </c>
       <c r="I40" s="1">
-        <v>-19.62</v>
+        <v>-17.9</v>
       </c>
       <c r="J40" s="1">
-        <v>0.00654322177489611</v>
+        <v>0.0021799008175573333</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>1</v>
@@ -4532,28 +4526,28 @@
         <v>52</v>
       </c>
       <c r="M40" s="1">
-        <v>0.04713784335297144</v>
+        <v>0.03652654679438272</v>
       </c>
       <c r="N40" s="1">
-        <v>13.751959523726967</v>
+        <v>14.210696449196705</v>
       </c>
       <c r="O40" s="1">
-        <v>65.82278481012658</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P40" s="1">
         <v>45.29877115964868</v>
       </c>
       <c r="Q40" s="1">
-        <v>36.32911392405063</v>
+        <v>34.93670886075949</v>
       </c>
       <c r="R40" s="1">
-        <v>33.60759493670885</v>
+        <v>31.835443037974677</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-7.15</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4573,49 +4567,49 @@
         <v>-1.71</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.03441757424506209</v>
+        <v>-0.048158066060495386</v>
       </c>
       <c r="G41" s="1">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="H41" s="1">
-        <v>59.29</v>
+        <v>60.44</v>
       </c>
       <c r="I41" s="1">
-        <v>-12.89</v>
+        <v>-11.73</v>
       </c>
       <c r="J41" s="1">
-        <v>0.023441624569661992</v>
+        <v>0.022054052318726453</v>
       </c>
       <c r="K41" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.028843351613161206</v>
+        <v>-0.04246824099864033</v>
       </c>
       <c r="N41" s="1">
-        <v>6.153840027113693</v>
+        <v>6.31121766989439</v>
       </c>
       <c r="O41" s="1">
-        <v>59.49367088607595</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>44.17721518987343</v>
+        <v>42.78481012658228</v>
       </c>
       <c r="R41" s="1">
-        <v>32.08860759493672</v>
+        <v>30.44303797468355</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>2.03</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4635,49 +4629,49 @@
         <v>0.29</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.0633823226651774</v>
+        <v>-0.08407063074083401</v>
       </c>
       <c r="G42" s="1">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H42" s="1">
-        <v>43.1</v>
+        <v>41.56</v>
       </c>
       <c r="I42" s="1">
-        <v>-0.39</v>
+        <v>-0.87</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.006358096147361646</v>
+        <v>-0.0059719137821893946</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.11434664387112825</v>
+        <v>-0.14381379389031212</v>
       </c>
       <c r="N42" s="1">
-        <v>-2.396489198683003</v>
+        <v>-3.823337619272786</v>
       </c>
       <c r="O42" s="1">
-        <v>40.50632911392405</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>44.050632911392405</v>
+        <v>42.278481012658226</v>
       </c>
       <c r="R42" s="1">
-        <v>39.11392405063291</v>
+        <v>38.101265822784804</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>0.57</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4697,49 +4691,49 @@
         <v>6.54</v>
       </c>
       <c r="F43" s="1">
-        <v>0.029859632219619917</v>
+        <v>0.009829210152880186</v>
       </c>
       <c r="G43" s="1">
         <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>55.45</v>
+        <v>54.61</v>
       </c>
       <c r="I43" s="1">
-        <v>-9.96</v>
+        <v>-10.34</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.006700277013963392</v>
+        <v>-0.0072621040302470125</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43" s="1">
-        <v>0.05295284026606639</v>
+        <v>0.03733003128517964</v>
       </c>
       <c r="N43" s="1">
-        <v>14.33345921503645</v>
+        <v>14.291044898276398</v>
       </c>
       <c r="O43" s="1">
-        <v>68.35443037974683</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P43" s="1">
         <v>36.79958124823221</v>
       </c>
       <c r="Q43" s="1">
-        <v>54.30379746835443</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="R43" s="1">
-        <v>47.34177215189873</v>
+        <v>45.82278481012658</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>5.19</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4759,31 +4753,31 @@
         <v>-1.94</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.3889839843871479</v>
+        <v>-0.411931061972276</v>
       </c>
       <c r="G44" s="3">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="H44" s="3">
-        <v>38.48</v>
+        <v>43.29</v>
       </c>
       <c r="I44" s="3">
-        <v>-28.29</v>
+        <v>-25.4</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.02536336424811085</v>
+        <v>-0.025122965297178713</v>
       </c>
       <c r="K44" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.2599805463345848</v>
+        <v>-0.2573574811252136</v>
       </c>
       <c r="N44" s="3">
-        <v>-16.959879445028655</v>
+        <v>-15.177706342762928</v>
       </c>
       <c r="O44" s="3">
         <v>15.18987341772152</v>
@@ -4792,7 +4786,7 @@
         <v>44.155007607957295</v>
       </c>
       <c r="Q44" s="3">
-        <v>39.49367088607594</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="R44" s="3">
         <v>26.89873417721519</v>
@@ -4815,55 +4809,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.731182795698925</v>
+        <v>0.771804062126643</v>
       </c>
       <c r="E45" s="2">
         <v>1.15</v>
       </c>
       <c r="F45" s="2">
-        <v>0.13935809412711037</v>
+        <v>0.14441278578812533</v>
       </c>
       <c r="G45" s="2">
         <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>51.93</v>
+        <v>57.72</v>
       </c>
       <c r="I45" s="2">
-        <v>12.86</v>
+        <v>15.19</v>
       </c>
       <c r="J45" s="2">
-        <v>0.02179236752245355</v>
+        <v>0.02076525864641117</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.17598869999388755</v>
+        <v>0.18803477792901413</v>
       </c>
       <c r="N45" s="2">
-        <v>26.63704518781857</v>
+        <v>29.361519562659836</v>
       </c>
       <c r="O45" s="2">
-        <v>78.48101265822784</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>58.734177215189874</v>
+        <v>59.87341772151899</v>
       </c>
       <c r="R45" s="2">
-        <v>54.68354430379747</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-2.28</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4883,49 +4877,49 @@
         <v>-0.24</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3719970566229067</v>
+        <v>-0.39017509999581734</v>
       </c>
       <c r="G46" s="3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H46" s="3">
-        <v>34.24</v>
+        <v>37.29</v>
       </c>
       <c r="I46" s="3">
-        <v>-8.31</v>
+        <v>-5.1</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.010350607901697213</v>
+        <v>-0.013207756574737524</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L46" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.33218118068075764</v>
+        <v>-0.3418115869700493</v>
       </c>
       <c r="N46" s="3">
-        <v>-24.179942879645942</v>
+        <v>-23.6231169272465</v>
       </c>
       <c r="O46" s="3">
-        <v>6.329113924050633</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>44.30379746835443</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="R46" s="3">
-        <v>25.0632911392405</v>
+        <v>23.670886075949362</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-6.33</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4945,34 +4939,34 @@
         <v>-3.9</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.3955556422473674</v>
+        <v>-0.38713278429762255</v>
       </c>
       <c r="G47" s="3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H47" s="3">
-        <v>30.06</v>
+        <v>31.08</v>
       </c>
       <c r="I47" s="3">
-        <v>-20.2</v>
+        <v>-19.79</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.02994474249710443</v>
+        <v>-0.030066545340140322</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.35812871886174724</v>
+        <v>-0.3416141838027821</v>
       </c>
       <c r="N47" s="3">
-        <v>-26.774696697744897</v>
+        <v>-23.603376610519778</v>
       </c>
       <c r="O47" s="3">
-        <v>5.063291139240507</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P47" s="3">
         <v>31.304415950527737</v>
@@ -4981,13 +4975,13 @@
         <v>38.734177215189874</v>
       </c>
       <c r="R47" s="3">
-        <v>25.632911392405056</v>
+        <v>26.012658227848096</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>-0.13</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5007,49 +5001,49 @@
         <v>-0.2</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.18218573932361465</v>
+        <v>-0.19999446919070663</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>54.5</v>
+        <v>55.17</v>
       </c>
       <c r="I48" s="1">
-        <v>-5.24</v>
+        <v>-4.98</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.005451166591159077</v>
+        <v>-0.004658728666823754</v>
       </c>
       <c r="K48" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.18059310428592867</v>
+        <v>-0.19809786083675496</v>
       </c>
       <c r="N48" s="1">
-        <v>-9.021135240163044</v>
+        <v>-9.25174431391706</v>
       </c>
       <c r="O48" s="1">
-        <v>27.848101265822784</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>48.35443037974684</v>
+        <v>47.848101265822784</v>
       </c>
       <c r="R48" s="1">
-        <v>33.86075949367089</v>
+        <v>33.48101265822785</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>7.66</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5069,19 +5063,19 @@
         <v>-1.46</v>
       </c>
       <c r="F49" s="2">
-        <v>0.004905078657271966</v>
+        <v>-0.017070155312429336</v>
       </c>
       <c r="G49" s="2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H49" s="2">
-        <v>51.65</v>
+        <v>54.18</v>
       </c>
       <c r="I49" s="2">
-        <v>38.88</v>
+        <v>40.39</v>
       </c>
       <c r="J49" s="2">
-        <v>0.023056684405063557</v>
+        <v>0.02232370560220781</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5090,28 +5084,28 @@
         <v>268</v>
       </c>
       <c r="M49" s="2">
-        <v>0.05348044730669388</v>
+        <v>0.04172470366007297</v>
       </c>
       <c r="N49" s="2">
-        <v>14.386219919099217</v>
+        <v>14.73051213576572</v>
       </c>
       <c r="O49" s="2">
-        <v>69.62025316455697</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>63.164556962025316</v>
+        <v>63.291139240506325</v>
       </c>
       <c r="R49" s="2">
-        <v>55.75949367088608</v>
+        <v>54.62025316455696</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>0.44</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5131,31 +5125,31 @@
         <v>3.55</v>
       </c>
       <c r="F50" s="2">
-        <v>0.3491738299917643</v>
+        <v>0.40348068441241614</v>
       </c>
       <c r="G50" s="2">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="H50" s="2">
-        <v>53.77</v>
+        <v>59.31</v>
       </c>
       <c r="I50" s="2">
-        <v>102.25</v>
+        <v>116.42</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06516006028912798</v>
+        <v>0.06337730421075859</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M50" s="2">
-        <v>0.5713464177489562</v>
+        <v>0.669954158142628</v>
       </c>
       <c r="N50" s="2">
-        <v>66.17281696332545</v>
+        <v>77.55345758402122</v>
       </c>
       <c r="O50" s="2">
         <v>93.67088607594937</v>
@@ -5164,7 +5158,7 @@
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>72.27848101265823</v>
+        <v>72.9113924050633</v>
       </c>
       <c r="R50" s="2">
         <v>62.21518987341772</v>
@@ -5187,55 +5181,55 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D51" s="2">
-        <v>7.673366834170855</v>
+        <v>7.748743718592965</v>
       </c>
       <c r="E51" s="2">
         <v>-0.69</v>
       </c>
       <c r="F51" s="2">
-        <v>0.1493686948363873</v>
+        <v>0.08978731847287727</v>
       </c>
       <c r="G51" s="2">
         <v>2.09</v>
       </c>
       <c r="H51" s="2">
-        <v>47.52</v>
+        <v>45.23</v>
       </c>
       <c r="I51" s="2">
-        <v>57.39</v>
+        <v>53.34</v>
       </c>
       <c r="J51" s="2">
-        <v>0.03650757721219353</v>
+        <v>0.030712783573591588</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M51" s="2">
-        <v>0.23616730439027234</v>
+        <v>0.19315247376324418</v>
       </c>
       <c r="N51" s="2">
-        <v>32.65490562745706</v>
+        <v>29.873289146082847</v>
       </c>
       <c r="O51" s="2">
-        <v>84.81012658227847</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P51" s="2">
-        <v>15.18684888660459</v>
+        <v>16.096535574030653</v>
       </c>
       <c r="Q51" s="2">
-        <v>65.56962025316456</v>
+        <v>63.291139240506325</v>
       </c>
       <c r="R51" s="2">
-        <v>61.13924050632911</v>
+        <v>60.12658227848101</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-1.9</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5255,19 +5249,19 @@
         <v>2.59</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.4447601399912655</v>
+        <v>-0.4167732656205182</v>
       </c>
       <c r="G52" s="3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H52" s="3">
-        <v>37.38</v>
+        <v>45.37</v>
       </c>
       <c r="I52" s="3">
-        <v>-26.3</v>
+        <v>-21.23</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.0393890667011606</v>
+        <v>-0.04258186181103661</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
@@ -5276,28 +5270,28 @@
         <v>-2</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.4017589939737445</v>
+        <v>-0.36461653588684684</v>
       </c>
       <c r="N52" s="3">
-        <v>-31.137724208944622</v>
+        <v>-25.903611818926258</v>
       </c>
       <c r="O52" s="3">
-        <v>2.5316455696202533</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P52" s="3">
         <v>46.37680917379436</v>
       </c>
       <c r="Q52" s="3">
-        <v>38.35443037974684</v>
+        <v>40.63291139240506</v>
       </c>
       <c r="R52" s="3">
-        <v>21.89873417721519</v>
+        <v>21.962025316455694</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T52" s="3">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5317,49 +5311,49 @@
         <v>16.72</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.10090663255117185</v>
+        <v>-0.00914892571855691</v>
       </c>
       <c r="G53" s="1">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="H53" s="1">
-        <v>39.92</v>
+        <v>48.59</v>
       </c>
       <c r="I53" s="1">
-        <v>5.67</v>
+        <v>19.18</v>
       </c>
       <c r="J53" s="1">
-        <v>0.022259614660490392</v>
+        <v>0.01827539964330227</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M53" s="1">
-        <v>0.006596232492630749</v>
+        <v>0.12171705070410943</v>
       </c>
       <c r="N53" s="1">
-        <v>9.697798437692896</v>
+        <v>22.729746840169366</v>
       </c>
       <c r="O53" s="1">
-        <v>62.0253164556962</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>45.69620253164557</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="R53" s="1">
-        <v>36.01265822784811</v>
+        <v>38.54430379746835</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>9.37</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5373,55 +5367,55 @@
         <v>62.0253164556962</v>
       </c>
       <c r="D54" s="2">
-        <v>6.507547169811321</v>
+        <v>6.560377358490567</v>
       </c>
       <c r="E54" s="2">
         <v>0.25</v>
       </c>
       <c r="F54" s="2">
-        <v>-0.017023413517112118</v>
+        <v>0.04708113900637412</v>
       </c>
       <c r="G54" s="2">
         <v>1.82</v>
       </c>
       <c r="H54" s="2">
-        <v>51.23</v>
+        <v>59.07</v>
       </c>
       <c r="I54" s="2">
-        <v>47.39</v>
+        <v>56.66</v>
       </c>
       <c r="J54" s="2">
-        <v>0.030013098625128666</v>
+        <v>0.029714571253490193</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M54" s="2">
-        <v>0.04827462302801244</v>
+        <v>0.12484208151839327</v>
       </c>
       <c r="N54" s="2">
-        <v>13.865637491231073</v>
+        <v>23.04224992159776</v>
       </c>
       <c r="O54" s="2">
-        <v>67.08860759493672</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>65.82278481012659</v>
+        <v>67.72151898734178</v>
       </c>
       <c r="R54" s="2">
-        <v>54.43037974683545</v>
+        <v>56.708860759493675</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>-2.34</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5441,19 +5435,19 @@
         <v>6.64</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.19442456830534355</v>
+        <v>-0.18472916725132155</v>
       </c>
       <c r="G55" s="1">
         <v>2.57</v>
       </c>
       <c r="H55" s="1">
-        <v>47.35</v>
+        <v>52.21</v>
       </c>
       <c r="I55" s="1">
-        <v>-27.91</v>
+        <v>-24.23</v>
       </c>
       <c r="J55" s="1">
-        <v>0.0179290384271083</v>
+        <v>0.014163573541884859</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5462,90 +5456,90 @@
         <v>-15</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.06940271784699537</v>
+        <v>-0.035845411466114196</v>
       </c>
       <c r="N55" s="1">
-        <v>2.0979034037302804</v>
+        <v>6.973500623147019</v>
       </c>
       <c r="O55" s="1">
-        <v>49.36708860759494</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P55" s="1">
         <v>48.21894075039502</v>
       </c>
       <c r="Q55" s="1">
-        <v>43.54430379746835</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="R55" s="1">
-        <v>33.0379746835443</v>
+        <v>35.31645569620253</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>-2.09</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>0.54</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="1">
         <v>35.44303797468354</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="1">
         <v>40.407407407407405</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>-0.43</v>
       </c>
-      <c r="F56" s="2">
-        <v>-0.07817453845352429</v>
-      </c>
-      <c r="G56" s="2">
+      <c r="F56" s="1">
+        <v>-0.08833034037214557</v>
+      </c>
+      <c r="G56" s="1">
         <v>1.44</v>
       </c>
-      <c r="H56" s="2">
-        <v>52.84</v>
-      </c>
-      <c r="I56" s="2">
-        <v>2.49</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0.028515566693884147</v>
-      </c>
-      <c r="K56" s="2" t="b">
+      <c r="H56" s="1">
+        <v>55.99</v>
+      </c>
+      <c r="I56" s="1">
+        <v>4.89</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.026583598231624345</v>
+      </c>
+      <c r="K56" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="1">
         <v>14</v>
       </c>
-      <c r="M56" s="2">
-        <v>-0.043136567624433075</v>
-      </c>
-      <c r="N56" s="2">
-        <v>4.724518425986517</v>
-      </c>
-      <c r="O56" s="2">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="P56" s="2">
+      <c r="M56" s="1">
+        <v>-0.04660495658520847</v>
+      </c>
+      <c r="N56" s="1">
+        <v>5.8975461112375935</v>
+      </c>
+      <c r="O56" s="1">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="P56" s="1">
         <v>25.062459708672506</v>
       </c>
-      <c r="Q56" s="2">
-        <v>63.924050632911396</v>
-      </c>
-      <c r="R56" s="2">
-        <v>50</v>
-      </c>
-      <c r="S56" s="2" t="s">
+      <c r="Q56" s="1">
+        <v>64.0506329113924</v>
+      </c>
+      <c r="R56" s="1">
+        <v>49.493670886075954</v>
+      </c>
+      <c r="S56" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T56" s="2">
-        <v>-2.66</v>
+      <c r="T56" s="1">
+        <v>-3.16</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5565,49 +5559,49 @@
         <v>-0.26</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.15695449131272274</v>
+        <v>-0.15562637474489605</v>
       </c>
       <c r="G57" s="1">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H57" s="1">
-        <v>44.77</v>
+        <v>48.65</v>
       </c>
       <c r="I57" s="1">
-        <v>-1.84</v>
+        <v>-0.86</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0016737278743720902</v>
+        <v>0.0027817767590546006</v>
       </c>
       <c r="K57" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="1">
-        <v>-56</v>
+        <v>-58</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.14023182341702012</v>
+        <v>-0.13476368285142748</v>
       </c>
       <c r="N57" s="1">
-        <v>-4.98500715327219</v>
+        <v>-2.918326515384319</v>
       </c>
       <c r="O57" s="1">
-        <v>35.44303797468354</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>48.98734177215191</v>
+        <v>51.01265822784811</v>
       </c>
       <c r="R57" s="1">
-        <v>38.54430379746836</v>
+        <v>40.18987341772152</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>1.96</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5627,19 +5621,19 @@
         <v>0.81</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.09264044740411104</v>
+        <v>-0.10664642570072012</v>
       </c>
       <c r="G58" s="1">
         <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>51.35</v>
+        <v>50.13</v>
       </c>
       <c r="I58" s="1">
-        <v>9.61</v>
+        <v>9.14</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.005762453981182471</v>
+        <v>-0.005605395541752041</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
@@ -5648,28 +5642,28 @@
         <v>163</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.1515679437984917</v>
+        <v>-0.1768209347969325</v>
       </c>
       <c r="N58" s="1">
-        <v>-6.118619191419353</v>
+        <v>-7.124051709934818</v>
       </c>
       <c r="O58" s="1">
-        <v>32.91139240506329</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>48.22784810126582</v>
+        <v>47.72151898734177</v>
       </c>
       <c r="R58" s="1">
-        <v>37.088607594936704</v>
+        <v>35.949367088607595</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5689,31 +5683,31 @@
         <v>0.11</v>
       </c>
       <c r="F59" s="2">
-        <v>0.49388011606644744</v>
+        <v>0.5591785452661154</v>
       </c>
       <c r="G59" s="2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H59" s="2">
-        <v>61.29</v>
+        <v>64.36</v>
       </c>
       <c r="I59" s="2">
-        <v>123.27</v>
+        <v>131.58</v>
       </c>
       <c r="J59" s="2">
-        <v>0.07537002172374156</v>
+        <v>0.06998974441866626</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M59" s="2">
-        <v>0.5695302803565307</v>
+        <v>0.6483191379018447</v>
       </c>
       <c r="N59" s="2">
-        <v>65.9912032240829</v>
+        <v>75.38995555994289</v>
       </c>
       <c r="O59" s="2">
         <v>92.40506329113924</v>
@@ -5722,7 +5716,7 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>79.62025316455697</v>
+        <v>80.12658227848101</v>
       </c>
       <c r="R59" s="2">
         <v>66.77215189873418</v>
@@ -5751,49 +5745,49 @@
         <v>-2.31</v>
       </c>
       <c r="F60" s="2">
-        <v>0.12810677799114745</v>
+        <v>0.09541051379947513</v>
       </c>
       <c r="G60" s="2">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="H60" s="2">
-        <v>46.21</v>
+        <v>48.37</v>
       </c>
       <c r="I60" s="2">
-        <v>37.59</v>
+        <v>38.98</v>
       </c>
       <c r="J60" s="2">
-        <v>0.023283659555353383</v>
+        <v>0.022439490291569168</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M60" s="2">
-        <v>0.14721839844337903</v>
+        <v>0.12196303075479875</v>
       </c>
       <c r="N60" s="2">
-        <v>23.760015032767715</v>
+        <v>22.754344845238315</v>
       </c>
       <c r="O60" s="2">
-        <v>75.9493670886076</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P60" s="2">
         <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>58.60759493670886</v>
+        <v>58.607594936708864</v>
       </c>
       <c r="R60" s="2">
-        <v>55.63291139240508</v>
+        <v>54.873417721519</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-0.95</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5813,49 +5807,49 @@
         <v>0.62</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.12709140254575158</v>
+        <v>-0.14069214343052988</v>
       </c>
       <c r="G61" s="1">
         <v>0.39</v>
       </c>
       <c r="H61" s="1">
-        <v>42.34</v>
+        <v>40.14</v>
       </c>
       <c r="I61" s="1">
-        <v>-0.09</v>
+        <v>-0.84</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.00820564370970525</v>
+        <v>-0.007688978137916444</v>
       </c>
       <c r="K61" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="1">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.1756667711951735</v>
+        <v>-0.1985386982260563</v>
       </c>
       <c r="N61" s="1">
-        <v>-8.528501931087524</v>
+        <v>-9.295828052847197</v>
       </c>
       <c r="O61" s="1">
-        <v>29.11392405063291</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P61" s="1">
         <v>12.798408482128673</v>
       </c>
       <c r="Q61" s="1">
-        <v>38.607594936708864</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="R61" s="1">
-        <v>31.202531645569614</v>
+        <v>30.063291139240505</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T61" s="1">
-        <v>2.41</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5875,49 +5869,49 @@
         <v>-0.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.14652867633789168</v>
+        <v>-0.25517085359896147</v>
       </c>
       <c r="G62" s="1">
         <v>0.96</v>
       </c>
       <c r="H62" s="1">
-        <v>41.43</v>
+        <v>42.65</v>
       </c>
       <c r="I62" s="1">
-        <v>7.28</v>
+        <v>7.69</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.005954810300976654</v>
+        <v>-0.005745870886821533</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.14971394641326363</v>
+        <v>-0.25896407030686486</v>
       </c>
       <c r="N62" s="1">
-        <v>-5.933219452896544</v>
+        <v>-15.338365260928057</v>
       </c>
       <c r="O62" s="1">
-        <v>34.177215189873415</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P62" s="1">
         <v>16.149676494964734</v>
       </c>
       <c r="Q62" s="1">
-        <v>52.53164556962025</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="R62" s="1">
-        <v>42.27848101265823</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-0.57</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5937,19 +5931,19 @@
         <v>-8.13</v>
       </c>
       <c r="F63" s="4">
-        <v>0.9157428358648717</v>
+        <v>0.7761867121787323</v>
       </c>
       <c r="G63" s="4">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="H63" s="4">
-        <v>62.05</v>
+        <v>62.51</v>
       </c>
       <c r="I63" s="4">
-        <v>217.92</v>
+        <v>215.16</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09415981916637181</v>
+        <v>0.08986427164951427</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
@@ -5958,10 +5952,10 @@
         <v>479</v>
       </c>
       <c r="M63" s="4">
-        <v>1.213565587912147</v>
+        <v>1.1365422994295526</v>
       </c>
       <c r="N63" s="4">
-        <v>130.3947339796445</v>
+        <v>124.2122717127137</v>
       </c>
       <c r="O63" s="4">
         <v>98.73417721518987</v>
@@ -5970,7 +5964,7 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.78481012658227</v>
+        <v>82.53164556962025</v>
       </c>
       <c r="R63" s="4">
         <v>72.02531645569621</v>
@@ -5999,31 +5993,31 @@
         <v>-5.36</v>
       </c>
       <c r="F64" s="2">
-        <v>0.5582182125183286</v>
+        <v>0.6351325470611234</v>
       </c>
       <c r="G64" s="2">
         <v>2.01</v>
       </c>
       <c r="H64" s="2">
-        <v>59.04</v>
+        <v>61.46</v>
       </c>
       <c r="I64" s="2">
-        <v>113.33</v>
+        <v>116.61</v>
       </c>
       <c r="J64" s="2">
-        <v>0.0804520211397876</v>
+        <v>0.07547802540153473</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M64" s="2">
-        <v>0.6386462819214698</v>
+        <v>0.7309112689356836</v>
       </c>
       <c r="N64" s="2">
-        <v>72.9028033805768</v>
+        <v>83.6491686633268</v>
       </c>
       <c r="O64" s="2">
         <v>94.9367088607595</v>
@@ -6055,55 +6049,55 @@
         <v>89.87341772151899</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.27504445761707175</v>
+        <v>-0.2928275044457618</v>
       </c>
       <c r="E65" s="1">
         <v>-0.88</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.11118478334606827</v>
+        <v>-0.12194463957896008</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>47.41</v>
+        <v>44.84</v>
       </c>
       <c r="I65" s="1">
-        <v>-0.02</v>
+        <v>-0.87</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.005345493843639389</v>
+        <v>-0.007483096510571766</v>
       </c>
       <c r="K65" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="1">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.166927009665077</v>
+        <v>-0.1883259319672691</v>
       </c>
       <c r="N65" s="1">
-        <v>-7.654525778077878</v>
+        <v>-8.274551426968483</v>
       </c>
       <c r="O65" s="1">
-        <v>30.37974683544304</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>48.98734177215189</v>
+        <v>44.810126582278485</v>
       </c>
       <c r="R65" s="1">
-        <v>37.151898734177216</v>
+        <v>35.50632911392405</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-0.25</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6117,55 +6111,55 @@
         <v>87.34177215189874</v>
       </c>
       <c r="D66" s="1">
-        <v>-0.10837118754055808</v>
+        <v>-0.10902011680726799</v>
       </c>
       <c r="E66" s="1">
         <v>-0.2</v>
       </c>
       <c r="F66" s="1">
-        <v>-0.067538364875655</v>
+        <v>-0.10310958849330647</v>
       </c>
       <c r="G66" s="1">
         <v>1.04</v>
       </c>
       <c r="H66" s="1">
-        <v>51.05</v>
+        <v>45.35</v>
       </c>
       <c r="I66" s="1">
-        <v>-29.34</v>
+        <v>-31.89</v>
       </c>
       <c r="J66" s="1">
-        <v>-0.0167961655692444</v>
+        <v>-0.017250314305971653</v>
       </c>
       <c r="K66" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="1">
-        <v>-187</v>
+        <v>-192</v>
       </c>
       <c r="M66" s="1">
-        <v>-0.06435309480028306</v>
+        <v>-0.09931637178540309</v>
       </c>
       <c r="N66" s="1">
-        <v>2.6028657084015188</v>
+        <v>0.626404591218114</v>
       </c>
       <c r="O66" s="1">
-        <v>50.63291139240506</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P66" s="1">
         <v>48.12800106814908</v>
       </c>
       <c r="Q66" s="1">
-        <v>38.607594936708864</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="R66" s="1">
-        <v>32.72151898734177</v>
+        <v>31.20253164556962</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="1">
-        <v>3.67</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6179,55 +6173,55 @@
         <v>55.69620253164557</v>
       </c>
       <c r="D67" s="1">
-        <v>7.266832917705736</v>
+        <v>7.239401496259353</v>
       </c>
       <c r="E67" s="1">
         <v>-1.48</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.0841871748879574</v>
+        <v>-0.09704660391744808</v>
       </c>
       <c r="G67" s="1">
         <v>1.15</v>
       </c>
       <c r="H67" s="1">
-        <v>46.91</v>
+        <v>48.75</v>
       </c>
       <c r="I67" s="1">
-        <v>-12.15</v>
+        <v>-11.47</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.0010148770194261503</v>
+        <v>0.00003501062543400538</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.07224241210531268</v>
+        <v>-0.08282204126281045</v>
       </c>
       <c r="N67" s="1">
-        <v>1.813933977898554</v>
+        <v>2.2758376434773804</v>
       </c>
       <c r="O67" s="1">
-        <v>48.10126582278481</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>49.74683544303797</v>
+        <v>50.12658227848101</v>
       </c>
       <c r="R67" s="1">
-        <v>42.784810126582286</v>
+        <v>43.16455696202532</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-1.33</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6241,25 +6235,25 @@
         <v>69.62025316455697</v>
       </c>
       <c r="D68" s="1">
-        <v>200.22857142857146</v>
+        <v>485.7265306122449</v>
       </c>
       <c r="E68" s="1">
         <v>-0.18</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.18263542255890908</v>
+        <v>-0.17723457076695825</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>42.2</v>
+        <v>42.75</v>
       </c>
       <c r="I68" s="1">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.011120849696270613</v>
+        <v>-0.011592547022159807</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6268,10 +6262,10 @@
         <v>148</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.23598869632138886</v>
+        <v>-0.24077095062433973</v>
       </c>
       <c r="N68" s="1">
-        <v>-14.560694443709066</v>
+        <v>-13.51905329267554</v>
       </c>
       <c r="O68" s="1">
         <v>17.72151898734177</v>
@@ -6280,16 +6274,16 @@
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>60.37974683544303</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="R68" s="1">
-        <v>44.87341772151899</v>
+        <v>45.75949367088607</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>-0.06</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6309,49 +6303,49 @@
         <v>0.19</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.24837803768197456</v>
+        <v>-0.2540906561209906</v>
       </c>
       <c r="G69" s="3">
         <v>1.5</v>
       </c>
       <c r="H69" s="3">
-        <v>45.71</v>
+        <v>49.59</v>
       </c>
       <c r="I69" s="3">
-        <v>-11.06</v>
+        <v>-9.53</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.013532139114412724</v>
+        <v>-0.01235368357219521</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-63</v>
+        <v>-65</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.20856216173982545</v>
+        <v>-0.20667544727219844</v>
       </c>
       <c r="N69" s="3">
-        <v>-11.818040985552722</v>
+        <v>-10.109502957461418</v>
       </c>
       <c r="O69" s="3">
-        <v>22.78481012658228</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P69" s="3">
         <v>29.145649851223904</v>
       </c>
       <c r="Q69" s="3">
-        <v>41.0126582278481</v>
+        <v>43.0379746835443</v>
       </c>
       <c r="R69" s="3">
-        <v>28.29113924050633</v>
+        <v>28.924050632911392</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>0.57</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6371,49 +6365,49 @@
         <v>1.82</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.20805750853954208</v>
+        <v>-0.2171429697259346</v>
       </c>
       <c r="G70" s="3">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H70" s="3">
-        <v>38.93</v>
+        <v>41.29</v>
       </c>
       <c r="I70" s="3">
-        <v>-14.99</v>
+        <v>-14.23</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.013480278978388126</v>
+        <v>-0.012948885801887805</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.21840963628450083</v>
+        <v>-0.22852261984964473</v>
       </c>
       <c r="N70" s="3">
-        <v>-12.802788440020265</v>
+        <v>-12.294220215206039</v>
       </c>
       <c r="O70" s="3">
-        <v>20.253164556962027</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>39.11392405063292</v>
+        <v>38.35443037974684</v>
       </c>
       <c r="R70" s="3">
-        <v>27.531645569620256</v>
+        <v>27.151898734177212</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>-0.19</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6433,31 +6427,31 @@
         <v>-1.56</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.452798032071784</v>
+        <v>-0.4434347177889558</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>35.45</v>
+        <v>48.49</v>
       </c>
       <c r="I71" s="3">
-        <v>-31.66</v>
+        <v>-28.63</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.03225248689308389</v>
+        <v>-0.030341592034696174</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-97</v>
+        <v>-99</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.4432422218456682</v>
+        <v>-0.4320550676652457</v>
       </c>
       <c r="N71" s="3">
-        <v>-35.286046996137</v>
+        <v>-32.64746499676614</v>
       </c>
       <c r="O71" s="3">
         <v>1.2658227848101267</v>
@@ -6466,7 +6460,7 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>36.70886075949367</v>
+        <v>40.25316455696203</v>
       </c>
       <c r="R71" s="3">
         <v>22.27848101265823</v>
@@ -6495,49 +6489,49 @@
         <v>-1.49</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.2847139277015262</v>
+        <v>-0.2593703593655213</v>
       </c>
       <c r="G72" s="3">
         <v>1.15</v>
       </c>
       <c r="H72" s="3">
-        <v>34.55</v>
+        <v>42.88</v>
       </c>
       <c r="I72" s="3">
-        <v>-12.14</v>
+        <v>-9.54</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.010941501290329845</v>
+        <v>-0.009744696232501321</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L72" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.2727691649188815</v>
+        <v>-0.24514579671088366</v>
       </c>
       <c r="N72" s="3">
-        <v>-18.238741303458326</v>
+        <v>-13.956537901329934</v>
       </c>
       <c r="O72" s="3">
-        <v>12.658227848101266</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P72" s="3">
         <v>19.739671794345924</v>
       </c>
       <c r="Q72" s="3">
-        <v>38.35443037974683</v>
+        <v>41.51898734177215</v>
       </c>
       <c r="R72" s="3">
-        <v>28.10126582278481</v>
+        <v>29.746835443037973</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T72" s="3">
-        <v>0.63</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6557,49 +6551,49 @@
         <v>-1.26</v>
       </c>
       <c r="F73" s="2">
-        <v>0.31362469015228267</v>
+        <v>0.3346671731960124</v>
       </c>
       <c r="G73" s="2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>64.55</v>
+        <v>67.17</v>
       </c>
       <c r="I73" s="2">
-        <v>42.98</v>
+        <v>44.62</v>
       </c>
       <c r="J73" s="2">
-        <v>0.030617865994081703</v>
+        <v>0.03103910463020445</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M73" s="2">
-        <v>0.32716208797261337</v>
+        <v>0.3517366483815776</v>
       </c>
       <c r="N73" s="2">
-        <v>41.754383985691156</v>
+        <v>45.731706607916195</v>
       </c>
       <c r="O73" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>68.22784810126582</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="R73" s="2">
-        <v>62.151898734177216</v>
+        <v>62.65822784810127</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6619,34 +6613,34 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="2">
-        <v>0.20378191439857105</v>
+        <v>0.1830505137246994</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
       </c>
       <c r="H74" s="2">
-        <v>80.13</v>
+        <v>80.47</v>
       </c>
       <c r="I74" s="2">
-        <v>31.09</v>
+        <v>30.85</v>
       </c>
       <c r="J74" s="2">
-        <v>0.019894183659761838</v>
+        <v>0.01850987680405728</v>
       </c>
       <c r="K74" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.18705924650286843</v>
+        <v>0.1631361260082067</v>
       </c>
       <c r="N74" s="2">
-        <v>27.744099838716657</v>
+        <v>26.871654370579094</v>
       </c>
       <c r="O74" s="2">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
@@ -6655,13 +6649,13 @@
         <v>65.0632911392405</v>
       </c>
       <c r="R74" s="2">
-        <v>58.670886075949376</v>
+        <v>58.29113924050633</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6681,49 +6675,49 @@
         <v>-2.27</v>
       </c>
       <c r="F75" s="1">
-        <v>0.047742627284892966</v>
+        <v>0.055862293812288175</v>
       </c>
       <c r="G75" s="1">
         <v>0.96</v>
       </c>
       <c r="H75" s="1">
-        <v>61.96</v>
+        <v>64.97</v>
       </c>
       <c r="I75" s="1">
-        <v>16.2</v>
+        <v>18.36</v>
       </c>
       <c r="J75" s="1">
-        <v>0.006054596459029677</v>
+        <v>0.007826150800004537</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L75" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>0.04455735720952103</v>
+        <v>0.0520690771043848</v>
       </c>
       <c r="N75" s="1">
-        <v>13.493910909381924</v>
+        <v>15.764949480196902</v>
       </c>
       <c r="O75" s="1">
-        <v>64.55696202531645</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>60.379746835443036</v>
+        <v>61.51898734177215</v>
       </c>
       <c r="R75" s="1">
-        <v>45.69620253164557</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>-0.76</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6743,19 +6737,19 @@
         <v>3.5</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.019951222580168418</v>
+        <v>0.08522081436684652</v>
       </c>
       <c r="G76" s="1">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H76" s="1">
-        <v>53.36</v>
+        <v>49</v>
       </c>
       <c r="I76" s="1">
-        <v>14.87</v>
+        <v>11.89</v>
       </c>
       <c r="J76" s="1">
-        <v>0.015723621144014217</v>
+        <v>0.014257280253357972</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6764,28 +6758,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.043044430626614893</v>
+        <v>0.05866829741152291</v>
       </c>
       <c r="N76" s="1">
-        <v>4.7337321257683325</v>
+        <v>16.424871510910727</v>
       </c>
       <c r="O76" s="1">
-        <v>56.9620253164557</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>50.12658227848101</v>
+        <v>48.9873417721519</v>
       </c>
       <c r="R76" s="1">
-        <v>41.39240506329114</v>
+        <v>45.37974683544304</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>-0.82</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6805,19 +6799,19 @@
         <v>-0.19</v>
       </c>
       <c r="F77" s="2">
-        <v>0.021243186683114132</v>
+        <v>0.021049672747980433</v>
       </c>
       <c r="G77" s="2">
         <v>0.98</v>
       </c>
       <c r="H77" s="2">
-        <v>60.18</v>
+        <v>65.61</v>
       </c>
       <c r="I77" s="2">
-        <v>10.52</v>
+        <v>13.21</v>
       </c>
       <c r="J77" s="2">
-        <v>0.008170585819772246</v>
+        <v>0.009360371516803734</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6826,28 +6820,28 @@
         <v>8</v>
       </c>
       <c r="M77" s="2">
-        <v>0.01965055164542817</v>
+        <v>0.01915306439402875</v>
       </c>
       <c r="N77" s="2">
-        <v>11.003230352972645</v>
+        <v>12.473348209161312</v>
       </c>
       <c r="O77" s="2">
-        <v>63.29113924050633</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>63.67088607594937</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="R77" s="2">
-        <v>55.822784810126585</v>
+        <v>54.74683544303799</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>1.39</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6861,13 +6855,13 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D78" s="2">
-        <v>-0.7162471395881006</v>
+        <v>-0.7139588100686499</v>
       </c>
       <c r="E78" s="2">
         <v>0.93</v>
       </c>
       <c r="F78" s="2">
-        <v>0.1552823245490744</v>
+        <v>0.13771728086955823</v>
       </c>
       <c r="G78" s="2">
         <v>1.26</v>
@@ -6876,22 +6870,22 @@
         <v>62.3</v>
       </c>
       <c r="I78" s="2">
-        <v>31.26</v>
+        <v>30.84</v>
       </c>
       <c r="J78" s="2">
-        <v>0.028006030363875126</v>
+        <v>0.026771763612095684</v>
       </c>
       <c r="K78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M78" s="2">
-        <v>0.17598658003899192</v>
+        <v>0.16237318947093016</v>
       </c>
       <c r="N78" s="2">
-        <v>26.636833192329018</v>
+        <v>26.79536071685144</v>
       </c>
       <c r="O78" s="2">
         <v>77.21518987341773</v>
@@ -6900,16 +6894,16 @@
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="2">
-        <v>60.63291139240506</v>
+        <v>60</v>
       </c>
       <c r="R78" s="2">
-        <v>50.88607594936709</v>
+        <v>51.0126582278481</v>
       </c>
       <c r="S78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="2">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6929,49 +6923,49 @@
         <v>0.99</v>
       </c>
       <c r="F79" s="2">
-        <v>0.38942481400400625</v>
+        <v>0.35663309376848606</v>
       </c>
       <c r="G79" s="2">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="H79" s="2">
-        <v>79.38</v>
+        <v>76.82</v>
       </c>
       <c r="I79" s="2">
-        <v>49.56</v>
+        <v>47.79</v>
       </c>
       <c r="J79" s="2">
-        <v>0.04170852902060031</v>
+        <v>0.04473586149310199</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L79" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M79" s="2">
-        <v>0.38544322640979134</v>
+        <v>0.3499949645296552</v>
       </c>
       <c r="N79" s="2">
-        <v>47.582497829408965</v>
+        <v>45.55753822272394</v>
       </c>
       <c r="O79" s="2">
-        <v>89.87341772151899</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>66.32911392405063</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="R79" s="2">
-        <v>59.620253164556964</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>1.58</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6985,37 +6979,37 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8371559633027521</v>
+        <v>0.8428899082568806</v>
       </c>
       <c r="E80" s="2">
         <v>4.67</v>
       </c>
       <c r="F80" s="2">
-        <v>0.9241755093420445</v>
+        <v>0.935767665223101</v>
       </c>
       <c r="G80" s="2">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H80" s="2">
-        <v>58.78</v>
+        <v>62.02</v>
       </c>
       <c r="I80" s="2">
-        <v>58.68</v>
+        <v>63.24</v>
       </c>
       <c r="J80" s="2">
-        <v>0.05149076759945039</v>
+        <v>0.05099319169628612</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M80" s="2">
-        <v>0.9241755093420445</v>
+        <v>0.9348193610461251</v>
       </c>
       <c r="N80" s="2">
-        <v>101.45572612263425</v>
+        <v>104.03997787437092</v>
       </c>
       <c r="O80" s="2">
         <v>96.20253164556962</v>
@@ -7024,7 +7018,7 @@
         <v>14.059118714058641</v>
       </c>
       <c r="Q80" s="2">
-        <v>69.11392405063292</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="R80" s="2">
         <v>65.31645569620254</v>
@@ -7052,7 +7046,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7060,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38.734177215189874</v>
+        <v>36.075949367088604</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7068,7 +7062,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65.69620253164557</v>
+        <v>65.37974683544304</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7070,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>21.835443037974684</v>
+        <v>20.06329113924051</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7078,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>42.27848101265823</v>
+        <v>43.60759493670886</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7086,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>43.67088607594937</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7094,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.87341772151898</v>
+        <v>54.367088607594944</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7102,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.18987341772152</v>
+        <v>55.25316455696202</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7110,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.67088607594936</v>
+        <v>39.430379746835435</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7118,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35.9493670886076</v>
+        <v>37.59493670886076</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7126,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>51.26582278481013</v>
+        <v>52.784810126582286</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7134,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>26.645569620253163</v>
+        <v>31.07594936708861</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7142,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>8.670886075949369</v>
+        <v>7.278481012658229</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7150,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>40.31645569620253</v>
+        <v>42.59493670886076</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7166,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>28.924050632911392</v>
+        <v>26.898734177215186</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7174,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>16.582278481012658</v>
+        <v>15.443037974683545</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7182,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>30.189873417721518</v>
+        <v>29.43037974683544</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7190,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>41.64556962025317</v>
+        <v>40.8860759493671</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7198,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39.81012658227848</v>
+        <v>39.936708860759495</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7206,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>41.13924050632911</v>
+        <v>49.49367088607595</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7214,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>28.79746835443038</v>
+        <v>30.506329113924053</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7222,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>32.91139240506329</v>
+        <v>33.544303797468345</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7230,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>29.49367088607595</v>
+        <v>27.658227848101266</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7238,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.7721518987341796</v>
+        <v>6.0126582278481</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7246,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>32.278481012658226</v>
+        <v>32.78481012658228</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7254,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>23.164556962025316</v>
+        <v>22.658227848101262</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7262,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>18.734177215189877</v>
+        <v>16.07594936708861</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7270,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>24.36708860759493</v>
+        <v>25.506329113924046</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7278,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>44.9367088607595</v>
+        <v>47.34177215189874</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7286,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>59.620253164556964</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7294,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>15.379746835443036</v>
+        <v>17.91139240506329</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7302,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>42.59493670886076</v>
+        <v>41.9620253164557</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7318,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>23.417721518987342</v>
+        <v>23.79746835443038</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7326,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>28.29113924050633</v>
+        <v>32.46835443037974</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7334,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>37.21518987341772</v>
+        <v>36.708860759493675</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7342,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>55.56962025316456</v>
+        <v>55.31645569620253</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7350,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>54.11392405063292</v>
+        <v>45.12658227848101</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7358,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>33.60759493670885</v>
+        <v>31.835443037974677</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7366,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>32.08860759493672</v>
+        <v>30.44303797468355</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7374,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>39.11392405063291</v>
+        <v>38.101265822784804</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7382,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>47.34177215189873</v>
+        <v>45.82278481012658</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7398,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>54.68354430379747</v>
+        <v>55.822784810126585</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7406,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.0632911392405</v>
+        <v>23.670886075949362</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7414,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.632911392405056</v>
+        <v>26.012658227848096</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7422,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>33.86075949367089</v>
+        <v>33.48101265822785</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7430,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>55.75949367088608</v>
+        <v>54.62025316455696</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7446,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>61.13924050632911</v>
+        <v>60.12658227848101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7460,7 +7454,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>21.89873417721519</v>
+        <v>21.962025316455694</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7462,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>36.01265822784811</v>
+        <v>38.54430379746835</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7470,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>54.43037974683545</v>
+        <v>56.708860759493675</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7478,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>33.0379746835443</v>
+        <v>35.31645569620253</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7486,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>50</v>
+        <v>49.493670886075954</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7494,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>38.54430379746836</v>
+        <v>40.18987341772152</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7502,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>37.088607594936704</v>
+        <v>35.949367088607595</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7518,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>55.63291139240508</v>
+        <v>54.873417721519</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7526,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>31.202531645569614</v>
+        <v>30.063291139240505</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7534,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>42.27848101265823</v>
+        <v>36.20253164556962</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7558,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>37.151898734177216</v>
+        <v>35.50632911392405</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7566,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>32.72151898734177</v>
+        <v>31.20253164556962</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7574,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>42.784810126582286</v>
+        <v>43.16455696202532</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7582,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>44.87341772151899</v>
+        <v>45.75949367088607</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7590,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>28.29113924050633</v>
+        <v>28.924050632911392</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7598,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>27.531645569620256</v>
+        <v>27.151898734177212</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7614,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>28.10126582278481</v>
+        <v>29.746835443037973</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7622,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.151898734177216</v>
+        <v>62.65822784810127</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7630,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>58.670886075949376</v>
+        <v>58.29113924050633</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7638,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>45.69620253164557</v>
+        <v>46.835443037974684</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7646,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>41.39240506329114</v>
+        <v>45.37974683544304</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7654,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>55.822784810126585</v>
+        <v>54.74683544303799</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7662,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>50.88607594936709</v>
+        <v>51.0126582278481</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7670,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>59.620253164556964</v>
+        <v>58.9873417721519</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7703,10 +7697,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7714,7 +7708,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7725,10 +7719,10 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
         <v>133</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7736,10 +7730,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
         <v>135</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7747,10 +7741,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" t="s">
         <v>137</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7758,82 +7752,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" t="s">
         <v>139</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
         <v>141</v>
-      </c>
-      <c r="D7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s">
         <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" t="s">
         <v>145</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
         <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
         <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" t="s">
         <v>155</v>
-      </c>
-      <c r="D14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
         <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7852,15 +7846,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7868,98 +7862,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
         <v>143</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
         <v>147</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" t="s">
         <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
         <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
         <v>153</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" t="s">
         <v>155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -7978,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7989,7 +7983,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8000,10 +7994,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8011,90 +8005,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" t="s">
         <v>139</v>
-      </c>
-      <c r="D5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
         <v>143</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" t="s">
         <v>145</v>
-      </c>
-      <c r="D8" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
         <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
         <v>153</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" t="s">
         <v>155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -8113,10 +8107,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8124,7 +8118,7 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8132,106 +8126,106 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s">
         <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" t="s">
         <v>145</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
         <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
         <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" t="s">
         <v>155</v>
-      </c>
-      <c r="D14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -8247,212 +8241,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" t="s">
         <v>175</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>176</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>177</v>
-      </c>
-      <c r="D1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
         <v>179</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>180</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>181</v>
-      </c>
-      <c r="D2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
         <v>183</v>
       </c>
-      <c r="B3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" t="s">
-        <v>184</v>
-      </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" t="s">
         <v>185</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>186</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>187</v>
-      </c>
-      <c r="D4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" t="s">
         <v>189</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>190</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>191</v>
-      </c>
-      <c r="D5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
         <v>193</v>
       </c>
-      <c r="B6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>194</v>
-      </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" t="s">
         <v>195</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>196</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" t="s">
         <v>200</v>
       </c>
-      <c r="B9" t="s">
-        <v>201</v>
-      </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" t="s">
         <v>202</v>
       </c>
-      <c r="B11" t="s">
-        <v>203</v>
-      </c>
       <c r="C11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" t="s">
         <v>204</v>
       </c>
-      <c r="B12" t="s">
-        <v>205</v>
-      </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
         <v>206</v>
       </c>
-      <c r="B13" t="s">
-        <v>207</v>
-      </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" t="s">
         <v>208</v>
       </c>
-      <c r="B14" t="s">
-        <v>209</v>
-      </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" t="s">
         <v>210</v>
       </c>
-      <c r="B15" t="s">
-        <v>211</v>
-      </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="228">
   <si>
     <t>Ticker</t>
   </si>
@@ -313,7 +313,7 @@
     <t>2026-05-20</t>
   </si>
   <si>
-    <t>2026-04-21</t>
+    <t>2027-04-21</t>
   </si>
   <si>
     <t>2026-05-04</t>
@@ -667,6 +667,9 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
   </si>
   <si>
@@ -676,22 +679,25 @@
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
+    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
@@ -1363,7 +1369,7 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>72.02531645569621</v>
+        <v>72.34177215189874</v>
       </c>
       <c r="C2" t="s">
         <v>213</v>
@@ -1374,7 +1380,7 @@
         <v>63</v>
       </c>
       <c r="B3">
-        <v>67.40506329113924</v>
+        <v>67.02531645569621</v>
       </c>
       <c r="C3" t="s">
         <v>214</v>
@@ -1385,7 +1391,7 @@
         <v>58</v>
       </c>
       <c r="B4">
-        <v>66.77215189873418</v>
+        <v>66.39240506329114</v>
       </c>
       <c r="C4" t="s">
         <v>214</v>
@@ -1407,7 +1413,7 @@
         <v>127</v>
       </c>
       <c r="B6">
-        <v>65.31645569620254</v>
+        <v>64.9367088607595</v>
       </c>
       <c r="C6" t="s">
         <v>215</v>
@@ -1415,24 +1421,24 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B7">
-        <v>62.65822784810127</v>
+        <v>62.97468354430381</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B8">
-        <v>62.21518987341772</v>
+        <v>62.27848101265823</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1440,7 +1446,7 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>61.962025316455694</v>
+        <v>62.27848101265822</v>
       </c>
       <c r="C9" t="s">
         <v>214</v>
@@ -1451,29 +1457,29 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>60.12658227848101</v>
+        <v>59.36708860759494</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B11">
-        <v>60</v>
+        <v>59.36708860759494</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="B12">
-        <v>58.9873417721519</v>
+        <v>59.177215189873415</v>
       </c>
       <c r="C12" t="s">
         <v>217</v>
@@ -1484,10 +1490,10 @@
         <v>120</v>
       </c>
       <c r="B13">
-        <v>58.29113924050633</v>
+        <v>57.53164556962027</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1495,40 +1501,40 @@
         <v>53</v>
       </c>
       <c r="B14">
-        <v>56.708860759493675</v>
+        <v>56.139240506329116</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B15">
-        <v>55.822784810126585</v>
+        <v>55.8860759493671</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>55.31645569620253</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="B17">
-        <v>55.25316455696202</v>
+        <v>55.506329113924046</v>
       </c>
       <c r="C17" t="s">
         <v>219</v>
@@ -1536,90 +1542,90 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>54.873417721519</v>
+        <v>55.31645569620253</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="B19">
-        <v>54.74683544303799</v>
+        <v>54.36708860759494</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>54.62025316455696</v>
+        <v>54.177215189873415</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B21">
-        <v>52.784810126582286</v>
+        <v>54.11392405063291</v>
       </c>
       <c r="C21" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B22">
-        <v>52.21518987341772</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="B23">
-        <v>51.0126582278481</v>
+        <v>49.74683544303797</v>
       </c>
       <c r="C23" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>49.493670886075954</v>
+        <v>49.55696202531646</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="B25">
-        <v>49.49367088607595</v>
+        <v>48.607594936708864</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1627,18 +1633,18 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>47.34177215189874</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="C26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="B27">
-        <v>46.835443037974684</v>
+        <v>45.88607594936709</v>
       </c>
       <c r="C27" t="s">
         <v>221</v>
@@ -1646,21 +1652,21 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B28">
-        <v>45.82278481012658</v>
+        <v>45.12658227848102</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="B29">
-        <v>45.75949367088607</v>
+        <v>44.62025316455696</v>
       </c>
       <c r="C29" t="s">
         <v>221</v>
@@ -1668,10 +1674,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="B30">
-        <v>45.37974683544304</v>
+        <v>44.430379746835435</v>
       </c>
       <c r="C30" t="s">
         <v>221</v>
@@ -1679,43 +1685,43 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="B31">
-        <v>45.12658227848101</v>
+        <v>44.30379746835443</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>42.59493670886076</v>
+        <v>43.29113924050633</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B33">
-        <v>42.27848101265823</v>
+        <v>42.72151898734178</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B34">
-        <v>41.9620253164557</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="C34" t="s">
         <v>221</v>
@@ -1723,24 +1729,24 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>40.8860759493671</v>
+        <v>41.835443037974684</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B36">
-        <v>40.18987341772152</v>
+        <v>41.51898734177216</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1748,51 +1754,51 @@
         <v>19</v>
       </c>
       <c r="B37">
-        <v>39.936708860759495</v>
+        <v>40.25316455696203</v>
       </c>
       <c r="C37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B38">
-        <v>38.54430379746835</v>
+        <v>39.683544303797476</v>
       </c>
       <c r="C38" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>38.101265822784804</v>
+        <v>39.493670886075954</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>36.20253164556962</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>36.075949367088604</v>
+        <v>36.962025316455694</v>
       </c>
       <c r="C41" t="s">
         <v>221</v>
@@ -1800,13 +1806,13 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="B42">
-        <v>35.949367088607595</v>
+        <v>35.88607594936709</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1814,62 +1820,62 @@
         <v>64</v>
       </c>
       <c r="B43">
-        <v>35.50632911392405</v>
+        <v>34.74683544303797</v>
       </c>
       <c r="C43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B44">
-        <v>33.544303797468345</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B45">
         <v>32.78481012658228</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>31.835443037974677</v>
+        <v>32.0253164556962</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B47">
-        <v>31.20253164556962</v>
+        <v>30.949367088607595</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B48">
-        <v>30.506329113924053</v>
+        <v>30.88607594936709</v>
       </c>
       <c r="C48" t="s">
         <v>221</v>
@@ -1877,10 +1883,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>30.44303797468355</v>
+        <v>30.379746835443036</v>
       </c>
       <c r="C49" t="s">
         <v>221</v>
@@ -1888,24 +1894,24 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B50">
-        <v>30.063291139240505</v>
+        <v>30.253164556962027</v>
       </c>
       <c r="C50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B51">
-        <v>29.746835443037973</v>
+        <v>30.063291139240505</v>
       </c>
       <c r="C51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2146,7 @@
         <v>5.93</v>
       </c>
       <c r="C2" s="1">
-        <v>64.55696202531645</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="D2" s="1">
         <v>-1.5446880269814502</v>
@@ -2149,31 +2155,31 @@
         <v>0.4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.006404755019511793</v>
+        <v>0.027931860353250838</v>
       </c>
       <c r="G2" s="1">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>53.8</v>
+        <v>52.28</v>
       </c>
       <c r="I2" s="1">
-        <v>19.64</v>
+        <v>18.67</v>
       </c>
       <c r="J2" s="1">
-        <v>0.005125373750331907</v>
+        <v>0.005220301483400658</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1">
         <v>296</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.0704078833155315</v>
+        <v>-0.04360997786596865</v>
       </c>
       <c r="N2" s="1">
-        <v>3.517253438205291</v>
+        <v>5.438616630381111</v>
       </c>
       <c r="O2" s="1">
         <v>50.63291139240506</v>
@@ -2182,16 +2188,16 @@
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>44.68354430379747</v>
+        <v>44.05063291139241</v>
       </c>
       <c r="R2" s="1">
-        <v>36.075949367088604</v>
+        <v>35.88607594936709</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2211,19 +2217,19 @@
         <v>1.88</v>
       </c>
       <c r="F3" s="2">
-        <v>0.962473230590845</v>
+        <v>1.0235072208940463</v>
       </c>
       <c r="G3" s="2">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="H3" s="2">
-        <v>69.59</v>
+        <v>69.9</v>
       </c>
       <c r="I3" s="2">
-        <v>96.33</v>
+        <v>96.02</v>
       </c>
       <c r="J3" s="2">
-        <v>0.08574510564501076</v>
+        <v>0.08399036581141517</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -2232,10 +2238,10 @@
         <v>105</v>
       </c>
       <c r="M3" s="2">
-        <v>1.095235815367463</v>
+        <v>1.1482692070568317</v>
       </c>
       <c r="N3" s="2">
-        <v>120.08162330650471</v>
+        <v>124.62653512266115</v>
       </c>
       <c r="O3" s="2">
         <v>97.46835443037975</v>
@@ -2267,55 +2273,55 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D4" s="3">
-        <v>9.868354430379748</v>
+        <v>9.865822784810128</v>
       </c>
       <c r="E4" s="3">
         <v>1.25</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.18331120464487982</v>
+        <v>-0.14794108503638143</v>
       </c>
       <c r="G4" s="3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H4" s="3">
-        <v>63.4</v>
+        <v>61.71</v>
       </c>
       <c r="I4" s="3">
-        <v>-17.79</v>
+        <v>-18.42</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.009728224775035507</v>
+        <v>-0.00928318100321039</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>-93</v>
+        <v>-92</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.17382816287512137</v>
+        <v>-0.13834400917770562</v>
       </c>
       <c r="N4" s="3">
-        <v>-6.8247745177537125</v>
+        <v>-4.034786500792572</v>
       </c>
       <c r="O4" s="3">
-        <v>31.645569620253166</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>36.45569620253164</v>
+        <v>35.56962025316456</v>
       </c>
       <c r="R4" s="3">
-        <v>20.06329113924051</v>
+        <v>20.822784810126585</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>5.25</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2335,19 +2341,19 @@
         <v>0.73</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.16701604053351085</v>
+        <v>-0.15227828182852804</v>
       </c>
       <c r="G5" s="1">
         <v>1.79</v>
       </c>
       <c r="H5" s="1">
-        <v>55.17</v>
+        <v>55.38</v>
       </c>
       <c r="I5" s="1">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="J5" s="1">
-        <v>0.004706264373024448</v>
+        <v>0.0032827368053967737</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
@@ -2356,10 +2362,10 @@
         <v>-82</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.09210001055241923</v>
+        <v>-0.08335382793440194</v>
       </c>
       <c r="N5" s="1">
-        <v>1.3480407145165045</v>
+        <v>1.464231623537795</v>
       </c>
       <c r="O5" s="1">
         <v>46.835443037974684</v>
@@ -2368,16 +2374,16 @@
         <v>29.766948563835548</v>
       </c>
       <c r="Q5" s="1">
-        <v>58.9873417721519</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="R5" s="1">
-        <v>43.60759493670886</v>
+        <v>43.35443037974684</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.71</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2397,49 +2403,49 @@
         <v>-0.11</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.012762916788167739</v>
+        <v>-0.00911514220646606</v>
       </c>
       <c r="G6" s="1">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>41.72</v>
+        <v>45.77</v>
       </c>
       <c r="I6" s="1">
-        <v>-13.77</v>
+        <v>-12.47</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.010761659579127787</v>
+        <v>-0.009493616798490945</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M6" s="1">
-        <v>0.038445508768527814</v>
+        <v>0.03712531420351728</v>
       </c>
       <c r="N6" s="1">
-        <v>14.4025926466112</v>
+        <v>13.512145837329706</v>
       </c>
       <c r="O6" s="1">
-        <v>64.55696202531645</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>37.721518987341774</v>
+        <v>39.49367088607595</v>
       </c>
       <c r="R6" s="1">
-        <v>42.27848101265823</v>
+        <v>41.51898734177216</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>0.19</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2447,31 +2453,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>4.9</v>
+        <v>6.53</v>
       </c>
       <c r="C7" s="2">
-        <v>58.22784810126582</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>6.2693877551020405</v>
+        <v>4.895865237366003</v>
       </c>
       <c r="E7" s="2">
         <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.034815574041854425</v>
+        <v>-0.05064256088486585</v>
       </c>
       <c r="G7" s="2">
         <v>2.25</v>
       </c>
       <c r="H7" s="2">
-        <v>61.85</v>
+        <v>57.76</v>
       </c>
       <c r="I7" s="2">
-        <v>19.73</v>
+        <v>17.48</v>
       </c>
       <c r="J7" s="2">
-        <v>0.022580054089422926</v>
+        <v>0.02045657536540953</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2480,28 +2486,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.08372244808012597</v>
+        <v>0.05841511932735899</v>
       </c>
       <c r="N7" s="2">
-        <v>18.93028657777102</v>
+        <v>15.641126349713877</v>
       </c>
       <c r="O7" s="2">
-        <v>69.62025316455697</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>63.417721518987335</v>
+        <v>63.16455696202532</v>
       </c>
       <c r="R7" s="2">
-        <v>54.367088607594944</v>
+        <v>55.18987341772152</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.19</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2521,19 +2527,19 @@
         <v>0.19</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2496534716100896</v>
+        <v>0.2514365958976711</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>65.4</v>
+        <v>64.55</v>
       </c>
       <c r="I8" s="2">
-        <v>18.79</v>
+        <v>18.3</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03302739540391629</v>
+        <v>0.03218269509605345</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -2542,28 +2548,28 @@
         <v>-215</v>
       </c>
       <c r="M8" s="2">
-        <v>0.2164628254159351</v>
+        <v>0.22090044543824816</v>
       </c>
       <c r="N8" s="2">
-        <v>32.20432431135193</v>
+        <v>31.8896589608028</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>64.9367088607595</v>
+        <v>64.30379746835443</v>
       </c>
       <c r="R8" s="2">
-        <v>55.25316455696202</v>
+        <v>54.11392405063291</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.06</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2583,31 +2589,31 @@
         <v>2.36</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.1371895789028914</v>
+        <v>-0.12553678720538466</v>
       </c>
       <c r="G9" s="1">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>47.87</v>
+        <v>48.25</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.87</v>
+        <v>-15.62</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.01313251653666682</v>
+        <v>-0.012439115221174126</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.08882606587712338</v>
+        <v>-0.08191371512049472</v>
       </c>
       <c r="N9" s="1">
-        <v>1.6754351820460984</v>
+        <v>1.6082429049285185</v>
       </c>
       <c r="O9" s="1">
         <v>48.10126582278481</v>
@@ -2616,16 +2622,16 @@
         <v>34.04748479877408</v>
       </c>
       <c r="Q9" s="1">
-        <v>45.56962025316456</v>
+        <v>46.20253164556962</v>
       </c>
       <c r="R9" s="1">
-        <v>39.430379746835435</v>
+        <v>39.55696202531645</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-1.77</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2636,7 +2642,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" s="1">
-        <v>67.08860759493672</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="D10" s="1">
         <v>0.5663999999999999</v>
@@ -2645,31 +2651,31 @@
         <v>1.48</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.1625740792266629</v>
+        <v>-0.1527100445761728</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>51.4</v>
+        <v>50.15</v>
       </c>
       <c r="I10" s="1">
-        <v>-4.18</v>
+        <v>-4.58</v>
       </c>
       <c r="J10" s="1">
-        <v>0.001672895700534598</v>
+        <v>0.0017334524830326288</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-131</v>
+        <v>-130</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.12369360797065332</v>
+        <v>-0.11693912546656304</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.8113190273068986</v>
+        <v>-1.8942981296783155</v>
       </c>
       <c r="O10" s="1">
         <v>41.77215189873418</v>
@@ -2678,16 +2684,16 @@
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>47.72151898734178</v>
+        <v>46.20253164556962</v>
       </c>
       <c r="R10" s="1">
-        <v>37.59493670886076</v>
+        <v>37.15189873417721</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.2</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2701,55 +2707,55 @@
         <v>12.658227848101266</v>
       </c>
       <c r="D11" s="2">
-        <v>31.88970588235294</v>
+        <v>31.911764705882348</v>
       </c>
       <c r="E11" s="2">
         <v>5.47</v>
       </c>
       <c r="F11" s="2">
-        <v>0.23765850895622276</v>
+        <v>0.31313487053950356</v>
       </c>
       <c r="G11" s="2">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="H11" s="2">
-        <v>72.26</v>
+        <v>72.98</v>
       </c>
       <c r="I11" s="2">
-        <v>15.31</v>
+        <v>16.18</v>
       </c>
       <c r="J11" s="2">
-        <v>0.02318709521283926</v>
+        <v>0.024397799365266714</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.21964072959368175</v>
+        <v>0.29830302603064096</v>
       </c>
       <c r="N11" s="2">
-        <v>32.52211472912661</v>
+        <v>39.629917020042086</v>
       </c>
       <c r="O11" s="2">
-        <v>86.07594936708861</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>60.126582278481024</v>
+        <v>59.87341772151899</v>
       </c>
       <c r="R11" s="2">
-        <v>52.784810126582286</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>6.33</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2769,49 +2775,49 @@
         <v>5.82</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.16138872777707075</v>
+        <v>-0.11495934856439913</v>
       </c>
       <c r="G12" s="1">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H12" s="1">
-        <v>63.48</v>
+        <v>57.83</v>
       </c>
       <c r="I12" s="1">
-        <v>-25.74</v>
+        <v>-28.56</v>
       </c>
       <c r="J12" s="1">
-        <v>0.00036432772497650137</v>
+        <v>0.004737690201871549</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>-51</v>
+        <v>-50</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.17656159460868426</v>
+        <v>-0.1271738087481683</v>
       </c>
       <c r="N12" s="1">
-        <v>-7.098117691109997</v>
+        <v>-2.917766457838849</v>
       </c>
       <c r="O12" s="1">
-        <v>30.37974683544304</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P12" s="1">
         <v>49.40073075603063</v>
       </c>
       <c r="Q12" s="1">
-        <v>50.75949367088608</v>
+        <v>50.88607594936709</v>
       </c>
       <c r="R12" s="1">
-        <v>31.07594936708861</v>
+        <v>35.063291139240505</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="1">
-        <v>10.38</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2831,49 +2837,49 @@
         <v>1.61</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.3378974859954296</v>
+        <v>-0.3062912793813802</v>
       </c>
       <c r="G13" s="3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H13" s="3">
-        <v>39.34</v>
+        <v>40.75</v>
       </c>
       <c r="I13" s="3">
-        <v>-9.73</v>
+        <v>-8.77</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.0038188457370752706</v>
+        <v>-0.005272784783982098</v>
       </c>
       <c r="K13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3">
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.2980687105624442</v>
+        <v>-0.27139282171346824</v>
       </c>
       <c r="N13" s="3">
-        <v>-19.24882928648599</v>
+        <v>-17.339667754368836</v>
       </c>
       <c r="O13" s="3">
-        <v>10.126582278481013</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>22.27848101265823</v>
+        <v>22.405063291139236</v>
       </c>
       <c r="R13" s="3">
-        <v>7.278481012658229</v>
+        <v>7.405063291139241</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-8.61</v>
+        <v>-8.48</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2887,55 +2893,55 @@
         <v>44.303797468354425</v>
       </c>
       <c r="D14" s="1">
-        <v>7.580152671755725</v>
+        <v>7.572519083969465</v>
       </c>
       <c r="E14" s="1">
         <v>-0.14</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0208602774213386</v>
+        <v>0.1390879511097546</v>
       </c>
       <c r="G14" s="1">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="H14" s="1">
-        <v>66.65</v>
+        <v>67.12</v>
       </c>
       <c r="I14" s="1">
-        <v>4.73</v>
+        <v>5.25</v>
       </c>
       <c r="J14" s="1">
-        <v>0.008917514457697458</v>
+        <v>0.008708453415281732</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.017071889657695127</v>
+        <v>0.10593441632523826</v>
       </c>
       <c r="N14" s="1">
-        <v>8.850852803988923</v>
+        <v>20.39305604950182</v>
       </c>
       <c r="O14" s="1">
-        <v>59.49367088607595</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>57.46835443037975</v>
+        <v>57.088607594936704</v>
       </c>
       <c r="R14" s="1">
-        <v>42.59493670886076</v>
+        <v>45.12658227848102</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>7.41</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2955,31 +2961,31 @@
         <v>5.49</v>
       </c>
       <c r="F15" s="2">
-        <v>1.4466921517094573</v>
+        <v>1.4820291768170744</v>
       </c>
       <c r="G15" s="2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H15" s="2">
-        <v>67.94</v>
+        <v>67.42</v>
       </c>
       <c r="I15" s="2">
-        <v>157.57</v>
+        <v>153.88</v>
       </c>
       <c r="J15" s="2">
-        <v>0.10034053155023638</v>
+        <v>0.0983215951414108</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M15" s="2">
-        <v>1.5604886529465585</v>
+        <v>1.588469472704206</v>
       </c>
       <c r="N15" s="2">
-        <v>166.6069070644143</v>
+        <v>168.6465616873986</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2991,13 +2997,13 @@
         <v>70.63291139240506</v>
       </c>
       <c r="R15" s="2">
-        <v>61.962025316455694</v>
+        <v>62.27848101265822</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T15" s="2">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -3017,49 +3023,49 @@
         <v>8.13</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2526403325969223</v>
+        <v>-0.19875093049323717</v>
       </c>
       <c r="G16" s="3">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H16" s="3">
-        <v>41.69</v>
+        <v>42.53</v>
       </c>
       <c r="I16" s="3">
-        <v>-7.24</v>
+        <v>-6.43</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.0060341985187148395</v>
+        <v>-0.005908702053133881</v>
       </c>
       <c r="K16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
         <v>16</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.16539634831514471</v>
+        <v>-0.11935693929873747</v>
       </c>
       <c r="N16" s="3">
-        <v>-5.981593061756044</v>
+        <v>-2.1360795128957664</v>
       </c>
       <c r="O16" s="3">
-        <v>34.177215189873415</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="3">
-        <v>35.56962025316456</v>
+        <v>36.202531645569614</v>
       </c>
       <c r="R16" s="3">
-        <v>26.898734177215186</v>
+        <v>28.924050632911392</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="3">
-        <v>-9.75</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3079,49 +3085,49 @@
         <v>4.24</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.28626343485356553</v>
+        <v>-0.2274051678141531</v>
       </c>
       <c r="G17" s="3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>42.03</v>
+        <v>45.88</v>
       </c>
       <c r="I17" s="3">
-        <v>-12.99</v>
+        <v>-10.53</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.016150723998906397</v>
+        <v>-0.012522925267832436</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.21703722993432895</v>
+        <v>-0.16458794401191157</v>
       </c>
       <c r="N17" s="3">
-        <v>-11.145681223674469</v>
+        <v>-6.659179984213176</v>
       </c>
       <c r="O17" s="3">
-        <v>21.518987341772153</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>22.78481012658228</v>
+        <v>25.443037974683545</v>
       </c>
       <c r="R17" s="3">
-        <v>15.443037974683545</v>
+        <v>18.354430379746837</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-7.72</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3141,19 +3147,19 @@
         <v>8.39</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.32891554685912827</v>
+        <v>-0.3225300756883653</v>
       </c>
       <c r="G18" s="3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="H18" s="3">
-        <v>38.13</v>
+        <v>36.75</v>
       </c>
       <c r="I18" s="3">
-        <v>-9.89</v>
+        <v>-11.53</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.011080273503358553</v>
+        <v>-0.010395965688135948</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>0</v>
@@ -3162,28 +3168,28 @@
         <v>37</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.30615624661170804</v>
+        <v>-0.3033359239710137</v>
       </c>
       <c r="N18" s="3">
-        <v>-20.057582891412373</v>
+        <v>-20.533977980123392</v>
       </c>
       <c r="O18" s="3">
-        <v>7.59493670886076</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P18" s="3">
         <v>33.93532173431426</v>
       </c>
       <c r="Q18" s="3">
-        <v>46.582278481012665</v>
+        <v>46.58227848101266</v>
       </c>
       <c r="R18" s="3">
-        <v>29.43037974683544</v>
+        <v>28.797468354430382</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T18" s="3">
-        <v>-1.52</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3203,49 +3209,49 @@
         <v>-0.16</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.05199845931261464</v>
+        <v>-0.0406580050888016</v>
       </c>
       <c r="G19" s="1">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H19" s="1">
-        <v>47.99</v>
+        <v>49.93</v>
       </c>
       <c r="I19" s="1">
-        <v>11.38</v>
+        <v>12.18</v>
       </c>
       <c r="J19" s="1">
-        <v>0.001624719483051169</v>
+        <v>0.0013611008632546321</v>
       </c>
       <c r="K19" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
         <v>80</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.12786279347068208</v>
+        <v>-0.1113273818663233</v>
       </c>
       <c r="N19" s="1">
-        <v>-2.2282375773097804</v>
+        <v>-1.3331237696543423</v>
       </c>
       <c r="O19" s="1">
-        <v>40.50632911392405</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>50.379746835443036</v>
+        <v>50.63291139240507</v>
       </c>
       <c r="R19" s="1">
-        <v>40.8860759493671</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3256,7 +3262,7 @@
         <v>6.07</v>
       </c>
       <c r="C20" s="1">
-        <v>65.82278481012658</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="D20" s="1">
         <v>0.6392092257001646</v>
@@ -3265,19 +3271,19 @@
         <v>-3.42</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.052572222114560974</v>
+        <v>-0.04631973281214208</v>
       </c>
       <c r="G20" s="1">
         <v>1.06</v>
       </c>
       <c r="H20" s="1">
-        <v>61.66</v>
+        <v>60.82</v>
       </c>
       <c r="I20" s="1">
-        <v>-1.58</v>
+        <v>-1.99</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.00206880999129</v>
+        <v>0.001973531003116155</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>1</v>
@@ -3286,10 +3292,10 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.046882397052705915</v>
+        <v>-0.041084964161955284</v>
       </c>
       <c r="N20" s="1">
-        <v>5.869802064487831</v>
+        <v>5.691118000782456</v>
       </c>
       <c r="O20" s="1">
         <v>53.16455696202531</v>
@@ -3298,78 +3304,78 @@
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>50</v>
+        <v>50.63291139240507</v>
       </c>
       <c r="R20" s="1">
-        <v>39.936708860759495</v>
+        <v>40.25316455696203</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>12.53</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>1.02</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>41.77215189873418</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>14.009803921568627</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>4.96</v>
       </c>
-      <c r="F21" s="1">
-        <v>0.06804873915608012</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.29</v>
-      </c>
-      <c r="H21" s="1">
-        <v>70.56</v>
-      </c>
-      <c r="I21" s="1">
-        <v>44.8</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0.022507725535026318</v>
-      </c>
-      <c r="K21" s="1" t="b">
+      <c r="F21" s="2">
+        <v>0.20951273348804555</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.36</v>
+      </c>
+      <c r="H21" s="2">
+        <v>77.28</v>
+      </c>
+      <c r="I21" s="2">
+        <v>69.13</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.029735763076465374</v>
+      </c>
+      <c r="K21" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L21" s="1">
-        <v>36</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0.09554956028837958</v>
-      </c>
-      <c r="N21" s="1">
-        <v>20.1129977985964</v>
-      </c>
-      <c r="O21" s="1">
-        <v>70.88607594936708</v>
-      </c>
-      <c r="P21" s="1">
+      <c r="L21" s="2">
+        <v>37</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.24092134538916632</v>
+      </c>
+      <c r="N21" s="2">
+        <v>33.89174895589461</v>
+      </c>
+      <c r="O21" s="2">
+        <v>83.54430379746836</v>
+      </c>
+      <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
-      <c r="Q21" s="1">
-        <v>67.34177215189874</v>
-      </c>
-      <c r="R21" s="1">
-        <v>49.49367088607595</v>
-      </c>
-      <c r="S21" s="1" t="s">
+      <c r="Q21" s="2">
+        <v>69.62025316455696</v>
+      </c>
+      <c r="R21" s="2">
+        <v>54.177215189873415</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T21" s="1">
-        <v>10.7</v>
+      <c r="T21" s="2">
+        <v>15.38</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3389,49 +3395,49 @@
         <v>-0.12</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.24299348474188467</v>
+        <v>-0.2510743485294993</v>
       </c>
       <c r="G22" s="1">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H22" s="1">
-        <v>54.12</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.012993468467941877</v>
+        <v>-0.011362562556863336</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.2088545343707543</v>
+        <v>-0.21879327518668068</v>
       </c>
       <c r="N22" s="1">
-        <v>-10.327411667317</v>
+        <v>-12.079713101690079</v>
       </c>
       <c r="O22" s="1">
-        <v>22.78481012658228</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P22" s="1">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="1">
-        <v>45.189873417721515</v>
+        <v>46.70886075949367</v>
       </c>
       <c r="R22" s="1">
-        <v>30.506329113924053</v>
+        <v>30.379746835443036</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3445,55 +3451,55 @@
         <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.7695383496910214</v>
+        <v>-0.7684478371501272</v>
       </c>
       <c r="E23" s="1">
         <v>-0.36</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.18994217139195058</v>
+        <v>-0.19169843777180187</v>
       </c>
       <c r="G23" s="1">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="H23" s="1">
-        <v>42.66</v>
+        <v>43.84</v>
       </c>
       <c r="I23" s="1">
-        <v>-9.83</v>
+        <v>-9.38</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.007152481007156544</v>
+        <v>-0.007105358471664092</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.16718287114453034</v>
+        <v>-0.1716318246127525</v>
       </c>
       <c r="N23" s="1">
-        <v>-6.160245344694604</v>
+        <v>-7.363568044297268</v>
       </c>
       <c r="O23" s="1">
-        <v>32.91139240506329</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>43.291139240506325</v>
+        <v>43.417721518987335</v>
       </c>
       <c r="R23" s="1">
-        <v>33.544303797468345</v>
+        <v>32.0253164556962</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>1.58</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3513,49 +3519,49 @@
         <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.06841393094452197</v>
+        <v>-0.0634294303244769</v>
       </c>
       <c r="G24" s="3">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="H24" s="3">
-        <v>48.09</v>
+        <v>47.53</v>
       </c>
       <c r="I24" s="3">
-        <v>-22.77</v>
+        <v>-22.84</v>
       </c>
       <c r="J24" s="3">
-        <v>0.021818737762920145</v>
+        <v>0.019851032629593705</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="M24" s="3">
-        <v>0.1753002425382697</v>
+        <v>0.15992069875015957</v>
       </c>
       <c r="N24" s="3">
-        <v>28.088066023585405</v>
+        <v>25.79168429199395</v>
       </c>
       <c r="O24" s="3">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>25.06329113924051</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="R24" s="3">
-        <v>27.658227848101266</v>
+        <v>27.151898734177212</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-3.35</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3575,19 +3581,19 @@
         <v>14.49</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.5125223711058603</v>
+        <v>-0.3605580055909993</v>
       </c>
       <c r="G25" s="3">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="H25" s="3">
-        <v>41.83</v>
+        <v>48</v>
       </c>
       <c r="I25" s="3">
-        <v>-55.45</v>
+        <v>-51.07</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.010958903546823775</v>
+        <v>-0.011950955072586474</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3596,28 +3602,28 @@
         <v>40</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.3958809573378316</v>
+        <v>-0.25499017114556566</v>
       </c>
       <c r="N25" s="3">
-        <v>-29.03005396402472</v>
+        <v>-15.699402697578583</v>
       </c>
       <c r="O25" s="3">
-        <v>2.5316455696202533</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>22.025316455696203</v>
+        <v>23.16455696202532</v>
       </c>
       <c r="R25" s="3">
-        <v>6.0126582278481</v>
+        <v>9.303797468354428</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-5.95</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3637,49 +3643,49 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="1">
-        <v>0.2705138622877369</v>
+        <v>0.5692307679270818</v>
       </c>
       <c r="G26" s="1">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="H26" s="1">
-        <v>58.19</v>
+        <v>65.13</v>
       </c>
       <c r="I26" s="1">
-        <v>11.31</v>
+        <v>24.7</v>
       </c>
       <c r="J26" s="1">
-        <v>0.041701520339968344</v>
+        <v>0.043476688115520065</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-29</v>
+        <v>-27</v>
       </c>
       <c r="M26" s="1">
-        <v>0.46396791439080887</v>
+        <v>0.7480853634751305</v>
       </c>
       <c r="N26" s="1">
-        <v>56.954833208839325</v>
+        <v>84.60815076449106</v>
       </c>
       <c r="O26" s="1">
-        <v>91.13924050632912</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P26" s="1">
         <v>50.63126652197354</v>
       </c>
       <c r="Q26" s="1">
-        <v>38.48101265822785</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="R26" s="1">
-        <v>32.78481012658228</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3699,49 +3705,49 @@
         <v>5.04</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.27581839557369814</v>
+        <v>-0.1847643877404258</v>
       </c>
       <c r="G27" s="3">
         <v>2.61</v>
       </c>
       <c r="H27" s="3">
-        <v>53.31</v>
+        <v>56.59</v>
       </c>
       <c r="I27" s="3">
-        <v>-22.8</v>
+        <v>-19.99</v>
       </c>
       <c r="J27" s="3">
-        <v>0.005309580651560144</v>
+        <v>0.004046042404553266</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.1231414230805874</v>
+        <v>-0.0442980956270802</v>
       </c>
       <c r="N27" s="3">
-        <v>-1.756100538300305</v>
+        <v>5.3698048542699635</v>
       </c>
       <c r="O27" s="3">
-        <v>43.037974683544306</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>34.683544303797476</v>
+        <v>35.189873417721515</v>
       </c>
       <c r="R27" s="3">
-        <v>22.658227848101262</v>
+        <v>24.303797468354432</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>-3.73</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3761,49 +3767,49 @@
         <v>-1.13</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.5081224308291079</v>
+        <v>-0.3989686198894955</v>
       </c>
       <c r="G28" s="3">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="H28" s="3">
-        <v>43.84</v>
+        <v>51.8</v>
       </c>
       <c r="I28" s="3">
-        <v>-28.47</v>
+        <v>-24.07</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.007637735377120385</v>
+        <v>-0.007510875574774697</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.30613364113325336</v>
+        <v>-0.21487925569125998</v>
       </c>
       <c r="N28" s="3">
-        <v>-20.05532234356691</v>
+        <v>-11.688311152148007</v>
       </c>
       <c r="O28" s="3">
-        <v>8.860759493670885</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>32.151898734177216</v>
+        <v>34.68354430379747</v>
       </c>
       <c r="R28" s="3">
-        <v>16.07594936708861</v>
+        <v>20.379746835443044</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-5.82</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3823,49 +3829,49 @@
         <v>0.88</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.3997854114255175</v>
+        <v>-0.37289377927431483</v>
       </c>
       <c r="G29" s="3">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>43.27</v>
+        <v>42.98</v>
       </c>
       <c r="I29" s="3">
-        <v>-32.91</v>
+        <v>-33</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.01824777471718841</v>
+        <v>-0.0185385326743265</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-70</v>
+        <v>-69</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.2926270394272472</v>
+        <v>-0.27517809780416136</v>
       </c>
       <c r="N29" s="3">
-        <v>-18.704662172966287</v>
+        <v>-17.718195363438152</v>
       </c>
       <c r="O29" s="3">
-        <v>11.39240506329114</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.13924050632911</v>
+        <v>41.39240506329114</v>
       </c>
       <c r="R29" s="3">
-        <v>25.506329113924046</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3885,49 +3891,49 @@
         <v>2.51</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.17379561096699297</v>
+        <v>-0.16897292648512433</v>
       </c>
       <c r="G30" s="1">
         <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>47.32</v>
+        <v>45.31</v>
       </c>
       <c r="I30" s="1">
-        <v>1.17</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.001442740576152576</v>
+        <v>-0.001111231471188121</v>
       </c>
       <c r="K30" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.15482952742747613</v>
+        <v>-0.15152369765116835</v>
       </c>
       <c r="N30" s="1">
-        <v>-4.924910972989183</v>
+        <v>-5.352755348138846</v>
       </c>
       <c r="O30" s="1">
-        <v>35.44303797468354</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>62.0253164556962</v>
+        <v>60.63291139240506</v>
       </c>
       <c r="R30" s="1">
-        <v>47.34177215189874</v>
+        <v>46.07594936708861</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.19</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3938,7 +3944,7 @@
         <v>5.13</v>
       </c>
       <c r="C31" s="2">
-        <v>59.49367088607595</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="D31" s="2">
         <v>10.83625730994152</v>
@@ -3947,49 +3953,49 @@
         <v>0.99</v>
       </c>
       <c r="F31" s="2">
-        <v>0.10445846119607602</v>
+        <v>0.11075290164967816</v>
       </c>
       <c r="G31" s="2">
         <v>1.43</v>
       </c>
       <c r="H31" s="2">
-        <v>54.77</v>
+        <v>53.28</v>
       </c>
       <c r="I31" s="2">
-        <v>19.81</v>
+        <v>18.69</v>
       </c>
       <c r="J31" s="2">
-        <v>0.02439872967559199</v>
+        <v>0.021555994091210093</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M31" s="2">
-        <v>0.1452355408060373</v>
+        <v>0.1482687436426835</v>
       </c>
       <c r="N31" s="2">
-        <v>25.081595850362167</v>
+        <v>24.626488781246344</v>
       </c>
       <c r="O31" s="2">
-        <v>75.9493670886076</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>67.46835443037975</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="R31" s="2">
-        <v>60</v>
+        <v>59.177215189873415</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-0.82</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4009,49 +4015,49 @@
         <v>1.51</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.2846308670655817</v>
+        <v>-0.22456277578446823</v>
       </c>
       <c r="G32" s="3">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H32" s="3">
-        <v>40.34</v>
+        <v>44.69</v>
       </c>
       <c r="I32" s="3">
-        <v>-10.53</v>
+        <v>-7.85</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.012341235670792932</v>
+        <v>-0.015048619622600816</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L32" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.22488770391610358</v>
+        <v>-0.17134262784090248</v>
       </c>
       <c r="N32" s="3">
-        <v>-11.930728621851927</v>
+        <v>-7.334648367112265</v>
       </c>
       <c r="O32" s="3">
-        <v>20.253164556962027</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P32" s="3">
         <v>40.689656926297594</v>
       </c>
       <c r="Q32" s="3">
-        <v>29.620253164556956</v>
+        <v>30.50632911392405</v>
       </c>
       <c r="R32" s="3">
-        <v>17.91139240506329</v>
+        <v>19.81012658227848</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-11.46</v>
+        <v>-9.56</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4071,31 +4077,31 @@
         <v>0.66</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.05739677304831063</v>
+        <v>-0.05081724524320652</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>56.36</v>
+        <v>54.83</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.76</v>
+        <v>-9.08</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0026763281941871143</v>
+        <v>0.0031762123683346044</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.04886203545552803</v>
+        <v>-0.04296509226792633</v>
       </c>
       <c r="N33" s="1">
-        <v>5.671838224205635</v>
+        <v>5.5031051901853605</v>
       </c>
       <c r="O33" s="1">
         <v>51.89873417721519</v>
@@ -4104,78 +4110,78 @@
         <v>26.894390179645494</v>
       </c>
       <c r="Q33" s="1">
-        <v>52.40506329113923</v>
+        <v>51.01265822784809</v>
       </c>
       <c r="R33" s="1">
-        <v>41.9620253164557</v>
+        <v>41.835443037974684</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>13.11</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>84.81012658227847</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>-0.7170099160945842</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="1">
         <v>0.94</v>
       </c>
-      <c r="F34" s="2">
-        <v>0.15393073932486953</v>
-      </c>
-      <c r="G34" s="2">
+      <c r="F34" s="1">
+        <v>0.11006463623909721</v>
+      </c>
+      <c r="G34" s="1">
         <v>1.26</v>
       </c>
-      <c r="H34" s="2">
-        <v>62.7</v>
-      </c>
-      <c r="I34" s="2">
-        <v>32.15</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0.027697165010491343</v>
-      </c>
-      <c r="K34" s="2" t="b">
+      <c r="H34" s="1">
+        <v>61.59</v>
+      </c>
+      <c r="I34" s="1">
+        <v>31.3</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.02638572750280521</v>
+      </c>
+      <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L34" s="2">
-        <v>36</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0.17858664792624146</v>
-      </c>
-      <c r="N34" s="2">
-        <v>28.416706562382576</v>
-      </c>
-      <c r="O34" s="2">
-        <v>81.0126582278481</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="L34" s="1">
+        <v>38</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0.13274863372323997</v>
+      </c>
+      <c r="N34" s="1">
+        <v>23.07447778930199</v>
+      </c>
+      <c r="O34" s="1">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="P34" s="1">
         <v>20.42247430615109</v>
       </c>
-      <c r="Q34" s="2">
-        <v>60.37974683544304</v>
-      </c>
-      <c r="R34" s="2">
-        <v>52.21518987341772</v>
-      </c>
-      <c r="S34" s="2" t="s">
+      <c r="Q34" s="1">
+        <v>59.87341772151899</v>
+      </c>
+      <c r="R34" s="1">
+        <v>49.55696202531646</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="T34" s="2">
-        <v>1.08</v>
+      <c r="T34" s="1">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4195,34 +4201,34 @@
         <v>4.55</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.286104456782967</v>
+        <v>-0.27603505142950363</v>
       </c>
       <c r="G35" s="3">
         <v>1.01</v>
       </c>
       <c r="H35" s="3">
-        <v>38.24</v>
+        <v>38.67</v>
       </c>
       <c r="I35" s="3">
-        <v>-21.69</v>
+        <v>-21.44</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.026985346199492784</v>
+        <v>-0.025712962349870347</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.28515615260599114</v>
+        <v>-0.27516258998780585</v>
       </c>
       <c r="N35" s="3">
-        <v>-17.957573490840687</v>
+        <v>-17.7166445818026</v>
       </c>
       <c r="O35" s="3">
-        <v>12.658227848101266</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P35" s="3">
         <v>29.3533388963776</v>
@@ -4231,13 +4237,13 @@
         <v>33.67088607594936</v>
       </c>
       <c r="R35" s="3">
-        <v>23.79746835443038</v>
+        <v>23.037974683544306</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4251,25 +4257,25 @@
         <v>82.27848101265823</v>
       </c>
       <c r="D36" s="1">
-        <v>0.38488271068635965</v>
+        <v>0.40225890529973946</v>
       </c>
       <c r="E36" s="1">
         <v>-1.05</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.1545146126968847</v>
+        <v>-0.13902466219710818</v>
       </c>
       <c r="G36" s="1">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>45.39</v>
+        <v>47.71</v>
       </c>
       <c r="I36" s="1">
-        <v>-13.36</v>
+        <v>-11.87</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.017864087744349548</v>
+        <v>-0.015729673228476845</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
@@ -4278,28 +4284,28 @@
         <v>-56</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.14123835421922293</v>
+        <v>-0.1285551248967346</v>
       </c>
       <c r="N36" s="1">
-        <v>-3.5657936521638587</v>
+        <v>-3.0558980726954723</v>
       </c>
       <c r="O36" s="1">
-        <v>37.9746835443038</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="1">
-        <v>40.12658227848101</v>
+        <v>40.75949367088607</v>
       </c>
       <c r="R36" s="1">
-        <v>32.46835443037974</v>
+        <v>31.83544303797468</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>-1.84</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4310,58 +4316,58 @@
         <v>5.33</v>
       </c>
       <c r="C37" s="1">
-        <v>63.29113924050633</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="D37" s="1">
-        <v>0.6022514071294557</v>
+        <v>0.5722326454033773</v>
       </c>
       <c r="E37" s="1">
         <v>1.72</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.07918061209309032</v>
+        <v>-0.06665182461711225</v>
       </c>
       <c r="G37" s="1">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H37" s="1">
-        <v>36.85</v>
+        <v>36.52</v>
       </c>
       <c r="I37" s="1">
-        <v>-22.79</v>
+        <v>-22.77</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.004481032438917695</v>
+        <v>-0.004296391795720951</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-208</v>
+        <v>-209</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.042196749191032445</v>
+        <v>-0.034370751274293676</v>
       </c>
       <c r="N37" s="1">
-        <v>6.338366850655194</v>
+        <v>6.362539289548609</v>
       </c>
       <c r="O37" s="1">
-        <v>56.9620253164557</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P37" s="1">
         <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
-        <v>37.08860759493671</v>
+        <v>36.835443037974684</v>
       </c>
       <c r="R37" s="1">
-        <v>36.708860759493675</v>
+        <v>35.63291139240506</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>-2.09</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4381,19 +4387,19 @@
         <v>-0.05</v>
       </c>
       <c r="F38" s="2">
-        <v>0.42591886847537525</v>
+        <v>0.5587780956043003</v>
       </c>
       <c r="G38" s="2">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="H38" s="2">
-        <v>86.58</v>
+        <v>85.71</v>
       </c>
       <c r="I38" s="2">
-        <v>40.38</v>
+        <v>39.66</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04252872102580373</v>
+        <v>0.04374023280066799</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
@@ -4402,10 +4408,10 @@
         <v>-43</v>
       </c>
       <c r="M38" s="2">
-        <v>0.43445360606815786</v>
+        <v>0.5701200943463716</v>
       </c>
       <c r="N38" s="2">
-        <v>54.00340237657421</v>
+        <v>66.81162385161515</v>
       </c>
       <c r="O38" s="2">
         <v>89.87341772151899</v>
@@ -4431,31 +4437,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>-0.18</v>
+        <v>-0.25</v>
       </c>
       <c r="C39" s="1">
         <v>22.78481012658228</v>
       </c>
       <c r="D39" s="1">
-        <v>79.72222222222223</v>
+        <v>58.28</v>
       </c>
       <c r="E39" s="1">
         <v>-6.6</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.1448679734272538</v>
+        <v>-0.14020282536088596</v>
       </c>
       <c r="G39" s="1">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="H39" s="1">
-        <v>34.08</v>
+        <v>32.73</v>
       </c>
       <c r="I39" s="1">
-        <v>-5.73</v>
+        <v>-7.44</v>
       </c>
       <c r="J39" s="1">
-        <v>0.014175230667651575</v>
+        <v>0.011332756504892363</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4464,28 +4470,28 @@
         <v>-4</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.11547054394100265</v>
+        <v>-0.11577390499334761</v>
       </c>
       <c r="N39" s="1">
-        <v>-0.9890126243418337</v>
+        <v>-1.7777760823567708</v>
       </c>
       <c r="O39" s="1">
-        <v>44.303797468354425</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P39" s="1">
-        <v>18.53526322746658</v>
+        <v>20.072334383381026</v>
       </c>
       <c r="Q39" s="1">
-        <v>50.88607594936709</v>
+        <v>49.49367088607595</v>
       </c>
       <c r="R39" s="1">
-        <v>45.12658227848101</v>
+        <v>43.29113924050633</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1">
-        <v>-8.29</v>
+        <v>-10.13</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4505,49 +4511,49 @@
         <v>10.16</v>
       </c>
       <c r="F40" s="1">
-        <v>0.13135696449196702</v>
+        <v>0.12113538137666495</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>43.69</v>
+        <v>41.58</v>
       </c>
       <c r="I40" s="1">
-        <v>-17.9</v>
+        <v>-20.06</v>
       </c>
       <c r="J40" s="1">
-        <v>0.0021799008175573333</v>
+        <v>0.00021513960292798547</v>
       </c>
       <c r="K40" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M40" s="1">
-        <v>0.03652654679438272</v>
+        <v>0.03388923720688508</v>
       </c>
       <c r="N40" s="1">
-        <v>14.210696449196705</v>
+        <v>13.188538137666503</v>
       </c>
       <c r="O40" s="1">
-        <v>62.0253164556962</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P40" s="1">
         <v>45.29877115964868</v>
       </c>
       <c r="Q40" s="1">
-        <v>34.93670886075949</v>
+        <v>32.15189873417721</v>
       </c>
       <c r="R40" s="1">
-        <v>31.835443037974677</v>
+        <v>30.949367088607595</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-8.92</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4561,25 +4567,25 @@
         <v>5.063291139240507</v>
       </c>
       <c r="D41" s="1">
-        <v>7.405566600397614</v>
+        <v>7.121272365805169</v>
       </c>
       <c r="E41" s="1">
         <v>-1.71</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.048158066060495386</v>
+        <v>-0.022102909273169644</v>
       </c>
       <c r="G41" s="1">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H41" s="1">
-        <v>60.44</v>
+        <v>60.76</v>
       </c>
       <c r="I41" s="1">
-        <v>-11.73</v>
+        <v>-11.29</v>
       </c>
       <c r="J41" s="1">
-        <v>0.022054052318726453</v>
+        <v>0.021516600527013423</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -4588,28 +4594,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.04246824099864033</v>
+        <v>-0.015123217739587247</v>
       </c>
       <c r="N41" s="1">
-        <v>6.31121766989439</v>
+        <v>8.287292643019267</v>
       </c>
       <c r="O41" s="1">
-        <v>55.69620253164557</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>42.78481012658228</v>
+        <v>43.41772151898734</v>
       </c>
       <c r="R41" s="1">
-        <v>30.44303797468355</v>
+        <v>30.88607594936709</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4623,25 +4629,25 @@
         <v>53.16455696202531</v>
       </c>
       <c r="D42" s="1">
-        <v>1.0692520775623269</v>
+        <v>1.0637119113573408</v>
       </c>
       <c r="E42" s="1">
         <v>0.29</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.08407063074083401</v>
+        <v>-0.07142306224176825</v>
       </c>
       <c r="G42" s="1">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>41.56</v>
+        <v>45.57</v>
       </c>
       <c r="I42" s="1">
-        <v>-0.87</v>
+        <v>0.07</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.0059719137821893946</v>
+        <v>-0.005283726792209556</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4650,28 +4656,28 @@
         <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.14381379389031212</v>
+        <v>-0.12726059451042737</v>
       </c>
       <c r="N42" s="1">
-        <v>-3.823337619272786</v>
+        <v>-2.9264450340647534</v>
       </c>
       <c r="O42" s="1">
-        <v>36.708860759493675</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>42.278481012658226</v>
+        <v>44.81012658227848</v>
       </c>
       <c r="R42" s="1">
-        <v>38.101265822784804</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.44</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4691,49 +4697,49 @@
         <v>6.54</v>
       </c>
       <c r="F43" s="1">
-        <v>0.009829210152880186</v>
+        <v>0.0021223541321298833</v>
       </c>
       <c r="G43" s="1">
         <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>54.61</v>
+        <v>52.07</v>
       </c>
       <c r="I43" s="1">
-        <v>-10.34</v>
+        <v>-11.67</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.0072621040302470125</v>
+        <v>-0.008069792515067628</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M43" s="1">
-        <v>0.03733003128517964</v>
+        <v>0.027423735941366045</v>
       </c>
       <c r="N43" s="1">
-        <v>14.291044898276398</v>
+        <v>12.541988011114594</v>
       </c>
       <c r="O43" s="1">
-        <v>63.29113924050633</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P43" s="1">
         <v>36.79958124823221</v>
       </c>
       <c r="Q43" s="1">
-        <v>52.65822784810126</v>
+        <v>50.88607594936709</v>
       </c>
       <c r="R43" s="1">
-        <v>45.82278481012658</v>
+        <v>44.430379746835435</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>3.67</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4747,55 +4753,55 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="3">
-        <v>26.784313725490197</v>
+        <v>26.666666666666664</v>
       </c>
       <c r="E44" s="3">
         <v>-1.94</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.411931061972276</v>
+        <v>-0.4075590833031939</v>
       </c>
       <c r="G44" s="3">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="H44" s="3">
-        <v>43.29</v>
+        <v>43.15</v>
       </c>
       <c r="I44" s="3">
-        <v>-25.4</v>
+        <v>-25.44</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.025122965297178713</v>
+        <v>-0.023995073485427624</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.2573574811252136</v>
+        <v>-0.2670927911898483</v>
       </c>
       <c r="N44" s="3">
-        <v>-15.177706342762928</v>
+        <v>-16.909664702006847</v>
       </c>
       <c r="O44" s="3">
-        <v>15.18987341772152</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P44" s="3">
         <v>44.155007607957295</v>
       </c>
       <c r="Q44" s="3">
-        <v>40.88607594936709</v>
+        <v>40.25316455696202</v>
       </c>
       <c r="R44" s="3">
-        <v>26.89873417721519</v>
+        <v>26.13924050632911</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>0.38</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4809,55 +4815,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.771804062126643</v>
+        <v>0.739545997610514</v>
       </c>
       <c r="E45" s="2">
         <v>1.15</v>
       </c>
       <c r="F45" s="2">
-        <v>0.14441278578812533</v>
+        <v>0.13958225996866705</v>
       </c>
       <c r="G45" s="2">
         <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>57.72</v>
+        <v>60.81</v>
       </c>
       <c r="I45" s="2">
-        <v>15.19</v>
+        <v>16.55</v>
       </c>
       <c r="J45" s="2">
-        <v>0.02076525864641117</v>
+        <v>0.021135348615555098</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M45" s="2">
-        <v>0.18803477792901413</v>
+        <v>0.1797154862867658</v>
       </c>
       <c r="N45" s="2">
-        <v>29.361519562659836</v>
+        <v>27.77116304565458</v>
       </c>
       <c r="O45" s="2">
-        <v>82.27848101265823</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>59.87341772151899</v>
+        <v>61.01265822784809</v>
       </c>
       <c r="R45" s="2">
-        <v>55.822784810126585</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-1.14</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4877,19 +4883,19 @@
         <v>-0.24</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.39017509999581734</v>
+        <v>-0.3042127833263596</v>
       </c>
       <c r="G46" s="3">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H46" s="3">
-        <v>37.29</v>
+        <v>42.46</v>
       </c>
       <c r="I46" s="3">
-        <v>-5.1</v>
+        <v>0.78</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.013207756574737524</v>
+        <v>-0.013137369371077465</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4898,28 +4904,28 @@
         <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.3418115869700493</v>
+        <v>-0.2614621726831674</v>
       </c>
       <c r="N46" s="3">
-        <v>-23.6231169272465</v>
+        <v>-16.346602851338748</v>
       </c>
       <c r="O46" s="3">
-        <v>5.063291139240507</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>42.27848101265823</v>
+        <v>44.55696202531645</v>
       </c>
       <c r="R46" s="3">
-        <v>23.670886075949362</v>
+        <v>26.329113924050628</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-7.72</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4939,19 +4945,19 @@
         <v>-3.9</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.38713278429762255</v>
+        <v>-0.3939530003995467</v>
       </c>
       <c r="G47" s="3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H47" s="3">
-        <v>31.08</v>
+        <v>31.87</v>
       </c>
       <c r="I47" s="3">
-        <v>-19.79</v>
+        <v>-19.49</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030066545340140322</v>
+        <v>-0.030086966933014016</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4960,28 +4966,28 @@
         <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.3416141838027821</v>
+        <v>-0.3529473126397502</v>
       </c>
       <c r="N47" s="3">
-        <v>-23.603376610519778</v>
+        <v>-25.495116846997036</v>
       </c>
       <c r="O47" s="3">
-        <v>6.329113924050633</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P47" s="3">
         <v>31.304415950527737</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.734177215189874</v>
+        <v>38.60759493670887</v>
       </c>
       <c r="R47" s="3">
-        <v>26.012658227848096</v>
+        <v>25.12658227848101</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>0.25</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -4992,58 +4998,58 @@
         <v>5.18</v>
       </c>
       <c r="C48" s="1">
-        <v>60.75949367088608</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="D48" s="1">
-        <v>0.7837837837837839</v>
+        <v>0.7683397683397685</v>
       </c>
       <c r="E48" s="1">
         <v>-0.2</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.19999446919070663</v>
+        <v>-0.19228261907645844</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>55.17</v>
+        <v>58.05</v>
       </c>
       <c r="I48" s="1">
-        <v>-4.98</v>
+        <v>-3.83</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.004658728666823754</v>
+        <v>-0.003011979719898767</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>-66</v>
+        <v>-65</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.19809786083675496</v>
+        <v>-0.19053769619306282</v>
       </c>
       <c r="N48" s="1">
-        <v>-9.25174431391706</v>
+        <v>-9.254155202328294</v>
       </c>
       <c r="O48" s="1">
-        <v>26.582278481012654</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>47.848101265822784</v>
+        <v>48.35443037974684</v>
       </c>
       <c r="R48" s="1">
-        <v>33.48101265822785</v>
+        <v>33.291139240506325</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>7.28</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5063,49 +5069,49 @@
         <v>-1.46</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.017070155312429336</v>
+        <v>-0.011418435823207312</v>
       </c>
       <c r="G49" s="2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>54.18</v>
+        <v>52.6</v>
       </c>
       <c r="I49" s="2">
-        <v>40.39</v>
+        <v>38.85</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02232370560220781</v>
+        <v>0.02144784795912899</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M49" s="2">
-        <v>0.04172470366007297</v>
+        <v>0.041801712120358436</v>
       </c>
       <c r="N49" s="2">
-        <v>14.73051213576572</v>
+        <v>13.979785629013833</v>
       </c>
       <c r="O49" s="2">
-        <v>65.82278481012658</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>63.291139240506325</v>
+        <v>62.78481012658227</v>
       </c>
       <c r="R49" s="2">
-        <v>54.62025316455696</v>
+        <v>54.36708860759494</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.7</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5125,19 +5131,19 @@
         <v>3.55</v>
       </c>
       <c r="F50" s="2">
-        <v>0.40348068441241614</v>
+        <v>0.7452018104109689</v>
       </c>
       <c r="G50" s="2">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="H50" s="2">
-        <v>59.31</v>
+        <v>64.84</v>
       </c>
       <c r="I50" s="2">
-        <v>116.42</v>
+        <v>133.6</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06337730421075859</v>
+        <v>0.06350441819852608</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
@@ -5146,28 +5152,28 @@
         <v>209</v>
       </c>
       <c r="M50" s="2">
-        <v>0.669954158142628</v>
+        <v>0.9886185526446547</v>
       </c>
       <c r="N50" s="2">
-        <v>77.55345758402122</v>
+        <v>108.66146968144344</v>
       </c>
       <c r="O50" s="2">
-        <v>93.67088607594937</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P50" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>72.9113924050633</v>
+        <v>74.17721518987341</v>
       </c>
       <c r="R50" s="2">
-        <v>62.21518987341772</v>
+        <v>62.97468354430381</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-1.33</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5181,25 +5187,25 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D51" s="2">
-        <v>7.748743718592965</v>
+        <v>7.768844221105527</v>
       </c>
       <c r="E51" s="2">
         <v>-0.69</v>
       </c>
       <c r="F51" s="2">
-        <v>0.08978731847287727</v>
+        <v>0.13454722585602455</v>
       </c>
       <c r="G51" s="2">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H51" s="2">
-        <v>45.23</v>
+        <v>48.21</v>
       </c>
       <c r="I51" s="2">
-        <v>53.34</v>
+        <v>56.39</v>
       </c>
       <c r="J51" s="2">
-        <v>0.030712783573591588</v>
+        <v>0.025706510035935094</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
@@ -5208,13 +5214,13 @@
         <v>247</v>
       </c>
       <c r="M51" s="2">
-        <v>0.19315247376324418</v>
+        <v>0.22877306155938681</v>
       </c>
       <c r="N51" s="2">
-        <v>29.873289146082847</v>
+        <v>32.67692057291667</v>
       </c>
       <c r="O51" s="2">
-        <v>83.54430379746836</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P51" s="2">
         <v>16.096535574030653</v>
@@ -5223,13 +5229,13 @@
         <v>63.291139240506325</v>
       </c>
       <c r="R51" s="2">
-        <v>60.12658227848101</v>
+        <v>59.36708860759494</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-2.91</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5249,49 +5255,49 @@
         <v>2.59</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.4167732656205182</v>
+        <v>-0.4020790605047201</v>
       </c>
       <c r="G52" s="3">
         <v>1.55</v>
       </c>
       <c r="H52" s="3">
-        <v>45.37</v>
+        <v>44.61</v>
       </c>
       <c r="I52" s="3">
-        <v>-21.23</v>
+        <v>-21.93</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.04258186181103661</v>
+        <v>-0.043348280154426724</v>
       </c>
       <c r="K52" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>-2</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.36461653588684684</v>
+        <v>-0.3540936812113411</v>
       </c>
       <c r="N52" s="3">
-        <v>-25.903611818926258</v>
+        <v>-25.609753704156123</v>
       </c>
       <c r="O52" s="3">
-        <v>3.79746835443038</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="P52" s="3">
         <v>46.37680917379436</v>
       </c>
       <c r="Q52" s="3">
-        <v>40.63291139240506</v>
+        <v>39.36708860759494</v>
       </c>
       <c r="R52" s="3">
-        <v>21.962025316455694</v>
+        <v>21.582278481012658</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T52" s="3">
-        <v>0.19</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5311,49 +5317,49 @@
         <v>16.72</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.00914892571855691</v>
+        <v>0.19484454851966937</v>
       </c>
       <c r="G53" s="1">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H53" s="1">
-        <v>48.59</v>
+        <v>53.38</v>
       </c>
       <c r="I53" s="1">
-        <v>19.18</v>
+        <v>27.92</v>
       </c>
       <c r="J53" s="1">
-        <v>0.01827539964330227</v>
+        <v>0.015484289853139582</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M53" s="1">
-        <v>0.12171705070410943</v>
+        <v>0.3117543817071744</v>
       </c>
       <c r="N53" s="1">
-        <v>22.729746840169366</v>
+        <v>40.97505258769542</v>
       </c>
       <c r="O53" s="1">
-        <v>72.15189873417721</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>48.10126582278481</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R53" s="1">
-        <v>38.54430379746835</v>
+        <v>42.72151898734178</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>11.9</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5364,7 +5370,7 @@
         <v>5.3</v>
       </c>
       <c r="C54" s="2">
-        <v>62.0253164556962</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="D54" s="2">
         <v>6.560377358490567</v>
@@ -5373,19 +5379,19 @@
         <v>0.25</v>
       </c>
       <c r="F54" s="2">
-        <v>0.04708113900637412</v>
+        <v>0.06362512898475944</v>
       </c>
       <c r="G54" s="2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H54" s="2">
-        <v>59.07</v>
+        <v>62.58</v>
       </c>
       <c r="I54" s="2">
-        <v>56.66</v>
+        <v>61.21</v>
       </c>
       <c r="J54" s="2">
-        <v>0.029714571253490193</v>
+        <v>0.03011599986989472</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
@@ -5394,28 +5400,28 @@
         <v>297</v>
       </c>
       <c r="M54" s="2">
-        <v>0.12484208151839327</v>
+        <v>0.13603942864567675</v>
       </c>
       <c r="N54" s="2">
-        <v>23.04224992159776</v>
+        <v>23.403557281545655</v>
       </c>
       <c r="O54" s="2">
-        <v>74.68354430379746</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>67.72151898734178</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="R54" s="2">
-        <v>56.708860759493675</v>
+        <v>56.139240506329116</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>-0.06</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5435,49 +5441,49 @@
         <v>6.64</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.18472916725132155</v>
+        <v>-0.016949338328947877</v>
       </c>
       <c r="G55" s="1">
         <v>2.57</v>
       </c>
       <c r="H55" s="1">
-        <v>52.21</v>
+        <v>59.85</v>
       </c>
       <c r="I55" s="1">
-        <v>-24.23</v>
+        <v>-17.2</v>
       </c>
       <c r="J55" s="1">
-        <v>0.014163573541884859</v>
+        <v>0.013468207208819055</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.035845411466114196</v>
+        <v>0.12002710801760652</v>
       </c>
       <c r="N55" s="1">
-        <v>6.973500623147019</v>
+        <v>21.80232521873865</v>
       </c>
       <c r="O55" s="1">
-        <v>58.22784810126582</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P55" s="1">
         <v>48.21894075039502</v>
       </c>
       <c r="Q55" s="1">
-        <v>43.79746835443038</v>
+        <v>46.962025316455694</v>
       </c>
       <c r="R55" s="1">
-        <v>35.31645569620253</v>
+        <v>39.493670886075954</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>0.19</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5497,19 +5503,19 @@
         <v>-0.43</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.08833034037214557</v>
+        <v>-0.06780606705672479</v>
       </c>
       <c r="G56" s="1">
         <v>1.44</v>
       </c>
       <c r="H56" s="1">
-        <v>55.99</v>
+        <v>57.7</v>
       </c>
       <c r="I56" s="1">
-        <v>4.89</v>
+        <v>6.17</v>
       </c>
       <c r="J56" s="1">
-        <v>0.026583598231624345</v>
+        <v>0.02475993056153192</v>
       </c>
       <c r="K56" s="1" t="b">
         <v>0</v>
@@ -5518,28 +5524,28 @@
         <v>14</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.04660495658520847</v>
+        <v>-0.029417763622021642</v>
       </c>
       <c r="N56" s="1">
-        <v>5.8975461112375935</v>
+        <v>6.857838054775812</v>
       </c>
       <c r="O56" s="1">
-        <v>54.43037974683544</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P56" s="1">
         <v>25.062459708672506</v>
       </c>
       <c r="Q56" s="1">
-        <v>64.0506329113924</v>
+        <v>63.79746835443038</v>
       </c>
       <c r="R56" s="1">
-        <v>49.493670886075954</v>
+        <v>49.74683544303797</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>93</v>
       </c>
       <c r="T56" s="1">
-        <v>-3.16</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5559,19 +5565,19 @@
         <v>-0.26</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.15562637474489605</v>
+        <v>-0.14590697229295946</v>
       </c>
       <c r="G57" s="1">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H57" s="1">
-        <v>48.65</v>
+        <v>50.49</v>
       </c>
       <c r="I57" s="1">
-        <v>-0.86</v>
+        <v>-0.42</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0027817767590546006</v>
+        <v>0.004135811761639357</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>1</v>
@@ -5580,28 +5586,28 @@
         <v>-58</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.13476368285142748</v>
+        <v>-0.12758528201730568</v>
       </c>
       <c r="N57" s="1">
-        <v>-2.918326515384319</v>
+        <v>-2.958913784752585</v>
       </c>
       <c r="O57" s="1">
-        <v>39.24050632911392</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>51.01265822784811</v>
+        <v>51.139240506329116</v>
       </c>
       <c r="R57" s="1">
-        <v>40.18987341772152</v>
+        <v>39.683544303797476</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5621,49 +5627,49 @@
         <v>0.81</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.10664642570072012</v>
+        <v>-0.0778070005847936</v>
       </c>
       <c r="G58" s="1">
         <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>50.13</v>
+        <v>54.27</v>
       </c>
       <c r="I58" s="1">
-        <v>9.14</v>
+        <v>10.12</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.005605395541752041</v>
+        <v>-0.0053363047072461966</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.1768209347969325</v>
+        <v>-0.1423691472704307</v>
       </c>
       <c r="N58" s="1">
-        <v>-7.124051709934818</v>
+        <v>-4.437300310065081</v>
       </c>
       <c r="O58" s="1">
-        <v>29.11392405063291</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>47.72151898734177</v>
+        <v>48.22784810126582</v>
       </c>
       <c r="R58" s="1">
-        <v>35.949367088607595</v>
+        <v>36.962025316455694</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>1.96</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5683,49 +5689,49 @@
         <v>0.11</v>
       </c>
       <c r="F59" s="2">
-        <v>0.5591785452661154</v>
+        <v>0.5972754899550032</v>
       </c>
       <c r="G59" s="2">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H59" s="2">
-        <v>64.36</v>
+        <v>66.92</v>
       </c>
       <c r="I59" s="2">
-        <v>131.58</v>
+        <v>138.64</v>
       </c>
       <c r="J59" s="2">
-        <v>0.06998974441866626</v>
+        <v>0.06756761523097267</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M59" s="2">
-        <v>0.6483191379018447</v>
+        <v>0.6819042497996897</v>
       </c>
       <c r="N59" s="2">
-        <v>75.38995555994289</v>
+        <v>77.99003939694697</v>
       </c>
       <c r="O59" s="2">
-        <v>92.40506329113924</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P59" s="2">
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>80.12658227848101</v>
+        <v>80.25316455696203</v>
       </c>
       <c r="R59" s="2">
-        <v>66.77215189873418</v>
+        <v>66.39240506329114</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T59" s="2">
-        <v>-0.57</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5745,49 +5751,49 @@
         <v>-2.31</v>
       </c>
       <c r="F60" s="2">
-        <v>0.09541051379947513</v>
+        <v>0.13903663873672087</v>
       </c>
       <c r="G60" s="2">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="H60" s="2">
-        <v>48.37</v>
+        <v>51.54</v>
       </c>
       <c r="I60" s="2">
-        <v>38.98</v>
+        <v>41.22</v>
       </c>
       <c r="J60" s="2">
-        <v>0.022439490291569168</v>
+        <v>0.02121920637804616</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M60" s="2">
-        <v>0.12196303075479875</v>
+        <v>0.15910325189577024</v>
       </c>
       <c r="N60" s="2">
-        <v>22.754344845238315</v>
+        <v>25.70993960655502</v>
       </c>
       <c r="O60" s="2">
-        <v>73.41772151898735</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P60" s="2">
         <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>58.607594936708864</v>
+        <v>59.24050632911392</v>
       </c>
       <c r="R60" s="2">
-        <v>54.873417721519</v>
+        <v>55.8860759493671</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-1.71</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5798,7 +5804,7 @@
         <v>6.37</v>
       </c>
       <c r="C61" s="1">
-        <v>68.35443037974683</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="D61" s="1">
         <v>-0.13029827315541603</v>
@@ -5807,19 +5813,19 @@
         <v>0.62</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.14069214343052988</v>
+        <v>-0.14145413560742148</v>
       </c>
       <c r="G61" s="1">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H61" s="1">
-        <v>40.14</v>
+        <v>39.25</v>
       </c>
       <c r="I61" s="1">
-        <v>-0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="J61" s="1">
-        <v>-0.007688978137916444</v>
+        <v>-0.007195614413038062</v>
       </c>
       <c r="K61" s="1" t="b">
         <v>1</v>
@@ -5828,19 +5834,19 @@
         <v>102</v>
       </c>
       <c r="M61" s="1">
-        <v>-0.1985386982260563</v>
+        <v>-0.19554674499268498</v>
       </c>
       <c r="N61" s="1">
-        <v>-9.295828052847197</v>
+        <v>-9.755060082290516</v>
       </c>
       <c r="O61" s="1">
-        <v>25.31645569620253</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P61" s="1">
         <v>12.798408482128673</v>
       </c>
       <c r="Q61" s="1">
-        <v>36.45569620253165</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="R61" s="1">
         <v>30.063291139240505</v>
@@ -5863,55 +5869,55 @@
         <v>92.40506329113924</v>
       </c>
       <c r="D62" s="1">
-        <v>0.6178128523111613</v>
+        <v>0.6251409244644871</v>
       </c>
       <c r="E62" s="1">
         <v>-0.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.25517085359896147</v>
+        <v>-0.2915840197286455</v>
       </c>
       <c r="G62" s="1">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H62" s="1">
-        <v>42.65</v>
+        <v>33.5</v>
       </c>
       <c r="I62" s="1">
-        <v>7.69</v>
+        <v>2.07</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.005745870886821533</v>
+        <v>-0.006555066634342177</v>
       </c>
       <c r="K62" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="1">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.25896407030686486</v>
+        <v>-0.2959463269371345</v>
       </c>
       <c r="N62" s="1">
-        <v>-15.338365260928057</v>
+        <v>-19.79501827673546</v>
       </c>
       <c r="O62" s="1">
-        <v>13.924050632911392</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P62" s="1">
-        <v>16.149676494964734</v>
+        <v>19.79501827673546</v>
       </c>
       <c r="Q62" s="1">
-        <v>51.89873417721519</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R62" s="1">
-        <v>36.20253164556962</v>
+        <v>32.78481012658228</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-6.65</v>
+        <v>-10.06</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5931,31 +5937,31 @@
         <v>-8.13</v>
       </c>
       <c r="F63" s="4">
-        <v>0.7761867121787323</v>
+        <v>0.9493622663007135</v>
       </c>
       <c r="G63" s="4">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="H63" s="4">
-        <v>62.51</v>
+        <v>69.05</v>
       </c>
       <c r="I63" s="4">
-        <v>215.16</v>
+        <v>243.21</v>
       </c>
       <c r="J63" s="4">
-        <v>0.08986427164951427</v>
+        <v>0.09058687062645834</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="4">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="M63" s="4">
-        <v>1.1365422994295526</v>
+        <v>1.2747903840539925</v>
       </c>
       <c r="N63" s="4">
-        <v>124.2122717127137</v>
+        <v>137.27865282237724</v>
       </c>
       <c r="O63" s="4">
         <v>98.73417721518987</v>
@@ -5964,16 +5970,16 @@
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.53164556962025</v>
+        <v>84.17721518987342</v>
       </c>
       <c r="R63" s="4">
-        <v>72.02531645569621</v>
+        <v>72.34177215189874</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5993,49 +5999,49 @@
         <v>-5.36</v>
       </c>
       <c r="F64" s="2">
-        <v>0.6351325470611234</v>
+        <v>0.7852798911919795</v>
       </c>
       <c r="G64" s="2">
         <v>2.01</v>
       </c>
       <c r="H64" s="2">
-        <v>61.46</v>
+        <v>68.25</v>
       </c>
       <c r="I64" s="2">
-        <v>116.61</v>
+        <v>131.53</v>
       </c>
       <c r="J64" s="2">
-        <v>0.07547802540153473</v>
+        <v>0.07405834123421048</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M64" s="2">
-        <v>0.7309112689356836</v>
+        <v>0.8733984968034572</v>
       </c>
       <c r="N64" s="2">
-        <v>83.6491686633268</v>
+        <v>97.1394640973237</v>
       </c>
       <c r="O64" s="2">
-        <v>94.9367088607595</v>
+        <v>93.67088607594937</v>
       </c>
       <c r="P64" s="2">
         <v>20.9978319173529</v>
       </c>
       <c r="Q64" s="2">
-        <v>76.07594936708861</v>
+        <v>77.59493670886076</v>
       </c>
       <c r="R64" s="2">
-        <v>67.40506329113924</v>
+        <v>67.02531645569621</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T64" s="2">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6055,111 +6061,111 @@
         <v>-0.88</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.12194463957896008</v>
+        <v>-0.1278443421112761</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>44.84</v>
+        <v>47.3</v>
       </c>
       <c r="I65" s="1">
-        <v>-0.87</v>
+        <v>-0.22</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.007483096510571766</v>
+        <v>-0.008901388539462785</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L65" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.1883259319672691</v>
+        <v>-0.188916643030122</v>
       </c>
       <c r="N65" s="1">
-        <v>-8.274551426968483</v>
+        <v>-9.092049886034218</v>
       </c>
       <c r="O65" s="1">
-        <v>27.848101265822784</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>44.810126582278485</v>
+        <v>44.55696202531646</v>
       </c>
       <c r="R65" s="1">
-        <v>35.50632911392405</v>
+        <v>34.74683544303797</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-1.9</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
-        <v>15.41</v>
-      </c>
-      <c r="C66" s="1">
+      <c r="B66" s="3">
+        <v>16.51</v>
+      </c>
+      <c r="C66" s="3">
         <v>87.34177215189874</v>
       </c>
-      <c r="D66" s="1">
-        <v>-0.10902011680726799</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="D66" s="3">
+        <v>-0.13325257419745615</v>
+      </c>
+      <c r="E66" s="3">
         <v>-0.2</v>
       </c>
-      <c r="F66" s="1">
-        <v>-0.10310958849330647</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1.04</v>
-      </c>
-      <c r="H66" s="1">
-        <v>45.35</v>
-      </c>
-      <c r="I66" s="1">
-        <v>-31.89</v>
-      </c>
-      <c r="J66" s="1">
-        <v>-0.017250314305971653</v>
-      </c>
-      <c r="K66" s="1" t="b">
+      <c r="F66" s="3">
+        <v>-0.2937024335685622</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="H66" s="3">
+        <v>28.59</v>
+      </c>
+      <c r="I66" s="3">
+        <v>-45.3</v>
+      </c>
+      <c r="J66" s="3">
+        <v>-0.020762511040299483</v>
+      </c>
+      <c r="K66" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L66" s="1">
-        <v>-192</v>
-      </c>
-      <c r="M66" s="1">
-        <v>-0.09931637178540309</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0.626404591218114</v>
-      </c>
-      <c r="O66" s="1">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="P66" s="1">
-        <v>48.12800106814908</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>36.45569620253165</v>
-      </c>
-      <c r="R66" s="1">
-        <v>31.20253164556962</v>
-      </c>
-      <c r="S66" s="1" t="s">
+      <c r="L66" s="3">
+        <v>-191</v>
+      </c>
+      <c r="M66" s="3">
+        <v>-0.2910850492434688</v>
+      </c>
+      <c r="N66" s="3">
+        <v>-19.308890507368886</v>
+      </c>
+      <c r="O66" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P66" s="3">
+        <v>54.61236968964586</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>32.27848101265823</v>
+      </c>
+      <c r="R66" s="3">
+        <v>18.481012658227847</v>
+      </c>
+      <c r="S66" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T66" s="1">
-        <v>2.15</v>
+      <c r="T66" s="3">
+        <v>-10.57</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6173,55 +6179,55 @@
         <v>55.69620253164557</v>
       </c>
       <c r="D67" s="1">
-        <v>7.239401496259353</v>
+        <v>7.241895261845387</v>
       </c>
       <c r="E67" s="1">
         <v>-1.48</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.09704660391744808</v>
+        <v>-0.11446784778731421</v>
       </c>
       <c r="G67" s="1">
         <v>1.15</v>
       </c>
       <c r="H67" s="1">
-        <v>48.75</v>
+        <v>45.46</v>
       </c>
       <c r="I67" s="1">
-        <v>-11.47</v>
+        <v>-12.56</v>
       </c>
       <c r="J67" s="1">
-        <v>0.00003501062543400538</v>
+        <v>0.00019670496386489357</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.08282204126281045</v>
+        <v>-0.10138092616184724</v>
       </c>
       <c r="N67" s="1">
-        <v>2.2758376434773804</v>
+        <v>-0.33847819920673305</v>
       </c>
       <c r="O67" s="1">
-        <v>49.36708860759494</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>50.12658227848101</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="R67" s="1">
-        <v>43.16455696202532</v>
+        <v>42.21518987341772</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-0.95</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6241,19 +6247,19 @@
         <v>-0.18</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.17723457076695825</v>
+        <v>-0.17758610696204752</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>42.75</v>
+        <v>42.32</v>
       </c>
       <c r="I68" s="1">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.011592547022159807</v>
+        <v>-0.011523876210831585</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6262,10 +6268,10 @@
         <v>148</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.24077095062433973</v>
+        <v>-0.23604102355580003</v>
       </c>
       <c r="N68" s="1">
-        <v>-13.51905329267554</v>
+        <v>-13.804487938602017</v>
       </c>
       <c r="O68" s="1">
         <v>17.72151898734177</v>
@@ -6274,16 +6280,16 @@
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>60.88607594936709</v>
+        <v>60.12658227848102</v>
       </c>
       <c r="R68" s="1">
-        <v>45.75949367088607</v>
+        <v>45.88607594936709</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6303,49 +6309,49 @@
         <v>0.19</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.2540906561209906</v>
+        <v>-0.2690867324852023</v>
       </c>
       <c r="G69" s="3">
         <v>1.5</v>
       </c>
       <c r="H69" s="3">
-        <v>49.59</v>
+        <v>45.27</v>
       </c>
       <c r="I69" s="3">
-        <v>-9.53</v>
+        <v>-11.36</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.01235368357219521</v>
+        <v>-0.011529060744810636</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.20667544727219844</v>
+        <v>-0.2254636604003124</v>
       </c>
       <c r="N69" s="3">
-        <v>-10.109502957461418</v>
+        <v>-12.74675162305326</v>
       </c>
       <c r="O69" s="3">
-        <v>24.050632911392405</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P69" s="3">
         <v>29.145649851223904</v>
       </c>
       <c r="Q69" s="3">
-        <v>43.0379746835443</v>
+        <v>40.379746835443036</v>
       </c>
       <c r="R69" s="3">
-        <v>28.924050632911392</v>
+        <v>27.53164556962025</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>1.2</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6365,49 +6371,49 @@
         <v>1.82</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.2171429697259346</v>
+        <v>-0.20714031465061727</v>
       </c>
       <c r="G70" s="3">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H70" s="3">
-        <v>41.29</v>
+        <v>40.27</v>
       </c>
       <c r="I70" s="3">
-        <v>-14.23</v>
+        <v>-14.67</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.012948885801887805</v>
+        <v>-0.012236944844050341</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-58</v>
+        <v>-57</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.22852261984964473</v>
+        <v>-0.21848231339268864</v>
       </c>
       <c r="N70" s="3">
-        <v>-12.294220215206039</v>
+        <v>-12.048616922290883</v>
       </c>
       <c r="O70" s="3">
-        <v>18.9873417721519</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>38.35443037974684</v>
+        <v>38.22784810126583</v>
       </c>
       <c r="R70" s="3">
-        <v>27.151898734177212</v>
+        <v>27.911392405063292</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>-0.57</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6427,31 +6433,31 @@
         <v>-1.56</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.4434347177889558</v>
+        <v>-0.429719529268869</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>48.49</v>
+        <v>49.73</v>
       </c>
       <c r="I71" s="3">
-        <v>-28.63</v>
+        <v>-28.14</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.030341592034696174</v>
+        <v>-0.02833579033638761</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-99</v>
+        <v>-100</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.4320550676652457</v>
+        <v>-0.41924999196849544</v>
       </c>
       <c r="N71" s="3">
-        <v>-32.64746499676614</v>
+        <v>-32.12538477987156</v>
       </c>
       <c r="O71" s="3">
         <v>1.2658227848101267</v>
@@ -6460,78 +6466,78 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>40.25316455696203</v>
+        <v>40.632911392405056</v>
       </c>
       <c r="R71" s="3">
-        <v>22.27848101265823</v>
+        <v>22.40506329113924</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T71" s="3">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="1">
         <v>10.42</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="1">
         <v>78.48101265822784</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="1">
         <v>0.21976967370441466</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="1">
         <v>-1.49</v>
       </c>
-      <c r="F72" s="3">
-        <v>-0.2593703593655213</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1.15</v>
-      </c>
-      <c r="H72" s="3">
-        <v>42.88</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-9.54</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-0.009744696232501321</v>
-      </c>
-      <c r="K72" s="3" t="b">
+      <c r="F72" s="1">
+        <v>-0.25243395751460584</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H72" s="1">
+        <v>44.33</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-9</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.008215991391423793</v>
+      </c>
+      <c r="K72" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="1">
         <v>2</v>
       </c>
-      <c r="M72" s="3">
-        <v>-0.24514579671088366</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-13.956537901329934</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="M72" s="1">
+        <v>-0.2402194973308367</v>
+      </c>
+      <c r="N72" s="1">
+        <v>-14.222335316105678</v>
+      </c>
+      <c r="O72" s="1">
         <v>16.455696202531644</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="1">
         <v>19.739671794345924</v>
       </c>
-      <c r="Q72" s="3">
-        <v>41.51898734177215</v>
-      </c>
-      <c r="R72" s="3">
-        <v>29.746835443037973</v>
-      </c>
-      <c r="S72" s="3" t="s">
+      <c r="Q72" s="1">
+        <v>42.025316455696206</v>
+      </c>
+      <c r="R72" s="1">
+        <v>30.253164556962027</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T72" s="3">
-        <v>2.28</v>
+      <c r="T72" s="1">
+        <v>2.78</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6551,49 +6557,49 @@
         <v>-1.26</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3346671731960124</v>
+        <v>0.3042174964651143</v>
       </c>
       <c r="G73" s="2">
         <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>67.17</v>
+        <v>62.81</v>
       </c>
       <c r="I73" s="2">
-        <v>44.62</v>
+        <v>42.47</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03103910463020445</v>
+        <v>0.03087006486436829</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M73" s="2">
-        <v>0.3517366483815776</v>
+        <v>0.3199218024156747</v>
       </c>
       <c r="N73" s="2">
-        <v>45.731706607916195</v>
+        <v>41.79179465854544</v>
       </c>
       <c r="O73" s="2">
-        <v>88.60759493670885</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>68.35443037974683</v>
+        <v>67.21518987341773</v>
       </c>
       <c r="R73" s="2">
-        <v>62.65822784810127</v>
+        <v>62.27848101265823</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6613,7 +6619,7 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="2">
-        <v>0.1830505137246994</v>
+        <v>0.16736885814528502</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
@@ -6622,10 +6628,10 @@
         <v>80.47</v>
       </c>
       <c r="I74" s="2">
-        <v>30.85</v>
+        <v>30.55</v>
       </c>
       <c r="J74" s="2">
-        <v>0.01850987680405728</v>
+        <v>0.01684470025837608</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
@@ -6634,13 +6640,13 @@
         <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.1631361260082067</v>
+        <v>0.14904716786963124</v>
       </c>
       <c r="N74" s="2">
-        <v>26.871654370579094</v>
+        <v>24.70433120394112</v>
       </c>
       <c r="O74" s="2">
-        <v>78.48101265822784</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
@@ -6649,13 +6655,13 @@
         <v>65.0632911392405</v>
       </c>
       <c r="R74" s="2">
-        <v>58.29113924050633</v>
+        <v>57.53164556962027</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>1.96</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6675,19 +6681,19 @@
         <v>-2.27</v>
       </c>
       <c r="F75" s="1">
-        <v>0.055862293812288175</v>
+        <v>-0.008443833219813346</v>
       </c>
       <c r="G75" s="1">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H75" s="1">
-        <v>64.97</v>
+        <v>59.55</v>
       </c>
       <c r="I75" s="1">
-        <v>18.36</v>
+        <v>15.61</v>
       </c>
       <c r="J75" s="1">
-        <v>0.007826150800004537</v>
+        <v>0.009937538495671276</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6696,28 +6702,28 @@
         <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>0.0520690771043848</v>
+        <v>-0.011061217544906743</v>
       </c>
       <c r="N75" s="1">
-        <v>15.764949480196902</v>
+        <v>8.693492662487303</v>
       </c>
       <c r="O75" s="1">
-        <v>67.08860759493672</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>61.51898734177215</v>
+        <v>59.620253164556964</v>
       </c>
       <c r="R75" s="1">
-        <v>46.835443037974684</v>
+        <v>44.30379746835443</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>0.38</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6737,19 +6743,19 @@
         <v>3.5</v>
       </c>
       <c r="F76" s="1">
-        <v>0.08522081436684652</v>
+        <v>0.07236366412748221</v>
       </c>
       <c r="G76" s="1">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H76" s="1">
-        <v>49</v>
+        <v>42.61</v>
       </c>
       <c r="I76" s="1">
-        <v>11.89</v>
+        <v>7.08</v>
       </c>
       <c r="J76" s="1">
-        <v>0.014257280253357972</v>
+        <v>0.012504167396938246</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6758,28 +6764,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>0.05866829741152291</v>
+        <v>0.04706228231824605</v>
       </c>
       <c r="N76" s="1">
-        <v>16.424871510910727</v>
+        <v>14.505842648802586</v>
       </c>
       <c r="O76" s="1">
-        <v>68.35443037974683</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>48.9873417721519</v>
+        <v>45.44303797468355</v>
       </c>
       <c r="R76" s="1">
-        <v>45.37974683544304</v>
+        <v>44.62025316455696</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>3.16</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6799,19 +6805,19 @@
         <v>-0.19</v>
       </c>
       <c r="F77" s="2">
-        <v>0.021049672747980433</v>
+        <v>0.043110531136912364</v>
       </c>
       <c r="G77" s="2">
         <v>0.98</v>
       </c>
       <c r="H77" s="2">
-        <v>65.61</v>
+        <v>68.46</v>
       </c>
       <c r="I77" s="2">
-        <v>13.21</v>
+        <v>14.8</v>
       </c>
       <c r="J77" s="2">
-        <v>0.009360371516803734</v>
+        <v>0.011052862268375178</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6820,90 +6826,90 @@
         <v>8</v>
       </c>
       <c r="M77" s="2">
-        <v>0.01915306439402875</v>
+        <v>0.04136560825351676</v>
       </c>
       <c r="N77" s="2">
-        <v>12.473348209161312</v>
+        <v>13.936175242329668</v>
       </c>
       <c r="O77" s="2">
-        <v>60.75949367088608</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>64.55696202531645</v>
+        <v>64.68354430379748</v>
       </c>
       <c r="R77" s="2">
-        <v>54.74683544303799</v>
+        <v>55.506329113924046</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>13.11</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78" s="1">
         <v>84.81012658227847</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>-0.7139588100686499</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>0.93</v>
       </c>
-      <c r="F78" s="2">
-        <v>0.13771728086955823</v>
-      </c>
-      <c r="G78" s="2">
-        <v>1.26</v>
-      </c>
-      <c r="H78" s="2">
-        <v>62.3</v>
-      </c>
-      <c r="I78" s="2">
-        <v>30.84</v>
-      </c>
-      <c r="J78" s="2">
-        <v>0.026771763612095684</v>
-      </c>
-      <c r="K78" s="2" t="b">
+      <c r="F78" s="1">
+        <v>0.09794401446313132</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H78" s="1">
+        <v>60.99</v>
+      </c>
+      <c r="I78" s="1">
+        <v>29.94</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0.025484029716650775</v>
+      </c>
+      <c r="K78" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L78" s="2">
-        <v>60</v>
-      </c>
-      <c r="M78" s="2">
-        <v>0.16237318947093016</v>
-      </c>
-      <c r="N78" s="2">
-        <v>26.79536071685144</v>
-      </c>
-      <c r="O78" s="2">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="P78" s="2">
+      <c r="L78" s="1">
+        <v>59</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0.11975555050557629</v>
+      </c>
+      <c r="N78" s="1">
+        <v>21.775169467535605</v>
+      </c>
+      <c r="O78" s="1">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="P78" s="1">
         <v>20.806025084936465</v>
       </c>
-      <c r="Q78" s="2">
-        <v>60</v>
-      </c>
-      <c r="R78" s="2">
-        <v>51.0126582278481</v>
-      </c>
-      <c r="S78" s="2" t="s">
+      <c r="Q78" s="1">
+        <v>59.36708860759494</v>
+      </c>
+      <c r="R78" s="1">
+        <v>48.607594936708864</v>
+      </c>
+      <c r="S78" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="T78" s="2">
-        <v>1.33</v>
+      <c r="T78" s="1">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6923,49 +6929,49 @@
         <v>0.99</v>
       </c>
       <c r="F79" s="2">
-        <v>0.35663309376848606</v>
+        <v>0.3987904244371889</v>
       </c>
       <c r="G79" s="2">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="H79" s="2">
-        <v>76.82</v>
+        <v>79.49</v>
       </c>
       <c r="I79" s="2">
-        <v>47.79</v>
+        <v>52.27</v>
       </c>
       <c r="J79" s="2">
-        <v>0.04473586149310199</v>
+        <v>0.04564937937053453</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L79" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M79" s="2">
-        <v>0.3499949645296552</v>
+        <v>0.39442811722869986</v>
       </c>
       <c r="N79" s="2">
-        <v>45.55753822272394</v>
+        <v>49.242426139847964</v>
       </c>
       <c r="O79" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>66.45569620253164</v>
+        <v>66.32911392405063</v>
       </c>
       <c r="R79" s="2">
-        <v>58.9873417721519</v>
+        <v>59.36708860759494</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6979,55 +6985,55 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8428899082568806</v>
+        <v>0.8348623853211008</v>
       </c>
       <c r="E80" s="2">
         <v>4.67</v>
       </c>
       <c r="F80" s="2">
-        <v>0.935767665223101</v>
+        <v>0.9695593477121562</v>
       </c>
       <c r="G80" s="2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2">
-        <v>62.02</v>
+        <v>65.75</v>
       </c>
       <c r="I80" s="2">
-        <v>63.24</v>
+        <v>69.17</v>
       </c>
       <c r="J80" s="2">
-        <v>0.05099319169628612</v>
+        <v>0.050940209043059737</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M80" s="2">
-        <v>0.9348193610461251</v>
+        <v>0.9695593477121562</v>
       </c>
       <c r="N80" s="2">
-        <v>104.03997787437092</v>
+        <v>106.75554918819358</v>
       </c>
       <c r="O80" s="2">
-        <v>96.20253164556962</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P80" s="2">
         <v>14.059118714058641</v>
       </c>
       <c r="Q80" s="2">
-        <v>69.62025316455697</v>
+        <v>70.37974683544304</v>
       </c>
       <c r="R80" s="2">
-        <v>65.31645569620254</v>
+        <v>64.9367088607595</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -7046,7 +7052,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7054,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>36.075949367088604</v>
+        <v>35.88607594936709</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7070,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20.06329113924051</v>
+        <v>20.822784810126585</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7078,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>43.60759493670886</v>
+        <v>43.35443037974684</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7086,7 +7092,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42.27848101265823</v>
+        <v>41.51898734177216</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7094,7 +7100,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>54.367088607594944</v>
+        <v>55.18987341772152</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7102,7 +7108,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.25316455696202</v>
+        <v>54.11392405063291</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7110,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.430379746835435</v>
+        <v>39.55696202531645</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7118,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.59493670886076</v>
+        <v>37.15189873417721</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7126,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>52.784810126582286</v>
+        <v>52.40506329113924</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7134,7 +7140,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>31.07594936708861</v>
+        <v>35.063291139240505</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7142,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.278481012658229</v>
+        <v>7.405063291139241</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7150,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>42.59493670886076</v>
+        <v>45.12658227848102</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7158,7 +7164,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>61.962025316455694</v>
+        <v>62.27848101265822</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -7166,7 +7172,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.898734177215186</v>
+        <v>28.924050632911392</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7174,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>15.443037974683545</v>
+        <v>18.354430379746837</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7182,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>29.43037974683544</v>
+        <v>28.797468354430382</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7190,7 +7196,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>40.8860759493671</v>
+        <v>41.89873417721519</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7198,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39.936708860759495</v>
+        <v>40.25316455696203</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7206,7 +7212,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49.49367088607595</v>
+        <v>54.177215189873415</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7214,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.506329113924053</v>
+        <v>30.379746835443036</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7222,7 +7228,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>33.544303797468345</v>
+        <v>32.0253164556962</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7230,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>27.658227848101266</v>
+        <v>27.151898734177212</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7238,7 +7244,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6.0126582278481</v>
+        <v>9.303797468354428</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7246,7 +7252,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>32.78481012658228</v>
+        <v>33.29113924050633</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7254,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>22.658227848101262</v>
+        <v>24.303797468354432</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7262,7 +7268,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>16.07594936708861</v>
+        <v>20.379746835443044</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7270,7 +7276,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>25.506329113924046</v>
+        <v>25.31645569620253</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7278,7 +7284,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>47.34177215189874</v>
+        <v>46.07594936708861</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7286,7 +7292,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>60</v>
+        <v>59.177215189873415</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7294,7 +7300,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>17.91139240506329</v>
+        <v>19.81012658227848</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7302,7 +7308,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>41.9620253164557</v>
+        <v>41.835443037974684</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7310,7 +7316,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>52.21518987341772</v>
+        <v>49.55696202531646</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7318,7 +7324,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>23.79746835443038</v>
+        <v>23.037974683544306</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7326,7 +7332,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>32.46835443037974</v>
+        <v>31.83544303797468</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7334,7 +7340,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>36.708860759493675</v>
+        <v>35.63291139240506</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7350,7 +7356,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>45.12658227848101</v>
+        <v>43.29113924050633</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7358,7 +7364,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>31.835443037974677</v>
+        <v>30.949367088607595</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7366,7 +7372,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>30.44303797468355</v>
+        <v>30.88607594936709</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7374,7 +7380,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.101265822784804</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7382,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>45.82278481012658</v>
+        <v>44.430379746835435</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7390,7 +7396,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>26.89873417721519</v>
+        <v>26.13924050632911</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7398,7 +7404,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>55.822784810126585</v>
+        <v>55.56962025316456</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7406,7 +7412,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>23.670886075949362</v>
+        <v>26.329113924050628</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7414,7 +7420,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>26.012658227848096</v>
+        <v>25.12658227848101</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7422,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>33.48101265822785</v>
+        <v>33.291139240506325</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7430,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.62025316455696</v>
+        <v>54.36708860759494</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7438,7 +7444,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>62.21518987341772</v>
+        <v>62.97468354430381</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7446,7 +7452,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>60.12658227848101</v>
+        <v>59.36708860759494</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7454,7 +7460,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>21.962025316455694</v>
+        <v>21.582278481012658</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7462,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>38.54430379746835</v>
+        <v>42.72151898734178</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>56.708860759493675</v>
+        <v>56.139240506329116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7478,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>35.31645569620253</v>
+        <v>39.493670886075954</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7486,7 +7492,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>49.493670886075954</v>
+        <v>49.74683544303797</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7494,7 +7500,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>40.18987341772152</v>
+        <v>39.683544303797476</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7502,7 +7508,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>35.949367088607595</v>
+        <v>36.962025316455694</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7510,7 +7516,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>66.77215189873418</v>
+        <v>66.39240506329114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7518,7 +7524,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>54.873417721519</v>
+        <v>55.8860759493671</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7534,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>36.20253164556962</v>
+        <v>32.78481012658228</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7542,7 +7548,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>72.02531645569621</v>
+        <v>72.34177215189874</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7550,7 +7556,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>67.40506329113924</v>
+        <v>67.02531645569621</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7558,7 +7564,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>35.50632911392405</v>
+        <v>34.74683544303797</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7566,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>31.20253164556962</v>
+        <v>18.481012658227847</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7574,7 +7580,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>43.16455696202532</v>
+        <v>42.21518987341772</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7582,7 +7588,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>45.75949367088607</v>
+        <v>45.88607594936709</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7590,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>28.924050632911392</v>
+        <v>27.53164556962025</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7598,7 +7604,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>27.151898734177212</v>
+        <v>27.911392405063292</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7606,7 +7612,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>22.27848101265823</v>
+        <v>22.40506329113924</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7614,7 +7620,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>29.746835443037973</v>
+        <v>30.253164556962027</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7622,7 +7628,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.65822784810127</v>
+        <v>62.27848101265823</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7630,7 +7636,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>58.29113924050633</v>
+        <v>57.53164556962027</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7644,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>46.835443037974684</v>
+        <v>44.30379746835443</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7646,7 +7652,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>45.37974683544304</v>
+        <v>44.62025316455696</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7654,7 +7660,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>54.74683544303799</v>
+        <v>55.506329113924046</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,7 +7668,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>51.0126582278481</v>
+        <v>48.607594936708864</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7670,7 +7676,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>58.9873417721519</v>
+        <v>59.36708860759494</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7678,7 +7684,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>65.31645569620254</v>
+        <v>64.9367088607595</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -304,7 +304,7 @@
     <t>2026-05-27</t>
   </si>
   <si>
-    <t>2026-04-22</t>
+    <t>2027-04-22</t>
   </si>
   <si>
     <t>2027-04-16</t>
@@ -409,6 +409,9 @@
     <t>_date_</t>
   </si>
   <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -676,28 +679,25 @@
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Earnings Upcoming, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,10 +1369,10 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>72.34177215189874</v>
+        <v>71.26582278481013</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,37 +1383,37 @@
         <v>67.02531645569621</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B4">
-        <v>66.39240506329114</v>
+        <v>66.39240506329115</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="B5">
-        <v>65.37974683544304</v>
+        <v>66.0126582278481</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>64.9367088607595</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="C6" t="s">
         <v>215</v>
@@ -1421,13 +1421,13 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>62.97468354430381</v>
+        <v>62.27848101265822</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1435,40 +1435,40 @@
         <v>119</v>
       </c>
       <c r="B8">
-        <v>62.27848101265823</v>
+        <v>62.025316455696206</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B9">
-        <v>62.27848101265822</v>
+        <v>61.77215189873419</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="B10">
-        <v>59.36708860759494</v>
+        <v>59.24050632911393</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="B11">
-        <v>59.36708860759494</v>
+        <v>58.67088607594937</v>
       </c>
       <c r="C11" t="s">
         <v>218</v>
@@ -1479,43 +1479,43 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>59.177215189873415</v>
+        <v>58.0379746835443</v>
       </c>
       <c r="C12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="B13">
-        <v>57.53164556962027</v>
+        <v>56.64556962025316</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>56.139240506329116</v>
+        <v>56.075949367088604</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15">
-        <v>55.8860759493671</v>
+        <v>56.075949367088604</v>
       </c>
       <c r="C15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1523,43 +1523,43 @@
         <v>44</v>
       </c>
       <c r="B16">
-        <v>55.56962025316456</v>
+        <v>56.01265822784811</v>
       </c>
       <c r="C16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B17">
-        <v>55.506329113924046</v>
+        <v>55.50632911392406</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>55.31645569620253</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="B19">
-        <v>54.36708860759494</v>
+        <v>54.49367088607595</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1567,40 +1567,40 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>54.177215189873415</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B21">
-        <v>54.11392405063291</v>
+        <v>54.17721518987342</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B22">
-        <v>52.40506329113924</v>
+        <v>53.924050632911396</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>49.74683544303797</v>
+        <v>53.29113924050633</v>
       </c>
       <c r="C23" t="s">
         <v>225</v>
@@ -1608,21 +1608,21 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B24">
-        <v>49.55696202531646</v>
+        <v>48.79746835443038</v>
       </c>
       <c r="C24" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>48.607594936708864</v>
+        <v>48.48101265822785</v>
       </c>
       <c r="C25" t="s">
         <v>221</v>
@@ -1630,21 +1630,21 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>46.07594936708861</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="C26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="B27">
-        <v>45.88607594936709</v>
+        <v>48.037974683544306</v>
       </c>
       <c r="C27" t="s">
         <v>221</v>
@@ -1652,21 +1652,21 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B28">
-        <v>45.12658227848102</v>
+        <v>46.64556962025317</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="B29">
-        <v>44.62025316455696</v>
+        <v>45.25316455696203</v>
       </c>
       <c r="C29" t="s">
         <v>221</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B30">
-        <v>44.430379746835435</v>
+        <v>44.05063291139241</v>
       </c>
       <c r="C30" t="s">
         <v>221</v>
@@ -1685,54 +1685,54 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>44.30379746835443</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B32">
-        <v>43.29113924050633</v>
+        <v>42.151898734177216</v>
       </c>
       <c r="C32" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>42.72151898734178</v>
+        <v>42.025316455696206</v>
       </c>
       <c r="C33" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B34">
-        <v>41.89873417721519</v>
+        <v>41.70886075949368</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B35">
-        <v>41.835443037974684</v>
+        <v>40.31645569620253</v>
       </c>
       <c r="C35" t="s">
         <v>221</v>
@@ -1740,65 +1740,65 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B36">
-        <v>41.51898734177216</v>
+        <v>40.06329113924051</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="B37">
-        <v>40.25316455696203</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>39.683544303797476</v>
+        <v>38.10126582278481</v>
       </c>
       <c r="C38" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B39">
-        <v>39.493670886075954</v>
+        <v>37.025316455696206</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B40">
-        <v>38.734177215189874</v>
+        <v>34.55696202531646</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="B41">
-        <v>36.962025316455694</v>
+        <v>34.49367088607595</v>
       </c>
       <c r="C41" t="s">
         <v>221</v>
@@ -1809,32 +1809,32 @@
         <v>1</v>
       </c>
       <c r="B42">
-        <v>35.88607594936709</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B43">
-        <v>34.74683544303797</v>
+        <v>33.41772151898735</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <v>33.29113924050633</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1842,18 +1842,18 @@
         <v>61</v>
       </c>
       <c r="B45">
-        <v>32.78481012658228</v>
+        <v>32.405063291139236</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B46">
-        <v>32.0253164556962</v>
+        <v>30.949367088607595</v>
       </c>
       <c r="C46" t="s">
         <v>221</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B47">
-        <v>30.949367088607595</v>
+        <v>30.31645569620253</v>
       </c>
       <c r="C47" t="s">
         <v>221</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B48">
-        <v>30.88607594936709</v>
+        <v>30.189873417721518</v>
       </c>
       <c r="C48" t="s">
         <v>221</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B49">
-        <v>30.379746835443036</v>
+        <v>29.303797468354432</v>
       </c>
       <c r="C49" t="s">
         <v>221</v>
@@ -1894,24 +1894,24 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B50">
-        <v>30.253164556962027</v>
+        <v>29.050632911392405</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B51">
-        <v>30.063291139240505</v>
+        <v>26.9620253164557</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2155,49 +2155,49 @@
         <v>0.4</v>
       </c>
       <c r="F2" s="1">
-        <v>0.027931860353250838</v>
+        <v>-0.001133992070301515</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>52.28</v>
+        <v>51.69</v>
       </c>
       <c r="I2" s="1">
-        <v>18.67</v>
+        <v>18.17</v>
       </c>
       <c r="J2" s="1">
-        <v>0.005220301483400658</v>
+        <v>0.0044707771952847</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.04360997786596865</v>
+        <v>-0.08303169024131707</v>
       </c>
       <c r="N2" s="1">
-        <v>5.438616630381111</v>
+        <v>2.7593551430653225</v>
       </c>
       <c r="O2" s="1">
-        <v>50.63291139240506</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>44.05063291139241</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="R2" s="1">
-        <v>35.88607594936709</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>3.04</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2217,31 +2217,31 @@
         <v>1.88</v>
       </c>
       <c r="F3" s="2">
-        <v>1.0235072208940463</v>
+        <v>1.1245287235286383</v>
       </c>
       <c r="G3" s="2">
         <v>2.43</v>
       </c>
       <c r="H3" s="2">
-        <v>69.9</v>
+        <v>72.59</v>
       </c>
       <c r="I3" s="2">
-        <v>96.02</v>
+        <v>102.49</v>
       </c>
       <c r="J3" s="2">
-        <v>0.08399036581141517</v>
+        <v>0.0858707650915428</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M3" s="2">
-        <v>1.1482692070568317</v>
+        <v>1.2673503191195556</v>
       </c>
       <c r="N3" s="2">
-        <v>124.62653512266115</v>
+        <v>137.7975560791526</v>
       </c>
       <c r="O3" s="2">
         <v>97.46835443037975</v>
@@ -2250,7 +2250,7 @@
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.82278481012658</v>
+        <v>75.69620253164557</v>
       </c>
       <c r="R3" s="2">
         <v>65.37974683544304</v>
@@ -2273,55 +2273,55 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D4" s="3">
-        <v>9.865822784810128</v>
+        <v>9.868354430379748</v>
       </c>
       <c r="E4" s="3">
         <v>1.25</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.14794108503638143</v>
+        <v>-0.02897198602682774</v>
       </c>
       <c r="G4" s="3">
         <v>1.11</v>
       </c>
       <c r="H4" s="3">
-        <v>61.71</v>
+        <v>66.21</v>
       </c>
       <c r="I4" s="3">
-        <v>-18.42</v>
+        <v>-15.05</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.00928318100321039</v>
+        <v>-0.007370556919205959</v>
       </c>
       <c r="K4" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>-92</v>
+        <v>-91</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.13834400917770562</v>
+        <v>-0.017985709442911002</v>
       </c>
       <c r="N4" s="3">
-        <v>-4.034786500792572</v>
+        <v>9.26395322290592</v>
       </c>
       <c r="O4" s="3">
-        <v>34.177215189873415</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>35.56962025316456</v>
+        <v>37.34177215189874</v>
       </c>
       <c r="R4" s="3">
-        <v>20.822784810126585</v>
+        <v>26.898734177215193</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>6.01</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2335,55 +2335,55 @@
         <v>43.037974683544306</v>
       </c>
       <c r="D5" s="1">
-        <v>25.247706422018346</v>
+        <v>24.65137614678899</v>
       </c>
       <c r="E5" s="1">
         <v>0.73</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.15227828182852804</v>
+        <v>-0.12404879430885826</v>
       </c>
       <c r="G5" s="1">
         <v>1.79</v>
       </c>
       <c r="H5" s="1">
-        <v>55.38</v>
+        <v>58.3</v>
       </c>
       <c r="I5" s="1">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0032827368053967737</v>
+        <v>0.004019859892690031</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>-82</v>
+        <v>-81</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.08335382793440194</v>
+        <v>-0.0451473533880018</v>
       </c>
       <c r="N5" s="1">
-        <v>1.464231623537795</v>
+        <v>6.547788828396834</v>
       </c>
       <c r="O5" s="1">
-        <v>46.835443037974684</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P5" s="1">
-        <v>29.766948563835548</v>
+        <v>29.30842702737695</v>
       </c>
       <c r="Q5" s="1">
-        <v>58.22784810126582</v>
+        <v>58.607594936708864</v>
       </c>
       <c r="R5" s="1">
-        <v>43.35443037974684</v>
+        <v>43.60759493670887</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.96</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2403,49 +2403,49 @@
         <v>-0.11</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.00911514220646606</v>
+        <v>0.0019236793285661025</v>
       </c>
       <c r="G6" s="1">
         <v>1.53</v>
       </c>
       <c r="H6" s="1">
-        <v>45.77</v>
+        <v>43.87</v>
       </c>
       <c r="I6" s="1">
-        <v>-12.47</v>
+        <v>-13.04</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.009493616798490945</v>
+        <v>-0.00815438806640506</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M6" s="1">
-        <v>0.03712531420351728</v>
+        <v>0.05485755741471032</v>
       </c>
       <c r="N6" s="1">
-        <v>13.512145837329706</v>
+        <v>16.548279908668054</v>
       </c>
       <c r="O6" s="1">
-        <v>62.0253164556962</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>39.49367088607595</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="R6" s="1">
-        <v>41.51898734177216</v>
+        <v>42.151898734177216</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-0.57</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2459,25 +2459,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>4.895865237366003</v>
+        <v>5.070444104134762</v>
       </c>
       <c r="E7" s="2">
         <v>0.36</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.05064256088486585</v>
+        <v>-0.11032541787647918</v>
       </c>
       <c r="G7" s="2">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="H7" s="2">
-        <v>57.76</v>
+        <v>53.71</v>
       </c>
       <c r="I7" s="2">
-        <v>17.48</v>
+        <v>15.13</v>
       </c>
       <c r="J7" s="2">
-        <v>0.02045657536540953</v>
+        <v>0.01935348222607045</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2486,28 +2486,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.05841511932735899</v>
+        <v>0.013519881796763888</v>
       </c>
       <c r="N7" s="2">
-        <v>15.641126349713877</v>
+        <v>12.414512346873414</v>
       </c>
       <c r="O7" s="2">
-        <v>67.08860759493672</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>63.16455696202532</v>
+        <v>61.64556962025316</v>
       </c>
       <c r="R7" s="2">
-        <v>55.18987341772152</v>
+        <v>52.468354430379755</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>0.63</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2521,55 +2521,55 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>-0.003776435045317274</v>
+        <v>0.004531722054380702</v>
       </c>
       <c r="E8" s="2">
         <v>0.19</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2514365958976711</v>
+        <v>0.30022542690549336</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>64.55</v>
+        <v>67.84</v>
       </c>
       <c r="I8" s="2">
-        <v>18.3</v>
+        <v>19.89</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03218269509605345</v>
+        <v>0.032367424037634956</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-215</v>
+        <v>-220</v>
       </c>
       <c r="M8" s="2">
-        <v>0.22090044543824816</v>
+        <v>0.2652690923203038</v>
       </c>
       <c r="N8" s="2">
-        <v>31.8896589608028</v>
+        <v>37.58943339922741</v>
       </c>
       <c r="O8" s="2">
-        <v>81.0126582278481</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>64.30379746835443</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="R8" s="2">
-        <v>54.11392405063291</v>
+        <v>55.31645569620253</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2589,49 +2589,49 @@
         <v>2.36</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.12553678720538466</v>
+        <v>-0.1124771160622832</v>
       </c>
       <c r="G9" s="1">
         <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>48.25</v>
+        <v>47.49</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.62</v>
+        <v>-15.84</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.012439115221174126</v>
+        <v>-0.012185986493189084</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.08191371512049472</v>
+        <v>-0.06253949522629809</v>
       </c>
       <c r="N9" s="1">
-        <v>1.6082429049285185</v>
+        <v>4.808574644567205</v>
       </c>
       <c r="O9" s="1">
-        <v>48.10126582278481</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P9" s="1">
         <v>34.04748479877408</v>
       </c>
       <c r="Q9" s="1">
-        <v>46.20253164556962</v>
+        <v>44.55696202531645</v>
       </c>
       <c r="R9" s="1">
-        <v>39.55696202531645</v>
+        <v>38.54430379746835</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-1.65</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2651,49 +2651,49 @@
         <v>1.48</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.1527100445761728</v>
+        <v>-0.16507857895453248</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>50.15</v>
+        <v>48.68</v>
       </c>
       <c r="I10" s="1">
-        <v>-4.58</v>
+        <v>-5.06</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0017334524830326288</v>
+        <v>0.0023784044631915443</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.11693912546656304</v>
+        <v>-0.12412972986902471</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.8942981296783155</v>
+        <v>-1.3504488197054516</v>
       </c>
       <c r="O10" s="1">
-        <v>41.77215189873418</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>46.20253164556962</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="R10" s="1">
-        <v>37.15189873417721</v>
+        <v>35.9493670886076</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.65</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2713,19 +2713,19 @@
         <v>5.47</v>
       </c>
       <c r="F11" s="2">
-        <v>0.31313487053950356</v>
+        <v>0.4188838046724108</v>
       </c>
       <c r="G11" s="2">
         <v>0.83</v>
       </c>
       <c r="H11" s="2">
-        <v>72.98</v>
+        <v>75.87</v>
       </c>
       <c r="I11" s="2">
-        <v>16.18</v>
+        <v>19.97</v>
       </c>
       <c r="J11" s="2">
-        <v>0.024397799365266714</v>
+        <v>0.027159281919290783</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2734,28 +2734,28 @@
         <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.29830302603064096</v>
+        <v>0.4019050135881759</v>
       </c>
       <c r="N11" s="2">
-        <v>39.629917020042086</v>
+        <v>51.2530255260146</v>
       </c>
       <c r="O11" s="2">
-        <v>84.81012658227847</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>59.87341772151899</v>
+        <v>61.39240506329114</v>
       </c>
       <c r="R11" s="2">
-        <v>52.40506329113924</v>
+        <v>53.29113924050633</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>5.95</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2775,19 +2775,19 @@
         <v>5.82</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.11495934856439913</v>
+        <v>0.016715544305819674</v>
       </c>
       <c r="G12" s="1">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H12" s="1">
-        <v>57.83</v>
+        <v>61.61</v>
       </c>
       <c r="I12" s="1">
-        <v>-28.56</v>
+        <v>-25.29</v>
       </c>
       <c r="J12" s="1">
-        <v>0.004737690201871549</v>
+        <v>0.00975740328561801</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
@@ -2796,28 +2796,28 @@
         <v>-50</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.1271738087481683</v>
+        <v>0.0017342580550241404</v>
       </c>
       <c r="N12" s="1">
-        <v>-2.917766457838849</v>
+        <v>11.235949972699437</v>
       </c>
       <c r="O12" s="1">
-        <v>39.24050632911392</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P12" s="1">
-        <v>49.40073075603063</v>
+        <v>49.188907754993835</v>
       </c>
       <c r="Q12" s="1">
-        <v>50.88607594936709</v>
+        <v>52.27848101265822</v>
       </c>
       <c r="R12" s="1">
-        <v>35.063291139240505</v>
+        <v>39.74683544303798</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="1">
-        <v>14.37</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2837,49 +2837,49 @@
         <v>1.61</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.3062912793813802</v>
+        <v>-0.34627943391667687</v>
       </c>
       <c r="G13" s="3">
         <v>1.4</v>
       </c>
       <c r="H13" s="3">
-        <v>40.75</v>
+        <v>38.12</v>
       </c>
       <c r="I13" s="3">
-        <v>-8.77</v>
+        <v>-11.72</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.005272784783982098</v>
+        <v>-0.0077494339547497315</v>
       </c>
       <c r="K13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3">
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.27139282171346824</v>
+        <v>-0.3063293372478888</v>
       </c>
       <c r="N13" s="3">
-        <v>-17.339667754368836</v>
+        <v>-19.570409557591855</v>
       </c>
       <c r="O13" s="3">
-        <v>11.39240506329114</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>22.405063291139236</v>
+        <v>18.607594936708857</v>
       </c>
       <c r="R13" s="3">
-        <v>7.405063291139241</v>
+        <v>4.620253164556961</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-8.48</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2899,19 +2899,19 @@
         <v>-0.14</v>
       </c>
       <c r="F14" s="1">
-        <v>0.1390879511097546</v>
+        <v>0.25433058752469034</v>
       </c>
       <c r="G14" s="1">
         <v>0.62</v>
       </c>
       <c r="H14" s="1">
-        <v>67.12</v>
+        <v>70.28</v>
       </c>
       <c r="I14" s="1">
-        <v>5.25</v>
+        <v>8.58</v>
       </c>
       <c r="J14" s="1">
-        <v>0.008708453415281732</v>
+        <v>0.011346920685124297</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
@@ -2920,28 +2920,28 @@
         <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>0.10593441632523826</v>
+        <v>0.21637799568934168</v>
       </c>
       <c r="N14" s="1">
-        <v>20.39305604950182</v>
+        <v>32.70032373613118</v>
       </c>
       <c r="O14" s="1">
-        <v>68.35443037974683</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>57.088607594936704</v>
+        <v>58.10126582278481</v>
       </c>
       <c r="R14" s="1">
-        <v>45.12658227848102</v>
+        <v>48.79746835443038</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>9.94</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2961,31 +2961,31 @@
         <v>5.49</v>
       </c>
       <c r="F15" s="2">
-        <v>1.4820291768170744</v>
+        <v>1.5142607110028368</v>
       </c>
       <c r="G15" s="2">
         <v>2.22</v>
       </c>
       <c r="H15" s="2">
-        <v>67.42</v>
+        <v>68.18</v>
       </c>
       <c r="I15" s="2">
-        <v>153.88</v>
+        <v>154.04</v>
       </c>
       <c r="J15" s="2">
-        <v>0.0983215951414108</v>
+        <v>0.09993122229238127</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M15" s="2">
-        <v>1.588469472704206</v>
+        <v>1.6361085058426403</v>
       </c>
       <c r="N15" s="2">
-        <v>168.6465616873986</v>
+        <v>174.67337475146107</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2994,7 +2994,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>70.63291139240506</v>
+        <v>70.50632911392405</v>
       </c>
       <c r="R15" s="2">
         <v>62.27848101265822</v>
@@ -3023,19 +3023,19 @@
         <v>8.13</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.19875093049323717</v>
+        <v>-0.2440648629943353</v>
       </c>
       <c r="G16" s="3">
         <v>1.91</v>
       </c>
       <c r="H16" s="3">
-        <v>42.53</v>
+        <v>44.33</v>
       </c>
       <c r="I16" s="3">
-        <v>-6.43</v>
+        <v>-4.74</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.005908702053133881</v>
+        <v>-0.007032298971321377</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3044,28 +3044,28 @@
         <v>16</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.11935693929873747</v>
+        <v>-0.15317839307284242</v>
       </c>
       <c r="N16" s="3">
-        <v>-2.1360795128957664</v>
+        <v>-4.255315140087222</v>
       </c>
       <c r="O16" s="3">
-        <v>40.50632911392405</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="3">
-        <v>36.202531645569614</v>
+        <v>36.07594936708861</v>
       </c>
       <c r="R16" s="3">
-        <v>28.924050632911392</v>
+        <v>26.265822784810123</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="3">
-        <v>-7.72</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3085,19 +3085,19 @@
         <v>4.24</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.2274051678141531</v>
+        <v>-0.24959727122568215</v>
       </c>
       <c r="G17" s="3">
         <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>45.88</v>
+        <v>47.16</v>
       </c>
       <c r="I17" s="3">
-        <v>-10.53</v>
+        <v>-9.65</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.012522925267832436</v>
+        <v>-0.008520080406664325</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3106,90 +3106,90 @@
         <v>25</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.16458794401191157</v>
+        <v>-0.1776870972218636</v>
       </c>
       <c r="N17" s="3">
-        <v>-6.659179984213176</v>
+        <v>-6.706185554989343</v>
       </c>
       <c r="O17" s="3">
-        <v>30.37974683544304</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>25.443037974683545</v>
+        <v>26.962025316455694</v>
       </c>
       <c r="R17" s="3">
-        <v>18.354430379746837</v>
+        <v>18.60759493670886</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.81</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>8.39</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.3225300756883653</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1.22</v>
-      </c>
-      <c r="H18" s="3">
-        <v>36.75</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-11.53</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.010395965688135948</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="F18" s="1">
+        <v>-0.3099909673030672</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="H18" s="1">
+        <v>36.66</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-11.7</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.00825553229642634</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>37</v>
       </c>
-      <c r="M18" s="3">
-        <v>-0.3033359239710137</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-20.533977980123392</v>
-      </c>
-      <c r="O18" s="3">
-        <v>5.063291139240507</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="M18" s="1">
+        <v>-0.2890171665519534</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-17.83919248799832</v>
+      </c>
+      <c r="O18" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P18" s="1">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="3">
-        <v>46.58227848101266</v>
-      </c>
-      <c r="R18" s="3">
-        <v>28.797468354430382</v>
-      </c>
-      <c r="S18" s="3" t="s">
+      <c r="Q18" s="1">
+        <v>46.962025316455694</v>
+      </c>
+      <c r="R18" s="1">
+        <v>30.189873417721518</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="3">
-        <v>-2.15</v>
+      <c r="T18" s="1">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,49 +3209,49 @@
         <v>-0.16</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.0406580050888016</v>
+        <v>-0.04286677610091033</v>
       </c>
       <c r="G19" s="1">
         <v>0.19</v>
       </c>
       <c r="H19" s="1">
-        <v>49.93</v>
+        <v>54.59</v>
       </c>
       <c r="I19" s="1">
-        <v>12.18</v>
+        <v>14.5</v>
       </c>
       <c r="J19" s="1">
-        <v>0.0013611008632546321</v>
+        <v>0.0017908335374055109</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.1113273818663233</v>
+        <v>-0.12376572185520618</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.3331237696543423</v>
+        <v>-1.3140480183236036</v>
       </c>
       <c r="O19" s="1">
-        <v>44.303797468354425</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>50.63291139240507</v>
+        <v>51.898734177215196</v>
       </c>
       <c r="R19" s="1">
-        <v>41.89873417721519</v>
+        <v>40.31645569620253</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>1.01</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3265,25 +3265,25 @@
         <v>64.55696202531645</v>
       </c>
       <c r="D20" s="1">
-        <v>0.6392092257001646</v>
+        <v>0.6820428336079079</v>
       </c>
       <c r="E20" s="1">
         <v>-3.42</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.04631973281214208</v>
+        <v>-0.04396168819698541</v>
       </c>
       <c r="G20" s="1">
         <v>1.06</v>
       </c>
       <c r="H20" s="1">
-        <v>60.82</v>
+        <v>61.32</v>
       </c>
       <c r="I20" s="1">
-        <v>-1.99</v>
+        <v>-1.69</v>
       </c>
       <c r="J20" s="1">
-        <v>0.001973531003116155</v>
+        <v>0.006194222734067824</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>1</v>
@@ -3292,28 +3292,28 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.041084964161955284</v>
+        <v>-0.03796917369666719</v>
       </c>
       <c r="N20" s="1">
-        <v>5.691118000782456</v>
+        <v>7.265606797530289</v>
       </c>
       <c r="O20" s="1">
-        <v>53.16455696202531</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>50.63291139240507</v>
+        <v>52.025316455696206</v>
       </c>
       <c r="R20" s="1">
-        <v>40.25316455696203</v>
+        <v>40.06329113924051</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>12.85</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3333,19 +3333,19 @@
         <v>4.96</v>
       </c>
       <c r="F21" s="2">
-        <v>0.20951273348804555</v>
+        <v>0.1992697218600915</v>
       </c>
       <c r="G21" s="2">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="H21" s="2">
-        <v>77.28</v>
+        <v>78.27</v>
       </c>
       <c r="I21" s="2">
-        <v>69.13</v>
+        <v>72.92</v>
       </c>
       <c r="J21" s="2">
-        <v>0.029735763076465374</v>
+        <v>0.03469493860499573</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
@@ -3354,10 +3354,10 @@
         <v>37</v>
       </c>
       <c r="M21" s="2">
-        <v>0.24092134538916632</v>
+        <v>0.24021857094559929</v>
       </c>
       <c r="N21" s="2">
-        <v>33.89174895589461</v>
+        <v>35.08438126175695</v>
       </c>
       <c r="O21" s="2">
         <v>83.54430379746836</v>
@@ -3366,16 +3366,16 @@
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="2">
-        <v>69.62025316455696</v>
+        <v>70.37974683544304</v>
       </c>
       <c r="R21" s="2">
-        <v>54.177215189873415</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="2">
-        <v>15.38</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3395,49 +3395,49 @@
         <v>-0.12</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.2510743485294993</v>
+        <v>-0.2542193800312568</v>
       </c>
       <c r="G22" s="1">
         <v>1.37</v>
       </c>
       <c r="H22" s="1">
-        <v>55</v>
+        <v>55.62</v>
       </c>
       <c r="I22" s="1">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.011362562556863336</v>
+        <v>-0.008591392077507557</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.21879327518668068</v>
+        <v>-0.21726554061262782</v>
       </c>
       <c r="N22" s="1">
-        <v>-12.079713101690079</v>
+        <v>-10.664029894065767</v>
       </c>
       <c r="O22" s="1">
-        <v>20.253164556962027</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P22" s="1">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="1">
-        <v>46.70886075949367</v>
+        <v>46.58227848101266</v>
       </c>
       <c r="R22" s="1">
-        <v>30.379746835443036</v>
+        <v>30.31645569620253</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3451,55 +3451,55 @@
         <v>97.46835443037975</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.7684478371501272</v>
+        <v>-0.772446383133406</v>
       </c>
       <c r="E23" s="1">
         <v>-0.36</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.19169843777180187</v>
+        <v>-0.1759503961923806</v>
       </c>
       <c r="G23" s="1">
         <v>1.23</v>
       </c>
       <c r="H23" s="1">
-        <v>43.84</v>
+        <v>45.34</v>
       </c>
       <c r="I23" s="1">
-        <v>-9.38</v>
+        <v>-8.84</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.007105358471664092</v>
+        <v>-0.006523540464090489</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.1716318246127525</v>
+        <v>-0.15297909060782744</v>
       </c>
       <c r="N23" s="1">
-        <v>-7.363568044297268</v>
+        <v>-4.23538489358572</v>
       </c>
       <c r="O23" s="1">
-        <v>27.848101265822784</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>43.417721518987335</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="R23" s="1">
-        <v>32.0253164556962</v>
+        <v>34.49367088607595</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>0.06</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3519,49 +3519,49 @@
         <v>13.86</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.0634294303244769</v>
+        <v>-0.07284893500744283</v>
       </c>
       <c r="G24" s="3">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="H24" s="3">
-        <v>47.53</v>
+        <v>44.64</v>
       </c>
       <c r="I24" s="3">
-        <v>-22.84</v>
+        <v>-24.77</v>
       </c>
       <c r="J24" s="3">
-        <v>0.019851032629593705</v>
+        <v>0.017773128640658612</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="M24" s="3">
-        <v>0.15992069875015957</v>
+        <v>0.18183293125608113</v>
       </c>
       <c r="N24" s="3">
-        <v>25.79168429199395</v>
+        <v>29.24581729280514</v>
       </c>
       <c r="O24" s="3">
-        <v>78.48101265822784</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>24.050632911392405</v>
+        <v>23.29113924050633</v>
       </c>
       <c r="R24" s="3">
-        <v>27.151898734177212</v>
+        <v>26.9620253164557</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-3.86</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3575,55 +3575,55 @@
         <v>11.39240506329114</v>
       </c>
       <c r="D25" s="3">
-        <v>0.8859649122807016</v>
+        <v>-7.127192982456141</v>
       </c>
       <c r="E25" s="3">
         <v>14.49</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.3605580055909993</v>
+        <v>-0.3277111894172485</v>
       </c>
       <c r="G25" s="3">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="H25" s="3">
-        <v>48</v>
+        <v>48.44</v>
       </c>
       <c r="I25" s="3">
-        <v>-51.07</v>
+        <v>-50.4</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.011950955072586474</v>
+        <v>-0.010951427092932576</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.25499017114556566</v>
+        <v>-0.20586339457744485</v>
       </c>
       <c r="N25" s="3">
-        <v>-15.699402697578583</v>
+        <v>-9.523815290547468</v>
       </c>
       <c r="O25" s="3">
-        <v>15.18987341772152</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>23.16455696202532</v>
+        <v>11.265822784810128</v>
       </c>
       <c r="R25" s="3">
-        <v>9.303797468354428</v>
+        <v>2.531645569620256</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-2.66</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3643,49 +3643,49 @@
         <v>3.56</v>
       </c>
       <c r="F26" s="1">
-        <v>0.5692307679270818</v>
+        <v>0.7492105379751037</v>
       </c>
       <c r="G26" s="1">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="H26" s="1">
-        <v>65.13</v>
+        <v>69.21</v>
       </c>
       <c r="I26" s="1">
-        <v>24.7</v>
+        <v>34.44</v>
       </c>
       <c r="J26" s="1">
-        <v>0.043476688115520065</v>
+        <v>0.05065285036023047</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>-27</v>
+        <v>-29</v>
       </c>
       <c r="M26" s="1">
-        <v>0.7480853634751305</v>
+        <v>0.9569510406528017</v>
       </c>
       <c r="N26" s="1">
-        <v>84.60815076449106</v>
+        <v>106.75762823247716</v>
       </c>
       <c r="O26" s="1">
-        <v>92.40506329113924</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P26" s="1">
-        <v>50.63126652197354</v>
+        <v>48.258415122799256</v>
       </c>
       <c r="Q26" s="1">
-        <v>41.265822784810126</v>
+        <v>42.911392405063296</v>
       </c>
       <c r="R26" s="1">
-        <v>33.29113924050633</v>
+        <v>34.55696202531646</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>0.25</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3705,49 +3705,49 @@
         <v>5.04</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.1847643877404258</v>
+        <v>-0.1277690325559252</v>
       </c>
       <c r="G27" s="3">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="H27" s="3">
-        <v>56.59</v>
+        <v>61.22</v>
       </c>
       <c r="I27" s="3">
-        <v>-19.99</v>
+        <v>-15.73</v>
       </c>
       <c r="J27" s="3">
-        <v>0.004046042404553266</v>
+        <v>0.004968354140175307</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M27" s="3">
-        <v>-0.0442980956270802</v>
+        <v>0.034028858952666496</v>
       </c>
       <c r="N27" s="3">
-        <v>5.3698048542699635</v>
+        <v>14.465410062463668</v>
       </c>
       <c r="O27" s="3">
-        <v>49.36708860759494</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>35.189873417721515</v>
+        <v>36.32911392405063</v>
       </c>
       <c r="R27" s="3">
-        <v>24.303797468354432</v>
+        <v>26.9620253164557</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>-2.09</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3767,19 +3767,19 @@
         <v>-1.13</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.3989686198894955</v>
+        <v>-0.4085676363935638</v>
       </c>
       <c r="G28" s="3">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="H28" s="3">
-        <v>51.8</v>
+        <v>56.49</v>
       </c>
       <c r="I28" s="3">
-        <v>-24.07</v>
+        <v>-20.92</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.007510875574774697</v>
+        <v>-0.005411292738181298</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
@@ -3788,28 +3788,28 @@
         <v>-2</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.21487925569125998</v>
+        <v>-0.19683212404898698</v>
       </c>
       <c r="N28" s="3">
-        <v>-11.688311152148007</v>
+        <v>-8.620688237701678</v>
       </c>
       <c r="O28" s="3">
-        <v>22.78481012658228</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>34.68354430379747</v>
+        <v>37.08860759493671</v>
       </c>
       <c r="R28" s="3">
-        <v>20.379746835443044</v>
+        <v>21.32911392405063</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-1.52</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3829,49 +3829,49 @@
         <v>0.88</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.37289377927431483</v>
+        <v>-0.36518581562558294</v>
       </c>
       <c r="G29" s="3">
         <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>42.98</v>
+        <v>42.75</v>
       </c>
       <c r="I29" s="3">
-        <v>-33</v>
+        <v>-33.04</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.0185385326743265</v>
+        <v>-0.01678760244586837</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.27517809780416136</v>
+        <v>-0.2533255449529763</v>
       </c>
       <c r="N29" s="3">
-        <v>-17.718195363438152</v>
+        <v>-14.270030328100617</v>
       </c>
       <c r="O29" s="3">
-        <v>8.860759493670885</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.39240506329114</v>
+        <v>41.139240506329116</v>
       </c>
       <c r="R29" s="3">
-        <v>25.31645569620253</v>
+        <v>26.075949367088604</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>0.95</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3885,55 +3885,55 @@
         <v>46.835443037974684</v>
       </c>
       <c r="D30" s="1">
-        <v>2783.0820512820515</v>
+        <v>1500.169230769231</v>
       </c>
       <c r="E30" s="1">
         <v>2.51</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.16897292648512433</v>
+        <v>-0.18015765004783127</v>
       </c>
       <c r="G30" s="1">
         <v>1.2</v>
       </c>
       <c r="H30" s="1">
-        <v>45.31</v>
+        <v>44.85</v>
       </c>
       <c r="I30" s="1">
-        <v>0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.001111231471188121</v>
+        <v>0.0003414019685547603</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.15152369765116835</v>
+        <v>-0.16018260171343723</v>
       </c>
       <c r="N30" s="1">
-        <v>-5.352755348138846</v>
+        <v>-4.955736004146704</v>
       </c>
       <c r="O30" s="1">
-        <v>31.645569620253166</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>60.63291139240506</v>
+        <v>60.25316455696203</v>
       </c>
       <c r="R30" s="1">
-        <v>46.07594936708861</v>
+        <v>45.25316455696203</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-1.46</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3953,49 +3953,49 @@
         <v>0.99</v>
       </c>
       <c r="F31" s="2">
-        <v>0.11075290164967816</v>
+        <v>0.10110524376514901</v>
       </c>
       <c r="G31" s="2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H31" s="2">
-        <v>53.28</v>
+        <v>53.07</v>
       </c>
       <c r="I31" s="2">
-        <v>18.69</v>
+        <v>18.38</v>
       </c>
       <c r="J31" s="2">
-        <v>0.021555994091210093</v>
+        <v>0.020676617691050638</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M31" s="2">
-        <v>0.1482687436426835</v>
+        <v>0.1430528452673765</v>
       </c>
       <c r="N31" s="2">
-        <v>24.626488781246344</v>
+        <v>25.36780869393467</v>
       </c>
       <c r="O31" s="2">
-        <v>74.68354430379746</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>65.69620253164557</v>
+        <v>64.17721518987341</v>
       </c>
       <c r="R31" s="2">
-        <v>59.177215189873415</v>
+        <v>58.0379746835443</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-1.65</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4015,19 +4015,19 @@
         <v>1.51</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.22456277578446823</v>
+        <v>-0.22101436430786242</v>
       </c>
       <c r="G32" s="3">
         <v>1.61</v>
       </c>
       <c r="H32" s="3">
-        <v>44.69</v>
+        <v>45.41</v>
       </c>
       <c r="I32" s="3">
-        <v>-7.85</v>
+        <v>-7.47</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.015048619622600816</v>
+        <v>-0.014663438154852729</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>1</v>
@@ -4036,28 +4036,28 @@
         <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.17134262784090248</v>
+        <v>-0.16009046688796058</v>
       </c>
       <c r="N32" s="3">
-        <v>-7.334648367112265</v>
+        <v>-4.946522521599034</v>
       </c>
       <c r="O32" s="3">
-        <v>29.11392405063291</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P32" s="3">
-        <v>40.689656926297594</v>
+        <v>39.09348709793037</v>
       </c>
       <c r="Q32" s="3">
-        <v>30.50632911392405</v>
+        <v>30.63291139240506</v>
       </c>
       <c r="R32" s="3">
-        <v>19.81012658227848</v>
+        <v>20.44303797468354</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-9.56</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4077,19 +4077,19 @@
         <v>0.66</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.05081724524320652</v>
+        <v>-0.03092047167602477</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>54.83</v>
+        <v>54.42</v>
       </c>
       <c r="I33" s="1">
-        <v>-9.08</v>
+        <v>-9.09</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0031762123683346044</v>
+        <v>0.003448564153746001</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
@@ -4098,10 +4098,10 @@
         <v>7</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.04296509226792633</v>
+        <v>-0.021931699925547443</v>
       </c>
       <c r="N33" s="1">
-        <v>5.5031051901853605</v>
+        <v>8.869354174642272</v>
       </c>
       <c r="O33" s="1">
         <v>51.89873417721519</v>
@@ -4110,16 +4110,16 @@
         <v>26.894390179645494</v>
       </c>
       <c r="Q33" s="1">
-        <v>51.01265822784809</v>
+        <v>50.25316455696202</v>
       </c>
       <c r="R33" s="1">
-        <v>41.835443037974684</v>
+        <v>42.025316455696206</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4139,49 +4139,49 @@
         <v>0.94</v>
       </c>
       <c r="F34" s="1">
-        <v>0.11006463623909721</v>
+        <v>0.09288490979336392</v>
       </c>
       <c r="G34" s="1">
         <v>1.26</v>
       </c>
       <c r="H34" s="1">
-        <v>61.59</v>
+        <v>57.49</v>
       </c>
       <c r="I34" s="1">
-        <v>31.3</v>
+        <v>29.3</v>
       </c>
       <c r="J34" s="1">
-        <v>0.02638572750280521</v>
+        <v>0.025243074025964922</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M34" s="1">
-        <v>0.13274863372323997</v>
+        <v>0.11885247262807619</v>
       </c>
       <c r="N34" s="1">
-        <v>23.07447778930199</v>
+        <v>22.947771430004632</v>
       </c>
       <c r="O34" s="1">
-        <v>72.15189873417721</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P34" s="1">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="1">
-        <v>59.87341772151899</v>
+        <v>58.10126582278481</v>
       </c>
       <c r="R34" s="1">
-        <v>49.55696202531646</v>
+        <v>48.48101265822785</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="1">
-        <v>-1.58</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4201,19 +4201,19 @@
         <v>4.55</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.27603505142950363</v>
+        <v>-0.32003676981025153</v>
       </c>
       <c r="G35" s="3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>38.67</v>
+        <v>38.72</v>
       </c>
       <c r="I35" s="3">
-        <v>-21.44</v>
+        <v>-21.31</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.025712962349870347</v>
+        <v>-0.02469207948983701</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
@@ -4222,28 +4222,28 @@
         <v>18</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.27516258998780585</v>
+        <v>-0.32003676981025153</v>
       </c>
       <c r="N35" s="3">
-        <v>-17.7166445818026</v>
+        <v>-20.941152813828133</v>
       </c>
       <c r="O35" s="3">
-        <v>10.126582278481013</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P35" s="3">
-        <v>29.3533388963776</v>
+        <v>29.069873353982</v>
       </c>
       <c r="Q35" s="3">
-        <v>33.67088607594936</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="R35" s="3">
-        <v>23.037974683544306</v>
+        <v>21.582278481012654</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>1.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4263,49 +4263,49 @@
         <v>-1.05</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.13902466219710818</v>
+        <v>-0.12169121164446169</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>47.71</v>
+        <v>51.69</v>
       </c>
       <c r="I36" s="1">
-        <v>-11.87</v>
+        <v>-9.27</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.015729673228476845</v>
+        <v>-0.011939157521507997</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.1285551248967346</v>
+        <v>-0.10970618264382526</v>
       </c>
       <c r="N36" s="1">
-        <v>-3.0558980726954723</v>
+        <v>0.09190590281449364</v>
       </c>
       <c r="O36" s="1">
-        <v>35.44303797468354</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="1">
-        <v>40.75949367088607</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="R36" s="1">
-        <v>31.83544303797468</v>
+        <v>33.670886075949355</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>-2.47</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4319,55 +4319,55 @@
         <v>62.0253164556962</v>
       </c>
       <c r="D37" s="1">
-        <v>0.5722326454033773</v>
+        <v>0.6022514071294557</v>
       </c>
       <c r="E37" s="1">
         <v>1.72</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.06665182461711225</v>
+        <v>-0.14349280848462048</v>
       </c>
       <c r="G37" s="1">
         <v>1.37</v>
       </c>
       <c r="H37" s="1">
-        <v>36.52</v>
+        <v>36.18</v>
       </c>
       <c r="I37" s="1">
-        <v>-22.77</v>
+        <v>-22.72</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.004296391795720951</v>
+        <v>-0.0029765608373550573</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>-209</v>
+        <v>-214</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.034370751274293676</v>
+        <v>-0.10653896906599147</v>
       </c>
       <c r="N37" s="1">
-        <v>6.362539289548609</v>
+        <v>0.4086272605978657</v>
       </c>
       <c r="O37" s="1">
-        <v>54.43037974683544</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P37" s="1">
         <v>34.910057902834</v>
       </c>
       <c r="Q37" s="1">
-        <v>36.835443037974684</v>
+        <v>37.46835443037975</v>
       </c>
       <c r="R37" s="1">
-        <v>35.63291139240506</v>
+        <v>31.962025316455698</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>-3.16</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4387,49 +4387,49 @@
         <v>-0.05</v>
       </c>
       <c r="F38" s="2">
-        <v>0.5587780956043003</v>
+        <v>0.769206763363862</v>
       </c>
       <c r="G38" s="2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H38" s="2">
-        <v>85.71</v>
+        <v>86.86</v>
       </c>
       <c r="I38" s="2">
-        <v>39.66</v>
+        <v>42.62</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04374023280066799</v>
+        <v>0.04584876050881439</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L38" s="2">
-        <v>-43</v>
+        <v>-45</v>
       </c>
       <c r="M38" s="2">
-        <v>0.5701200943463716</v>
+        <v>0.7831892971979377</v>
       </c>
       <c r="N38" s="2">
-        <v>66.81162385161515</v>
+        <v>89.3814538869908</v>
       </c>
       <c r="O38" s="2">
-        <v>89.87341772151899</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P38" s="2">
-        <v>27.505487150580247</v>
+        <v>27.21170468568715</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.94936708860759</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="R38" s="2">
-        <v>55.31645569620253</v>
+        <v>56.075949367088604</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4449,19 +4449,19 @@
         <v>-6.6</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.14020282536088596</v>
+        <v>-0.0811210225426576</v>
       </c>
       <c r="G39" s="1">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H39" s="1">
-        <v>32.73</v>
+        <v>35.01</v>
       </c>
       <c r="I39" s="1">
-        <v>-7.44</v>
+        <v>-5.9</v>
       </c>
       <c r="J39" s="1">
-        <v>0.011332756504892363</v>
+        <v>0.009717900111905141</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4470,28 +4470,28 @@
         <v>-4</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.11577390499334761</v>
+        <v>-0.05415470729122562</v>
       </c>
       <c r="N39" s="1">
-        <v>-1.7777760823567708</v>
+        <v>5.647053438074448</v>
       </c>
       <c r="O39" s="1">
-        <v>43.037974683544306</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P39" s="1">
         <v>20.072334383381026</v>
       </c>
       <c r="Q39" s="1">
-        <v>49.49367088607595</v>
+        <v>48.607594936708864</v>
       </c>
       <c r="R39" s="1">
-        <v>43.29113924050633</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1">
-        <v>-10.13</v>
+        <v>-9.37</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4511,19 +4511,19 @@
         <v>10.16</v>
       </c>
       <c r="F40" s="1">
-        <v>0.12113538137666495</v>
+        <v>0.13779721740368814</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>41.58</v>
+        <v>39.98</v>
       </c>
       <c r="I40" s="1">
-        <v>-20.06</v>
+        <v>-21.71</v>
       </c>
       <c r="J40" s="1">
-        <v>0.00021513960292798547</v>
+        <v>-0.0006554449553725636</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4532,19 +4532,19 @@
         <v>54</v>
       </c>
       <c r="M40" s="1">
-        <v>0.03388923720688508</v>
+        <v>0.03792197573171796</v>
       </c>
       <c r="N40" s="1">
-        <v>13.188538137666503</v>
+        <v>14.854721740368806</v>
       </c>
       <c r="O40" s="1">
         <v>60.75949367088608</v>
       </c>
       <c r="P40" s="1">
-        <v>45.29877115964868</v>
+        <v>41.90387479248795</v>
       </c>
       <c r="Q40" s="1">
-        <v>32.15189873417721</v>
+        <v>31.139240506329113</v>
       </c>
       <c r="R40" s="1">
         <v>30.949367088607595</v>
@@ -4573,19 +4573,19 @@
         <v>-1.71</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.022102909273169644</v>
+        <v>0.050500989837036075</v>
       </c>
       <c r="G41" s="1">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H41" s="1">
-        <v>60.76</v>
+        <v>64.73</v>
       </c>
       <c r="I41" s="1">
-        <v>-11.29</v>
+        <v>-7.69</v>
       </c>
       <c r="J41" s="1">
-        <v>0.021516600527013423</v>
+        <v>0.023121818474921865</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -4594,28 +4594,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.015123217739587247</v>
+        <v>0.0594897615875134</v>
       </c>
       <c r="N41" s="1">
-        <v>8.287292643019267</v>
+        <v>17.01150032594835</v>
       </c>
       <c r="O41" s="1">
-        <v>56.9620253164557</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>43.41772151898734</v>
+        <v>45.31645569620253</v>
       </c>
       <c r="R41" s="1">
-        <v>30.88607594936709</v>
+        <v>33.41772151898735</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>0.82</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4635,19 +4635,19 @@
         <v>0.29</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.07142306224176825</v>
+        <v>-0.0699030450840376</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>45.57</v>
+        <v>50.31</v>
       </c>
       <c r="I42" s="1">
-        <v>0.07</v>
+        <v>1.28</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.005283726792209556</v>
+        <v>-0.004424363322930709</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4656,28 +4656,28 @@
         <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.12726059451042737</v>
+        <v>-0.1338231997540985</v>
       </c>
       <c r="N42" s="1">
-        <v>-2.9264450340647534</v>
+        <v>-2.319795808212828</v>
       </c>
       <c r="O42" s="1">
-        <v>37.9746835443038</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>44.81012658227848</v>
+        <v>46.075949367088604</v>
       </c>
       <c r="R42" s="1">
-        <v>38.734177215189874</v>
+        <v>38.10126582278481</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>0.19</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4697,49 +4697,49 @@
         <v>6.54</v>
       </c>
       <c r="F43" s="1">
-        <v>0.0021223541321298833</v>
+        <v>0.12052422642201771</v>
       </c>
       <c r="G43" s="1">
         <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>52.07</v>
+        <v>56.6</v>
       </c>
       <c r="I43" s="1">
-        <v>-11.67</v>
+        <v>-8.67</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.008069792515067628</v>
+        <v>-0.00852113243900843</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M43" s="1">
-        <v>0.027423735941366045</v>
+        <v>0.14948804650688907</v>
       </c>
       <c r="N43" s="1">
-        <v>12.541988011114594</v>
+        <v>26.011328817885932</v>
       </c>
       <c r="O43" s="1">
-        <v>59.49367088607595</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P43" s="1">
-        <v>36.79958124823221</v>
+        <v>34.72409420196845</v>
       </c>
       <c r="Q43" s="1">
-        <v>50.88607594936709</v>
+        <v>51.39240506329114</v>
       </c>
       <c r="R43" s="1">
-        <v>44.430379746835435</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>2.28</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4759,49 +4759,49 @@
         <v>-1.94</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.4075590833031939</v>
+        <v>-0.39318426248220456</v>
       </c>
       <c r="G44" s="3">
         <v>2.61</v>
       </c>
       <c r="H44" s="3">
-        <v>43.15</v>
+        <v>41.41</v>
       </c>
       <c r="I44" s="3">
-        <v>-25.44</v>
+        <v>-26.63</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.023995073485427624</v>
+        <v>-0.022231096579952134</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.2670927911898483</v>
+        <v>-0.23238512339033257</v>
       </c>
       <c r="N44" s="3">
-        <v>-16.909664702006847</v>
+        <v>-12.175988171836241</v>
       </c>
       <c r="O44" s="3">
-        <v>12.658227848101266</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P44" s="3">
         <v>44.155007607957295</v>
       </c>
       <c r="Q44" s="3">
-        <v>40.25316455696202</v>
+        <v>39.87341772151898</v>
       </c>
       <c r="R44" s="3">
-        <v>26.13924050632911</v>
+        <v>26.89873417721519</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>-0.38</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4815,55 +4815,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.739545997610514</v>
+        <v>0.7335722819593788</v>
       </c>
       <c r="E45" s="2">
         <v>1.15</v>
       </c>
       <c r="F45" s="2">
-        <v>0.13958225996866705</v>
+        <v>0.14084531898662195</v>
       </c>
       <c r="G45" s="2">
         <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>60.81</v>
+        <v>57.98</v>
       </c>
       <c r="I45" s="2">
-        <v>16.55</v>
+        <v>15.51</v>
       </c>
       <c r="J45" s="2">
-        <v>0.021135348615555098</v>
+        <v>0.022033896895650402</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M45" s="2">
-        <v>0.1797154862867658</v>
+        <v>0.18678793015572825</v>
       </c>
       <c r="N45" s="2">
-        <v>27.77116304565458</v>
+        <v>29.741317182769844</v>
       </c>
       <c r="O45" s="2">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>61.01265822784809</v>
+        <v>61.39240506329115</v>
       </c>
       <c r="R45" s="2">
-        <v>55.56962025316456</v>
+        <v>56.01265822784811</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-1.39</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4883,19 +4883,19 @@
         <v>-0.24</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3042127833263596</v>
+        <v>-0.3013338283281196</v>
       </c>
       <c r="G46" s="3">
         <v>1.49</v>
       </c>
       <c r="H46" s="3">
-        <v>42.46</v>
+        <v>43.29</v>
       </c>
       <c r="I46" s="3">
-        <v>0.78</v>
+        <v>1.56</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.013137369371077465</v>
+        <v>-0.013030900913801135</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4904,13 +4904,13 @@
         <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2614621726831674</v>
+        <v>-0.2523949599088542</v>
       </c>
       <c r="N46" s="3">
-        <v>-16.346602851338748</v>
+        <v>-14.176971823688397</v>
       </c>
       <c r="O46" s="3">
-        <v>13.924050632911392</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
@@ -4919,13 +4919,13 @@
         <v>44.55696202531645</v>
       </c>
       <c r="R46" s="3">
-        <v>26.329113924050628</v>
+        <v>25.82278481012658</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-5.06</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4945,19 +4945,19 @@
         <v>-3.9</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.3939530003995467</v>
+        <v>-0.4150914673166066</v>
       </c>
       <c r="G47" s="3">
         <v>1.47</v>
       </c>
       <c r="H47" s="3">
-        <v>31.87</v>
+        <v>29.59</v>
       </c>
       <c r="I47" s="3">
-        <v>-19.49</v>
+        <v>-21.33</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030086966933014016</v>
+        <v>-0.030154678156920967</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4966,28 +4966,28 @@
         <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.3529473126397502</v>
+        <v>-0.3681501037307806</v>
       </c>
       <c r="N47" s="3">
-        <v>-25.495116846997036</v>
+        <v>-25.75248620588105</v>
       </c>
       <c r="O47" s="3">
-        <v>3.79746835443038</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="P47" s="3">
         <v>31.304415950527737</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.60759493670887</v>
+        <v>38.35443037974684</v>
       </c>
       <c r="R47" s="3">
-        <v>25.12658227848101</v>
+        <v>25.06329113924051</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>-0.63</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5007,19 +5007,19 @@
         <v>-0.2</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.19228261907645844</v>
+        <v>-0.1961864966707575</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>58.05</v>
+        <v>59.34</v>
       </c>
       <c r="I48" s="1">
-        <v>-3.83</v>
+        <v>-3.3</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.003011979719898767</v>
+        <v>-0.0012034373497541123</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>0</v>
@@ -5028,28 +5028,28 @@
         <v>-65</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.19053769619306282</v>
+        <v>-0.19418899183731808</v>
       </c>
       <c r="N48" s="1">
-        <v>-9.254155202328294</v>
+        <v>-8.35637501653479</v>
       </c>
       <c r="O48" s="1">
-        <v>25.31645569620253</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>48.35443037974684</v>
+        <v>48.860759493670884</v>
       </c>
       <c r="R48" s="1">
-        <v>33.291139240506325</v>
+        <v>33.9873417721519</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>7.09</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5069,19 +5069,19 @@
         <v>-1.46</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.011418435823207312</v>
+        <v>-0.008396537236975032</v>
       </c>
       <c r="G49" s="2">
         <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>52.6</v>
+        <v>55.55</v>
       </c>
       <c r="I49" s="2">
-        <v>38.85</v>
+        <v>40.57</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02144784795912899</v>
+        <v>0.021270426257997646</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5090,28 +5090,28 @@
         <v>267</v>
       </c>
       <c r="M49" s="2">
-        <v>0.041801712120358436</v>
+        <v>0.05252736018292681</v>
       </c>
       <c r="N49" s="2">
-        <v>13.979785629013833</v>
+        <v>16.315260185489695</v>
       </c>
       <c r="O49" s="2">
-        <v>64.55696202531645</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>62.78481012658227</v>
+        <v>63.41772151898734</v>
       </c>
       <c r="R49" s="2">
-        <v>54.36708860759494</v>
+        <v>53.924050632911396</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.95</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5125,55 +5125,55 @@
         <v>26.582278481012654</v>
       </c>
       <c r="D50" s="2">
-        <v>1709.8333333333335</v>
+        <v>1715.8333333333335</v>
       </c>
       <c r="E50" s="2">
         <v>3.55</v>
       </c>
       <c r="F50" s="2">
-        <v>0.7452018104109689</v>
+        <v>0.49598507803288117</v>
       </c>
       <c r="G50" s="2">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="H50" s="2">
-        <v>64.84</v>
+        <v>62.9</v>
       </c>
       <c r="I50" s="2">
-        <v>133.6</v>
+        <v>127.24</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06350441819852608</v>
+        <v>0.06570818455956147</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M50" s="2">
-        <v>0.9886185526446547</v>
+        <v>0.7766345071311174</v>
       </c>
       <c r="N50" s="2">
-        <v>108.66146968144344</v>
+        <v>88.72597488030875</v>
       </c>
       <c r="O50" s="2">
-        <v>96.20253164556962</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P50" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>74.17721518987341</v>
+        <v>73.67088607594935</v>
       </c>
       <c r="R50" s="2">
-        <v>62.97468354430381</v>
+        <v>61.77215189873419</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-0.57</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5187,55 +5187,55 @@
         <v>54.43037974683544</v>
       </c>
       <c r="D51" s="2">
-        <v>7.768844221105527</v>
+        <v>7.922110552763819</v>
       </c>
       <c r="E51" s="2">
         <v>-0.69</v>
       </c>
       <c r="F51" s="2">
-        <v>0.13454722585602455</v>
+        <v>0.11579355688641743</v>
       </c>
       <c r="G51" s="2">
         <v>2.08</v>
       </c>
       <c r="H51" s="2">
-        <v>48.21</v>
+        <v>49.75</v>
       </c>
       <c r="I51" s="2">
-        <v>56.39</v>
+        <v>57.64</v>
       </c>
       <c r="J51" s="2">
-        <v>0.025706510035935094</v>
+        <v>0.021511233691275233</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M51" s="2">
-        <v>0.22877306155938681</v>
+        <v>0.22365881789214526</v>
       </c>
       <c r="N51" s="2">
-        <v>32.67692057291667</v>
+        <v>33.428405956411545</v>
       </c>
       <c r="O51" s="2">
-        <v>82.27848101265823</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P51" s="2">
         <v>16.096535574030653</v>
       </c>
       <c r="Q51" s="2">
-        <v>63.291139240506325</v>
+        <v>62.15189873417721</v>
       </c>
       <c r="R51" s="2">
-        <v>59.36708860759494</v>
+        <v>58.67088607594937</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-3.67</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5255,49 +5255,49 @@
         <v>2.59</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.4020790605047201</v>
+        <v>-0.364557901977156</v>
       </c>
       <c r="G52" s="3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H52" s="3">
-        <v>44.61</v>
+        <v>50.05</v>
       </c>
       <c r="I52" s="3">
-        <v>-21.93</v>
+        <v>-18.12</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.043348280154426724</v>
+        <v>-0.04015899048815746</v>
       </c>
       <c r="K52" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.3540936812113411</v>
+        <v>-0.3106252714742921</v>
       </c>
       <c r="N52" s="3">
-        <v>-25.609753704156123</v>
+        <v>-20.000002980232196</v>
       </c>
       <c r="O52" s="3">
-        <v>2.5316455696202533</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P52" s="3">
         <v>46.37680917379436</v>
       </c>
       <c r="Q52" s="3">
-        <v>39.36708860759494</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="R52" s="3">
-        <v>21.582278481012658</v>
+        <v>22.34177215189873</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T52" s="3">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5317,49 +5317,49 @@
         <v>16.72</v>
       </c>
       <c r="F53" s="1">
-        <v>0.19484454851966937</v>
+        <v>0.1010039593108322</v>
       </c>
       <c r="G53" s="1">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="H53" s="1">
-        <v>53.38</v>
+        <v>55.97</v>
       </c>
       <c r="I53" s="1">
-        <v>27.92</v>
+        <v>32.83</v>
       </c>
       <c r="J53" s="1">
-        <v>0.015484289853139582</v>
+        <v>0.01565913053868878</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M53" s="1">
-        <v>0.3117543817071744</v>
+        <v>0.23583553556799197</v>
       </c>
       <c r="N53" s="1">
-        <v>40.97505258769542</v>
+        <v>34.64607772399621</v>
       </c>
       <c r="O53" s="1">
-        <v>86.07594936708861</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>49.620253164556964</v>
+        <v>50.253164556962034</v>
       </c>
       <c r="R53" s="1">
-        <v>42.72151898734178</v>
+        <v>41.70886075949368</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>16.08</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5379,49 +5379,49 @@
         <v>0.25</v>
       </c>
       <c r="F54" s="2">
-        <v>0.06362512898475944</v>
+        <v>0.06585021912277064</v>
       </c>
       <c r="G54" s="2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H54" s="2">
-        <v>62.58</v>
+        <v>63.61</v>
       </c>
       <c r="I54" s="2">
-        <v>61.21</v>
+        <v>61.97</v>
       </c>
       <c r="J54" s="2">
-        <v>0.03011599986989472</v>
+        <v>0.03202917030148295</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M54" s="2">
-        <v>0.13603942864567675</v>
+        <v>0.14974542212722564</v>
       </c>
       <c r="N54" s="2">
-        <v>23.403557281545655</v>
+        <v>26.037066379919594</v>
       </c>
       <c r="O54" s="2">
-        <v>73.41772151898735</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>68.35443037974683</v>
+        <v>68.1012658227848</v>
       </c>
       <c r="R54" s="2">
-        <v>56.139240506329116</v>
+        <v>56.64556962025316</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5441,19 +5441,19 @@
         <v>6.64</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.016949338328947877</v>
+        <v>-0.07234659513805125</v>
       </c>
       <c r="G55" s="1">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="H55" s="1">
-        <v>59.85</v>
+        <v>57.35</v>
       </c>
       <c r="I55" s="1">
-        <v>-17.2</v>
+        <v>-18.98</v>
       </c>
       <c r="J55" s="1">
-        <v>0.013468207208819055</v>
+        <v>0.01402616645189427</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5462,90 +5462,90 @@
         <v>-16</v>
       </c>
       <c r="M55" s="1">
-        <v>0.12002710801760652</v>
+        <v>0.08645503912038133</v>
       </c>
       <c r="N55" s="1">
-        <v>21.80232521873865</v>
+        <v>19.708028079235163</v>
       </c>
       <c r="O55" s="1">
-        <v>70.88607594936708</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P55" s="1">
-        <v>48.21894075039502</v>
+        <v>47.85651899372094</v>
       </c>
       <c r="Q55" s="1">
-        <v>46.962025316455694</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="R55" s="1">
-        <v>39.493670886075954</v>
+        <v>37.84810126582278</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>4.37</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>0.54</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>35.44303797468354</v>
       </c>
-      <c r="D56" s="1">
-        <v>40.407407407407405</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="D56" s="2">
+        <v>41.24074074074074</v>
+      </c>
+      <c r="E56" s="2">
         <v>-0.43</v>
       </c>
-      <c r="F56" s="1">
-        <v>-0.06780606705672479</v>
-      </c>
-      <c r="G56" s="1">
+      <c r="F56" s="2">
+        <v>0.11953827030950842</v>
+      </c>
+      <c r="G56" s="2">
         <v>1.44</v>
       </c>
-      <c r="H56" s="1">
-        <v>57.7</v>
-      </c>
-      <c r="I56" s="1">
-        <v>6.17</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0.02475993056153192</v>
-      </c>
-      <c r="K56" s="1" t="b">
+      <c r="H56" s="2">
+        <v>67.97</v>
+      </c>
+      <c r="I56" s="2">
+        <v>16.95</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.02643282429830356</v>
+      </c>
+      <c r="K56" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L56" s="1">
-        <v>14</v>
-      </c>
-      <c r="M56" s="1">
-        <v>-0.029417763622021642</v>
-      </c>
-      <c r="N56" s="1">
-        <v>6.857838054775812</v>
-      </c>
-      <c r="O56" s="1">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="P56" s="1">
+      <c r="L56" s="2">
+        <v>13</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.16348337664517532</v>
+      </c>
+      <c r="N56" s="2">
+        <v>27.410861831714556</v>
+      </c>
+      <c r="O56" s="2">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
-      <c r="Q56" s="1">
-        <v>63.79746835443038</v>
-      </c>
-      <c r="R56" s="1">
-        <v>49.74683544303797</v>
-      </c>
-      <c r="S56" s="1" t="s">
+      <c r="Q56" s="2">
+        <v>67.21518987341771</v>
+      </c>
+      <c r="R56" s="2">
+        <v>56.075949367088604</v>
+      </c>
+      <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="T56" s="1">
-        <v>-2.91</v>
+      <c r="T56" s="2">
+        <v>3.42</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5565,49 +5565,49 @@
         <v>-0.26</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.14590697229295946</v>
+        <v>-0.11730494517228027</v>
       </c>
       <c r="G57" s="1">
         <v>1.21</v>
       </c>
       <c r="H57" s="1">
-        <v>50.49</v>
+        <v>52.67</v>
       </c>
       <c r="I57" s="1">
-        <v>-0.42</v>
+        <v>0.12</v>
       </c>
       <c r="J57" s="1">
-        <v>0.004135811761639357</v>
+        <v>0.005999990509569193</v>
       </c>
       <c r="K57" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>-58</v>
+        <v>-61</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.12758528201730568</v>
+        <v>-0.09633114442116653</v>
       </c>
       <c r="N57" s="1">
-        <v>-2.958913784752585</v>
+        <v>1.429409725080361</v>
       </c>
       <c r="O57" s="1">
-        <v>36.708860759493675</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>51.139240506329116</v>
+        <v>51.39240506329114</v>
       </c>
       <c r="R57" s="1">
-        <v>39.683544303797476</v>
+        <v>41.20253164556962</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5627,49 +5627,49 @@
         <v>0.81</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.0778070005847936</v>
+        <v>-0.08349595598191203</v>
       </c>
       <c r="G58" s="1">
         <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>54.27</v>
+        <v>58.3</v>
       </c>
       <c r="I58" s="1">
-        <v>10.12</v>
+        <v>11.2</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.0053363047072461966</v>
+        <v>-0.004897002451665471</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.1423691472704307</v>
+        <v>-0.15740363481916997</v>
       </c>
       <c r="N58" s="1">
-        <v>-4.437300310065081</v>
+        <v>-4.677839314719978</v>
       </c>
       <c r="O58" s="1">
-        <v>32.91139240506329</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>48.22784810126582</v>
+        <v>49.74683544303798</v>
       </c>
       <c r="R58" s="1">
-        <v>36.962025316455694</v>
+        <v>37.025316455696206</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5689,49 +5689,49 @@
         <v>0.11</v>
       </c>
       <c r="F59" s="2">
-        <v>0.5972754899550032</v>
+        <v>0.5744733690140957</v>
       </c>
       <c r="G59" s="2">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H59" s="2">
-        <v>66.92</v>
+        <v>65.07</v>
       </c>
       <c r="I59" s="2">
-        <v>138.64</v>
+        <v>132.83</v>
       </c>
       <c r="J59" s="2">
-        <v>0.06756761523097267</v>
+        <v>0.06739914545941446</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M59" s="2">
-        <v>0.6819042497996897</v>
+        <v>0.6733498582693462</v>
       </c>
       <c r="N59" s="2">
-        <v>77.99003939694697</v>
+        <v>78.39750999413165</v>
       </c>
       <c r="O59" s="2">
-        <v>91.13924050632912</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P59" s="2">
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>80.25316455696203</v>
+        <v>79.62025316455697</v>
       </c>
       <c r="R59" s="2">
-        <v>66.39240506329114</v>
+        <v>66.0126582278481</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T59" s="2">
-        <v>-0.95</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5751,111 +5751,111 @@
         <v>-2.31</v>
       </c>
       <c r="F60" s="2">
-        <v>0.13903663873672087</v>
+        <v>0.1153393370630337</v>
       </c>
       <c r="G60" s="2">
         <v>1.23</v>
       </c>
       <c r="H60" s="2">
-        <v>51.54</v>
+        <v>50.66</v>
       </c>
       <c r="I60" s="2">
-        <v>41.22</v>
+        <v>40.18</v>
       </c>
       <c r="J60" s="2">
-        <v>0.02121920637804616</v>
+        <v>0.020545424539150047</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M60" s="2">
-        <v>0.15910325189577024</v>
+        <v>0.13831064264758686</v>
       </c>
       <c r="N60" s="2">
-        <v>25.70993960655502</v>
+        <v>24.89358843195571</v>
       </c>
       <c r="O60" s="2">
-        <v>77.21518987341773</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P60" s="2">
         <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>59.24050632911392</v>
+        <v>58.48101265822784</v>
       </c>
       <c r="R60" s="2">
-        <v>55.8860759493671</v>
+        <v>54.17721518987342</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-0.7</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="3">
         <v>6.37</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="3">
         <v>67.08860759493672</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="3">
         <v>-0.13029827315541603</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="3">
         <v>0.62</v>
       </c>
-      <c r="F61" s="1">
-        <v>-0.14145413560742148</v>
-      </c>
-      <c r="G61" s="1">
+      <c r="F61" s="3">
+        <v>-0.15415648458506717</v>
+      </c>
+      <c r="G61" s="3">
         <v>0.38</v>
       </c>
-      <c r="H61" s="1">
-        <v>39.25</v>
-      </c>
-      <c r="I61" s="1">
-        <v>-1.16</v>
-      </c>
-      <c r="J61" s="1">
-        <v>-0.007195614413038062</v>
-      </c>
-      <c r="K61" s="1" t="b">
+      <c r="H61" s="3">
+        <v>44.46</v>
+      </c>
+      <c r="I61" s="3">
+        <v>-0.05</v>
+      </c>
+      <c r="J61" s="3">
+        <v>-0.006782224340803354</v>
+      </c>
+      <c r="K61" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L61" s="1">
+      <c r="L61" s="3">
         <v>102</v>
       </c>
-      <c r="M61" s="1">
-        <v>-0.19554674499268498</v>
-      </c>
-      <c r="N61" s="1">
-        <v>-9.755060082290516</v>
-      </c>
-      <c r="O61" s="1">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="P61" s="1">
+      <c r="M61" s="3">
+        <v>-0.2160791344216887</v>
+      </c>
+      <c r="N61" s="3">
+        <v>-10.545389274971852</v>
+      </c>
+      <c r="O61" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="P61" s="3">
         <v>12.798408482128673</v>
       </c>
-      <c r="Q61" s="1">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="R61" s="1">
-        <v>30.063291139240505</v>
-      </c>
-      <c r="S61" s="1" t="s">
+      <c r="Q61" s="3">
+        <v>38.607594936708864</v>
+      </c>
+      <c r="R61" s="3">
+        <v>29.050632911392405</v>
+      </c>
+      <c r="S61" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="T61" s="1">
-        <v>1.27</v>
+      <c r="T61" s="3">
+        <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5863,61 +5863,61 @@
         <v>61</v>
       </c>
       <c r="B62" s="1">
-        <v>17.74</v>
+        <v>17.65</v>
       </c>
       <c r="C62" s="1">
         <v>92.40506329113924</v>
       </c>
       <c r="D62" s="1">
-        <v>0.6251409244644871</v>
+        <v>0.5943342776203968</v>
       </c>
       <c r="E62" s="1">
         <v>-0.07</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.2915840197286455</v>
+        <v>-0.2865787997014262</v>
       </c>
       <c r="G62" s="1">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="H62" s="1">
-        <v>33.5</v>
+        <v>32.92</v>
       </c>
       <c r="I62" s="1">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.006555066634342177</v>
+        <v>-0.0075198154678723875</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L62" s="1">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.2959463269371345</v>
+        <v>-0.2925713142017444</v>
       </c>
       <c r="N62" s="1">
-        <v>-19.79501827673546</v>
+        <v>-18.194607252977427</v>
       </c>
       <c r="O62" s="1">
-        <v>6.329113924050633</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P62" s="1">
-        <v>19.79501827673546</v>
+        <v>20.127091395469936</v>
       </c>
       <c r="Q62" s="1">
-        <v>49.620253164556964</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="R62" s="1">
-        <v>32.78481012658228</v>
+        <v>32.405063291139236</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-10.06</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5931,55 +5931,55 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D63" s="4">
-        <v>4.982273201251304</v>
+        <v>4.987486965589155</v>
       </c>
       <c r="E63" s="4">
         <v>-8.13</v>
       </c>
       <c r="F63" s="4">
-        <v>0.9493622663007135</v>
+        <v>0.7264742148129504</v>
       </c>
       <c r="G63" s="4">
-        <v>4.73</v>
+        <v>4.82</v>
       </c>
       <c r="H63" s="4">
-        <v>69.05</v>
+        <v>63.95</v>
       </c>
       <c r="I63" s="4">
-        <v>243.21</v>
+        <v>223.89</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09058687062645834</v>
+        <v>0.08932039391139888</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="4">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M63" s="4">
-        <v>1.2747903840539925</v>
+        <v>1.1079976379998766</v>
       </c>
       <c r="N63" s="4">
-        <v>137.27865282237724</v>
+        <v>121.86228796718466</v>
       </c>
       <c r="O63" s="4">
-        <v>98.73417721518987</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>84.17721518987342</v>
+        <v>82.27848101265822</v>
       </c>
       <c r="R63" s="4">
-        <v>72.34177215189874</v>
+        <v>71.26582278481013</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5999,31 +5999,31 @@
         <v>-5.36</v>
       </c>
       <c r="F64" s="2">
-        <v>0.7852798911919795</v>
+        <v>0.7814222398790698</v>
       </c>
       <c r="G64" s="2">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="H64" s="2">
-        <v>68.25</v>
+        <v>68.48</v>
       </c>
       <c r="I64" s="2">
-        <v>131.53</v>
+        <v>130</v>
       </c>
       <c r="J64" s="2">
-        <v>0.07405834123421048</v>
+        <v>0.07327680547531976</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M64" s="2">
-        <v>0.8733984968034572</v>
+        <v>0.8842937388011991</v>
       </c>
       <c r="N64" s="2">
-        <v>97.1394640973237</v>
+        <v>99.49189804731692</v>
       </c>
       <c r="O64" s="2">
         <v>93.67088607594937</v>
@@ -6061,19 +6061,19 @@
         <v>-0.88</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.1278443421112761</v>
+        <v>-0.13736341096253218</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>47.3</v>
+        <v>48.09</v>
       </c>
       <c r="I65" s="1">
-        <v>-0.22</v>
+        <v>-0.05</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.008901388539462785</v>
+        <v>-0.009798847532780089</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
@@ -6082,28 +6082,28 @@
         <v>55</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.188916643030122</v>
+        <v>-0.20727608013291132</v>
       </c>
       <c r="N65" s="1">
-        <v>-9.092049886034218</v>
+        <v>-9.665083846094111</v>
       </c>
       <c r="O65" s="1">
-        <v>26.582278481012654</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>44.55696202531646</v>
+        <v>43.54430379746836</v>
       </c>
       <c r="R65" s="1">
-        <v>34.74683544303797</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-2.66</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6117,55 +6117,55 @@
         <v>87.34177215189874</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.13325257419745615</v>
+        <v>-0.12356147789218659</v>
       </c>
       <c r="E66" s="3">
         <v>-0.2</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.2937024335685622</v>
+        <v>-0.2197919368880013</v>
       </c>
       <c r="G66" s="3">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="H66" s="3">
-        <v>28.59</v>
+        <v>33.05</v>
       </c>
       <c r="I66" s="3">
-        <v>-45.3</v>
+        <v>-42.77</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.020762511040299483</v>
+        <v>-0.02284698017530048</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L66" s="3">
-        <v>-191</v>
+        <v>-194</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.2910850492434688</v>
+        <v>-0.220790689304721</v>
       </c>
       <c r="N66" s="3">
-        <v>-19.308890507368886</v>
+        <v>-11.016544763275084</v>
       </c>
       <c r="O66" s="3">
-        <v>7.59493670886076</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P66" s="3">
         <v>54.61236968964586</v>
       </c>
       <c r="Q66" s="3">
-        <v>32.27848101265823</v>
+        <v>33.037974683544306</v>
       </c>
       <c r="R66" s="3">
-        <v>18.481012658227847</v>
+        <v>21.645569620253163</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="3">
-        <v>-10.57</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6185,49 +6185,49 @@
         <v>-1.48</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.11446784778731421</v>
+        <v>-0.11005225112505734</v>
       </c>
       <c r="G67" s="1">
         <v>1.15</v>
       </c>
       <c r="H67" s="1">
-        <v>45.46</v>
+        <v>40.18</v>
       </c>
       <c r="I67" s="1">
-        <v>-12.56</v>
+        <v>-14.6</v>
       </c>
       <c r="J67" s="1">
-        <v>0.00019670496386489357</v>
+        <v>-0.00001886392709427514</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-75</v>
+        <v>-77</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.10138092616184724</v>
+        <v>-0.09507096487426181</v>
       </c>
       <c r="N67" s="1">
-        <v>-0.33847819920673305</v>
+        <v>1.5554276797708422</v>
       </c>
       <c r="O67" s="1">
-        <v>45.56962025316456</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>48.10126582278481</v>
+        <v>46.45569620253164</v>
       </c>
       <c r="R67" s="1">
-        <v>42.21518987341772</v>
+        <v>41.45569620253165</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-1.9</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6247,49 +6247,49 @@
         <v>-0.18</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.17758610696204752</v>
+        <v>-0.14695918703431088</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>42.32</v>
+        <v>52.76</v>
       </c>
       <c r="I68" s="1">
-        <v>1.8</v>
+        <v>4.71</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.011523876210831585</v>
+        <v>-0.010864152352817177</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.23604102355580003</v>
+        <v>-0.2138755989545309</v>
       </c>
       <c r="N68" s="1">
-        <v>-13.804487938602017</v>
+        <v>-10.325035728256072</v>
       </c>
       <c r="O68" s="1">
-        <v>17.72151898734177</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P68" s="1">
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>60.12658227848102</v>
+        <v>62.9113924050633</v>
       </c>
       <c r="R68" s="1">
-        <v>45.88607594936709</v>
+        <v>46.64556962025317</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>0.95</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6309,34 +6309,34 @@
         <v>0.19</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.2690867324852023</v>
+        <v>-0.2692979026745278</v>
       </c>
       <c r="G69" s="3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H69" s="3">
-        <v>45.27</v>
+        <v>44.5</v>
       </c>
       <c r="I69" s="3">
-        <v>-11.36</v>
+        <v>-11.67</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.011529060744810636</v>
+        <v>-0.010079876768963403</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-66</v>
+        <v>-68</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.2254636604003124</v>
+        <v>-0.22035903425526238</v>
       </c>
       <c r="N69" s="3">
-        <v>-12.74675162305326</v>
+        <v>-10.973379258329217</v>
       </c>
       <c r="O69" s="3">
-        <v>18.9873417721519</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P69" s="3">
         <v>29.145649851223904</v>
@@ -6345,13 +6345,13 @@
         <v>40.379746835443036</v>
       </c>
       <c r="R69" s="3">
-        <v>27.53164556962025</v>
+        <v>27.341772151898734</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.19</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6371,49 +6371,49 @@
         <v>1.82</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.20714031465061727</v>
+        <v>-0.22962194848149697</v>
       </c>
       <c r="G70" s="3">
         <v>0.87</v>
       </c>
       <c r="H70" s="3">
-        <v>40.27</v>
+        <v>39.8</v>
       </c>
       <c r="I70" s="3">
-        <v>-14.67</v>
+        <v>-14.88</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.012236944844050341</v>
+        <v>-0.010093204836148496</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.21848231339268864</v>
+        <v>-0.2426057298988531</v>
       </c>
       <c r="N70" s="3">
-        <v>-12.048616922290883</v>
+        <v>-13.198048822688285</v>
       </c>
       <c r="O70" s="3">
-        <v>21.518987341772153</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>38.22784810126583</v>
+        <v>38.860759493670884</v>
       </c>
       <c r="R70" s="3">
-        <v>27.911392405063292</v>
+        <v>26.075949367088608</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>0.19</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6433,19 +6433,19 @@
         <v>-1.56</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.429719529268869</v>
+        <v>-0.4145741625586808</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>49.73</v>
+        <v>51.49</v>
       </c>
       <c r="I71" s="3">
-        <v>-28.14</v>
+        <v>-27.5</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.02833579033638761</v>
+        <v>-0.025720975933946837</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
@@ -6454,10 +6454,10 @@
         <v>-100</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.41924999196849544</v>
+        <v>-0.4025891335580444</v>
       </c>
       <c r="N71" s="3">
-        <v>-32.12538477987156</v>
+        <v>-29.196389188607423</v>
       </c>
       <c r="O71" s="3">
         <v>1.2658227848101267</v>
@@ -6466,7 +6466,7 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>40.632911392405056</v>
+        <v>40.506329113924046</v>
       </c>
       <c r="R71" s="3">
         <v>22.40506329113924</v>
@@ -6479,65 +6479,65 @@
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="3">
         <v>10.42</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="3">
         <v>78.48101265822784</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="3">
         <v>0.21976967370441466</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="3">
         <v>-1.49</v>
       </c>
-      <c r="F72" s="1">
-        <v>-0.25243395751460584</v>
-      </c>
-      <c r="G72" s="1">
+      <c r="F72" s="3">
+        <v>-0.27611628322265297</v>
+      </c>
+      <c r="G72" s="3">
         <v>1.14</v>
       </c>
-      <c r="H72" s="1">
-        <v>44.33</v>
-      </c>
-      <c r="I72" s="1">
-        <v>-9</v>
-      </c>
-      <c r="J72" s="1">
-        <v>-0.008215991391423793</v>
-      </c>
-      <c r="K72" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L72" s="1">
+      <c r="H72" s="3">
+        <v>44.14</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-9.02</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-0.006577030997239965</v>
+      </c>
+      <c r="K72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3">
         <v>2</v>
       </c>
-      <c r="M72" s="1">
-        <v>-0.2402194973308367</v>
-      </c>
-      <c r="N72" s="1">
-        <v>-14.222335316105678</v>
-      </c>
-      <c r="O72" s="1">
-        <v>16.455696202531644</v>
-      </c>
-      <c r="P72" s="1">
+      <c r="M72" s="3">
+        <v>-0.26213374938857714</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-15.150850771660698</v>
+      </c>
+      <c r="O72" s="3">
+        <v>10.126582278481013</v>
+      </c>
+      <c r="P72" s="3">
         <v>19.739671794345924</v>
       </c>
-      <c r="Q72" s="1">
-        <v>42.025316455696206</v>
-      </c>
-      <c r="R72" s="1">
-        <v>30.253164556962027</v>
-      </c>
-      <c r="S72" s="1" t="s">
+      <c r="Q72" s="3">
+        <v>43.164556962025316</v>
+      </c>
+      <c r="R72" s="3">
+        <v>29.303797468354432</v>
+      </c>
+      <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T72" s="1">
-        <v>2.78</v>
+      <c r="T72" s="3">
+        <v>1.84</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6551,25 +6551,25 @@
         <v>36.708860759493675</v>
       </c>
       <c r="D73" s="2">
-        <v>22.40983606557377</v>
+        <v>20.426229508196723</v>
       </c>
       <c r="E73" s="2">
         <v>-1.26</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3042174964651143</v>
+        <v>0.4109958961986542</v>
       </c>
       <c r="G73" s="2">
         <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>62.81</v>
+        <v>68.1</v>
       </c>
       <c r="I73" s="2">
-        <v>42.47</v>
+        <v>46.26</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03087006486436829</v>
+        <v>0.031508908728787234</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
@@ -6578,10 +6578,10 @@
         <v>28</v>
       </c>
       <c r="M73" s="2">
-        <v>0.3199218024156747</v>
+        <v>0.42897343969960877</v>
       </c>
       <c r="N73" s="2">
-        <v>41.79179465854544</v>
+        <v>53.9598681371579</v>
       </c>
       <c r="O73" s="2">
         <v>87.34177215189874</v>
@@ -6590,16 +6590,16 @@
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.21518987341773</v>
+        <v>67.34177215189874</v>
       </c>
       <c r="R73" s="2">
-        <v>62.27848101265823</v>
+        <v>62.025316455696206</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6619,19 +6619,19 @@
         <v>2.01</v>
       </c>
       <c r="F74" s="2">
-        <v>0.16736885814528502</v>
+        <v>0.1555944457098428</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
       </c>
       <c r="H74" s="2">
-        <v>80.47</v>
+        <v>80.86</v>
       </c>
       <c r="I74" s="2">
-        <v>30.55</v>
+        <v>30.31</v>
       </c>
       <c r="J74" s="2">
-        <v>0.01684470025837608</v>
+        <v>0.015382182508375218</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>0</v>
@@ -6640,28 +6640,28 @@
         <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.14904716786963124</v>
+        <v>0.13462064495872905</v>
       </c>
       <c r="N74" s="2">
-        <v>24.70433120394112</v>
+        <v>24.52458866306993</v>
       </c>
       <c r="O74" s="2">
-        <v>75.9493670886076</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>65.0632911392405</v>
+        <v>64.68354430379748</v>
       </c>
       <c r="R74" s="2">
-        <v>57.53164556962027</v>
+        <v>55.50632911392406</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>1.2</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6681,19 +6681,19 @@
         <v>-2.27</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.008443833219813346</v>
+        <v>0.014969557179746504</v>
       </c>
       <c r="G75" s="1">
         <v>0.97</v>
       </c>
       <c r="H75" s="1">
-        <v>59.55</v>
+        <v>61.87</v>
       </c>
       <c r="I75" s="1">
-        <v>15.61</v>
+        <v>17.13</v>
       </c>
       <c r="J75" s="1">
-        <v>0.009937538495671276</v>
+        <v>0.014394612010311373</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6702,28 +6702,28 @@
         <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>-0.011061217544906743</v>
+        <v>0.0119732999295874</v>
       </c>
       <c r="N75" s="1">
-        <v>8.693492662487303</v>
+        <v>12.259854160155758</v>
       </c>
       <c r="O75" s="1">
-        <v>58.22784810126582</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>59.620253164556964</v>
+        <v>61.392405063291136</v>
       </c>
       <c r="R75" s="1">
-        <v>44.30379746835443</v>
+        <v>44.05063291139241</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>-2.15</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6743,19 +6743,19 @@
         <v>3.5</v>
       </c>
       <c r="F76" s="1">
-        <v>0.07236366412748221</v>
+        <v>-0.0036616319166906663</v>
       </c>
       <c r="G76" s="1">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H76" s="1">
-        <v>42.61</v>
+        <v>40.8</v>
       </c>
       <c r="I76" s="1">
-        <v>7.08</v>
+        <v>5.46</v>
       </c>
       <c r="J76" s="1">
-        <v>0.012504167396938246</v>
+        <v>0.01117333763661347</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6764,28 +6764,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>0.04706228231824605</v>
+        <v>-0.03362420441828173</v>
       </c>
       <c r="N76" s="1">
-        <v>14.505842648802586</v>
+        <v>7.700103725368848</v>
       </c>
       <c r="O76" s="1">
-        <v>65.82278481012658</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>45.44303797468355</v>
+        <v>44.43037974683544</v>
       </c>
       <c r="R76" s="1">
-        <v>44.62025316455696</v>
+        <v>40</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>2.41</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6805,19 +6805,19 @@
         <v>-0.19</v>
       </c>
       <c r="F77" s="2">
-        <v>0.043110531136912364</v>
+        <v>0.03724172057863512</v>
       </c>
       <c r="G77" s="2">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H77" s="2">
-        <v>68.46</v>
+        <v>65.19</v>
       </c>
       <c r="I77" s="2">
-        <v>14.8</v>
+        <v>13.72</v>
       </c>
       <c r="J77" s="2">
-        <v>0.011052862268375178</v>
+        <v>0.013142398547700614</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6826,28 +6826,28 @@
         <v>8</v>
       </c>
       <c r="M77" s="2">
-        <v>0.04136560825351676</v>
+        <v>0.03624296816191541</v>
       </c>
       <c r="N77" s="2">
-        <v>13.936175242329668</v>
+        <v>14.68682098338856</v>
       </c>
       <c r="O77" s="2">
-        <v>63.29113924050633</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>64.68354430379748</v>
+        <v>63.67088607594937</v>
       </c>
       <c r="R77" s="2">
-        <v>55.506329113924046</v>
+        <v>54.49367088607595</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>1.08</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6867,19 +6867,19 @@
         <v>0.93</v>
       </c>
       <c r="F78" s="1">
-        <v>0.09794401446313132</v>
+        <v>0.08157686103270348</v>
       </c>
       <c r="G78" s="1">
         <v>1.25</v>
       </c>
       <c r="H78" s="1">
-        <v>60.99</v>
+        <v>57.31</v>
       </c>
       <c r="I78" s="1">
-        <v>29.94</v>
+        <v>28.16</v>
       </c>
       <c r="J78" s="1">
-        <v>0.025484029716650775</v>
+        <v>0.02435973156182326</v>
       </c>
       <c r="K78" s="1" t="b">
         <v>0</v>
@@ -6888,28 +6888,28 @@
         <v>59</v>
       </c>
       <c r="M78" s="1">
-        <v>0.11975555050557629</v>
+        <v>0.10654567145069604</v>
       </c>
       <c r="N78" s="1">
-        <v>21.775169467535605</v>
+        <v>21.71709131226662</v>
       </c>
       <c r="O78" s="1">
-        <v>69.62025316455697</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P78" s="1">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="1">
-        <v>59.36708860759494</v>
+        <v>57.84810126582278</v>
       </c>
       <c r="R78" s="1">
-        <v>48.607594936708864</v>
+        <v>48.037974683544306</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="1">
-        <v>-1.08</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6929,31 +6929,31 @@
         <v>0.99</v>
       </c>
       <c r="F79" s="2">
-        <v>0.3987904244371889</v>
+        <v>0.4422507426652984</v>
       </c>
       <c r="G79" s="2">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="H79" s="2">
-        <v>79.49</v>
+        <v>80.85</v>
       </c>
       <c r="I79" s="2">
-        <v>52.27</v>
+        <v>54.6</v>
       </c>
       <c r="J79" s="2">
-        <v>0.04564937937053453</v>
+        <v>0.046283989519480505</v>
       </c>
       <c r="K79" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2">
         <v>80</v>
       </c>
       <c r="M79" s="2">
-        <v>0.39442811722869986</v>
+        <v>0.4382557329984196</v>
       </c>
       <c r="N79" s="2">
-        <v>49.242426139847964</v>
+        <v>54.88809746703899</v>
       </c>
       <c r="O79" s="2">
         <v>88.60759493670885</v>
@@ -6962,16 +6962,16 @@
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>66.32911392405063</v>
+        <v>66.07594936708861</v>
       </c>
       <c r="R79" s="2">
-        <v>59.36708860759494</v>
+        <v>59.24050632911393</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6985,55 +6985,55 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8348623853211008</v>
+        <v>0.8268348623853209</v>
       </c>
       <c r="E80" s="2">
         <v>4.67</v>
       </c>
       <c r="F80" s="2">
-        <v>0.9695593477121562</v>
+        <v>1.3660493645956988</v>
       </c>
       <c r="G80" s="2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H80" s="2">
-        <v>65.75</v>
+        <v>76.45</v>
       </c>
       <c r="I80" s="2">
-        <v>69.17</v>
+        <v>96.44</v>
       </c>
       <c r="J80" s="2">
-        <v>0.050940209043059737</v>
+        <v>0.05565914536366011</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L80" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>0.9695593477121562</v>
+        <v>1.3670481170124185</v>
       </c>
       <c r="N80" s="2">
-        <v>106.75554918819358</v>
+        <v>147.76733586843886</v>
       </c>
       <c r="O80" s="2">
-        <v>94.9367088607595</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P80" s="2">
         <v>14.059118714058641</v>
       </c>
       <c r="Q80" s="2">
-        <v>70.37974683544304</v>
+        <v>71.77215189873418</v>
       </c>
       <c r="R80" s="2">
-        <v>64.9367088607595</v>
+        <v>66.39240506329115</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>0.7</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>
@@ -7052,7 +7052,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7060,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>35.88607594936709</v>
+        <v>33.79746835443038</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20.822784810126585</v>
+        <v>26.898734177215193</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>43.35443037974684</v>
+        <v>43.60759493670887</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>41.51898734177216</v>
+        <v>42.151898734177216</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>55.18987341772152</v>
+        <v>52.468354430379755</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>54.11392405063291</v>
+        <v>55.31645569620253</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.55696202531645</v>
+        <v>38.54430379746835</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.15189873417721</v>
+        <v>35.9493670886076</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>52.40506329113924</v>
+        <v>53.29113924050633</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>35.063291139240505</v>
+        <v>39.74683544303798</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7.405063291139241</v>
+        <v>4.620253164556961</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>45.12658227848102</v>
+        <v>48.79746835443038</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7172,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>28.924050632911392</v>
+        <v>26.265822784810123</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18.354430379746837</v>
+        <v>18.60759493670886</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.797468354430382</v>
+        <v>30.189873417721518</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>41.89873417721519</v>
+        <v>40.31645569620253</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>40.25316455696203</v>
+        <v>40.06329113924051</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7212,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>54.177215189873415</v>
+        <v>54.43037974683544</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.379746835443036</v>
+        <v>30.31645569620253</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>32.0253164556962</v>
+        <v>34.49367088607595</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>27.151898734177212</v>
+        <v>26.9620253164557</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7244,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9.303797468354428</v>
+        <v>2.531645569620256</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7252,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33.29113924050633</v>
+        <v>34.55696202531646</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>24.303797468354432</v>
+        <v>26.9620253164557</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>20.379746835443044</v>
+        <v>21.32911392405063</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7276,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>25.31645569620253</v>
+        <v>26.075949367088604</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7284,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>46.07594936708861</v>
+        <v>45.25316455696203</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>59.177215189873415</v>
+        <v>58.0379746835443</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>19.81012658227848</v>
+        <v>20.44303797468354</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>41.835443037974684</v>
+        <v>42.025316455696206</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7316,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>49.55696202531646</v>
+        <v>48.48101265822785</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7324,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>23.037974683544306</v>
+        <v>21.582278481012654</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>31.83544303797468</v>
+        <v>33.670886075949355</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7340,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>35.63291139240506</v>
+        <v>31.962025316455698</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>55.31645569620253</v>
+        <v>56.075949367088604</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7356,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>43.29113924050633</v>
+        <v>44.050632911392405</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7372,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>30.88607594936709</v>
+        <v>33.41772151898735</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.734177215189874</v>
+        <v>38.10126582278481</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>44.430379746835435</v>
+        <v>48.10126582278481</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7396,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>26.13924050632911</v>
+        <v>26.89873417721519</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7404,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>55.56962025316456</v>
+        <v>56.01265822784811</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>26.329113924050628</v>
+        <v>25.82278481012658</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.12658227848101</v>
+        <v>25.06329113924051</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>33.291139240506325</v>
+        <v>33.9873417721519</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.36708860759494</v>
+        <v>53.924050632911396</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7444,7 +7444,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>62.97468354430381</v>
+        <v>61.77215189873419</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>59.36708860759494</v>
+        <v>58.67088607594937</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7460,7 +7460,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>21.582278481012658</v>
+        <v>22.34177215189873</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>42.72151898734178</v>
+        <v>41.70886075949368</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>56.139240506329116</v>
+        <v>56.64556962025316</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>39.493670886075954</v>
+        <v>37.84810126582278</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7492,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>49.74683544303797</v>
+        <v>56.075949367088604</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>39.683544303797476</v>
+        <v>41.20253164556962</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>36.962025316455694</v>
+        <v>37.025316455696206</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>66.39240506329114</v>
+        <v>66.0126582278481</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7524,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>55.8860759493671</v>
+        <v>54.17721518987342</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7532,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>30.063291139240505</v>
+        <v>29.050632911392405</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>32.78481012658228</v>
+        <v>32.405063291139236</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>72.34177215189874</v>
+        <v>71.26582278481013</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>34.74683544303797</v>
+        <v>33.29113924050633</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>18.481012658227847</v>
+        <v>21.645569620253163</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>42.21518987341772</v>
+        <v>41.45569620253165</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>45.88607594936709</v>
+        <v>46.64556962025317</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.53164556962025</v>
+        <v>27.341772151898734</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7604,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>27.911392405063292</v>
+        <v>26.075949367088608</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>30.253164556962027</v>
+        <v>29.303797468354432</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7628,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.27848101265823</v>
+        <v>62.025316455696206</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7636,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>57.53164556962027</v>
+        <v>55.50632911392406</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7644,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>44.30379746835443</v>
+        <v>44.05063291139241</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>44.62025316455696</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7660,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>55.506329113924046</v>
+        <v>54.49367088607595</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>48.607594936708864</v>
+        <v>48.037974683544306</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7676,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>59.36708860759494</v>
+        <v>59.24050632911393</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>64.9367088607595</v>
+        <v>66.39240506329115</v>
       </c>
     </row>
   </sheetData>
@@ -7703,10 +7703,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7714,7 +7714,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7725,10 +7725,10 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7736,10 +7736,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7747,10 +7747,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7758,82 +7758,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7852,15 +7852,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7868,98 +7868,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7978,10 +7978,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7989,7 +7989,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8000,10 +8000,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8011,90 +8011,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -8113,10 +8113,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8124,7 +8124,7 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8132,106 +8132,106 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -8247,212 +8247,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" t="s">
         <v>182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" t="s">
         <v>192</v>
-      </c>
-      <c r="B6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" t="s">
         <v>199</v>
       </c>
-      <c r="B9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" t="s">
-        <v>198</v>
-      </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -331,7 +331,7 @@
     <t>2027-03-10</t>
   </si>
   <si>
-    <t>2026-04-23</t>
+    <t>2027-04-23</t>
   </si>
   <si>
     <t>2026-05-11</t>
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-22</t>
+    <t>2026-05-25</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -685,16 +685,16 @@
     <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Earnings Upcoming, Institutional Buying</t>
@@ -1559,7 +1559,7 @@
         <v>54.49367088607595</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1570,7 +1570,7 @@
         <v>54.43037974683544</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1592,7 +1592,7 @@
         <v>53.924050632911396</v>
       </c>
       <c r="C22" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1611,7 +1611,7 @@
         <v>13</v>
       </c>
       <c r="B24">
-        <v>48.79746835443038</v>
+        <v>48.67088607594937</v>
       </c>
       <c r="C24" t="s">
         <v>220</v>
@@ -1625,7 +1625,7 @@
         <v>48.48101265822785</v>
       </c>
       <c r="C25" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1633,7 +1633,7 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>48.10126582278481</v>
+        <v>48.22784810126582</v>
       </c>
       <c r="C26" t="s">
         <v>218</v>
@@ -1647,7 +1647,7 @@
         <v>48.037974683544306</v>
       </c>
       <c r="C27" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,7 +1658,7 @@
         <v>46.64556962025317</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
         <v>45.25316455696203</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1680,7 +1680,7 @@
         <v>44.05063291139241</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,7 +1702,7 @@
         <v>42.151898734177216</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1713,7 +1713,7 @@
         <v>42.025316455696206</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
         <v>40.31645569620253</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1746,7 +1746,7 @@
         <v>40.06329113924051</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1757,7 +1757,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
         <v>38.10126582278481</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,7 +1779,7 @@
         <v>37.025316455696206</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
         <v>25</v>
       </c>
       <c r="B40">
-        <v>34.55696202531646</v>
+        <v>34.68354430379747</v>
       </c>
       <c r="C40" t="s">
         <v>227</v>
@@ -1798,10 +1798,10 @@
         <v>22</v>
       </c>
       <c r="B41">
-        <v>34.49367088607595</v>
+        <v>34.36708860759494</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1812,7 +1812,7 @@
         <v>33.79746835443038</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1823,7 +1823,7 @@
         <v>33.41772151898735</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>33.29113924050633</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1842,10 +1842,10 @@
         <v>61</v>
       </c>
       <c r="B45">
-        <v>32.405063291139236</v>
+        <v>32.088607594936704</v>
       </c>
       <c r="C45" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1853,10 +1853,10 @@
         <v>39</v>
       </c>
       <c r="B46">
-        <v>30.949367088607595</v>
+        <v>31.20253164556962</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1867,7 +1867,7 @@
         <v>30.31645569620253</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1875,10 +1875,10 @@
         <v>17</v>
       </c>
       <c r="B48">
-        <v>30.189873417721518</v>
+        <v>29.936708860759495</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1889,7 +1889,7 @@
         <v>29.303797468354432</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1900,18 +1900,18 @@
         <v>29.050632911392405</v>
       </c>
       <c r="C50" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B51">
         <v>26.9620253164557</v>
       </c>
       <c r="C51" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2152,7 +2152,7 @@
         <v>-1.5446880269814502</v>
       </c>
       <c r="E2" s="1">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="F2" s="1">
         <v>-0.001133992070301515</v>
@@ -2214,7 +2214,7 @@
         <v>23.93770491803279</v>
       </c>
       <c r="E3" s="2">
-        <v>1.88</v>
+        <v>-0.5</v>
       </c>
       <c r="F3" s="2">
         <v>1.1245287235286383</v>
@@ -2276,7 +2276,7 @@
         <v>9.868354430379748</v>
       </c>
       <c r="E4" s="3">
-        <v>1.25</v>
+        <v>-1.02</v>
       </c>
       <c r="F4" s="3">
         <v>-0.02897198602682774</v>
@@ -2338,7 +2338,7 @@
         <v>24.65137614678899</v>
       </c>
       <c r="E5" s="1">
-        <v>0.73</v>
+        <v>0.34</v>
       </c>
       <c r="F5" s="1">
         <v>-0.12404879430885826</v>
@@ -2371,19 +2371,19 @@
         <v>48.10126582278481</v>
       </c>
       <c r="P5" s="1">
-        <v>29.30842702737695</v>
+        <v>27.76573618206019</v>
       </c>
       <c r="Q5" s="1">
         <v>58.607594936708864</v>
       </c>
       <c r="R5" s="1">
-        <v>43.60759493670887</v>
+        <v>44.11392405063292</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.71</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2400,7 +2400,7 @@
         <v>1.5210355987055018</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.11</v>
+        <v>0.97</v>
       </c>
       <c r="F6" s="1">
         <v>0.0019236793285661025</v>
@@ -2459,10 +2459,10 @@
         <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>5.070444104134762</v>
+        <v>5.0520673813169985</v>
       </c>
       <c r="E7" s="2">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="2">
         <v>-0.11032541787647918</v>
@@ -2524,7 +2524,7 @@
         <v>0.004531722054380702</v>
       </c>
       <c r="E8" s="2">
-        <v>0.19</v>
+        <v>1.61</v>
       </c>
       <c r="F8" s="2">
         <v>0.30022542690549336</v>
@@ -2586,7 +2586,7 @@
         <v>46.831460674157306</v>
       </c>
       <c r="E9" s="1">
-        <v>2.36</v>
+        <v>0.88</v>
       </c>
       <c r="F9" s="1">
         <v>-0.1124771160622832</v>
@@ -2619,19 +2619,19 @@
         <v>45.56962025316456</v>
       </c>
       <c r="P9" s="1">
-        <v>34.04748479877408</v>
+        <v>32.13926500847113</v>
       </c>
       <c r="Q9" s="1">
         <v>44.55696202531645</v>
       </c>
       <c r="R9" s="1">
-        <v>38.54430379746835</v>
+        <v>38.92405063291139</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-2.66</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2648,7 +2648,7 @@
         <v>0.5663999999999999</v>
       </c>
       <c r="E10" s="1">
-        <v>1.48</v>
+        <v>-0.77</v>
       </c>
       <c r="F10" s="1">
         <v>-0.16507857895453248</v>
@@ -2684,16 +2684,16 @@
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>45.56962025316456</v>
+        <v>45.949367088607595</v>
       </c>
       <c r="R10" s="1">
-        <v>35.9493670886076</v>
+        <v>36.265822784810126</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-2.85</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2710,7 +2710,7 @@
         <v>31.911764705882348</v>
       </c>
       <c r="E11" s="2">
-        <v>5.47</v>
+        <v>-0.88</v>
       </c>
       <c r="F11" s="2">
         <v>0.4188838046724108</v>
@@ -2772,7 +2772,7 @@
         <v>65.70588235294117</v>
       </c>
       <c r="E12" s="1">
-        <v>5.82</v>
+        <v>3.81</v>
       </c>
       <c r="F12" s="1">
         <v>0.016715544305819674</v>
@@ -2834,7 +2834,7 @@
         <v>-1653.5</v>
       </c>
       <c r="E13" s="3">
-        <v>1.61</v>
+        <v>6.41</v>
       </c>
       <c r="F13" s="3">
         <v>-0.34627943391667687</v>
@@ -2896,7 +2896,7 @@
         <v>7.572519083969465</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.14</v>
+        <v>4.73</v>
       </c>
       <c r="F14" s="1">
         <v>0.25433058752469034</v>
@@ -2935,13 +2935,13 @@
         <v>58.10126582278481</v>
       </c>
       <c r="R14" s="1">
-        <v>48.79746835443038</v>
+        <v>48.67088607594937</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>13.61</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2958,7 +2958,7 @@
         <v>63.57142857142858</v>
       </c>
       <c r="E15" s="2">
-        <v>5.49</v>
+        <v>2.23</v>
       </c>
       <c r="F15" s="2">
         <v>1.5142607110028368</v>
@@ -3017,10 +3017,10 @@
         <v>8.860759493670885</v>
       </c>
       <c r="D16" s="3">
-        <v>12.218130311614733</v>
+        <v>12.651558073654392</v>
       </c>
       <c r="E16" s="3">
-        <v>8.13</v>
+        <v>5.41</v>
       </c>
       <c r="F16" s="3">
         <v>-0.2440648629943353</v>
@@ -3079,10 +3079,10 @@
         <v>3.79746835443038</v>
       </c>
       <c r="D17" s="3">
-        <v>4.355877616747182</v>
+        <v>4.685990338164252</v>
       </c>
       <c r="E17" s="3">
-        <v>4.24</v>
+        <v>1.52</v>
       </c>
       <c r="F17" s="3">
         <v>-0.24959727122568215</v>
@@ -3121,75 +3121,75 @@
         <v>26.962025316455694</v>
       </c>
       <c r="R17" s="3">
-        <v>18.60759493670886</v>
+        <v>18.481012658227847</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.56</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="1">
-        <v>8.39</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="3">
+        <v>6.73</v>
+      </c>
+      <c r="F18" s="3">
         <v>-0.3099909673030672</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="3">
         <v>1.21</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="3">
         <v>36.66</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="3">
         <v>-11.7</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="3">
         <v>-0.00825553229642634</v>
       </c>
-      <c r="K18" s="1" t="b">
+      <c r="K18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="3">
         <v>37</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M18" s="3">
         <v>-0.2890171665519534</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="3">
         <v>-17.83919248799832</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18" s="3">
         <v>8.860759493670885</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="3">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="3">
         <v>46.962025316455694</v>
       </c>
-      <c r="R18" s="1">
-        <v>30.189873417721518</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="R18" s="3">
+        <v>29.936708860759495</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="1">
-        <v>-0.76</v>
+      <c r="T18" s="3">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3206,7 +3206,7 @@
         <v>0.24463519313304713</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.16</v>
+        <v>-1.48</v>
       </c>
       <c r="F19" s="1">
         <v>-0.04286677610091033</v>
@@ -3268,7 +3268,7 @@
         <v>0.6820428336079079</v>
       </c>
       <c r="E20" s="1">
-        <v>-3.42</v>
+        <v>6.54</v>
       </c>
       <c r="F20" s="1">
         <v>-0.04396168819698541</v>
@@ -3330,7 +3330,7 @@
         <v>14.009803921568627</v>
       </c>
       <c r="E21" s="2">
-        <v>4.96</v>
+        <v>2.47</v>
       </c>
       <c r="F21" s="2">
         <v>0.1992697218600915</v>
@@ -3392,7 +3392,7 @@
         <v>0.6954377311960543</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.12</v>
+        <v>-0.84</v>
       </c>
       <c r="F22" s="1">
         <v>-0.2542193800312568</v>
@@ -3454,7 +3454,7 @@
         <v>-0.772446383133406</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.36</v>
+        <v>0.96</v>
       </c>
       <c r="F23" s="1">
         <v>-0.1759503961923806</v>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M23" s="1">
         <v>-0.15297909060782744</v>
@@ -3493,13 +3493,13 @@
         <v>45.063291139240505</v>
       </c>
       <c r="R23" s="1">
-        <v>34.49367088607595</v>
+        <v>34.36708860759494</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3516,7 +3516,7 @@
         <v>-0.009462151394422375</v>
       </c>
       <c r="E24" s="3">
-        <v>13.86</v>
+        <v>9.47</v>
       </c>
       <c r="F24" s="3">
         <v>-0.07284893500744283</v>
@@ -3555,13 +3555,13 @@
         <v>23.29113924050633</v>
       </c>
       <c r="R24" s="3">
-        <v>26.9620253164557</v>
+        <v>26.835443037974688</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-4.05</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3578,7 +3578,7 @@
         <v>-7.127192982456141</v>
       </c>
       <c r="E25" s="3">
-        <v>14.49</v>
+        <v>11.95</v>
       </c>
       <c r="F25" s="3">
         <v>-0.3277111894172485</v>
@@ -3640,7 +3640,7 @@
         <v>-2569.235294117647</v>
       </c>
       <c r="E26" s="1">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="F26" s="1">
         <v>0.7492105379751037</v>
@@ -3673,19 +3673,19 @@
         <v>94.9367088607595</v>
       </c>
       <c r="P26" s="1">
-        <v>48.258415122799256</v>
+        <v>47.81158046237125</v>
       </c>
       <c r="Q26" s="1">
         <v>42.911392405063296</v>
       </c>
       <c r="R26" s="1">
-        <v>34.55696202531646</v>
+        <v>34.68354430379747</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3702,7 +3702,7 @@
         <v>1.0176991150442478</v>
       </c>
       <c r="E27" s="3">
-        <v>5.04</v>
+        <v>8.19</v>
       </c>
       <c r="F27" s="3">
         <v>-0.1277690325559252</v>
@@ -3764,7 +3764,7 @@
         <v>7.899999999999999</v>
       </c>
       <c r="E28" s="3">
-        <v>-1.13</v>
+        <v>-4.03</v>
       </c>
       <c r="F28" s="3">
         <v>-0.4085676363935638</v>
@@ -3826,7 +3826,7 @@
         <v>77.20454545454545</v>
       </c>
       <c r="E29" s="3">
-        <v>0.88</v>
+        <v>1.51</v>
       </c>
       <c r="F29" s="3">
         <v>-0.36518581562558294</v>
@@ -3865,13 +3865,13 @@
         <v>41.139240506329116</v>
       </c>
       <c r="R29" s="3">
-        <v>26.075949367088604</v>
+        <v>25.949367088607595</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3888,7 +3888,7 @@
         <v>1500.169230769231</v>
       </c>
       <c r="E30" s="1">
-        <v>2.51</v>
+        <v>1.79</v>
       </c>
       <c r="F30" s="1">
         <v>-0.18015765004783127</v>
@@ -3950,7 +3950,7 @@
         <v>10.83625730994152</v>
       </c>
       <c r="E31" s="2">
-        <v>0.99</v>
+        <v>0.38</v>
       </c>
       <c r="F31" s="2">
         <v>0.10110524376514901</v>
@@ -4012,7 +4012,7 @@
         <v>8.178082191780822</v>
       </c>
       <c r="E32" s="3">
-        <v>1.51</v>
+        <v>-2.98</v>
       </c>
       <c r="F32" s="3">
         <v>-0.22101436430786242</v>
@@ -4045,7 +4045,7 @@
         <v>30.37974683544304</v>
       </c>
       <c r="P32" s="3">
-        <v>39.09348709793037</v>
+        <v>38.277512660369005</v>
       </c>
       <c r="Q32" s="3">
         <v>30.63291139240506</v>
@@ -4071,10 +4071,10 @@
         <v>88.60759493670885</v>
       </c>
       <c r="D33" s="1">
-        <v>-0.0601548540798094</v>
+        <v>-0.05955926146515784</v>
       </c>
       <c r="E33" s="1">
-        <v>0.66</v>
+        <v>-0.44</v>
       </c>
       <c r="F33" s="1">
         <v>-0.03092047167602477</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M33" s="1">
         <v>-0.021931699925547443</v>
@@ -4107,7 +4107,7 @@
         <v>51.89873417721519</v>
       </c>
       <c r="P33" s="1">
-        <v>26.894390179645494</v>
+        <v>26.847922891788212</v>
       </c>
       <c r="Q33" s="1">
         <v>50.25316455696202</v>
@@ -4136,7 +4136,7 @@
         <v>-0.7170099160945842</v>
       </c>
       <c r="E34" s="1">
-        <v>0.94</v>
+        <v>0.77</v>
       </c>
       <c r="F34" s="1">
         <v>0.09288490979336392</v>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M34" s="1">
         <v>0.11885247262807619</v>
@@ -4198,7 +4198,7 @@
         <v>-0.4801381692573403</v>
       </c>
       <c r="E35" s="3">
-        <v>4.55</v>
+        <v>9.42</v>
       </c>
       <c r="F35" s="3">
         <v>-0.32003676981025153</v>
@@ -4231,19 +4231,19 @@
         <v>3.79746835443038</v>
       </c>
       <c r="P35" s="3">
-        <v>29.069873353982</v>
+        <v>28.966535793040393</v>
       </c>
       <c r="Q35" s="3">
         <v>34.177215189873415</v>
       </c>
       <c r="R35" s="3">
-        <v>21.582278481012654</v>
+        <v>21.455696202531644</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4260,7 +4260,7 @@
         <v>0.40225890529973946</v>
       </c>
       <c r="E36" s="1">
-        <v>-1.05</v>
+        <v>3.24</v>
       </c>
       <c r="F36" s="1">
         <v>-0.12169121164446169</v>
@@ -4299,13 +4299,13 @@
         <v>43.164556962025316</v>
       </c>
       <c r="R36" s="1">
-        <v>33.670886075949355</v>
+        <v>33.544303797468345</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.63</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4322,7 +4322,7 @@
         <v>0.6022514071294557</v>
       </c>
       <c r="E37" s="1">
-        <v>1.72</v>
+        <v>-5.1</v>
       </c>
       <c r="F37" s="1">
         <v>-0.14349280848462048</v>
@@ -4355,7 +4355,7 @@
         <v>40.50632911392405</v>
       </c>
       <c r="P37" s="1">
-        <v>34.910057902834</v>
+        <v>34.834081981703704</v>
       </c>
       <c r="Q37" s="1">
         <v>37.46835443037975</v>
@@ -4381,10 +4381,10 @@
         <v>16.455696202531644</v>
       </c>
       <c r="D38" s="2">
-        <v>36.648648648648646</v>
+        <v>36.54054054054054</v>
       </c>
       <c r="E38" s="2">
-        <v>-0.05</v>
+        <v>-0.57</v>
       </c>
       <c r="F38" s="2">
         <v>0.769206763363862</v>
@@ -4446,7 +4446,7 @@
         <v>58.28</v>
       </c>
       <c r="E39" s="1">
-        <v>-6.6</v>
+        <v>6.03</v>
       </c>
       <c r="F39" s="1">
         <v>-0.0811210225426576</v>
@@ -4508,7 +4508,7 @@
         <v>10.126365054602184</v>
       </c>
       <c r="E40" s="1">
-        <v>10.16</v>
+        <v>2.22</v>
       </c>
       <c r="F40" s="1">
         <v>0.13779721740368814</v>
@@ -4541,19 +4541,19 @@
         <v>60.75949367088608</v>
       </c>
       <c r="P40" s="1">
-        <v>41.90387479248795</v>
+        <v>39.97107065255327</v>
       </c>
       <c r="Q40" s="1">
         <v>31.139240506329113</v>
       </c>
       <c r="R40" s="1">
-        <v>30.949367088607595</v>
+        <v>31.20253164556962</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-9.81</v>
+        <v>-9.56</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>7.121272365805169</v>
       </c>
       <c r="E41" s="1">
-        <v>-1.71</v>
+        <v>-1.06</v>
       </c>
       <c r="F41" s="1">
         <v>0.050500989837036075</v>
@@ -4632,7 +4632,7 @@
         <v>1.0637119113573408</v>
       </c>
       <c r="E42" s="1">
-        <v>0.29</v>
+        <v>2.81</v>
       </c>
       <c r="F42" s="1">
         <v>-0.0699030450840376</v>
@@ -4694,7 +4694,7 @@
         <v>1214</v>
       </c>
       <c r="E43" s="1">
-        <v>6.54</v>
+        <v>10.72</v>
       </c>
       <c r="F43" s="1">
         <v>0.12052422642201771</v>
@@ -4727,19 +4727,19 @@
         <v>73.41772151898735</v>
       </c>
       <c r="P43" s="1">
-        <v>34.72409420196845</v>
+        <v>33.52521846409704</v>
       </c>
       <c r="Q43" s="1">
         <v>51.39240506329114</v>
       </c>
       <c r="R43" s="1">
-        <v>48.10126582278481</v>
+        <v>48.22784810126582</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>5.95</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4756,7 +4756,7 @@
         <v>26.666666666666664</v>
       </c>
       <c r="E44" s="3">
-        <v>-1.94</v>
+        <v>-0.99</v>
       </c>
       <c r="F44" s="3">
         <v>-0.39318426248220456</v>
@@ -4815,10 +4815,10 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.7335722819593788</v>
+        <v>0.7419354838709679</v>
       </c>
       <c r="E45" s="2">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="F45" s="2">
         <v>0.14084531898662195</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M45" s="2">
         <v>0.18678793015572825</v>
@@ -4880,7 +4880,7 @@
         <v>543.5000000000001</v>
       </c>
       <c r="E46" s="3">
-        <v>-0.24</v>
+        <v>5.16</v>
       </c>
       <c r="F46" s="3">
         <v>-0.3013338283281196</v>
@@ -4919,13 +4919,13 @@
         <v>44.55696202531645</v>
       </c>
       <c r="R46" s="3">
-        <v>25.82278481012658</v>
+        <v>25.696202531645568</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-5.57</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4942,7 +4942,7 @@
         <v>0.8549905838041432</v>
       </c>
       <c r="E47" s="3">
-        <v>-3.9</v>
+        <v>1.38</v>
       </c>
       <c r="F47" s="3">
         <v>-0.4150914673166066</v>
@@ -5004,7 +5004,7 @@
         <v>0.7683397683397685</v>
       </c>
       <c r="E48" s="1">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F48" s="1">
         <v>-0.1961864966707575</v>
@@ -5066,7 +5066,7 @@
         <v>0.09701492537313429</v>
       </c>
       <c r="E49" s="2">
-        <v>-1.46</v>
+        <v>-0.36</v>
       </c>
       <c r="F49" s="2">
         <v>-0.008396537236975032</v>
@@ -5128,7 +5128,7 @@
         <v>1715.8333333333335</v>
       </c>
       <c r="E50" s="2">
-        <v>3.55</v>
+        <v>5.72</v>
       </c>
       <c r="F50" s="2">
         <v>0.49598507803288117</v>
@@ -5190,7 +5190,7 @@
         <v>7.922110552763819</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.69</v>
+        <v>4.31</v>
       </c>
       <c r="F51" s="2">
         <v>0.11579355688641743</v>
@@ -5252,7 +5252,7 @@
         <v>300.1538461538462</v>
       </c>
       <c r="E52" s="3">
-        <v>2.59</v>
+        <v>6.03</v>
       </c>
       <c r="F52" s="3">
         <v>-0.364557901977156</v>
@@ -5285,7 +5285,7 @@
         <v>5.063291139240507</v>
       </c>
       <c r="P52" s="3">
-        <v>46.37680917379436</v>
+        <v>45.32019556900826</v>
       </c>
       <c r="Q52" s="3">
         <v>41.265822784810126</v>
@@ -5314,7 +5314,7 @@
         <v>13.440721649484537</v>
       </c>
       <c r="E53" s="1">
-        <v>16.72</v>
+        <v>37.01</v>
       </c>
       <c r="F53" s="1">
         <v>0.1010039593108322</v>
@@ -5376,7 +5376,7 @@
         <v>6.560377358490567</v>
       </c>
       <c r="E54" s="2">
-        <v>0.25</v>
+        <v>-0.82</v>
       </c>
       <c r="F54" s="2">
         <v>0.06585021912277064</v>
@@ -5438,7 +5438,7 @@
         <v>10.605633802816902</v>
       </c>
       <c r="E55" s="1">
-        <v>6.64</v>
+        <v>6.07</v>
       </c>
       <c r="F55" s="1">
         <v>-0.07234659513805125</v>
@@ -5471,7 +5471,7 @@
         <v>65.82278481012658</v>
       </c>
       <c r="P55" s="1">
-        <v>47.85651899372094</v>
+        <v>47.39629233644822</v>
       </c>
       <c r="Q55" s="1">
         <v>45.56962025316456</v>
@@ -5500,7 +5500,7 @@
         <v>41.24074074074074</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.43</v>
+        <v>-1.41</v>
       </c>
       <c r="F56" s="2">
         <v>0.11953827030950842</v>
@@ -5559,10 +5559,10 @@
         <v>56.9620253164557</v>
       </c>
       <c r="D57" s="1">
-        <v>2.2580645161290325</v>
+        <v>2.307692307692308</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.26</v>
+        <v>-1.23</v>
       </c>
       <c r="F57" s="1">
         <v>-0.11730494517228027</v>
@@ -5624,7 +5624,7 @@
         <v>0.1757225433526011</v>
       </c>
       <c r="E58" s="1">
-        <v>0.81</v>
+        <v>1.28</v>
       </c>
       <c r="F58" s="1">
         <v>-0.08349595598191203</v>
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M58" s="1">
         <v>-0.15740363481916997</v>
@@ -5686,7 +5686,7 @@
         <v>2.3866855524079322</v>
       </c>
       <c r="E59" s="2">
-        <v>0.11</v>
+        <v>-1.3</v>
       </c>
       <c r="F59" s="2">
         <v>0.5744733690140957</v>
@@ -5748,7 +5748,7 @@
         <v>-1.4889277389277389</v>
       </c>
       <c r="E60" s="2">
-        <v>-2.31</v>
+        <v>-0.04</v>
       </c>
       <c r="F60" s="2">
         <v>0.1153393370630337</v>
@@ -5810,7 +5810,7 @@
         <v>-0.13029827315541603</v>
       </c>
       <c r="E61" s="3">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="F61" s="3">
         <v>-0.15415648458506717</v>
@@ -5869,10 +5869,10 @@
         <v>92.40506329113924</v>
       </c>
       <c r="D62" s="1">
-        <v>0.5943342776203968</v>
+        <v>0.552974504249292</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.07</v>
+        <v>-0.19</v>
       </c>
       <c r="F62" s="1">
         <v>-0.2865787997014262</v>
@@ -5908,16 +5908,16 @@
         <v>20.127091395469936</v>
       </c>
       <c r="Q62" s="1">
-        <v>48.10126582278481</v>
+        <v>47.721518987341774</v>
       </c>
       <c r="R62" s="1">
-        <v>32.405063291139236</v>
+        <v>32.088607594936704</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-10.44</v>
+        <v>-10.76</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5934,7 +5934,7 @@
         <v>4.987486965589155</v>
       </c>
       <c r="E63" s="4">
-        <v>-8.13</v>
+        <v>-3.33</v>
       </c>
       <c r="F63" s="4">
         <v>0.7264742148129504</v>
@@ -5996,7 +5996,7 @@
         <v>6.3927893738140416</v>
       </c>
       <c r="E64" s="2">
-        <v>-5.36</v>
+        <v>-1.41</v>
       </c>
       <c r="F64" s="2">
         <v>0.7814222398790698</v>
@@ -6055,10 +6055,10 @@
         <v>89.87341772151899</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.2928275044457618</v>
+        <v>-0.28986366330764674</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.88</v>
+        <v>0.14</v>
       </c>
       <c r="F65" s="1">
         <v>-0.13736341096253218</v>
@@ -6120,7 +6120,7 @@
         <v>-0.12356147789218659</v>
       </c>
       <c r="E66" s="3">
-        <v>-0.2</v>
+        <v>1.66</v>
       </c>
       <c r="F66" s="3">
         <v>-0.2197919368880013</v>
@@ -6182,7 +6182,7 @@
         <v>7.241895261845387</v>
       </c>
       <c r="E67" s="1">
-        <v>-1.48</v>
+        <v>-0.68</v>
       </c>
       <c r="F67" s="1">
         <v>-0.11005225112505734</v>
@@ -6244,7 +6244,7 @@
         <v>485.7265306122449</v>
       </c>
       <c r="E68" s="1">
-        <v>-0.18</v>
+        <v>-0.41</v>
       </c>
       <c r="F68" s="1">
         <v>-0.14695918703431088</v>
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M68" s="1">
         <v>-0.2138755989545309</v>
@@ -6306,7 +6306,7 @@
         <v>0.6286407766990291</v>
       </c>
       <c r="E69" s="3">
-        <v>0.19</v>
+        <v>-0.24</v>
       </c>
       <c r="F69" s="3">
         <v>-0.2692979026745278</v>
@@ -6345,13 +6345,13 @@
         <v>40.379746835443036</v>
       </c>
       <c r="R69" s="3">
-        <v>27.341772151898734</v>
+        <v>27.21518987341772</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.38</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6368,7 +6368,7 @@
         <v>-0.47608576140736675</v>
       </c>
       <c r="E70" s="3">
-        <v>1.82</v>
+        <v>-1.55</v>
       </c>
       <c r="F70" s="3">
         <v>-0.22962194848149697</v>
@@ -6430,7 +6430,7 @@
         <v>13.532894736842104</v>
       </c>
       <c r="E71" s="3">
-        <v>-1.56</v>
+        <v>-0.71</v>
       </c>
       <c r="F71" s="3">
         <v>-0.4145741625586808</v>
@@ -6492,7 +6492,7 @@
         <v>0.21976967370441466</v>
       </c>
       <c r="E72" s="3">
-        <v>-1.49</v>
+        <v>-0.66</v>
       </c>
       <c r="F72" s="3">
         <v>-0.27611628322265297</v>
@@ -6554,7 +6554,7 @@
         <v>20.426229508196723</v>
       </c>
       <c r="E73" s="2">
-        <v>-1.26</v>
+        <v>3.07</v>
       </c>
       <c r="F73" s="2">
         <v>0.4109958961986542</v>
@@ -6616,7 +6616,7 @@
         <v>14.25</v>
       </c>
       <c r="E74" s="2">
-        <v>2.01</v>
+        <v>1.29</v>
       </c>
       <c r="F74" s="2">
         <v>0.1555944457098428</v>
@@ -6634,7 +6634,7 @@
         <v>0.015382182508375218</v>
       </c>
       <c r="K74" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2">
         <v>13</v>
@@ -6678,7 +6678,7 @@
         <v>29.204545454545453</v>
       </c>
       <c r="E75" s="1">
-        <v>-2.27</v>
+        <v>-0.35</v>
       </c>
       <c r="F75" s="1">
         <v>0.014969557179746504</v>
@@ -6740,7 +6740,7 @@
         <v>0.7170731707317075</v>
       </c>
       <c r="E76" s="1">
-        <v>3.5</v>
+        <v>0.91</v>
       </c>
       <c r="F76" s="1">
         <v>-0.0036616319166906663</v>
@@ -6802,7 +6802,7 @@
         <v>281.33333333333337</v>
       </c>
       <c r="E77" s="2">
-        <v>-0.19</v>
+        <v>2.54</v>
       </c>
       <c r="F77" s="2">
         <v>0.03724172057863512</v>
@@ -6864,7 +6864,7 @@
         <v>-0.7139588100686499</v>
       </c>
       <c r="E78" s="1">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="F78" s="1">
         <v>0.08157686103270348</v>
@@ -6885,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M78" s="1">
         <v>0.10654567145069604</v>
@@ -6926,7 +6926,7 @@
         <v>2.775244299674267</v>
       </c>
       <c r="E79" s="2">
-        <v>0.99</v>
+        <v>0.81</v>
       </c>
       <c r="F79" s="2">
         <v>0.4422507426652984</v>
@@ -6988,7 +6988,7 @@
         <v>0.8268348623853209</v>
       </c>
       <c r="E80" s="2">
-        <v>4.67</v>
+        <v>-1.21</v>
       </c>
       <c r="F80" s="2">
         <v>1.3660493645956988</v>
@@ -7084,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>43.60759493670887</v>
+        <v>44.11392405063292</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.54430379746835</v>
+        <v>38.92405063291139</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35.9493670886076</v>
+        <v>36.265822784810126</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>48.79746835443038</v>
+        <v>48.67088607594937</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18.60759493670886</v>
+        <v>18.481012658227847</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>30.189873417721518</v>
+        <v>29.936708860759495</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34.49367088607595</v>
+        <v>34.36708860759494</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>26.9620253164557</v>
+        <v>26.835443037974688</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7252,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>34.55696202531646</v>
+        <v>34.68354430379747</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7276,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>26.075949367088604</v>
+        <v>25.949367088607595</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7324,7 +7324,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>21.582278481012654</v>
+        <v>21.455696202531644</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>33.670886075949355</v>
+        <v>33.544303797468345</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7364,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>30.949367088607595</v>
+        <v>31.20253164556962</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>48.10126582278481</v>
+        <v>48.22784810126582</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.82278481012658</v>
+        <v>25.696202531645568</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>32.405063291139236</v>
+        <v>32.088607594936704</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.341772151898734</v>
+        <v>27.21518987341772</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -409,7 +409,7 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-25</t>
+    <t>2026-05-26</t>
   </si>
   <si>
     <t>Criteria</t>
@@ -670,7 +670,7 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Earnings Upcoming, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Earnings Upcoming, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
@@ -679,21 +679,21 @@
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader</t>
+  </si>
+  <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Institutional Buying</t>
   </si>
   <si>
@@ -703,7 +703,7 @@
     <t>Volume Spike</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader</t>
+    <t>Earnings Upcoming</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1369,7 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>71.26582278481013</v>
+        <v>71.51898734177216</v>
       </c>
       <c r="C2" t="s">
         <v>214</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B3">
-        <v>67.02531645569621</v>
+        <v>67.53164556962025</v>
       </c>
       <c r="C3" t="s">
         <v>215</v>
@@ -1388,24 +1388,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="B4">
-        <v>66.39240506329115</v>
+        <v>67.15189873417722</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="B5">
-        <v>66.0126582278481</v>
+        <v>66.7721518987342</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1413,7 +1413,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>65.37974683544304</v>
+        <v>64.87341772151899</v>
       </c>
       <c r="C6" t="s">
         <v>215</v>
@@ -1421,24 +1421,24 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B7">
-        <v>62.27848101265822</v>
+        <v>62.53164556962025</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>62.025316455696206</v>
+        <v>62.27848101265822</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1446,7 +1446,7 @@
         <v>49</v>
       </c>
       <c r="B9">
-        <v>61.77215189873419</v>
+        <v>61.26582278481011</v>
       </c>
       <c r="C9" t="s">
         <v>215</v>
@@ -1454,21 +1454,21 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>59.24050632911393</v>
+        <v>59.55696202531646</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>58.67088607594937</v>
+        <v>58.797468354430386</v>
       </c>
       <c r="C11" t="s">
         <v>218</v>
@@ -1476,43 +1476,43 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B12">
-        <v>58.0379746835443</v>
+        <v>58.734177215189874</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13">
-        <v>56.64556962025316</v>
+        <v>56.96202531645569</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B14">
-        <v>56.075949367088604</v>
+        <v>56.265822784810126</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="B15">
-        <v>56.075949367088604</v>
+        <v>55.88607594936709</v>
       </c>
       <c r="C15" t="s">
         <v>220</v>
@@ -1520,24 +1520,24 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>56.01265822784811</v>
+        <v>55.696202531645575</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B17">
-        <v>55.50632911392406</v>
+        <v>55.379746835443036</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1545,51 +1545,51 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>55.31645569620253</v>
+        <v>54.936708860759495</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="B19">
-        <v>54.49367088607595</v>
+        <v>54.49367088607596</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>54.43037974683544</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>54.17721518987342</v>
+        <v>54.050632911392405</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B22">
-        <v>53.924050632911396</v>
+        <v>53.29113924050634</v>
       </c>
       <c r="C22" t="s">
         <v>224</v>
@@ -1600,7 +1600,7 @@
         <v>10</v>
       </c>
       <c r="B23">
-        <v>53.29113924050633</v>
+        <v>53.16455696202532</v>
       </c>
       <c r="C23" t="s">
         <v>225</v>
@@ -1608,43 +1608,43 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>48.67088607594937</v>
+        <v>49.24050632911393</v>
       </c>
       <c r="C24" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B25">
-        <v>48.48101265822785</v>
+        <v>48.67088607594937</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="B26">
-        <v>48.22784810126582</v>
+        <v>48.41772151898734</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="B27">
-        <v>48.037974683544306</v>
+        <v>46.77215189873418</v>
       </c>
       <c r="C27" t="s">
         <v>224</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>46.64556962025317</v>
+        <v>46.58227848101265</v>
       </c>
       <c r="C28" t="s">
         <v>224</v>
@@ -1666,7 +1666,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>45.25316455696203</v>
+        <v>46.0126582278481</v>
       </c>
       <c r="C29" t="s">
         <v>224</v>
@@ -1677,7 +1677,7 @@
         <v>122</v>
       </c>
       <c r="B30">
-        <v>44.05063291139241</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="C30" t="s">
         <v>224</v>
@@ -1685,21 +1685,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B31">
-        <v>44.050632911392405</v>
+        <v>42.468354430379755</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B32">
-        <v>42.151898734177216</v>
+        <v>41.962025316455694</v>
       </c>
       <c r="C32" t="s">
         <v>224</v>
@@ -1707,32 +1707,32 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B33">
-        <v>42.025316455696206</v>
+        <v>41.835443037974684</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B34">
-        <v>41.70886075949368</v>
+        <v>41.58227848101266</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B35">
-        <v>40.31645569620253</v>
+        <v>41.26582278481012</v>
       </c>
       <c r="C35" t="s">
         <v>224</v>
@@ -1740,13 +1740,13 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B36">
-        <v>40.06329113924051</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1754,7 +1754,7 @@
         <v>123</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>40.253164556962034</v>
       </c>
       <c r="C37" t="s">
         <v>224</v>
@@ -1762,21 +1762,21 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B38">
-        <v>38.10126582278481</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>37.025316455696206</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="C39" t="s">
         <v>224</v>
@@ -1784,13 +1784,13 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B40">
-        <v>34.68354430379747</v>
+        <v>36.392405063291136</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>22</v>
       </c>
       <c r="B41">
-        <v>34.36708860759494</v>
+        <v>34.24050632911393</v>
       </c>
       <c r="C41" t="s">
         <v>224</v>
@@ -1806,21 +1806,21 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B42">
-        <v>33.79746835443038</v>
+        <v>33.924050632911396</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B43">
-        <v>33.41772151898735</v>
+        <v>33.60759493670886</v>
       </c>
       <c r="C43" t="s">
         <v>224</v>
@@ -1828,54 +1828,54 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B44">
-        <v>33.29113924050633</v>
+        <v>33.037974683544306</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B45">
-        <v>32.088607594936704</v>
+        <v>32.53164556962026</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>31.20253164556962</v>
+        <v>31.962025316455687</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B47">
-        <v>30.31645569620253</v>
+        <v>31.645569620253163</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B48">
-        <v>29.936708860759495</v>
+        <v>30.69620253164556</v>
       </c>
       <c r="C48" t="s">
         <v>224</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="B49">
-        <v>29.303797468354432</v>
+        <v>30.063291139240512</v>
       </c>
       <c r="C49" t="s">
         <v>224</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B50">
-        <v>29.050632911392405</v>
+        <v>29.81012658227848</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1908,7 +1908,7 @@
         <v>26</v>
       </c>
       <c r="B51">
-        <v>26.9620253164557</v>
+        <v>28.9873417721519</v>
       </c>
       <c r="C51" t="s">
         <v>224</v>
@@ -2149,55 +2149,55 @@
         <v>63.29113924050633</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.5446880269814502</v>
+        <v>-1.630691399662732</v>
       </c>
       <c r="E2" s="1">
         <v>0.98</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.001133992070301515</v>
+        <v>-0.024723464469771136</v>
       </c>
       <c r="G2" s="1">
         <v>0.18</v>
       </c>
       <c r="H2" s="1">
-        <v>51.69</v>
+        <v>44.29</v>
       </c>
       <c r="I2" s="1">
-        <v>18.17</v>
+        <v>14.08</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0044707771952847</v>
+        <v>0.002455727619990929</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.08303169024131707</v>
+        <v>-0.10516696911420542</v>
       </c>
       <c r="N2" s="1">
-        <v>2.7593551430653225</v>
+        <v>0.3684865818031522</v>
       </c>
       <c r="O2" s="1">
-        <v>44.303797468354425</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>42.53164556962026</v>
+        <v>38.73417721518988</v>
       </c>
       <c r="R2" s="1">
-        <v>33.79746835443038</v>
+        <v>33.037974683544306</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>0.95</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2217,49 +2217,49 @@
         <v>-0.5</v>
       </c>
       <c r="F3" s="2">
-        <v>1.1245287235286383</v>
+        <v>1.1062695852316171</v>
       </c>
       <c r="G3" s="2">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="H3" s="2">
-        <v>72.59</v>
+        <v>77.07</v>
       </c>
       <c r="I3" s="2">
-        <v>102.49</v>
+        <v>116.7</v>
       </c>
       <c r="J3" s="2">
-        <v>0.0858707650915428</v>
+        <v>0.09026237558486737</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M3" s="2">
-        <v>1.2673503191195556</v>
+        <v>1.2475362275340383</v>
       </c>
       <c r="N3" s="2">
-        <v>137.7975560791526</v>
+        <v>135.63880624662755</v>
       </c>
       <c r="O3" s="2">
-        <v>97.46835443037975</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.69620253164557</v>
+        <v>75.94936708860759</v>
       </c>
       <c r="R3" s="2">
-        <v>65.37974683544304</v>
+        <v>64.87341772151899</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.44</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2273,55 +2273,55 @@
         <v>6.329113924050633</v>
       </c>
       <c r="D4" s="3">
-        <v>9.868354430379748</v>
+        <v>10.116455696202532</v>
       </c>
       <c r="E4" s="3">
         <v>-1.02</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.02897198602682774</v>
+        <v>-0.018910370905183854</v>
       </c>
       <c r="G4" s="3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H4" s="3">
-        <v>66.21</v>
+        <v>69.36</v>
       </c>
       <c r="I4" s="3">
-        <v>-15.05</v>
+        <v>-12.33</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.007370556919205959</v>
+        <v>-0.005412846431288901</v>
       </c>
       <c r="K4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.017985709442911002</v>
+        <v>-0.0061571323639930675</v>
       </c>
       <c r="N4" s="3">
-        <v>9.26395322290592</v>
+        <v>10.269470256824391</v>
       </c>
       <c r="O4" s="3">
-        <v>53.16455696202531</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>37.34177215189874</v>
+        <v>38.35443037974684</v>
       </c>
       <c r="R4" s="3">
-        <v>26.898734177215193</v>
+        <v>27.53164556962025</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>12.09</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2341,49 +2341,49 @@
         <v>0.34</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.12404879430885826</v>
+        <v>-0.12819511545725013</v>
       </c>
       <c r="G5" s="1">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="1">
-        <v>58.3</v>
+        <v>60.86</v>
       </c>
       <c r="I5" s="1">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="J5" s="1">
-        <v>0.004019859892690031</v>
+        <v>0.005522357877051351</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.0451473533880018</v>
+        <v>-0.04971364751146057</v>
       </c>
       <c r="N5" s="1">
-        <v>6.547788828396834</v>
+        <v>5.91381874207764</v>
       </c>
       <c r="O5" s="1">
-        <v>48.10126582278481</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P5" s="1">
-        <v>27.76573618206019</v>
+        <v>25.321993503429013</v>
       </c>
       <c r="Q5" s="1">
         <v>58.607594936708864</v>
       </c>
       <c r="R5" s="1">
-        <v>44.11392405063292</v>
+        <v>44.620253164556964</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2403,19 +2403,19 @@
         <v>0.97</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0019236793285661025</v>
+        <v>-0.03633840164753008</v>
       </c>
       <c r="G6" s="1">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H6" s="1">
-        <v>43.87</v>
+        <v>41.43</v>
       </c>
       <c r="I6" s="1">
-        <v>-13.04</v>
+        <v>-13.81</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.00815438806640506</v>
+        <v>-0.007801426772082932</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
@@ -2424,28 +2424,28 @@
         <v>124</v>
       </c>
       <c r="M6" s="1">
-        <v>0.05485755741471032</v>
+        <v>0.014674552517233153</v>
       </c>
       <c r="N6" s="1">
-        <v>16.548279908668054</v>
+        <v>12.352638744947017</v>
       </c>
       <c r="O6" s="1">
-        <v>63.29113924050633</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>38.734177215189874</v>
+        <v>37.46835443037975</v>
       </c>
       <c r="R6" s="1">
-        <v>42.151898734177216</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>0.06</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2459,25 +2459,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>5.0520673813169985</v>
+        <v>5.032159264931087</v>
       </c>
       <c r="E7" s="2">
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.11032541787647918</v>
+        <v>-0.11636798937581794</v>
       </c>
       <c r="G7" s="2">
         <v>2.24</v>
       </c>
       <c r="H7" s="2">
-        <v>53.71</v>
+        <v>53.26</v>
       </c>
       <c r="I7" s="2">
-        <v>15.13</v>
+        <v>14.77</v>
       </c>
       <c r="J7" s="2">
-        <v>0.01935348222607045</v>
+        <v>0.01824488634695496</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.013519881796763888</v>
+        <v>0.005278285940155891</v>
       </c>
       <c r="N7" s="2">
-        <v>12.414512346873414</v>
+        <v>11.413012087239286</v>
       </c>
       <c r="O7" s="2">
         <v>56.9620253164557</v>
@@ -2498,16 +2498,16 @@
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>61.64556962025316</v>
+        <v>60.75949367088607</v>
       </c>
       <c r="R7" s="2">
-        <v>52.468354430379755</v>
+        <v>52.21518987341773</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>-2.09</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2521,25 +2521,25 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>0.004531722054380702</v>
+        <v>0.021903323262839815</v>
       </c>
       <c r="E8" s="2">
         <v>1.61</v>
       </c>
       <c r="F8" s="2">
-        <v>0.30022542690549336</v>
+        <v>0.30113618385521035</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>67.84</v>
+        <v>56.83</v>
       </c>
       <c r="I8" s="2">
-        <v>19.89</v>
+        <v>16.07</v>
       </c>
       <c r="J8" s="2">
-        <v>0.032367424037634956</v>
+        <v>0.03154432129640191</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>-220</v>
       </c>
       <c r="M8" s="2">
-        <v>0.2652690923203038</v>
+        <v>0.2668005416289274</v>
       </c>
       <c r="N8" s="2">
-        <v>37.58943339922741</v>
+        <v>37.56523765611643</v>
       </c>
       <c r="O8" s="2">
         <v>84.81012658227847</v>
@@ -2560,16 +2560,16 @@
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>64.81012658227849</v>
+        <v>61.26582278481013</v>
       </c>
       <c r="R8" s="2">
-        <v>55.31645569620253</v>
+        <v>54.936708860759495</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2589,19 +2589,19 @@
         <v>0.88</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.1124771160622832</v>
+        <v>-0.09767293257381973</v>
       </c>
       <c r="G9" s="1">
         <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>47.49</v>
+        <v>47.07</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.84</v>
+        <v>-15.89</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.012185986493189084</v>
+        <v>-0.011157712883681248</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
@@ -2610,28 +2610,28 @@
         <v>-14</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.06253949522629809</v>
+        <v>-0.048622015107701255</v>
       </c>
       <c r="N9" s="1">
-        <v>4.808574644567205</v>
+        <v>6.022981982453576</v>
       </c>
       <c r="O9" s="1">
-        <v>45.56962025316456</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P9" s="1">
-        <v>32.13926500847113</v>
+        <v>30.47019076386737</v>
       </c>
       <c r="Q9" s="1">
-        <v>44.55696202531645</v>
+        <v>44.81012658227848</v>
       </c>
       <c r="R9" s="1">
-        <v>38.92405063291139</v>
+        <v>40.37974683544304</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-2.28</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2651,49 +2651,49 @@
         <v>-0.77</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.16507857895453248</v>
+        <v>-0.17519338162267328</v>
       </c>
       <c r="G10" s="1">
         <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>48.68</v>
+        <v>49.45</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.06</v>
+        <v>-4.76</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0023784044631915443</v>
+        <v>0.002697688644044308</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.12412972986902471</v>
+        <v>-0.13497162930045614</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.3504488197054516</v>
+        <v>-2.6119794368219247</v>
       </c>
       <c r="O10" s="1">
-        <v>36.708860759493675</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>45.949367088607595</v>
+        <v>46.45569620253165</v>
       </c>
       <c r="R10" s="1">
-        <v>36.265822784810126</v>
+        <v>37.27848101265823</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-2.53</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2707,25 +2707,25 @@
         <v>12.658227848101266</v>
       </c>
       <c r="D11" s="2">
-        <v>31.911764705882348</v>
+        <v>31.985294117647058</v>
       </c>
       <c r="E11" s="2">
         <v>-0.88</v>
       </c>
       <c r="F11" s="2">
-        <v>0.4188838046724108</v>
+        <v>0.36040882690817566</v>
       </c>
       <c r="G11" s="2">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H11" s="2">
-        <v>75.87</v>
+        <v>73.75</v>
       </c>
       <c r="I11" s="2">
-        <v>19.97</v>
+        <v>18.94</v>
       </c>
       <c r="J11" s="2">
-        <v>0.027159281919290783</v>
+        <v>0.027995251552379325</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.4019050135881759</v>
+        <v>0.34569355166834015</v>
       </c>
       <c r="N11" s="2">
-        <v>51.2530255260146</v>
+        <v>45.454538660057715</v>
       </c>
       <c r="O11" s="2">
         <v>86.07594936708861</v>
@@ -2746,16 +2746,16 @@
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>61.39240506329114</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="R11" s="2">
-        <v>53.29113924050633</v>
+        <v>53.16455696202532</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>6.84</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2775,34 +2775,34 @@
         <v>3.81</v>
       </c>
       <c r="F12" s="1">
-        <v>0.016715544305819674</v>
+        <v>-0.022291932529678885</v>
       </c>
       <c r="G12" s="1">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H12" s="1">
-        <v>61.61</v>
+        <v>61.74</v>
       </c>
       <c r="I12" s="1">
-        <v>-25.29</v>
+        <v>-25.02</v>
       </c>
       <c r="J12" s="1">
-        <v>0.00975740328561801</v>
+        <v>0.013233694366704676</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="1">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0017342580550241404</v>
+        <v>-0.035045171070869685</v>
       </c>
       <c r="N12" s="1">
-        <v>11.235949972699437</v>
+        <v>7.38066638613672</v>
       </c>
       <c r="O12" s="1">
-        <v>54.43037974683544</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P12" s="1">
         <v>49.188907754993835</v>
@@ -2811,13 +2811,13 @@
         <v>52.27848101265822</v>
       </c>
       <c r="R12" s="1">
-        <v>39.74683544303798</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="1">
-        <v>19.05</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2837,19 +2837,19 @@
         <v>6.41</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.34627943391667687</v>
+        <v>-0.34065996600621173</v>
       </c>
       <c r="G13" s="3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H13" s="3">
-        <v>38.12</v>
+        <v>42.82</v>
       </c>
       <c r="I13" s="3">
-        <v>-11.72</v>
+        <v>-8.42</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.0077494339547497315</v>
+        <v>-0.009577099600196395</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
@@ -2858,10 +2858,10 @@
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.3063293372478888</v>
+        <v>-0.3024002503826393</v>
       </c>
       <c r="N13" s="3">
-        <v>-19.570409557591855</v>
+        <v>-19.354841545040237</v>
       </c>
       <c r="O13" s="3">
         <v>6.329113924050633</v>
@@ -2870,16 +2870,16 @@
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>18.607594936708857</v>
+        <v>17.974683544303797</v>
       </c>
       <c r="R13" s="3">
-        <v>4.620253164556961</v>
+        <v>3.4810126582278462</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-11.27</v>
+        <v>-12.41</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2893,25 +2893,25 @@
         <v>44.303797468354425</v>
       </c>
       <c r="D14" s="1">
-        <v>7.572519083969465</v>
+        <v>7.564885496183206</v>
       </c>
       <c r="E14" s="1">
         <v>4.73</v>
       </c>
       <c r="F14" s="1">
-        <v>0.25433058752469034</v>
+        <v>0.2451322190007546</v>
       </c>
       <c r="G14" s="1">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H14" s="1">
-        <v>70.28</v>
+        <v>71.91</v>
       </c>
       <c r="I14" s="1">
-        <v>8.58</v>
+        <v>10.42</v>
       </c>
       <c r="J14" s="1">
-        <v>0.011346920685124297</v>
+        <v>0.013491630876964871</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>0.21637799568934168</v>
+        <v>0.20981555842514932</v>
       </c>
       <c r="N14" s="1">
-        <v>32.70032373613118</v>
+        <v>31.866739335738618</v>
       </c>
       <c r="O14" s="1">
         <v>79.74683544303798</v>
@@ -2961,19 +2961,19 @@
         <v>2.23</v>
       </c>
       <c r="F15" s="2">
-        <v>1.5142607110028368</v>
+        <v>1.448713599855782</v>
       </c>
       <c r="G15" s="2">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="H15" s="2">
-        <v>68.18</v>
+        <v>70.23</v>
       </c>
       <c r="I15" s="2">
-        <v>154.04</v>
+        <v>158.99</v>
       </c>
       <c r="J15" s="2">
-        <v>0.09993122229238127</v>
+        <v>0.1017758350432543</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2982,10 +2982,10 @@
         <v>193</v>
       </c>
       <c r="M15" s="2">
-        <v>1.6361085058426403</v>
+        <v>1.5693788568224336</v>
       </c>
       <c r="N15" s="2">
-        <v>174.67337475146107</v>
+        <v>167.82306917546705</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2994,7 +2994,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>70.50632911392405</v>
+        <v>70.25316455696203</v>
       </c>
       <c r="R15" s="2">
         <v>62.27848101265822</v>
@@ -3023,19 +3023,19 @@
         <v>5.41</v>
       </c>
       <c r="F16" s="3">
-        <v>-0.2440648629943353</v>
+        <v>-0.2695530962138256</v>
       </c>
       <c r="G16" s="3">
         <v>1.91</v>
       </c>
       <c r="H16" s="3">
-        <v>44.33</v>
+        <v>44.41</v>
       </c>
       <c r="I16" s="3">
-        <v>-4.74</v>
+        <v>-4.7</v>
       </c>
       <c r="J16" s="3">
-        <v>-0.007032298971321377</v>
+        <v>-0.006160031268303892</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>0</v>
@@ -3044,28 +3044,28 @@
         <v>16</v>
       </c>
       <c r="M16" s="3">
-        <v>-0.15317839307284242</v>
+        <v>-0.18028042642549003</v>
       </c>
       <c r="N16" s="3">
-        <v>-4.255315140087222</v>
+        <v>-7.142859149325314</v>
       </c>
       <c r="O16" s="3">
-        <v>32.91139240506329</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
       <c r="Q16" s="3">
-        <v>36.07594936708861</v>
+        <v>35.31645569620253</v>
       </c>
       <c r="R16" s="3">
-        <v>26.265822784810123</v>
+        <v>24.746835443037973</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T16" s="3">
-        <v>-10.38</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3085,19 +3085,19 @@
         <v>1.52</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.24959727122568215</v>
+        <v>-0.27073053680225956</v>
       </c>
       <c r="G17" s="3">
         <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>47.16</v>
+        <v>50.55</v>
       </c>
       <c r="I17" s="3">
-        <v>-9.65</v>
+        <v>-7.41</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.008520080406664325</v>
+        <v>-0.004343408377603495</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3106,90 +3106,90 @@
         <v>25</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.1776870972218636</v>
+        <v>-0.200097215651049</v>
       </c>
       <c r="N17" s="3">
-        <v>-6.706185554989343</v>
+        <v>-9.124538071881206</v>
       </c>
       <c r="O17" s="3">
-        <v>27.848101265822784</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>26.962025316455694</v>
+        <v>31.139240506329116</v>
       </c>
       <c r="R17" s="3">
-        <v>18.481012658227847</v>
+        <v>18.607594936708864</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.68</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>6.73</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.3099909673030672</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1.21</v>
-      </c>
-      <c r="H18" s="3">
-        <v>36.66</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-11.7</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.00825553229642634</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="F18" s="1">
+        <v>-0.31061503994634965</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>35.04</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-13.48</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.007012635546003202</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>37</v>
       </c>
-      <c r="M18" s="3">
-        <v>-0.2890171665519534</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-17.83919248799832</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="M18" s="1">
+        <v>-0.2909946729599022</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-18.21428380276653</v>
+      </c>
+      <c r="O18" s="1">
         <v>8.860759493670885</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="1">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="3">
-        <v>46.962025316455694</v>
-      </c>
-      <c r="R18" s="3">
-        <v>29.936708860759495</v>
-      </c>
-      <c r="S18" s="3" t="s">
+      <c r="Q18" s="1">
+        <v>46.708860759493675</v>
+      </c>
+      <c r="R18" s="1">
+        <v>30.063291139240512</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="3">
-        <v>-1.01</v>
+      <c r="T18" s="1">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,19 +3209,19 @@
         <v>-1.48</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.04286677610091033</v>
+        <v>-0.0408761989982334</v>
       </c>
       <c r="G19" s="1">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>54.59</v>
+        <v>53.74</v>
       </c>
       <c r="I19" s="1">
-        <v>14.5</v>
+        <v>13.88</v>
       </c>
       <c r="J19" s="1">
-        <v>0.0017908335374055109</v>
+        <v>0.0022734937249961917</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>0</v>
@@ -3230,28 +3230,28 @@
         <v>79</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.12376572185520618</v>
+        <v>-0.11935766694402294</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.3140480183236036</v>
+        <v>-1.0505832011786014</v>
       </c>
       <c r="O19" s="1">
-        <v>37.9746835443038</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>51.898734177215196</v>
+        <v>51.39240506329114</v>
       </c>
       <c r="R19" s="1">
-        <v>40.31645569620253</v>
+        <v>41.58227848101266</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>-0.57</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3271,49 +3271,49 @@
         <v>6.54</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.04396168819698541</v>
+        <v>-0.009788259846447836</v>
       </c>
       <c r="G20" s="1">
         <v>1.06</v>
       </c>
       <c r="H20" s="1">
-        <v>61.32</v>
+        <v>65.69</v>
       </c>
       <c r="I20" s="1">
-        <v>-1.69</v>
+        <v>1.39</v>
       </c>
       <c r="J20" s="1">
-        <v>0.006194222734067824</v>
+        <v>0.007812277045019132</v>
       </c>
       <c r="K20" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.03796917369666719</v>
+        <v>-0.003902149750513617</v>
       </c>
       <c r="N20" s="1">
-        <v>7.265606797530289</v>
+        <v>10.494968518172325</v>
       </c>
       <c r="O20" s="1">
-        <v>49.36708860759494</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>52.025316455696206</v>
+        <v>53.41772151898734</v>
       </c>
       <c r="R20" s="1">
-        <v>40.06329113924051</v>
+        <v>41.962025316455694</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>12.66</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3333,19 +3333,19 @@
         <v>2.47</v>
       </c>
       <c r="F21" s="2">
-        <v>0.1992697218600915</v>
+        <v>0.19199629327570336</v>
       </c>
       <c r="G21" s="2">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H21" s="2">
-        <v>78.27</v>
+        <v>79.86</v>
       </c>
       <c r="I21" s="2">
-        <v>72.92</v>
+        <v>79.82</v>
       </c>
       <c r="J21" s="2">
-        <v>0.03469493860499573</v>
+        <v>0.041584347423851274</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
@@ -3354,28 +3354,28 @@
         <v>37</v>
       </c>
       <c r="M21" s="2">
-        <v>0.24021857094559929</v>
+        <v>0.23614211899520998</v>
       </c>
       <c r="N21" s="2">
-        <v>35.08438126175695</v>
+        <v>34.499395392744695</v>
       </c>
       <c r="O21" s="2">
-        <v>83.54430379746836</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="2">
-        <v>70.37974683544304</v>
+        <v>70.50632911392405</v>
       </c>
       <c r="R21" s="2">
-        <v>54.43037974683544</v>
+        <v>54.050632911392405</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="2">
-        <v>15.63</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3395,49 +3395,49 @@
         <v>-0.84</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.2542193800312568</v>
+        <v>-0.23429123330990573</v>
       </c>
       <c r="G22" s="1">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H22" s="1">
-        <v>55.62</v>
+        <v>61.77</v>
       </c>
       <c r="I22" s="1">
-        <v>0.89</v>
+        <v>4.7</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.008591392077507557</v>
+        <v>-0.005102046491354681</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.21726554061262782</v>
+        <v>-0.19897457273430041</v>
       </c>
       <c r="N22" s="1">
-        <v>-10.664029894065767</v>
+        <v>-9.012273780206344</v>
       </c>
       <c r="O22" s="1">
-        <v>18.9873417721519</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P22" s="1">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="1">
-        <v>46.58227848101266</v>
+        <v>51.26582278481012</v>
       </c>
       <c r="R22" s="1">
-        <v>30.31645569620253</v>
+        <v>33.60759493670886</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>0.06</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3457,19 +3457,19 @@
         <v>0.96</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.1759503961923806</v>
+        <v>-0.17358632133750004</v>
       </c>
       <c r="G23" s="1">
         <v>1.23</v>
       </c>
       <c r="H23" s="1">
-        <v>45.34</v>
+        <v>46.45</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.84</v>
+        <v>-8.43</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.006523540464090489</v>
+        <v>-0.005491326524766096</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
@@ -3478,28 +3478,28 @@
         <v>22</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.15297909060782744</v>
+        <v>-0.15102289930308554</v>
       </c>
       <c r="N23" s="1">
-        <v>-4.23538489358572</v>
+        <v>-4.217106437084858</v>
       </c>
       <c r="O23" s="1">
-        <v>34.177215189873415</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>45.063291139240505</v>
+        <v>43.92405063291139</v>
       </c>
       <c r="R23" s="1">
-        <v>34.36708860759494</v>
+        <v>34.24050632911393</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3519,19 +3519,19 @@
         <v>9.47</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.07284893500744283</v>
+        <v>-0.07458621436303953</v>
       </c>
       <c r="G24" s="3">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="H24" s="3">
-        <v>44.64</v>
+        <v>44.67</v>
       </c>
       <c r="I24" s="3">
-        <v>-24.77</v>
+        <v>-24.32</v>
       </c>
       <c r="J24" s="3">
-        <v>0.017773128640658612</v>
+        <v>0.016015518165394222</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
@@ -3540,28 +3540,28 @@
         <v>-13</v>
       </c>
       <c r="M24" s="3">
-        <v>0.18183293125608113</v>
+        <v>0.17459244636484228</v>
       </c>
       <c r="N24" s="3">
-        <v>29.24581729280514</v>
+        <v>28.34442812970791</v>
       </c>
       <c r="O24" s="3">
-        <v>77.21518987341773</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>23.29113924050633</v>
+        <v>22.278481012658233</v>
       </c>
       <c r="R24" s="3">
-        <v>26.835443037974688</v>
+        <v>26.075949367088608</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-4.18</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3581,19 +3581,19 @@
         <v>11.95</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.3277111894172485</v>
+        <v>-0.31765185420632047</v>
       </c>
       <c r="G25" s="3">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="H25" s="3">
-        <v>48.44</v>
+        <v>53.4</v>
       </c>
       <c r="I25" s="3">
-        <v>-50.4</v>
+        <v>-46.45</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.010951427092932576</v>
+        <v>-0.008187214722448165</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3602,28 +3602,28 @@
         <v>41</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.20586339457744485</v>
+        <v>-0.19894863393831375</v>
       </c>
       <c r="N25" s="3">
-        <v>-9.523815290547468</v>
+        <v>-9.009679900607681</v>
       </c>
       <c r="O25" s="3">
-        <v>24.050632911392405</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>11.265822784810128</v>
+        <v>13.797468354430382</v>
       </c>
       <c r="R25" s="3">
-        <v>2.531645569620256</v>
+        <v>3.9240506329113938</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-9.43</v>
+        <v>-8.04</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3643,19 +3643,19 @@
         <v>3.39</v>
       </c>
       <c r="F26" s="1">
-        <v>0.7492105379751037</v>
+        <v>0.6971519348388568</v>
       </c>
       <c r="G26" s="1">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="H26" s="1">
-        <v>69.21</v>
+        <v>69.17</v>
       </c>
       <c r="I26" s="1">
-        <v>34.44</v>
+        <v>34.07</v>
       </c>
       <c r="J26" s="1">
-        <v>0.05065285036023047</v>
+        <v>0.05899436026223026</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>0</v>
@@ -3664,28 +3664,28 @@
         <v>-29</v>
       </c>
       <c r="M26" s="1">
-        <v>0.9569510406528017</v>
+        <v>0.9031657881965545</v>
       </c>
       <c r="N26" s="1">
-        <v>106.75762823247716</v>
+        <v>101.20176231287911</v>
       </c>
       <c r="O26" s="1">
-        <v>94.9367088607595</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P26" s="1">
         <v>47.81158046237125</v>
       </c>
       <c r="Q26" s="1">
-        <v>42.911392405063296</v>
+        <v>42.02531645569621</v>
       </c>
       <c r="R26" s="1">
-        <v>34.68354430379747</v>
+        <v>33.924050632911396</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>1.65</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3705,19 +3705,19 @@
         <v>8.19</v>
       </c>
       <c r="F27" s="3">
-        <v>-0.1277690325559252</v>
+        <v>-0.08357262615109584</v>
       </c>
       <c r="G27" s="3">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="H27" s="3">
-        <v>61.22</v>
+        <v>65.75</v>
       </c>
       <c r="I27" s="3">
-        <v>-15.73</v>
+        <v>-10.9</v>
       </c>
       <c r="J27" s="3">
-        <v>0.004968354140175307</v>
+        <v>0.0071593397768241595</v>
       </c>
       <c r="K27" s="3" t="b">
         <v>0</v>
@@ -3726,28 +3726,28 @@
         <v>42</v>
       </c>
       <c r="M27" s="3">
-        <v>0.034028858952666496</v>
+        <v>0.07633336478845032</v>
       </c>
       <c r="N27" s="3">
-        <v>14.465410062463668</v>
+        <v>18.518519972068724</v>
       </c>
       <c r="O27" s="3">
-        <v>58.22784810126582</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P27" s="3">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="3">
-        <v>36.32911392405063</v>
+        <v>38.10126582278481</v>
       </c>
       <c r="R27" s="3">
-        <v>26.9620253164557</v>
+        <v>28.9873417721519</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="3">
-        <v>0.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3767,49 +3767,49 @@
         <v>-4.03</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.4085676363935638</v>
+        <v>-0.41238451843205376</v>
       </c>
       <c r="G28" s="3">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="H28" s="3">
-        <v>56.49</v>
+        <v>59.16</v>
       </c>
       <c r="I28" s="3">
-        <v>-20.92</v>
+        <v>-18.89</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.005411292738181298</v>
+        <v>-0.0026235986840229294</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="3">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.19683212404898698</v>
+        <v>-0.2034276100263891</v>
       </c>
       <c r="N28" s="3">
-        <v>-8.620688237701678</v>
+        <v>-9.457577509415213</v>
       </c>
       <c r="O28" s="3">
-        <v>25.31645569620253</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>37.08860759493671</v>
+        <v>37.721518987341774</v>
       </c>
       <c r="R28" s="3">
-        <v>21.32911392405063</v>
+        <v>20.44303797468354</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-0.57</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3829,49 +3829,49 @@
         <v>1.51</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.36518581562558294</v>
+        <v>-0.36136761163686304</v>
       </c>
       <c r="G29" s="3">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H29" s="3">
-        <v>42.75</v>
+        <v>46.48</v>
       </c>
       <c r="I29" s="3">
-        <v>-33.04</v>
+        <v>-31.41</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.01678760244586837</v>
+        <v>-0.015190326766006321</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.2533255449529763</v>
+        <v>-0.25247457486208</v>
       </c>
       <c r="N29" s="3">
-        <v>-14.270030328100617</v>
+        <v>-14.36227399298431</v>
       </c>
       <c r="O29" s="3">
-        <v>11.39240506329114</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>41.139240506329116</v>
+        <v>42.40506329113924</v>
       </c>
       <c r="R29" s="3">
-        <v>25.949367088607595</v>
+        <v>26.708860759493668</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3891,49 +3891,49 @@
         <v>1.79</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.18015765004783127</v>
+        <v>-0.18957612950131153</v>
       </c>
       <c r="G30" s="1">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H30" s="1">
-        <v>44.85</v>
+        <v>44.74</v>
       </c>
       <c r="I30" s="1">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="J30" s="1">
-        <v>0.0003414019685547603</v>
+        <v>0.002133982095610389</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.16018260171343723</v>
+        <v>-0.1709367808641865</v>
       </c>
       <c r="N30" s="1">
-        <v>-4.955736004146704</v>
+        <v>-6.208494593194955</v>
       </c>
       <c r="O30" s="1">
-        <v>29.11392405063291</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>60.25316455696203</v>
+        <v>60</v>
       </c>
       <c r="R30" s="1">
-        <v>45.25316455696203</v>
+        <v>46.0126582278481</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-2.28</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3953,19 +3953,19 @@
         <v>0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>0.10110524376514901</v>
+        <v>0.1464829913335334</v>
       </c>
       <c r="G31" s="2">
         <v>1.42</v>
       </c>
       <c r="H31" s="2">
-        <v>53.07</v>
+        <v>56.45</v>
       </c>
       <c r="I31" s="2">
-        <v>18.38</v>
+        <v>20.42</v>
       </c>
       <c r="J31" s="2">
-        <v>0.020676617691050638</v>
+        <v>0.021094409729336107</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
@@ -3974,28 +3974,28 @@
         <v>67</v>
       </c>
       <c r="M31" s="2">
-        <v>0.1430528452673765</v>
+        <v>0.18768576200507292</v>
       </c>
       <c r="N31" s="2">
-        <v>25.36780869393467</v>
+        <v>29.65375969373098</v>
       </c>
       <c r="O31" s="2">
-        <v>72.15189873417721</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>64.17721518987341</v>
+        <v>64.9367088607595</v>
       </c>
       <c r="R31" s="2">
-        <v>58.0379746835443</v>
+        <v>59.55696202531646</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-2.78</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4015,49 +4015,49 @@
         <v>-2.98</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.22101436430786242</v>
+        <v>-0.21697434761137646</v>
       </c>
       <c r="G32" s="3">
         <v>1.61</v>
       </c>
       <c r="H32" s="3">
-        <v>45.41</v>
+        <v>47.2</v>
       </c>
       <c r="I32" s="3">
-        <v>-7.47</v>
+        <v>-6.43</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.014663438154852729</v>
+        <v>-0.012699275100331421</v>
       </c>
       <c r="K32" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.16009046688796058</v>
+        <v>-0.1571322283027119</v>
       </c>
       <c r="N32" s="3">
-        <v>-4.946522521599034</v>
+        <v>-4.828039337047492</v>
       </c>
       <c r="O32" s="3">
-        <v>30.37974683544304</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P32" s="3">
-        <v>38.277512660369005</v>
+        <v>37.59071325149605</v>
       </c>
       <c r="Q32" s="3">
-        <v>30.63291139240506</v>
+        <v>31.0126582278481</v>
       </c>
       <c r="R32" s="3">
-        <v>20.44303797468354</v>
+        <v>21.582278481012658</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-8.92</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4071,55 +4071,55 @@
         <v>88.60759493670885</v>
       </c>
       <c r="D33" s="1">
-        <v>-0.05955926146515784</v>
+        <v>-0.06611078022632516</v>
       </c>
       <c r="E33" s="1">
         <v>-0.44</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.03092047167602477</v>
+        <v>-0.048195142031673216</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>54.42</v>
+        <v>52.31</v>
       </c>
       <c r="I33" s="1">
-        <v>-9.09</v>
+        <v>-9.53</v>
       </c>
       <c r="J33" s="1">
-        <v>0.003448564153746001</v>
+        <v>0.0037415212105996578</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.021931699925547443</v>
+        <v>-0.03936597688777188</v>
       </c>
       <c r="N33" s="1">
-        <v>8.869354174642272</v>
+        <v>6.948585804446497</v>
       </c>
       <c r="O33" s="1">
-        <v>51.89873417721519</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P33" s="1">
-        <v>26.847922891788212</v>
+        <v>26.81341163265095</v>
       </c>
       <c r="Q33" s="1">
-        <v>50.25316455696202</v>
+        <v>49.36708860759493</v>
       </c>
       <c r="R33" s="1">
-        <v>42.025316455696206</v>
+        <v>41.26582278481012</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>2.09</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4139,49 +4139,49 @@
         <v>0.77</v>
       </c>
       <c r="F34" s="1">
-        <v>0.09288490979336392</v>
+        <v>0.11744294601695968</v>
       </c>
       <c r="G34" s="1">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H34" s="1">
-        <v>57.49</v>
+        <v>61.01</v>
       </c>
       <c r="I34" s="1">
-        <v>29.3</v>
+        <v>30.87</v>
       </c>
       <c r="J34" s="1">
-        <v>0.025243074025964922</v>
+        <v>0.024388336180927072</v>
       </c>
       <c r="K34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M34" s="1">
-        <v>0.11885247262807619</v>
+        <v>0.14196840475001893</v>
       </c>
       <c r="N34" s="1">
-        <v>22.947771430004632</v>
+        <v>25.0820239682256</v>
       </c>
       <c r="O34" s="1">
-        <v>68.35443037974683</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P34" s="1">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="1">
-        <v>58.10126582278481</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="R34" s="1">
-        <v>48.48101265822785</v>
+        <v>49.24050632911393</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T34" s="1">
-        <v>-2.66</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4201,40 +4201,40 @@
         <v>9.42</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.32003676981025153</v>
+        <v>-0.35940711190172214</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>38.72</v>
+        <v>35.22</v>
       </c>
       <c r="I35" s="3">
-        <v>-21.31</v>
+        <v>-22.7</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.02469207948983701</v>
+        <v>-0.024316454607649276</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.32003676981025153</v>
+        <v>-0.35940711190172214</v>
       </c>
       <c r="N35" s="3">
-        <v>-20.941152813828133</v>
+        <v>-25.05552769694852</v>
       </c>
       <c r="O35" s="3">
         <v>3.79746835443038</v>
       </c>
       <c r="P35" s="3">
-        <v>28.966535793040393</v>
+        <v>28.919768290867083</v>
       </c>
       <c r="Q35" s="3">
-        <v>34.177215189873415</v>
+        <v>33.797468354430386</v>
       </c>
       <c r="R35" s="3">
         <v>21.455696202531644</v>
@@ -4263,111 +4263,111 @@
         <v>3.24</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.12169121164446169</v>
+        <v>-0.1560322140466506</v>
       </c>
       <c r="G36" s="1">
         <v>1.12</v>
       </c>
       <c r="H36" s="1">
-        <v>51.69</v>
+        <v>55.05</v>
       </c>
       <c r="I36" s="1">
-        <v>-9.27</v>
+        <v>-6.91</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.011939157521507997</v>
+        <v>-0.008146925649258702</v>
       </c>
       <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>-57</v>
+        <v>-55</v>
       </c>
       <c r="M36" s="1">
-        <v>-0.10970618264382526</v>
+        <v>-0.14425999385478216</v>
       </c>
       <c r="N36" s="1">
-        <v>0.09190590281449364</v>
+        <v>-3.540815892254525</v>
       </c>
       <c r="O36" s="1">
-        <v>39.24050632911392</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="1">
-        <v>43.164556962025316</v>
+        <v>46.20253164556962</v>
       </c>
       <c r="R36" s="1">
-        <v>33.544303797468345</v>
+        <v>33.67088607594937</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.76</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="3">
         <v>5.33</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="3">
         <v>62.0253164556962</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="3">
         <v>0.6022514071294557</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="3">
         <v>-5.1</v>
       </c>
-      <c r="F37" s="1">
-        <v>-0.14349280848462048</v>
-      </c>
-      <c r="G37" s="1">
+      <c r="F37" s="3">
+        <v>-0.20597470701981874</v>
+      </c>
+      <c r="G37" s="3">
         <v>1.37</v>
       </c>
-      <c r="H37" s="1">
-        <v>36.18</v>
-      </c>
-      <c r="I37" s="1">
-        <v>-22.72</v>
-      </c>
-      <c r="J37" s="1">
-        <v>-0.0029765608373550573</v>
-      </c>
-      <c r="K37" s="1" t="b">
+      <c r="H37" s="3">
+        <v>35.83</v>
+      </c>
+      <c r="I37" s="3">
+        <v>-22.68</v>
+      </c>
+      <c r="J37" s="3">
+        <v>-0.0021899364392746613</v>
+      </c>
+      <c r="K37" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L37" s="1">
-        <v>-214</v>
-      </c>
-      <c r="M37" s="1">
-        <v>-0.10653896906599147</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0.4086272605978657</v>
-      </c>
-      <c r="O37" s="1">
-        <v>40.50632911392405</v>
-      </c>
-      <c r="P37" s="1">
-        <v>34.834081981703704</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>37.46835443037975</v>
-      </c>
-      <c r="R37" s="1">
-        <v>31.962025316455698</v>
-      </c>
-      <c r="S37" s="1" t="s">
+      <c r="L37" s="3">
+        <v>-213</v>
+      </c>
+      <c r="M37" s="3">
+        <v>-0.16967702809489105</v>
+      </c>
+      <c r="N37" s="3">
+        <v>-6.082519316265416</v>
+      </c>
+      <c r="O37" s="3">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="P37" s="3">
+        <v>34.65975433248125</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>38.10126582278481</v>
+      </c>
+      <c r="R37" s="3">
+        <v>29.683544303797472</v>
+      </c>
+      <c r="S37" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T37" s="1">
-        <v>-6.84</v>
+      <c r="T37" s="3">
+        <v>-9.11</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4387,49 +4387,49 @@
         <v>-0.57</v>
       </c>
       <c r="F38" s="2">
-        <v>0.769206763363862</v>
+        <v>0.7927965903735908</v>
       </c>
       <c r="G38" s="2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="H38" s="2">
-        <v>86.86</v>
+        <v>87.44</v>
       </c>
       <c r="I38" s="2">
-        <v>42.62</v>
+        <v>43.97</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04584876050881439</v>
+        <v>0.04724798191008728</v>
       </c>
       <c r="K38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2">
         <v>-45</v>
       </c>
       <c r="M38" s="2">
-        <v>0.7831892971979377</v>
+        <v>0.8084928839627488</v>
       </c>
       <c r="N38" s="2">
-        <v>89.3814538869908</v>
+        <v>91.73447188949856</v>
       </c>
       <c r="O38" s="2">
-        <v>92.40506329113924</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P38" s="2">
-        <v>27.21170468568715</v>
+        <v>26.865173556258448</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.82278481012659</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="R38" s="2">
-        <v>56.075949367088604</v>
+        <v>55.696202531645575</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4443,25 +4443,25 @@
         <v>22.78481012658228</v>
       </c>
       <c r="D39" s="1">
-        <v>58.28</v>
+        <v>44.4</v>
       </c>
       <c r="E39" s="1">
         <v>6.03</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.0811210225426576</v>
+        <v>-0.09821364751602973</v>
       </c>
       <c r="G39" s="1">
         <v>1.27</v>
       </c>
       <c r="H39" s="1">
-        <v>35.01</v>
+        <v>32.31</v>
       </c>
       <c r="I39" s="1">
-        <v>-5.9</v>
+        <v>-9.19</v>
       </c>
       <c r="J39" s="1">
-        <v>0.009717900111905141</v>
+        <v>0.006020118944067225</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4470,28 +4470,28 @@
         <v>-4</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.05415470729122562</v>
+        <v>-0.07172615208432576</v>
       </c>
       <c r="N39" s="1">
-        <v>5.647053438074448</v>
+        <v>3.7125682847911228</v>
       </c>
       <c r="O39" s="1">
-        <v>46.835443037974684</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P39" s="1">
-        <v>20.072334383381026</v>
+        <v>21.69982351852176</v>
       </c>
       <c r="Q39" s="1">
-        <v>48.607594936708864</v>
+        <v>46.32911392405063</v>
       </c>
       <c r="R39" s="1">
-        <v>44.050632911392405</v>
+        <v>41.835443037974684</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1">
-        <v>-9.37</v>
+        <v>-11.58</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4505,25 +4505,25 @@
         <v>2.5316455696202533</v>
       </c>
       <c r="D40" s="1">
-        <v>10.126365054602184</v>
+        <v>10.182527301092042</v>
       </c>
       <c r="E40" s="1">
         <v>2.22</v>
       </c>
       <c r="F40" s="1">
-        <v>0.13779721740368814</v>
+        <v>0.11668823300148405</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>39.98</v>
+        <v>38.95</v>
       </c>
       <c r="I40" s="1">
-        <v>-21.71</v>
+        <v>-22.73</v>
       </c>
       <c r="J40" s="1">
-        <v>-0.0006554449553725636</v>
+        <v>-0.0019554944392674366</v>
       </c>
       <c r="K40" s="1" t="b">
         <v>0</v>
@@ -4532,28 +4532,28 @@
         <v>54</v>
       </c>
       <c r="M40" s="1">
-        <v>0.03792197573171796</v>
+        <v>0.018586398069247112</v>
       </c>
       <c r="N40" s="1">
-        <v>14.854721740368806</v>
+        <v>12.743823300148401</v>
       </c>
       <c r="O40" s="1">
-        <v>60.75949367088608</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P40" s="1">
         <v>39.97107065255327</v>
       </c>
       <c r="Q40" s="1">
-        <v>31.139240506329113</v>
+        <v>30.759493670886073</v>
       </c>
       <c r="R40" s="1">
-        <v>31.20253164556962</v>
+        <v>30.69620253164556</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="1">
-        <v>-9.56</v>
+        <v>-10.06</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4573,19 +4573,19 @@
         <v>-1.06</v>
       </c>
       <c r="F41" s="1">
-        <v>0.050500989837036075</v>
+        <v>0.014143850527291654</v>
       </c>
       <c r="G41" s="1">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H41" s="1">
-        <v>64.73</v>
+        <v>61.55</v>
       </c>
       <c r="I41" s="1">
-        <v>-7.69</v>
+        <v>-9.16</v>
       </c>
       <c r="J41" s="1">
-        <v>0.023121818474921865</v>
+        <v>0.02575731648836686</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -4594,28 +4594,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>0.0594897615875134</v>
+        <v>0.02493505236983773</v>
       </c>
       <c r="N41" s="1">
-        <v>17.01150032594835</v>
+        <v>13.378688730207472</v>
       </c>
       <c r="O41" s="1">
-        <v>64.55696202531645</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>45.31645569620253</v>
+        <v>44.17721518987342</v>
       </c>
       <c r="R41" s="1">
-        <v>33.41772151898735</v>
+        <v>32.53164556962026</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>3.35</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4635,19 +4635,19 @@
         <v>2.81</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.0699030450840376</v>
+        <v>-0.07966918560912176</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>50.31</v>
+        <v>48.62</v>
       </c>
       <c r="I42" s="1">
-        <v>1.28</v>
+        <v>0.83</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.004424363322930709</v>
+        <v>-0.004062984230224514</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4656,28 +4656,28 @@
         <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.1338231997540985</v>
+        <v>-0.1424543599657534</v>
       </c>
       <c r="N42" s="1">
-        <v>-2.319795808212828</v>
+        <v>-3.3602525033516475</v>
       </c>
       <c r="O42" s="1">
-        <v>35.44303797468354</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>46.075949367088604</v>
+        <v>45.0632911392405</v>
       </c>
       <c r="R42" s="1">
-        <v>38.10126582278481</v>
+        <v>38.734177215189874</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.44</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4697,19 +4697,19 @@
         <v>10.72</v>
       </c>
       <c r="F43" s="1">
-        <v>0.12052422642201771</v>
+        <v>0.057942216066355745</v>
       </c>
       <c r="G43" s="1">
         <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>56.6</v>
+        <v>56.64</v>
       </c>
       <c r="I43" s="1">
-        <v>-8.67</v>
+        <v>-8.59</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.00852113243900843</v>
+        <v>-0.005799043510940266</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
@@ -4718,28 +4718,28 @@
         <v>10</v>
       </c>
       <c r="M43" s="1">
-        <v>0.14948804650688907</v>
+        <v>0.08639174819670448</v>
       </c>
       <c r="N43" s="1">
-        <v>26.011328817885932</v>
+        <v>19.524358312894144</v>
       </c>
       <c r="O43" s="1">
-        <v>73.41772151898735</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P43" s="1">
-        <v>33.52521846409704</v>
+        <v>33.21399316212126</v>
       </c>
       <c r="Q43" s="1">
-        <v>51.39240506329114</v>
+        <v>52.0253164556962</v>
       </c>
       <c r="R43" s="1">
-        <v>48.22784810126582</v>
+        <v>46.58227848101265</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>6.08</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4759,19 +4759,19 @@
         <v>-0.99</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.39318426248220456</v>
+        <v>-0.3686968263091472</v>
       </c>
       <c r="G44" s="3">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="H44" s="3">
-        <v>41.41</v>
+        <v>43.9</v>
       </c>
       <c r="I44" s="3">
-        <v>-26.63</v>
+        <v>-25.15</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.022231096579952134</v>
+        <v>-0.020691537987769633</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
@@ -4780,28 +4780,28 @@
         <v>-114</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.23238512339033257</v>
+        <v>-0.21173389041756807</v>
       </c>
       <c r="N44" s="3">
-        <v>-12.175988171836241</v>
+        <v>-10.288205548533108</v>
       </c>
       <c r="O44" s="3">
-        <v>15.18987341772152</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P44" s="3">
-        <v>44.155007607957295</v>
+        <v>43.36598203964858</v>
       </c>
       <c r="Q44" s="3">
-        <v>39.87341772151898</v>
+        <v>40.25316455696202</v>
       </c>
       <c r="R44" s="3">
-        <v>26.89873417721519</v>
+        <v>28.417721518987342</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>0.38</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4821,49 +4821,49 @@
         <v>0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>0.14084531898662195</v>
+        <v>0.11901045044535288</v>
       </c>
       <c r="G45" s="2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="2">
-        <v>57.98</v>
+        <v>56.61</v>
       </c>
       <c r="I45" s="2">
-        <v>15.51</v>
+        <v>14.96</v>
       </c>
       <c r="J45" s="2">
-        <v>0.022033896895650402</v>
+        <v>0.022440388114184733</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M45" s="2">
-        <v>0.18678793015572825</v>
+        <v>0.1631562761648595</v>
       </c>
       <c r="N45" s="2">
-        <v>29.741317182769844</v>
+        <v>27.200811109709637</v>
       </c>
       <c r="O45" s="2">
-        <v>78.48101265822784</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>61.39240506329115</v>
+        <v>60.50632911392406</v>
       </c>
       <c r="R45" s="2">
-        <v>56.01265822784811</v>
+        <v>54.49367088607596</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-0.95</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4883,19 +4883,19 @@
         <v>5.16</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3013338283281196</v>
+        <v>-0.3478599406175741</v>
       </c>
       <c r="G46" s="3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H46" s="3">
-        <v>43.29</v>
+        <v>45.02</v>
       </c>
       <c r="I46" s="3">
-        <v>1.56</v>
+        <v>3.33</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.013030900913801135</v>
+        <v>-0.011669984976052239</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4904,28 +4904,28 @@
         <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2523949599088542</v>
+        <v>-0.30077105985010033</v>
       </c>
       <c r="N46" s="3">
-        <v>-14.176971823688397</v>
+        <v>-19.19192249178634</v>
       </c>
       <c r="O46" s="3">
-        <v>12.658227848101266</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>44.55696202531645</v>
+        <v>45.31645569620254</v>
       </c>
       <c r="R46" s="3">
-        <v>25.696202531645568</v>
+        <v>24.177215189873415</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-5.7</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4945,19 +4945,19 @@
         <v>1.38</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.4150914673166066</v>
+        <v>-0.42838910562750215</v>
       </c>
       <c r="G47" s="3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H47" s="3">
-        <v>29.59</v>
+        <v>31.64</v>
       </c>
       <c r="I47" s="3">
-        <v>-21.33</v>
+        <v>-20.61</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030154678156920967</v>
+        <v>-0.030480465723502825</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4966,10 +4966,10 @@
         <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.3681501037307806</v>
+        <v>-0.38326226155867316</v>
       </c>
       <c r="N47" s="3">
-        <v>-25.75248620588105</v>
+        <v>-27.44104266264362</v>
       </c>
       <c r="O47" s="3">
         <v>2.5316455696202533</v>
@@ -4978,16 +4978,16 @@
         <v>31.304415950527737</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.35443037974684</v>
+        <v>38.607594936708864</v>
       </c>
       <c r="R47" s="3">
-        <v>25.06329113924051</v>
+        <v>24.9367088607595</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>-0.7</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5007,19 +5007,19 @@
         <v>0.6</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.1961864966707575</v>
+        <v>-0.18548651030220292</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>59.34</v>
+        <v>61.75</v>
       </c>
       <c r="I48" s="1">
-        <v>-3.3</v>
+        <v>-2.3</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.0012034373497541123</v>
+        <v>-0.0006663904737025214</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>0</v>
@@ -5028,28 +5028,28 @@
         <v>-65</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.19418899183731808</v>
+        <v>-0.18352447360355817</v>
       </c>
       <c r="N48" s="1">
-        <v>-8.35637501653479</v>
+        <v>-7.467263867132125</v>
       </c>
       <c r="O48" s="1">
-        <v>26.582278481012654</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>48.860759493670884</v>
+        <v>49.74683544303798</v>
       </c>
       <c r="R48" s="1">
-        <v>33.9873417721519</v>
+        <v>34.620253164556964</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>7.78</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5069,49 +5069,49 @@
         <v>-0.36</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.008396537236975032</v>
+        <v>0.013959692312439098</v>
       </c>
       <c r="G49" s="2">
         <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>55.55</v>
+        <v>60.92</v>
       </c>
       <c r="I49" s="2">
-        <v>40.57</v>
+        <v>44.58</v>
       </c>
       <c r="J49" s="2">
-        <v>0.021270426257997646</v>
+        <v>0.021973315229901976</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M49" s="2">
-        <v>0.05252736018292681</v>
+        <v>0.07380181162110366</v>
       </c>
       <c r="N49" s="2">
-        <v>16.315260185489695</v>
+        <v>18.26536465533405</v>
       </c>
       <c r="O49" s="2">
-        <v>62.0253164556962</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>63.41772151898734</v>
+        <v>64.68354430379748</v>
       </c>
       <c r="R49" s="2">
-        <v>53.924050632911396</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-1.39</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5131,34 +5131,34 @@
         <v>5.72</v>
       </c>
       <c r="F50" s="2">
-        <v>0.49598507803288117</v>
+        <v>0.4359576087806115</v>
       </c>
       <c r="G50" s="2">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="H50" s="2">
-        <v>62.9</v>
+        <v>62.87</v>
       </c>
       <c r="I50" s="2">
-        <v>127.24</v>
+        <v>124.93</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06570818455956147</v>
+        <v>0.06731672956555627</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M50" s="2">
-        <v>0.7766345071311174</v>
+        <v>0.7106427465908749</v>
       </c>
       <c r="N50" s="2">
-        <v>88.72597488030875</v>
+        <v>81.94945815231118</v>
       </c>
       <c r="O50" s="2">
-        <v>91.13924050632912</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P50" s="2">
         <v>31.61869931071345</v>
@@ -5167,13 +5167,13 @@
         <v>73.67088607594935</v>
       </c>
       <c r="R50" s="2">
-        <v>61.77215189873419</v>
+        <v>61.26582278481011</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-1.77</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5193,19 +5193,19 @@
         <v>4.31</v>
       </c>
       <c r="F51" s="2">
-        <v>0.11579355688641743</v>
+        <v>0.0656973192951211</v>
       </c>
       <c r="G51" s="2">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H51" s="2">
-        <v>49.75</v>
+        <v>48.39</v>
       </c>
       <c r="I51" s="2">
-        <v>57.64</v>
+        <v>55.24</v>
       </c>
       <c r="J51" s="2">
-        <v>0.021511233691275233</v>
+        <v>0.019165180803654598</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
@@ -5214,28 +5214,28 @@
         <v>248</v>
       </c>
       <c r="M51" s="2">
-        <v>0.22365881789214526</v>
+        <v>0.17066628267261463</v>
       </c>
       <c r="N51" s="2">
-        <v>33.428405956411545</v>
+        <v>27.951811760485167</v>
       </c>
       <c r="O51" s="2">
-        <v>81.0126582278481</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P51" s="2">
         <v>16.096535574030653</v>
       </c>
       <c r="Q51" s="2">
-        <v>62.15189873417721</v>
+        <v>60.75949367088607</v>
       </c>
       <c r="R51" s="2">
-        <v>58.67088607594937</v>
+        <v>56.265822784810126</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-4.37</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5255,19 +5255,19 @@
         <v>6.03</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.364557901977156</v>
+        <v>-0.35901040969479636</v>
       </c>
       <c r="G52" s="3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H52" s="3">
-        <v>50.05</v>
+        <v>49.19</v>
       </c>
       <c r="I52" s="3">
-        <v>-18.12</v>
+        <v>-18.79</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.04015899048815746</v>
+        <v>-0.03732890815529442</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
@@ -5276,10 +5276,10 @@
         <v>-1</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.3106252714742921</v>
+        <v>-0.305054400482066</v>
       </c>
       <c r="N52" s="3">
-        <v>-20.000002980232196</v>
+        <v>-19.620256554982905</v>
       </c>
       <c r="O52" s="3">
         <v>5.063291139240507</v>
@@ -5288,7 +5288,7 @@
         <v>45.32019556900826</v>
       </c>
       <c r="Q52" s="3">
-        <v>41.265822784810126</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="R52" s="3">
         <v>22.34177215189873</v>
@@ -5317,19 +5317,19 @@
         <v>37.01</v>
       </c>
       <c r="F53" s="1">
-        <v>0.1010039593108322</v>
+        <v>0.1186910887087767</v>
       </c>
       <c r="G53" s="1">
         <v>2.35</v>
       </c>
       <c r="H53" s="1">
-        <v>55.97</v>
+        <v>61.51</v>
       </c>
       <c r="I53" s="1">
-        <v>32.83</v>
+        <v>45.1</v>
       </c>
       <c r="J53" s="1">
-        <v>0.01565913053868878</v>
+        <v>0.01994816170035744</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
@@ -5338,28 +5338,28 @@
         <v>95</v>
       </c>
       <c r="M53" s="1">
-        <v>0.23583553556799197</v>
+        <v>0.2511285658672966</v>
       </c>
       <c r="N53" s="1">
-        <v>34.64607772399621</v>
+        <v>35.99804007995336</v>
       </c>
       <c r="O53" s="1">
-        <v>82.27848101265823</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>50.253164556962034</v>
+        <v>52.53164556962026</v>
       </c>
       <c r="R53" s="1">
-        <v>41.70886075949368</v>
+        <v>42.468354430379755</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>15.06</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5379,49 +5379,49 @@
         <v>-0.82</v>
       </c>
       <c r="F54" s="2">
-        <v>0.06585021912277064</v>
+        <v>0.12984801850782104</v>
       </c>
       <c r="G54" s="2">
         <v>1.84</v>
       </c>
       <c r="H54" s="2">
-        <v>63.61</v>
+        <v>68.77</v>
       </c>
       <c r="I54" s="2">
-        <v>61.97</v>
+        <v>70.15</v>
       </c>
       <c r="J54" s="2">
-        <v>0.03202917030148295</v>
+        <v>0.03438095878036791</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M54" s="2">
-        <v>0.14974542212722564</v>
+        <v>0.2122535598509001</v>
       </c>
       <c r="N54" s="2">
-        <v>26.037066379919594</v>
+        <v>32.11053947831372</v>
       </c>
       <c r="O54" s="2">
-        <v>74.68354430379746</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>68.1012658227848</v>
+        <v>68.73417721518987</v>
       </c>
       <c r="R54" s="2">
-        <v>56.64556962025316</v>
+        <v>58.797468354430386</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>-0.13</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5441,19 +5441,19 @@
         <v>6.07</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.07234659513805125</v>
+        <v>-0.025757463753413257</v>
       </c>
       <c r="G55" s="1">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="H55" s="1">
-        <v>57.35</v>
+        <v>62.18</v>
       </c>
       <c r="I55" s="1">
-        <v>-18.98</v>
+        <v>-13.92</v>
       </c>
       <c r="J55" s="1">
-        <v>0.01402616645189427</v>
+        <v>0.0171254337680704</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5462,28 +5462,28 @@
         <v>-16</v>
       </c>
       <c r="M55" s="1">
-        <v>0.08645503912038133</v>
+        <v>0.1292434354395211</v>
       </c>
       <c r="N55" s="1">
-        <v>19.708028079235163</v>
+        <v>23.809527037175812</v>
       </c>
       <c r="O55" s="1">
-        <v>65.82278481012658</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P55" s="1">
         <v>47.39629233644822</v>
       </c>
       <c r="Q55" s="1">
-        <v>45.56962025316456</v>
+        <v>47.721518987341774</v>
       </c>
       <c r="R55" s="1">
-        <v>37.84810126582278</v>
+        <v>39.24050632911393</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>2.72</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5503,19 +5503,19 @@
         <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>0.11953827030950842</v>
+        <v>0.14967699611604698</v>
       </c>
       <c r="G56" s="2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="H56" s="2">
-        <v>67.97</v>
+        <v>69.1</v>
       </c>
       <c r="I56" s="2">
-        <v>16.95</v>
+        <v>18.25</v>
       </c>
       <c r="J56" s="2">
-        <v>0.02643282429830356</v>
+        <v>0.029452125755517783</v>
       </c>
       <c r="K56" s="2" t="b">
         <v>0</v>
@@ -5524,28 +5524,28 @@
         <v>13</v>
       </c>
       <c r="M56" s="2">
-        <v>0.16348337664517532</v>
+        <v>0.19578485853419836</v>
       </c>
       <c r="N56" s="2">
-        <v>27.410861831714556</v>
+        <v>30.46366934664354</v>
       </c>
       <c r="O56" s="2">
-        <v>75.9493670886076</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q56" s="2">
-        <v>67.21518987341771</v>
+        <v>67.46835443037975</v>
       </c>
       <c r="R56" s="2">
-        <v>56.075949367088604</v>
+        <v>56.96202531645569</v>
       </c>
       <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T56" s="2">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5565,49 +5565,49 @@
         <v>-1.23</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.11730494517228027</v>
+        <v>-0.09394437438533337</v>
       </c>
       <c r="G57" s="1">
         <v>1.21</v>
       </c>
       <c r="H57" s="1">
-        <v>52.67</v>
+        <v>55.39</v>
       </c>
       <c r="I57" s="1">
-        <v>0.12</v>
+        <v>0.82</v>
       </c>
       <c r="J57" s="1">
-        <v>0.005999990509569193</v>
+        <v>0.007351543994161778</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.09633114442116653</v>
+        <v>-0.0733429890495636</v>
       </c>
       <c r="N57" s="1">
-        <v>1.429409725080361</v>
+        <v>3.5508845882673348</v>
       </c>
       <c r="O57" s="1">
-        <v>41.77215189873418</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>51.39240506329114</v>
+        <v>52.02531645569621</v>
       </c>
       <c r="R57" s="1">
-        <v>41.20253164556962</v>
+        <v>42.088607594936704</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>4.62</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5627,49 +5627,49 @@
         <v>1.28</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.08349595598191203</v>
+        <v>-0.10261026700599486</v>
       </c>
       <c r="G58" s="1">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H58" s="1">
-        <v>58.3</v>
+        <v>50.64</v>
       </c>
       <c r="I58" s="1">
-        <v>11.2</v>
+        <v>9.07</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.004897002451665471</v>
+        <v>-0.00488985150967395</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.15740363481916997</v>
+        <v>-0.17422460650652782</v>
       </c>
       <c r="N58" s="1">
-        <v>-4.677839314719978</v>
+        <v>-6.537277157429093</v>
       </c>
       <c r="O58" s="1">
-        <v>31.645569620253166</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P58" s="1">
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>49.74683544303798</v>
+        <v>46.58227848101265</v>
       </c>
       <c r="R58" s="1">
-        <v>37.025316455696206</v>
+        <v>36.392405063291136</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5683,25 +5683,25 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D59" s="2">
-        <v>2.3866855524079322</v>
+        <v>2.4079320113314453</v>
       </c>
       <c r="E59" s="2">
         <v>-1.3</v>
       </c>
       <c r="F59" s="2">
-        <v>0.5744733690140957</v>
+        <v>0.9372296258301339</v>
       </c>
       <c r="G59" s="2">
         <v>1.99</v>
       </c>
       <c r="H59" s="2">
-        <v>65.07</v>
+        <v>74.86</v>
       </c>
       <c r="I59" s="2">
-        <v>132.83</v>
+        <v>174.41</v>
       </c>
       <c r="J59" s="2">
-        <v>0.06739914545941446</v>
+        <v>0.07298465613947767</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
@@ -5710,28 +5710,28 @@
         <v>370</v>
       </c>
       <c r="M59" s="2">
-        <v>0.6733498582693462</v>
+        <v>1.0343504424130485</v>
       </c>
       <c r="N59" s="2">
-        <v>78.39750999413165</v>
+        <v>114.32022773452854</v>
       </c>
       <c r="O59" s="2">
-        <v>89.87341772151899</v>
+        <v>94.9367088607595</v>
       </c>
       <c r="P59" s="2">
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>79.62025316455697</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="R59" s="2">
-        <v>66.0126582278481</v>
+        <v>67.53164556962025</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T59" s="2">
-        <v>-1.33</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5745,55 +5745,55 @@
         <v>100</v>
       </c>
       <c r="D60" s="2">
-        <v>-1.4889277389277389</v>
+        <v>-1.487762237762238</v>
       </c>
       <c r="E60" s="2">
         <v>-0.04</v>
       </c>
       <c r="F60" s="2">
-        <v>0.1153393370630337</v>
+        <v>0.08834431504569398</v>
       </c>
       <c r="G60" s="2">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="H60" s="2">
-        <v>50.66</v>
+        <v>55.76</v>
       </c>
       <c r="I60" s="2">
-        <v>40.18</v>
+        <v>44.05</v>
       </c>
       <c r="J60" s="2">
-        <v>0.020545424539150047</v>
+        <v>0.021325035352015107</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M60" s="2">
-        <v>0.13831064264758686</v>
+        <v>0.10796468203214138</v>
       </c>
       <c r="N60" s="2">
-        <v>24.89358843195571</v>
+        <v>21.68165169643784</v>
       </c>
       <c r="O60" s="2">
-        <v>70.88607594936708</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P60" s="2">
         <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>58.48101265822784</v>
+        <v>60.12658227848101</v>
       </c>
       <c r="R60" s="2">
-        <v>54.17721518987342</v>
+        <v>53.29113924050634</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-2.41</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5813,19 +5813,19 @@
         <v>0.85</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.15415648458506717</v>
+        <v>-0.1887624565948784</v>
       </c>
       <c r="G61" s="3">
         <v>0.38</v>
       </c>
       <c r="H61" s="3">
-        <v>44.46</v>
+        <v>35.21</v>
       </c>
       <c r="I61" s="3">
-        <v>-0.05</v>
+        <v>-3.31</v>
       </c>
       <c r="J61" s="3">
-        <v>-0.006782224340803354</v>
+        <v>-0.007285711481955117</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
@@ -5834,28 +5834,28 @@
         <v>102</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.2160791344216887</v>
+        <v>-0.2495855942528653</v>
       </c>
       <c r="N61" s="3">
-        <v>-10.545389274971852</v>
+        <v>-14.073375932062834</v>
       </c>
       <c r="O61" s="3">
-        <v>20.253164556962027</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P61" s="3">
-        <v>12.798408482128673</v>
+        <v>14.552180197083512</v>
       </c>
       <c r="Q61" s="3">
-        <v>38.607594936708864</v>
+        <v>34.936708860759495</v>
       </c>
       <c r="R61" s="3">
-        <v>29.050632911392405</v>
+        <v>26.26582278481013</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>95</v>
       </c>
       <c r="T61" s="3">
-        <v>0.25</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5875,49 +5875,49 @@
         <v>-0.19</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.2865787997014262</v>
+        <v>-0.2820391521563683</v>
       </c>
       <c r="G62" s="1">
         <v>0.94</v>
       </c>
       <c r="H62" s="1">
-        <v>32.92</v>
+        <v>32.91</v>
       </c>
       <c r="I62" s="1">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.0075198154678723875</v>
+        <v>-0.00832271834079009</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L62" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.2925713142017444</v>
+        <v>-0.2879252622523025</v>
       </c>
       <c r="N62" s="1">
-        <v>-18.194607252977427</v>
+        <v>-17.907342732006565</v>
       </c>
       <c r="O62" s="1">
-        <v>7.59493670886076</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P62" s="1">
-        <v>20.127091395469936</v>
+        <v>20.131624188012864</v>
       </c>
       <c r="Q62" s="1">
-        <v>47.721518987341774</v>
+        <v>45.69620253164557</v>
       </c>
       <c r="R62" s="1">
-        <v>32.088607594936704</v>
+        <v>31.962025316455687</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-10.76</v>
+        <v>-10.89</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5937,49 +5937,49 @@
         <v>-3.33</v>
       </c>
       <c r="F63" s="4">
-        <v>0.7264742148129504</v>
+        <v>1.012694963215004</v>
       </c>
       <c r="G63" s="4">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="H63" s="4">
-        <v>63.95</v>
+        <v>68.34</v>
       </c>
       <c r="I63" s="4">
-        <v>223.89</v>
+        <v>242.37</v>
       </c>
       <c r="J63" s="4">
-        <v>0.08932039391139888</v>
+        <v>0.09039172227078207</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
       </c>
       <c r="L63" s="4">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M63" s="4">
-        <v>1.1079976379998766</v>
+        <v>1.3805768442108926</v>
       </c>
       <c r="N63" s="4">
-        <v>121.86228796718466</v>
+        <v>148.94286791431298</v>
       </c>
       <c r="O63" s="4">
-        <v>96.20253164556962</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.27848101265822</v>
+        <v>82.40506329113924</v>
       </c>
       <c r="R63" s="4">
-        <v>71.26582278481013</v>
+        <v>71.51898734177216</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>-1.08</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5999,31 +5999,31 @@
         <v>-1.41</v>
       </c>
       <c r="F64" s="2">
-        <v>0.7814222398790698</v>
+        <v>0.9257530736547384</v>
       </c>
       <c r="G64" s="2">
         <v>2.03</v>
       </c>
       <c r="H64" s="2">
-        <v>68.48</v>
+        <v>71.68</v>
       </c>
       <c r="I64" s="2">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="J64" s="2">
-        <v>0.07327680547531976</v>
+        <v>0.07494203297919609</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M64" s="2">
-        <v>0.8842937388011991</v>
+        <v>1.0267979636349425</v>
       </c>
       <c r="N64" s="2">
-        <v>99.49189804731692</v>
+        <v>113.56497985671797</v>
       </c>
       <c r="O64" s="2">
         <v>93.67088607594937</v>
@@ -6035,13 +6035,13 @@
         <v>77.59493670886076</v>
       </c>
       <c r="R64" s="2">
-        <v>67.02531645569621</v>
+        <v>67.15189873417722</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T64" s="2">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6061,49 +6061,49 @@
         <v>0.14</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.13736341096253218</v>
+        <v>-0.1458367488545128</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>48.09</v>
+        <v>49.27</v>
       </c>
       <c r="I65" s="1">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.009798847532780089</v>
+        <v>-0.010406491238242494</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L65" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.20727608013291132</v>
+        <v>-0.21450803330707868</v>
       </c>
       <c r="N65" s="1">
-        <v>-9.665083846094111</v>
+        <v>-10.565619837484173</v>
       </c>
       <c r="O65" s="1">
-        <v>22.78481012658228</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>43.54430379746836</v>
+        <v>42.784810126582286</v>
       </c>
       <c r="R65" s="1">
-        <v>33.29113924050633</v>
+        <v>31.645569620253163</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-4.11</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6117,25 +6117,25 @@
         <v>87.34177215189874</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.12356147789218659</v>
+        <v>-0.11387038158691706</v>
       </c>
       <c r="E66" s="3">
         <v>1.66</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.2197919368880013</v>
+        <v>-0.25941380854434726</v>
       </c>
       <c r="G66" s="3">
         <v>0.99</v>
       </c>
       <c r="H66" s="3">
-        <v>33.05</v>
+        <v>30.56</v>
       </c>
       <c r="I66" s="3">
-        <v>-42.77</v>
+        <v>-45.34</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.02284698017530048</v>
+        <v>-0.025741113849072836</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>1</v>
@@ -6144,28 +6144,28 @@
         <v>-194</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.220790689304721</v>
+        <v>-0.26039482689366966</v>
       </c>
       <c r="N66" s="3">
-        <v>-11.016544763275084</v>
+        <v>-15.15429919614327</v>
       </c>
       <c r="O66" s="3">
-        <v>16.455696202531644</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P66" s="3">
-        <v>54.61236968964586</v>
+        <v>54.854261650729526</v>
       </c>
       <c r="Q66" s="3">
-        <v>33.037974683544306</v>
+        <v>32.27848101265823</v>
       </c>
       <c r="R66" s="3">
-        <v>21.645569620253163</v>
+        <v>19.873417721518983</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="3">
-        <v>-7.41</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6185,49 +6185,49 @@
         <v>-0.68</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.11005225112505734</v>
+        <v>-0.1402380189076255</v>
       </c>
       <c r="G67" s="1">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H67" s="1">
-        <v>40.18</v>
+        <v>35.91</v>
       </c>
       <c r="I67" s="1">
-        <v>-14.6</v>
+        <v>-16.51</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.00001886392709427514</v>
+        <v>-0.000870451920174501</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-77</v>
+        <v>-76</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.09507096487426181</v>
+        <v>-0.12650376201711233</v>
       </c>
       <c r="N67" s="1">
-        <v>1.5554276797708422</v>
+        <v>-1.765192708487536</v>
       </c>
       <c r="O67" s="1">
-        <v>43.037974683544306</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>46.45569620253164</v>
+        <v>45.31645569620254</v>
       </c>
       <c r="R67" s="1">
-        <v>41.45569620253165</v>
+        <v>40.69620253164557</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-2.66</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6247,19 +6247,19 @@
         <v>-0.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.14695918703431088</v>
+        <v>-0.13733929043426288</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>52.76</v>
+        <v>51.13</v>
       </c>
       <c r="I68" s="1">
-        <v>4.71</v>
+        <v>4.12</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.010864152352817177</v>
+        <v>-0.010449013617032257</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6268,28 +6268,28 @@
         <v>147</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.2138755989545309</v>
+        <v>-0.20306751983886162</v>
       </c>
       <c r="N68" s="1">
-        <v>-10.325035728256072</v>
+        <v>-9.421568490662466</v>
       </c>
       <c r="O68" s="1">
-        <v>21.518987341772153</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P68" s="1">
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>62.9113924050633</v>
+        <v>61.64556962025317</v>
       </c>
       <c r="R68" s="1">
-        <v>46.64556962025317</v>
+        <v>46.77215189873418</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6309,19 +6309,19 @@
         <v>-0.24</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.2692979026745278</v>
+        <v>-0.27307082850125447</v>
       </c>
       <c r="G69" s="3">
         <v>1.49</v>
       </c>
       <c r="H69" s="3">
-        <v>44.5</v>
+        <v>43.82</v>
       </c>
       <c r="I69" s="3">
-        <v>-11.67</v>
+        <v>-11.93</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.010079876768963403</v>
+        <v>-0.009464380736295156</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
@@ -6330,10 +6330,10 @@
         <v>-68</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.22035903425526238</v>
+        <v>-0.22500092938445837</v>
       </c>
       <c r="N69" s="3">
-        <v>-10.973379258329217</v>
+        <v>-11.614909445222144</v>
       </c>
       <c r="O69" s="3">
         <v>17.72151898734177</v>
@@ -6342,16 +6342,16 @@
         <v>29.145649851223904</v>
       </c>
       <c r="Q69" s="3">
-        <v>40.379746835443036</v>
+        <v>39.24050632911393</v>
       </c>
       <c r="R69" s="3">
-        <v>27.21518987341772</v>
+        <v>27.08860759493671</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.51</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6371,19 +6371,19 @@
         <v>-1.55</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.22962194848149697</v>
+        <v>-0.2258778303740458</v>
       </c>
       <c r="G70" s="3">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H70" s="3">
-        <v>39.8</v>
+        <v>39.75</v>
       </c>
       <c r="I70" s="3">
-        <v>-14.88</v>
+        <v>-14.89</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.010093204836148496</v>
+        <v>-0.008305606873988663</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
@@ -6392,28 +6392,28 @@
         <v>-58</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.2426057298988531</v>
+        <v>-0.23961208726455896</v>
       </c>
       <c r="N70" s="3">
-        <v>-13.198048822688285</v>
+        <v>-13.0760252332322</v>
       </c>
       <c r="O70" s="3">
-        <v>13.924050632911392</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>38.860759493670884</v>
+        <v>39.36708860759494</v>
       </c>
       <c r="R70" s="3">
-        <v>26.075949367088608</v>
+        <v>26.9620253164557</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>-1.65</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6433,31 +6433,31 @@
         <v>-0.71</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.4145741625586808</v>
+        <v>-0.41942260100356543</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>51.49</v>
+        <v>53.19</v>
       </c>
       <c r="I71" s="3">
-        <v>-27.5</v>
+        <v>-26.89</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.025720975933946837</v>
+        <v>-0.023595020204156474</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L71" s="3">
-        <v>-100</v>
+        <v>-99</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.4025891335580444</v>
+        <v>-0.407650380811697</v>
       </c>
       <c r="N71" s="3">
-        <v>-29.196389188607423</v>
+        <v>-29.87985458794601</v>
       </c>
       <c r="O71" s="3">
         <v>1.2658227848101267</v>
@@ -6466,16 +6466,16 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>40.506329113924046</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="R71" s="3">
-        <v>22.40506329113924</v>
+        <v>22.658227848101266</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T71" s="3">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -6495,19 +6495,19 @@
         <v>-0.66</v>
       </c>
       <c r="F72" s="3">
-        <v>-0.27611628322265297</v>
+        <v>-0.2692151307705016</v>
       </c>
       <c r="G72" s="3">
         <v>1.14</v>
       </c>
       <c r="H72" s="3">
-        <v>44.14</v>
+        <v>46.22</v>
       </c>
       <c r="I72" s="3">
-        <v>-9.02</v>
+        <v>-8.33</v>
       </c>
       <c r="J72" s="3">
-        <v>-0.006577030997239965</v>
+        <v>-0.005435025521056235</v>
       </c>
       <c r="K72" s="3" t="b">
         <v>0</v>
@@ -6516,28 +6516,28 @@
         <v>2</v>
       </c>
       <c r="M72" s="3">
-        <v>-0.26213374938857714</v>
+        <v>-0.2554808738799884</v>
       </c>
       <c r="N72" s="3">
-        <v>-15.150850771660698</v>
+        <v>-14.662903894775145</v>
       </c>
       <c r="O72" s="3">
-        <v>10.126582278481013</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P72" s="3">
         <v>19.739671794345924</v>
       </c>
       <c r="Q72" s="3">
-        <v>43.164556962025316</v>
+        <v>43.54430379746835</v>
       </c>
       <c r="R72" s="3">
-        <v>29.303797468354432</v>
+        <v>29.81012658227848</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
       <c r="T72" s="3">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6557,49 +6557,49 @@
         <v>3.07</v>
       </c>
       <c r="F73" s="2">
-        <v>0.4109958961986542</v>
+        <v>0.430098566861153</v>
       </c>
       <c r="G73" s="2">
         <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>68.1</v>
+        <v>70.29</v>
       </c>
       <c r="I73" s="2">
-        <v>46.26</v>
+        <v>47.83</v>
       </c>
       <c r="J73" s="2">
-        <v>0.031508908728787234</v>
+        <v>0.03206985463415866</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L73" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M73" s="2">
-        <v>0.42897343969960877</v>
+        <v>0.4477568971489556</v>
       </c>
       <c r="N73" s="2">
-        <v>53.9598681371579</v>
+        <v>55.660873208119256</v>
       </c>
       <c r="O73" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.34177215189874</v>
+        <v>67.72151898734177</v>
       </c>
       <c r="R73" s="2">
-        <v>62.025316455696206</v>
+        <v>62.53164556962025</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6619,7 +6619,7 @@
         <v>1.29</v>
       </c>
       <c r="F74" s="2">
-        <v>0.1555944457098428</v>
+        <v>0.17690607815481968</v>
       </c>
       <c r="G74" s="2">
         <v>0.79</v>
@@ -6628,10 +6628,10 @@
         <v>80.86</v>
       </c>
       <c r="I74" s="2">
-        <v>30.31</v>
+        <v>30</v>
       </c>
       <c r="J74" s="2">
-        <v>0.015382182508375218</v>
+        <v>0.014981395306821884</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>1</v>
@@ -6640,28 +6640,28 @@
         <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.13462064495872905</v>
+        <v>0.1563046928190499</v>
       </c>
       <c r="N74" s="2">
-        <v>24.52458866306993</v>
+        <v>26.515652775128686</v>
       </c>
       <c r="O74" s="2">
-        <v>69.62025316455697</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>64.68354430379748</v>
+        <v>63.797468354430386</v>
       </c>
       <c r="R74" s="2">
-        <v>55.50632911392406</v>
+        <v>55.88607594936709</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>-0.82</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6681,19 +6681,19 @@
         <v>-0.35</v>
       </c>
       <c r="F75" s="1">
-        <v>0.014969557179746504</v>
+        <v>-0.0075277886482870565</v>
       </c>
       <c r="G75" s="1">
         <v>0.97</v>
       </c>
       <c r="H75" s="1">
-        <v>61.87</v>
+        <v>60.1</v>
       </c>
       <c r="I75" s="1">
-        <v>17.13</v>
+        <v>16.11</v>
       </c>
       <c r="J75" s="1">
-        <v>0.014394612010311373</v>
+        <v>0.0184885903071271</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6702,28 +6702,28 @@
         <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>0.0119732999295874</v>
+        <v>-0.010470843696254173</v>
       </c>
       <c r="N75" s="1">
-        <v>12.259854160155758</v>
+        <v>9.838099123598278</v>
       </c>
       <c r="O75" s="1">
-        <v>55.69620253164557</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>61.392405063291136</v>
+        <v>60.88607594936708</v>
       </c>
       <c r="R75" s="1">
-        <v>44.05063291139241</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>-2.41</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6743,19 +6743,19 @@
         <v>0.91</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.0036616319166906663</v>
+        <v>-0.004645609480755375</v>
       </c>
       <c r="G76" s="1">
         <v>0.7</v>
       </c>
       <c r="H76" s="1">
-        <v>40.8</v>
+        <v>43.47</v>
       </c>
       <c r="I76" s="1">
-        <v>5.46</v>
+        <v>6.76</v>
       </c>
       <c r="J76" s="1">
-        <v>0.01117333763661347</v>
+        <v>0.010323245621496727</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6764,13 +6764,13 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.03362420441828173</v>
+        <v>-0.034076159960426455</v>
       </c>
       <c r="N76" s="1">
-        <v>7.700103725368848</v>
+        <v>7.477567497181051</v>
       </c>
       <c r="O76" s="1">
-        <v>50.63291139240506</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
@@ -6779,13 +6779,13 @@
         <v>44.43037974683544</v>
       </c>
       <c r="R76" s="1">
-        <v>40</v>
+        <v>40.253164556962034</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>-2.22</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6805,49 +6805,49 @@
         <v>2.54</v>
       </c>
       <c r="F77" s="2">
-        <v>0.03724172057863512</v>
+        <v>0.0658963128082876</v>
       </c>
       <c r="G77" s="2">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="H77" s="2">
-        <v>65.19</v>
+        <v>69.39</v>
       </c>
       <c r="I77" s="2">
-        <v>13.72</v>
+        <v>16.17</v>
       </c>
       <c r="J77" s="2">
-        <v>0.013142398547700614</v>
+        <v>0.01502370831594207</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L77" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M77" s="2">
-        <v>0.03624296816191541</v>
+        <v>0.06393427610964286</v>
       </c>
       <c r="N77" s="2">
-        <v>14.68682098338856</v>
+        <v>17.27861110418799</v>
       </c>
       <c r="O77" s="2">
-        <v>59.49367088607595</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>63.67088607594937</v>
+        <v>65.0632911392405</v>
       </c>
       <c r="R77" s="2">
-        <v>54.49367088607595</v>
+        <v>55.379746835443036</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>0.06</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6867,49 +6867,49 @@
         <v>0.76</v>
       </c>
       <c r="F78" s="1">
-        <v>0.08157686103270348</v>
+        <v>0.10534970344951694</v>
       </c>
       <c r="G78" s="1">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H78" s="1">
-        <v>57.31</v>
+        <v>60.72</v>
       </c>
       <c r="I78" s="1">
-        <v>28.16</v>
+        <v>29.59</v>
       </c>
       <c r="J78" s="1">
-        <v>0.02435973156182326</v>
+        <v>0.023533739794426568</v>
       </c>
       <c r="K78" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M78" s="1">
-        <v>0.10654567145069604</v>
+        <v>0.12889414383325382</v>
       </c>
       <c r="N78" s="1">
-        <v>21.71709131226662</v>
+        <v>23.77459787654908</v>
       </c>
       <c r="O78" s="1">
-        <v>67.08860759493672</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P78" s="1">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="1">
-        <v>57.84810126582278</v>
+        <v>57.72151898734178</v>
       </c>
       <c r="R78" s="1">
-        <v>48.037974683544306</v>
+        <v>48.41772151898734</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="1">
-        <v>-1.65</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6923,25 +6923,25 @@
         <v>50.63291139240506</v>
       </c>
       <c r="D79" s="2">
-        <v>2.775244299674267</v>
+        <v>2.804560260586319</v>
       </c>
       <c r="E79" s="2">
         <v>0.81</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4422507426652984</v>
+        <v>0.4084245033935695</v>
       </c>
       <c r="G79" s="2">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H79" s="2">
-        <v>80.85</v>
+        <v>75.76</v>
       </c>
       <c r="I79" s="2">
-        <v>54.6</v>
+        <v>51.46</v>
       </c>
       <c r="J79" s="2">
-        <v>0.046283989519480505</v>
+        <v>0.0457991158639314</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6950,28 +6950,28 @@
         <v>80</v>
       </c>
       <c r="M79" s="2">
-        <v>0.4382557329984196</v>
+        <v>0.4054814483456024</v>
       </c>
       <c r="N79" s="2">
-        <v>54.88809746703899</v>
+        <v>51.43332832778395</v>
       </c>
       <c r="O79" s="2">
-        <v>88.60759493670885</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>66.07594936708861</v>
+        <v>65.44303797468353</v>
       </c>
       <c r="R79" s="2">
-        <v>59.24050632911393</v>
+        <v>58.734177215189874</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6985,55 +6985,55 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.8268348623853209</v>
+        <v>0.7889908256880732</v>
       </c>
       <c r="E80" s="2">
         <v>-1.21</v>
       </c>
       <c r="F80" s="2">
-        <v>1.3660493645956988</v>
+        <v>1.4322648073628779</v>
       </c>
       <c r="G80" s="2">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="H80" s="2">
-        <v>76.45</v>
+        <v>78.16</v>
       </c>
       <c r="I80" s="2">
-        <v>96.44</v>
+        <v>101.87</v>
       </c>
       <c r="J80" s="2">
-        <v>0.05565914536366011</v>
+        <v>0.06156727370708342</v>
       </c>
       <c r="K80" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2">
         <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>1.3670481170124185</v>
+        <v>1.438150917458812</v>
       </c>
       <c r="N80" s="2">
-        <v>147.76733586843886</v>
+        <v>154.7002752391049</v>
       </c>
       <c r="O80" s="2">
         <v>98.73417721518987</v>
       </c>
       <c r="P80" s="2">
-        <v>14.059118714058641</v>
+        <v>13.172294180200911</v>
       </c>
       <c r="Q80" s="2">
-        <v>71.77215189873418</v>
+        <v>71.89873417721519</v>
       </c>
       <c r="R80" s="2">
-        <v>66.39240506329115</v>
+        <v>66.7721518987342</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
     </row>
   </sheetData>
@@ -7060,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>33.79746835443038</v>
+        <v>33.037974683544306</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7068,7 +7068,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65.37974683544304</v>
+        <v>64.87341772151899</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26.898734177215193</v>
+        <v>27.53164556962025</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>44.11392405063292</v>
+        <v>44.620253164556964</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>42.151898734177216</v>
+        <v>40.50632911392405</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.468354430379755</v>
+        <v>52.21518987341773</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7108,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>55.31645569620253</v>
+        <v>54.936708860759495</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>38.92405063291139</v>
+        <v>40.37974683544304</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>36.265822784810126</v>
+        <v>37.27848101265823</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>53.29113924050633</v>
+        <v>53.16455696202532</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7140,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>39.74683544303798</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7148,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4.620253164556961</v>
+        <v>3.4810126582278462</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7172,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.265822784810123</v>
+        <v>24.746835443037973</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18.481012658227847</v>
+        <v>18.607594936708864</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>29.936708860759495</v>
+        <v>30.063291139240512</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7196,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>40.31645569620253</v>
+        <v>41.58227848101266</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>40.06329113924051</v>
+        <v>41.962025316455694</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7212,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>54.43037974683544</v>
+        <v>54.050632911392405</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30.31645569620253</v>
+        <v>33.60759493670886</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34.36708860759494</v>
+        <v>34.24050632911393</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7236,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>26.835443037974688</v>
+        <v>26.075949367088608</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7244,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.531645569620256</v>
+        <v>3.9240506329113938</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7252,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>34.68354430379747</v>
+        <v>33.924050632911396</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>26.9620253164557</v>
+        <v>28.9873417721519</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21.32911392405063</v>
+        <v>20.44303797468354</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7276,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>25.949367088607595</v>
+        <v>26.708860759493668</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7284,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>45.25316455696203</v>
+        <v>46.0126582278481</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>58.0379746835443</v>
+        <v>59.55696202531646</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>20.44303797468354</v>
+        <v>21.582278481012658</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7308,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>42.025316455696206</v>
+        <v>41.26582278481012</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7316,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>48.48101265822785</v>
+        <v>49.24050632911393</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>33.544303797468345</v>
+        <v>33.67088607594937</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7340,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>31.962025316455698</v>
+        <v>29.683544303797472</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>56.075949367088604</v>
+        <v>55.696202531645575</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7356,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>44.050632911392405</v>
+        <v>41.835443037974684</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7364,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>31.20253164556962</v>
+        <v>30.69620253164556</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7372,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>33.41772151898735</v>
+        <v>32.53164556962026</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.10126582278481</v>
+        <v>38.734177215189874</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>48.22784810126582</v>
+        <v>46.58227848101265</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7396,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>26.89873417721519</v>
+        <v>28.417721518987342</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7404,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>56.01265822784811</v>
+        <v>54.49367088607596</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.696202531645568</v>
+        <v>24.177215189873415</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>25.06329113924051</v>
+        <v>24.9367088607595</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7428,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>33.9873417721519</v>
+        <v>34.620253164556964</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>53.924050632911396</v>
+        <v>54.43037974683544</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7444,7 +7444,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>61.77215189873419</v>
+        <v>61.26582278481011</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7452,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>58.67088607594937</v>
+        <v>56.265822784810126</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>41.70886075949368</v>
+        <v>42.468354430379755</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7476,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>56.64556962025316</v>
+        <v>58.797468354430386</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>37.84810126582278</v>
+        <v>39.24050632911393</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7492,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>56.075949367088604</v>
+        <v>56.96202531645569</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7500,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>41.20253164556962</v>
+        <v>42.088607594936704</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>37.025316455696206</v>
+        <v>36.392405063291136</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>66.0126582278481</v>
+        <v>67.53164556962025</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7524,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>54.17721518987342</v>
+        <v>53.29113924050634</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7532,7 +7532,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>29.050632911392405</v>
+        <v>26.26582278481013</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7540,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>32.088607594936704</v>
+        <v>31.962025316455687</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7548,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>71.26582278481013</v>
+        <v>71.51898734177216</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7556,7 +7556,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>67.02531645569621</v>
+        <v>67.15189873417722</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>33.29113924050633</v>
+        <v>31.645569620253163</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>21.645569620253163</v>
+        <v>19.873417721518983</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7580,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>41.45569620253165</v>
+        <v>40.69620253164557</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7588,7 +7588,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>46.64556962025317</v>
+        <v>46.77215189873418</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7596,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.21518987341772</v>
+        <v>27.08860759493671</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7604,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>26.075949367088608</v>
+        <v>26.9620253164557</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7612,7 +7612,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>22.40506329113924</v>
+        <v>22.658227848101266</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7620,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>29.303797468354432</v>
+        <v>29.81012658227848</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7628,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.025316455696206</v>
+        <v>62.53164556962025</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7636,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>55.50632911392406</v>
+        <v>55.88607594936709</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7644,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>44.05063291139241</v>
+        <v>43.67088607594937</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>40</v>
+        <v>40.253164556962034</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7660,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>54.49367088607595</v>
+        <v>55.379746835443036</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>48.037974683544306</v>
+        <v>48.41772151898734</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7676,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>59.24050632911393</v>
+        <v>58.734177215189874</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7684,7 +7684,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>66.39240506329115</v>
+        <v>66.7721518987342</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="229">
   <si>
     <t>Ticker</t>
   </si>
@@ -352,7 +352,7 @@
     <t>2026-06-03</t>
   </si>
   <si>
-    <t>2026-04-27</t>
+    <t>2027-04-27</t>
   </si>
   <si>
     <t>2026-05-14</t>
@@ -409,9 +409,6 @@
     <t>_date_</t>
   </si>
   <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -676,34 +673,40 @@
     <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Earnings Upcoming, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader</t>
-  </si>
-  <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Earnings Upcoming, Institutional Buying</t>
+    <t>Momentum Breakout, Earnings Upcoming, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
   </si>
   <si>
     <t>Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike</t>
   </si>
 </sst>
 </file>
@@ -1358,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" t="s">
         <v>212</v>
-      </c>
-      <c r="C1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,10 +1372,10 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>71.51898734177216</v>
+        <v>71.7721518987342</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1380,10 +1383,10 @@
         <v>58</v>
       </c>
       <c r="B3">
-        <v>67.53164556962025</v>
+        <v>67.65822784810126</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1391,10 +1394,10 @@
         <v>63</v>
       </c>
       <c r="B4">
-        <v>67.15189873417722</v>
+        <v>67.0253164556962</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1402,10 +1405,10 @@
         <v>127</v>
       </c>
       <c r="B5">
-        <v>66.7721518987342</v>
+        <v>66.26582278481013</v>
       </c>
       <c r="C5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1413,32 +1416,32 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>64.87341772151899</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="B7">
-        <v>62.53164556962025</v>
+        <v>62.27848101265822</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B8">
-        <v>62.27848101265822</v>
+        <v>62.151898734177216</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1446,10 +1449,10 @@
         <v>49</v>
       </c>
       <c r="B9">
-        <v>61.26582278481011</v>
+        <v>61.39240506329113</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,37 +1463,37 @@
         <v>59.55696202531646</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="B11">
-        <v>58.797468354430386</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="B12">
-        <v>58.734177215189874</v>
+        <v>58.037974683544306</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="B13">
-        <v>56.96202531645569</v>
+        <v>56.8987341772152</v>
       </c>
       <c r="C13" t="s">
         <v>219</v>
@@ -1498,10 +1501,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>56.265822784810126</v>
+        <v>56.39240506329115</v>
       </c>
       <c r="C14" t="s">
         <v>218</v>
@@ -1509,10 +1512,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B15">
-        <v>55.88607594936709</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="C15" t="s">
         <v>220</v>
@@ -1520,10 +1523,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>55.696202531645575</v>
+        <v>56.20253164556962</v>
       </c>
       <c r="C16" t="s">
         <v>221</v>
@@ -1531,10 +1534,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="B17">
-        <v>55.379746835443036</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="C17" t="s">
         <v>222</v>
@@ -1542,10 +1545,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>54.936708860759495</v>
+        <v>55.44303797468355</v>
       </c>
       <c r="C18" t="s">
         <v>223</v>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B19">
-        <v>54.49367088607596</v>
+        <v>54.87341772151899</v>
       </c>
       <c r="C19" t="s">
         <v>218</v>
@@ -1564,7 +1567,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>54.43037974683544</v>
@@ -1575,24 +1578,24 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B21">
-        <v>54.050632911392405</v>
+        <v>53.29113924050634</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B22">
-        <v>53.29113924050634</v>
+        <v>53.291139240506325</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1600,10 +1603,10 @@
         <v>10</v>
       </c>
       <c r="B23">
-        <v>53.16455696202532</v>
+        <v>52.78481012658228</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1611,7 +1614,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>49.24050632911393</v>
+        <v>50.25316455696202</v>
       </c>
       <c r="C24" t="s">
         <v>218</v>
@@ -1619,24 +1622,24 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="B25">
-        <v>48.67088607594937</v>
+        <v>49.683544303797476</v>
       </c>
       <c r="C25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>48.41772151898734</v>
+        <v>48.54430379746835</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1647,51 +1650,51 @@
         <v>46.77215189873418</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B28">
-        <v>46.58227848101265</v>
+        <v>46.64556962025316</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B29">
-        <v>46.0126582278481</v>
+        <v>44.24050632911393</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="B30">
         <v>43.67088607594937</v>
       </c>
       <c r="C30" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="B31">
-        <v>42.468354430379755</v>
+        <v>43.607594936708864</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1699,40 +1702,40 @@
         <v>19</v>
       </c>
       <c r="B32">
-        <v>41.962025316455694</v>
+        <v>43.48101265822784</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="B33">
-        <v>41.835443037974684</v>
+        <v>42.911392405063296</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B34">
-        <v>41.58227848101266</v>
+        <v>42.84810126582279</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B35">
-        <v>41.26582278481012</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C35" t="s">
         <v>224</v>
@@ -1740,76 +1743,76 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="B36">
-        <v>40.50632911392405</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="B37">
-        <v>40.253164556962034</v>
+        <v>40.50632911392404</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B38">
-        <v>38.734177215189874</v>
+        <v>38.9873417721519</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B39">
-        <v>38.734177215189874</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>36.392405063291136</v>
+        <v>36.70886075949366</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>34.24050632911393</v>
+        <v>35.63291139240506</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B42">
-        <v>33.924050632911396</v>
+        <v>35.00000000000001</v>
       </c>
       <c r="C42" t="s">
         <v>221</v>
@@ -1820,21 +1823,21 @@
         <v>21</v>
       </c>
       <c r="B43">
-        <v>33.60759493670886</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B44">
-        <v>33.037974683544306</v>
+        <v>34.05063291139241</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1842,10 +1845,10 @@
         <v>40</v>
       </c>
       <c r="B45">
-        <v>32.53164556962026</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1853,54 +1856,54 @@
         <v>61</v>
       </c>
       <c r="B46">
-        <v>31.962025316455687</v>
+        <v>33.101265822784804</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B47">
-        <v>31.645569620253163</v>
+        <v>32.40506329113924</v>
       </c>
       <c r="C47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B48">
-        <v>30.69620253164556</v>
+        <v>32.025316455696206</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B49">
-        <v>30.063291139240512</v>
+        <v>30.569620253164558</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B50">
-        <v>29.81012658227848</v>
+        <v>30.189873417721518</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1908,10 +1911,10 @@
         <v>26</v>
       </c>
       <c r="B51">
-        <v>28.9873417721519</v>
+        <v>30.126582278481024</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2149,37 +2152,37 @@
         <v>63.29113924050633</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.630691399662732</v>
+        <v>-1.7858347386172007</v>
       </c>
       <c r="E2" s="1">
         <v>0.98</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.024723464469771136</v>
+        <v>-0.03374324803579983</v>
       </c>
       <c r="G2" s="1">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="1">
-        <v>44.29</v>
+        <v>41.87</v>
       </c>
       <c r="I2" s="1">
-        <v>14.08</v>
+        <v>12.45</v>
       </c>
       <c r="J2" s="1">
-        <v>0.002455727619990929</v>
+        <v>-0.0003076157793132085</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.10516696911420542</v>
+        <v>-0.10800931511574874</v>
       </c>
       <c r="N2" s="1">
-        <v>0.3684865818031522</v>
+        <v>-0.778212586279824</v>
       </c>
       <c r="O2" s="1">
         <v>43.037974683544306</v>
@@ -2188,16 +2191,16 @@
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>38.73417721518988</v>
+        <v>37.08860759493671</v>
       </c>
       <c r="R2" s="1">
-        <v>33.037974683544306</v>
+        <v>32.40506329113924</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>0.19</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2217,31 +2220,31 @@
         <v>-0.5</v>
       </c>
       <c r="F3" s="2">
-        <v>1.1062695852316171</v>
+        <v>1.1174367115544217</v>
       </c>
       <c r="G3" s="2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H3" s="2">
-        <v>77.07</v>
+        <v>74.08</v>
       </c>
       <c r="I3" s="2">
-        <v>116.7</v>
+        <v>111.64</v>
       </c>
       <c r="J3" s="2">
-        <v>0.09026237558486737</v>
+        <v>0.0950199165121971</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M3" s="2">
-        <v>1.2475362275340383</v>
+        <v>1.2498629516487885</v>
       </c>
       <c r="N3" s="2">
-        <v>135.63880624662755</v>
+        <v>135.0090140901739</v>
       </c>
       <c r="O3" s="2">
         <v>96.20253164556962</v>
@@ -2250,16 +2253,16 @@
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.94936708860759</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="R3" s="2">
-        <v>64.87341772151899</v>
+        <v>65</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -2279,49 +2282,49 @@
         <v>-1.02</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.018910370905183854</v>
+        <v>-0.07789445316232181</v>
       </c>
       <c r="G4" s="3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H4" s="3">
-        <v>69.36</v>
+        <v>66.47</v>
       </c>
       <c r="I4" s="3">
-        <v>-12.33</v>
+        <v>-13.45</v>
       </c>
       <c r="J4" s="3">
-        <v>-0.005412846431288901</v>
+        <v>-0.0035796515034801826</v>
       </c>
       <c r="K4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="M4" s="3">
-        <v>-0.0061571323639930675</v>
+        <v>-0.06447287477437924</v>
       </c>
       <c r="N4" s="3">
-        <v>10.269470256824391</v>
+        <v>3.5754314478571194</v>
       </c>
       <c r="O4" s="3">
-        <v>54.43037974683544</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
       <c r="Q4" s="3">
-        <v>38.35443037974684</v>
+        <v>39.1139240506329</v>
       </c>
       <c r="R4" s="3">
-        <v>27.53164556962025</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
       <c r="T4" s="3">
-        <v>12.72</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2341,49 +2344,49 @@
         <v>0.34</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.12819511545725013</v>
+        <v>-0.11680177297247615</v>
       </c>
       <c r="G5" s="1">
         <v>1.8</v>
       </c>
       <c r="H5" s="1">
-        <v>60.86</v>
+        <v>63.05</v>
       </c>
       <c r="I5" s="1">
-        <v>5.6</v>
+        <v>7.11</v>
       </c>
       <c r="J5" s="1">
-        <v>0.005522357877051351</v>
+        <v>0.0075546277074118985</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.04971364751146057</v>
+        <v>-0.04522002157011573</v>
       </c>
       <c r="N5" s="1">
-        <v>5.91381874207764</v>
+        <v>5.500716768283477</v>
       </c>
       <c r="O5" s="1">
-        <v>46.835443037974684</v>
+        <v>53.16455696202531</v>
       </c>
       <c r="P5" s="1">
         <v>25.321993503429013</v>
       </c>
       <c r="Q5" s="1">
-        <v>58.607594936708864</v>
+        <v>60</v>
       </c>
       <c r="R5" s="1">
-        <v>44.620253164556964</v>
+        <v>46.64556962025316</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>-0.7</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2403,49 +2406,49 @@
         <v>0.97</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.03633840164753008</v>
+        <v>-0.08963320755585905</v>
       </c>
       <c r="G6" s="1">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6" s="1">
-        <v>41.43</v>
+        <v>40.57</v>
       </c>
       <c r="I6" s="1">
-        <v>-13.81</v>
+        <v>-13.99</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.007801426772082932</v>
+        <v>-0.007574001660456642</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M6" s="1">
-        <v>0.014674552517233153</v>
+        <v>-0.04399984103685428</v>
       </c>
       <c r="N6" s="1">
-        <v>12.352638744947017</v>
+        <v>5.62273482160962</v>
       </c>
       <c r="O6" s="1">
-        <v>58.22784810126582</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>37.46835443037975</v>
+        <v>36.58227848101265</v>
       </c>
       <c r="R6" s="1">
-        <v>40.50632911392405</v>
+        <v>38.9873417721519</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-1.58</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2465,19 +2468,19 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.11636798937581794</v>
+        <v>-0.12314970394217742</v>
       </c>
       <c r="G7" s="2">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="H7" s="2">
-        <v>53.26</v>
+        <v>51.04</v>
       </c>
       <c r="I7" s="2">
-        <v>14.77</v>
+        <v>13.48</v>
       </c>
       <c r="J7" s="2">
-        <v>0.01824488634695496</v>
+        <v>0.017292487128875076</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2486,28 +2489,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.005278285940155891</v>
+        <v>-0.013092761161048294</v>
       </c>
       <c r="N7" s="2">
-        <v>11.413012087239286</v>
+        <v>8.713442809190228</v>
       </c>
       <c r="O7" s="2">
-        <v>56.9620253164557</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>60.75949367088607</v>
+        <v>60.25316455696202</v>
       </c>
       <c r="R7" s="2">
-        <v>52.21518987341773</v>
+        <v>52.46835443037975</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>-2.34</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2521,25 +2524,25 @@
         <v>86.07594936708861</v>
       </c>
       <c r="D8" s="2">
-        <v>0.021903323262839815</v>
+        <v>0.027945619335347373</v>
       </c>
       <c r="E8" s="2">
         <v>1.61</v>
       </c>
       <c r="F8" s="2">
-        <v>0.30113618385521035</v>
+        <v>0.2822861439156642</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>56.83</v>
+        <v>61.02</v>
       </c>
       <c r="I8" s="2">
-        <v>16.07</v>
+        <v>18.03</v>
       </c>
       <c r="J8" s="2">
-        <v>0.03154432129640191</v>
+        <v>0.030999849916510537</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -2548,28 +2551,28 @@
         <v>-220</v>
       </c>
       <c r="M8" s="2">
-        <v>0.2668005416289274</v>
+        <v>0.25096912767713153</v>
       </c>
       <c r="N8" s="2">
-        <v>37.56523765611643</v>
+        <v>35.119631693008216</v>
       </c>
       <c r="O8" s="2">
-        <v>84.81012658227847</v>
+        <v>83.54430379746836</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>61.26582278481013</v>
+        <v>62.27848101265823</v>
       </c>
       <c r="R8" s="2">
-        <v>54.936708860759495</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.38</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2589,49 +2592,49 @@
         <v>0.88</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.09767293257381973</v>
+        <v>-0.15659063270382614</v>
       </c>
       <c r="G9" s="1">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H9" s="1">
-        <v>47.07</v>
+        <v>41.36</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.89</v>
+        <v>-18.27</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.011157712883681248</v>
+        <v>-0.011056865217076543</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.048622015107701255</v>
+        <v>-0.1127468099698804</v>
       </c>
       <c r="N9" s="1">
-        <v>6.022981982453576</v>
+        <v>-1.2519620716929967</v>
       </c>
       <c r="O9" s="1">
-        <v>48.10126582278481</v>
+        <v>39.24050632911392</v>
       </c>
       <c r="P9" s="1">
         <v>30.47019076386737</v>
       </c>
       <c r="Q9" s="1">
-        <v>44.81012658227848</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="R9" s="1">
-        <v>40.37974683544304</v>
+        <v>37.46835443037974</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.82</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2651,19 +2654,19 @@
         <v>-0.77</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.17519338162267328</v>
+        <v>-0.14429986144444948</v>
       </c>
       <c r="G10" s="1">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H10" s="1">
-        <v>49.45</v>
+        <v>51.95</v>
       </c>
       <c r="I10" s="1">
-        <v>-4.76</v>
+        <v>-3.89</v>
       </c>
       <c r="J10" s="1">
-        <v>0.002697688644044308</v>
+        <v>0.0036643652342656036</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
@@ -2672,28 +2675,28 @@
         <v>-131</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.13497162930045614</v>
+        <v>-0.10850898574326928</v>
       </c>
       <c r="N10" s="1">
-        <v>-2.6119794368219247</v>
+        <v>-0.828179649031884</v>
       </c>
       <c r="O10" s="1">
-        <v>39.24050632911392</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>46.45569620253165</v>
+        <v>47.08860759493671</v>
       </c>
       <c r="R10" s="1">
-        <v>37.27848101265823</v>
+        <v>38.037974683544306</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.52</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2713,19 +2716,19 @@
         <v>-0.88</v>
       </c>
       <c r="F11" s="2">
-        <v>0.36040882690817566</v>
+        <v>0.3016185535383472</v>
       </c>
       <c r="G11" s="2">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H11" s="2">
-        <v>73.75</v>
+        <v>65.69</v>
       </c>
       <c r="I11" s="2">
-        <v>18.94</v>
+        <v>14.96</v>
       </c>
       <c r="J11" s="2">
-        <v>0.027995251552379325</v>
+        <v>0.028352733655701592</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>0</v>
@@ -2734,28 +2737,28 @@
         <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.34569355166834015</v>
+        <v>0.28909174704293417</v>
       </c>
       <c r="N11" s="2">
-        <v>45.454538660057715</v>
+        <v>38.93189362958847</v>
       </c>
       <c r="O11" s="2">
-        <v>86.07594936708861</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>60.75949367088608</v>
+        <v>59.24050632911393</v>
       </c>
       <c r="R11" s="2">
-        <v>53.16455696202532</v>
+        <v>52.78481012658228</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>6.71</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2775,19 +2778,19 @@
         <v>3.81</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.022291932529678885</v>
+        <v>-0.06831159928225057</v>
       </c>
       <c r="G12" s="1">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H12" s="1">
-        <v>61.74</v>
+        <v>60.34</v>
       </c>
       <c r="I12" s="1">
-        <v>-25.02</v>
+        <v>-25.57</v>
       </c>
       <c r="J12" s="1">
-        <v>0.013233694366704676</v>
+        <v>0.01595887032593726</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
@@ -2796,28 +2799,28 @@
         <v>-51</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.035045171070869685</v>
+        <v>-0.07904886199260464</v>
       </c>
       <c r="N12" s="1">
-        <v>7.38066638613672</v>
+        <v>2.1178327260345897</v>
       </c>
       <c r="O12" s="1">
-        <v>50.63291139240506</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P12" s="1">
         <v>49.188907754993835</v>
       </c>
       <c r="Q12" s="1">
-        <v>52.27848101265822</v>
+        <v>52.151898734177216</v>
       </c>
       <c r="R12" s="1">
-        <v>38.734177215189874</v>
+        <v>37.59493670886076</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="1">
-        <v>18.04</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2837,19 +2840,19 @@
         <v>6.41</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.34065996600621173</v>
+        <v>-0.3306167647969178</v>
       </c>
       <c r="G13" s="3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H13" s="3">
-        <v>42.82</v>
+        <v>44.9</v>
       </c>
       <c r="I13" s="3">
-        <v>-8.42</v>
+        <v>-6.96</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.009577099600196395</v>
+        <v>-0.00872891796016568</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
@@ -2858,10 +2861,10 @@
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.3024002503826393</v>
+        <v>-0.2966154328807966</v>
       </c>
       <c r="N13" s="3">
-        <v>-19.354841545040237</v>
+        <v>-19.63882436278461</v>
       </c>
       <c r="O13" s="3">
         <v>6.329113924050633</v>
@@ -2870,16 +2873,16 @@
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>17.974683544303797</v>
+        <v>18.987341772151897</v>
       </c>
       <c r="R13" s="3">
-        <v>3.4810126582278462</v>
+        <v>3.6075949367088596</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-12.41</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2899,49 +2902,49 @@
         <v>4.73</v>
       </c>
       <c r="F14" s="1">
-        <v>0.2451322190007546</v>
+        <v>0.15703330164011697</v>
       </c>
       <c r="G14" s="1">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H14" s="1">
-        <v>71.91</v>
+        <v>61.87</v>
       </c>
       <c r="I14" s="1">
-        <v>10.42</v>
+        <v>5.36</v>
       </c>
       <c r="J14" s="1">
-        <v>0.013491630876964871</v>
+        <v>0.015117235179156368</v>
       </c>
       <c r="K14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>0.20981555842514932</v>
+        <v>0.1257162854015843</v>
       </c>
       <c r="N14" s="1">
-        <v>31.866739335738618</v>
+        <v>22.594347465453488</v>
       </c>
       <c r="O14" s="1">
-        <v>79.74683544303798</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>58.10126582278481</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="R14" s="1">
-        <v>48.67088607594937</v>
+        <v>46.64556962025316</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>13.48</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2961,31 +2964,31 @@
         <v>2.23</v>
       </c>
       <c r="F15" s="2">
-        <v>1.448713599855782</v>
+        <v>1.386303900438908</v>
       </c>
       <c r="G15" s="2">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H15" s="2">
-        <v>70.23</v>
+        <v>67.99</v>
       </c>
       <c r="I15" s="2">
-        <v>158.99</v>
+        <v>152.63</v>
       </c>
       <c r="J15" s="2">
-        <v>0.1017758350432543</v>
+        <v>0.10292763062815169</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M15" s="2">
-        <v>1.5693788568224336</v>
+        <v>1.4972556151125667</v>
       </c>
       <c r="N15" s="2">
-        <v>167.82306917546705</v>
+        <v>159.74828043655174</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2994,7 +2997,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>70.25316455696203</v>
+        <v>70.12658227848101</v>
       </c>
       <c r="R15" s="2">
         <v>62.27848101265822</v>
@@ -3007,65 +3010,65 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>-3.53</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>8.860759493670885</v>
       </c>
-      <c r="D16" s="3">
-        <v>12.651558073654392</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D16" s="1">
+        <v>12.69971671388102</v>
+      </c>
+      <c r="E16" s="1">
         <v>5.41</v>
       </c>
-      <c r="F16" s="3">
-        <v>-0.2695530962138256</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1.91</v>
-      </c>
-      <c r="H16" s="3">
-        <v>44.41</v>
-      </c>
-      <c r="I16" s="3">
-        <v>-4.7</v>
-      </c>
-      <c r="J16" s="3">
-        <v>-0.006160031268303892</v>
-      </c>
-      <c r="K16" s="3" t="b">
+      <c r="F16" s="1">
+        <v>-0.17926638357645863</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="H16" s="1">
+        <v>50.85</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-0.003221229937621772</v>
+      </c>
+      <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="1">
         <v>16</v>
       </c>
-      <c r="M16" s="3">
-        <v>-0.18028042642549003</v>
-      </c>
-      <c r="N16" s="3">
-        <v>-7.142859149325314</v>
-      </c>
-      <c r="O16" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="P16" s="3">
+      <c r="M16" s="1">
+        <v>-0.09873691324880318</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.1490276004147275</v>
+      </c>
+      <c r="O16" s="1">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="P16" s="1">
         <v>30.2515696939809</v>
       </c>
-      <c r="Q16" s="3">
-        <v>35.31645569620253</v>
-      </c>
-      <c r="R16" s="3">
-        <v>24.746835443037973</v>
-      </c>
-      <c r="S16" s="3" t="s">
+      <c r="Q16" s="1">
+        <v>39.620253164556964</v>
+      </c>
+      <c r="R16" s="1">
+        <v>30.189873417721518</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="3">
-        <v>-11.9</v>
+      <c r="T16" s="1">
+        <v>-6.46</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3085,19 +3088,19 @@
         <v>1.52</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.27073053680225956</v>
+        <v>-0.19490442422088772</v>
       </c>
       <c r="G17" s="3">
         <v>1.72</v>
       </c>
       <c r="H17" s="3">
-        <v>50.55</v>
+        <v>55.4</v>
       </c>
       <c r="I17" s="3">
-        <v>-7.41</v>
+        <v>-3.92</v>
       </c>
       <c r="J17" s="3">
-        <v>-0.004343408377603495</v>
+        <v>0.0020206662459270235</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3106,90 +3109,90 @@
         <v>25</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.200097215651049</v>
+        <v>-0.13048084795876336</v>
       </c>
       <c r="N17" s="3">
-        <v>-9.124538071881206</v>
+        <v>-3.025365870581283</v>
       </c>
       <c r="O17" s="3">
-        <v>24.050632911392405</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>31.139240506329116</v>
+        <v>34.30379746835443</v>
       </c>
       <c r="R17" s="3">
-        <v>18.607594936708864</v>
+        <v>22.531645569620252</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-4.56</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="3">
         <v>0.09</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>6.73</v>
       </c>
-      <c r="F18" s="1">
-        <v>-0.31061503994634965</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H18" s="1">
-        <v>35.04</v>
-      </c>
-      <c r="I18" s="1">
-        <v>-13.48</v>
-      </c>
-      <c r="J18" s="1">
-        <v>-0.007012635546003202</v>
-      </c>
-      <c r="K18" s="1" t="b">
+      <c r="F18" s="3">
+        <v>-0.32497685036724655</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1.18</v>
+      </c>
+      <c r="H18" s="3">
+        <v>34.53</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-14.05</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-0.0067314168475332255</v>
+      </c>
+      <c r="K18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="3">
         <v>37</v>
       </c>
-      <c r="M18" s="1">
-        <v>-0.2909946729599022</v>
-      </c>
-      <c r="N18" s="1">
-        <v>-18.21428380276653</v>
-      </c>
-      <c r="O18" s="1">
-        <v>8.860759493670885</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="M18" s="3">
+        <v>-0.30887095630171546</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-20.86437670487649</v>
+      </c>
+      <c r="O18" s="3">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="P18" s="3">
         <v>33.93532173431426</v>
       </c>
-      <c r="Q18" s="1">
-        <v>46.708860759493675</v>
-      </c>
-      <c r="R18" s="1">
-        <v>30.063291139240512</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="Q18" s="3">
+        <v>45.822784810126585</v>
+      </c>
+      <c r="R18" s="3">
+        <v>28.54430379746836</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="1">
-        <v>-0.89</v>
+      <c r="T18" s="3">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3209,19 +3212,19 @@
         <v>-1.48</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.0408761989982334</v>
+        <v>0.004070997072829149</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>53.74</v>
+        <v>57.8</v>
       </c>
       <c r="I19" s="1">
-        <v>13.88</v>
+        <v>15.95</v>
       </c>
       <c r="J19" s="1">
-        <v>0.0022734937249961917</v>
+        <v>0.0035004576038287953</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>0</v>
@@ -3230,28 +3233,28 @@
         <v>79</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.11935766694402294</v>
+        <v>-0.06751075432953124</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.0505832011786014</v>
+        <v>3.2716434923419246</v>
       </c>
       <c r="O19" s="1">
-        <v>41.77215189873418</v>
+        <v>48.10126582278481</v>
       </c>
       <c r="P19" s="1">
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>51.39240506329114</v>
+        <v>52.911392405063296</v>
       </c>
       <c r="R19" s="1">
-        <v>41.58227848101266</v>
+        <v>43.607594936708864</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T19" s="1">
-        <v>0.7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -3271,19 +3274,19 @@
         <v>6.54</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.009788259846447836</v>
+        <v>0.025680798024644888</v>
       </c>
       <c r="G20" s="1">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H20" s="1">
-        <v>65.69</v>
+        <v>69.12</v>
       </c>
       <c r="I20" s="1">
-        <v>1.39</v>
+        <v>4.18</v>
       </c>
       <c r="J20" s="1">
-        <v>0.007812277045019132</v>
+        <v>0.0103315709282782</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>0</v>
@@ -3292,28 +3295,28 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.003902149750513617</v>
+        <v>0.031944201272351425</v>
       </c>
       <c r="N20" s="1">
-        <v>10.494968518172325</v>
+        <v>13.217139052530186</v>
       </c>
       <c r="O20" s="1">
-        <v>55.69620253164557</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>53.41772151898734</v>
+        <v>54.936708860759495</v>
       </c>
       <c r="R20" s="1">
-        <v>41.962025316455694</v>
+        <v>43.48101265822784</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>14.56</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3333,19 +3336,19 @@
         <v>2.47</v>
       </c>
       <c r="F21" s="2">
-        <v>0.19199629327570336</v>
+        <v>0.30261560132243825</v>
       </c>
       <c r="G21" s="2">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H21" s="2">
-        <v>79.86</v>
+        <v>81.58</v>
       </c>
       <c r="I21" s="2">
-        <v>79.82</v>
+        <v>87.95</v>
       </c>
       <c r="J21" s="2">
-        <v>0.041584347423851274</v>
+        <v>0.05119225833009738</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
@@ -3354,28 +3357,28 @@
         <v>37</v>
       </c>
       <c r="M21" s="2">
-        <v>0.23614211899520998</v>
+        <v>0.3491437397339725</v>
       </c>
       <c r="N21" s="2">
-        <v>34.499395392744695</v>
+        <v>44.93709289869229</v>
       </c>
       <c r="O21" s="2">
-        <v>82.27848101265823</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="2">
-        <v>70.50632911392405</v>
+        <v>71.26582278481013</v>
       </c>
       <c r="R21" s="2">
-        <v>54.050632911392405</v>
+        <v>55.44303797468355</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="2">
-        <v>15.25</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3389,25 +3392,25 @@
         <v>70.88607594936708</v>
       </c>
       <c r="D22" s="1">
-        <v>0.6954377311960543</v>
+        <v>0.7016029593094947</v>
       </c>
       <c r="E22" s="1">
         <v>-0.84</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.23429123330990573</v>
+        <v>-0.2082266364890465</v>
       </c>
       <c r="G22" s="1">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H22" s="1">
-        <v>61.77</v>
+        <v>63.05</v>
       </c>
       <c r="I22" s="1">
-        <v>4.7</v>
+        <v>5.53</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.005102046491354681</v>
+        <v>-0.001734735067681004</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
@@ -3416,28 +3419,28 @@
         <v>58</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.19897457273430041</v>
+        <v>-0.1751200764654548</v>
       </c>
       <c r="N22" s="1">
-        <v>-9.012273780206344</v>
+        <v>-7.489288721250429</v>
       </c>
       <c r="O22" s="1">
-        <v>25.31645569620253</v>
+        <v>27.848101265822784</v>
       </c>
       <c r="P22" s="1">
         <v>20.966620085005058</v>
       </c>
       <c r="Q22" s="1">
-        <v>51.26582278481012</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="R22" s="1">
-        <v>33.60759493670886</v>
+        <v>35</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3457,49 +3460,49 @@
         <v>0.96</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.17358632133750004</v>
+        <v>-0.14900837999103375</v>
       </c>
       <c r="G23" s="1">
         <v>1.23</v>
       </c>
       <c r="H23" s="1">
-        <v>46.45</v>
+        <v>56.86</v>
       </c>
       <c r="I23" s="1">
-        <v>-8.43</v>
+        <v>-4.9</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.005491326524766096</v>
+        <v>-0.0038037903419921764</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.15102289930308554</v>
+        <v>-0.12842862646285513</v>
       </c>
       <c r="N23" s="1">
-        <v>-4.217106437084858</v>
+        <v>-2.820143720990467</v>
       </c>
       <c r="O23" s="1">
-        <v>35.44303797468354</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>43.92405063291139</v>
+        <v>47.59493670886076</v>
       </c>
       <c r="R23" s="1">
-        <v>34.24050632911393</v>
+        <v>35.00000000000001</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T23" s="1">
-        <v>2.28</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -3519,49 +3522,49 @@
         <v>9.47</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.07458621436303953</v>
+        <v>-0.18985546305069573</v>
       </c>
       <c r="G24" s="3">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="H24" s="3">
-        <v>44.67</v>
+        <v>41.3</v>
       </c>
       <c r="I24" s="3">
-        <v>-24.32</v>
+        <v>-26.61</v>
       </c>
       <c r="J24" s="3">
-        <v>0.016015518165394222</v>
+        <v>0.013483314120105023</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="M24" s="3">
-        <v>0.17459244636484228</v>
+        <v>0.03652182575926899</v>
       </c>
       <c r="N24" s="3">
-        <v>28.34442812970791</v>
+        <v>13.674901501221939</v>
       </c>
       <c r="O24" s="3">
-        <v>75.9493670886076</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P24" s="3">
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>22.278481012658233</v>
+        <v>20.126582278481013</v>
       </c>
       <c r="R24" s="3">
-        <v>26.075949367088608</v>
+        <v>21.39240506329114</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-4.94</v>
+        <v>-9.62</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3581,19 +3584,19 @@
         <v>11.95</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.31765185420632047</v>
+        <v>-0.2936079173987655</v>
       </c>
       <c r="G25" s="3">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="H25" s="3">
-        <v>53.4</v>
+        <v>52.41</v>
       </c>
       <c r="I25" s="3">
-        <v>-46.45</v>
+        <v>-46.79</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.008187214722448165</v>
+        <v>-0.0043951856131987975</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3602,28 +3605,28 @@
         <v>41</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.19894863393831375</v>
+        <v>-0.18444574651016588</v>
       </c>
       <c r="N25" s="3">
-        <v>-9.009679900607681</v>
+        <v>-8.421855725721535</v>
       </c>
       <c r="O25" s="3">
-        <v>26.582278481012654</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>13.797468354430382</v>
+        <v>15.443037974683545</v>
       </c>
       <c r="R25" s="3">
-        <v>3.9240506329113938</v>
+        <v>4.050632911392407</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-8.04</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3643,31 +3646,31 @@
         <v>3.39</v>
       </c>
       <c r="F26" s="1">
-        <v>0.6971519348388568</v>
+        <v>0.6579840161118936</v>
       </c>
       <c r="G26" s="1">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="H26" s="1">
-        <v>69.17</v>
+        <v>70.66</v>
       </c>
       <c r="I26" s="1">
-        <v>34.07</v>
+        <v>37.48</v>
       </c>
       <c r="J26" s="1">
-        <v>0.05899436026223026</v>
+        <v>0.06851111305724455</v>
       </c>
       <c r="K26" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="1">
         <v>-29</v>
       </c>
       <c r="M26" s="1">
-        <v>0.9031657881965545</v>
+        <v>0.8467808854356191</v>
       </c>
       <c r="N26" s="1">
-        <v>101.20176231287911</v>
+        <v>94.70080746885695</v>
       </c>
       <c r="O26" s="1">
         <v>92.40506329113924</v>
@@ -3676,78 +3679,78 @@
         <v>47.81158046237125</v>
       </c>
       <c r="Q26" s="1">
-        <v>42.02531645569621</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="R26" s="1">
-        <v>33.924050632911396</v>
+        <v>34.05063291139241</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>0.89</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>-1.13</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="1">
         <v>13.924050632911392</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="1">
         <v>1.0176991150442478</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="1">
         <v>8.19</v>
       </c>
-      <c r="F27" s="3">
-        <v>-0.08357262615109584</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="H27" s="3">
-        <v>65.75</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-10.9</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0.0071593397768241595</v>
-      </c>
-      <c r="K27" s="3" t="b">
+      <c r="F27" s="1">
+        <v>-0.07882179194803116</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.65</v>
+      </c>
+      <c r="H27" s="1">
+        <v>65.21</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-11.04</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.010826199479166711</v>
+      </c>
+      <c r="K27" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="1">
         <v>42</v>
       </c>
-      <c r="M27" s="3">
-        <v>0.07633336478845032</v>
-      </c>
-      <c r="N27" s="3">
-        <v>18.518519972068724</v>
-      </c>
-      <c r="O27" s="3">
-        <v>64.55696202531645</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="M27" s="1">
+        <v>0.06881557031933716</v>
+      </c>
+      <c r="N27" s="1">
+        <v>16.904275957228773</v>
+      </c>
+      <c r="O27" s="1">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P27" s="1">
         <v>51.28834092723359</v>
       </c>
-      <c r="Q27" s="3">
-        <v>38.10126582278481</v>
-      </c>
-      <c r="R27" s="3">
-        <v>28.9873417721519</v>
-      </c>
-      <c r="S27" s="3" t="s">
+      <c r="Q27" s="1">
+        <v>38.86075949367089</v>
+      </c>
+      <c r="R27" s="1">
+        <v>30.126582278481024</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T27" s="3">
-        <v>2.59</v>
+      <c r="T27" s="1">
+        <v>3.73</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3767,19 +3770,19 @@
         <v>-4.03</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.41238451843205376</v>
+        <v>-0.3682783518385405</v>
       </c>
       <c r="G28" s="3">
         <v>3.13</v>
       </c>
       <c r="H28" s="3">
-        <v>59.16</v>
+        <v>59.87</v>
       </c>
       <c r="I28" s="3">
-        <v>-18.89</v>
+        <v>-18.23</v>
       </c>
       <c r="J28" s="3">
-        <v>-0.0026235986840229294</v>
+        <v>0.0009218808275710569</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
@@ -3788,28 +3791,28 @@
         <v>-3</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.2034276100263891</v>
+        <v>-0.17769193872975597</v>
       </c>
       <c r="N28" s="3">
-        <v>-9.457577509415213</v>
+        <v>-7.746474947680554</v>
       </c>
       <c r="O28" s="3">
-        <v>21.518987341772153</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>37.721518987341774</v>
+        <v>38.9873417721519</v>
       </c>
       <c r="R28" s="3">
-        <v>20.44303797468354</v>
+        <v>22.088607594936704</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>-1.46</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3823,25 +3826,25 @@
         <v>34.177215189873415</v>
       </c>
       <c r="D29" s="3">
-        <v>77.20454545454545</v>
+        <v>79.11363636363637</v>
       </c>
       <c r="E29" s="3">
         <v>1.51</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.36136761163686304</v>
+        <v>-0.36128874030113833</v>
       </c>
       <c r="G29" s="3">
         <v>2.11</v>
       </c>
       <c r="H29" s="3">
-        <v>46.48</v>
+        <v>48.4</v>
       </c>
       <c r="I29" s="3">
-        <v>-31.41</v>
+        <v>-30.51</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.015190326766006321</v>
+        <v>-0.012771018064302118</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
@@ -3850,28 +3853,28 @@
         <v>-71</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.25247457486208</v>
+        <v>-0.26196906023036326</v>
       </c>
       <c r="N29" s="3">
-        <v>-14.36227399298431</v>
+        <v>-16.17418709774128</v>
       </c>
       <c r="O29" s="3">
-        <v>13.924050632911392</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>42.40506329113924</v>
+        <v>42.53164556962025</v>
       </c>
       <c r="R29" s="3">
-        <v>26.708860759493668</v>
+        <v>26.32911392405063</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3891,19 +3894,19 @@
         <v>1.79</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.18957612950131153</v>
+        <v>-0.14353449500323823</v>
       </c>
       <c r="G30" s="1">
         <v>1.19</v>
       </c>
       <c r="H30" s="1">
-        <v>44.74</v>
+        <v>50.19</v>
       </c>
       <c r="I30" s="1">
-        <v>-0.29</v>
+        <v>2.19</v>
       </c>
       <c r="J30" s="1">
-        <v>0.002133982095610389</v>
+        <v>0.004050291917695464</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
@@ -3912,28 +3915,28 @@
         <v>24</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.1709367808641865</v>
+        <v>-0.12653382904517763</v>
       </c>
       <c r="N30" s="1">
-        <v>-6.208494593194955</v>
+        <v>-2.6306639792227173</v>
       </c>
       <c r="O30" s="1">
-        <v>31.645569620253166</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>60</v>
+        <v>63.037974683544306</v>
       </c>
       <c r="R30" s="1">
-        <v>46.0126582278481</v>
+        <v>48.54430379746835</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>-1.52</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3947,25 +3950,25 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D31" s="2">
-        <v>10.83625730994152</v>
+        <v>10.894736842105264</v>
       </c>
       <c r="E31" s="2">
         <v>0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>0.1464829913335334</v>
+        <v>0.1316696518032923</v>
       </c>
       <c r="G31" s="2">
         <v>1.42</v>
       </c>
       <c r="H31" s="2">
-        <v>56.45</v>
+        <v>56.37</v>
       </c>
       <c r="I31" s="2">
-        <v>20.42</v>
+        <v>20.18</v>
       </c>
       <c r="J31" s="2">
-        <v>0.021094409729336107</v>
+        <v>0.022718085284339593</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
@@ -3974,10 +3977,10 @@
         <v>67</v>
       </c>
       <c r="M31" s="2">
-        <v>0.18768576200507292</v>
+        <v>0.1692500712895315</v>
       </c>
       <c r="N31" s="2">
-        <v>29.65375969373098</v>
+        <v>26.947726054248207</v>
       </c>
       <c r="O31" s="2">
         <v>77.21518987341773</v>
@@ -3986,7 +3989,7 @@
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>64.9367088607595</v>
+        <v>64.81012658227847</v>
       </c>
       <c r="R31" s="2">
         <v>59.55696202531646</v>
@@ -4009,25 +4012,25 @@
         <v>10.126582278481013</v>
       </c>
       <c r="D32" s="3">
-        <v>8.178082191780822</v>
+        <v>8.041095890410958</v>
       </c>
       <c r="E32" s="3">
         <v>-2.98</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.21697434761137646</v>
+        <v>-0.18997908908241676</v>
       </c>
       <c r="G32" s="3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H32" s="3">
-        <v>47.2</v>
+        <v>50.39</v>
       </c>
       <c r="I32" s="3">
-        <v>-6.43</v>
+        <v>-4.51</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.012699275100331421</v>
+        <v>-0.009713523366369447</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
@@ -4036,28 +4039,28 @@
         <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.1571322283027119</v>
+        <v>-0.13629277553064645</v>
       </c>
       <c r="N32" s="3">
-        <v>-4.828039337047492</v>
+        <v>-3.606558627769595</v>
       </c>
       <c r="O32" s="3">
-        <v>34.177215189873415</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P32" s="3">
         <v>37.59071325149605</v>
       </c>
       <c r="Q32" s="3">
-        <v>31.0126582278481</v>
+        <v>32.65822784810126</v>
       </c>
       <c r="R32" s="3">
-        <v>21.582278481012658</v>
+        <v>21.32911392405063</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-7.78</v>
+        <v>-8.04</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4077,111 +4080,111 @@
         <v>-0.44</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.048195142031673216</v>
+        <v>-0.07815031316958804</v>
       </c>
       <c r="G33" s="1">
         <v>1.09</v>
       </c>
       <c r="H33" s="1">
-        <v>52.31</v>
+        <v>49.59</v>
       </c>
       <c r="I33" s="1">
-        <v>-9.53</v>
+        <v>-10.16</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0037415212105996578</v>
+        <v>0.003975805434924213</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L33" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.03936597688777188</v>
+        <v>-0.07009736613682249</v>
       </c>
       <c r="N33" s="1">
-        <v>6.948585804446497</v>
+        <v>3.0129823116128067</v>
       </c>
       <c r="O33" s="1">
-        <v>49.36708860759494</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P33" s="1">
         <v>26.81341163265095</v>
       </c>
       <c r="Q33" s="1">
-        <v>49.36708860759493</v>
+        <v>48.734177215189874</v>
       </c>
       <c r="R33" s="1">
-        <v>41.26582278481012</v>
+        <v>40.50632911392404</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>1.33</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <v>13.11</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="2">
         <v>84.81012658227847</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="2">
         <v>-0.7170099160945842</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>0.77</v>
       </c>
-      <c r="F34" s="1">
-        <v>0.11744294601695968</v>
-      </c>
-      <c r="G34" s="1">
+      <c r="F34" s="2">
+        <v>0.12006888306274481</v>
+      </c>
+      <c r="G34" s="2">
         <v>1.25</v>
       </c>
-      <c r="H34" s="1">
-        <v>61.01</v>
-      </c>
-      <c r="I34" s="1">
-        <v>30.87</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0.024388336180927072</v>
-      </c>
-      <c r="K34" s="1" t="b">
+      <c r="H34" s="2">
+        <v>60.97</v>
+      </c>
+      <c r="I34" s="2">
+        <v>30.44</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.02438757494779184</v>
+      </c>
+      <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="L34" s="1">
-        <v>37</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0.14196840475001893</v>
-      </c>
-      <c r="N34" s="1">
-        <v>25.0820239682256</v>
-      </c>
-      <c r="O34" s="1">
-        <v>70.88607594936708</v>
-      </c>
-      <c r="P34" s="1">
+      <c r="L34" s="2">
+        <v>36</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0.14243818037598244</v>
+      </c>
+      <c r="N34" s="2">
+        <v>24.266536962893294</v>
+      </c>
+      <c r="O34" s="2">
+        <v>74.68354430379746</v>
+      </c>
+      <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
-      <c r="Q34" s="1">
-        <v>58.22784810126582</v>
-      </c>
-      <c r="R34" s="1">
-        <v>49.24050632911393</v>
-      </c>
-      <c r="S34" s="1" t="s">
+      <c r="Q34" s="2">
+        <v>57.848101265822784</v>
+      </c>
+      <c r="R34" s="2">
+        <v>50.25316455696202</v>
+      </c>
+      <c r="S34" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="T34" s="1">
-        <v>-1.9</v>
+      <c r="T34" s="2">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4195,25 +4198,25 @@
         <v>91.13924050632912</v>
       </c>
       <c r="D35" s="3">
-        <v>-0.4801381692573403</v>
+        <v>-0.4830166954519286</v>
       </c>
       <c r="E35" s="3">
         <v>9.42</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.35940711190172214</v>
+        <v>-0.32763365185892834</v>
       </c>
       <c r="G35" s="3">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H35" s="3">
-        <v>35.22</v>
+        <v>36.54</v>
       </c>
       <c r="I35" s="3">
-        <v>-22.7</v>
+        <v>-22.25</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.024316454607649276</v>
+        <v>-0.023193585401175824</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
@@ -4222,10 +4225,10 @@
         <v>19</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.35940711190172214</v>
+        <v>-0.32852842375145785</v>
       </c>
       <c r="N35" s="3">
-        <v>-25.05552769694852</v>
+        <v>-22.83012344985074</v>
       </c>
       <c r="O35" s="3">
         <v>3.79746835443038</v>
@@ -4234,7 +4237,7 @@
         <v>28.919768290867083</v>
       </c>
       <c r="Q35" s="3">
-        <v>33.797468354430386</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="R35" s="3">
         <v>21.455696202531644</v>
@@ -4247,65 +4250,65 @@
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="3">
         <v>11.51</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="3">
         <v>82.27848101265823</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="3">
         <v>0.40225890529973946</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="3">
         <v>3.24</v>
       </c>
-      <c r="F36" s="1">
-        <v>-0.1560322140466506</v>
-      </c>
-      <c r="G36" s="1">
+      <c r="F36" s="3">
+        <v>-0.2250081669146608</v>
+      </c>
+      <c r="G36" s="3">
         <v>1.12</v>
       </c>
-      <c r="H36" s="1">
-        <v>55.05</v>
-      </c>
-      <c r="I36" s="1">
-        <v>-6.91</v>
-      </c>
-      <c r="J36" s="1">
-        <v>-0.008146925649258702</v>
-      </c>
-      <c r="K36" s="1" t="b">
+      <c r="H36" s="3">
+        <v>48.78</v>
+      </c>
+      <c r="I36" s="3">
+        <v>-10.82</v>
+      </c>
+      <c r="J36" s="3">
+        <v>-0.005102408068476226</v>
+      </c>
+      <c r="K36" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L36" s="3">
         <v>-55</v>
       </c>
-      <c r="M36" s="1">
-        <v>-0.14425999385478216</v>
-      </c>
-      <c r="N36" s="1">
-        <v>-3.540815892254525</v>
-      </c>
-      <c r="O36" s="1">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="P36" s="1">
+      <c r="M36" s="3">
+        <v>-0.21427090420430672</v>
+      </c>
+      <c r="N36" s="3">
+        <v>-11.40437149513563</v>
+      </c>
+      <c r="O36" s="3">
+        <v>17.72151898734177</v>
+      </c>
+      <c r="P36" s="3">
         <v>32.54334537649318</v>
       </c>
-      <c r="Q36" s="1">
-        <v>46.20253164556962</v>
-      </c>
-      <c r="R36" s="1">
-        <v>33.67088607594937</v>
-      </c>
-      <c r="S36" s="1" t="s">
+      <c r="Q36" s="3">
+        <v>44.303797468354425</v>
+      </c>
+      <c r="R36" s="3">
+        <v>28.481012658227844</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="1">
-        <v>-0.63</v>
+      <c r="T36" s="3">
+        <v>-5.82</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4325,49 +4328,49 @@
         <v>-5.1</v>
       </c>
       <c r="F37" s="3">
-        <v>-0.20597470701981874</v>
+        <v>-0.20767146673841141</v>
       </c>
       <c r="G37" s="3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H37" s="3">
-        <v>35.83</v>
+        <v>33.82</v>
       </c>
       <c r="I37" s="3">
-        <v>-22.68</v>
+        <v>-23.22</v>
       </c>
       <c r="J37" s="3">
-        <v>-0.0021899364392746613</v>
+        <v>-0.001904983818433394</v>
       </c>
       <c r="K37" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L37" s="3">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="M37" s="3">
-        <v>-0.16967702809489105</v>
+        <v>-0.17545967860734923</v>
       </c>
       <c r="N37" s="3">
-        <v>-6.082519316265416</v>
+        <v>-7.523248935439876</v>
       </c>
       <c r="O37" s="3">
-        <v>32.91139240506329</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="P37" s="3">
         <v>34.65975433248125</v>
       </c>
       <c r="Q37" s="3">
-        <v>38.10126582278481</v>
+        <v>37.46835443037975</v>
       </c>
       <c r="R37" s="3">
-        <v>29.683544303797472</v>
+        <v>27.658227848101266</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="3">
-        <v>-9.11</v>
+        <v>-11.14</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4381,25 +4384,25 @@
         <v>16.455696202531644</v>
       </c>
       <c r="D38" s="2">
-        <v>36.54054054054054</v>
+        <v>36.74324324324324</v>
       </c>
       <c r="E38" s="2">
         <v>-0.57</v>
       </c>
       <c r="F38" s="2">
-        <v>0.7927965903735908</v>
+        <v>0.6600011482972626</v>
       </c>
       <c r="G38" s="2">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H38" s="2">
-        <v>87.44</v>
+        <v>75.81</v>
       </c>
       <c r="I38" s="2">
-        <v>43.97</v>
+        <v>38.03</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04724798191008728</v>
+        <v>0.04858736547414308</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
@@ -4408,10 +4411,10 @@
         <v>-45</v>
       </c>
       <c r="M38" s="2">
-        <v>0.8084928839627488</v>
+        <v>0.6761070423627937</v>
       </c>
       <c r="N38" s="2">
-        <v>91.73447188949856</v>
+        <v>77.63342316157441</v>
       </c>
       <c r="O38" s="2">
         <v>91.13924050632912</v>
@@ -4420,16 +4423,16 @@
         <v>26.865173556258448</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.69620253164557</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="R38" s="2">
-        <v>55.696202531645575</v>
+        <v>55.56962025316456</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4449,19 +4452,19 @@
         <v>6.03</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.09821364751602973</v>
+        <v>-0.06384501315689235</v>
       </c>
       <c r="G39" s="1">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H39" s="1">
-        <v>32.31</v>
+        <v>32.23</v>
       </c>
       <c r="I39" s="1">
-        <v>-9.19</v>
+        <v>-9.22</v>
       </c>
       <c r="J39" s="1">
-        <v>0.006020118944067225</v>
+        <v>0.002052035658048767</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4470,90 +4473,90 @@
         <v>-4</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.07172615208432576</v>
+        <v>-0.041475715843654726</v>
       </c>
       <c r="N39" s="1">
-        <v>3.7125682847911228</v>
+        <v>5.875147340929577</v>
       </c>
       <c r="O39" s="1">
-        <v>45.56962025316456</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P39" s="1">
-        <v>21.69982351852176</v>
+        <v>21.790241497748045</v>
       </c>
       <c r="Q39" s="1">
-        <v>46.32911392405063</v>
+        <v>45.316455696202524</v>
       </c>
       <c r="R39" s="1">
-        <v>41.835443037974684</v>
+        <v>44.24050632911393</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1">
-        <v>-11.58</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="3">
         <v>-6.41</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="3">
         <v>2.5316455696202533</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="3">
         <v>10.182527301092042</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="3">
         <v>2.22</v>
       </c>
-      <c r="F40" s="1">
-        <v>0.11668823300148405</v>
-      </c>
-      <c r="G40" s="1">
+      <c r="F40" s="3">
+        <v>0.032728270955086944</v>
+      </c>
+      <c r="G40" s="3">
         <v>0</v>
       </c>
-      <c r="H40" s="1">
-        <v>38.95</v>
-      </c>
-      <c r="I40" s="1">
-        <v>-22.73</v>
-      </c>
-      <c r="J40" s="1">
-        <v>-0.0019554944392674366</v>
-      </c>
-      <c r="K40" s="1" t="b">
+      <c r="H40" s="3">
+        <v>38.18</v>
+      </c>
+      <c r="I40" s="3">
+        <v>-23.44</v>
+      </c>
+      <c r="J40" s="3">
+        <v>-0.0047552246966131835</v>
+      </c>
+      <c r="K40" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L40" s="3">
         <v>54</v>
       </c>
-      <c r="M40" s="1">
-        <v>0.018586398069247112</v>
-      </c>
-      <c r="N40" s="1">
-        <v>12.743823300148401</v>
-      </c>
-      <c r="O40" s="1">
-        <v>59.49367088607595</v>
-      </c>
-      <c r="P40" s="1">
+      <c r="M40" s="3">
+        <v>-0.05674891829786355</v>
+      </c>
+      <c r="N40" s="3">
+        <v>4.347827095508702</v>
+      </c>
+      <c r="O40" s="3">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P40" s="3">
         <v>39.97107065255327</v>
       </c>
-      <c r="Q40" s="1">
-        <v>30.759493670886073</v>
-      </c>
-      <c r="R40" s="1">
-        <v>30.69620253164556</v>
-      </c>
-      <c r="S40" s="1" t="s">
+      <c r="Q40" s="3">
+        <v>28.607594936708857</v>
+      </c>
+      <c r="R40" s="3">
+        <v>27.468354430379748</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="T40" s="1">
-        <v>-10.06</v>
+      <c r="T40" s="3">
+        <v>-13.29</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4573,19 +4576,19 @@
         <v>-1.06</v>
       </c>
       <c r="F41" s="1">
-        <v>0.014143850527291654</v>
+        <v>0.045789238189137105</v>
       </c>
       <c r="G41" s="1">
         <v>1.11</v>
       </c>
       <c r="H41" s="1">
-        <v>61.55</v>
+        <v>63.28</v>
       </c>
       <c r="I41" s="1">
-        <v>-9.16</v>
+        <v>-7.56</v>
       </c>
       <c r="J41" s="1">
-        <v>0.02575731648836686</v>
+        <v>0.027102667429829527</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -4594,28 +4597,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>0.02493505236983773</v>
+        <v>0.05563172900696167</v>
       </c>
       <c r="N41" s="1">
-        <v>13.378688730207472</v>
+        <v>15.585891825991215</v>
       </c>
       <c r="O41" s="1">
-        <v>60.75949367088608</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>44.17721518987342</v>
+        <v>45.06329113924051</v>
       </c>
       <c r="R41" s="1">
-        <v>32.53164556962026</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>2.47</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4635,19 +4638,19 @@
         <v>2.81</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.07966918560912176</v>
+        <v>-0.07390571332374447</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>48.62</v>
+        <v>48.73</v>
       </c>
       <c r="I42" s="1">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.004062984230224514</v>
+        <v>-0.004098683644283372</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4656,28 +4659,28 @@
         <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.1424543599657534</v>
+        <v>-0.13117111444563279</v>
       </c>
       <c r="N42" s="1">
-        <v>-3.3602525033516475</v>
+        <v>-3.0943925192682316</v>
       </c>
       <c r="O42" s="1">
-        <v>37.9746835443038</v>
+        <v>32.91139240506329</v>
       </c>
       <c r="P42" s="1">
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>45.0632911392405</v>
+        <v>43.54430379746836</v>
       </c>
       <c r="R42" s="1">
-        <v>38.734177215189874</v>
+        <v>36.70886075949366</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>0.19</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4697,19 +4700,19 @@
         <v>10.72</v>
       </c>
       <c r="F43" s="1">
-        <v>0.057942216066355745</v>
+        <v>-0.052196028225681645</v>
       </c>
       <c r="G43" s="1">
         <v>1.29</v>
       </c>
       <c r="H43" s="1">
-        <v>56.64</v>
+        <v>47.79</v>
       </c>
       <c r="I43" s="1">
-        <v>-8.59</v>
+        <v>-13.49</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.005799043510940266</v>
+        <v>-0.005634380469718134</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
@@ -4718,28 +4721,28 @@
         <v>10</v>
       </c>
       <c r="M43" s="1">
-        <v>0.08639174819670448</v>
+        <v>-0.026247643342325988</v>
       </c>
       <c r="N43" s="1">
-        <v>19.524358312894144</v>
+        <v>7.397954591062446</v>
       </c>
       <c r="O43" s="1">
-        <v>65.82278481012658</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P43" s="1">
         <v>33.21399316212126</v>
       </c>
       <c r="Q43" s="1">
-        <v>52.0253164556962</v>
+        <v>47.721518987341774</v>
       </c>
       <c r="R43" s="1">
-        <v>46.58227848101265</v>
+        <v>43.67088607594937</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>4.43</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4753,25 +4756,25 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D44" s="3">
-        <v>26.666666666666664</v>
+        <v>26.69607843137255</v>
       </c>
       <c r="E44" s="3">
         <v>-0.99</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.3686968263091472</v>
+        <v>-0.355556757637458</v>
       </c>
       <c r="G44" s="3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H44" s="3">
-        <v>43.9</v>
+        <v>46.11</v>
       </c>
       <c r="I44" s="3">
-        <v>-25.15</v>
+        <v>-23.82</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.020691537987769633</v>
+        <v>-0.018684776336559197</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
@@ -4780,28 +4783,28 @@
         <v>-114</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.21173389041756807</v>
+        <v>-0.2141827986177962</v>
       </c>
       <c r="N44" s="3">
-        <v>-10.288205548533108</v>
+        <v>-11.395560936484577</v>
       </c>
       <c r="O44" s="3">
-        <v>20.253164556962027</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P44" s="3">
         <v>43.36598203964858</v>
       </c>
       <c r="Q44" s="3">
-        <v>40.25316455696202</v>
+        <v>41.26582278481012</v>
       </c>
       <c r="R44" s="3">
-        <v>28.417721518987342</v>
+        <v>28.0379746835443</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4815,55 +4818,55 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.7419354838709679</v>
+        <v>0.720430107526882</v>
       </c>
       <c r="E45" s="2">
         <v>0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>0.11901045044535288</v>
+        <v>0.15009868938510945</v>
       </c>
       <c r="G45" s="2">
         <v>1.45</v>
       </c>
       <c r="H45" s="2">
-        <v>56.61</v>
+        <v>62.65</v>
       </c>
       <c r="I45" s="2">
-        <v>14.96</v>
+        <v>17.68</v>
       </c>
       <c r="J45" s="2">
-        <v>0.022440388114184733</v>
+        <v>0.023549181299388926</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M45" s="2">
-        <v>0.1631562761648595</v>
+        <v>0.19036342454893718</v>
       </c>
       <c r="N45" s="2">
-        <v>27.200811109709637</v>
+        <v>29.059061380188766</v>
       </c>
       <c r="O45" s="2">
-        <v>73.41772151898735</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>60.50632911392406</v>
+        <v>62.40506329113925</v>
       </c>
       <c r="R45" s="2">
-        <v>54.49367088607596</v>
+        <v>56.39240506329115</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-2.47</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4883,19 +4886,19 @@
         <v>5.16</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.3478599406175741</v>
+        <v>-0.33033456237278586</v>
       </c>
       <c r="G46" s="3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H46" s="3">
-        <v>45.02</v>
+        <v>44.82</v>
       </c>
       <c r="I46" s="3">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.011669984976052239</v>
+        <v>-0.008856868141176399</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4904,28 +4907,28 @@
         <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.30077105985010033</v>
+        <v>-0.2882802834238991</v>
       </c>
       <c r="N46" s="3">
-        <v>-19.19192249178634</v>
+        <v>-18.805309417094858</v>
       </c>
       <c r="O46" s="3">
-        <v>7.59493670886076</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>45.31645569620254</v>
+        <v>45.69620253164557</v>
       </c>
       <c r="R46" s="3">
-        <v>24.177215189873415</v>
+        <v>25.44303797468354</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-7.22</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4945,19 +4948,19 @@
         <v>1.38</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.42838910562750215</v>
+        <v>-0.47443207463103015</v>
       </c>
       <c r="G47" s="3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H47" s="3">
-        <v>31.64</v>
+        <v>27.67</v>
       </c>
       <c r="I47" s="3">
-        <v>-20.61</v>
+        <v>-23.88</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.030480465723502825</v>
+        <v>-0.03109130420197483</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4966,28 +4969,28 @@
         <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.38326226155867316</v>
+        <v>-0.43416733946720243</v>
       </c>
       <c r="N47" s="3">
-        <v>-27.44104266264362</v>
+        <v>-33.39401502142519</v>
       </c>
       <c r="O47" s="3">
-        <v>2.5316455696202533</v>
+        <v>1.2658227848101267</v>
       </c>
       <c r="P47" s="3">
-        <v>31.304415950527737</v>
+        <v>33.39401502142519</v>
       </c>
       <c r="Q47" s="3">
-        <v>38.607594936708864</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="R47" s="3">
-        <v>24.9367088607595</v>
+        <v>23.9240506329114</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T47" s="3">
-        <v>-0.82</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -5007,19 +5010,19 @@
         <v>0.6</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.18548651030220292</v>
+        <v>-0.16466017593862114</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>61.75</v>
+        <v>63.42</v>
       </c>
       <c r="I48" s="1">
-        <v>-2.3</v>
+        <v>-1.58</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.0006663904737025214</v>
+        <v>0.00035234258215829776</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>0</v>
@@ -5028,28 +5031,28 @@
         <v>-65</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.18352447360355817</v>
+        <v>-0.16287063215356212</v>
       </c>
       <c r="N48" s="1">
-        <v>-7.467263867132125</v>
+        <v>-6.264344290061167</v>
       </c>
       <c r="O48" s="1">
-        <v>27.848101265822784</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>49.74683544303798</v>
+        <v>49.74683544303797</v>
       </c>
       <c r="R48" s="1">
-        <v>34.620253164556964</v>
+        <v>34.87341772151899</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>8.42</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5069,49 +5072,49 @@
         <v>-0.36</v>
       </c>
       <c r="F49" s="2">
-        <v>0.013959692312439098</v>
+        <v>0.03214468712530286</v>
       </c>
       <c r="G49" s="2">
         <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>60.92</v>
+        <v>61.16</v>
       </c>
       <c r="I49" s="2">
-        <v>44.58</v>
+        <v>44.24</v>
       </c>
       <c r="J49" s="2">
-        <v>0.021973315229901976</v>
+        <v>0.02327656005186917</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M49" s="2">
-        <v>0.07380181162110366</v>
+        <v>0.08672577256960268</v>
       </c>
       <c r="N49" s="2">
-        <v>18.26536465533405</v>
+        <v>18.695296182255323</v>
       </c>
       <c r="O49" s="2">
-        <v>63.29113924050633</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>64.68354430379748</v>
+        <v>64.81012658227849</v>
       </c>
       <c r="R49" s="2">
-        <v>54.43037974683544</v>
+        <v>56.20253164556962</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.89</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5131,19 +5134,19 @@
         <v>5.72</v>
       </c>
       <c r="F50" s="2">
-        <v>0.4359576087806115</v>
+        <v>0.33209265828338874</v>
       </c>
       <c r="G50" s="2">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="H50" s="2">
-        <v>62.87</v>
+        <v>59.57</v>
       </c>
       <c r="I50" s="2">
-        <v>124.93</v>
+        <v>116.46</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06731672956555627</v>
+        <v>0.06953842510636646</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
@@ -5152,10 +5155,10 @@
         <v>209</v>
       </c>
       <c r="M50" s="2">
-        <v>0.7106427465908749</v>
+        <v>0.5808392444065911</v>
       </c>
       <c r="N50" s="2">
-        <v>81.94945815231118</v>
+        <v>68.10664336595416</v>
       </c>
       <c r="O50" s="2">
         <v>89.87341772151899</v>
@@ -5164,16 +5167,16 @@
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>73.67088607594935</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="R50" s="2">
-        <v>61.26582278481011</v>
+        <v>61.39240506329113</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-2.28</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5193,49 +5196,49 @@
         <v>4.31</v>
       </c>
       <c r="F51" s="2">
-        <v>0.0656973192951211</v>
+        <v>0.02457684635630672</v>
       </c>
       <c r="G51" s="2">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="H51" s="2">
-        <v>48.39</v>
+        <v>46.79</v>
       </c>
       <c r="I51" s="2">
-        <v>55.24</v>
+        <v>52.6</v>
       </c>
       <c r="J51" s="2">
-        <v>0.019165180803654598</v>
+        <v>0.01887449509550755</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M51" s="2">
-        <v>0.17066628267261463</v>
+        <v>0.11942266696443427</v>
       </c>
       <c r="N51" s="2">
-        <v>27.951811760485167</v>
+        <v>21.96498562173847</v>
       </c>
       <c r="O51" s="2">
-        <v>74.68354430379746</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P51" s="2">
         <v>16.096535574030653</v>
       </c>
       <c r="Q51" s="2">
-        <v>60.75949367088607</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="R51" s="2">
-        <v>56.265822784810126</v>
+        <v>54.87341772151899</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-6.77</v>
+        <v>-8.16</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5255,19 +5258,19 @@
         <v>6.03</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.35901040969479636</v>
+        <v>-0.3448639226079545</v>
       </c>
       <c r="G52" s="3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H52" s="3">
-        <v>49.19</v>
+        <v>52.72</v>
       </c>
       <c r="I52" s="3">
-        <v>-18.79</v>
+        <v>-16.24</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.03732890815529442</v>
+        <v>-0.03458856370187141</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
@@ -5276,28 +5279,28 @@
         <v>-1</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.305054400482066</v>
+        <v>-0.29654624041136124</v>
       </c>
       <c r="N52" s="3">
-        <v>-19.620256554982905</v>
+        <v>-19.63190511584108</v>
       </c>
       <c r="O52" s="3">
-        <v>5.063291139240507</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P52" s="3">
         <v>45.32019556900826</v>
       </c>
       <c r="Q52" s="3">
-        <v>40.88607594936709</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="R52" s="3">
-        <v>22.34177215189873</v>
+        <v>23.10126582278481</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T52" s="3">
-        <v>0.57</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5317,19 +5320,19 @@
         <v>37.01</v>
       </c>
       <c r="F53" s="1">
-        <v>0.1186910887087767</v>
+        <v>0.10597560752549204</v>
       </c>
       <c r="G53" s="1">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="H53" s="1">
-        <v>61.51</v>
+        <v>58.17</v>
       </c>
       <c r="I53" s="1">
-        <v>45.1</v>
+        <v>39.33</v>
       </c>
       <c r="J53" s="1">
-        <v>0.01994816170035744</v>
+        <v>0.02574109483902342</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
@@ -5338,28 +5341,28 @@
         <v>95</v>
       </c>
       <c r="M53" s="1">
-        <v>0.2511285658672966</v>
+        <v>0.22945412869456372</v>
       </c>
       <c r="N53" s="1">
-        <v>35.99804007995336</v>
+        <v>32.96813179475143</v>
       </c>
       <c r="O53" s="1">
-        <v>83.54430379746836</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>52.53164556962026</v>
+        <v>52.91139240506329</v>
       </c>
       <c r="R53" s="1">
-        <v>42.468354430379755</v>
+        <v>42.84810126582279</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>15.82</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5373,25 +5376,25 @@
         <v>60.75949367088608</v>
       </c>
       <c r="D54" s="2">
-        <v>6.560377358490567</v>
+        <v>6.598113207547171</v>
       </c>
       <c r="E54" s="2">
         <v>-0.82</v>
       </c>
       <c r="F54" s="2">
-        <v>0.12984801850782104</v>
+        <v>0.10120144890343571</v>
       </c>
       <c r="G54" s="2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H54" s="2">
-        <v>68.77</v>
+        <v>66.57</v>
       </c>
       <c r="I54" s="2">
-        <v>70.15</v>
+        <v>67.22</v>
       </c>
       <c r="J54" s="2">
-        <v>0.03438095878036791</v>
+        <v>0.037186109509096</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
@@ -5400,28 +5403,28 @@
         <v>298</v>
       </c>
       <c r="M54" s="2">
-        <v>0.2122535598509001</v>
+        <v>0.17815183166097315</v>
       </c>
       <c r="N54" s="2">
-        <v>32.11053947831372</v>
+        <v>27.83790209139237</v>
       </c>
       <c r="O54" s="2">
-        <v>81.0126582278481</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>68.73417721518987</v>
+        <v>69.11392405063292</v>
       </c>
       <c r="R54" s="2">
-        <v>58.797468354430386</v>
+        <v>58.037974683544306</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>2.03</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5435,25 +5438,25 @@
         <v>17.72151898734177</v>
       </c>
       <c r="D55" s="1">
-        <v>10.605633802816902</v>
+        <v>10.056338028169014</v>
       </c>
       <c r="E55" s="1">
         <v>6.07</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.025757463753413257</v>
+        <v>0.05248404262112047</v>
       </c>
       <c r="G55" s="1">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H55" s="1">
-        <v>62.18</v>
+        <v>65.48</v>
       </c>
       <c r="I55" s="1">
-        <v>-13.92</v>
+        <v>-9.98</v>
       </c>
       <c r="J55" s="1">
-        <v>0.0171254337680704</v>
+        <v>0.02199521827200483</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5462,28 +5465,28 @@
         <v>-16</v>
       </c>
       <c r="M55" s="1">
-        <v>0.1292434354395211</v>
+        <v>0.19564754542584128</v>
       </c>
       <c r="N55" s="1">
-        <v>23.809527037175812</v>
+        <v>29.58747346787918</v>
       </c>
       <c r="O55" s="1">
-        <v>69.62025316455697</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P55" s="1">
         <v>47.39629233644822</v>
       </c>
       <c r="Q55" s="1">
-        <v>47.721518987341774</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R55" s="1">
-        <v>39.24050632911393</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>4.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5503,49 +5506,49 @@
         <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>0.14967699611604698</v>
+        <v>0.022402888636216478</v>
       </c>
       <c r="G56" s="2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H56" s="2">
-        <v>69.1</v>
+        <v>63.6</v>
       </c>
       <c r="I56" s="2">
-        <v>18.25</v>
+        <v>14.55</v>
       </c>
       <c r="J56" s="2">
-        <v>0.029452125755517783</v>
+        <v>0.03219276760462638</v>
       </c>
       <c r="K56" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2">
         <v>13</v>
       </c>
       <c r="M56" s="2">
-        <v>0.19578485853419836</v>
+        <v>0.06535193947763274</v>
       </c>
       <c r="N56" s="2">
-        <v>30.46366934664354</v>
+        <v>16.55791287305832</v>
       </c>
       <c r="O56" s="2">
-        <v>78.48101265822784</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q56" s="2">
-        <v>67.46835443037975</v>
+        <v>66.70886075949367</v>
       </c>
       <c r="R56" s="2">
-        <v>56.96202531645569</v>
+        <v>53.291139240506325</v>
       </c>
       <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T56" s="2">
-        <v>4.3</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5565,49 +5568,49 @@
         <v>-1.23</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.09394437438533337</v>
+        <v>-0.12953683039746422</v>
       </c>
       <c r="G57" s="1">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H57" s="1">
-        <v>55.39</v>
+        <v>47.32</v>
       </c>
       <c r="I57" s="1">
-        <v>0.82</v>
+        <v>-1.35</v>
       </c>
       <c r="J57" s="1">
-        <v>0.007351543994161778</v>
+        <v>0.007833236236756675</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.0733429890495636</v>
+        <v>-0.11164139254687411</v>
       </c>
       <c r="N57" s="1">
-        <v>3.5508845882673348</v>
+        <v>-1.141420329392365</v>
       </c>
       <c r="O57" s="1">
-        <v>44.303797468354425</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>52.02531645569621</v>
+        <v>49.11392405063292</v>
       </c>
       <c r="R57" s="1">
-        <v>42.088607594936704</v>
+        <v>40.82278481012658</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>5.51</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5627,31 +5630,31 @@
         <v>1.28</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.10261026700599486</v>
+        <v>-0.09062786773933754</v>
       </c>
       <c r="G58" s="1">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>50.64</v>
+        <v>52.43</v>
       </c>
       <c r="I58" s="1">
-        <v>9.07</v>
+        <v>9.45</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.00488985150967395</v>
+        <v>-0.004836146806834635</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.17422460650652782</v>
+        <v>-0.1568409877865209</v>
       </c>
       <c r="N58" s="1">
-        <v>-6.537277157429093</v>
+        <v>-5.661379853357042</v>
       </c>
       <c r="O58" s="1">
         <v>30.37974683544304</v>
@@ -5660,16 +5663,16 @@
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>46.58227848101265</v>
+        <v>45.82278481012658</v>
       </c>
       <c r="R58" s="1">
-        <v>36.392405063291136</v>
+        <v>35.63291139240506</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5683,25 +5686,25 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D59" s="2">
-        <v>2.4079320113314453</v>
+        <v>2.4258734655335226</v>
       </c>
       <c r="E59" s="2">
         <v>-1.3</v>
       </c>
       <c r="F59" s="2">
-        <v>0.9372296258301339</v>
+        <v>0.967263257879577</v>
       </c>
       <c r="G59" s="2">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="H59" s="2">
-        <v>74.86</v>
+        <v>76.45</v>
       </c>
       <c r="I59" s="2">
-        <v>174.41</v>
+        <v>180.89</v>
       </c>
       <c r="J59" s="2">
-        <v>0.07298465613947767</v>
+        <v>0.0791856725928882</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
@@ -5710,10 +5713,10 @@
         <v>370</v>
       </c>
       <c r="M59" s="2">
-        <v>1.0343504424130485</v>
+        <v>1.0638986222727636</v>
       </c>
       <c r="N59" s="2">
-        <v>114.32022773452854</v>
+        <v>116.41258115257138</v>
       </c>
       <c r="O59" s="2">
         <v>94.9367088607595</v>
@@ -5722,16 +5725,16 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>81.0126582278481</v>
+        <v>81.51898734177216</v>
       </c>
       <c r="R59" s="2">
-        <v>67.53164556962025</v>
+        <v>67.65822784810126</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T59" s="2">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -5751,19 +5754,19 @@
         <v>-0.04</v>
       </c>
       <c r="F60" s="2">
-        <v>0.08834431504569398</v>
+        <v>0.06071532254390745</v>
       </c>
       <c r="G60" s="2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H60" s="2">
-        <v>55.76</v>
+        <v>49.11</v>
       </c>
       <c r="I60" s="2">
-        <v>44.05</v>
+        <v>38.5</v>
       </c>
       <c r="J60" s="2">
-        <v>0.021325035352015107</v>
+        <v>0.021713824423646638</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
@@ -5772,19 +5775,19 @@
         <v>365</v>
       </c>
       <c r="M60" s="2">
-        <v>0.10796468203214138</v>
+        <v>0.07771598850196804</v>
       </c>
       <c r="N60" s="2">
-        <v>21.68165169643784</v>
+        <v>17.794317775491848</v>
       </c>
       <c r="O60" s="2">
-        <v>67.08860759493672</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P60" s="2">
         <v>11.981421797928204</v>
       </c>
       <c r="Q60" s="2">
-        <v>60.12658227848101</v>
+        <v>57.59493670886076</v>
       </c>
       <c r="R60" s="2">
         <v>53.29113924050634</v>
@@ -5813,40 +5816,40 @@
         <v>0.85</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.1887624565948784</v>
+        <v>-0.17053382495079067</v>
       </c>
       <c r="G61" s="3">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H61" s="3">
-        <v>35.21</v>
+        <v>40.8</v>
       </c>
       <c r="I61" s="3">
-        <v>-3.31</v>
+        <v>-1.95</v>
       </c>
       <c r="J61" s="3">
-        <v>-0.007285711481955117</v>
+        <v>-0.0071436782649213606</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L61" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.2495855942528653</v>
+        <v>-0.22690445418014948</v>
       </c>
       <c r="N61" s="3">
-        <v>-14.073375932062834</v>
+        <v>-12.667726492719897</v>
       </c>
       <c r="O61" s="3">
-        <v>15.18987341772152</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P61" s="3">
         <v>14.552180197083512</v>
       </c>
       <c r="Q61" s="3">
-        <v>34.936708860759495</v>
+        <v>34.810126582278485</v>
       </c>
       <c r="R61" s="3">
         <v>26.26582278481013</v>
@@ -5869,55 +5872,55 @@
         <v>92.40506329113924</v>
       </c>
       <c r="D62" s="1">
-        <v>0.552974504249292</v>
+        <v>0.5331444759206799</v>
       </c>
       <c r="E62" s="1">
         <v>-0.19</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.2820391521563683</v>
+        <v>-0.2450517623307163</v>
       </c>
       <c r="G62" s="1">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="H62" s="1">
-        <v>32.91</v>
+        <v>33.08</v>
       </c>
       <c r="I62" s="1">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.00832271834079009</v>
+        <v>-0.008392615499502975</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L62" s="1">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.2879252622523025</v>
+        <v>-0.2513151655784228</v>
       </c>
       <c r="N62" s="1">
-        <v>-17.907342732006565</v>
+        <v>-15.10879763254723</v>
       </c>
       <c r="O62" s="1">
-        <v>10.126582278481013</v>
+        <v>13.924050632911392</v>
       </c>
       <c r="P62" s="1">
         <v>20.131624188012864</v>
       </c>
       <c r="Q62" s="1">
-        <v>45.69620253164557</v>
+        <v>45.44303797468354</v>
       </c>
       <c r="R62" s="1">
-        <v>31.962025316455687</v>
+        <v>33.101265822784804</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-10.89</v>
+        <v>-9.75</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5931,25 +5934,25 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D63" s="4">
-        <v>4.987486965589155</v>
+        <v>4.9409106708376775</v>
       </c>
       <c r="E63" s="4">
         <v>-3.33</v>
       </c>
       <c r="F63" s="4">
-        <v>1.012694963215004</v>
+        <v>1.073080743491981</v>
       </c>
       <c r="G63" s="4">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="H63" s="4">
-        <v>68.34</v>
+        <v>68.36</v>
       </c>
       <c r="I63" s="4">
-        <v>242.37</v>
+        <v>236.84</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09039172227078207</v>
+        <v>0.09080921656329333</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
@@ -5958,28 +5961,28 @@
         <v>475</v>
       </c>
       <c r="M63" s="4">
-        <v>1.3805768442108926</v>
+        <v>1.413988834545722</v>
       </c>
       <c r="N63" s="4">
-        <v>148.94286791431298</v>
+        <v>151.42160237986727</v>
       </c>
       <c r="O63" s="4">
-        <v>97.46835443037975</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.40506329113924</v>
+        <v>82.9113924050633</v>
       </c>
       <c r="R63" s="4">
-        <v>71.51898734177216</v>
+        <v>71.7721518987342</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>-0.82</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5993,37 +5996,37 @@
         <v>79.74683544303798</v>
       </c>
       <c r="D64" s="2">
-        <v>6.3927893738140416</v>
+        <v>6.5379506641366225</v>
       </c>
       <c r="E64" s="2">
         <v>-1.41</v>
       </c>
       <c r="F64" s="2">
-        <v>0.9257530736547384</v>
+        <v>0.8697306408922579</v>
       </c>
       <c r="G64" s="2">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="H64" s="2">
-        <v>71.68</v>
+        <v>73.83</v>
       </c>
       <c r="I64" s="2">
-        <v>137</v>
+        <v>141.54</v>
       </c>
       <c r="J64" s="2">
-        <v>0.07494203297919609</v>
+        <v>0.07804193826126511</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L64" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M64" s="2">
-        <v>1.0267979636349425</v>
+        <v>0.9636816896078559</v>
       </c>
       <c r="N64" s="2">
-        <v>113.56497985671797</v>
+        <v>106.39088788608065</v>
       </c>
       <c r="O64" s="2">
         <v>93.67088607594937</v>
@@ -6035,13 +6038,13 @@
         <v>77.59493670886076</v>
       </c>
       <c r="R64" s="2">
-        <v>67.15189873417722</v>
+        <v>67.0253164556962</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T64" s="2">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -6061,19 +6064,19 @@
         <v>0.14</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.1458367488545128</v>
+        <v>-0.1324694381762026</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>49.27</v>
+        <v>50.38</v>
       </c>
       <c r="I65" s="1">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.010406491238242494</v>
+        <v>-0.010523522588461044</v>
       </c>
       <c r="K65" s="1" t="b">
         <v>1</v>
@@ -6082,28 +6085,28 @@
         <v>56</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.21450803330707868</v>
+        <v>-0.19510347065326794</v>
       </c>
       <c r="N65" s="1">
-        <v>-10.565619837484173</v>
+        <v>-9.487628140031749</v>
       </c>
       <c r="O65" s="1">
-        <v>18.9873417721519</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>42.784810126582286</v>
+        <v>42.025316455696206</v>
       </c>
       <c r="R65" s="1">
-        <v>31.645569620253163</v>
+        <v>32.025316455696206</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-5.76</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6117,55 +6120,55 @@
         <v>87.34177215189874</v>
       </c>
       <c r="D66" s="3">
-        <v>-0.11387038158691706</v>
+        <v>-0.1144760751059965</v>
       </c>
       <c r="E66" s="3">
         <v>1.66</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.25941380854434726</v>
+        <v>-0.29033986720615956</v>
       </c>
       <c r="G66" s="3">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H66" s="3">
-        <v>30.56</v>
+        <v>31.76</v>
       </c>
       <c r="I66" s="3">
-        <v>-45.34</v>
+        <v>-44.51</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.025741113849072836</v>
+        <v>-0.029288516712837352</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L66" s="3">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.26039482689366966</v>
+        <v>-0.2930241828837481</v>
       </c>
       <c r="N66" s="3">
-        <v>-15.15429919614327</v>
+        <v>-19.279699363079757</v>
       </c>
       <c r="O66" s="3">
-        <v>11.39240506329114</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P66" s="3">
         <v>54.854261650729526</v>
       </c>
       <c r="Q66" s="3">
-        <v>32.27848101265823</v>
+        <v>32.40506329113924</v>
       </c>
       <c r="R66" s="3">
-        <v>19.873417721518983</v>
+        <v>19.11392405063291</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="3">
-        <v>-9.18</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6185,19 +6188,19 @@
         <v>-0.68</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.1402380189076255</v>
+        <v>-0.14069347377103392</v>
       </c>
       <c r="G67" s="1">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H67" s="1">
-        <v>35.91</v>
+        <v>38.44</v>
       </c>
       <c r="I67" s="1">
-        <v>-16.51</v>
+        <v>-15.69</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.000870451920174501</v>
+        <v>-0.0019967834944604667</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
@@ -6206,28 +6209,28 @@
         <v>-76</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.12650376201711233</v>
+        <v>-0.12906143916815038</v>
       </c>
       <c r="N67" s="1">
-        <v>-1.765192708487536</v>
+        <v>-2.8834249915199854</v>
       </c>
       <c r="O67" s="1">
-        <v>40.50632911392405</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>45.31645569620254</v>
+        <v>44.55696202531645</v>
       </c>
       <c r="R67" s="1">
-        <v>40.69620253164557</v>
+        <v>38.67088607594937</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-3.42</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6247,31 +6250,31 @@
         <v>-0.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.13733929043426288</v>
+        <v>-0.13156345071281003</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>51.13</v>
+        <v>51.02</v>
       </c>
       <c r="I68" s="1">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.010449013617032257</v>
+        <v>-0.009799406985092737</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.20306751983886162</v>
+        <v>-0.19151316751228686</v>
       </c>
       <c r="N68" s="1">
-        <v>-9.421568490662466</v>
+        <v>-9.128597825933635</v>
       </c>
       <c r="O68" s="1">
         <v>22.78481012658228</v>
@@ -6280,7 +6283,7 @@
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>61.64556962025317</v>
+        <v>61.51898734177216</v>
       </c>
       <c r="R68" s="1">
         <v>46.77215189873418</v>
@@ -6303,55 +6306,55 @@
         <v>72.15189873417721</v>
       </c>
       <c r="D69" s="3">
-        <v>0.6286407766990291</v>
+        <v>0.6262135922330098</v>
       </c>
       <c r="E69" s="3">
         <v>-0.24</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.27307082850125447</v>
+        <v>-0.31628018404673813</v>
       </c>
       <c r="G69" s="3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H69" s="3">
-        <v>43.82</v>
+        <v>36.33</v>
       </c>
       <c r="I69" s="3">
-        <v>-11.93</v>
+        <v>-15.54</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.009464380736295156</v>
+        <v>-0.010046907446086535</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L69" s="3">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.22500092938445837</v>
+        <v>-0.2733311332053219</v>
       </c>
       <c r="N69" s="3">
-        <v>-11.614909445222144</v>
+        <v>-17.310394395237143</v>
       </c>
       <c r="O69" s="3">
-        <v>17.72151898734177</v>
+        <v>11.39240506329114</v>
       </c>
       <c r="P69" s="3">
-        <v>29.145649851223904</v>
+        <v>29.40035337282439</v>
       </c>
       <c r="Q69" s="3">
-        <v>39.24050632911393</v>
+        <v>36.582278481012665</v>
       </c>
       <c r="R69" s="3">
-        <v>27.08860759493671</v>
+        <v>24.68354430379747</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-0.63</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -6371,49 +6374,49 @@
         <v>-1.55</v>
       </c>
       <c r="F70" s="3">
-        <v>-0.2258778303740458</v>
+        <v>-0.19957937754053331</v>
       </c>
       <c r="G70" s="3">
         <v>0.86</v>
       </c>
       <c r="H70" s="3">
-        <v>39.75</v>
+        <v>45.27</v>
       </c>
       <c r="I70" s="3">
-        <v>-14.89</v>
+        <v>-13.36</v>
       </c>
       <c r="J70" s="3">
-        <v>-0.008305606873988663</v>
+        <v>-0.00631916762307576</v>
       </c>
       <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="M70" s="3">
-        <v>-0.23961208726455896</v>
+        <v>-0.2121061840359464</v>
       </c>
       <c r="N70" s="3">
-        <v>-13.0760252332322</v>
+        <v>-11.187899478299594</v>
       </c>
       <c r="O70" s="3">
-        <v>16.455696202531644</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P70" s="3">
         <v>31.450467124868602</v>
       </c>
       <c r="Q70" s="3">
-        <v>39.36708860759494</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="R70" s="3">
-        <v>26.9620253164557</v>
+        <v>28.60759493670886</v>
       </c>
       <c r="S70" s="3" t="s">
         <v>103</v>
       </c>
       <c r="T70" s="3">
-        <v>-0.76</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6433,19 +6436,19 @@
         <v>-0.71</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.41942260100356543</v>
+        <v>-0.3857278835782391</v>
       </c>
       <c r="G71" s="3">
         <v>1.12</v>
       </c>
       <c r="H71" s="3">
-        <v>53.19</v>
+        <v>59.12</v>
       </c>
       <c r="I71" s="3">
-        <v>-26.89</v>
+        <v>-25.03</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.023595020204156474</v>
+        <v>-0.02148246863470858</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
@@ -6454,90 +6457,90 @@
         <v>-99</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.407650380811697</v>
+        <v>-0.37499062086788504</v>
       </c>
       <c r="N71" s="3">
-        <v>-29.87985458794601</v>
+        <v>-27.47634316149346</v>
       </c>
       <c r="O71" s="3">
-        <v>1.2658227848101267</v>
+        <v>2.5316455696202533</v>
       </c>
       <c r="P71" s="3">
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>41.265822784810126</v>
+        <v>42.78481012658227</v>
       </c>
       <c r="R71" s="3">
-        <v>22.658227848101266</v>
+        <v>23.037974683544302</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>118</v>
       </c>
       <c r="T71" s="3">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="1">
         <v>10.42</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="1">
         <v>78.48101265822784</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="1">
         <v>0.21976967370441466</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="1">
         <v>-0.66</v>
       </c>
-      <c r="F72" s="3">
-        <v>-0.2692151307705016</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="F72" s="1">
+        <v>-0.2450982890424066</v>
+      </c>
+      <c r="G72" s="1">
         <v>1.14</v>
       </c>
-      <c r="H72" s="3">
-        <v>46.22</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-8.33</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-0.005435025521056235</v>
-      </c>
-      <c r="K72" s="3" t="b">
+      <c r="H72" s="1">
+        <v>45.15</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-8.65</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.004101937600406126</v>
+      </c>
+      <c r="K72" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="1">
         <v>2</v>
       </c>
-      <c r="M72" s="3">
-        <v>-0.2554808738799884</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-14.662903894775145</v>
-      </c>
-      <c r="O72" s="3">
-        <v>12.658227848101266</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="M72" s="1">
+        <v>-0.23257148254699356</v>
+      </c>
+      <c r="N72" s="1">
+        <v>-13.234429329404303</v>
+      </c>
+      <c r="O72" s="1">
+        <v>15.18987341772152</v>
+      </c>
+      <c r="P72" s="1">
         <v>19.739671794345924</v>
       </c>
-      <c r="Q72" s="3">
-        <v>43.54430379746835</v>
-      </c>
-      <c r="R72" s="3">
-        <v>29.81012658227848</v>
-      </c>
-      <c r="S72" s="3" t="s">
+      <c r="Q72" s="1">
+        <v>42.91139240506329</v>
+      </c>
+      <c r="R72" s="1">
+        <v>30.569620253164558</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="T72" s="3">
-        <v>2.34</v>
+      <c r="T72" s="1">
+        <v>3.1</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6557,19 +6560,19 @@
         <v>3.07</v>
       </c>
       <c r="F73" s="2">
-        <v>0.430098566861153</v>
+        <v>0.3947015317376794</v>
       </c>
       <c r="G73" s="2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H73" s="2">
-        <v>70.29</v>
+        <v>65.33</v>
       </c>
       <c r="I73" s="2">
-        <v>47.83</v>
+        <v>45.36</v>
       </c>
       <c r="J73" s="2">
-        <v>0.03206985463415866</v>
+        <v>0.0323241834550241</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
@@ -6578,28 +6581,28 @@
         <v>29</v>
       </c>
       <c r="M73" s="2">
-        <v>0.4477568971489556</v>
+        <v>0.41170219769574</v>
       </c>
       <c r="N73" s="2">
-        <v>55.660873208119256</v>
+        <v>51.19293869486904</v>
       </c>
       <c r="O73" s="2">
-        <v>88.60759493670885</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>67.72151898734177</v>
+        <v>66.83544303797468</v>
       </c>
       <c r="R73" s="2">
-        <v>62.53164556962025</v>
+        <v>62.151898734177216</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6619,19 +6622,19 @@
         <v>1.29</v>
       </c>
       <c r="F74" s="2">
-        <v>0.17690607815481968</v>
+        <v>0.16879989826501837</v>
       </c>
       <c r="G74" s="2">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="H74" s="2">
         <v>80.86</v>
       </c>
       <c r="I74" s="2">
-        <v>30</v>
+        <v>29.69</v>
       </c>
       <c r="J74" s="2">
-        <v>0.014981395306821884</v>
+        <v>0.014654803180689104</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>1</v>
@@ -6640,28 +6643,28 @@
         <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.1563046928190499</v>
+        <v>0.14911491662936927</v>
       </c>
       <c r="N74" s="2">
-        <v>26.515652775128686</v>
+        <v>24.934210588231974</v>
       </c>
       <c r="O74" s="2">
-        <v>72.15189873417721</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>63.797468354430386</v>
+        <v>63.54430379746836</v>
       </c>
       <c r="R74" s="2">
-        <v>55.88607594936709</v>
+        <v>56.8987341772152</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>-0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6681,19 +6684,19 @@
         <v>-0.35</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.0075277886482870565</v>
+        <v>-0.05524168805004072</v>
       </c>
       <c r="G75" s="1">
         <v>0.97</v>
       </c>
       <c r="H75" s="1">
-        <v>60.1</v>
+        <v>54.77</v>
       </c>
       <c r="I75" s="1">
-        <v>16.11</v>
+        <v>13.34</v>
       </c>
       <c r="J75" s="1">
-        <v>0.0184885903071271</v>
+        <v>0.021000318728723905</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6702,28 +6705,28 @@
         <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>-0.010470843696254173</v>
+        <v>-0.05792600372762924</v>
       </c>
       <c r="N75" s="1">
-        <v>9.838099123598278</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="O75" s="1">
-        <v>53.16455696202531</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>60.88607594936708</v>
+        <v>59.36708860759494</v>
       </c>
       <c r="R75" s="1">
-        <v>43.67088607594937</v>
+        <v>42.911392405063296</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>-2.78</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6743,19 +6746,19 @@
         <v>0.91</v>
       </c>
       <c r="F76" s="1">
-        <v>-0.004645609480755375</v>
+        <v>0.014555667701142291</v>
       </c>
       <c r="G76" s="1">
         <v>0.7</v>
       </c>
       <c r="H76" s="1">
-        <v>43.47</v>
+        <v>44.28</v>
       </c>
       <c r="I76" s="1">
-        <v>6.76</v>
+        <v>7.02</v>
       </c>
       <c r="J76" s="1">
-        <v>0.010323245621496727</v>
+        <v>0.00960619105056567</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6764,28 +6767,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.034076159960426455</v>
+        <v>-0.012287489074742863</v>
       </c>
       <c r="N76" s="1">
-        <v>7.477567497181051</v>
+        <v>8.79397001782077</v>
       </c>
       <c r="O76" s="1">
-        <v>51.89873417721519</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>44.43037974683544</v>
+        <v>44.177215189873415</v>
       </c>
       <c r="R76" s="1">
-        <v>40.253164556962034</v>
+        <v>42.27848101265823</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>-1.96</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6805,19 +6808,19 @@
         <v>2.54</v>
       </c>
       <c r="F77" s="2">
-        <v>0.0658963128082876</v>
+        <v>0.0618202237627693</v>
       </c>
       <c r="G77" s="2">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H77" s="2">
-        <v>69.39</v>
+        <v>69.72</v>
       </c>
       <c r="I77" s="2">
-        <v>16.17</v>
+        <v>16.24</v>
       </c>
       <c r="J77" s="2">
-        <v>0.01502370831594207</v>
+        <v>0.016732283036046857</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6826,28 +6829,28 @@
         <v>6</v>
       </c>
       <c r="M77" s="2">
-        <v>0.06393427610964286</v>
+        <v>0.06092545187023979</v>
       </c>
       <c r="N77" s="2">
-        <v>17.27861110418799</v>
+        <v>16.115264112319018</v>
       </c>
       <c r="O77" s="2">
-        <v>62.0253164556962</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>65.0632911392405</v>
+        <v>65.69620253164557</v>
       </c>
       <c r="R77" s="2">
-        <v>55.379746835443036</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6867,49 +6870,49 @@
         <v>0.76</v>
       </c>
       <c r="F78" s="1">
-        <v>0.10534970344951694</v>
+        <v>0.10766923403081889</v>
       </c>
       <c r="G78" s="1">
         <v>1.24</v>
       </c>
       <c r="H78" s="1">
-        <v>60.72</v>
+        <v>60.71</v>
       </c>
       <c r="I78" s="1">
-        <v>29.59</v>
+        <v>29.19</v>
       </c>
       <c r="J78" s="1">
-        <v>0.023533739794426568</v>
+        <v>0.02351360039616708</v>
       </c>
       <c r="K78" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L78" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M78" s="1">
-        <v>0.12889414383325382</v>
+        <v>0.129143759451527</v>
       </c>
       <c r="N78" s="1">
-        <v>23.77459787654908</v>
+        <v>22.937094870447748</v>
       </c>
       <c r="O78" s="1">
-        <v>68.35443037974683</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P78" s="1">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="1">
-        <v>57.72151898734178</v>
+        <v>57.34177215189874</v>
       </c>
       <c r="R78" s="1">
-        <v>48.41772151898734</v>
+        <v>49.683544303797476</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="1">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6929,49 +6932,49 @@
         <v>0.81</v>
       </c>
       <c r="F79" s="2">
-        <v>0.4084245033935695</v>
+        <v>0.41407491791311823</v>
       </c>
       <c r="G79" s="2">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H79" s="2">
-        <v>75.76</v>
+        <v>76.77</v>
       </c>
       <c r="I79" s="2">
-        <v>51.46</v>
+        <v>52.71</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0457991158639314</v>
+        <v>0.0457547866299621</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L79" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M79" s="2">
-        <v>0.4054814483456024</v>
+        <v>0.4122853741280592</v>
       </c>
       <c r="N79" s="2">
-        <v>51.43332832778395</v>
+        <v>51.25125633810097</v>
       </c>
       <c r="O79" s="2">
-        <v>87.34177215189874</v>
+        <v>88.60759493670885</v>
       </c>
       <c r="P79" s="2">
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>65.44303797468353</v>
+        <v>65.56962025316456</v>
       </c>
       <c r="R79" s="2">
-        <v>58.734177215189874</v>
+        <v>58.9873417721519</v>
       </c>
       <c r="S79" s="2" t="s">
         <v>113</v>
       </c>
       <c r="T79" s="2">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -6985,25 +6988,25 @@
         <v>75.9493670886076</v>
       </c>
       <c r="D80" s="2">
-        <v>0.7889908256880732</v>
+        <v>0.7993119266055044</v>
       </c>
       <c r="E80" s="2">
         <v>-1.21</v>
       </c>
       <c r="F80" s="2">
-        <v>1.4322648073628779</v>
+        <v>1.3643470019048707</v>
       </c>
       <c r="G80" s="2">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H80" s="2">
-        <v>78.16</v>
+        <v>78.2</v>
       </c>
       <c r="I80" s="2">
-        <v>101.87</v>
+        <v>100.92</v>
       </c>
       <c r="J80" s="2">
-        <v>0.06156727370708342</v>
+        <v>0.0671896932162768</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>1</v>
@@ -7012,28 +7015,28 @@
         <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>1.438150917458812</v>
+        <v>1.3723999489376362</v>
       </c>
       <c r="N80" s="2">
-        <v>154.7002752391049</v>
+        <v>147.26271381905866</v>
       </c>
       <c r="O80" s="2">
-        <v>98.73417721518987</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P80" s="2">
         <v>13.172294180200911</v>
       </c>
       <c r="Q80" s="2">
-        <v>71.89873417721519</v>
+        <v>71.77215189873417</v>
       </c>
       <c r="R80" s="2">
-        <v>66.7721518987342</v>
+        <v>66.26582278481013</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
     </row>
   </sheetData>
@@ -7052,7 +7055,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7060,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>33.037974683544306</v>
+        <v>32.40506329113924</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7068,7 +7071,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>64.87341772151899</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7076,7 +7079,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>27.53164556962025</v>
+        <v>26.582278481012654</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7084,7 +7087,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>44.620253164556964</v>
+        <v>46.64556962025316</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7095,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>40.50632911392405</v>
+        <v>38.9873417721519</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7100,7 +7103,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.21518987341773</v>
+        <v>52.46835443037975</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7108,7 +7111,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>54.936708860759495</v>
+        <v>54.43037974683544</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7119,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>40.37974683544304</v>
+        <v>37.46835443037974</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7124,7 +7127,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>37.27848101265823</v>
+        <v>38.037974683544306</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7132,7 +7135,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>53.16455696202532</v>
+        <v>52.78481012658228</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7140,7 +7143,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>38.734177215189874</v>
+        <v>37.59493670886076</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7148,7 +7151,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.4810126582278462</v>
+        <v>3.6075949367088596</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7156,7 +7159,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>48.67088607594937</v>
+        <v>46.64556962025316</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7172,7 +7175,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>24.746835443037973</v>
+        <v>30.189873417721518</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7180,7 +7183,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18.607594936708864</v>
+        <v>22.531645569620252</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7191,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>30.063291139240512</v>
+        <v>28.54430379746836</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7196,7 +7199,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>41.58227848101266</v>
+        <v>43.607594936708864</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -7204,7 +7207,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>41.962025316455694</v>
+        <v>43.48101265822784</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7212,7 +7215,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>54.050632911392405</v>
+        <v>55.44303797468355</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7220,7 +7223,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>33.60759493670886</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7228,7 +7231,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34.24050632911393</v>
+        <v>35.00000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7239,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>26.075949367088608</v>
+        <v>21.39240506329114</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7244,7 +7247,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3.9240506329113938</v>
+        <v>4.050632911392407</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7252,7 +7255,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33.924050632911396</v>
+        <v>34.05063291139241</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>28.9873417721519</v>
+        <v>30.126582278481024</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7268,7 +7271,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>20.44303797468354</v>
+        <v>22.088607594936704</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7276,7 +7279,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>26.708860759493668</v>
+        <v>26.32911392405063</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7284,7 +7287,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>46.0126582278481</v>
+        <v>48.54430379746835</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7300,7 +7303,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>21.582278481012658</v>
+        <v>21.32911392405063</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7311,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>41.26582278481012</v>
+        <v>40.50632911392404</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7316,7 +7319,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>49.24050632911393</v>
+        <v>50.25316455696202</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7335,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>33.67088607594937</v>
+        <v>28.481012658227844</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7340,7 +7343,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>29.683544303797472</v>
+        <v>27.658227848101266</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7348,7 +7351,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>55.696202531645575</v>
+        <v>55.56962025316456</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7356,7 +7359,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>41.835443037974684</v>
+        <v>44.24050632911393</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7364,7 +7367,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>30.69620253164556</v>
+        <v>27.468354430379748</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7372,7 +7375,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>32.53164556962026</v>
+        <v>33.29113924050633</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7383,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38.734177215189874</v>
+        <v>36.70886075949366</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7388,7 +7391,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>46.58227848101265</v>
+        <v>43.67088607594937</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7396,7 +7399,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>28.417721518987342</v>
+        <v>28.0379746835443</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7407,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>54.49367088607596</v>
+        <v>56.39240506329115</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7412,7 +7415,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>24.177215189873415</v>
+        <v>25.44303797468354</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7420,7 +7423,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>24.9367088607595</v>
+        <v>23.9240506329114</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7428,7 +7431,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>34.620253164556964</v>
+        <v>34.87341772151899</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7436,7 +7439,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>54.43037974683544</v>
+        <v>56.20253164556962</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7444,7 +7447,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>61.26582278481011</v>
+        <v>61.39240506329113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7455,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>56.265822784810126</v>
+        <v>54.87341772151899</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7460,7 +7463,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>22.34177215189873</v>
+        <v>23.10126582278481</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7468,7 +7471,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>42.468354430379755</v>
+        <v>42.84810126582279</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7479,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>58.797468354430386</v>
+        <v>58.037974683544306</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7484,7 +7487,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>39.24050632911393</v>
+        <v>42.53164556962026</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7492,7 +7495,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>56.96202531645569</v>
+        <v>53.291139240506325</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7500,7 +7503,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>42.088607594936704</v>
+        <v>40.82278481012658</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7508,7 +7511,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>36.392405063291136</v>
+        <v>35.63291139240506</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7516,7 +7519,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>67.53164556962025</v>
+        <v>67.65822784810126</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7540,7 +7543,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>31.962025316455687</v>
+        <v>33.101265822784804</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7551,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>71.51898734177216</v>
+        <v>71.7721518987342</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7556,7 +7559,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>67.15189873417722</v>
+        <v>67.0253164556962</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7564,7 +7567,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>31.645569620253163</v>
+        <v>32.025316455696206</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7572,7 +7575,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>19.873417721518983</v>
+        <v>19.11392405063291</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7580,7 +7583,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>40.69620253164557</v>
+        <v>38.67088607594937</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7599,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>27.08860759493671</v>
+        <v>24.68354430379747</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7604,7 +7607,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>26.9620253164557</v>
+        <v>28.60759493670886</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7612,7 +7615,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>22.658227848101266</v>
+        <v>23.037974683544302</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7623,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>29.81012658227848</v>
+        <v>30.569620253164558</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7628,7 +7631,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.53164556962025</v>
+        <v>62.151898734177216</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7636,7 +7639,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>55.88607594936709</v>
+        <v>56.8987341772152</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7644,7 +7647,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>43.67088607594937</v>
+        <v>42.911392405063296</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7652,7 +7655,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>40.253164556962034</v>
+        <v>42.27848101265823</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7660,7 +7663,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>55.379746835443036</v>
+        <v>56.26582278481013</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7671,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>48.41772151898734</v>
+        <v>49.683544303797476</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7676,7 +7679,7 @@
         <v>126</v>
       </c>
       <c r="B79">
-        <v>58.734177215189874</v>
+        <v>58.9873417721519</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7684,7 +7687,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>66.7721518987342</v>
+        <v>66.26582278481013</v>
       </c>
     </row>
   </sheetData>
@@ -7703,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7714,7 +7717,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7725,10 +7728,10 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
         <v>133</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7736,10 +7739,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
         <v>135</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -7747,10 +7750,10 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" t="s">
         <v>137</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7758,82 +7761,82 @@
         <v>124</v>
       </c>
       <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" t="s">
         <v>139</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
         <v>141</v>
-      </c>
-      <c r="D7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s">
         <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" t="s">
         <v>145</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
         <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
         <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" t="s">
         <v>155</v>
-      </c>
-      <c r="D14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
         <v>157</v>
-      </c>
-      <c r="D15" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7852,15 +7855,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -7868,98 +7871,98 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
         <v>143</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
         <v>147</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" t="s">
         <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
         <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
         <v>153</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" t="s">
         <v>155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -7978,10 +7981,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -7989,7 +7992,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8000,10 +8003,10 @@
         <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8011,90 +8014,90 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" t="s">
         <v>139</v>
-      </c>
-      <c r="D5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
         <v>143</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" t="s">
         <v>145</v>
-      </c>
-      <c r="D8" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
         <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
         <v>153</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" t="s">
         <v>155</v>
-      </c>
-      <c r="D13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -8113,10 +8116,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8124,7 +8127,7 @@
         <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -8132,106 +8135,106 @@
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s">
         <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" t="s">
         <v>145</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
         <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
         <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
         <v>153</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14" t="s">
         <v>155</v>
-      </c>
-      <c r="D14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -8247,212 +8250,212 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" t="s">
         <v>175</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>176</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>177</v>
-      </c>
-      <c r="D1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
         <v>179</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>180</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>181</v>
-      </c>
-      <c r="D2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
         <v>183</v>
       </c>
-      <c r="B3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" t="s">
-        <v>184</v>
-      </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" t="s">
         <v>185</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>186</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>187</v>
-      </c>
-      <c r="D4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" t="s">
         <v>189</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>190</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>191</v>
-      </c>
-      <c r="D5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
         <v>193</v>
       </c>
-      <c r="B6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>194</v>
-      </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" t="s">
         <v>195</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>196</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" t="s">
         <v>200</v>
       </c>
-      <c r="B9" t="s">
-        <v>201</v>
-      </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" t="s">
         <v>202</v>
       </c>
-      <c r="B11" t="s">
-        <v>203</v>
-      </c>
       <c r="C11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" t="s">
         <v>204</v>
       </c>
-      <c r="B12" t="s">
-        <v>205</v>
-      </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" t="s">
         <v>206</v>
       </c>
-      <c r="B13" t="s">
-        <v>207</v>
-      </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" t="s">
         <v>208</v>
       </c>
-      <c r="B14" t="s">
-        <v>209</v>
-      </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" t="s">
         <v>210</v>
       </c>
-      <c r="B15" t="s">
-        <v>211</v>
-      </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="230">
   <si>
     <t>Ticker</t>
   </si>
@@ -343,7 +343,7 @@
     <t>2026-04-29</t>
   </si>
   <si>
-    <t>2026-04-28</t>
+    <t>2027-04-28</t>
   </si>
   <si>
     <t>2026-05-07</t>
@@ -667,7 +667,7 @@
     <t>Momentum Breakout, Market Leader, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Market Leader, Stable Uptrend, Earnings Upcoming, Volume Spike, Institutional Buying</t>
+    <t>Momentum Breakout, Market Leader, Stable Uptrend, Volume Spike, Institutional Buying</t>
   </si>
   <si>
     <t>Momentum Breakout, Market Leader, Stable Uptrend, Institutional Buying</t>
@@ -679,28 +679,31 @@
     <t>Momentum Breakout, Institutional Buying</t>
   </si>
   <si>
+    <t>Momentum Breakout, Market Leader, Earnings Upcoming</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
   </si>
   <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
     <t>Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
-    <t>Momentum Breakout, Earnings Upcoming, Volume Spike, Institutional Buying</t>
+    <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
     <t>Volume Spike</t>
+  </si>
+  <si>
+    <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
     <t>Earnings Upcoming</t>
@@ -1372,7 +1375,7 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>71.7721518987342</v>
+        <v>70.69620253164558</v>
       </c>
       <c r="C2" t="s">
         <v>213</v>
@@ -1405,7 +1408,7 @@
         <v>127</v>
       </c>
       <c r="B5">
-        <v>66.26582278481013</v>
+        <v>66.8987341772152</v>
       </c>
       <c r="C5" t="s">
         <v>215</v>
@@ -1416,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>65</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="C6" t="s">
         <v>214</v>
@@ -1435,24 +1438,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B8">
-        <v>62.151898734177216</v>
+        <v>61.51898734177215</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B9">
-        <v>61.39240506329113</v>
+        <v>61.455696202531655</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1460,7 +1463,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>59.55696202531646</v>
+        <v>59.99999999999999</v>
       </c>
       <c r="C10" t="s">
         <v>217</v>
@@ -1482,7 +1485,7 @@
         <v>53</v>
       </c>
       <c r="B12">
-        <v>58.037974683544306</v>
+        <v>58.41772151898735</v>
       </c>
       <c r="C12" t="s">
         <v>218</v>
@@ -1490,10 +1493,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="B13">
-        <v>56.8987341772152</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="C13" t="s">
         <v>219</v>
@@ -1501,32 +1504,32 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B14">
-        <v>56.39240506329115</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="B15">
-        <v>56.26582278481013</v>
+        <v>55.50632911392405</v>
       </c>
       <c r="C15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="B16">
-        <v>56.20253164556962</v>
+        <v>55.25316455696203</v>
       </c>
       <c r="C16" t="s">
         <v>221</v>
@@ -1534,10 +1537,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B17">
-        <v>55.56962025316456</v>
+        <v>54.93670886075949</v>
       </c>
       <c r="C17" t="s">
         <v>222</v>
@@ -1545,10 +1548,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="B18">
-        <v>55.44303797468355</v>
+        <v>54.87341772151898</v>
       </c>
       <c r="C18" t="s">
         <v>223</v>
@@ -1559,10 +1562,10 @@
         <v>50</v>
       </c>
       <c r="B19">
-        <v>54.87341772151899</v>
+        <v>54.49367088607596</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1570,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>54.43037974683544</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="C20" t="s">
         <v>224</v>
@@ -1578,10 +1581,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>53.29113924050634</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="C21" t="s">
         <v>221</v>
@@ -1592,21 +1595,21 @@
         <v>55</v>
       </c>
       <c r="B22">
-        <v>53.291139240506325</v>
+        <v>50.75949367088608</v>
       </c>
       <c r="C22" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="B23">
-        <v>52.78481012658228</v>
+        <v>50.75949367088608</v>
       </c>
       <c r="C23" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1614,7 +1617,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>50.25316455696202</v>
+        <v>50.253164556962034</v>
       </c>
       <c r="C24" t="s">
         <v>218</v>
@@ -1622,24 +1625,24 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>49.683544303797476</v>
+        <v>49.810126582278485</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="B26">
-        <v>48.54430379746835</v>
+        <v>48.924050632911396</v>
       </c>
       <c r="C26" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1647,10 +1650,10 @@
         <v>67</v>
       </c>
       <c r="B27">
-        <v>46.77215189873418</v>
+        <v>48.67088607594937</v>
       </c>
       <c r="C27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,32 +1661,32 @@
         <v>13</v>
       </c>
       <c r="B28">
-        <v>46.64556962025316</v>
+        <v>47.53164556962025</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B29">
-        <v>44.24050632911393</v>
+        <v>44.36708860759494</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B30">
-        <v>43.67088607594937</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="C30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1694,40 +1697,40 @@
         <v>43.607594936708864</v>
       </c>
       <c r="C31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="B32">
-        <v>43.48101265822784</v>
+        <v>43.41772151898735</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="B33">
-        <v>42.911392405063296</v>
+        <v>43.291139240506325</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>42.84810126582279</v>
+        <v>41.26582278481012</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1735,7 +1738,7 @@
         <v>54</v>
       </c>
       <c r="B35">
-        <v>42.53164556962026</v>
+        <v>40.8860759493671</v>
       </c>
       <c r="C35" t="s">
         <v>224</v>
@@ -1746,32 +1749,32 @@
         <v>123</v>
       </c>
       <c r="B36">
-        <v>42.27848101265823</v>
+        <v>40.75949367088609</v>
       </c>
       <c r="C36" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B37">
-        <v>40.50632911392404</v>
+        <v>40.44303797468355</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B38">
-        <v>38.9873417721519</v>
+        <v>39.62025316455696</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,43 +1782,43 @@
         <v>11</v>
       </c>
       <c r="B39">
-        <v>37.59493670886076</v>
+        <v>37.34177215189873</v>
       </c>
       <c r="C39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B40">
-        <v>36.70886075949366</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="C40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>35.63291139240506</v>
+        <v>36.0759493670886</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>35.00000000000001</v>
+        <v>35.75949367088607</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1823,21 +1826,21 @@
         <v>21</v>
       </c>
       <c r="B43">
-        <v>35</v>
+        <v>35.12658227848101</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>34.05063291139241</v>
+        <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,76 +1848,76 @@
         <v>40</v>
       </c>
       <c r="B45">
-        <v>33.29113924050633</v>
+        <v>34.430379746835456</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B46">
-        <v>33.101265822784804</v>
+        <v>33.54430379746835</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B47">
-        <v>32.40506329113924</v>
+        <v>33.41772151898734</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B48">
-        <v>32.025316455696206</v>
+        <v>32.46835443037974</v>
       </c>
       <c r="C48" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="B49">
-        <v>30.569620253164558</v>
+        <v>31.26582278481013</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B50">
-        <v>30.189873417721518</v>
+        <v>30.75949367088608</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B51">
-        <v>30.126582278481024</v>
+        <v>29.936708860759488</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2158,49 +2161,49 @@
         <v>0.98</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.03374324803579983</v>
+        <v>-0.039666571589430086</v>
       </c>
       <c r="G2" s="1">
         <v>0.17</v>
       </c>
       <c r="H2" s="1">
-        <v>41.87</v>
+        <v>40.7</v>
       </c>
       <c r="I2" s="1">
-        <v>12.45</v>
+        <v>11.56</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0003076157793132085</v>
+        <v>-0.0028787689020423456</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.10800931511574874</v>
+        <v>-0.12891498743218077</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.778212586279824</v>
+        <v>-1.063677557344502</v>
       </c>
       <c r="O2" s="1">
-        <v>43.037974683544306</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>37.08860759493671</v>
+        <v>35.31645569620253</v>
       </c>
       <c r="R2" s="1">
-        <v>32.40506329113924</v>
+        <v>31.26582278481013</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>-0.44</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2220,111 +2223,111 @@
         <v>-0.5</v>
       </c>
       <c r="F3" s="2">
-        <v>1.1174367115544217</v>
+        <v>1.267302437121809</v>
       </c>
       <c r="G3" s="2">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="H3" s="2">
-        <v>74.08</v>
+        <v>76.71</v>
       </c>
       <c r="I3" s="2">
-        <v>111.64</v>
+        <v>119.64</v>
       </c>
       <c r="J3" s="2">
-        <v>0.0950199165121971</v>
+        <v>0.0987216751882343</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M3" s="2">
-        <v>1.2498629516487885</v>
+        <v>1.4253689085541505</v>
       </c>
       <c r="N3" s="2">
-        <v>135.0090140901739</v>
+        <v>154.36471204128864</v>
       </c>
       <c r="O3" s="2">
-        <v>96.20253164556962</v>
+        <v>97.46835443037975</v>
       </c>
       <c r="P3" s="2">
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>75.9493670886076</v>
+        <v>76.20253164556962</v>
       </c>
       <c r="R3" s="2">
-        <v>65</v>
+        <v>65.37974683544304</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>-3.95</v>
-      </c>
-      <c r="C4" s="3">
-        <v>6.329113924050633</v>
-      </c>
-      <c r="D4" s="3">
-        <v>10.116455696202532</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B4" s="1">
+        <v>-3.51</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="D4" s="1">
+        <v>11.4985754985755</v>
+      </c>
+      <c r="E4" s="1">
         <v>-1.02</v>
       </c>
-      <c r="F4" s="3">
-        <v>-0.07789445316232181</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="1">
+        <v>0.24777214912048057</v>
+      </c>
+      <c r="G4" s="1">
         <v>1.15</v>
       </c>
-      <c r="H4" s="3">
-        <v>66.47</v>
-      </c>
-      <c r="I4" s="3">
-        <v>-13.45</v>
-      </c>
-      <c r="J4" s="3">
-        <v>-0.0035796515034801826</v>
-      </c>
-      <c r="K4" s="3" t="b">
+      <c r="H4" s="1">
+        <v>84.93</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.99</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.005926083139163227</v>
+      </c>
+      <c r="K4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="1">
         <v>-93</v>
       </c>
-      <c r="M4" s="3">
-        <v>-0.06447287477437924</v>
-      </c>
-      <c r="N4" s="3">
-        <v>3.5754314478571194</v>
-      </c>
-      <c r="O4" s="3">
-        <v>49.36708860759494</v>
-      </c>
-      <c r="P4" s="3">
+      <c r="M4" s="1">
+        <v>0.26390138089929094</v>
+      </c>
+      <c r="N4" s="1">
+        <v>38.21795927580266</v>
+      </c>
+      <c r="O4" s="1">
+        <v>83.54430379746836</v>
+      </c>
+      <c r="P4" s="1">
         <v>48.360550359989794</v>
       </c>
-      <c r="Q4" s="3">
-        <v>39.1139240506329</v>
-      </c>
-      <c r="R4" s="3">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="S4" s="3" t="s">
+      <c r="Q4" s="1">
+        <v>50.12658227848102</v>
+      </c>
+      <c r="R4" s="1">
+        <v>39.62025316455696</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="3">
-        <v>11.77</v>
+      <c r="T4" s="1">
+        <v>24.81</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2344,31 +2347,31 @@
         <v>0.34</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.11680177297247615</v>
+        <v>-0.12333577604724485</v>
       </c>
       <c r="G5" s="1">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H5" s="1">
-        <v>63.05</v>
+        <v>63.61</v>
       </c>
       <c r="I5" s="1">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0075546277074118985</v>
+        <v>0.008828072058440347</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1">
-        <v>-83</v>
+        <v>-84</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.04522002157011573</v>
+        <v>-0.036237924441668845</v>
       </c>
       <c r="N5" s="1">
-        <v>5.500716768283477</v>
+        <v>8.204028741706688</v>
       </c>
       <c r="O5" s="1">
         <v>53.16455696202531</v>
@@ -2377,16 +2380,16 @@
         <v>25.321993503429013</v>
       </c>
       <c r="Q5" s="1">
-        <v>60</v>
+        <v>59.49367088607596</v>
       </c>
       <c r="R5" s="1">
-        <v>46.64556962025316</v>
+        <v>46.77215189873417</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T5" s="1">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2406,49 +2409,49 @@
         <v>0.97</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.08963320755585905</v>
+        <v>-0.15219308933701634</v>
       </c>
       <c r="G6" s="1">
         <v>1.51</v>
       </c>
       <c r="H6" s="1">
-        <v>40.57</v>
+        <v>37.99</v>
       </c>
       <c r="I6" s="1">
-        <v>-13.99</v>
+        <v>-14.82</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.007574001660456642</v>
+        <v>-0.007407247785412419</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.04399984103685428</v>
+        <v>-0.09735370128906107</v>
       </c>
       <c r="N6" s="1">
-        <v>5.62273482160962</v>
+        <v>2.0924510569674712</v>
       </c>
       <c r="O6" s="1">
-        <v>54.43037974683544</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>36.58227848101265</v>
+        <v>35.0632911392405</v>
       </c>
       <c r="R6" s="1">
-        <v>38.9873417721519</v>
+        <v>36.45569620253165</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-3.1</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2468,19 +2471,19 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.12314970394217742</v>
+        <v>-0.0917407860061597</v>
       </c>
       <c r="G7" s="2">
         <v>2.23</v>
       </c>
       <c r="H7" s="2">
-        <v>51.04</v>
+        <v>52.59</v>
       </c>
       <c r="I7" s="2">
-        <v>13.48</v>
+        <v>14.26</v>
       </c>
       <c r="J7" s="2">
-        <v>0.017292487128875076</v>
+        <v>0.01657131978881227</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2489,28 +2492,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>-0.013092761161048294</v>
+        <v>0.040518914580085275</v>
       </c>
       <c r="N7" s="2">
-        <v>8.713442809190228</v>
+        <v>15.879712643882113</v>
       </c>
       <c r="O7" s="2">
-        <v>58.22784810126582</v>
+        <v>64.55696202531645</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>60.25316455696202</v>
+        <v>58.10126582278481</v>
       </c>
       <c r="R7" s="2">
-        <v>52.46835443037975</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>-2.09</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2530,49 +2533,49 @@
         <v>1.61</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2822861439156642</v>
+        <v>0.2537946511721644</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>61.02</v>
+        <v>59.73</v>
       </c>
       <c r="I8" s="2">
-        <v>18.03</v>
+        <v>17.34</v>
       </c>
       <c r="J8" s="2">
-        <v>0.030999849916510537</v>
+        <v>0.030440553351013474</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="M8" s="2">
-        <v>0.25096912767713153</v>
+        <v>0.21615977702160682</v>
       </c>
       <c r="N8" s="2">
-        <v>35.119631693008216</v>
+        <v>33.44379888803426</v>
       </c>
       <c r="O8" s="2">
-        <v>83.54430379746836</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>62.27848101265823</v>
+        <v>61.26582278481013</v>
       </c>
       <c r="R8" s="2">
-        <v>54.43037974683544</v>
+        <v>53.67088607594937</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.89</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2592,49 +2595,49 @@
         <v>0.88</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.15659063270382614</v>
+        <v>-0.11545601893577045</v>
       </c>
       <c r="G9" s="1">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H9" s="1">
-        <v>41.36</v>
+        <v>56.43</v>
       </c>
       <c r="I9" s="1">
-        <v>-18.27</v>
+        <v>-11.48</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.011056865217076543</v>
+        <v>-0.010764346105064788</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="1">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.1127468099698804</v>
+        <v>-0.06384247724357728</v>
       </c>
       <c r="N9" s="1">
-        <v>-1.2519620716929967</v>
+        <v>5.4435734615158395</v>
       </c>
       <c r="O9" s="1">
-        <v>39.24050632911392</v>
+        <v>49.36708860759494</v>
       </c>
       <c r="P9" s="1">
         <v>30.47019076386737</v>
       </c>
       <c r="Q9" s="1">
-        <v>42.53164556962026</v>
+        <v>46.20253164556963</v>
       </c>
       <c r="R9" s="1">
-        <v>37.46835443037974</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T9" s="1">
-        <v>-3.73</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -2654,49 +2657,49 @@
         <v>-0.77</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.14429986144444948</v>
+        <v>-0.17960778812112754</v>
       </c>
       <c r="G10" s="1">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H10" s="1">
-        <v>51.95</v>
+        <v>50.6</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.89</v>
+        <v>-4.27</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0036643652342656036</v>
+        <v>0.0037947882765627427</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="1">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.10850898574326928</v>
+        <v>-0.13552122125904587</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.828179649031884</v>
+        <v>-1.724300940031009</v>
       </c>
       <c r="O10" s="1">
-        <v>41.77215189873418</v>
+        <v>40.50632911392405</v>
       </c>
       <c r="P10" s="1">
         <v>20.24508080818123</v>
       </c>
       <c r="Q10" s="1">
-        <v>47.08860759493671</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="R10" s="1">
-        <v>38.037974683544306</v>
+        <v>37.151898734177216</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T10" s="1">
-        <v>-0.76</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2710,55 +2713,55 @@
         <v>12.658227848101266</v>
       </c>
       <c r="D11" s="2">
-        <v>31.985294117647058</v>
+        <v>31.963235294117645</v>
       </c>
       <c r="E11" s="2">
         <v>-0.88</v>
       </c>
       <c r="F11" s="2">
-        <v>0.3016185535383472</v>
+        <v>0.23464635150019414</v>
       </c>
       <c r="G11" s="2">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="H11" s="2">
-        <v>65.69</v>
+        <v>66.14</v>
       </c>
       <c r="I11" s="2">
-        <v>14.96</v>
+        <v>15.32</v>
       </c>
       <c r="J11" s="2">
-        <v>0.028352733655701592</v>
+        <v>0.027788142154114414</v>
       </c>
       <c r="K11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.28909174704293417</v>
+        <v>0.21851711972138377</v>
       </c>
       <c r="N11" s="2">
-        <v>38.93189362958847</v>
+        <v>33.67953315801196</v>
       </c>
       <c r="O11" s="2">
-        <v>84.81012658227847</v>
+        <v>82.27848101265823</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>59.24050632911393</v>
+        <v>58.35443037974684</v>
       </c>
       <c r="R11" s="2">
-        <v>52.78481012658228</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>6.33</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -2778,19 +2781,19 @@
         <v>3.81</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.06831159928225057</v>
+        <v>-0.10394058776940081</v>
       </c>
       <c r="G12" s="1">
         <v>0.88</v>
       </c>
       <c r="H12" s="1">
-        <v>60.34</v>
+        <v>65.16</v>
       </c>
       <c r="I12" s="1">
-        <v>-25.57</v>
+        <v>-21.5</v>
       </c>
       <c r="J12" s="1">
-        <v>0.01595887032593726</v>
+        <v>0.01727706612210851</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
@@ -2799,28 +2802,28 @@
         <v>-51</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.07904886199260464</v>
+        <v>-0.1168439731924491</v>
       </c>
       <c r="N12" s="1">
-        <v>2.1178327260345897</v>
+        <v>0.14342386662866102</v>
       </c>
       <c r="O12" s="1">
-        <v>45.56962025316456</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P12" s="1">
         <v>49.188907754993835</v>
       </c>
       <c r="Q12" s="1">
-        <v>52.151898734177216</v>
+        <v>53.92405063291139</v>
       </c>
       <c r="R12" s="1">
-        <v>37.59493670886076</v>
+        <v>37.34177215189873</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>101</v>
       </c>
       <c r="T12" s="1">
-        <v>16.9</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -2840,19 +2843,19 @@
         <v>6.41</v>
       </c>
       <c r="F13" s="3">
-        <v>-0.3306167647969178</v>
+        <v>-0.35929886170160874</v>
       </c>
       <c r="G13" s="3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H13" s="3">
-        <v>44.9</v>
+        <v>43.21</v>
       </c>
       <c r="I13" s="3">
-        <v>-6.96</v>
+        <v>-8.64</v>
       </c>
       <c r="J13" s="3">
-        <v>-0.00872891796016568</v>
+        <v>-0.007828951166343617</v>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
@@ -2861,28 +2864,28 @@
         <v>12</v>
       </c>
       <c r="M13" s="3">
-        <v>-0.2966154328807966</v>
+        <v>-0.3173628590767018</v>
       </c>
       <c r="N13" s="3">
-        <v>-19.63882436278461</v>
+        <v>-19.90846472179661</v>
       </c>
       <c r="O13" s="3">
-        <v>6.329113924050633</v>
+        <v>7.59493670886076</v>
       </c>
       <c r="P13" s="3">
         <v>39.74359086324119</v>
       </c>
       <c r="Q13" s="3">
-        <v>18.987341772151897</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="R13" s="3">
-        <v>3.6075949367088596</v>
+        <v>3.8607594936708844</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>102</v>
       </c>
       <c r="T13" s="3">
-        <v>-12.28</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -2896,25 +2899,25 @@
         <v>44.303797468354425</v>
       </c>
       <c r="D14" s="1">
-        <v>7.564885496183206</v>
+        <v>7.572519083969465</v>
       </c>
       <c r="E14" s="1">
         <v>4.73</v>
       </c>
       <c r="F14" s="1">
-        <v>0.15703330164011697</v>
+        <v>0.17916950216061667</v>
       </c>
       <c r="G14" s="1">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H14" s="1">
-        <v>61.87</v>
+        <v>67.74</v>
       </c>
       <c r="I14" s="1">
-        <v>5.36</v>
+        <v>11.47</v>
       </c>
       <c r="J14" s="1">
-        <v>0.015117235179156368</v>
+        <v>0.016828958828485927</v>
       </c>
       <c r="K14" s="1" t="b">
         <v>1</v>
@@ -2923,28 +2926,28 @@
         <v>12</v>
       </c>
       <c r="M14" s="1">
-        <v>0.1257162854015843</v>
+        <v>0.1404593458914718</v>
       </c>
       <c r="N14" s="1">
-        <v>22.594347465453488</v>
+        <v>25.87375577502076</v>
       </c>
       <c r="O14" s="1">
-        <v>72.15189873417721</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P14" s="1">
         <v>33.10300785656511</v>
       </c>
       <c r="Q14" s="1">
-        <v>55.69620253164557</v>
+        <v>57.84810126582279</v>
       </c>
       <c r="R14" s="1">
-        <v>46.64556962025316</v>
+        <v>47.53164556962025</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>100</v>
       </c>
       <c r="T14" s="1">
-        <v>11.46</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2964,19 +2967,19 @@
         <v>2.23</v>
       </c>
       <c r="F15" s="2">
-        <v>1.386303900438908</v>
+        <v>1.4076477342590126</v>
       </c>
       <c r="G15" s="2">
         <v>2.24</v>
       </c>
       <c r="H15" s="2">
-        <v>67.99</v>
+        <v>66.83</v>
       </c>
       <c r="I15" s="2">
-        <v>152.63</v>
+        <v>148.22</v>
       </c>
       <c r="J15" s="2">
-        <v>0.10292763062815169</v>
+        <v>0.1021717935655029</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2985,10 +2988,10 @@
         <v>195</v>
       </c>
       <c r="M15" s="2">
-        <v>1.4972556151125667</v>
+        <v>1.540982716963845</v>
       </c>
       <c r="N15" s="2">
-        <v>159.74828043655174</v>
+        <v>165.9260928822581</v>
       </c>
       <c r="O15" s="2">
         <v>100</v>
@@ -2997,7 +3000,7 @@
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>70.12658227848101</v>
+        <v>69.74683544303798</v>
       </c>
       <c r="R15" s="2">
         <v>62.27848101265822</v>
@@ -3010,65 +3013,65 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="3">
         <v>-3.53</v>
       </c>
-      <c r="C16" s="1">
-        <v>8.860759493670885</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="C16" s="3">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="D16" s="3">
         <v>12.69971671388102</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="3">
         <v>5.41</v>
       </c>
-      <c r="F16" s="1">
-        <v>-0.17926638357645863</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.9</v>
-      </c>
-      <c r="H16" s="1">
-        <v>50.85</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="J16" s="1">
-        <v>-0.003221229937621772</v>
-      </c>
-      <c r="K16" s="1" t="b">
+      <c r="F16" s="3">
+        <v>-0.25922093420680475</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.92</v>
+      </c>
+      <c r="H16" s="3">
+        <v>52.56</v>
+      </c>
+      <c r="I16" s="3">
+        <v>3.17</v>
+      </c>
+      <c r="J16" s="3">
+        <v>-0.0011493331487258444</v>
+      </c>
+      <c r="K16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="3">
         <v>16</v>
       </c>
-      <c r="M16" s="1">
-        <v>-0.09873691324880318</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0.1490276004147275</v>
-      </c>
-      <c r="O16" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="M16" s="3">
+        <v>-0.16029497929676784</v>
+      </c>
+      <c r="N16" s="3">
+        <v>-4.201676743803204</v>
+      </c>
+      <c r="O16" s="3">
+        <v>34.177215189873415</v>
+      </c>
+      <c r="P16" s="3">
         <v>30.2515696939809</v>
       </c>
-      <c r="Q16" s="1">
-        <v>39.620253164556964</v>
-      </c>
-      <c r="R16" s="1">
-        <v>30.189873417721518</v>
-      </c>
-      <c r="S16" s="1" t="s">
+      <c r="Q16" s="3">
+        <v>39.11392405063291</v>
+      </c>
+      <c r="R16" s="3">
+        <v>27.088607594936708</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="1">
-        <v>-6.46</v>
+      <c r="T16" s="3">
+        <v>-9.56</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -3082,25 +3085,25 @@
         <v>3.79746835443038</v>
       </c>
       <c r="D17" s="3">
-        <v>4.685990338164252</v>
+        <v>5.15780998389694</v>
       </c>
       <c r="E17" s="3">
         <v>1.52</v>
       </c>
       <c r="F17" s="3">
-        <v>-0.19490442422088772</v>
+        <v>-0.2835894926936874</v>
       </c>
       <c r="G17" s="3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H17" s="3">
-        <v>55.4</v>
+        <v>61.39</v>
       </c>
       <c r="I17" s="3">
-        <v>-3.92</v>
+        <v>1.19</v>
       </c>
       <c r="J17" s="3">
-        <v>0.0020206662459270235</v>
+        <v>0.00615839807043041</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>0</v>
@@ -3109,28 +3112,28 @@
         <v>25</v>
       </c>
       <c r="M17" s="3">
-        <v>-0.13048084795876336</v>
+        <v>-0.20509389803681022</v>
       </c>
       <c r="N17" s="3">
-        <v>-3.025365870581283</v>
+        <v>-8.681568617807443</v>
       </c>
       <c r="O17" s="3">
-        <v>34.177215189873415</v>
+        <v>18.9873417721519</v>
       </c>
       <c r="P17" s="3">
         <v>28.182703357372183</v>
       </c>
       <c r="Q17" s="3">
-        <v>34.30379746835443</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="R17" s="3">
-        <v>22.531645569620252</v>
+        <v>19.240506329113924</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>98</v>
       </c>
       <c r="T17" s="3">
-        <v>-0.63</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -3150,19 +3153,19 @@
         <v>6.73</v>
       </c>
       <c r="F18" s="3">
-        <v>-0.32497685036724655</v>
+        <v>-0.3596236439255154</v>
       </c>
       <c r="G18" s="3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H18" s="3">
-        <v>34.53</v>
+        <v>34.18</v>
       </c>
       <c r="I18" s="3">
-        <v>-14.05</v>
+        <v>-14.43</v>
       </c>
       <c r="J18" s="3">
-        <v>-0.0067314168475332255</v>
+        <v>-0.007390486959443497</v>
       </c>
       <c r="K18" s="3" t="b">
         <v>0</v>
@@ -3171,28 +3174,28 @@
         <v>37</v>
       </c>
       <c r="M18" s="3">
-        <v>-0.30887095630171546</v>
+        <v>-0.3413438479095303</v>
       </c>
       <c r="N18" s="3">
-        <v>-20.86437670487649</v>
+        <v>-22.30656360507945</v>
       </c>
       <c r="O18" s="3">
-        <v>5.063291139240507</v>
+        <v>3.79746835443038</v>
       </c>
       <c r="P18" s="3">
         <v>33.93532173431426</v>
       </c>
       <c r="Q18" s="3">
-        <v>45.822784810126585</v>
+        <v>44.810126582278485</v>
       </c>
       <c r="R18" s="3">
-        <v>28.54430379746836</v>
+        <v>27.78481012658228</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T18" s="3">
-        <v>-2.41</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -3212,31 +3215,31 @@
         <v>-1.48</v>
       </c>
       <c r="F19" s="1">
-        <v>0.004070997072829149</v>
+        <v>0.012260871440573091</v>
       </c>
       <c r="G19" s="1">
         <v>0.2</v>
       </c>
       <c r="H19" s="1">
-        <v>57.8</v>
+        <v>57</v>
       </c>
       <c r="I19" s="1">
-        <v>15.95</v>
+        <v>15.38</v>
       </c>
       <c r="J19" s="1">
-        <v>0.0035004576038287953</v>
+        <v>0.004762789440933372</v>
       </c>
       <c r="K19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.06751075432953124</v>
+        <v>-0.07376169804641552</v>
       </c>
       <c r="N19" s="1">
-        <v>3.2716434923419246</v>
+        <v>4.451651381232014</v>
       </c>
       <c r="O19" s="1">
         <v>48.10126582278481</v>
@@ -3245,7 +3248,7 @@
         <v>14.335419717590279</v>
       </c>
       <c r="Q19" s="1">
-        <v>52.911392405063296</v>
+        <v>52.02531645569621</v>
       </c>
       <c r="R19" s="1">
         <v>43.607594936708864</v>
@@ -3274,19 +3277,19 @@
         <v>6.54</v>
       </c>
       <c r="F20" s="1">
-        <v>0.025680798024644888</v>
+        <v>0.029400229935457545</v>
       </c>
       <c r="G20" s="1">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H20" s="1">
-        <v>69.12</v>
+        <v>73.52</v>
       </c>
       <c r="I20" s="1">
-        <v>4.18</v>
+        <v>8.49</v>
       </c>
       <c r="J20" s="1">
-        <v>0.0103315709282782</v>
+        <v>0.012419548476684491</v>
       </c>
       <c r="K20" s="1" t="b">
         <v>0</v>
@@ -3295,28 +3298,28 @@
         <v>9</v>
       </c>
       <c r="M20" s="1">
-        <v>0.031944201272351425</v>
+        <v>0.03800248688415642</v>
       </c>
       <c r="N20" s="1">
-        <v>13.217139052530186</v>
+        <v>15.628069874289219</v>
       </c>
       <c r="O20" s="1">
-        <v>60.75949367088608</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P20" s="1">
         <v>25.74193342123896</v>
       </c>
       <c r="Q20" s="1">
-        <v>54.936708860759495</v>
+        <v>55.56962025316455</v>
       </c>
       <c r="R20" s="1">
-        <v>43.48101265822784</v>
+        <v>44.36708860759494</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>105</v>
       </c>
       <c r="T20" s="1">
-        <v>16.08</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3330,25 +3333,25 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D21" s="2">
-        <v>14.009803921568627</v>
+        <v>13.558823529411764</v>
       </c>
       <c r="E21" s="2">
         <v>2.47</v>
       </c>
       <c r="F21" s="2">
-        <v>0.30261560132243825</v>
+        <v>0.34104313102257167</v>
       </c>
       <c r="G21" s="2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="H21" s="2">
-        <v>81.58</v>
+        <v>79.89</v>
       </c>
       <c r="I21" s="2">
-        <v>87.95</v>
+        <v>84.95</v>
       </c>
       <c r="J21" s="2">
-        <v>0.05119225833009738</v>
+        <v>0.05892123627948859</v>
       </c>
       <c r="K21" s="2" t="b">
         <v>1</v>
@@ -3357,28 +3360,28 @@
         <v>37</v>
       </c>
       <c r="M21" s="2">
-        <v>0.3491437397339725</v>
+        <v>0.40018364754487634</v>
       </c>
       <c r="N21" s="2">
-        <v>44.93709289869229</v>
+        <v>51.8461859403612</v>
       </c>
       <c r="O21" s="2">
-        <v>86.07594936708861</v>
+        <v>87.34177215189874</v>
       </c>
       <c r="P21" s="2">
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="2">
-        <v>71.26582278481013</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="R21" s="2">
-        <v>55.44303797468355</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T21" s="2">
-        <v>16.65</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -3398,31 +3401,31 @@
         <v>-0.84</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.2082266364890465</v>
+        <v>-0.21680085605791607</v>
       </c>
       <c r="G22" s="1">
         <v>1.37</v>
       </c>
       <c r="H22" s="1">
-        <v>63.05</v>
+        <v>64.75</v>
       </c>
       <c r="I22" s="1">
-        <v>5.53</v>
+        <v>6.65</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.001734735067681004</v>
+        <v>0.0013235824787247237</v>
       </c>
       <c r="K22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.1751200764654548</v>
+        <v>-0.1770154176701838</v>
       </c>
       <c r="N22" s="1">
-        <v>-7.489288721250429</v>
+        <v>-5.873720581144804</v>
       </c>
       <c r="O22" s="1">
         <v>27.848101265822784</v>
@@ -3434,13 +3437,13 @@
         <v>52.65822784810126</v>
       </c>
       <c r="R22" s="1">
-        <v>35</v>
+        <v>35.12658227848101</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T22" s="1">
-        <v>4.75</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3460,19 +3463,19 @@
         <v>0.96</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.14900837999103375</v>
+        <v>-0.17714388807223977</v>
       </c>
       <c r="G23" s="1">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H23" s="1">
-        <v>56.86</v>
+        <v>56.87</v>
       </c>
       <c r="I23" s="1">
-        <v>-4.9</v>
+        <v>-4.81</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.0038037903419921764</v>
+        <v>-0.0018190846186676589</v>
       </c>
       <c r="K23" s="1" t="b">
         <v>0</v>
@@ -3481,22 +3484,22 @@
         <v>21</v>
       </c>
       <c r="M23" s="1">
-        <v>-0.12842862646285513</v>
+        <v>-0.15133711722614318</v>
       </c>
       <c r="N23" s="1">
-        <v>-2.820143720990467</v>
+        <v>-3.3058905367407467</v>
       </c>
       <c r="O23" s="1">
-        <v>36.708860759493675</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="P23" s="1">
         <v>28.794141696367475</v>
       </c>
       <c r="Q23" s="1">
-        <v>47.59493670886076</v>
+        <v>47.468354430379755</v>
       </c>
       <c r="R23" s="1">
-        <v>35.00000000000001</v>
+        <v>35</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>106</v>
@@ -3522,31 +3525,31 @@
         <v>9.47</v>
       </c>
       <c r="F24" s="3">
-        <v>-0.18985546305069573</v>
+        <v>-0.25251762412574824</v>
       </c>
       <c r="G24" s="3">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="H24" s="3">
-        <v>41.3</v>
+        <v>39.86</v>
       </c>
       <c r="I24" s="3">
-        <v>-26.61</v>
+        <v>-27.4</v>
       </c>
       <c r="J24" s="3">
-        <v>0.013483314120105023</v>
+        <v>0.010057037308579353</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="M24" s="3">
-        <v>0.03652182575926899</v>
+        <v>0.018453469758265895</v>
       </c>
       <c r="N24" s="3">
-        <v>13.674901501221939</v>
+        <v>13.673168161700163</v>
       </c>
       <c r="O24" s="3">
         <v>62.0253164556962</v>
@@ -3555,16 +3558,16 @@
         <v>40.33904155950217</v>
       </c>
       <c r="Q24" s="3">
-        <v>20.126582278481013</v>
+        <v>19.240506329113924</v>
       </c>
       <c r="R24" s="3">
-        <v>21.39240506329114</v>
+        <v>21.139240506329116</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T24" s="3">
-        <v>-9.62</v>
+        <v>-9.87</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -3584,19 +3587,19 @@
         <v>11.95</v>
       </c>
       <c r="F25" s="3">
-        <v>-0.2936079173987655</v>
+        <v>-0.3339087547980175</v>
       </c>
       <c r="G25" s="3">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="H25" s="3">
-        <v>52.41</v>
+        <v>53.16</v>
       </c>
       <c r="I25" s="3">
-        <v>-46.79</v>
+        <v>-45.95</v>
       </c>
       <c r="J25" s="3">
-        <v>-0.0043951856131987975</v>
+        <v>-0.001986099582476645</v>
       </c>
       <c r="K25" s="3" t="b">
         <v>0</v>
@@ -3605,28 +3608,28 @@
         <v>41</v>
       </c>
       <c r="M25" s="3">
-        <v>-0.18444574651016588</v>
+        <v>-0.20379961844894723</v>
       </c>
       <c r="N25" s="3">
-        <v>-8.421855725721535</v>
+        <v>-8.552140659021152</v>
       </c>
       <c r="O25" s="3">
-        <v>24.050632911392405</v>
+        <v>21.518987341772153</v>
       </c>
       <c r="P25" s="3">
         <v>55.620154465672535</v>
       </c>
       <c r="Q25" s="3">
-        <v>15.443037974683545</v>
+        <v>15.822784810126585</v>
       </c>
       <c r="R25" s="3">
-        <v>4.050632911392407</v>
+        <v>3.9240506329113938</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T25" s="3">
-        <v>-7.91</v>
+        <v>-8.04</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -3640,25 +3643,25 @@
         <v>24.050632911392405</v>
       </c>
       <c r="D26" s="1">
-        <v>-2569.235294117647</v>
+        <v>-2529.3529411764703</v>
       </c>
       <c r="E26" s="1">
         <v>3.39</v>
       </c>
       <c r="F26" s="1">
-        <v>0.6579840161118936</v>
+        <v>0.36951534389864393</v>
       </c>
       <c r="G26" s="1">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="H26" s="1">
-        <v>70.66</v>
+        <v>74.23</v>
       </c>
       <c r="I26" s="1">
-        <v>37.48</v>
+        <v>47.06</v>
       </c>
       <c r="J26" s="1">
-        <v>0.06851111305724455</v>
+        <v>0.0776905112005027</v>
       </c>
       <c r="K26" s="1" t="b">
         <v>1</v>
@@ -3667,28 +3670,28 @@
         <v>-29</v>
       </c>
       <c r="M26" s="1">
-        <v>0.8467808854356191</v>
+        <v>0.5974751530391638</v>
       </c>
       <c r="N26" s="1">
-        <v>94.70080746885695</v>
+        <v>71.57533648978995</v>
       </c>
       <c r="O26" s="1">
-        <v>92.40506329113924</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P26" s="1">
         <v>47.81158046237125</v>
       </c>
       <c r="Q26" s="1">
-        <v>43.03797468354431</v>
+        <v>43.924050632911396</v>
       </c>
       <c r="R26" s="1">
-        <v>34.05063291139241</v>
+        <v>33.41772151898734</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T26" s="1">
-        <v>1.01</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3708,19 +3711,19 @@
         <v>8.19</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.07882179194803116</v>
+        <v>-0.09335364792367185</v>
       </c>
       <c r="G27" s="1">
         <v>2.65</v>
       </c>
       <c r="H27" s="1">
-        <v>65.21</v>
+        <v>70.61</v>
       </c>
       <c r="I27" s="1">
-        <v>-11.04</v>
+        <v>-4.51</v>
       </c>
       <c r="J27" s="1">
-        <v>0.010826199479166711</v>
+        <v>0.015521257090109087</v>
       </c>
       <c r="K27" s="1" t="b">
         <v>0</v>
@@ -3729,28 +3732,28 @@
         <v>42</v>
       </c>
       <c r="M27" s="1">
-        <v>0.06881557031933716</v>
+        <v>0.08406790164324218</v>
       </c>
       <c r="N27" s="1">
-        <v>16.904275957228773</v>
+        <v>20.234611350197802</v>
       </c>
       <c r="O27" s="1">
-        <v>67.08860759493672</v>
+        <v>68.35443037974683</v>
       </c>
       <c r="P27" s="1">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="1">
-        <v>38.86075949367089</v>
+        <v>41.139240506329116</v>
       </c>
       <c r="R27" s="1">
-        <v>30.126582278481024</v>
+        <v>30.75949367088608</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="1">
-        <v>3.73</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -3770,19 +3773,19 @@
         <v>-4.03</v>
       </c>
       <c r="F28" s="3">
-        <v>-0.3682783518385405</v>
+        <v>-0.42454909753822806</v>
       </c>
       <c r="G28" s="3">
         <v>3.13</v>
       </c>
       <c r="H28" s="3">
-        <v>59.87</v>
+        <v>64.22</v>
       </c>
       <c r="I28" s="3">
-        <v>-18.23</v>
+        <v>-14.84</v>
       </c>
       <c r="J28" s="3">
-        <v>0.0009218808275710569</v>
+        <v>0.004549498513752033</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
@@ -3791,28 +3794,28 @@
         <v>-3</v>
       </c>
       <c r="M28" s="3">
-        <v>-0.17769193872975597</v>
+        <v>-0.19551400627912086</v>
       </c>
       <c r="N28" s="3">
-        <v>-7.746474947680554</v>
+        <v>-7.723579442038505</v>
       </c>
       <c r="O28" s="3">
-        <v>25.31645569620253</v>
+        <v>24.050632911392405</v>
       </c>
       <c r="P28" s="3">
         <v>45.17203183430412</v>
       </c>
       <c r="Q28" s="3">
-        <v>38.9873417721519</v>
+        <v>40.12658227848102</v>
       </c>
       <c r="R28" s="3">
-        <v>22.088607594936704</v>
+        <v>21.835443037974684</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>104</v>
       </c>
       <c r="T28" s="3">
-        <v>0.19</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3826,55 +3829,55 @@
         <v>34.177215189873415</v>
       </c>
       <c r="D29" s="3">
-        <v>79.11363636363637</v>
+        <v>79.00000000000001</v>
       </c>
       <c r="E29" s="3">
         <v>1.51</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.36128874030113833</v>
+        <v>-0.3491529053242544</v>
       </c>
       <c r="G29" s="3">
         <v>2.11</v>
       </c>
       <c r="H29" s="3">
-        <v>48.4</v>
+        <v>55.6</v>
       </c>
       <c r="I29" s="3">
-        <v>-30.51</v>
+        <v>-26.98</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.012771018064302118</v>
+        <v>-0.010200877996192138</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-71</v>
+        <v>-70</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.26196906023036326</v>
+        <v>-0.2297965901610577</v>
       </c>
       <c r="N29" s="3">
-        <v>-16.17418709774128</v>
+        <v>-11.151837830232195</v>
       </c>
       <c r="O29" s="3">
-        <v>12.658227848101266</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>42.53164556962025</v>
+        <v>44.43037974683544</v>
       </c>
       <c r="R29" s="3">
-        <v>26.32911392405063</v>
+        <v>28.10126582278481</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>1.96</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -3894,19 +3897,19 @@
         <v>1.79</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.14353449500323823</v>
+        <v>-0.14145476832285253</v>
       </c>
       <c r="G30" s="1">
         <v>1.19</v>
       </c>
       <c r="H30" s="1">
-        <v>50.19</v>
+        <v>54.21</v>
       </c>
       <c r="I30" s="1">
-        <v>2.19</v>
+        <v>4.22</v>
       </c>
       <c r="J30" s="1">
-        <v>0.004050291917695464</v>
+        <v>0.00529126227078774</v>
       </c>
       <c r="K30" s="1" t="b">
         <v>0</v>
@@ -3915,28 +3918,28 @@
         <v>24</v>
       </c>
       <c r="M30" s="1">
-        <v>-0.12653382904517763</v>
+        <v>-0.12102440806969272</v>
       </c>
       <c r="N30" s="1">
-        <v>-2.6306639792227173</v>
+        <v>-0.27461962109569293</v>
       </c>
       <c r="O30" s="1">
-        <v>37.9746835443038</v>
+        <v>43.037974683544306</v>
       </c>
       <c r="P30" s="1">
         <v>24.961328061128594</v>
       </c>
       <c r="Q30" s="1">
-        <v>63.037974683544306</v>
+        <v>62.78481012658228</v>
       </c>
       <c r="R30" s="1">
-        <v>48.54430379746835</v>
+        <v>49.810126582278485</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T30" s="1">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3950,55 +3953,55 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D31" s="2">
-        <v>10.894736842105264</v>
+        <v>10.984405458089668</v>
       </c>
       <c r="E31" s="2">
         <v>0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>0.1316696518032923</v>
+        <v>0.16257787632417373</v>
       </c>
       <c r="G31" s="2">
         <v>1.42</v>
       </c>
       <c r="H31" s="2">
-        <v>56.37</v>
+        <v>58.44</v>
       </c>
       <c r="I31" s="2">
-        <v>20.18</v>
+        <v>21.31</v>
       </c>
       <c r="J31" s="2">
-        <v>0.022718085284339593</v>
+        <v>0.02423576973198872</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M31" s="2">
-        <v>0.1692500712895315</v>
+        <v>0.20773972530484275</v>
       </c>
       <c r="N31" s="2">
-        <v>26.947726054248207</v>
+        <v>32.60179371635786</v>
       </c>
       <c r="O31" s="2">
-        <v>77.21518987341773</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>64.81012658227847</v>
+        <v>65.31645569620252</v>
       </c>
       <c r="R31" s="2">
-        <v>59.55696202531646</v>
+        <v>59.99999999999999</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-1.27</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -4018,19 +4021,19 @@
         <v>-2.98</v>
       </c>
       <c r="F32" s="3">
-        <v>-0.18997908908241676</v>
+        <v>-0.20906034438266097</v>
       </c>
       <c r="G32" s="3">
         <v>1.6</v>
       </c>
       <c r="H32" s="3">
-        <v>50.39</v>
+        <v>55.1</v>
       </c>
       <c r="I32" s="3">
-        <v>-4.51</v>
+        <v>-1.37</v>
       </c>
       <c r="J32" s="3">
-        <v>-0.009713523366369447</v>
+        <v>-0.006898525605326837</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>0</v>
@@ -4039,28 +4042,28 @@
         <v>23</v>
       </c>
       <c r="M32" s="3">
-        <v>-0.13629277553064645</v>
+        <v>-0.14454341726741948</v>
       </c>
       <c r="N32" s="3">
-        <v>-3.606558627769595</v>
+        <v>-2.6265205408683667</v>
       </c>
       <c r="O32" s="3">
-        <v>31.645569620253166</v>
+        <v>37.9746835443038</v>
       </c>
       <c r="P32" s="3">
         <v>37.59071325149605</v>
       </c>
       <c r="Q32" s="3">
-        <v>32.65822784810126</v>
+        <v>34.68354430379747</v>
       </c>
       <c r="R32" s="3">
-        <v>21.32911392405063</v>
+        <v>23.987341772151897</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>105</v>
       </c>
       <c r="T32" s="3">
-        <v>-8.04</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -4080,19 +4083,19 @@
         <v>-0.44</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.07815031316958804</v>
+        <v>-0.06397598574240393</v>
       </c>
       <c r="G33" s="1">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="H33" s="1">
-        <v>49.59</v>
+        <v>59.32</v>
       </c>
       <c r="I33" s="1">
-        <v>-10.16</v>
+        <v>-6.94</v>
       </c>
       <c r="J33" s="1">
-        <v>0.003975805434924213</v>
+        <v>0.0045870349662385755</v>
       </c>
       <c r="K33" s="1" t="b">
         <v>0</v>
@@ -4101,28 +4104,28 @@
         <v>5</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.07009736613682249</v>
+        <v>-0.05537372879370506</v>
       </c>
       <c r="N33" s="1">
-        <v>3.0129823116128067</v>
+        <v>6.290448306503081</v>
       </c>
       <c r="O33" s="1">
-        <v>46.835443037974684</v>
+        <v>50.63291139240506</v>
       </c>
       <c r="P33" s="1">
         <v>26.81341163265095</v>
       </c>
       <c r="Q33" s="1">
-        <v>48.734177215189874</v>
+        <v>50.25316455696202</v>
       </c>
       <c r="R33" s="1">
-        <v>40.50632911392404</v>
+        <v>41.26582278481012</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T33" s="1">
-        <v>0.57</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -4136,49 +4139,49 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D34" s="2">
-        <v>-0.7170099160945842</v>
+        <v>-0.7177726926010679</v>
       </c>
       <c r="E34" s="2">
         <v>0.77</v>
       </c>
       <c r="F34" s="2">
-        <v>0.12006888306274481</v>
+        <v>0.12405047981024028</v>
       </c>
       <c r="G34" s="2">
         <v>1.25</v>
       </c>
       <c r="H34" s="2">
-        <v>60.97</v>
+        <v>61.78</v>
       </c>
       <c r="I34" s="2">
-        <v>30.44</v>
+        <v>30.46</v>
       </c>
       <c r="J34" s="2">
-        <v>0.02438757494779184</v>
+        <v>0.024112013301512865</v>
       </c>
       <c r="K34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M34" s="2">
-        <v>0.14243818037598244</v>
+        <v>0.15093253277492424</v>
       </c>
       <c r="N34" s="2">
-        <v>24.266536962893294</v>
+        <v>26.921074463366</v>
       </c>
       <c r="O34" s="2">
-        <v>74.68354430379746</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P34" s="2">
         <v>20.42247430615109</v>
       </c>
       <c r="Q34" s="2">
-        <v>57.848101265822784</v>
+        <v>57.21518987341772</v>
       </c>
       <c r="R34" s="2">
-        <v>50.25316455696202</v>
+        <v>50.253164556962034</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>106</v>
@@ -4204,19 +4207,19 @@
         <v>9.42</v>
       </c>
       <c r="F35" s="3">
-        <v>-0.32763365185892834</v>
+        <v>-0.3399483041248423</v>
       </c>
       <c r="G35" s="3">
         <v>0.99</v>
       </c>
       <c r="H35" s="3">
-        <v>36.54</v>
+        <v>35.72</v>
       </c>
       <c r="I35" s="3">
-        <v>-22.25</v>
+        <v>-22.46</v>
       </c>
       <c r="J35" s="3">
-        <v>-0.023193585401175824</v>
+        <v>-0.02337664794308396</v>
       </c>
       <c r="K35" s="3" t="b">
         <v>0</v>
@@ -4225,28 +4228,28 @@
         <v>19</v>
       </c>
       <c r="M35" s="3">
-        <v>-0.32852842375145785</v>
+        <v>-0.34102358624342965</v>
       </c>
       <c r="N35" s="3">
-        <v>-22.83012344985074</v>
+        <v>-22.27453743846939</v>
       </c>
       <c r="O35" s="3">
-        <v>3.79746835443038</v>
+        <v>5.063291139240507</v>
       </c>
       <c r="P35" s="3">
         <v>28.919768290867083</v>
       </c>
       <c r="Q35" s="3">
-        <v>34.177215189873415</v>
+        <v>33.29113924050633</v>
       </c>
       <c r="R35" s="3">
-        <v>21.455696202531644</v>
+        <v>21.83544303797468</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>110</v>
       </c>
       <c r="T35" s="3">
-        <v>-0.13</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4260,25 +4263,25 @@
         <v>82.27848101265823</v>
       </c>
       <c r="D36" s="3">
-        <v>0.40225890529973946</v>
+        <v>0.3588184187662903</v>
       </c>
       <c r="E36" s="3">
         <v>3.24</v>
       </c>
       <c r="F36" s="3">
-        <v>-0.2250081669146608</v>
+        <v>-0.24523179507748796</v>
       </c>
       <c r="G36" s="3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H36" s="3">
-        <v>48.78</v>
+        <v>47.7</v>
       </c>
       <c r="I36" s="3">
-        <v>-10.82</v>
+        <v>-11.49</v>
       </c>
       <c r="J36" s="3">
-        <v>-0.005102408068476226</v>
+        <v>-0.004132909354969646</v>
       </c>
       <c r="K36" s="3" t="b">
         <v>0</v>
@@ -4287,22 +4290,22 @@
         <v>-55</v>
       </c>
       <c r="M36" s="3">
-        <v>-0.21427090420430672</v>
+        <v>-0.233403691773027</v>
       </c>
       <c r="N36" s="3">
-        <v>-11.40437149513563</v>
+        <v>-11.512547991429122</v>
       </c>
       <c r="O36" s="3">
-        <v>17.72151898734177</v>
+        <v>16.455696202531644</v>
       </c>
       <c r="P36" s="3">
         <v>32.54334537649318</v>
       </c>
       <c r="Q36" s="3">
-        <v>44.303797468354425</v>
+        <v>44.050632911392405</v>
       </c>
       <c r="R36" s="3">
-        <v>28.481012658227844</v>
+        <v>28.48101265822785</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>104</v>
@@ -4312,65 +4315,65 @@
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="1">
         <v>5.33</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="1">
         <v>62.0253164556962</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="1">
         <v>0.6022514071294557</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="1">
         <v>-5.1</v>
       </c>
-      <c r="F37" s="3">
-        <v>-0.20767146673841141</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1.36</v>
-      </c>
-      <c r="H37" s="3">
-        <v>33.82</v>
-      </c>
-      <c r="I37" s="3">
-        <v>-23.22</v>
-      </c>
-      <c r="J37" s="3">
-        <v>-0.001904983818433394</v>
-      </c>
-      <c r="K37" s="3" t="b">
+      <c r="F37" s="1">
+        <v>-0.17941406829596018</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="H37" s="1">
+        <v>40.16</v>
+      </c>
+      <c r="I37" s="1">
+        <v>-21.84</v>
+      </c>
+      <c r="J37" s="1">
+        <v>-0.002344914304175134</v>
+      </c>
+      <c r="K37" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="1">
         <v>-214</v>
       </c>
-      <c r="M37" s="3">
-        <v>-0.17545967860734923</v>
-      </c>
-      <c r="N37" s="3">
-        <v>-7.523248935439876</v>
-      </c>
-      <c r="O37" s="3">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="P37" s="3">
+      <c r="M37" s="1">
+        <v>-0.14177919414540263</v>
+      </c>
+      <c r="N37" s="1">
+        <v>-2.350098228666684</v>
+      </c>
+      <c r="O37" s="1">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="P37" s="1">
         <v>34.65975433248125</v>
       </c>
-      <c r="Q37" s="3">
-        <v>37.46835443037975</v>
-      </c>
-      <c r="R37" s="3">
-        <v>27.658227848101266</v>
-      </c>
-      <c r="S37" s="3" t="s">
+      <c r="Q37" s="1">
+        <v>37.34177215189874</v>
+      </c>
+      <c r="R37" s="1">
+        <v>31.075949367088608</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T37" s="3">
-        <v>-11.14</v>
+      <c r="T37" s="1">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4390,49 +4393,49 @@
         <v>-0.57</v>
       </c>
       <c r="F38" s="2">
-        <v>0.6600011482972626</v>
+        <v>0.6241346954933835</v>
       </c>
       <c r="G38" s="2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H38" s="2">
-        <v>75.81</v>
+        <v>78.78</v>
       </c>
       <c r="I38" s="2">
-        <v>38.03</v>
+        <v>43.14</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04858736547414308</v>
+        <v>0.04918758702244289</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-45</v>
+        <v>-44</v>
       </c>
       <c r="M38" s="2">
-        <v>0.6761070423627937</v>
+        <v>0.6424144915093686</v>
       </c>
       <c r="N38" s="2">
-        <v>77.63342316157441</v>
+        <v>76.06927033681043</v>
       </c>
       <c r="O38" s="2">
-        <v>91.13924050632912</v>
+        <v>92.40506329113924</v>
       </c>
       <c r="P38" s="2">
         <v>26.865173556258448</v>
       </c>
       <c r="Q38" s="2">
-        <v>64.81012658227849</v>
+        <v>65.44303797468353</v>
       </c>
       <c r="R38" s="2">
-        <v>55.56962025316456</v>
+        <v>56.26582278481013</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4452,19 +4455,19 @@
         <v>6.03</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.06384501315689235</v>
+        <v>-0.14160568092092332</v>
       </c>
       <c r="G39" s="1">
         <v>1.25</v>
       </c>
       <c r="H39" s="1">
-        <v>32.23</v>
+        <v>30.69</v>
       </c>
       <c r="I39" s="1">
-        <v>-9.22</v>
+        <v>-11.08</v>
       </c>
       <c r="J39" s="1">
-        <v>0.002052035658048767</v>
+        <v>0.0007765026087280258</v>
       </c>
       <c r="K39" s="1" t="b">
         <v>1</v>
@@ -4473,28 +4476,28 @@
         <v>-4</v>
       </c>
       <c r="M39" s="1">
-        <v>-0.041475715843654726</v>
+        <v>-0.11472362795623936</v>
       </c>
       <c r="N39" s="1">
-        <v>5.875147340929577</v>
+        <v>0.35545839024965137</v>
       </c>
       <c r="O39" s="1">
-        <v>55.69620253164557</v>
+        <v>45.56962025316456</v>
       </c>
       <c r="P39" s="1">
-        <v>21.790241497748045</v>
+        <v>23.417722010155686</v>
       </c>
       <c r="Q39" s="1">
-        <v>45.316455696202524</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="R39" s="1">
-        <v>44.24050632911393</v>
+        <v>40.44303797468355</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="T39" s="1">
-        <v>-9.18</v>
+        <v>-12.97</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4514,19 +4517,19 @@
         <v>2.22</v>
       </c>
       <c r="F40" s="3">
-        <v>0.032728270955086944</v>
+        <v>0.08365880524915408</v>
       </c>
       <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>38.18</v>
+        <v>43.2</v>
       </c>
       <c r="I40" s="3">
-        <v>-23.44</v>
+        <v>-20.01</v>
       </c>
       <c r="J40" s="3">
-        <v>-0.0047552246966131835</v>
+        <v>-0.00698609833271195</v>
       </c>
       <c r="K40" s="3" t="b">
         <v>0</v>
@@ -4535,28 +4538,28 @@
         <v>54</v>
       </c>
       <c r="M40" s="3">
-        <v>-0.05674891829786355</v>
+        <v>-0.0238694066095817</v>
       </c>
       <c r="N40" s="3">
-        <v>4.347827095508702</v>
+        <v>9.440880524915404</v>
       </c>
       <c r="O40" s="3">
-        <v>51.89873417721519</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="P40" s="3">
         <v>39.97107065255327</v>
       </c>
       <c r="Q40" s="3">
-        <v>28.607594936708857</v>
+        <v>27.594936708860757</v>
       </c>
       <c r="R40" s="3">
-        <v>27.468354430379748</v>
+        <v>27.91139240506329</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>111</v>
       </c>
       <c r="T40" s="3">
-        <v>-13.29</v>
+        <v>-12.85</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -4576,19 +4579,19 @@
         <v>-1.06</v>
       </c>
       <c r="F41" s="1">
-        <v>0.045789238189137105</v>
+        <v>0.05853267099388554</v>
       </c>
       <c r="G41" s="1">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H41" s="1">
-        <v>63.28</v>
+        <v>65.85</v>
       </c>
       <c r="I41" s="1">
-        <v>-7.56</v>
+        <v>-5.15</v>
       </c>
       <c r="J41" s="1">
-        <v>0.027102667429829527</v>
+        <v>0.02846949048870736</v>
       </c>
       <c r="K41" s="1" t="b">
         <v>0</v>
@@ -4597,28 +4600,28 @@
         <v>3</v>
       </c>
       <c r="M41" s="1">
-        <v>0.05563172900696167</v>
+        <v>0.07143605641693385</v>
       </c>
       <c r="N41" s="1">
-        <v>15.585891825991215</v>
+        <v>18.971426827566965</v>
       </c>
       <c r="O41" s="1">
-        <v>63.29113924050633</v>
+        <v>67.08860759493672</v>
       </c>
       <c r="P41" s="1">
         <v>46.4052282234621</v>
       </c>
       <c r="Q41" s="1">
-        <v>45.06329113924051</v>
+        <v>45.18987341772152</v>
       </c>
       <c r="R41" s="1">
-        <v>33.29113924050633</v>
+        <v>34.430379746835456</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="T41" s="1">
-        <v>3.23</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -4638,19 +4641,19 @@
         <v>2.81</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.07390571332374447</v>
+        <v>-0.09981712874332024</v>
       </c>
       <c r="G42" s="1">
         <v>0.36</v>
       </c>
       <c r="H42" s="1">
-        <v>48.73</v>
+        <v>43.37</v>
       </c>
       <c r="I42" s="1">
-        <v>0.85</v>
+        <v>-0.58</v>
       </c>
       <c r="J42" s="1">
-        <v>-0.004098683644283372</v>
+        <v>-0.004533437057777776</v>
       </c>
       <c r="K42" s="1" t="b">
         <v>0</v>
@@ -4659,10 +4662,10 @@
         <v>19</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.13117111444563279</v>
+        <v>-0.16863518433291114</v>
       </c>
       <c r="N42" s="1">
-        <v>-3.0943925192682316</v>
+        <v>-5.035697247417541</v>
       </c>
       <c r="O42" s="1">
         <v>32.91139240506329</v>
@@ -4671,16 +4674,16 @@
         <v>10.38279059078273</v>
       </c>
       <c r="Q42" s="1">
-        <v>43.54430379746836</v>
+        <v>40.88607594936709</v>
       </c>
       <c r="R42" s="1">
-        <v>36.70886075949366</v>
+        <v>36.0759493670886</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T42" s="1">
-        <v>-1.84</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -4700,19 +4703,19 @@
         <v>10.72</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.052196028225681645</v>
+        <v>-0.05718649574350687</v>
       </c>
       <c r="G43" s="1">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H43" s="1">
-        <v>47.79</v>
+        <v>56.82</v>
       </c>
       <c r="I43" s="1">
-        <v>-13.49</v>
+        <v>-7.32</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.005634380469718134</v>
+        <v>-0.005557203239642593</v>
       </c>
       <c r="K43" s="1" t="b">
         <v>0</v>
@@ -4721,28 +4724,28 @@
         <v>10</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.026247643342325988</v>
+        <v>-0.028153878541648192</v>
       </c>
       <c r="N43" s="1">
-        <v>7.397954591062446</v>
+        <v>9.012433331708749</v>
       </c>
       <c r="O43" s="1">
-        <v>56.9620253164557</v>
+        <v>55.69620253164557</v>
       </c>
       <c r="P43" s="1">
         <v>33.21399316212126</v>
       </c>
       <c r="Q43" s="1">
-        <v>47.721518987341774</v>
+        <v>50.12658227848101</v>
       </c>
       <c r="R43" s="1">
-        <v>43.67088607594937</v>
+        <v>43.291139240506325</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="T43" s="1">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4762,19 +4765,19 @@
         <v>-0.99</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.355556757637458</v>
+        <v>-0.37587664939233606</v>
       </c>
       <c r="G44" s="3">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="H44" s="3">
-        <v>46.11</v>
+        <v>55.46</v>
       </c>
       <c r="I44" s="3">
-        <v>-23.82</v>
+        <v>-17.7</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.018684776336559197</v>
+        <v>-0.016791017323795794</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
@@ -4783,28 +4786,28 @@
         <v>-114</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.2141827986177962</v>
+        <v>-0.20490679253694621</v>
       </c>
       <c r="N44" s="3">
-        <v>-11.395560936484577</v>
+        <v>-8.66285806782104</v>
       </c>
       <c r="O44" s="3">
-        <v>18.9873417721519</v>
+        <v>20.253164556962027</v>
       </c>
       <c r="P44" s="3">
         <v>43.36598203964858</v>
       </c>
       <c r="Q44" s="3">
-        <v>41.26582278481012</v>
+        <v>43.291139240506325</v>
       </c>
       <c r="R44" s="3">
-        <v>28.0379746835443</v>
+        <v>28.417721518987342</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4824,49 +4827,49 @@
         <v>0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>0.15009868938510945</v>
+        <v>0.1500733663470312</v>
       </c>
       <c r="G45" s="2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H45" s="2">
-        <v>62.65</v>
+        <v>64.4</v>
       </c>
       <c r="I45" s="2">
-        <v>17.68</v>
+        <v>18.47</v>
       </c>
       <c r="J45" s="2">
-        <v>0.023549181299388926</v>
+        <v>0.024127182400048644</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L45" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.19036342454893718</v>
+        <v>0.19953634380204965</v>
       </c>
       <c r="N45" s="2">
-        <v>29.059061380188766</v>
+        <v>31.78145556607855</v>
       </c>
       <c r="O45" s="2">
-        <v>79.74683544303798</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>62.40506329113925</v>
+        <v>62.27848101265823</v>
       </c>
       <c r="R45" s="2">
-        <v>56.39240506329115</v>
+        <v>55.50632911392405</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-0.57</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -4886,19 +4889,19 @@
         <v>5.16</v>
       </c>
       <c r="F46" s="3">
-        <v>-0.33033456237278586</v>
+        <v>-0.36146093680603075</v>
       </c>
       <c r="G46" s="3">
         <v>1.47</v>
       </c>
       <c r="H46" s="3">
-        <v>44.82</v>
+        <v>45.3</v>
       </c>
       <c r="I46" s="3">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="J46" s="3">
-        <v>-0.008856868141176399</v>
+        <v>-0.006175111991981685</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>0</v>
@@ -4907,28 +4910,28 @@
         <v>27</v>
       </c>
       <c r="M46" s="3">
-        <v>-0.2882802834238991</v>
+        <v>-0.31092267723242495</v>
       </c>
       <c r="N46" s="3">
-        <v>-18.805309417094858</v>
+        <v>-19.26444653736892</v>
       </c>
       <c r="O46" s="3">
-        <v>10.126582278481013</v>
+        <v>8.860759493670885</v>
       </c>
       <c r="P46" s="3">
         <v>41.630589083814144</v>
       </c>
       <c r="Q46" s="3">
-        <v>45.69620253164557</v>
+        <v>47.594936708860764</v>
       </c>
       <c r="R46" s="3">
-        <v>25.44303797468354</v>
+        <v>25.822784810126578</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T46" s="3">
-        <v>-5.95</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -4948,19 +4951,19 @@
         <v>1.38</v>
       </c>
       <c r="F47" s="3">
-        <v>-0.47443207463103015</v>
+        <v>-0.49744067626176725</v>
       </c>
       <c r="G47" s="3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H47" s="3">
-        <v>27.67</v>
+        <v>27.1</v>
       </c>
       <c r="I47" s="3">
-        <v>-23.88</v>
+        <v>-24.38</v>
       </c>
       <c r="J47" s="3">
-        <v>-0.03109130420197483</v>
+        <v>-0.03134447166022486</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
@@ -4969,19 +4972,19 @@
         <v>9</v>
       </c>
       <c r="M47" s="3">
-        <v>-0.43416733946720243</v>
+        <v>-0.4501282630439235</v>
       </c>
       <c r="N47" s="3">
-        <v>-33.39401502142519</v>
+        <v>-33.185005118518774</v>
       </c>
       <c r="O47" s="3">
         <v>1.2658227848101267</v>
       </c>
       <c r="P47" s="3">
-        <v>33.39401502142519</v>
+        <v>33.84253937304741</v>
       </c>
       <c r="Q47" s="3">
-        <v>37.9746835443038</v>
+        <v>37.721518987341774</v>
       </c>
       <c r="R47" s="3">
         <v>23.9240506329114</v>
@@ -5010,49 +5013,49 @@
         <v>0.6</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.16466017593862114</v>
+        <v>-0.20058760267233752</v>
       </c>
       <c r="G48" s="1">
         <v>1.02</v>
       </c>
       <c r="H48" s="1">
-        <v>63.42</v>
+        <v>57.88</v>
       </c>
       <c r="I48" s="1">
-        <v>-1.58</v>
+        <v>-3.05</v>
       </c>
       <c r="J48" s="1">
-        <v>0.00035234258215829776</v>
+        <v>0.0016132729502708948</v>
       </c>
       <c r="K48" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>-65</v>
+        <v>-67</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.16287063215356212</v>
+        <v>-0.1984370384351628</v>
       </c>
       <c r="N48" s="1">
-        <v>-6.264344290061167</v>
+        <v>-8.015882657642704</v>
       </c>
       <c r="O48" s="1">
-        <v>29.11392405063291</v>
+        <v>22.78481012658228</v>
       </c>
       <c r="P48" s="1">
         <v>19.13407224404345</v>
       </c>
       <c r="Q48" s="1">
-        <v>49.74683544303797</v>
+        <v>46.962025316455694</v>
       </c>
       <c r="R48" s="1">
-        <v>34.87341772151899</v>
+        <v>32.9746835443038</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="1">
-        <v>8.67</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5072,19 +5075,19 @@
         <v>-0.36</v>
       </c>
       <c r="F49" s="2">
-        <v>0.03214468712530286</v>
+        <v>-0.004916213470242792</v>
       </c>
       <c r="G49" s="2">
         <v>1.61</v>
       </c>
       <c r="H49" s="2">
-        <v>61.16</v>
+        <v>55.19</v>
       </c>
       <c r="I49" s="2">
-        <v>44.24</v>
+        <v>40.17</v>
       </c>
       <c r="J49" s="2">
-        <v>0.02327656005186917</v>
+        <v>0.023937188198511573</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
@@ -5093,28 +5096,28 @@
         <v>266</v>
       </c>
       <c r="M49" s="2">
-        <v>0.08672577256960268</v>
+        <v>0.060675995763586066</v>
       </c>
       <c r="N49" s="2">
-        <v>18.695296182255323</v>
+        <v>17.89542076223218</v>
       </c>
       <c r="O49" s="2">
-        <v>69.62025316455697</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>64.81012658227849</v>
+        <v>61.64556962025316</v>
       </c>
       <c r="R49" s="2">
-        <v>56.20253164556962</v>
+        <v>54.93670886075949</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>0.89</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5134,49 +5137,49 @@
         <v>5.72</v>
       </c>
       <c r="F50" s="2">
-        <v>0.33209265828338874</v>
+        <v>0.3032062272106687</v>
       </c>
       <c r="G50" s="2">
         <v>3.78</v>
       </c>
       <c r="H50" s="2">
-        <v>59.57</v>
+        <v>58.12</v>
       </c>
       <c r="I50" s="2">
-        <v>116.46</v>
+        <v>111.7</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06953842510636646</v>
+        <v>0.06883529244451002</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M50" s="2">
-        <v>0.5808392444065911</v>
+        <v>0.6021346561779541</v>
       </c>
       <c r="N50" s="2">
-        <v>68.10664336595416</v>
+        <v>72.041286803669</v>
       </c>
       <c r="O50" s="2">
-        <v>89.87341772151899</v>
+        <v>91.13924050632912</v>
       </c>
       <c r="P50" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>72.15189873417721</v>
+        <v>70.8860759493671</v>
       </c>
       <c r="R50" s="2">
-        <v>61.39240506329113</v>
+        <v>61.51898734177215</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-2.15</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5196,49 +5199,49 @@
         <v>4.31</v>
       </c>
       <c r="F51" s="2">
-        <v>0.02457684635630672</v>
+        <v>-0.02028427327566104</v>
       </c>
       <c r="G51" s="2">
         <v>2.06</v>
       </c>
       <c r="H51" s="2">
-        <v>46.79</v>
+        <v>44.64</v>
       </c>
       <c r="I51" s="2">
-        <v>52.6</v>
+        <v>49.31</v>
       </c>
       <c r="J51" s="2">
-        <v>0.01887449509550755</v>
+        <v>0.018827874856338744</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L51" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M51" s="2">
-        <v>0.11942266696443427</v>
+        <v>0.0936956312945989</v>
       </c>
       <c r="N51" s="2">
-        <v>21.96498562173847</v>
+        <v>21.197384315333462</v>
       </c>
       <c r="O51" s="2">
-        <v>70.88607594936708</v>
+        <v>69.62025316455697</v>
       </c>
       <c r="P51" s="2">
-        <v>16.096535574030653</v>
+        <v>16.492575418924176</v>
       </c>
       <c r="Q51" s="2">
-        <v>59.49367088607595</v>
+        <v>59.24050632911392</v>
       </c>
       <c r="R51" s="2">
-        <v>54.87341772151899</v>
+        <v>54.49367088607596</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-8.16</v>
+        <v>-8.54</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -5258,49 +5261,49 @@
         <v>6.03</v>
       </c>
       <c r="F52" s="3">
-        <v>-0.3448639226079545</v>
+        <v>-0.36877679077385783</v>
       </c>
       <c r="G52" s="3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H52" s="3">
         <v>52.72</v>
       </c>
       <c r="I52" s="3">
-        <v>-16.24</v>
+        <v>-16.26</v>
       </c>
       <c r="J52" s="3">
-        <v>-0.03458856370187141</v>
+        <v>-0.031104857918810264</v>
       </c>
       <c r="K52" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>-1</v>
       </c>
       <c r="M52" s="3">
-        <v>-0.29654624041136124</v>
+        <v>-0.30963627425155316</v>
       </c>
       <c r="N52" s="3">
-        <v>-19.63190511584108</v>
+        <v>-19.13580623928174</v>
       </c>
       <c r="O52" s="3">
-        <v>7.59493670886076</v>
+        <v>10.126582278481013</v>
       </c>
       <c r="P52" s="3">
         <v>45.32019556900826</v>
       </c>
       <c r="Q52" s="3">
-        <v>42.27848101265823</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="R52" s="3">
-        <v>23.10126582278481</v>
+        <v>24.11392405063291</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>99</v>
       </c>
       <c r="T52" s="3">
-        <v>1.33</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -5311,7 +5314,7 @@
         <v>-3.88</v>
       </c>
       <c r="C53" s="1">
-        <v>7.59493670886076</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="D53" s="1">
         <v>13.440721649484537</v>
@@ -5320,19 +5323,19 @@
         <v>37.01</v>
       </c>
       <c r="F53" s="1">
-        <v>0.10597560752549204</v>
+        <v>0.135880921718201</v>
       </c>
       <c r="G53" s="1">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H53" s="1">
-        <v>58.17</v>
+        <v>61.43</v>
       </c>
       <c r="I53" s="1">
-        <v>39.33</v>
+        <v>46.62</v>
       </c>
       <c r="J53" s="1">
-        <v>0.02574109483902342</v>
+        <v>0.03191733253584712</v>
       </c>
       <c r="K53" s="1" t="b">
         <v>0</v>
@@ -5341,28 +5344,28 @@
         <v>95</v>
       </c>
       <c r="M53" s="1">
-        <v>0.22945412869456372</v>
+        <v>0.2821192898460816</v>
       </c>
       <c r="N53" s="1">
-        <v>32.96813179475143</v>
+        <v>40.039750170481724</v>
       </c>
       <c r="O53" s="1">
-        <v>82.27848101265823</v>
+        <v>84.81012658227847</v>
       </c>
       <c r="P53" s="1">
         <v>46.744012320672994</v>
       </c>
       <c r="Q53" s="1">
-        <v>52.91139240506329</v>
+        <v>54.303797468354425</v>
       </c>
       <c r="R53" s="1">
-        <v>42.84810126582279</v>
+        <v>43.79746835443038</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>113</v>
       </c>
       <c r="T53" s="1">
-        <v>16.2</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5382,49 +5385,49 @@
         <v>-0.82</v>
       </c>
       <c r="F54" s="2">
-        <v>0.10120144890343571</v>
+        <v>0.11940183329063642</v>
       </c>
       <c r="G54" s="2">
         <v>1.86</v>
       </c>
       <c r="H54" s="2">
-        <v>66.57</v>
+        <v>66.01</v>
       </c>
       <c r="I54" s="2">
-        <v>67.22</v>
+        <v>65.79</v>
       </c>
       <c r="J54" s="2">
-        <v>0.037186109509096</v>
+        <v>0.03812273394786268</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L54" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M54" s="2">
-        <v>0.17815183166097315</v>
+        <v>0.2118760954891492</v>
       </c>
       <c r="N54" s="2">
-        <v>27.83790209139237</v>
+        <v>33.0154307347885</v>
       </c>
       <c r="O54" s="2">
-        <v>78.48101265822784</v>
+        <v>79.74683544303798</v>
       </c>
       <c r="P54" s="2">
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>69.11392405063292</v>
+        <v>68.60759493670886</v>
       </c>
       <c r="R54" s="2">
-        <v>58.037974683544306</v>
+        <v>58.41772151898735</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T54" s="2">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -5444,19 +5447,19 @@
         <v>6.07</v>
       </c>
       <c r="F55" s="1">
-        <v>0.05248404262112047</v>
+        <v>-0.03382289925919629</v>
       </c>
       <c r="G55" s="1">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="H55" s="1">
-        <v>65.48</v>
+        <v>65.64</v>
       </c>
       <c r="I55" s="1">
-        <v>-9.98</v>
+        <v>-9.78</v>
       </c>
       <c r="J55" s="1">
-        <v>0.02199521827200483</v>
+        <v>0.025689062074226256</v>
       </c>
       <c r="K55" s="1" t="b">
         <v>0</v>
@@ -5465,28 +5468,28 @@
         <v>-16</v>
       </c>
       <c r="M55" s="1">
-        <v>0.19564754542584128</v>
+        <v>0.1392975218333683</v>
       </c>
       <c r="N55" s="1">
-        <v>29.58747346787918</v>
+        <v>25.7575733692104</v>
       </c>
       <c r="O55" s="1">
-        <v>81.0126582278481</v>
+        <v>73.41772151898735</v>
       </c>
       <c r="P55" s="1">
         <v>47.39629233644822</v>
       </c>
       <c r="Q55" s="1">
-        <v>49.620253164556964</v>
+        <v>50.00000000000001</v>
       </c>
       <c r="R55" s="1">
-        <v>42.53164556962026</v>
+        <v>40.8860759493671</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>94</v>
       </c>
       <c r="T55" s="1">
-        <v>7.41</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5494,31 +5497,31 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="C56" s="2">
-        <v>35.44303797468354</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="D56" s="2">
-        <v>41.24074074074074</v>
+        <v>33.92424242424242</v>
       </c>
       <c r="E56" s="2">
         <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>0.022402888636216478</v>
+        <v>-0.061814392023507386</v>
       </c>
       <c r="G56" s="2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H56" s="2">
-        <v>63.6</v>
+        <v>44.88</v>
       </c>
       <c r="I56" s="2">
-        <v>14.55</v>
+        <v>-2.52</v>
       </c>
       <c r="J56" s="2">
-        <v>0.03219276760462638</v>
+        <v>0.02990603370605665</v>
       </c>
       <c r="K56" s="2" t="b">
         <v>1</v>
@@ -5527,28 +5530,28 @@
         <v>13</v>
       </c>
       <c r="M56" s="2">
-        <v>0.06535193947763274</v>
+        <v>-0.011276132449901555</v>
       </c>
       <c r="N56" s="2">
-        <v>16.55791287305832</v>
+        <v>10.700207940883413</v>
       </c>
       <c r="O56" s="2">
-        <v>65.82278481012658</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q56" s="2">
-        <v>66.70886075949367</v>
+        <v>58.73417721518987</v>
       </c>
       <c r="R56" s="2">
-        <v>53.291139240506325</v>
+        <v>50.75949367088608</v>
       </c>
       <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T56" s="2">
-        <v>0.63</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -5568,49 +5571,49 @@
         <v>-1.23</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.12953683039746422</v>
+        <v>-0.1690381334200837</v>
       </c>
       <c r="G57" s="1">
         <v>1.2</v>
       </c>
       <c r="H57" s="1">
-        <v>47.32</v>
+        <v>45.19</v>
       </c>
       <c r="I57" s="1">
-        <v>-1.35</v>
+        <v>-2.03</v>
       </c>
       <c r="J57" s="1">
-        <v>0.007833236236756675</v>
+        <v>0.008148559390721215</v>
       </c>
       <c r="K57" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>-63</v>
+        <v>-62</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.11164139254687411</v>
+        <v>-0.14753249104833654</v>
       </c>
       <c r="N57" s="1">
-        <v>-1.141420329392365</v>
+        <v>-2.9254279189600743</v>
       </c>
       <c r="O57" s="1">
-        <v>40.50632911392405</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P57" s="1">
         <v>18.39301096820415</v>
       </c>
       <c r="Q57" s="1">
-        <v>49.11392405063292</v>
+        <v>48.481012658227854</v>
       </c>
       <c r="R57" s="1">
-        <v>40.82278481012658</v>
+        <v>39.55696202531646</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T57" s="1">
-        <v>4.24</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -5630,31 +5633,31 @@
         <v>1.28</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.09062786773933754</v>
+        <v>-0.09074659291964061</v>
       </c>
       <c r="G58" s="1">
         <v>0.26</v>
       </c>
       <c r="H58" s="1">
-        <v>52.43</v>
+        <v>51.54</v>
       </c>
       <c r="I58" s="1">
-        <v>9.45</v>
+        <v>9.07</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.004836146806834635</v>
+        <v>-0.004236304102651456</v>
       </c>
       <c r="K58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.1568409877865209</v>
+        <v>-0.17031746969510508</v>
       </c>
       <c r="N58" s="1">
-        <v>-5.661379853357042</v>
+        <v>-5.203925783636928</v>
       </c>
       <c r="O58" s="1">
         <v>30.37974683544304</v>
@@ -5663,16 +5666,16 @@
         <v>10.95912073621325</v>
       </c>
       <c r="Q58" s="1">
-        <v>45.82278481012658</v>
+        <v>44.43037974683544</v>
       </c>
       <c r="R58" s="1">
-        <v>35.63291139240506</v>
+        <v>35.75949367088607</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>115</v>
       </c>
       <c r="T58" s="1">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5692,31 +5695,31 @@
         <v>-1.3</v>
       </c>
       <c r="F59" s="2">
-        <v>0.967263257879577</v>
+        <v>0.9857913782483314</v>
       </c>
       <c r="G59" s="2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H59" s="2">
-        <v>76.45</v>
+        <v>75.68</v>
       </c>
       <c r="I59" s="2">
-        <v>180.89</v>
+        <v>176.07</v>
       </c>
       <c r="J59" s="2">
-        <v>0.0791856725928882</v>
+        <v>0.08341771605575592</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L59" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M59" s="2">
-        <v>1.0638986222727636</v>
+        <v>1.1040724112929408</v>
       </c>
       <c r="N59" s="2">
-        <v>116.41258115257138</v>
+        <v>122.23506231516765</v>
       </c>
       <c r="O59" s="2">
         <v>94.9367088607595</v>
@@ -5725,7 +5728,7 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>81.51898734177216</v>
+        <v>81.26582278481013</v>
       </c>
       <c r="R59" s="2">
         <v>67.65822784810126</v>
@@ -5754,49 +5757,49 @@
         <v>-0.04</v>
       </c>
       <c r="F60" s="2">
-        <v>0.06071532254390745</v>
+        <v>0.0009068128771221595</v>
       </c>
       <c r="G60" s="2">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="H60" s="2">
-        <v>49.11</v>
+        <v>43.88</v>
       </c>
       <c r="I60" s="2">
-        <v>38.5</v>
+        <v>33.37</v>
       </c>
       <c r="J60" s="2">
-        <v>0.021713824423646638</v>
+        <v>0.020949342602410874</v>
       </c>
       <c r="K60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L60" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M60" s="2">
-        <v>0.07771598850196804</v>
+        <v>0.018111326774519876</v>
       </c>
       <c r="N60" s="2">
-        <v>17.794317775491848</v>
+        <v>13.63895386332557</v>
       </c>
       <c r="O60" s="2">
-        <v>68.35443037974683</v>
+        <v>60.75949367088608</v>
       </c>
       <c r="P60" s="2">
-        <v>11.981421797928204</v>
+        <v>13.3558954863305</v>
       </c>
       <c r="Q60" s="2">
-        <v>57.59493670886076</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="R60" s="2">
-        <v>53.29113924050634</v>
+        <v>50.75949367088608</v>
       </c>
       <c r="S60" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T60" s="2">
-        <v>-3.29</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -5816,49 +5819,49 @@
         <v>0.85</v>
       </c>
       <c r="F61" s="3">
-        <v>-0.17053382495079067</v>
+        <v>-0.1775792879658301</v>
       </c>
       <c r="G61" s="3">
         <v>0.37</v>
       </c>
       <c r="H61" s="3">
-        <v>40.8</v>
+        <v>38.3</v>
       </c>
       <c r="I61" s="3">
-        <v>-1.95</v>
+        <v>-2.91</v>
       </c>
       <c r="J61" s="3">
-        <v>-0.0071436782649213606</v>
+        <v>-0.006988588314239928</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L61" s="3">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M61" s="3">
-        <v>-0.22690445418014948</v>
+        <v>-0.24532206143683366</v>
       </c>
       <c r="N61" s="3">
-        <v>-12.667726492719897</v>
+        <v>-12.704384957809786</v>
       </c>
       <c r="O61" s="3">
-        <v>16.455696202531644</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="P61" s="3">
         <v>14.552180197083512</v>
       </c>
       <c r="Q61" s="3">
-        <v>34.810126582278485</v>
+        <v>33.67088607594937</v>
       </c>
       <c r="R61" s="3">
-        <v>26.26582278481013</v>
+        <v>25.75949367088608</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>95</v>
       </c>
       <c r="T61" s="3">
-        <v>-2.53</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -5878,19 +5881,19 @@
         <v>-0.19</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.2450517623307163</v>
+        <v>-0.24063858910734787</v>
       </c>
       <c r="G62" s="1">
         <v>0.93</v>
       </c>
       <c r="H62" s="1">
-        <v>33.08</v>
+        <v>38.8</v>
       </c>
       <c r="I62" s="1">
-        <v>1.63</v>
+        <v>3.45</v>
       </c>
       <c r="J62" s="1">
-        <v>-0.008392615499502975</v>
+        <v>-0.008505660486717501</v>
       </c>
       <c r="K62" s="1" t="b">
         <v>1</v>
@@ -5899,10 +5902,10 @@
         <v>169</v>
       </c>
       <c r="M62" s="1">
-        <v>-0.2513151655784228</v>
+        <v>-0.24816556393745937</v>
       </c>
       <c r="N62" s="1">
-        <v>-15.10879763254723</v>
+        <v>-12.98873520787236</v>
       </c>
       <c r="O62" s="1">
         <v>13.924050632911392</v>
@@ -5911,16 +5914,16 @@
         <v>20.131624188012864</v>
       </c>
       <c r="Q62" s="1">
-        <v>45.44303797468354</v>
+        <v>44.81012658227848</v>
       </c>
       <c r="R62" s="1">
-        <v>33.101265822784804</v>
+        <v>32.46835443037974</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="1">
-        <v>-9.75</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5934,25 +5937,25 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D63" s="4">
-        <v>4.9409106708376775</v>
+        <v>4.967674661105318</v>
       </c>
       <c r="E63" s="4">
         <v>-3.33</v>
       </c>
       <c r="F63" s="4">
-        <v>1.073080743491981</v>
+        <v>0.990278222830926</v>
       </c>
       <c r="G63" s="4">
         <v>4.81</v>
       </c>
       <c r="H63" s="4">
-        <v>68.36</v>
+        <v>70.32</v>
       </c>
       <c r="I63" s="4">
-        <v>236.84</v>
+        <v>242.01</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09080921656329333</v>
+        <v>0.09240783649048698</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
@@ -5961,28 +5964,28 @@
         <v>475</v>
       </c>
       <c r="M63" s="4">
-        <v>1.413988834545722</v>
+        <v>1.3999607100127094</v>
       </c>
       <c r="N63" s="4">
-        <v>151.42160237986727</v>
+        <v>151.8238921871445</v>
       </c>
       <c r="O63" s="4">
-        <v>98.73417721518987</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.9113924050633</v>
+        <v>82.40506329113924</v>
       </c>
       <c r="R63" s="4">
-        <v>71.7721518987342</v>
+        <v>70.69620253164558</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>-0.57</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -6002,19 +6005,19 @@
         <v>-1.41</v>
       </c>
       <c r="F64" s="2">
-        <v>0.8697306408922579</v>
+        <v>0.9175696518620894</v>
       </c>
       <c r="G64" s="2">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="H64" s="2">
-        <v>73.83</v>
+        <v>74.67</v>
       </c>
       <c r="I64" s="2">
-        <v>141.54</v>
+        <v>141.89</v>
       </c>
       <c r="J64" s="2">
-        <v>0.07804193826126511</v>
+        <v>0.08032797368304492</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
@@ -6023,10 +6026,10 @@
         <v>202</v>
       </c>
       <c r="M64" s="2">
-        <v>0.9636816896078559</v>
+        <v>1.0315495564323494</v>
       </c>
       <c r="N64" s="2">
-        <v>106.39088788608065</v>
+        <v>114.98277682910849</v>
       </c>
       <c r="O64" s="2">
         <v>93.67088607594937</v>
@@ -6064,49 +6067,49 @@
         <v>0.14</v>
       </c>
       <c r="F65" s="1">
-        <v>-0.1324694381762026</v>
+        <v>-0.10999032958359173</v>
       </c>
       <c r="G65" s="1">
         <v>0.3</v>
       </c>
       <c r="H65" s="1">
-        <v>50.38</v>
+        <v>58.52</v>
       </c>
       <c r="I65" s="1">
-        <v>0.42</v>
+        <v>2.8</v>
       </c>
       <c r="J65" s="1">
-        <v>-0.010523522588461044</v>
+        <v>-0.008105147602120888</v>
       </c>
       <c r="K65" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="1">
         <v>56</v>
       </c>
       <c r="M65" s="1">
-        <v>-0.19510347065326794</v>
+        <v>-0.18526007788470678</v>
       </c>
       <c r="N65" s="1">
-        <v>-9.487628140031749</v>
+        <v>-6.698186602597106</v>
       </c>
       <c r="O65" s="1">
-        <v>21.518987341772153</v>
+        <v>25.31645569620253</v>
       </c>
       <c r="P65" s="1">
         <v>15.211254913322609</v>
       </c>
       <c r="Q65" s="1">
-        <v>42.025316455696206</v>
+        <v>44.556962025316466</v>
       </c>
       <c r="R65" s="1">
-        <v>32.025316455696206</v>
+        <v>33.54430379746835</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>98</v>
       </c>
       <c r="T65" s="1">
-        <v>-5.38</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -6126,49 +6129,49 @@
         <v>1.66</v>
       </c>
       <c r="F66" s="3">
-        <v>-0.29033986720615956</v>
+        <v>-0.32148208675405354</v>
       </c>
       <c r="G66" s="3">
         <v>0.97</v>
       </c>
       <c r="H66" s="3">
-        <v>31.76</v>
+        <v>33.69</v>
       </c>
       <c r="I66" s="3">
-        <v>-44.51</v>
+        <v>-43.36</v>
       </c>
       <c r="J66" s="3">
-        <v>-0.029288516712837352</v>
+        <v>-0.033132146272255095</v>
       </c>
       <c r="K66" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L66" s="3">
-        <v>-195</v>
+        <v>-196</v>
       </c>
       <c r="M66" s="3">
-        <v>-0.2930241828837481</v>
+        <v>-0.3247079331098156</v>
       </c>
       <c r="N66" s="3">
-        <v>-19.279699363079757</v>
+        <v>-20.642972125107985</v>
       </c>
       <c r="O66" s="3">
-        <v>8.860759493670885</v>
+        <v>6.329113924050633</v>
       </c>
       <c r="P66" s="3">
         <v>54.854261650729526</v>
       </c>
       <c r="Q66" s="3">
-        <v>32.40506329113924</v>
+        <v>32.025316455696206</v>
       </c>
       <c r="R66" s="3">
-        <v>19.11392405063291</v>
+        <v>18.10126582278481</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>96</v>
       </c>
       <c r="T66" s="3">
-        <v>-9.94</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -6188,49 +6191,49 @@
         <v>-0.68</v>
       </c>
       <c r="F67" s="1">
-        <v>-0.14069347377103392</v>
+        <v>-0.18412860031631492</v>
       </c>
       <c r="G67" s="1">
         <v>1.13</v>
       </c>
       <c r="H67" s="1">
-        <v>38.44</v>
+        <v>39.24</v>
       </c>
       <c r="I67" s="1">
-        <v>-15.69</v>
+        <v>-15.36</v>
       </c>
       <c r="J67" s="1">
-        <v>-0.0019967834944604667</v>
+        <v>-0.004448981943545205</v>
       </c>
       <c r="K67" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>-76</v>
+        <v>-77</v>
       </c>
       <c r="M67" s="1">
-        <v>-0.12906143916815038</v>
+        <v>-0.17014993277467927</v>
       </c>
       <c r="N67" s="1">
-        <v>-2.8834249915199854</v>
+        <v>-5.187172091594346</v>
       </c>
       <c r="O67" s="1">
-        <v>35.44303797468354</v>
+        <v>31.645569620253166</v>
       </c>
       <c r="P67" s="1">
         <v>21.01837744312229</v>
       </c>
       <c r="Q67" s="1">
-        <v>44.55696202531645</v>
+        <v>42.151898734177216</v>
       </c>
       <c r="R67" s="1">
-        <v>38.67088607594937</v>
+        <v>36.518987341772146</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T67" s="1">
-        <v>-5.44</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -6250,19 +6253,19 @@
         <v>-0.41</v>
       </c>
       <c r="F68" s="1">
-        <v>-0.13156345071281003</v>
+        <v>-0.09874876235403014</v>
       </c>
       <c r="G68" s="1">
         <v>0.33</v>
       </c>
       <c r="H68" s="1">
-        <v>51.02</v>
+        <v>57.16</v>
       </c>
       <c r="I68" s="1">
-        <v>4.04</v>
+        <v>5.94</v>
       </c>
       <c r="J68" s="1">
-        <v>-0.009799406985092737</v>
+        <v>-0.008404114944081924</v>
       </c>
       <c r="K68" s="1" t="b">
         <v>0</v>
@@ -6271,28 +6274,28 @@
         <v>146</v>
       </c>
       <c r="M68" s="1">
-        <v>-0.19151316751228686</v>
+        <v>-0.1707926642993831</v>
       </c>
       <c r="N68" s="1">
-        <v>-9.128597825933635</v>
+        <v>-5.251445244064732</v>
       </c>
       <c r="O68" s="1">
-        <v>22.78481012658228</v>
+        <v>29.11392405063291</v>
       </c>
       <c r="P68" s="1">
         <v>18.003852697255347</v>
       </c>
       <c r="Q68" s="1">
-        <v>61.51898734177216</v>
+        <v>62.27848101265823</v>
       </c>
       <c r="R68" s="1">
-        <v>46.77215189873418</v>
+        <v>48.67088607594937</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>108</v>
       </c>
       <c r="T68" s="1">
-        <v>1.84</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -6312,19 +6315,19 @@
         <v>-0.24</v>
       </c>
       <c r="F69" s="3">
-        <v>-0.31628018404673813</v>
+        <v>-0.3330565266683868</v>
       </c>
       <c r="G69" s="3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H69" s="3">
-        <v>36.33</v>
+        <v>39.46</v>
       </c>
       <c r="I69" s="3">
-        <v>-15.54</v>
+        <v>-14.47</v>
       </c>
       <c r="J69" s="3">
-        <v>-0.010046907446086535</v>
+        <v>-0.011032815385040862</v>
       </c>
       <c r="K69" s="3" t="b">
         <v>0</v>
@@ -6333,10 +6336,10 @@
         <v>-69</v>
       </c>
       <c r="M69" s="3">
-        <v>-0.2733311332053219</v>
+        <v>-0.282518267094781</v>
       </c>
       <c r="N69" s="3">
-        <v>-17.310394395237143</v>
+        <v>-16.424005523604524</v>
       </c>
       <c r="O69" s="3">
         <v>11.39240506329114</v>
@@ -6345,78 +6348,78 @@
         <v>29.40035337282439</v>
       </c>
       <c r="Q69" s="3">
-        <v>36.582278481012665</v>
+        <v>36.20253164556962</v>
       </c>
       <c r="R69" s="3">
-        <v>24.68354430379747</v>
+        <v>24.303797468354432</v>
       </c>
       <c r="S69" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="3">
-        <v>-3.04</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="1">
         <v>18.19</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="1">
         <v>93.67088607594937</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="1">
         <v>-0.47608576140736675</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="1">
         <v>-1.55</v>
       </c>
-      <c r="F70" s="3">
-        <v>-0.19957937754053331</v>
-      </c>
-      <c r="G70" s="3">
+      <c r="F70" s="1">
+        <v>-0.16647888460362092</v>
+      </c>
+      <c r="G70" s="1">
         <v>0.86</v>
       </c>
-      <c r="H70" s="3">
-        <v>45.27</v>
-      </c>
-      <c r="I70" s="3">
-        <v>-13.36</v>
-      </c>
-      <c r="J70" s="3">
-        <v>-0.00631916762307576</v>
-      </c>
-      <c r="K70" s="3" t="b">
+      <c r="H70" s="1">
+        <v>60.38</v>
+      </c>
+      <c r="I70" s="1">
+        <v>-7.5</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-0.003719755361941329</v>
+      </c>
+      <c r="K70" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L70" s="3">
-        <v>-59</v>
-      </c>
-      <c r="M70" s="3">
-        <v>-0.2121061840359464</v>
-      </c>
-      <c r="N70" s="3">
-        <v>-11.187899478299594</v>
-      </c>
-      <c r="O70" s="3">
-        <v>20.253164556962027</v>
-      </c>
-      <c r="P70" s="3">
+      <c r="L70" s="1">
+        <v>-60</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.18153283426384392</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-6.325462240510812</v>
+      </c>
+      <c r="O70" s="1">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="P70" s="1">
         <v>31.450467124868602</v>
       </c>
-      <c r="Q70" s="3">
-        <v>41.89873417721519</v>
-      </c>
-      <c r="R70" s="3">
-        <v>28.60759493670886</v>
-      </c>
-      <c r="S70" s="3" t="s">
+      <c r="Q70" s="1">
+        <v>47.21518987341772</v>
+      </c>
+      <c r="R70" s="1">
+        <v>31.265822784810123</v>
+      </c>
+      <c r="S70" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T70" s="3">
-        <v>0.89</v>
+      <c r="T70" s="1">
+        <v>3.54</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -6436,19 +6439,19 @@
         <v>-0.71</v>
       </c>
       <c r="F71" s="3">
-        <v>-0.3857278835782391</v>
+        <v>-0.39152195576082705</v>
       </c>
       <c r="G71" s="3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H71" s="3">
-        <v>59.12</v>
+        <v>65.43</v>
       </c>
       <c r="I71" s="3">
-        <v>-25.03</v>
+        <v>-22.59</v>
       </c>
       <c r="J71" s="3">
-        <v>-0.02148246863470858</v>
+        <v>-0.019821917707988305</v>
       </c>
       <c r="K71" s="3" t="b">
         <v>0</v>
@@ -6457,10 +6460,10 @@
         <v>-99</v>
       </c>
       <c r="M71" s="3">
-        <v>-0.37499062086788504</v>
+        <v>-0.37754328821919136</v>
       </c>
       <c r="N71" s="3">
-        <v>-27.47634316149346</v>
+        <v>-25.926507636045553</v>
       </c>
       <c r="O71" s="3">
         <v>2.5316455696202533</v>
@@ -6469,7 +6472,7 @@
         <v>36.83258048205344</v>
       </c>
       <c r="Q71" s="3">
-        <v>42.78481012658227</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="R71" s="3">
         <v>23.037974683544302</v>
@@ -6482,65 +6485,65 @@
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="3">
         <v>10.42</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="3">
         <v>78.48101265822784</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="3">
         <v>0.21976967370441466</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="3">
         <v>-0.66</v>
       </c>
-      <c r="F72" s="1">
-        <v>-0.2450982890424066</v>
-      </c>
-      <c r="G72" s="1">
+      <c r="F72" s="3">
+        <v>-0.28689661464395877</v>
+      </c>
+      <c r="G72" s="3">
         <v>1.14</v>
       </c>
-      <c r="H72" s="1">
-        <v>45.15</v>
-      </c>
-      <c r="I72" s="1">
-        <v>-8.65</v>
-      </c>
-      <c r="J72" s="1">
-        <v>-0.004101937600406126</v>
-      </c>
-      <c r="K72" s="1" t="b">
+      <c r="H72" s="3">
+        <v>41.27</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-10.01</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-0.0036671651469527664</v>
+      </c>
+      <c r="K72" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L72" s="1">
+      <c r="L72" s="3">
         <v>2</v>
       </c>
-      <c r="M72" s="1">
-        <v>-0.23257148254699356</v>
-      </c>
-      <c r="N72" s="1">
-        <v>-13.234429329404303</v>
-      </c>
-      <c r="O72" s="1">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="P72" s="1">
+      <c r="M72" s="3">
+        <v>-0.27184266498373577</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-15.3564453125</v>
+      </c>
+      <c r="O72" s="3">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P72" s="3">
         <v>19.739671794345924</v>
       </c>
-      <c r="Q72" s="1">
-        <v>42.91139240506329</v>
-      </c>
-      <c r="R72" s="1">
-        <v>30.569620253164558</v>
-      </c>
-      <c r="S72" s="1" t="s">
+      <c r="Q72" s="3">
+        <v>41.77215189873418</v>
+      </c>
+      <c r="R72" s="3">
+        <v>29.936708860759488</v>
+      </c>
+      <c r="S72" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T72" s="1">
-        <v>3.1</v>
+      <c r="T72" s="3">
+        <v>2.47</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -6551,7 +6554,7 @@
         <v>0.61</v>
       </c>
       <c r="C73" s="2">
-        <v>36.708860759493675</v>
+        <v>35.44303797468354</v>
       </c>
       <c r="D73" s="2">
         <v>20.426229508196723</v>
@@ -6560,19 +6563,19 @@
         <v>3.07</v>
       </c>
       <c r="F73" s="2">
-        <v>0.3947015317376794</v>
+        <v>0.3805390580667171</v>
       </c>
       <c r="G73" s="2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H73" s="2">
-        <v>65.33</v>
+        <v>65.9</v>
       </c>
       <c r="I73" s="2">
-        <v>45.36</v>
+        <v>45.37</v>
       </c>
       <c r="J73" s="2">
-        <v>0.0323241834550241</v>
+        <v>0.03203822739406988</v>
       </c>
       <c r="K73" s="2" t="b">
         <v>0</v>
@@ -6581,28 +6584,28 @@
         <v>29</v>
       </c>
       <c r="M73" s="2">
-        <v>0.41170219769574</v>
+        <v>0.39989413620128955</v>
       </c>
       <c r="N73" s="2">
-        <v>51.19293869486904</v>
+        <v>51.817234806002546</v>
       </c>
       <c r="O73" s="2">
-        <v>87.34177215189874</v>
+        <v>86.07594936708861</v>
       </c>
       <c r="P73" s="2">
         <v>9.507882188735834</v>
       </c>
       <c r="Q73" s="2">
-        <v>66.83544303797468</v>
+        <v>66.0759493670886</v>
       </c>
       <c r="R73" s="2">
-        <v>62.151898734177216</v>
+        <v>61.455696202531655</v>
       </c>
       <c r="S73" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T73" s="2">
-        <v>1.14</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -6622,19 +6625,19 @@
         <v>1.29</v>
       </c>
       <c r="F74" s="2">
-        <v>0.16879989826501837</v>
+        <v>0.14381446096880612</v>
       </c>
       <c r="G74" s="2">
         <v>0.78</v>
       </c>
       <c r="H74" s="2">
-        <v>80.86</v>
+        <v>81.75</v>
       </c>
       <c r="I74" s="2">
-        <v>29.69</v>
+        <v>29.52</v>
       </c>
       <c r="J74" s="2">
-        <v>0.014654803180689104</v>
+        <v>0.014308691877174288</v>
       </c>
       <c r="K74" s="2" t="b">
         <v>1</v>
@@ -6643,28 +6646,28 @@
         <v>13</v>
       </c>
       <c r="M74" s="2">
-        <v>0.14911491662936927</v>
+        <v>0.12015825435988425</v>
       </c>
       <c r="N74" s="2">
-        <v>24.934210588231974</v>
+        <v>23.843646621861993</v>
       </c>
       <c r="O74" s="2">
-        <v>75.9493670886076</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P74" s="2">
         <v>3.6747023875523213</v>
       </c>
       <c r="Q74" s="2">
-        <v>63.54430379746836</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="R74" s="2">
-        <v>56.8987341772152</v>
+        <v>55.25316455696203</v>
       </c>
       <c r="S74" s="2" t="s">
         <v>121</v>
       </c>
       <c r="T74" s="2">
-        <v>0.57</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -6684,19 +6687,19 @@
         <v>-0.35</v>
       </c>
       <c r="F75" s="1">
-        <v>-0.05524168805004072</v>
+        <v>-0.047437591487865804</v>
       </c>
       <c r="G75" s="1">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H75" s="1">
-        <v>54.77</v>
+        <v>60.87</v>
       </c>
       <c r="I75" s="1">
-        <v>13.34</v>
+        <v>17.34</v>
       </c>
       <c r="J75" s="1">
-        <v>0.021000318728723905</v>
+        <v>0.022986148607532116</v>
       </c>
       <c r="K75" s="1" t="b">
         <v>0</v>
@@ -6705,28 +6708,28 @@
         <v>21</v>
       </c>
       <c r="M75" s="1">
-        <v>-0.05792600372762924</v>
+        <v>-0.05173871996221524</v>
       </c>
       <c r="N75" s="1">
-        <v>4.230118552532127</v>
+        <v>6.653949189652045</v>
       </c>
       <c r="O75" s="1">
-        <v>50.63291139240506</v>
+        <v>51.89873417721519</v>
       </c>
       <c r="P75" s="1">
         <v>37.05001195108517</v>
       </c>
       <c r="Q75" s="1">
-        <v>59.36708860759494</v>
+        <v>61.26582278481013</v>
       </c>
       <c r="R75" s="1">
-        <v>42.911392405063296</v>
+        <v>43.41772151898735</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>107</v>
       </c>
       <c r="T75" s="1">
-        <v>-3.54</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -6746,19 +6749,19 @@
         <v>0.91</v>
       </c>
       <c r="F76" s="1">
-        <v>0.014555667701142291</v>
+        <v>0.0020970667148850763</v>
       </c>
       <c r="G76" s="1">
         <v>0.7</v>
       </c>
       <c r="H76" s="1">
-        <v>44.28</v>
+        <v>43.98</v>
       </c>
       <c r="I76" s="1">
-        <v>7.02</v>
+        <v>6.62</v>
       </c>
       <c r="J76" s="1">
-        <v>0.00960619105056567</v>
+        <v>0.008903600047839343</v>
       </c>
       <c r="K76" s="1" t="b">
         <v>0</v>
@@ -6767,28 +6770,28 @@
         <v>4</v>
       </c>
       <c r="M76" s="1">
-        <v>-0.012287489074742863</v>
+        <v>-0.030161396842735666</v>
       </c>
       <c r="N76" s="1">
-        <v>8.79397001782077</v>
+        <v>8.811681501600022</v>
       </c>
       <c r="O76" s="1">
-        <v>59.49367088607595</v>
+        <v>54.43037974683544</v>
       </c>
       <c r="P76" s="1">
         <v>16.982798273104898</v>
       </c>
       <c r="Q76" s="1">
-        <v>44.177215189873415</v>
+        <v>44.17721518987342</v>
       </c>
       <c r="R76" s="1">
-        <v>42.27848101265823</v>
+        <v>40.75949367088609</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T76" s="1">
-        <v>0.06</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -6808,19 +6811,19 @@
         <v>2.54</v>
       </c>
       <c r="F77" s="2">
-        <v>0.0618202237627693</v>
+        <v>0.012196658225152743</v>
       </c>
       <c r="G77" s="2">
         <v>0.99</v>
       </c>
       <c r="H77" s="2">
-        <v>69.72</v>
+        <v>70.23</v>
       </c>
       <c r="I77" s="2">
-        <v>16.24</v>
+        <v>16.42</v>
       </c>
       <c r="J77" s="2">
-        <v>0.016732283036046857</v>
+        <v>0.01785788725272515</v>
       </c>
       <c r="K77" s="2" t="b">
         <v>1</v>
@@ -6829,28 +6832,28 @@
         <v>6</v>
       </c>
       <c r="M77" s="2">
-        <v>0.06092545187023979</v>
+        <v>0.011121376106565384</v>
       </c>
       <c r="N77" s="2">
-        <v>16.115264112319018</v>
+        <v>12.939958796530126</v>
       </c>
       <c r="O77" s="2">
-        <v>64.55696202531645</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P77" s="2">
         <v>8.54788795515236</v>
       </c>
       <c r="Q77" s="2">
-        <v>65.69620253164557</v>
+        <v>65.18987341772151</v>
       </c>
       <c r="R77" s="2">
-        <v>56.26582278481013</v>
+        <v>54.87341772151898</v>
       </c>
       <c r="S77" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T77" s="2">
-        <v>1.84</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -6864,25 +6867,25 @@
         <v>84.81012658227847</v>
       </c>
       <c r="D78" s="1">
-        <v>-0.7139588100686499</v>
+        <v>-0.7147215865751334</v>
       </c>
       <c r="E78" s="1">
         <v>0.76</v>
       </c>
       <c r="F78" s="1">
-        <v>0.10766923403081889</v>
+        <v>0.11302067508436356</v>
       </c>
       <c r="G78" s="1">
         <v>1.24</v>
       </c>
       <c r="H78" s="1">
-        <v>60.71</v>
+        <v>61.55</v>
       </c>
       <c r="I78" s="1">
-        <v>29.19</v>
+        <v>29.22</v>
       </c>
       <c r="J78" s="1">
-        <v>0.02351360039616708</v>
+        <v>0.023329371174457818</v>
       </c>
       <c r="K78" s="1" t="b">
         <v>0</v>
@@ -6891,28 +6894,28 @@
         <v>58</v>
       </c>
       <c r="M78" s="1">
-        <v>0.129143759451527</v>
+        <v>0.13882744593046015</v>
       </c>
       <c r="N78" s="1">
-        <v>22.937094870447748</v>
+        <v>25.71056577891959</v>
       </c>
       <c r="O78" s="1">
-        <v>73.41772151898735</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P78" s="1">
         <v>20.806025084936465</v>
       </c>
       <c r="Q78" s="1">
-        <v>57.34177215189874</v>
+        <v>56.708860759493675</v>
       </c>
       <c r="R78" s="1">
-        <v>49.683544303797476</v>
+        <v>48.924050632911396</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>106</v>
       </c>
       <c r="T78" s="1">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -6932,19 +6935,19 @@
         <v>0.81</v>
       </c>
       <c r="F79" s="2">
-        <v>0.41407491791311823</v>
+        <v>0.402950479236028</v>
       </c>
       <c r="G79" s="2">
         <v>0.98</v>
       </c>
       <c r="H79" s="2">
-        <v>76.77</v>
+        <v>74.2</v>
       </c>
       <c r="I79" s="2">
-        <v>52.71</v>
+        <v>50.93</v>
       </c>
       <c r="J79" s="2">
-        <v>0.0457547866299621</v>
+        <v>0.045991211102388116</v>
       </c>
       <c r="K79" s="2" t="b">
         <v>0</v>
@@ -6953,10 +6956,10 @@
         <v>79</v>
       </c>
       <c r="M79" s="2">
-        <v>0.4122853741280592</v>
+        <v>0.40079991499885326</v>
       </c>
       <c r="N79" s="2">
-        <v>51.25125633810097</v>
+        <v>51.90781268575891</v>
       </c>
       <c r="O79" s="2">
         <v>88.60759493670885</v>
@@ -6965,7 +6968,7 @@
         <v>13.574555133673535</v>
       </c>
       <c r="Q79" s="2">
-        <v>65.56962025316456</v>
+        <v>64.81012658227847</v>
       </c>
       <c r="R79" s="2">
         <v>58.9873417721519</v>
@@ -6994,19 +6997,19 @@
         <v>-1.21</v>
       </c>
       <c r="F80" s="2">
-        <v>1.3643470019048707</v>
+        <v>1.4825835307512312</v>
       </c>
       <c r="G80" s="2">
         <v>1.09</v>
       </c>
       <c r="H80" s="2">
-        <v>78.2</v>
+        <v>80.18</v>
       </c>
       <c r="I80" s="2">
-        <v>100.92</v>
+        <v>107.42</v>
       </c>
       <c r="J80" s="2">
-        <v>0.0671896932162768</v>
+        <v>0.07313097855736095</v>
       </c>
       <c r="K80" s="2" t="b">
         <v>1</v>
@@ -7015,28 +7018,28 @@
         <v>139</v>
       </c>
       <c r="M80" s="2">
-        <v>1.3723999489376362</v>
+        <v>1.4922610698185175</v>
       </c>
       <c r="N80" s="2">
-        <v>147.26271381905866</v>
+        <v>161.05392816772533</v>
       </c>
       <c r="O80" s="2">
-        <v>97.46835443037975</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P80" s="2">
         <v>13.172294180200911</v>
       </c>
       <c r="Q80" s="2">
-        <v>71.77215189873417</v>
+        <v>72.0253164556962</v>
       </c>
       <c r="R80" s="2">
-        <v>66.26582278481013</v>
+        <v>66.8987341772152</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T80" s="2">
-        <v>2.03</v>
+        <v>2.66</v>
       </c>
     </row>
   </sheetData>
@@ -7055,7 +7058,7 @@
         <v>128</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -7063,7 +7066,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32.40506329113924</v>
+        <v>31.26582278481013</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -7071,7 +7074,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65</v>
+        <v>65.37974683544304</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7079,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26.582278481012654</v>
+        <v>39.62025316455696</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -7087,7 +7090,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>46.64556962025316</v>
+        <v>46.77215189873417</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -7095,7 +7098,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>38.9873417721519</v>
+        <v>36.45569620253165</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7103,7 +7106,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.46835443037975</v>
+        <v>53.67088607594937</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7111,7 +7114,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>54.43037974683544</v>
+        <v>53.67088607594937</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -7119,7 +7122,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>37.46835443037974</v>
+        <v>40.50632911392405</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7127,7 +7130,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.037974683544306</v>
+        <v>37.151898734177216</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -7135,7 +7138,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>52.78481012658228</v>
+        <v>51.89873417721519</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7143,7 +7146,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>37.59493670886076</v>
+        <v>37.34177215189873</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7151,7 +7154,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.6075949367088596</v>
+        <v>3.8607594936708844</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -7159,7 +7162,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>46.64556962025316</v>
+        <v>47.53164556962025</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -7175,7 +7178,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>30.189873417721518</v>
+        <v>27.088607594936708</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -7183,7 +7186,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>22.531645569620252</v>
+        <v>19.240506329113924</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -7191,7 +7194,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.54430379746836</v>
+        <v>27.78481012658228</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -7207,7 +7210,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>43.48101265822784</v>
+        <v>44.36708860759494</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -7215,7 +7218,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>55.44303797468355</v>
+        <v>55.822784810126585</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -7223,7 +7226,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>35</v>
+        <v>35.12658227848101</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -7231,7 +7234,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>35.00000000000001</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -7239,7 +7242,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>21.39240506329114</v>
+        <v>21.139240506329116</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -7247,7 +7250,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.050632911392407</v>
+        <v>3.9240506329113938</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -7255,7 +7258,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>34.05063291139241</v>
+        <v>33.41772151898734</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -7263,7 +7266,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>30.126582278481024</v>
+        <v>30.75949367088608</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -7271,7 +7274,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>22.088607594936704</v>
+        <v>21.835443037974684</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -7279,7 +7282,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>26.32911392405063</v>
+        <v>28.10126582278481</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7287,7 +7290,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>48.54430379746835</v>
+        <v>49.810126582278485</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7295,7 +7298,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>59.55696202531646</v>
+        <v>59.99999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7303,7 +7306,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>21.32911392405063</v>
+        <v>23.987341772151897</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7311,7 +7314,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>40.50632911392404</v>
+        <v>41.26582278481012</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7319,7 +7322,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>50.25316455696202</v>
+        <v>50.253164556962034</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7327,7 +7330,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>21.455696202531644</v>
+        <v>21.83544303797468</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7335,7 +7338,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>28.481012658227844</v>
+        <v>28.48101265822785</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7343,7 +7346,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>27.658227848101266</v>
+        <v>31.075949367088608</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7351,7 +7354,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>55.56962025316456</v>
+        <v>56.26582278481013</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7359,7 +7362,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>44.24050632911393</v>
+        <v>40.44303797468355</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7367,7 +7370,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>27.468354430379748</v>
+        <v>27.91139240506329</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7375,7 +7378,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>33.29113924050633</v>
+        <v>34.430379746835456</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7383,7 +7386,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>36.70886075949366</v>
+        <v>36.0759493670886</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7391,7 +7394,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>43.67088607594937</v>
+        <v>43.291139240506325</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7399,7 +7402,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>28.0379746835443</v>
+        <v>28.417721518987342</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7407,7 +7410,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>56.39240506329115</v>
+        <v>55.50632911392405</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7415,7 +7418,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>25.44303797468354</v>
+        <v>25.822784810126578</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7431,7 +7434,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>34.87341772151899</v>
+        <v>32.9746835443038</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7439,7 +7442,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>56.20253164556962</v>
+        <v>54.93670886075949</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7447,7 +7450,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>61.39240506329113</v>
+        <v>61.51898734177215</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7455,7 +7458,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>54.87341772151899</v>
+        <v>54.49367088607596</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7463,7 +7466,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>23.10126582278481</v>
+        <v>24.11392405063291</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7471,7 +7474,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>42.84810126582279</v>
+        <v>43.79746835443038</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7479,7 +7482,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>58.037974683544306</v>
+        <v>58.41772151898735</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7487,7 +7490,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>42.53164556962026</v>
+        <v>40.8860759493671</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7495,7 +7498,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>53.291139240506325</v>
+        <v>50.75949367088608</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7503,7 +7506,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>40.82278481012658</v>
+        <v>39.55696202531646</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7511,7 +7514,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>35.63291139240506</v>
+        <v>35.75949367088607</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7527,7 +7530,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>53.29113924050634</v>
+        <v>50.75949367088608</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7535,7 +7538,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>26.26582278481013</v>
+        <v>25.75949367088608</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7543,7 +7546,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>33.101265822784804</v>
+        <v>32.46835443037974</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7551,7 +7554,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>71.7721518987342</v>
+        <v>70.69620253164558</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7567,7 +7570,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>32.025316455696206</v>
+        <v>33.54430379746835</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7575,7 +7578,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>19.11392405063291</v>
+        <v>18.10126582278481</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7583,7 +7586,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>38.67088607594937</v>
+        <v>36.518987341772146</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7591,7 +7594,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>46.77215189873418</v>
+        <v>48.67088607594937</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7599,7 +7602,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>24.68354430379747</v>
+        <v>24.303797468354432</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7607,7 +7610,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>28.60759493670886</v>
+        <v>31.265822784810123</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7623,7 +7626,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>30.569620253164558</v>
+        <v>29.936708860759488</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7631,7 +7634,7 @@
         <v>119</v>
       </c>
       <c r="B73">
-        <v>62.151898734177216</v>
+        <v>61.455696202531655</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7639,7 +7642,7 @@
         <v>120</v>
       </c>
       <c r="B74">
-        <v>56.8987341772152</v>
+        <v>55.25316455696203</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7647,7 +7650,7 @@
         <v>122</v>
       </c>
       <c r="B75">
-        <v>42.911392405063296</v>
+        <v>43.41772151898735</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7655,7 +7658,7 @@
         <v>123</v>
       </c>
       <c r="B76">
-        <v>42.27848101265823</v>
+        <v>40.75949367088609</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7663,7 +7666,7 @@
         <v>124</v>
       </c>
       <c r="B77">
-        <v>56.26582278481013</v>
+        <v>54.87341772151898</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7671,7 +7674,7 @@
         <v>125</v>
       </c>
       <c r="B78">
-        <v>49.683544303797476</v>
+        <v>48.924050632911396</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7687,7 +7690,7 @@
         <v>127</v>
       </c>
       <c r="B80">
-        <v>66.26582278481013</v>
+        <v>66.8987341772152</v>
       </c>
     </row>
   </sheetData>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="231">
   <si>
     <t>Ticker</t>
   </si>
@@ -340,7 +340,7 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>2026-04-29</t>
+    <t>2027-04-29</t>
   </si>
   <si>
     <t>2027-04-28</t>
@@ -409,6 +409,9 @@
     <t>_date_</t>
   </si>
   <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
     <t>Criteria</t>
   </si>
   <si>
@@ -682,34 +685,34 @@
     <t>Momentum Breakout, Market Leader, Earnings Upcoming</t>
   </si>
   <si>
+    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Volume Spike, Institutional Buying</t>
+  </si>
+  <si>
+    <t>Institutional Buying</t>
+  </si>
+  <si>
     <t>Momentum Breakout, Market Leader, Volume Spike, Institutional Buying</t>
   </si>
   <si>
-    <t>Momentum Breakout, Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
-    <t>Institutional Buying</t>
-  </si>
-  <si>
-    <t>Volume Spike, Institutional Buying</t>
-  </si>
-  <si>
     <t>Momentum Breakout</t>
   </si>
   <si>
     <t>Earnings Upcoming, Institutional Buying</t>
   </si>
   <si>
+    <t>Earnings Upcoming</t>
+  </si>
+  <si>
     <t>Volume Spike</t>
   </si>
   <si>
     <t>Momentum Breakout, Volume Spike</t>
   </si>
   <si>
-    <t>Earnings Upcoming</t>
-  </si>
-  <si>
-    <t>Momentum Breakout, Market Leader, Volume Spike</t>
+    <t>Momentum Breakout, Market Leader</t>
   </si>
 </sst>
 </file>
@@ -734,7 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -744,7 +747,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1364,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1375,10 +1378,10 @@
         <v>62</v>
       </c>
       <c r="B2">
-        <v>70.69620253164558</v>
+        <v>72.08860759493672</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1386,29 +1389,29 @@
         <v>58</v>
       </c>
       <c r="B3">
-        <v>67.65822784810126</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="B4">
-        <v>67.0253164556962</v>
+        <v>67.34177215189875</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="B5">
-        <v>66.8987341772152</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="C5" t="s">
         <v>215</v>
@@ -1419,21 +1422,21 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>65.37974683544304</v>
+        <v>65.50632911392405</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B7">
-        <v>62.27848101265822</v>
+        <v>61.329113924050645</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1441,21 +1444,21 @@
         <v>49</v>
       </c>
       <c r="B8">
-        <v>61.51898734177215</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>61.455696202531655</v>
+        <v>61.01265822784811</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1463,32 +1466,32 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>59.99999999999999</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="B11">
-        <v>58.9873417721519</v>
+        <v>58.41772151898735</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="B12">
-        <v>58.41772151898735</v>
+        <v>57.59493670886076</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1496,73 +1499,73 @@
         <v>37</v>
       </c>
       <c r="B13">
-        <v>56.26582278481013</v>
+        <v>55.949367088607595</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="B14">
-        <v>55.822784810126585</v>
+        <v>55.8860759493671</v>
       </c>
       <c r="C14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>55.50632911392405</v>
+        <v>55.822784810126585</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>55.25316455696203</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="C16" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17">
-        <v>54.93670886075949</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="B18">
-        <v>54.87341772151898</v>
+        <v>53.98734177215191</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B19">
-        <v>54.49367088607596</v>
+        <v>53.9873417721519</v>
       </c>
       <c r="C19" t="s">
         <v>222</v>
@@ -1570,109 +1573,109 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>53.67088607594937</v>
+        <v>53.164556962025316</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21">
-        <v>51.89873417721519</v>
+        <v>52.65822784810126</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B22">
-        <v>50.75949367088608</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>50.75949367088608</v>
+        <v>51.139240506329116</v>
       </c>
       <c r="C23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>50.253164556962034</v>
+        <v>48.79746835443037</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>49.810126582278485</v>
+        <v>47.21518987341773</v>
       </c>
       <c r="C25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>48.924050632911396</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B27">
-        <v>48.67088607594937</v>
+        <v>46.835443037974684</v>
       </c>
       <c r="C27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="B28">
-        <v>47.53164556962025</v>
+        <v>46.39240506329114</v>
       </c>
       <c r="C28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="B29">
-        <v>44.36708860759494</v>
+        <v>46.265822784810126</v>
       </c>
       <c r="C29" t="s">
         <v>222</v>
@@ -1683,153 +1686,153 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>43.79746835443038</v>
+        <v>43.164556962025316</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>43.607594936708864</v>
+        <v>43.16455696202531</v>
       </c>
       <c r="C31" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="B32">
-        <v>43.41772151898735</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C32" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B33">
-        <v>43.291139240506325</v>
+        <v>42.53164556962026</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B34">
-        <v>41.26582278481012</v>
+        <v>42.08860759493671</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="B35">
-        <v>40.8860759493671</v>
+        <v>41.89873417721519</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="B36">
-        <v>40.75949367088609</v>
+        <v>41.64556962025317</v>
       </c>
       <c r="C36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="B37">
-        <v>40.44303797468355</v>
+        <v>41.265822784810126</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>39.62025316455696</v>
+        <v>40.632911392405056</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="B39">
-        <v>37.34177215189873</v>
+        <v>39.43037974683544</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>36.45569620253165</v>
+        <v>37.848101265822784</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B41">
-        <v>36.0759493670886</v>
+        <v>37.215189873417714</v>
       </c>
       <c r="C41" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B42">
-        <v>35.75949367088607</v>
+        <v>36.075949367088604</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B43">
-        <v>35.12658227848101</v>
+        <v>35.69620253164557</v>
       </c>
       <c r="C43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1840,48 +1843,48 @@
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B45">
-        <v>34.430379746835456</v>
+        <v>34.49367088607595</v>
       </c>
       <c r="C45" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B46">
-        <v>33.54430379746835</v>
+        <v>33.79746835443038</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B47">
-        <v>33.41772151898734</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B48">
-        <v>32.46835443037974</v>
+        <v>33.10126582278481</v>
       </c>
       <c r="C48" t="s">
         <v>223</v>
@@ -1889,10 +1892,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="B49">
-        <v>31.26582278481013</v>
+        <v>33.10126582278481</v>
       </c>
       <c r="C49" t="s">
         <v>222</v>
@@ -1900,24 +1903,24 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B50">
-        <v>30.75949367088608</v>
+        <v>32.53164556962025</v>
       </c>
       <c r="C50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B51">
-        <v>29.936708860759488</v>
+        <v>29.367088607594937</v>
       </c>
       <c r="C51" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2161,19 +2164,19 @@
         <v>0.98</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.039666571589430086</v>
+        <v>-0.07686573814465407</v>
       </c>
       <c r="G2" s="1">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H2" s="1">
-        <v>40.7</v>
+        <v>38.58</v>
       </c>
       <c r="I2" s="1">
-        <v>11.56</v>
+        <v>10.1</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.0028787689020423456</v>
+        <v>-0.004938737119039667</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -2182,28 +2185,28 @@
         <v>292</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.12891498743218077</v>
+        <v>-0.174727272655817</v>
       </c>
       <c r="N2" s="1">
-        <v>-1.063677557344502</v>
+        <v>-4.747544585681353</v>
       </c>
       <c r="O2" s="1">
-        <v>41.77215189873418</v>
+        <v>30.37974683544304</v>
       </c>
       <c r="P2" s="1">
         <v>15.687871758897787</v>
       </c>
       <c r="Q2" s="1">
-        <v>35.31645569620253</v>
+        <v>33.164556962025316</v>
       </c>
       <c r="R2" s="1">
-        <v>31.26582278481013</v>
+        <v>27.21518987341772</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>91</v>
       </c>
       <c r="T2" s="1">
-        <v>-1.58</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2223,19 +2226,19 @@
         <v>-0.5</v>
       </c>
       <c r="F3" s="2">
-        <v>1.267302437121809</v>
+        <v>1.2757885416333137</v>
       </c>
       <c r="G3" s="2">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="H3" s="2">
-        <v>76.71</v>
+        <v>75.98</v>
       </c>
       <c r="I3" s="2">
-        <v>119.64</v>
+        <v>117.23</v>
       </c>
       <c r="J3" s="2">
-        <v>0.0987216751882343</v>
+        <v>0.1019263706345017</v>
       </c>
       <c r="K3" s="2" t="b">
         <v>0</v>
@@ -2244,10 +2247,10 @@
         <v>108</v>
       </c>
       <c r="M3" s="2">
-        <v>1.4253689085541505</v>
+        <v>1.4505412818318189</v>
       </c>
       <c r="N3" s="2">
-        <v>154.36471204128864</v>
+        <v>157.77931086308223</v>
       </c>
       <c r="O3" s="2">
         <v>97.46835443037975</v>
@@ -2256,140 +2259,140 @@
         <v>26.467189489392297</v>
       </c>
       <c r="Q3" s="2">
-        <v>76.20253164556962</v>
+        <v>76.07594936708861</v>
       </c>
       <c r="R3" s="2">
-        <v>65.37974683544304</v>
+        <v>65.50632911392405</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="T3" s="2">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>-3.51</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="3">
         <v>8.860759493670885</v>
       </c>
-      <c r="D4" s="1">
-        <v>11.4985754985755</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="3">
+        <v>11.643874643874645</v>
+      </c>
+      <c r="E4" s="3">
         <v>-1.02</v>
       </c>
-      <c r="F4" s="1">
-        <v>0.24777214912048057</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.15</v>
-      </c>
-      <c r="H4" s="1">
-        <v>84.93</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.99</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.005926083139163227</v>
-      </c>
-      <c r="K4" s="1" t="b">
+      <c r="F4" s="3">
+        <v>0.3552253164787448</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H4" s="3">
+        <v>86.92</v>
+      </c>
+      <c r="I4" s="3">
+        <v>25.86</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.01849873493881134</v>
+      </c>
+      <c r="K4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="3">
         <v>-93</v>
       </c>
-      <c r="M4" s="1">
-        <v>0.26390138089929094</v>
-      </c>
-      <c r="N4" s="1">
-        <v>38.21795927580266</v>
-      </c>
-      <c r="O4" s="1">
-        <v>83.54430379746836</v>
-      </c>
-      <c r="P4" s="1">
+      <c r="M4" s="3">
+        <v>0.3901758645184459</v>
+      </c>
+      <c r="N4" s="3">
+        <v>51.74276913174493</v>
+      </c>
+      <c r="O4" s="3">
+        <v>84.81012658227847</v>
+      </c>
+      <c r="P4" s="3">
         <v>48.360550359989794</v>
       </c>
-      <c r="Q4" s="1">
-        <v>50.12658227848102</v>
-      </c>
-      <c r="R4" s="1">
-        <v>39.62025316455696</v>
-      </c>
-      <c r="S4" s="1" t="s">
+      <c r="Q4" s="3">
+        <v>52.658227848101276</v>
+      </c>
+      <c r="R4" s="3">
+        <v>41.265822784810126</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="1">
-        <v>24.81</v>
+      <c r="T4" s="3">
+        <v>26.46</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>1.09</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="3">
         <v>43.037974683544306</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <v>24.65137614678899</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="3">
         <v>0.34</v>
       </c>
-      <c r="F5" s="1">
-        <v>-0.12333577604724485</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="F5" s="3">
+        <v>-0.1389371359219536</v>
+      </c>
+      <c r="G5" s="3">
         <v>1.81</v>
       </c>
-      <c r="H5" s="1">
-        <v>63.61</v>
-      </c>
-      <c r="I5" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.008828072058440347</v>
-      </c>
-      <c r="K5" s="1" t="b">
+      <c r="H5" s="3">
+        <v>60.04</v>
+      </c>
+      <c r="I5" s="3">
+        <v>5.74</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.010524757318544712</v>
+      </c>
+      <c r="K5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="1">
-        <v>-84</v>
-      </c>
-      <c r="M5" s="1">
-        <v>-0.036237924441668845</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.204028741706688</v>
-      </c>
-      <c r="O5" s="1">
-        <v>53.16455696202531</v>
-      </c>
-      <c r="P5" s="1">
-        <v>25.321993503429013</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>59.49367088607596</v>
-      </c>
-      <c r="R5" s="1">
-        <v>46.77215189873417</v>
-      </c>
-      <c r="S5" s="1" t="s">
+      <c r="L5" s="3">
+        <v>-83</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-0.04457065621476075</v>
+      </c>
+      <c r="N5" s="3">
+        <v>8.268117058424279</v>
+      </c>
+      <c r="O5" s="3">
+        <v>49.36708860759494</v>
+      </c>
+      <c r="P5" s="3">
+        <v>24.465813099423656</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>58.60759493670887</v>
+      </c>
+      <c r="R5" s="3">
+        <v>46.01265822784811</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T5" s="1">
-        <v>1.46</v>
+      <c r="T5" s="3">
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2409,49 +2412,49 @@
         <v>0.97</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.15219308933701634</v>
+        <v>-0.2916956064449262</v>
       </c>
       <c r="G6" s="1">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="1">
-        <v>37.99</v>
+        <v>37.12</v>
       </c>
       <c r="I6" s="1">
-        <v>-14.82</v>
+        <v>-15</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.007407247785412419</v>
+        <v>-0.008074952972190496</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.09735370128906107</v>
+        <v>-0.23344469304542448</v>
       </c>
       <c r="N6" s="1">
-        <v>2.0924510569674712</v>
+        <v>-10.619286624642104</v>
       </c>
       <c r="O6" s="1">
-        <v>46.835443037974684</v>
+        <v>17.72151898734177</v>
       </c>
       <c r="P6" s="1">
         <v>20.72548824337846</v>
       </c>
       <c r="Q6" s="1">
-        <v>35.0632911392405</v>
+        <v>34.0506329113924</v>
       </c>
       <c r="R6" s="1">
-        <v>36.45569620253165</v>
+        <v>27.341772151898734</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="T6" s="1">
-        <v>-5.63</v>
+        <v>-14.75</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2465,25 +2468,25 @@
         <v>68.35443037974683</v>
       </c>
       <c r="D7" s="2">
-        <v>5.032159264931087</v>
+        <v>5.033690658499234</v>
       </c>
       <c r="E7" s="2">
         <v>0.5</v>
       </c>
       <c r="F7" s="2">
-        <v>-0.0917407860061597</v>
+        <v>-0.0777818404677516</v>
       </c>
       <c r="G7" s="2">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="H7" s="2">
-        <v>52.59</v>
+        <v>49.41</v>
       </c>
       <c r="I7" s="2">
-        <v>14.26</v>
+        <v>12.52</v>
       </c>
       <c r="J7" s="2">
-        <v>0.01657131978881227</v>
+        <v>0.016235396994504565</v>
       </c>
       <c r="K7" s="2" t="b">
         <v>0</v>
@@ -2492,28 +2495,28 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.040518914580085275</v>
+        <v>0.06435038822703265</v>
       </c>
       <c r="N7" s="2">
-        <v>15.879712643882113</v>
+        <v>19.160221502603612</v>
       </c>
       <c r="O7" s="2">
-        <v>64.55696202531645</v>
+        <v>63.29113924050633</v>
       </c>
       <c r="P7" s="2">
         <v>15.539987609451147</v>
       </c>
       <c r="Q7" s="2">
-        <v>58.10126582278481</v>
+        <v>56.9620253164557</v>
       </c>
       <c r="R7" s="2">
-        <v>53.67088607594937</v>
+        <v>52.848101265822784</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.89</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2533,19 +2536,19 @@
         <v>1.61</v>
       </c>
       <c r="F8" s="2">
-        <v>0.2537946511721644</v>
+        <v>0.21031520551401806</v>
       </c>
       <c r="G8" s="2">
         <v>0.65</v>
       </c>
       <c r="H8" s="2">
-        <v>59.73</v>
+        <v>57.75</v>
       </c>
       <c r="I8" s="2">
-        <v>17.34</v>
+        <v>16.44</v>
       </c>
       <c r="J8" s="2">
-        <v>0.030440553351013474</v>
+        <v>0.030184188099335905</v>
       </c>
       <c r="K8" s="2" t="b">
         <v>0</v>
@@ -2554,152 +2557,152 @@
         <v>-222</v>
       </c>
       <c r="M8" s="2">
-        <v>0.21615977702160682</v>
+        <v>0.16953956613436683</v>
       </c>
       <c r="N8" s="2">
-        <v>33.44379888803426</v>
+        <v>29.679139293337027</v>
       </c>
       <c r="O8" s="2">
-        <v>81.0126582278481</v>
+        <v>77.21518987341773</v>
       </c>
       <c r="P8" s="2">
         <v>27.294677507005353</v>
       </c>
       <c r="Q8" s="2">
-        <v>61.26582278481013</v>
+        <v>60.253164556962034</v>
       </c>
       <c r="R8" s="2">
-        <v>53.67088607594937</v>
+        <v>52.40506329113924</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T8" s="2">
-        <v>-1.65</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>0.89</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>37.9746835443038</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <v>46.831460674157306</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="3">
         <v>0.88</v>
       </c>
-      <c r="F9" s="1">
-        <v>-0.11545601893577045</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H9" s="1">
-        <v>56.43</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-11.48</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-0.010764346105064788</v>
-      </c>
-      <c r="K9" s="1" t="b">
+      <c r="F9" s="3">
+        <v>-0.04329252548487092</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="H9" s="3">
+        <v>67.42</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-3.24</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-0.008274099887544748</v>
+      </c>
+      <c r="K9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="3">
         <v>-17</v>
       </c>
-      <c r="M9" s="1">
-        <v>-0.06384247724357728</v>
-      </c>
-      <c r="N9" s="1">
-        <v>5.4435734615158395</v>
-      </c>
-      <c r="O9" s="1">
-        <v>49.36708860759494</v>
-      </c>
-      <c r="P9" s="1">
-        <v>30.47019076386737</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>46.20253164556963</v>
-      </c>
-      <c r="R9" s="1">
-        <v>40.50632911392405</v>
-      </c>
-      <c r="S9" s="1" t="s">
+      <c r="M9" s="3">
+        <v>0.013793369646640796</v>
+      </c>
+      <c r="N9" s="3">
+        <v>14.104519644564428</v>
+      </c>
+      <c r="O9" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="P9" s="3">
+        <v>29.51342870916754</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>50.75949367088608</v>
+      </c>
+      <c r="R9" s="3">
+        <v>42.46835443037975</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="T9" s="1">
-        <v>-0.7</v>
+      <c r="T9" s="3">
+        <v>1.27</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>6.25</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="3">
         <v>65.82278481012658</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="3">
         <v>0.5663999999999999</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="3">
         <v>-0.77</v>
       </c>
-      <c r="F10" s="1">
-        <v>-0.17960778812112754</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="H10" s="1">
-        <v>50.6</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-4.27</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.0037947882765627427</v>
-      </c>
-      <c r="K10" s="1" t="b">
+      <c r="F10" s="3">
+        <v>-0.21355454778760147</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>45.26</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-5.97</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.0037374607650429233</v>
+      </c>
+      <c r="K10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="1">
-        <v>-132</v>
-      </c>
-      <c r="M10" s="1">
-        <v>-0.13552122125904587</v>
-      </c>
-      <c r="N10" s="1">
-        <v>-1.724300940031009</v>
-      </c>
-      <c r="O10" s="1">
-        <v>40.50632911392405</v>
-      </c>
-      <c r="P10" s="1">
+      <c r="L10" s="3">
+        <v>-131</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-0.16695381706800005</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-3.970199026899659</v>
+      </c>
+      <c r="O10" s="3">
+        <v>32.91139240506329</v>
+      </c>
+      <c r="P10" s="3">
         <v>20.24508080818123</v>
       </c>
-      <c r="Q10" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="R10" s="1">
-        <v>37.151898734177216</v>
-      </c>
-      <c r="S10" s="1" t="s">
+      <c r="Q10" s="3">
+        <v>42.911392405063296</v>
+      </c>
+      <c r="R10" s="3">
+        <v>34.74683544303798</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T10" s="1">
-        <v>-1.65</v>
+      <c r="T10" s="3">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2707,31 +2710,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>-1.36</v>
+        <v>-0.95</v>
       </c>
       <c r="C11" s="2">
-        <v>12.658227848101266</v>
+        <v>15.18987341772152</v>
       </c>
       <c r="D11" s="2">
-        <v>31.963235294117645</v>
+        <v>46.905263157894744</v>
       </c>
       <c r="E11" s="2">
         <v>-0.88</v>
       </c>
       <c r="F11" s="2">
-        <v>0.23464635150019414</v>
+        <v>0.1504913086342657</v>
       </c>
       <c r="G11" s="2">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H11" s="2">
-        <v>66.14</v>
+        <v>50.83</v>
       </c>
       <c r="I11" s="2">
-        <v>15.32</v>
+        <v>5.91</v>
       </c>
       <c r="J11" s="2">
-        <v>0.027788142154114414</v>
+        <v>0.02519102707019821</v>
       </c>
       <c r="K11" s="2" t="b">
         <v>1</v>
@@ -2740,214 +2743,214 @@
         <v>25</v>
       </c>
       <c r="M11" s="2">
-        <v>0.21851711972138377</v>
+        <v>0.13418105288240523</v>
       </c>
       <c r="N11" s="2">
-        <v>33.67953315801196</v>
+        <v>26.143287968140882</v>
       </c>
       <c r="O11" s="2">
-        <v>82.27848101265823</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="P11" s="2">
         <v>23.11654999559394</v>
       </c>
       <c r="Q11" s="2">
-        <v>58.35443037974684</v>
+        <v>54.17721518987342</v>
       </c>
       <c r="R11" s="2">
-        <v>51.89873417721519</v>
+        <v>51.139240506329116</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="T11" s="2">
-        <v>5.44</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="3">
         <v>-0.34</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>20.253164556962027</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="3">
         <v>65.70588235294117</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="3">
         <v>3.81</v>
       </c>
-      <c r="F12" s="1">
-        <v>-0.10394058776940081</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.88</v>
-      </c>
-      <c r="H12" s="1">
-        <v>65.16</v>
-      </c>
-      <c r="I12" s="1">
-        <v>-21.5</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.01727706612210851</v>
-      </c>
-      <c r="K12" s="1" t="b">
+      <c r="F12" s="3">
+        <v>0.0638417078712054</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="H12" s="3">
+        <v>72.99</v>
+      </c>
+      <c r="I12" s="3">
+        <v>-12.63</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.022522005094730492</v>
+      </c>
+      <c r="K12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="3">
         <v>-51</v>
       </c>
-      <c r="M12" s="1">
-        <v>-0.1168439731924491</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0.14342386662866102</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="M12" s="3">
+        <v>0.05335654345929508</v>
+      </c>
+      <c r="N12" s="3">
+        <v>18.060837025829855</v>
+      </c>
+      <c r="O12" s="3">
+        <v>60.75949367088608</v>
+      </c>
+      <c r="P12" s="3">
+        <v>49.122344752707264</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>56.835443037974684</v>
+      </c>
+      <c r="R12" s="3">
+        <v>42.53164556962026</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T12" s="3">
+        <v>21.84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="1">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-1653.5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6.41</v>
+      </c>
+      <c r="F13" s="1">
+        <v>-0.3545066796092178</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="H13" s="1">
+        <v>43.21</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-8.75</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-0.0065988750880665754</v>
+      </c>
+      <c r="K13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>12</v>
+      </c>
+      <c r="M13" s="1">
+        <v>-0.3114010036935865</v>
+      </c>
+      <c r="N13" s="1">
+        <v>-18.414917689458296</v>
+      </c>
+      <c r="O13" s="1">
+        <v>7.59493670886076</v>
+      </c>
+      <c r="P13" s="1">
+        <v>39.74359086324119</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>18.354430379746834</v>
+      </c>
+      <c r="R13" s="1">
+        <v>4.113924050632909</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="T13" s="1">
+        <v>-11.77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="C14" s="2">
         <v>44.303797468354425</v>
       </c>
-      <c r="P12" s="1">
-        <v>49.188907754993835</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>53.92405063291139</v>
-      </c>
-      <c r="R12" s="1">
-        <v>37.34177215189873</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T12" s="1">
-        <v>16.65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="2">
+        <v>6.949275362318841</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4.73</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.6114695918111009</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="H14" s="2">
+        <v>83.09</v>
+      </c>
+      <c r="I14" s="2">
+        <v>44.77</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.026147583723401546</v>
+      </c>
+      <c r="K14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="C13" s="3">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-1653.5</v>
-      </c>
-      <c r="E13" s="3">
-        <v>6.41</v>
-      </c>
-      <c r="F13" s="3">
-        <v>-0.35929886170160874</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1.39</v>
-      </c>
-      <c r="H13" s="3">
-        <v>43.21</v>
-      </c>
-      <c r="I13" s="3">
-        <v>-8.64</v>
-      </c>
-      <c r="J13" s="3">
-        <v>-0.007828951166343617</v>
-      </c>
-      <c r="K13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>12</v>
-      </c>
-      <c r="M13" s="3">
-        <v>-0.3173628590767018</v>
-      </c>
-      <c r="N13" s="3">
-        <v>-19.90846472179661</v>
-      </c>
-      <c r="O13" s="3">
-        <v>7.59493670886076</v>
-      </c>
-      <c r="P13" s="3">
-        <v>39.74359086324119</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>17.72151898734177</v>
-      </c>
-      <c r="R13" s="3">
-        <v>3.8607594936708844</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="T13" s="3">
-        <v>-12.03</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1.31</v>
-      </c>
-      <c r="C14" s="1">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="D14" s="1">
-        <v>7.572519083969465</v>
-      </c>
-      <c r="E14" s="1">
-        <v>4.73</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.17916950216061667</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="H14" s="1">
-        <v>67.74</v>
-      </c>
-      <c r="I14" s="1">
-        <v>11.47</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.016828958828485927</v>
-      </c>
-      <c r="K14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
-        <v>12</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0.1404593458914718</v>
-      </c>
-      <c r="N14" s="1">
-        <v>25.87375577502076</v>
-      </c>
-      <c r="O14" s="1">
-        <v>74.68354430379746</v>
-      </c>
-      <c r="P14" s="1">
+      <c r="M14" s="2">
+        <v>0.5730239889674298</v>
+      </c>
+      <c r="N14" s="2">
+        <v>70.02758157664331</v>
+      </c>
+      <c r="O14" s="2">
+        <v>88.60759493670885</v>
+      </c>
+      <c r="P14" s="2">
         <v>33.10300785656511</v>
       </c>
-      <c r="Q14" s="1">
-        <v>57.84810126582279</v>
-      </c>
-      <c r="R14" s="1">
-        <v>47.53164556962025</v>
-      </c>
-      <c r="S14" s="1" t="s">
+      <c r="Q14" s="2">
+        <v>63.164556962025316</v>
+      </c>
+      <c r="R14" s="2">
+        <v>52.65822784810126</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="T14" s="1">
-        <v>12.34</v>
+      <c r="T14" s="2">
+        <v>17.47</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -2967,19 +2970,19 @@
         <v>2.23</v>
       </c>
       <c r="F15" s="2">
-        <v>1.4076477342590126</v>
+        <v>1.242646766784784</v>
       </c>
       <c r="G15" s="2">
         <v>2.24</v>
       </c>
       <c r="H15" s="2">
-        <v>66.83</v>
+        <v>59.19</v>
       </c>
       <c r="I15" s="2">
-        <v>148.22</v>
+        <v>133.25</v>
       </c>
       <c r="J15" s="2">
-        <v>0.1021717935655029</v>
+        <v>0.1000170746601051</v>
       </c>
       <c r="K15" s="2" t="b">
         <v>0</v>
@@ -2988,338 +2991,338 @@
         <v>195</v>
       </c>
       <c r="M15" s="2">
-        <v>1.540982716963845</v>
+        <v>1.3871090320155484</v>
       </c>
       <c r="N15" s="2">
-        <v>165.9260928822581</v>
+        <v>151.43608588145517</v>
       </c>
       <c r="O15" s="2">
-        <v>100</v>
+        <v>96.20253164556962</v>
       </c>
       <c r="P15" s="2">
         <v>24.171577948970977</v>
       </c>
       <c r="Q15" s="2">
-        <v>69.74683544303798</v>
+        <v>66.96202531645571</v>
       </c>
       <c r="R15" s="2">
-        <v>62.27848101265822</v>
+        <v>61.01265822784811</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>103</v>
       </c>
       <c r="T15" s="2">
-        <v>0.32</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>-3.53</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>7.59493670886076</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>12.69971671388102</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>5.41</v>
       </c>
-      <c r="F16" s="3">
-        <v>-0.25922093420680475</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1.92</v>
-      </c>
-      <c r="H16" s="3">
-        <v>52.56</v>
-      </c>
-      <c r="I16" s="3">
-        <v>3.17</v>
-      </c>
-      <c r="J16" s="3">
-        <v>-0.0011493331487258444</v>
-      </c>
-      <c r="K16" s="3" t="b">
+      <c r="F16" s="1">
+        <v>-0.21222349880346625</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.91</v>
+      </c>
+      <c r="H16" s="1">
+        <v>55.28</v>
+      </c>
+      <c r="I16" s="1">
+        <v>5.98</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.0010619223984947054</v>
+      </c>
+      <c r="K16" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="1">
         <v>16</v>
       </c>
-      <c r="M16" s="3">
-        <v>-0.16029497929676784</v>
-      </c>
-      <c r="N16" s="3">
-        <v>-4.201676743803204</v>
-      </c>
-      <c r="O16" s="3">
-        <v>34.177215189873415</v>
-      </c>
-      <c r="P16" s="3">
+      <c r="M16" s="1">
+        <v>-0.10620683641637307</v>
+      </c>
+      <c r="N16" s="1">
+        <v>2.1044990382630337</v>
+      </c>
+      <c r="O16" s="1">
+        <v>41.77215189873418</v>
+      </c>
+      <c r="P16" s="1">
         <v>30.2515696939809</v>
       </c>
-      <c r="Q16" s="3">
-        <v>39.11392405063291</v>
-      </c>
-      <c r="R16" s="3">
-        <v>27.088607594936708</v>
-      </c>
-      <c r="S16" s="3" t="s">
+      <c r="Q16" s="1">
+        <v>40.88607594936709</v>
+      </c>
+      <c r="R16" s="1">
+        <v>29.367088607594937</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T16" s="3">
-        <v>-9.56</v>
+      <c r="T16" s="1">
+        <v>-7.28</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>-6.21</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>3.79746835443038</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="1">
         <v>5.15780998389694</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="1">
         <v>1.52</v>
       </c>
-      <c r="F17" s="3">
-        <v>-0.2835894926936874</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.73</v>
-      </c>
-      <c r="H17" s="3">
-        <v>61.39</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1.19</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0.00615839807043041</v>
-      </c>
-      <c r="K17" s="3" t="b">
+      <c r="F17" s="1">
+        <v>-0.27930952257210306</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="H17" s="1">
+        <v>60.77</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.00950051872316976</v>
+      </c>
+      <c r="K17" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
-        <v>25</v>
-      </c>
-      <c r="M17" s="3">
-        <v>-0.20509389803681022</v>
-      </c>
-      <c r="N17" s="3">
-        <v>-8.681568617807443</v>
-      </c>
-      <c r="O17" s="3">
-        <v>18.9873417721519</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="L17" s="1">
+        <v>24</v>
+      </c>
+      <c r="M17" s="1">
+        <v>-0.19309817074084046</v>
+      </c>
+      <c r="N17" s="1">
+        <v>-6.584634394183697</v>
+      </c>
+      <c r="O17" s="1">
+        <v>26.582278481012654</v>
+      </c>
+      <c r="P17" s="1">
         <v>28.182703357372183</v>
       </c>
-      <c r="Q17" s="3">
-        <v>37.9746835443038</v>
-      </c>
-      <c r="R17" s="3">
-        <v>19.240506329113924</v>
-      </c>
-      <c r="S17" s="3" t="s">
+      <c r="Q17" s="1">
+        <v>37.721518987341774</v>
+      </c>
+      <c r="R17" s="1">
+        <v>21.455696202531644</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="T17" s="3">
-        <v>-3.92</v>
+      <c r="T17" s="1">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>0.09</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>30.37974683544304</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>1446.3333333333333</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>6.73</v>
       </c>
-      <c r="F18" s="3">
-        <v>-0.3596236439255154</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1.17</v>
-      </c>
-      <c r="H18" s="3">
-        <v>34.18</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-14.43</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-0.007390486959443497</v>
-      </c>
-      <c r="K18" s="3" t="b">
+      <c r="F18" s="1">
+        <v>-0.3488057381222238</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.16</v>
+      </c>
+      <c r="H18" s="1">
+        <v>31.33</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-17.39</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-0.008703234626623722</v>
+      </c>
+      <c r="K18" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>37</v>
       </c>
-      <c r="M18" s="3">
-        <v>-0.3413438479095303</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-22.30656360507945</v>
-      </c>
-      <c r="O18" s="3">
-        <v>3.79746835443038</v>
-      </c>
-      <c r="P18" s="3">
-        <v>33.93532173431426</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>44.810126582278485</v>
-      </c>
-      <c r="R18" s="3">
-        <v>27.78481012658228</v>
-      </c>
-      <c r="S18" s="3" t="s">
+      <c r="M18" s="1">
+        <v>-0.33016544583438323</v>
+      </c>
+      <c r="N18" s="1">
+        <v>-20.291361903537975</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5.063291139240507</v>
+      </c>
+      <c r="P18" s="1">
+        <v>35.65728669277035</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>42.151898734177216</v>
+      </c>
+      <c r="R18" s="1">
+        <v>27.15189873417722</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T18" s="3">
-        <v>-3.16</v>
+      <c r="T18" s="1">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="3">
         <v>9.32</v>
       </c>
-      <c r="C19" s="1">
-        <v>77.21518987341773</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="C19" s="3">
+        <v>75.9493670886076</v>
+      </c>
+      <c r="D19" s="3">
         <v>0.24463519313304713</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="3">
         <v>-1.48</v>
       </c>
-      <c r="F19" s="1">
-        <v>0.012260871440573091</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="F19" s="3">
+        <v>-0.012259141732558751</v>
+      </c>
+      <c r="G19" s="3">
         <v>0.2</v>
       </c>
-      <c r="H19" s="1">
-        <v>57</v>
-      </c>
-      <c r="I19" s="1">
-        <v>15.38</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.004762789440933372</v>
-      </c>
-      <c r="K19" s="1" t="b">
+      <c r="H19" s="3">
+        <v>56.43</v>
+      </c>
+      <c r="I19" s="3">
+        <v>14.92</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.006347842570531851</v>
+      </c>
+      <c r="K19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="3">
         <v>80</v>
       </c>
-      <c r="M19" s="1">
-        <v>-0.07376169804641552</v>
-      </c>
-      <c r="N19" s="1">
-        <v>4.451651381232014</v>
-      </c>
-      <c r="O19" s="1">
-        <v>48.10126582278481</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="M19" s="3">
+        <v>-0.10546060317176154</v>
+      </c>
+      <c r="N19" s="3">
+        <v>2.1791223627242005</v>
+      </c>
+      <c r="O19" s="3">
+        <v>43.037974683544306</v>
+      </c>
+      <c r="P19" s="3">
         <v>14.335419717590279</v>
       </c>
-      <c r="Q19" s="1">
-        <v>52.02531645569621</v>
-      </c>
-      <c r="R19" s="1">
-        <v>43.607594936708864</v>
-      </c>
-      <c r="S19" s="1" t="s">
+      <c r="Q19" s="3">
+        <v>51.0126582278481</v>
+      </c>
+      <c r="R19" s="3">
+        <v>41.64556962025317</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T19" s="1">
-        <v>2.72</v>
+      <c r="T19" s="3">
+        <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="3">
         <v>6.07</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="3">
         <v>64.55696202531645</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="3">
         <v>0.6820428336079079</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="3">
         <v>6.54</v>
       </c>
-      <c r="F20" s="1">
-        <v>0.029400229935457545</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="H20" s="1">
-        <v>73.52</v>
-      </c>
-      <c r="I20" s="1">
-        <v>8.49</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0.012419548476684491</v>
-      </c>
-      <c r="K20" s="1" t="b">
+      <c r="F20" s="3">
+        <v>-0.015484411673298337</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="H20" s="3">
+        <v>68.83</v>
+      </c>
+      <c r="I20" s="3">
+        <v>6.47</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0.014425078428826888</v>
+      </c>
+      <c r="K20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="3">
         <v>9</v>
       </c>
-      <c r="M20" s="1">
-        <v>0.03800248688415642</v>
-      </c>
-      <c r="N20" s="1">
-        <v>15.628069874289219</v>
-      </c>
-      <c r="O20" s="1">
-        <v>63.29113924050633</v>
-      </c>
-      <c r="P20" s="1">
+      <c r="M20" s="3">
+        <v>-0.004999247261388007</v>
+      </c>
+      <c r="N20" s="3">
+        <v>12.22525795376155</v>
+      </c>
+      <c r="O20" s="3">
+        <v>54.43037974683544</v>
+      </c>
+      <c r="P20" s="3">
         <v>25.74193342123896</v>
       </c>
-      <c r="Q20" s="1">
-        <v>55.56962025316455</v>
-      </c>
-      <c r="R20" s="1">
-        <v>44.36708860759494</v>
-      </c>
-      <c r="S20" s="1" t="s">
+      <c r="Q20" s="3">
+        <v>55.189873417721515</v>
+      </c>
+      <c r="R20" s="3">
+        <v>41.89873417721519</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T20" s="1">
-        <v>16.96</v>
+      <c r="T20" s="3">
+        <v>14.49</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -3333,37 +3336,37 @@
         <v>41.77215189873418</v>
       </c>
       <c r="D21" s="2">
-        <v>13.558823529411764</v>
+        <v>13.549019607843137</v>
       </c>
       <c r="E21" s="2">
         <v>2.47</v>
       </c>
       <c r="F21" s="2">
-        <v>0.34104313102257167</v>
+        <v>0.4212347088280941</v>
       </c>
       <c r="G21" s="2">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="H21" s="2">
-        <v>79.89</v>
+        <v>77.36</v>
       </c>
       <c r="I21" s="2">
-        <v>84.95</v>
+        <v>81.08</v>
       </c>
       <c r="J21" s="2">
-        <v>0.05892123627948859</v>
+        <v>0.061494802984585206</v>
       </c>
       <c r="K21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2">
         <v>37</v>
       </c>
       <c r="M21" s="2">
-        <v>0.40018364754487634</v>
+        <v>0.4899707866395062</v>
       </c>
       <c r="N21" s="2">
-        <v>51.8461859403612</v>
+        <v>61.72226134385096</v>
       </c>
       <c r="O21" s="2">
         <v>87.34177215189874</v>
@@ -3372,7 +3375,7 @@
         <v>39.63614933355383</v>
       </c>
       <c r="Q21" s="2">
-        <v>70.88607594936708</v>
+        <v>70.50632911392405</v>
       </c>
       <c r="R21" s="2">
         <v>55.822784810126585</v>
@@ -3385,313 +3388,313 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="3">
         <v>8.11</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>70.88607594936708</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="3">
         <v>0.7016029593094947</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="3">
         <v>-0.84</v>
       </c>
-      <c r="F22" s="1">
-        <v>-0.21680085605791607</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.37</v>
-      </c>
-      <c r="H22" s="1">
-        <v>64.75</v>
-      </c>
-      <c r="I22" s="1">
-        <v>6.65</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0.0013235824787247237</v>
-      </c>
-      <c r="K22" s="1" t="b">
+      <c r="F22" s="3">
+        <v>-0.22557499416717403</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="H22" s="3">
+        <v>66.11</v>
+      </c>
+      <c r="I22" s="3">
+        <v>7.54</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.004467482710446037</v>
+      </c>
+      <c r="K22" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="3">
         <v>57</v>
       </c>
-      <c r="M22" s="1">
-        <v>-0.1770154176701838</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-5.873720581144804</v>
-      </c>
-      <c r="O22" s="1">
-        <v>27.848101265822784</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="M22" s="3">
+        <v>-0.18130429998355269</v>
+      </c>
+      <c r="N22" s="3">
+        <v>-5.405247318454922</v>
+      </c>
+      <c r="O22" s="3">
+        <v>29.11392405063291</v>
+      </c>
+      <c r="P22" s="3">
         <v>20.966620085005058</v>
       </c>
-      <c r="Q22" s="1">
-        <v>52.65822784810126</v>
-      </c>
-      <c r="R22" s="1">
-        <v>35.12658227848101</v>
-      </c>
-      <c r="S22" s="1" t="s">
+      <c r="Q22" s="3">
+        <v>54.55696202531645</v>
+      </c>
+      <c r="R22" s="3">
+        <v>36.075949367088604</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T22" s="1">
-        <v>4.87</v>
+      <c r="T22" s="3">
+        <v>5.82</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="3">
         <v>27.51</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="3">
         <v>97.46835443037975</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="3">
         <v>-0.772446383133406</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="3">
         <v>0.96</v>
       </c>
-      <c r="F23" s="1">
-        <v>-0.17714388807223977</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="H23" s="1">
-        <v>56.87</v>
-      </c>
-      <c r="I23" s="1">
-        <v>-4.81</v>
-      </c>
-      <c r="J23" s="1">
-        <v>-0.0018190846186676589</v>
-      </c>
-      <c r="K23" s="1" t="b">
+      <c r="F23" s="3">
+        <v>-0.17822260425121553</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="H23" s="3">
+        <v>55.36</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-5.11</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0.00025809824374163577</v>
+      </c>
+      <c r="K23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="3">
         <v>21</v>
       </c>
-      <c r="M23" s="1">
-        <v>-0.15133711722614318</v>
-      </c>
-      <c r="N23" s="1">
-        <v>-3.3058905367407467</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="M23" s="3">
+        <v>-0.1514271840874447</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-2.417535728844126</v>
+      </c>
+      <c r="O23" s="3">
         <v>35.44303797468354</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="3">
         <v>28.794141696367475</v>
       </c>
-      <c r="Q23" s="1">
-        <v>47.468354430379755</v>
-      </c>
-      <c r="R23" s="1">
+      <c r="Q23" s="3">
+        <v>46.9620253164557</v>
+      </c>
+      <c r="R23" s="3">
         <v>35</v>
       </c>
-      <c r="S23" s="1" t="s">
+      <c r="S23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T23" s="1">
+      <c r="T23" s="3">
         <v>3.04</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <v>-40.16</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <v>1.2658227848101267</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="1">
         <v>-0.009462151394422375</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="1">
         <v>9.47</v>
       </c>
-      <c r="F24" s="3">
-        <v>-0.25251762412574824</v>
-      </c>
-      <c r="G24" s="3">
-        <v>3.52</v>
-      </c>
-      <c r="H24" s="3">
-        <v>39.86</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-27.4</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.010057037308579353</v>
-      </c>
-      <c r="K24" s="3" t="b">
+      <c r="F24" s="1">
+        <v>-0.18884719531315047</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3.49</v>
+      </c>
+      <c r="H24" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-23.4</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.00898746435782413</v>
+      </c>
+      <c r="K24" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
-        <v>-11</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0.018453469758265895</v>
-      </c>
-      <c r="N24" s="3">
-        <v>13.673168161700163</v>
-      </c>
-      <c r="O24" s="3">
-        <v>62.0253164556962</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="L24" s="1">
+        <v>-12</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.10124235341636822</v>
+      </c>
+      <c r="N24" s="1">
+        <v>22.84941802153716</v>
+      </c>
+      <c r="O24" s="1">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="P24" s="1">
         <v>40.33904155950217</v>
       </c>
-      <c r="Q24" s="3">
-        <v>19.240506329113924</v>
-      </c>
-      <c r="R24" s="3">
-        <v>21.139240506329116</v>
-      </c>
-      <c r="S24" s="3" t="s">
+      <c r="Q24" s="1">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="R24" s="1">
+        <v>23.037974683544306</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T24" s="3">
-        <v>-9.87</v>
+      <c r="T24" s="1">
+        <v>-7.97</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>-2.28</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>11.39240506329114</v>
       </c>
-      <c r="D25" s="3">
-        <v>-7.127192982456141</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="D25" s="1">
+        <v>-7.149122807017544</v>
+      </c>
+      <c r="E25" s="1">
         <v>11.95</v>
       </c>
-      <c r="F25" s="3">
-        <v>-0.3339087547980175</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2.21</v>
-      </c>
-      <c r="H25" s="3">
-        <v>53.16</v>
-      </c>
-      <c r="I25" s="3">
-        <v>-45.95</v>
-      </c>
-      <c r="J25" s="3">
-        <v>-0.001986099582476645</v>
-      </c>
-      <c r="K25" s="3" t="b">
+      <c r="F25" s="1">
+        <v>-0.28106182439222227</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="H25" s="1">
+        <v>56.14</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-43.5</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.0009599595740895468</v>
+      </c>
+      <c r="K25" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="1">
         <v>41</v>
       </c>
-      <c r="M25" s="3">
-        <v>-0.20379961844894723</v>
-      </c>
-      <c r="N25" s="3">
-        <v>-8.552140659021152</v>
-      </c>
-      <c r="O25" s="3">
-        <v>21.518987341772153</v>
-      </c>
-      <c r="P25" s="3">
+      <c r="M25" s="1">
+        <v>-0.1412596322334181</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-1.4007805434414595</v>
+      </c>
+      <c r="O25" s="1">
+        <v>37.9746835443038</v>
+      </c>
+      <c r="P25" s="1">
         <v>55.620154465672535</v>
       </c>
-      <c r="Q25" s="3">
-        <v>15.822784810126585</v>
-      </c>
-      <c r="R25" s="3">
-        <v>3.9240506329113938</v>
-      </c>
-      <c r="S25" s="3" t="s">
+      <c r="Q25" s="1">
+        <v>17.088607594936708</v>
+      </c>
+      <c r="R25" s="1">
+        <v>9.113924050632914</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="T25" s="3">
-        <v>-8.04</v>
+      <c r="T25" s="1">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="3">
         <v>-0.17</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="3">
         <v>24.050632911392405</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="3">
         <v>-2529.3529411764703</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="3">
         <v>3.39</v>
       </c>
-      <c r="F26" s="1">
-        <v>0.36951534389864393</v>
-      </c>
-      <c r="G26" s="1">
-        <v>3.12</v>
-      </c>
-      <c r="H26" s="1">
-        <v>74.23</v>
-      </c>
-      <c r="I26" s="1">
-        <v>47.06</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.0776905112005027</v>
-      </c>
-      <c r="K26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="F26" s="3">
+        <v>0.4993946026358366</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3.16</v>
+      </c>
+      <c r="H26" s="3">
+        <v>75.54</v>
+      </c>
+      <c r="I26" s="3">
+        <v>50.65</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.08421282073972343</v>
+      </c>
+      <c r="K26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-29</v>
       </c>
-      <c r="M26" s="1">
-        <v>0.5974751530391638</v>
-      </c>
-      <c r="N26" s="1">
-        <v>71.57533648978995</v>
-      </c>
-      <c r="O26" s="1">
-        <v>89.87341772151899</v>
-      </c>
-      <c r="P26" s="1">
+      <c r="M26" s="3">
+        <v>0.7510385485216842</v>
+      </c>
+      <c r="N26" s="3">
+        <v>87.82903753206877</v>
+      </c>
+      <c r="O26" s="3">
+        <v>91.13924050632912</v>
+      </c>
+      <c r="P26" s="3">
         <v>47.81158046237125</v>
       </c>
-      <c r="Q26" s="1">
-        <v>43.924050632911396</v>
-      </c>
-      <c r="R26" s="1">
-        <v>33.41772151898734</v>
-      </c>
-      <c r="S26" s="1" t="s">
+      <c r="Q26" s="3">
+        <v>43.79746835443038</v>
+      </c>
+      <c r="R26" s="3">
+        <v>33.79746835443038</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="T26" s="1">
-        <v>0.38</v>
+      <c r="T26" s="3">
+        <v>0.76</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -3702,7 +3705,7 @@
         <v>-1.13</v>
       </c>
       <c r="C27" s="1">
-        <v>13.924050632911392</v>
+        <v>12.658227848101266</v>
       </c>
       <c r="D27" s="1">
         <v>1.0176991150442478</v>
@@ -3711,19 +3714,19 @@
         <v>8.19</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.09335364792367185</v>
+        <v>-0.14007239858826454</v>
       </c>
       <c r="G27" s="1">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="H27" s="1">
-        <v>70.61</v>
+        <v>65.28</v>
       </c>
       <c r="I27" s="1">
-        <v>-4.51</v>
+        <v>-7.39</v>
       </c>
       <c r="J27" s="1">
-        <v>0.015521257090109087</v>
+        <v>0.020234889150990233</v>
       </c>
       <c r="K27" s="1" t="b">
         <v>0</v>
@@ -3732,90 +3735,90 @@
         <v>42</v>
       </c>
       <c r="M27" s="1">
-        <v>0.08406790164324218</v>
+        <v>0.055650670434061356</v>
       </c>
       <c r="N27" s="1">
-        <v>20.234611350197802</v>
+        <v>18.29024972330648</v>
       </c>
       <c r="O27" s="1">
-        <v>68.35443037974683</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="P27" s="1">
         <v>51.28834092723359</v>
       </c>
       <c r="Q27" s="1">
-        <v>41.139240506329116</v>
+        <v>39.620253164556964</v>
       </c>
       <c r="R27" s="1">
-        <v>30.75949367088608</v>
+        <v>29.050632911392405</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T27" s="1">
-        <v>4.37</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="1">
         <v>-1.1</v>
       </c>
-      <c r="C28" s="3">
-        <v>15.18987341772152</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="C28" s="1">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="D28" s="1">
         <v>7.899999999999999</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="1">
         <v>-4.03</v>
       </c>
-      <c r="F28" s="3">
-        <v>-0.42454909753822806</v>
-      </c>
-      <c r="G28" s="3">
-        <v>3.13</v>
-      </c>
-      <c r="H28" s="3">
+      <c r="F28" s="1">
+        <v>-0.4201050546548008</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3.14</v>
+      </c>
+      <c r="H28" s="1">
         <v>64.22</v>
       </c>
-      <c r="I28" s="3">
-        <v>-14.84</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0.004549498513752033</v>
-      </c>
-      <c r="K28" s="3" t="b">
+      <c r="I28" s="1">
+        <v>-14.65</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.008355306124368026</v>
+      </c>
+      <c r="K28" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="1">
         <v>-3</v>
       </c>
-      <c r="M28" s="3">
-        <v>-0.19551400627912086</v>
-      </c>
-      <c r="N28" s="3">
-        <v>-7.723579442038505</v>
-      </c>
-      <c r="O28" s="3">
-        <v>24.050632911392405</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="M28" s="1">
+        <v>-0.17079114530493333</v>
+      </c>
+      <c r="N28" s="1">
+        <v>-4.3539318505929865</v>
+      </c>
+      <c r="O28" s="1">
+        <v>31.645569620253166</v>
+      </c>
+      <c r="P28" s="1">
         <v>45.17203183430412</v>
       </c>
-      <c r="Q28" s="3">
-        <v>40.12658227848102</v>
-      </c>
-      <c r="R28" s="3">
-        <v>21.835443037974684</v>
-      </c>
-      <c r="S28" s="3" t="s">
+      <c r="Q28" s="1">
+        <v>41.139240506329116</v>
+      </c>
+      <c r="R28" s="1">
+        <v>24.493670886075947</v>
+      </c>
+      <c r="S28" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T28" s="3">
-        <v>-0.06</v>
+      <c r="T28" s="1">
+        <v>2.59</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -3835,111 +3838,111 @@
         <v>1.51</v>
       </c>
       <c r="F29" s="3">
-        <v>-0.3491529053242544</v>
+        <v>-0.23183302379674658</v>
       </c>
       <c r="G29" s="3">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="H29" s="3">
-        <v>55.6</v>
+        <v>64.04</v>
       </c>
       <c r="I29" s="3">
-        <v>-26.98</v>
+        <v>-21.51</v>
       </c>
       <c r="J29" s="3">
-        <v>-0.010200877996192138</v>
+        <v>-0.005570205553820807</v>
       </c>
       <c r="K29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3">
-        <v>-70</v>
+        <v>-69</v>
       </c>
       <c r="M29" s="3">
-        <v>-0.2297965901610577</v>
+        <v>-0.10135097778186264</v>
       </c>
       <c r="N29" s="3">
-        <v>-11.151837830232195</v>
+        <v>2.59008490171409</v>
       </c>
       <c r="O29" s="3">
-        <v>17.72151898734177</v>
+        <v>44.303797468354425</v>
       </c>
       <c r="P29" s="3">
         <v>48.25819923754261</v>
       </c>
       <c r="Q29" s="3">
-        <v>44.43037974683544</v>
+        <v>49.620253164556964</v>
       </c>
       <c r="R29" s="3">
-        <v>28.10126582278481</v>
+        <v>37.215189873417714</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>106</v>
       </c>
       <c r="T29" s="3">
-        <v>3.73</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="3">
         <v>1.95</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="3">
         <v>46.835443037974684</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="3">
         <v>1500.169230769231</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="3">
         <v>1.79</v>
       </c>
-      <c r="F30" s="1">
-        <v>-0.14145476832285253</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="F30" s="3">
+        <v>-0.13347720537409605</v>
+      </c>
+      <c r="G30" s="3">
         <v>1.19</v>
       </c>
-      <c r="H30" s="1">
-        <v>54.21</v>
-      </c>
-      <c r="I30" s="1">
-        <v>4.22</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0.00529126227078774</v>
-      </c>
-      <c r="K30" s="1" t="b">
+      <c r="H30" s="3">
+        <v>56.23</v>
+      </c>
+      <c r="I30" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.007093702256404355</v>
+      </c>
+      <c r="K30" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="3">
         <v>24</v>
       </c>
-      <c r="M30" s="1">
-        <v>-0.12102440806969272</v>
-      </c>
-      <c r="N30" s="1">
-        <v>-0.27461962109569293</v>
-      </c>
-      <c r="O30" s="1">
-        <v>43.037974683544306</v>
-      </c>
-      <c r="P30" s="1">
+      <c r="M30" s="3">
+        <v>-0.11134185828228538</v>
+      </c>
+      <c r="N30" s="3">
+        <v>1.590996851671801</v>
+      </c>
+      <c r="O30" s="3">
+        <v>40.50632911392405</v>
+      </c>
+      <c r="P30" s="3">
         <v>24.961328061128594</v>
       </c>
-      <c r="Q30" s="1">
-        <v>62.78481012658228</v>
-      </c>
-      <c r="R30" s="1">
-        <v>49.810126582278485</v>
-      </c>
-      <c r="S30" s="1" t="s">
+      <c r="Q30" s="3">
+        <v>63.164556962025316</v>
+      </c>
+      <c r="R30" s="3">
+        <v>48.79746835443037</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T30" s="1">
-        <v>2.28</v>
+      <c r="T30" s="3">
+        <v>1.27</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -3953,25 +3956,25 @@
         <v>58.22784810126582</v>
       </c>
       <c r="D31" s="2">
-        <v>10.984405458089668</v>
+        <v>11.077972709551657</v>
       </c>
       <c r="E31" s="2">
         <v>0.38</v>
       </c>
       <c r="F31" s="2">
-        <v>0.16257787632417373</v>
+        <v>0.22310480281016756</v>
       </c>
       <c r="G31" s="2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H31" s="2">
-        <v>58.44</v>
+        <v>65.92</v>
       </c>
       <c r="I31" s="2">
-        <v>21.31</v>
+        <v>26.81</v>
       </c>
       <c r="J31" s="2">
-        <v>0.02423576973198872</v>
+        <v>0.027222409406160743</v>
       </c>
       <c r="K31" s="2" t="b">
         <v>0</v>
@@ -3980,338 +3983,338 @@
         <v>66</v>
       </c>
       <c r="M31" s="2">
-        <v>0.20773972530484275</v>
+        <v>0.270870551797759</v>
       </c>
       <c r="N31" s="2">
-        <v>32.60179371635786</v>
+        <v>39.812237859676245</v>
       </c>
       <c r="O31" s="2">
-        <v>78.48101265822784</v>
+        <v>81.0126582278481</v>
       </c>
       <c r="P31" s="2">
         <v>17.25839209766727</v>
       </c>
       <c r="Q31" s="2">
-        <v>65.31645569620252</v>
+        <v>67.59493670886076</v>
       </c>
       <c r="R31" s="2">
-        <v>59.99999999999999</v>
+        <v>60.88607594936709</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T31" s="2">
-        <v>-0.82</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>-2.92</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>10.126582278481013</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="1">
         <v>8.041095890410958</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>-2.98</v>
       </c>
-      <c r="F32" s="3">
-        <v>-0.20906034438266097</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="1">
+        <v>-0.13387834243600763</v>
+      </c>
+      <c r="G32" s="1">
         <v>1.6</v>
       </c>
-      <c r="H32" s="3">
-        <v>55.1</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1.37</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-0.006898525605326837</v>
-      </c>
-      <c r="K32" s="3" t="b">
+      <c r="H32" s="1">
+        <v>63.34</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5.62</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-0.002650891559893463</v>
+      </c>
+      <c r="K32" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="1">
         <v>23</v>
       </c>
-      <c r="M32" s="3">
-        <v>-0.14454341726741948</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-2.6265205408683667</v>
-      </c>
-      <c r="O32" s="3">
-        <v>37.9746835443038</v>
-      </c>
-      <c r="P32" s="3">
-        <v>37.59071325149605</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>34.68354430379747</v>
-      </c>
-      <c r="R32" s="3">
-        <v>23.987341772151897</v>
-      </c>
-      <c r="S32" s="3" t="s">
+      <c r="M32" s="1">
+        <v>-0.06397724635660551</v>
+      </c>
+      <c r="N32" s="1">
+        <v>6.327458044239788</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="P32" s="1">
+        <v>35.692921425886716</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>40.50632911392406</v>
+      </c>
+      <c r="R32" s="1">
+        <v>28.22784810126582</v>
+      </c>
+      <c r="S32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T32" s="3">
-        <v>-5.38</v>
+      <c r="T32" s="1">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="3">
         <v>16.79</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="3">
         <v>88.60759493670885</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="3">
         <v>-0.06611078022632516</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="3">
         <v>-0.44</v>
       </c>
-      <c r="F33" s="1">
-        <v>-0.06397598574240393</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="H33" s="1">
-        <v>59.32</v>
-      </c>
-      <c r="I33" s="1">
-        <v>-6.94</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.0045870349662385755</v>
-      </c>
-      <c r="K33" s="1" t="b">
+      <c r="F33" s="3">
+        <v>0.008670304785823923</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="H33" s="3">
+        <v>69.59</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1.79</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.006795185819069533</v>
+      </c>
+      <c r="K33" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="3">
         <v>5</v>
       </c>
-      <c r="M33" s="1">
-        <v>-0.05537372879370506</v>
-      </c>
-      <c r="N33" s="1">
-        <v>6.290448306503081</v>
-      </c>
-      <c r="O33" s="1">
-        <v>50.63291139240506</v>
-      </c>
-      <c r="P33" s="1">
+      <c r="M33" s="3">
+        <v>0.019155469197734254</v>
+      </c>
+      <c r="N33" s="3">
+        <v>14.640729599673765</v>
+      </c>
+      <c r="O33" s="3">
+        <v>56.9620253164557</v>
+      </c>
+      <c r="P33" s="3">
         <v>26.81341163265095</v>
       </c>
-      <c r="Q33" s="1">
-        <v>50.25316455696202</v>
-      </c>
-      <c r="R33" s="1">
-        <v>41.26582278481012</v>
-      </c>
-      <c r="S33" s="1" t="s">
+      <c r="Q33" s="3">
+        <v>53.417721518987335</v>
+      </c>
+      <c r="R33" s="3">
+        <v>43.16455696202531</v>
+      </c>
+      <c r="S33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T33" s="1">
-        <v>1.33</v>
+      <c r="T33" s="3">
+        <v>3.23</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>13.11</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>84.81012658227847</v>
       </c>
-      <c r="D34" s="2">
-        <v>-0.7177726926010679</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="D34" s="3">
+        <v>-0.7360793287566743</v>
+      </c>
+      <c r="E34" s="3">
         <v>0.77</v>
       </c>
-      <c r="F34" s="2">
-        <v>0.12405047981024028</v>
-      </c>
-      <c r="G34" s="2">
+      <c r="F34" s="3">
+        <v>0.06359957185168871</v>
+      </c>
+      <c r="G34" s="3">
         <v>1.25</v>
       </c>
-      <c r="H34" s="2">
-        <v>61.78</v>
-      </c>
-      <c r="I34" s="2">
-        <v>30.46</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0.024112013301512865</v>
-      </c>
-      <c r="K34" s="2" t="b">
+      <c r="H34" s="3">
+        <v>52.9</v>
+      </c>
+      <c r="I34" s="3">
+        <v>26.81</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.023628206004680925</v>
+      </c>
+      <c r="K34" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="3">
         <v>35</v>
       </c>
-      <c r="M34" s="2">
-        <v>0.15093253277492424</v>
-      </c>
-      <c r="N34" s="2">
-        <v>26.921074463366</v>
-      </c>
-      <c r="O34" s="2">
-        <v>75.9493670886076</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="M34" s="3">
+        <v>0.0927250285514396</v>
+      </c>
+      <c r="N34" s="3">
+        <v>21.99768553504431</v>
+      </c>
+      <c r="O34" s="3">
+        <v>67.08860759493672</v>
+      </c>
+      <c r="P34" s="3">
         <v>20.42247430615109</v>
       </c>
-      <c r="Q34" s="2">
-        <v>57.21518987341772</v>
-      </c>
-      <c r="R34" s="2">
-        <v>50.253164556962034</v>
-      </c>
-      <c r="S34" s="2" t="s">
+      <c r="Q34" s="3">
+        <v>53.79746835443038</v>
+      </c>
+      <c r="R34" s="3">
+        <v>47.21518987341773</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T34" s="2">
-        <v>-0.89</v>
+      <c r="T34" s="3">
+        <v>-3.92</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>17.37</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="1">
         <v>91.13924050632912</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="1">
         <v>-0.4830166954519286</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="1">
         <v>9.42</v>
       </c>
-      <c r="F35" s="3">
-        <v>-0.3399483041248423</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0.99</v>
-      </c>
-      <c r="H35" s="3">
-        <v>35.72</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-22.46</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-0.02337664794308396</v>
-      </c>
-      <c r="K35" s="3" t="b">
+      <c r="F35" s="1">
+        <v>-0.35331368354013404</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="H35" s="1">
+        <v>35.98</v>
+      </c>
+      <c r="I35" s="1">
+        <v>-22.28</v>
+      </c>
+      <c r="J35" s="1">
+        <v>-0.022884000834602305</v>
+      </c>
+      <c r="K35" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L35" s="3">
-        <v>19</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-0.34102358624342965</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-22.27453743846939</v>
-      </c>
-      <c r="O35" s="3">
-        <v>5.063291139240507</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="L35" s="1">
+        <v>18</v>
+      </c>
+      <c r="M35" s="1">
+        <v>-0.3556437200761141</v>
+      </c>
+      <c r="N35" s="1">
+        <v>-22.83918932771106</v>
+      </c>
+      <c r="O35" s="1">
+        <v>3.79746835443038</v>
+      </c>
+      <c r="P35" s="1">
         <v>28.919768290867083</v>
       </c>
-      <c r="Q35" s="3">
-        <v>33.29113924050633</v>
-      </c>
-      <c r="R35" s="3">
-        <v>21.83544303797468</v>
-      </c>
-      <c r="S35" s="3" t="s">
+      <c r="Q35" s="1">
+        <v>33.164556962025316</v>
+      </c>
+      <c r="R35" s="1">
+        <v>21.455696202531644</v>
+      </c>
+      <c r="S35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T35" s="3">
-        <v>0.25</v>
+      <c r="T35" s="1">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="1">
         <v>11.51</v>
       </c>
-      <c r="C36" s="3">
-        <v>82.27848101265823</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C36" s="1">
+        <v>81.0126582278481</v>
+      </c>
+      <c r="D36" s="1">
         <v>0.3588184187662903</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="1">
         <v>3.24</v>
       </c>
-      <c r="F36" s="3">
-        <v>-0.24523179507748796</v>
-      </c>
-      <c r="G36" s="3">
-        <v>1.11</v>
-      </c>
-      <c r="H36" s="3">
-        <v>47.7</v>
-      </c>
-      <c r="I36" s="3">
-        <v>-11.49</v>
-      </c>
-      <c r="J36" s="3">
-        <v>-0.004132909354969646</v>
-      </c>
-      <c r="K36" s="3" t="b">
+      <c r="F36" s="1">
+        <v>-0.26545011191909035</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1.09</v>
+      </c>
+      <c r="H36" s="1">
+        <v>48.45</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-10.98</v>
+      </c>
+      <c r="J36" s="1">
+        <v>-0.0051308850552891794</v>
+      </c>
+      <c r="K36" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="1">
         <v>-55</v>
       </c>
-      <c r="M36" s="3">
-        <v>-0.233403691773027</v>
-      </c>
-      <c r="N36" s="3">
-        <v>-11.512547991429122</v>
-      </c>
-      <c r="O36" s="3">
+      <c r="M36" s="1">
+        <v>-0.25496494750718</v>
+      </c>
+      <c r="N36" s="1">
+        <v>-12.771312070817654</v>
+      </c>
+      <c r="O36" s="1">
         <v>16.455696202531644</v>
       </c>
-      <c r="P36" s="3">
+      <c r="P36" s="1">
         <v>32.54334537649318</v>
       </c>
-      <c r="Q36" s="3">
-        <v>44.050632911392405</v>
-      </c>
-      <c r="R36" s="3">
-        <v>28.48101265822785</v>
-      </c>
-      <c r="S36" s="3" t="s">
+      <c r="Q36" s="1">
+        <v>42.91139240506329</v>
+      </c>
+      <c r="R36" s="1">
+        <v>27.658227848101266</v>
+      </c>
+      <c r="S36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="3">
-        <v>-5.82</v>
+      <c r="T36" s="1">
+        <v>-6.65</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -4331,19 +4334,19 @@
         <v>-5.1</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.17941406829596018</v>
+        <v>-0.1996223398726307</v>
       </c>
       <c r="G37" s="1">
         <v>1.35</v>
       </c>
       <c r="H37" s="1">
-        <v>40.16</v>
+        <v>42.61</v>
       </c>
       <c r="I37" s="1">
-        <v>-21.84</v>
+        <v>-21.16</v>
       </c>
       <c r="J37" s="1">
-        <v>-0.002344914304175134</v>
+        <v>-0.001732836675708791</v>
       </c>
       <c r="K37" s="1" t="b">
         <v>0</v>
@@ -4352,28 +4355,28 @@
         <v>-214</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.14177919414540263</v>
+        <v>-0.15884670049297944</v>
       </c>
       <c r="N37" s="1">
-        <v>-2.350098228666684</v>
+        <v>-3.1594873693975916</v>
       </c>
       <c r="O37" s="1">
-        <v>39.24050632911392</v>
+        <v>34.177215189873415</v>
       </c>
       <c r="P37" s="1">
         <v>34.65975433248125</v>
       </c>
       <c r="Q37" s="1">
-        <v>37.34177215189874</v>
+        <v>37.72151898734178</v>
       </c>
       <c r="R37" s="1">
-        <v>31.075949367088608</v>
+        <v>29.55696202531646</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>92</v>
       </c>
       <c r="T37" s="1">
-        <v>-7.72</v>
+        <v>-9.24</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4387,37 +4390,37 @@
         <v>16.455696202531644</v>
       </c>
       <c r="D38" s="2">
-        <v>36.74324324324324</v>
+        <v>36.729729729729726</v>
       </c>
       <c r="E38" s="2">
         <v>-0.57</v>
       </c>
       <c r="F38" s="2">
-        <v>0.6241346954933835</v>
+        <v>0.8146071669737149</v>
       </c>
       <c r="G38" s="2">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="2">
-        <v>78.78</v>
+        <v>83.8</v>
       </c>
       <c r="I38" s="2">
-        <v>43.14</v>
+        <v>55.45</v>
       </c>
       <c r="J38" s="2">
-        <v>0.04918758702244289</v>
+        <v>0.05262778917701331</v>
       </c>
       <c r="K38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L38" s="2">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="M38" s="2">
-        <v>0.6424144915093686</v>
+        <v>0.8379075323335157</v>
       </c>
       <c r="N38" s="2">
-        <v>76.06927033681043</v>
+        <v>96.51593591325192</v>
       </c>
       <c r="O38" s="2">
         <v>92.40506329113924</v>
@@ -4426,326 +4429,326 @@
         <v>26.865173556258448</v>
       </c>
       <c r="Q38" s="2">
-        <v>65.44303797468353</v>
+        <v>65.82278481012659</v>
       </c>
       <c r="R38" s="2">
-        <v>56.26582278481013</v>
+        <v>55.949367088607595</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>109</v>
       </c>
       <c r="T38" s="2">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="3">
         <v>-0.25</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="3">
         <v>22.78481012658228</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="3">
         <v>44.4</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="3">
         <v>6.03</v>
       </c>
-      <c r="F39" s="1">
-        <v>-0.14160568092092332</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1.25</v>
-      </c>
-      <c r="H39" s="1">
-        <v>30.69</v>
-      </c>
-      <c r="I39" s="1">
-        <v>-11.08</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0.0007765026087280258</v>
-      </c>
-      <c r="K39" s="1" t="b">
+      <c r="F39" s="3">
+        <v>-0.16106483974385025</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="H39" s="3">
+        <v>31.09</v>
+      </c>
+      <c r="I39" s="3">
+        <v>-10.83</v>
+      </c>
+      <c r="J39" s="3">
+        <v>-0.00005971426348136263</v>
+      </c>
+      <c r="K39" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L39" s="3">
         <v>-4</v>
       </c>
-      <c r="M39" s="1">
-        <v>-0.11472362795623936</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0.35545839024965137</v>
-      </c>
-      <c r="O39" s="1">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="P39" s="1">
+      <c r="M39" s="3">
+        <v>-0.13426941958007943</v>
+      </c>
+      <c r="N39" s="3">
+        <v>-0.7017592781075979</v>
+      </c>
+      <c r="O39" s="3">
+        <v>39.24050632911392</v>
+      </c>
+      <c r="P39" s="3">
         <v>23.417722010155686</v>
       </c>
-      <c r="Q39" s="1">
-        <v>43.164556962025316</v>
-      </c>
-      <c r="R39" s="1">
-        <v>40.44303797468355</v>
-      </c>
-      <c r="S39" s="1" t="s">
+      <c r="Q39" s="3">
+        <v>42.025316455696206</v>
+      </c>
+      <c r="R39" s="3">
+        <v>37.848101265822784</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="T39" s="1">
-        <v>-12.97</v>
+      <c r="T39" s="3">
+        <v>-15.57</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="1">
         <v>-6.41</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="1">
         <v>2.5316455696202533</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="1">
         <v>10.182527301092042</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="1">
         <v>2.22</v>
       </c>
-      <c r="F40" s="3">
-        <v>0.08365880524915408</v>
-      </c>
-      <c r="G40" s="3">
+      <c r="F40" s="1">
+        <v>0.10138764021048279</v>
+      </c>
+      <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="H40" s="3">
-        <v>43.2</v>
-      </c>
-      <c r="I40" s="3">
-        <v>-20.01</v>
-      </c>
-      <c r="J40" s="3">
-        <v>-0.00698609833271195</v>
-      </c>
-      <c r="K40" s="3" t="b">
+      <c r="H40" s="1">
+        <v>41.02</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-21.96</v>
+      </c>
+      <c r="J40" s="1">
+        <v>-0.008086445195954525</v>
+      </c>
+      <c r="K40" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L40" s="3">
+      <c r="L40" s="1">
         <v>54</v>
       </c>
-      <c r="M40" s="3">
-        <v>-0.0238694066095817</v>
-      </c>
-      <c r="N40" s="3">
-        <v>9.440880524915404</v>
-      </c>
-      <c r="O40" s="3">
-        <v>56.9620253164557</v>
-      </c>
-      <c r="P40" s="3">
+      <c r="M40" s="1">
+        <v>-0.015114186588520706</v>
+      </c>
+      <c r="N40" s="1">
+        <v>11.213764021048283</v>
+      </c>
+      <c r="O40" s="1">
+        <v>53.16455696202531</v>
+      </c>
+      <c r="P40" s="1">
         <v>39.97107065255327</v>
       </c>
-      <c r="Q40" s="3">
-        <v>27.594936708860757</v>
-      </c>
-      <c r="R40" s="3">
-        <v>27.91139240506329</v>
-      </c>
-      <c r="S40" s="3" t="s">
+      <c r="Q40" s="1">
+        <v>25.44303797468354</v>
+      </c>
+      <c r="R40" s="1">
+        <v>25.886075949367083</v>
+      </c>
+      <c r="S40" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="T40" s="3">
-        <v>-12.85</v>
+      <c r="T40" s="1">
+        <v>-14.87</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="3">
         <v>-5.03</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="3">
         <v>5.063291139240507</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="3">
         <v>7.121272365805169</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="3">
         <v>-1.06</v>
       </c>
-      <c r="F41" s="1">
-        <v>0.05853267099388554</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.12</v>
-      </c>
-      <c r="H41" s="1">
-        <v>65.85</v>
-      </c>
-      <c r="I41" s="1">
-        <v>-5.15</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0.02846949048870736</v>
-      </c>
-      <c r="K41" s="1" t="b">
+      <c r="F41" s="3">
+        <v>0.07749513392864157</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1.15</v>
+      </c>
+      <c r="H41" s="3">
+        <v>64.49</v>
+      </c>
+      <c r="I41" s="3">
+        <v>-5.63</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0.030257333663119494</v>
+      </c>
+      <c r="K41" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L41" s="3">
         <v>3</v>
       </c>
-      <c r="M41" s="1">
-        <v>0.07143605641693385</v>
-      </c>
-      <c r="N41" s="1">
-        <v>18.971426827566965</v>
-      </c>
-      <c r="O41" s="1">
-        <v>67.08860759493672</v>
-      </c>
-      <c r="P41" s="1">
+      <c r="M41" s="3">
+        <v>0.0949704079484921</v>
+      </c>
+      <c r="N41" s="3">
+        <v>22.222223474749555</v>
+      </c>
+      <c r="O41" s="3">
+        <v>68.35443037974683</v>
+      </c>
+      <c r="P41" s="3">
         <v>46.4052282234621</v>
       </c>
-      <c r="Q41" s="1">
-        <v>45.18987341772152</v>
-      </c>
-      <c r="R41" s="1">
-        <v>34.430379746835456</v>
-      </c>
-      <c r="S41" s="1" t="s">
+      <c r="Q41" s="3">
+        <v>45.82278481012659</v>
+      </c>
+      <c r="R41" s="3">
+        <v>35.69620253164557</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T41" s="1">
-        <v>4.37</v>
+      <c r="T41" s="3">
+        <v>5.63</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="3">
         <v>3.61</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="3">
         <v>53.16455696202531</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="3">
         <v>1.0637119113573408</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="3">
         <v>2.81</v>
       </c>
-      <c r="F42" s="1">
-        <v>-0.09981712874332024</v>
-      </c>
-      <c r="G42" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="H42" s="1">
-        <v>43.37</v>
-      </c>
-      <c r="I42" s="1">
-        <v>-0.58</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-0.004533437057777776</v>
-      </c>
-      <c r="K42" s="1" t="b">
+      <c r="F42" s="3">
+        <v>-0.12197523617098611</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="H42" s="3">
+        <v>40.62</v>
+      </c>
+      <c r="I42" s="3">
+        <v>-1.39</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-0.005248683020322596</v>
+      </c>
+      <c r="K42" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L42" s="1">
-        <v>19</v>
-      </c>
-      <c r="M42" s="1">
-        <v>-0.16863518433291114</v>
-      </c>
-      <c r="N42" s="1">
-        <v>-5.035697247417541</v>
-      </c>
-      <c r="O42" s="1">
-        <v>32.91139240506329</v>
-      </c>
-      <c r="P42" s="1">
+      <c r="L42" s="3">
+        <v>17</v>
+      </c>
+      <c r="M42" s="3">
+        <v>-0.19770142359033838</v>
+      </c>
+      <c r="N42" s="3">
+        <v>-7.044959679133483</v>
+      </c>
+      <c r="O42" s="3">
+        <v>24.050632911392405</v>
+      </c>
+      <c r="P42" s="3">
         <v>10.38279059078273</v>
       </c>
-      <c r="Q42" s="1">
-        <v>40.88607594936709</v>
-      </c>
-      <c r="R42" s="1">
-        <v>36.0759493670886</v>
-      </c>
-      <c r="S42" s="1" t="s">
+      <c r="Q42" s="3">
+        <v>39.493670886075954</v>
+      </c>
+      <c r="R42" s="3">
+        <v>33.164556962025316</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="T42" s="1">
-        <v>-2.47</v>
+      <c r="T42" s="3">
+        <v>-5.38</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="3">
         <v>-0.02</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="3">
         <v>27.848101265822784</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="3">
         <v>1214</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="3">
         <v>10.72</v>
       </c>
-      <c r="F43" s="1">
-        <v>-0.05718649574350687</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="H43" s="1">
-        <v>56.82</v>
-      </c>
-      <c r="I43" s="1">
-        <v>-7.32</v>
-      </c>
-      <c r="J43" s="1">
-        <v>-0.005557203239642593</v>
-      </c>
-      <c r="K43" s="1" t="b">
+      <c r="F43" s="3">
+        <v>0.0485243428195096</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="3">
+        <v>66.87</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="J43" s="3">
+        <v>-0.003428224080707113</v>
+      </c>
+      <c r="K43" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L43" s="3">
         <v>10</v>
       </c>
-      <c r="M43" s="1">
-        <v>-0.028153878541648192</v>
-      </c>
-      <c r="N43" s="1">
-        <v>9.012433331708749</v>
-      </c>
-      <c r="O43" s="1">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="P43" s="1">
+      <c r="M43" s="3">
+        <v>0.08347489085921067</v>
+      </c>
+      <c r="N43" s="3">
+        <v>21.072671765821408</v>
+      </c>
+      <c r="O43" s="3">
+        <v>65.82278481012658</v>
+      </c>
+      <c r="P43" s="3">
         <v>33.21399316212126</v>
       </c>
-      <c r="Q43" s="1">
-        <v>50.12658227848101</v>
-      </c>
-      <c r="R43" s="1">
-        <v>43.291139240506325</v>
-      </c>
-      <c r="S43" s="1" t="s">
+      <c r="Q43" s="3">
+        <v>55.82278481012658</v>
+      </c>
+      <c r="R43" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T43" s="1">
-        <v>1.14</v>
+      <c r="T43" s="3">
+        <v>4.68</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -4765,49 +4768,49 @@
         <v>-0.99</v>
       </c>
       <c r="F44" s="3">
-        <v>-0.37587664939233606</v>
+        <v>-0.3292213160718403</v>
       </c>
       <c r="G44" s="3">
         <v>2.59</v>
       </c>
       <c r="H44" s="3">
-        <v>55.46</v>
+        <v>58.82</v>
       </c>
       <c r="I44" s="3">
-        <v>-17.7</v>
+        <v>-14.98</v>
       </c>
       <c r="J44" s="3">
-        <v>-0.016791017323795794</v>
+        <v>-0.013507900808196884</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="M44" s="3">
-        <v>-0.20490679253694621</v>
+        <v>-0.1439834114614248</v>
       </c>
       <c r="N44" s="3">
-        <v>-8.66285806782104</v>
+        <v>-1.6731584662421262</v>
       </c>
       <c r="O44" s="3">
-        <v>20.253164556962027</v>
+        <v>36.708860759493675</v>
       </c>
       <c r="P44" s="3">
         <v>43.36598203964858</v>
       </c>
       <c r="Q44" s="3">
-        <v>43.291139240506325</v>
+        <v>45.063291139240505</v>
       </c>
       <c r="R44" s="3">
-        <v>28.417721518987342</v>
+        <v>33.35443037974684</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>92</v>
       </c>
       <c r="T44" s="3">
-        <v>1.9</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -4821,25 +4824,25 @@
         <v>73.41772151898735</v>
       </c>
       <c r="D45" s="2">
-        <v>0.720430107526882</v>
+        <v>0.7228195937873358</v>
       </c>
       <c r="E45" s="2">
         <v>0.86</v>
       </c>
       <c r="F45" s="2">
-        <v>0.1500733663470312</v>
+        <v>0.10908432565781392</v>
       </c>
       <c r="G45" s="2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H45" s="2">
-        <v>64.4</v>
+        <v>59.69</v>
       </c>
       <c r="I45" s="2">
-        <v>18.47</v>
+        <v>16.9</v>
       </c>
       <c r="J45" s="2">
-        <v>0.024127182400048644</v>
+        <v>0.024427320861098265</v>
       </c>
       <c r="K45" s="2" t="b">
         <v>0</v>
@@ -4848,214 +4851,214 @@
         <v>33</v>
       </c>
       <c r="M45" s="2">
-        <v>0.19953634380204965</v>
+        <v>0.1615101477173655</v>
       </c>
       <c r="N45" s="2">
-        <v>31.78145556607855</v>
+        <v>28.876197451636905</v>
       </c>
       <c r="O45" s="2">
-        <v>77.21518987341773</v>
+        <v>75.9493670886076</v>
       </c>
       <c r="P45" s="2">
         <v>19.641850851970627</v>
       </c>
       <c r="Q45" s="2">
-        <v>62.27848101265823</v>
+        <v>60.63291139240506</v>
       </c>
       <c r="R45" s="2">
-        <v>55.50632911392405</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="T45" s="2">
-        <v>-1.46</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="1">
         <v>-0.3</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="1">
         <v>21.518987341772153</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="1">
         <v>543.5000000000001</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="1">
         <v>5.16</v>
       </c>
-      <c r="F46" s="3">
-        <v>-0.36146093680603075</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1.47</v>
-      </c>
-      <c r="H46" s="3">
-        <v>45.3</v>
-      </c>
-      <c r="I46" s="3">
-        <v>3.05</v>
-      </c>
-      <c r="J46" s="3">
-        <v>-0.006175111991981685</v>
-      </c>
-      <c r="K46" s="3" t="b">
+      <c r="F46" s="1">
+        <v>-0.3262460642111287</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H46" s="1">
+        <v>44.28</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.004423731687799573</v>
+      </c>
+      <c r="K46" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="1">
         <v>27</v>
       </c>
-      <c r="M46" s="3">
-        <v>-0.31092267723242495</v>
-      </c>
-      <c r="N46" s="3">
-        <v>-19.26444653736892</v>
-      </c>
-      <c r="O46" s="3">
-        <v>8.860759493670885</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="M46" s="1">
+        <v>-0.2726552238835871</v>
+      </c>
+      <c r="N46" s="1">
+        <v>-14.540339708458358</v>
+      </c>
+      <c r="O46" s="1">
+        <v>13.924050632911392</v>
+      </c>
+      <c r="P46" s="1">
         <v>41.630589083814144</v>
       </c>
-      <c r="Q46" s="3">
-        <v>47.594936708860764</v>
-      </c>
-      <c r="R46" s="3">
-        <v>25.822784810126578</v>
-      </c>
-      <c r="S46" s="3" t="s">
+      <c r="Q46" s="1">
+        <v>47.46835443037975</v>
+      </c>
+      <c r="R46" s="1">
+        <v>27.721518987341767</v>
+      </c>
+      <c r="S46" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T46" s="3">
-        <v>-5.57</v>
+      <c r="T46" s="1">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="1">
         <v>10.62</v>
       </c>
-      <c r="C47" s="3">
-        <v>81.0126582278481</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="C47" s="1">
+        <v>79.74683544303798</v>
+      </c>
+      <c r="D47" s="1">
         <v>0.8549905838041432</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="1">
         <v>1.38</v>
       </c>
-      <c r="F47" s="3">
-        <v>-0.49744067626176725</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1.44</v>
-      </c>
-      <c r="H47" s="3">
-        <v>27.1</v>
-      </c>
-      <c r="I47" s="3">
-        <v>-24.38</v>
-      </c>
-      <c r="J47" s="3">
-        <v>-0.03134447166022486</v>
-      </c>
-      <c r="K47" s="3" t="b">
+      <c r="F47" s="1">
+        <v>-0.48840806761074906</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="H47" s="1">
+        <v>28.35</v>
+      </c>
+      <c r="I47" s="1">
+        <v>-23.95</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-0.03146335978104784</v>
+      </c>
+      <c r="K47" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="1">
         <v>9</v>
       </c>
-      <c r="M47" s="3">
-        <v>-0.4501282630439235</v>
-      </c>
-      <c r="N47" s="3">
-        <v>-33.185005118518774</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="M47" s="1">
+        <v>-0.43947730035516763</v>
+      </c>
+      <c r="N47" s="1">
+        <v>-31.22254735561642</v>
+      </c>
+      <c r="O47" s="1">
         <v>1.2658227848101267</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="1">
         <v>33.84253937304741</v>
       </c>
-      <c r="Q47" s="3">
-        <v>37.721518987341774</v>
-      </c>
-      <c r="R47" s="3">
-        <v>23.9240506329114</v>
-      </c>
-      <c r="S47" s="3" t="s">
+      <c r="Q47" s="1">
+        <v>37.21518987341773</v>
+      </c>
+      <c r="R47" s="1">
+        <v>23.607594936708868</v>
+      </c>
+      <c r="S47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T47" s="3">
-        <v>-1.84</v>
+      <c r="T47" s="1">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="3">
         <v>5.18</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="3">
         <v>59.49367088607595</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="3">
         <v>0.7683397683397685</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="3">
         <v>0.6</v>
       </c>
-      <c r="F48" s="1">
-        <v>-0.20058760267233752</v>
-      </c>
-      <c r="G48" s="1">
+      <c r="F48" s="3">
+        <v>-0.20331765997996998</v>
+      </c>
+      <c r="G48" s="3">
         <v>1.02</v>
       </c>
-      <c r="H48" s="1">
-        <v>57.88</v>
-      </c>
-      <c r="I48" s="1">
-        <v>-3.05</v>
-      </c>
-      <c r="J48" s="1">
-        <v>0.0016132729502708948</v>
-      </c>
-      <c r="K48" s="1" t="b">
+      <c r="H48" s="3">
+        <v>58.35</v>
+      </c>
+      <c r="I48" s="3">
+        <v>-2.85</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0.0031967856605229932</v>
+      </c>
+      <c r="K48" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L48" s="3">
         <v>-67</v>
       </c>
-      <c r="M48" s="1">
-        <v>-0.1984370384351628</v>
-      </c>
-      <c r="N48" s="1">
-        <v>-8.015882657642704</v>
-      </c>
-      <c r="O48" s="1">
+      <c r="M48" s="3">
+        <v>-0.2009876234439899</v>
+      </c>
+      <c r="N48" s="3">
+        <v>-7.373579664498636</v>
+      </c>
+      <c r="O48" s="3">
         <v>22.78481012658228</v>
       </c>
-      <c r="P48" s="1">
+      <c r="P48" s="3">
         <v>19.13407224404345</v>
       </c>
-      <c r="Q48" s="1">
-        <v>46.962025316455694</v>
-      </c>
-      <c r="R48" s="1">
-        <v>32.9746835443038</v>
-      </c>
-      <c r="S48" s="1" t="s">
+      <c r="Q48" s="3">
+        <v>47.34177215189873</v>
+      </c>
+      <c r="R48" s="3">
+        <v>33.164556962025316</v>
+      </c>
+      <c r="S48" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T48" s="1">
-        <v>6.77</v>
+      <c r="T48" s="3">
+        <v>6.96</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -5075,49 +5078,49 @@
         <v>-0.36</v>
       </c>
       <c r="F49" s="2">
-        <v>-0.004916213470242792</v>
+        <v>-0.018054104889669326</v>
       </c>
       <c r="G49" s="2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H49" s="2">
-        <v>55.19</v>
+        <v>52.28</v>
       </c>
       <c r="I49" s="2">
-        <v>40.17</v>
+        <v>37.81</v>
       </c>
       <c r="J49" s="2">
-        <v>0.023937188198511573</v>
+        <v>0.02444271069944749</v>
       </c>
       <c r="K49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L49" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M49" s="2">
-        <v>0.060675995763586066</v>
+        <v>0.051846991189732794</v>
       </c>
       <c r="N49" s="2">
-        <v>17.89542076223218</v>
+        <v>17.909881798873624</v>
       </c>
       <c r="O49" s="2">
-        <v>65.82278481012658</v>
+        <v>59.49367088607595</v>
       </c>
       <c r="P49" s="2">
         <v>13.880000945060484</v>
       </c>
       <c r="Q49" s="2">
-        <v>61.64556962025316</v>
+        <v>61.139240506329116</v>
       </c>
       <c r="R49" s="2">
-        <v>54.93670886075949</v>
+        <v>53.164556962025316</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>105</v>
       </c>
       <c r="T49" s="2">
-        <v>-0.38</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -5137,49 +5140,49 @@
         <v>5.72</v>
       </c>
       <c r="F50" s="2">
-        <v>0.3032062272106687</v>
+        <v>0.38199906720470367</v>
       </c>
       <c r="G50" s="2">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="H50" s="2">
-        <v>58.12</v>
+        <v>56.18</v>
       </c>
       <c r="I50" s="2">
-        <v>111.7</v>
+        <v>106.21</v>
       </c>
       <c r="J50" s="2">
-        <v>0.06883529244451002</v>
+        <v>0.06592975996614166</v>
       </c>
       <c r="K50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L50" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M50" s="2">
-        <v>0.6021346561779541</v>
+        <v>0.7035441091699532</v>
       </c>
       <c r="N50" s="2">
-        <v>72.041286803669</v>
+        <v>83.07959359689566</v>
       </c>
       <c r="O50" s="2">
-        <v>91.13924050632912</v>
+        <v>89.87341772151899</v>
       </c>
       <c r="P50" s="2">
         <v>31.61869931071345</v>
       </c>
       <c r="Q50" s="2">
-        <v>70.8860759493671</v>
+        <v>70.12658227848101</v>
       </c>
       <c r="R50" s="2">
-        <v>61.51898734177215</v>
+        <v>61.13924050632911</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T50" s="2">
-        <v>-2.03</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -5199,19 +5202,19 @@
         <v>4.31</v>
       </c>
       <c r="F51" s="2">
-        <v>-0.02028427327566104</v>
+        <v>-0.009801022322729891</v>
       </c>
       <c r="G51" s="2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H51" s="2">
-        <v>44.64</v>
+        <v>45.38</v>
       </c>
       <c r="I51" s="2">
-        <v>49.31</v>
+        <v>49.43</v>
       </c>
       <c r="J51" s="2">
-        <v>0.018827874856338744</v>
+        <v>0.01848470606497522</v>
       </c>
       <c r="K51" s="2" t="b">
         <v>0</v>
@@ -5220,152 +5223,152 @@
         <v>248</v>
       </c>
       <c r="M51" s="2">
-        <v>0.0936956312945989</v>
+        <v>0.11136087754823376</v>
       </c>
       <c r="N51" s="2">
-        <v>21.197384315333462</v>
+        <v>23.861270434723732</v>
       </c>
       <c r="O51" s="2">
-        <v>69.62025316455697</v>
+        <v>72.15189873417721</v>
       </c>
       <c r="P51" s="2">
         <v>16.492575418924176</v>
       </c>
       <c r="Q51" s="2">
-        <v>59.24050632911392</v>
+        <v>58.607594936708864</v>
       </c>
       <c r="R51" s="2">
-        <v>54.49367088607596</v>
+        <v>55.063291139240505</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T51" s="2">
-        <v>-8.54</v>
+        <v>-7.97</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="1">
         <v>-0.13</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="1">
         <v>25.31645569620253</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="1">
         <v>300.1538461538462</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="1">
         <v>6.03</v>
       </c>
-      <c r="F52" s="3">
-        <v>-0.36877679077385783</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1.55</v>
-      </c>
-      <c r="H52" s="3">
-        <v>52.72</v>
-      </c>
-      <c r="I52" s="3">
-        <v>-16.26</v>
-      </c>
-      <c r="J52" s="3">
-        <v>-0.031104857918810264</v>
-      </c>
-      <c r="K52" s="3" t="b">
+      <c r="F52" s="1">
+        <v>-0.3612154407216672</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H52" s="1">
+        <v>47.89</v>
+      </c>
+      <c r="I52" s="1">
+        <v>-19.43</v>
+      </c>
+      <c r="J52" s="1">
+        <v>-0.027130684693928847</v>
+      </c>
+      <c r="K52" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="1">
         <v>-1</v>
       </c>
-      <c r="M52" s="3">
-        <v>-0.30963627425155316</v>
-      </c>
-      <c r="N52" s="3">
-        <v>-19.13580623928174</v>
-      </c>
-      <c r="O52" s="3">
-        <v>10.126582278481013</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="M52" s="1">
+        <v>-0.29830445425020535</v>
+      </c>
+      <c r="N52" s="1">
+        <v>-17.105262745120182</v>
+      </c>
+      <c r="O52" s="1">
+        <v>8.860759493670885</v>
+      </c>
+      <c r="P52" s="1">
         <v>45.32019556900826</v>
       </c>
-      <c r="Q52" s="3">
-        <v>41.265822784810126</v>
-      </c>
-      <c r="R52" s="3">
-        <v>24.11392405063291</v>
-      </c>
-      <c r="S52" s="3" t="s">
+      <c r="Q52" s="1">
+        <v>40.379746835443036</v>
+      </c>
+      <c r="R52" s="1">
+        <v>23.734177215189867</v>
+      </c>
+      <c r="S52" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T52" s="3">
-        <v>2.34</v>
+      <c r="T52" s="1">
+        <v>1.96</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="3">
         <v>-3.88</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="3">
         <v>6.329113924050633</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="3">
         <v>13.440721649484537</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="3">
         <v>37.01</v>
       </c>
-      <c r="F53" s="1">
-        <v>0.135880921718201</v>
-      </c>
-      <c r="G53" s="1">
-        <v>2.36</v>
-      </c>
-      <c r="H53" s="1">
-        <v>61.43</v>
-      </c>
-      <c r="I53" s="1">
-        <v>46.62</v>
-      </c>
-      <c r="J53" s="1">
-        <v>0.03191733253584712</v>
-      </c>
-      <c r="K53" s="1" t="b">
+      <c r="F53" s="3">
+        <v>0.1951512945193788</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.37</v>
+      </c>
+      <c r="H53" s="3">
+        <v>60.82</v>
+      </c>
+      <c r="I53" s="3">
+        <v>45.35</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0.03804757318712313</v>
+      </c>
+      <c r="K53" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L53" s="1">
+      <c r="L53" s="3">
         <v>95</v>
       </c>
-      <c r="M53" s="1">
-        <v>0.2821192898460816</v>
-      </c>
-      <c r="N53" s="1">
-        <v>40.039750170481724</v>
-      </c>
-      <c r="O53" s="1">
-        <v>84.81012658227847</v>
-      </c>
-      <c r="P53" s="1">
+      <c r="M53" s="3">
+        <v>0.3547587972340136</v>
+      </c>
+      <c r="N53" s="3">
+        <v>48.201062403301705</v>
+      </c>
+      <c r="O53" s="3">
+        <v>82.27848101265823</v>
+      </c>
+      <c r="P53" s="3">
         <v>46.744012320672994</v>
       </c>
-      <c r="Q53" s="1">
-        <v>54.303797468354425</v>
-      </c>
-      <c r="R53" s="1">
-        <v>43.79746835443038</v>
-      </c>
-      <c r="S53" s="1" t="s">
+      <c r="Q53" s="3">
+        <v>54.30379746835443</v>
+      </c>
+      <c r="R53" s="3">
+        <v>43.164556962025316</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="T53" s="1">
-        <v>17.15</v>
+      <c r="T53" s="3">
+        <v>16.52</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -5385,19 +5388,19 @@
         <v>-0.82</v>
       </c>
       <c r="F54" s="2">
-        <v>0.11940183329063642</v>
+        <v>0.1329396604551625</v>
       </c>
       <c r="G54" s="2">
         <v>1.86</v>
       </c>
       <c r="H54" s="2">
-        <v>66.01</v>
+        <v>66.07</v>
       </c>
       <c r="I54" s="2">
-        <v>65.79</v>
+        <v>64.97</v>
       </c>
       <c r="J54" s="2">
-        <v>0.03812273394786268</v>
+        <v>0.03866798658816369</v>
       </c>
       <c r="K54" s="2" t="b">
         <v>0</v>
@@ -5406,10 +5409,10 @@
         <v>297</v>
       </c>
       <c r="M54" s="2">
-        <v>0.2118760954891492</v>
+        <v>0.23313123150230552</v>
       </c>
       <c r="N54" s="2">
-        <v>33.0154307347885</v>
+        <v>36.03830583013091</v>
       </c>
       <c r="O54" s="2">
         <v>79.74683544303798</v>
@@ -5418,7 +5421,7 @@
         <v>20.10180966623631</v>
       </c>
       <c r="Q54" s="2">
-        <v>68.60759493670886</v>
+        <v>68.22784810126582</v>
       </c>
       <c r="R54" s="2">
         <v>58.41772151898735</v>
@@ -5431,65 +5434,65 @@
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="3">
         <v>-0.71</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="3">
         <v>17.72151898734177</v>
       </c>
-      <c r="D55" s="1">
-        <v>10.056338028169014</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="D55" s="3">
+        <v>6.873239436619719</v>
+      </c>
+      <c r="E55" s="3">
         <v>6.07</v>
       </c>
-      <c r="F55" s="1">
-        <v>-0.03382289925919629</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2.61</v>
-      </c>
-      <c r="H55" s="1">
-        <v>65.64</v>
-      </c>
-      <c r="I55" s="1">
-        <v>-9.78</v>
-      </c>
-      <c r="J55" s="1">
-        <v>0.025689062074226256</v>
-      </c>
-      <c r="K55" s="1" t="b">
+      <c r="F55" s="3">
+        <v>-0.018297005399717625</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2.62</v>
+      </c>
+      <c r="H55" s="3">
+        <v>63.25</v>
+      </c>
+      <c r="I55" s="3">
+        <v>-11.25</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0.027709444384052366</v>
+      </c>
+      <c r="K55" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L55" s="1">
-        <v>-16</v>
-      </c>
-      <c r="M55" s="1">
-        <v>0.1392975218333683</v>
-      </c>
-      <c r="N55" s="1">
-        <v>25.7575733692104</v>
-      </c>
-      <c r="O55" s="1">
-        <v>73.41772151898735</v>
-      </c>
-      <c r="P55" s="1">
+      <c r="L55" s="3">
+        <v>-15</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0.17043595401466805</v>
+      </c>
+      <c r="N55" s="3">
+        <v>29.76877808136716</v>
+      </c>
+      <c r="O55" s="3">
+        <v>78.48101265822784</v>
+      </c>
+      <c r="P55" s="3">
         <v>47.39629233644822</v>
       </c>
-      <c r="Q55" s="1">
-        <v>50.00000000000001</v>
-      </c>
-      <c r="R55" s="1">
-        <v>40.8860759493671</v>
-      </c>
-      <c r="S55" s="1" t="s">
+      <c r="Q55" s="3">
+        <v>46.58227848101265</v>
+      </c>
+      <c r="R55" s="3">
+        <v>40.632911392405056</v>
+      </c>
+      <c r="S55" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T55" s="1">
-        <v>5.76</v>
+      <c r="T55" s="3">
+        <v>5.51</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -5503,25 +5506,25 @@
         <v>36.708860759493675</v>
       </c>
       <c r="D56" s="2">
-        <v>33.92424242424242</v>
+        <v>33.96969696969697</v>
       </c>
       <c r="E56" s="2">
         <v>-1.41</v>
       </c>
       <c r="F56" s="2">
-        <v>-0.061814392023507386</v>
+        <v>0.06307025705197225</v>
       </c>
       <c r="G56" s="2">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="H56" s="2">
-        <v>44.88</v>
+        <v>52.55</v>
       </c>
       <c r="I56" s="2">
-        <v>-2.52</v>
+        <v>5.98</v>
       </c>
       <c r="J56" s="2">
-        <v>0.02990603370605665</v>
+        <v>0.029239188458194603</v>
       </c>
       <c r="K56" s="2" t="b">
         <v>1</v>
@@ -5530,152 +5533,152 @@
         <v>13</v>
       </c>
       <c r="M56" s="2">
-        <v>-0.011276132449901555</v>
+        <v>0.11083600603956367</v>
       </c>
       <c r="N56" s="2">
-        <v>10.700207940883413</v>
+        <v>23.808783283856716</v>
       </c>
       <c r="O56" s="2">
-        <v>58.22784810126582</v>
+        <v>70.88607594936708</v>
       </c>
       <c r="P56" s="2">
         <v>25.062459708672506</v>
       </c>
       <c r="Q56" s="2">
-        <v>58.73417721518987</v>
+        <v>61.0126582278481</v>
       </c>
       <c r="R56" s="2">
-        <v>50.75949367088608</v>
+        <v>53.98734177215191</v>
       </c>
       <c r="S56" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T56" s="2">
-        <v>-1.9</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="3">
         <v>4.03</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="3">
         <v>56.9620253164557</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="3">
         <v>2.307692307692308</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="3">
         <v>-1.23</v>
       </c>
-      <c r="F57" s="1">
-        <v>-0.1690381334200837</v>
-      </c>
-      <c r="G57" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="H57" s="1">
-        <v>45.19</v>
-      </c>
-      <c r="I57" s="1">
-        <v>-2.03</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0.008148559390721215</v>
-      </c>
-      <c r="K57" s="1" t="b">
+      <c r="F57" s="3">
+        <v>-0.11386647194367264</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="H57" s="3">
+        <v>51.14</v>
+      </c>
+      <c r="I57" s="3">
+        <v>-0.47</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0.008848473543211676</v>
+      </c>
+      <c r="K57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" s="3">
+        <v>-63</v>
+      </c>
+      <c r="M57" s="3">
+        <v>-0.09173112485186197</v>
+      </c>
+      <c r="N57" s="3">
+        <v>3.552070194714145</v>
+      </c>
+      <c r="O57" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="P57" s="3">
+        <v>18.39301096820415</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>48.860759493670884</v>
+      </c>
+      <c r="R57" s="3">
+        <v>42.08860759493671</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="T57" s="3">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3">
+        <v>8.65</v>
+      </c>
+      <c r="C58" s="3">
+        <v>74.68354430379746</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.18728323699421956</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="F58" s="3">
+        <v>-0.13402437999435216</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="H58" s="3">
+        <v>42.79</v>
+      </c>
+      <c r="I58" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="J58" s="3">
+        <v>-0.004299484933438593</v>
+      </c>
+      <c r="K58" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L57" s="1">
-        <v>-62</v>
-      </c>
-      <c r="M57" s="1">
-        <v>-0.14753249104833654</v>
-      </c>
-      <c r="N57" s="1">
-        <v>-2.9254279189600743</v>
-      </c>
-      <c r="O57" s="1">
-        <v>36.708860759493675</v>
-      </c>
-      <c r="P57" s="1">
-        <v>18.39301096820415</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>48.481012658227854</v>
-      </c>
-      <c r="R57" s="1">
-        <v>39.55696202531646</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="T57" s="1">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1">
-        <v>8.65</v>
-      </c>
-      <c r="C58" s="1">
-        <v>74.68354430379746</v>
-      </c>
-      <c r="D58" s="1">
-        <v>0.1757225433526011</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1.28</v>
-      </c>
-      <c r="F58" s="1">
-        <v>-0.09074659291964061</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="H58" s="1">
-        <v>51.54</v>
-      </c>
-      <c r="I58" s="1">
-        <v>9.07</v>
-      </c>
-      <c r="J58" s="1">
-        <v>-0.004236304102651456</v>
-      </c>
-      <c r="K58" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="L58" s="3">
         <v>164</v>
       </c>
-      <c r="M58" s="1">
-        <v>-0.17031746969510508</v>
-      </c>
-      <c r="N58" s="1">
-        <v>-5.203925783636928</v>
-      </c>
-      <c r="O58" s="1">
-        <v>30.37974683544304</v>
-      </c>
-      <c r="P58" s="1">
+      <c r="M58" s="3">
+        <v>-0.22023573182561473</v>
+      </c>
+      <c r="N58" s="3">
+        <v>-9.298390502661121</v>
+      </c>
+      <c r="O58" s="3">
+        <v>21.518987341772153</v>
+      </c>
+      <c r="P58" s="3">
         <v>10.95912073621325</v>
       </c>
-      <c r="Q58" s="1">
-        <v>44.43037974683544</v>
-      </c>
-      <c r="R58" s="1">
-        <v>35.75949367088607</v>
-      </c>
-      <c r="S58" s="1" t="s">
+      <c r="Q58" s="3">
+        <v>43.164556962025316</v>
+      </c>
+      <c r="R58" s="3">
+        <v>33.10126582278481</v>
+      </c>
+      <c r="S58" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="T58" s="1">
-        <v>1.77</v>
+      <c r="T58" s="3">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -5689,25 +5692,25 @@
         <v>96.20253164556962</v>
       </c>
       <c r="D59" s="2">
-        <v>2.4258734655335226</v>
+        <v>2.4466477809254012</v>
       </c>
       <c r="E59" s="2">
         <v>-1.3</v>
       </c>
       <c r="F59" s="2">
-        <v>0.9857913782483314</v>
+        <v>1.095782612173617</v>
       </c>
       <c r="G59" s="2">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="H59" s="2">
-        <v>75.68</v>
+        <v>78.01</v>
       </c>
       <c r="I59" s="2">
-        <v>176.07</v>
+        <v>186.65</v>
       </c>
       <c r="J59" s="2">
-        <v>0.08341771605575592</v>
+        <v>0.08877660888261664</v>
       </c>
       <c r="K59" s="2" t="b">
         <v>0</v>
@@ -5716,10 +5719,10 @@
         <v>369</v>
       </c>
       <c r="M59" s="2">
-        <v>1.1040724112929408</v>
+        <v>1.227429676456491</v>
       </c>
       <c r="N59" s="2">
-        <v>122.23506231516765</v>
+        <v>135.46815032554946</v>
       </c>
       <c r="O59" s="2">
         <v>94.9367088607595</v>
@@ -5728,202 +5731,202 @@
         <v>30.30559414893712</v>
       </c>
       <c r="Q59" s="2">
-        <v>81.26582278481013</v>
+        <v>81.13924050632912</v>
       </c>
       <c r="R59" s="2">
-        <v>67.65822784810126</v>
+        <v>67.40506329113924</v>
       </c>
       <c r="S59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="T59" s="2">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="3">
         <v>34.32</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="3">
         <v>100</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>-1.487762237762238</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="3">
         <v>-0.04</v>
       </c>
-      <c r="F60" s="2">
-        <v>0.0009068128771221595</v>
-      </c>
-      <c r="G60" s="2">
-        <v>1.16</v>
-      </c>
-      <c r="H60" s="2">
-        <v>43.88</v>
-      </c>
-      <c r="I60" s="2">
-        <v>33.37</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0.020949342602410874</v>
-      </c>
-      <c r="K60" s="2" t="b">
+      <c r="F60" s="3">
+        <v>-0.0293120434254574</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="H60" s="3">
+        <v>40.31</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0.019107989063646694</v>
+      </c>
+      <c r="K60" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L60" s="2">
+      <c r="L60" s="3">
         <v>363</v>
       </c>
-      <c r="M60" s="2">
-        <v>0.018111326774519876</v>
-      </c>
-      <c r="N60" s="2">
-        <v>13.63895386332557</v>
-      </c>
-      <c r="O60" s="2">
-        <v>60.75949367088608</v>
-      </c>
-      <c r="P60" s="2">
-        <v>13.3558954863305</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>55.822784810126585</v>
-      </c>
-      <c r="R60" s="2">
-        <v>50.75949367088608</v>
-      </c>
-      <c r="S60" s="2" t="s">
+      <c r="M60" s="3">
+        <v>-0.01882687901354707</v>
+      </c>
+      <c r="N60" s="3">
+        <v>10.842494778545639</v>
+      </c>
+      <c r="O60" s="3">
+        <v>51.89873417721519</v>
+      </c>
+      <c r="P60" s="3">
+        <v>15.763835424420858</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>54.050632911392405</v>
+      </c>
+      <c r="R60" s="3">
+        <v>46.835443037974684</v>
+      </c>
+      <c r="S60" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="T60" s="2">
-        <v>-5.82</v>
+      <c r="T60" s="3">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="1">
         <v>6.37</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="1">
         <v>67.08860759493672</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="1">
         <v>-0.13029827315541603</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="1">
         <v>0.85</v>
       </c>
-      <c r="F61" s="3">
-        <v>-0.1775792879658301</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="F61" s="1">
+        <v>-0.2043800203536123</v>
+      </c>
+      <c r="G61" s="1">
         <v>0.37</v>
       </c>
-      <c r="H61" s="3">
-        <v>38.3</v>
-      </c>
-      <c r="I61" s="3">
-        <v>-2.91</v>
-      </c>
-      <c r="J61" s="3">
-        <v>-0.006988588314239928</v>
-      </c>
-      <c r="K61" s="3" t="b">
+      <c r="H61" s="1">
+        <v>34.95</v>
+      </c>
+      <c r="I61" s="1">
+        <v>-4.3</v>
+      </c>
+      <c r="J61" s="1">
+        <v>-0.006745998671544878</v>
+      </c>
+      <c r="K61" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L61" s="3">
-        <v>99</v>
-      </c>
-      <c r="M61" s="3">
-        <v>-0.24532206143683366</v>
-      </c>
-      <c r="N61" s="3">
-        <v>-12.704384957809786</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+      <c r="M61" s="1">
+        <v>-0.2777761712369845</v>
+      </c>
+      <c r="N61" s="1">
+        <v>-15.052434443798099</v>
+      </c>
+      <c r="O61" s="1">
+        <v>12.658227848101266</v>
+      </c>
+      <c r="P61" s="1">
+        <v>15.426125992360493</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>32.278481012658226</v>
+      </c>
+      <c r="R61" s="1">
+        <v>24.746835443037973</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T61" s="1">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3">
+        <v>17.65</v>
+      </c>
+      <c r="C62" s="3">
+        <v>92.40506329113924</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.5269121813031162</v>
+      </c>
+      <c r="E62" s="3">
+        <v>-0.19</v>
+      </c>
+      <c r="F62" s="3">
+        <v>-0.2580972328873807</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="H62" s="3">
+        <v>40.6</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="J62" s="3">
+        <v>-0.007351672799078714</v>
+      </c>
+      <c r="K62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" s="3">
+        <v>169</v>
+      </c>
+      <c r="M62" s="3">
+        <v>-0.26625236076331094</v>
+      </c>
+      <c r="N62" s="3">
+        <v>-13.900053396430746</v>
+      </c>
+      <c r="O62" s="3">
         <v>15.18987341772152</v>
       </c>
-      <c r="P61" s="3">
-        <v>14.552180197083512</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>33.67088607594937</v>
-      </c>
-      <c r="R61" s="3">
-        <v>25.75949367088608</v>
-      </c>
-      <c r="S61" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T61" s="3">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <v>17.65</v>
-      </c>
-      <c r="C62" s="1">
-        <v>92.40506329113924</v>
-      </c>
-      <c r="D62" s="1">
-        <v>0.5331444759206799</v>
-      </c>
-      <c r="E62" s="1">
-        <v>-0.19</v>
-      </c>
-      <c r="F62" s="1">
-        <v>-0.24063858910734787</v>
-      </c>
-      <c r="G62" s="1">
-        <v>0.93</v>
-      </c>
-      <c r="H62" s="1">
-        <v>38.8</v>
-      </c>
-      <c r="I62" s="1">
-        <v>3.45</v>
-      </c>
-      <c r="J62" s="1">
-        <v>-0.008505660486717501</v>
-      </c>
-      <c r="K62" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L62" s="1">
-        <v>169</v>
-      </c>
-      <c r="M62" s="1">
-        <v>-0.24816556393745937</v>
-      </c>
-      <c r="N62" s="1">
-        <v>-12.98873520787236</v>
-      </c>
-      <c r="O62" s="1">
-        <v>13.924050632911392</v>
-      </c>
-      <c r="P62" s="1">
+      <c r="P62" s="3">
         <v>20.131624188012864</v>
       </c>
-      <c r="Q62" s="1">
-        <v>44.81012658227848</v>
-      </c>
-      <c r="R62" s="1">
-        <v>32.46835443037974</v>
-      </c>
-      <c r="S62" s="1" t="s">
+      <c r="Q62" s="3">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="R62" s="3">
+        <v>33.10126582278481</v>
+      </c>
+      <c r="S62" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="T62" s="1">
-        <v>-10.38</v>
+      <c r="T62" s="3">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -5937,25 +5940,25 @@
         <v>98.73417721518987</v>
       </c>
       <c r="D63" s="4">
-        <v>4.967674661105318</v>
+        <v>5.210288494960027</v>
       </c>
       <c r="E63" s="4">
         <v>-3.33</v>
       </c>
       <c r="F63" s="4">
-        <v>0.990278222830926</v>
+        <v>1.0942936261123775</v>
       </c>
       <c r="G63" s="4">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
       <c r="H63" s="4">
-        <v>70.32</v>
+        <v>72.22</v>
       </c>
       <c r="I63" s="4">
-        <v>242.01</v>
+        <v>247.16</v>
       </c>
       <c r="J63" s="4">
-        <v>0.09240783649048698</v>
+        <v>0.09185172560782784</v>
       </c>
       <c r="K63" s="4" t="b">
         <v>0</v>
@@ -5964,28 +5967,28 @@
         <v>475</v>
       </c>
       <c r="M63" s="4">
-        <v>1.3999607100127094</v>
+        <v>1.5404956227525608</v>
       </c>
       <c r="N63" s="4">
-        <v>151.8238921871445</v>
+        <v>166.7747449551564</v>
       </c>
       <c r="O63" s="4">
-        <v>96.20253164556962</v>
+        <v>98.73417721518987</v>
       </c>
       <c r="P63" s="4">
         <v>25.85061584959845</v>
       </c>
       <c r="Q63" s="4">
-        <v>82.40506329113924</v>
+        <v>83.1645569620253</v>
       </c>
       <c r="R63" s="4">
-        <v>70.69620253164558</v>
+        <v>72.08860759493672</v>
       </c>
       <c r="S63" s="4" t="s">
         <v>105</v>
       </c>
       <c r="T63" s="4">
-        <v>-1.65</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -5996,7 +5999,7 @@
         <v>10.54</v>
       </c>
       <c r="C64" s="2">
-        <v>79.74683544303798</v>
+        <v>78.48101265822784</v>
       </c>
       <c r="D64" s="2">
         <v>6.5379506641366225</v>
@@ -6005,19 +6008,19 @@
         <v>-1.41</v>
       </c>
       <c r="F64" s="2">
-        <v>0.9175696518620894</v>
+        <v>0.905309725030915</v>
       </c>
       <c r="G64" s="2">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="H64" s="2">
-        <v>74.67</v>
+        <v>74.43</v>
       </c>
       <c r="I64" s="2">
-        <v>141.89</v>
+        <v>139.26</v>
       </c>
       <c r="J64" s="2">
-        <v>0.08032797368304492</v>
+        <v>0.08083435181170055</v>
       </c>
       <c r="K64" s="2" t="b">
         <v>0</v>
@@ -6026,10 +6029,10 @@
         <v>202</v>
       </c>
       <c r="M64" s="2">
-        <v>1.0315495564323494</v>
+        <v>1.0299666797058487</v>
       </c>
       <c r="N64" s="2">
-        <v>114.98277682910849</v>
+        <v>115.72185065048521</v>
       </c>
       <c r="O64" s="2">
         <v>93.67088607594937</v>
@@ -6038,512 +6041,512 @@
         <v>20.9978319173529</v>
       </c>
       <c r="Q64" s="2">
-        <v>77.59493670886076</v>
+        <v>76.32911392405063</v>
       </c>
       <c r="R64" s="2">
-        <v>67.0253164556962</v>
+        <v>66.45569620253164</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>107</v>
       </c>
       <c r="T64" s="2">
-        <v>0.06</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="3">
         <v>16.87</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="3">
         <v>89.87341772151899</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="3">
         <v>-0.28986366330764674</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="3">
         <v>0.14</v>
       </c>
-      <c r="F65" s="1">
-        <v>-0.10999032958359173</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="H65" s="1">
-        <v>58.52</v>
-      </c>
-      <c r="I65" s="1">
-        <v>2.8</v>
-      </c>
-      <c r="J65" s="1">
-        <v>-0.008105147602120888</v>
-      </c>
-      <c r="K65" s="1" t="b">
+      <c r="F65" s="3">
+        <v>-0.14607450972796582</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="H65" s="3">
+        <v>58.11</v>
+      </c>
+      <c r="I65" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="J65" s="3">
+        <v>-0.005642858388220164</v>
+      </c>
+      <c r="K65" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L65" s="1">
+      <c r="L65" s="3">
         <v>56</v>
       </c>
-      <c r="M65" s="1">
-        <v>-0.18526007788470678</v>
-      </c>
-      <c r="N65" s="1">
-        <v>-6.698186602597106</v>
-      </c>
-      <c r="O65" s="1">
+      <c r="M65" s="3">
+        <v>-0.22646077021927824</v>
+      </c>
+      <c r="N65" s="3">
+        <v>-9.920894342027472</v>
+      </c>
+      <c r="O65" s="3">
+        <v>18.9873417721519</v>
+      </c>
+      <c r="P65" s="3">
+        <v>15.211254913322609</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>45.443037974683556</v>
+      </c>
+      <c r="R65" s="3">
+        <v>32.53164556962025</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="T65" s="3">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <v>16.51</v>
+      </c>
+      <c r="C66" s="1">
+        <v>87.34177215189874</v>
+      </c>
+      <c r="D66" s="1">
+        <v>-0.11265899454875838</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="F66" s="1">
+        <v>-0.3120644091099978</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="H66" s="1">
+        <v>40.09</v>
+      </c>
+      <c r="I66" s="1">
+        <v>-39.8</v>
+      </c>
+      <c r="J66" s="1">
+        <v>-0.032455254246706575</v>
+      </c>
+      <c r="K66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>-196</v>
+      </c>
+      <c r="M66" s="1">
+        <v>-0.3167244821819579</v>
+      </c>
+      <c r="N66" s="1">
+        <v>-18.947265538295447</v>
+      </c>
+      <c r="O66" s="1">
+        <v>6.329113924050633</v>
+      </c>
+      <c r="P66" s="1">
+        <v>54.56648894054421</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>32.911392405063296</v>
+      </c>
+      <c r="R66" s="1">
+        <v>18.10126582278481</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T66" s="1">
+        <v>-10.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3">
+        <v>4.01</v>
+      </c>
+      <c r="C67" s="3">
+        <v>55.69620253164557</v>
+      </c>
+      <c r="D67" s="3">
+        <v>7.241895261845387</v>
+      </c>
+      <c r="E67" s="3">
+        <v>-0.68</v>
+      </c>
+      <c r="F67" s="3">
+        <v>-0.20779259712788334</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1.12</v>
+      </c>
+      <c r="H67" s="3">
+        <v>37.79</v>
+      </c>
+      <c r="I67" s="3">
+        <v>-15.88</v>
+      </c>
+      <c r="J67" s="3">
+        <v>-0.005770708881856257</v>
+      </c>
+      <c r="K67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3">
+        <v>-77</v>
+      </c>
+      <c r="M67" s="3">
+        <v>-0.1938123779120029</v>
+      </c>
+      <c r="N67" s="3">
+        <v>-6.656055111299941</v>
+      </c>
+      <c r="O67" s="3">
         <v>25.31645569620253</v>
       </c>
-      <c r="P65" s="1">
-        <v>15.211254913322609</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>44.556962025316466</v>
-      </c>
-      <c r="R65" s="1">
-        <v>33.54430379746835</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T65" s="1">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3">
-        <v>16.51</v>
-      </c>
-      <c r="C66" s="3">
-        <v>87.34177215189874</v>
-      </c>
-      <c r="D66" s="3">
-        <v>-0.1144760751059965</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1.66</v>
-      </c>
-      <c r="F66" s="3">
-        <v>-0.32148208675405354</v>
-      </c>
-      <c r="G66" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="H66" s="3">
-        <v>33.69</v>
-      </c>
-      <c r="I66" s="3">
-        <v>-43.36</v>
-      </c>
-      <c r="J66" s="3">
-        <v>-0.033132146272255095</v>
-      </c>
-      <c r="K66" s="3" t="b">
+      <c r="P67" s="3">
+        <v>21.01837744312229</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>41.0126582278481</v>
+      </c>
+      <c r="R67" s="3">
+        <v>34.49367088607595</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T67" s="3">
+        <v>-9.62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3">
+        <v>7.35</v>
+      </c>
+      <c r="C68" s="3">
+        <v>69.62025316455697</v>
+      </c>
+      <c r="D68" s="3">
+        <v>485.7265306122449</v>
+      </c>
+      <c r="E68" s="3">
+        <v>-0.41</v>
+      </c>
+      <c r="F68" s="3">
+        <v>-0.1478430284292418</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="H68" s="3">
+        <v>52.18</v>
+      </c>
+      <c r="I68" s="3">
+        <v>4.49</v>
+      </c>
+      <c r="J68" s="3">
+        <v>-0.007153378496309148</v>
+      </c>
+      <c r="K68" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L66" s="3">
-        <v>-196</v>
-      </c>
-      <c r="M66" s="3">
-        <v>-0.3247079331098156</v>
-      </c>
-      <c r="N66" s="3">
-        <v>-20.642972125107985</v>
-      </c>
-      <c r="O66" s="3">
-        <v>6.329113924050633</v>
-      </c>
-      <c r="P66" s="3">
-        <v>54.854261650729526</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>32.025316455696206</v>
-      </c>
-      <c r="R66" s="3">
-        <v>18.10126582278481</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T66" s="3">
-        <v>-10.95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1">
-        <v>4.01</v>
-      </c>
-      <c r="C67" s="1">
-        <v>55.69620253164557</v>
-      </c>
-      <c r="D67" s="1">
-        <v>7.241895261845387</v>
-      </c>
-      <c r="E67" s="1">
-        <v>-0.68</v>
-      </c>
-      <c r="F67" s="1">
-        <v>-0.18412860031631492</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1.13</v>
-      </c>
-      <c r="H67" s="1">
-        <v>39.24</v>
-      </c>
-      <c r="I67" s="1">
-        <v>-15.36</v>
-      </c>
-      <c r="J67" s="1">
-        <v>-0.004448981943545205</v>
-      </c>
-      <c r="K67" s="1" t="b">
+      <c r="L68" s="3">
+        <v>146</v>
+      </c>
+      <c r="M68" s="3">
+        <v>-0.2247342341165841</v>
+      </c>
+      <c r="N68" s="3">
+        <v>-9.748240731758063</v>
+      </c>
+      <c r="O68" s="3">
+        <v>20.253164556962027</v>
+      </c>
+      <c r="P68" s="3">
+        <v>18.003852697255347</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>60.8860759493671</v>
+      </c>
+      <c r="R68" s="3">
+        <v>46.265822784810126</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="T68" s="3">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <v>8.24</v>
+      </c>
+      <c r="C69" s="1">
+        <v>72.15189873417721</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0.6262135922330098</v>
+      </c>
+      <c r="E69" s="1">
+        <v>-0.24</v>
+      </c>
+      <c r="F69" s="1">
+        <v>-0.33748303889174613</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H69" s="1">
+        <v>40.09</v>
+      </c>
+      <c r="I69" s="1">
+        <v>-14.22</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-0.011059197669783964</v>
+      </c>
+      <c r="K69" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L67" s="1">
-        <v>-77</v>
-      </c>
-      <c r="M67" s="1">
-        <v>-0.17014993277467927</v>
-      </c>
-      <c r="N67" s="1">
-        <v>-5.187172091594346</v>
-      </c>
-      <c r="O67" s="1">
-        <v>31.645569620253166</v>
-      </c>
-      <c r="P67" s="1">
-        <v>21.01837744312229</v>
-      </c>
-      <c r="Q67" s="1">
-        <v>42.151898734177216</v>
-      </c>
-      <c r="R67" s="1">
-        <v>36.518987341772146</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="T67" s="1">
-        <v>-7.59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
-        <v>7.35</v>
-      </c>
-      <c r="C68" s="1">
-        <v>69.62025316455697</v>
-      </c>
-      <c r="D68" s="1">
-        <v>485.7265306122449</v>
-      </c>
-      <c r="E68" s="1">
-        <v>-0.41</v>
-      </c>
-      <c r="F68" s="1">
-        <v>-0.09874876235403014</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="H68" s="1">
-        <v>57.16</v>
-      </c>
-      <c r="I68" s="1">
-        <v>5.94</v>
-      </c>
-      <c r="J68" s="1">
-        <v>-0.008404114944081924</v>
-      </c>
-      <c r="K68" s="1" t="b">
+      <c r="L69" s="1">
+        <v>-69</v>
+      </c>
+      <c r="M69" s="1">
+        <v>-0.28389219856420456</v>
+      </c>
+      <c r="N69" s="1">
+        <v>-15.664037176520102</v>
+      </c>
+      <c r="O69" s="1">
+        <v>11.39240506329114</v>
+      </c>
+      <c r="P69" s="1">
+        <v>29.40035337282439</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>36.58227848101265</v>
+      </c>
+      <c r="R69" s="1">
+        <v>24.620253164556964</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T69" s="1">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3">
+        <v>18.19</v>
+      </c>
+      <c r="C70" s="3">
+        <v>93.67088607594937</v>
+      </c>
+      <c r="D70" s="3">
+        <v>-0.47608576140736675</v>
+      </c>
+      <c r="E70" s="3">
+        <v>-1.55</v>
+      </c>
+      <c r="F70" s="3">
+        <v>-0.1681544085078506</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="H70" s="3">
+        <v>62.29</v>
+      </c>
+      <c r="I70" s="3">
+        <v>-6.51</v>
+      </c>
+      <c r="J70" s="3">
+        <v>-0.0006359513945416026</v>
+      </c>
+      <c r="K70" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="L68" s="1">
-        <v>146</v>
-      </c>
-      <c r="M68" s="1">
-        <v>-0.1707926642993831</v>
-      </c>
-      <c r="N68" s="1">
-        <v>-5.251445244064732</v>
-      </c>
-      <c r="O68" s="1">
-        <v>29.11392405063291</v>
-      </c>
-      <c r="P68" s="1">
-        <v>18.003852697255347</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>62.27848101265823</v>
-      </c>
-      <c r="R68" s="1">
-        <v>48.67088607594937</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="T68" s="1">
-        <v>3.73</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3">
-        <v>8.24</v>
-      </c>
-      <c r="C69" s="3">
-        <v>72.15189873417721</v>
-      </c>
-      <c r="D69" s="3">
-        <v>0.6262135922330098</v>
-      </c>
-      <c r="E69" s="3">
-        <v>-0.24</v>
-      </c>
-      <c r="F69" s="3">
-        <v>-0.3330565266683868</v>
-      </c>
-      <c r="G69" s="3">
-        <v>1.47</v>
-      </c>
-      <c r="H69" s="3">
-        <v>39.46</v>
-      </c>
-      <c r="I69" s="3">
-        <v>-14.47</v>
-      </c>
-      <c r="J69" s="3">
-        <v>-0.011032815385040862</v>
-      </c>
-      <c r="K69" s="3" t="b">
+      <c r="L70" s="3">
+        <v>-60</v>
+      </c>
+      <c r="M70" s="3">
+        <v>-0.182134627723731</v>
+      </c>
+      <c r="N70" s="3">
+        <v>-5.488280092472756</v>
+      </c>
+      <c r="O70" s="3">
+        <v>27.848101265822784</v>
+      </c>
+      <c r="P70" s="3">
+        <v>31.450467124868602</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>48.481012658227854</v>
+      </c>
+      <c r="R70" s="3">
+        <v>32.0253164556962</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T70" s="3">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="C71" s="1">
+        <v>45.56962025316456</v>
+      </c>
+      <c r="D71" s="1">
+        <v>13.532894736842104</v>
+      </c>
+      <c r="E71" s="1">
+        <v>-0.71</v>
+      </c>
+      <c r="F71" s="1">
+        <v>-0.4000754419052832</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.14</v>
+      </c>
+      <c r="H71" s="1">
+        <v>57.58</v>
+      </c>
+      <c r="I71" s="1">
+        <v>-24.28</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-0.018169950028812467</v>
+      </c>
+      <c r="K71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1">
+        <v>-99</v>
+      </c>
+      <c r="M71" s="1">
+        <v>-0.3837651861534227</v>
+      </c>
+      <c r="N71" s="1">
+        <v>-25.65133593544192</v>
+      </c>
+      <c r="O71" s="1">
+        <v>2.5316455696202533</v>
+      </c>
+      <c r="P71" s="1">
+        <v>36.83258048205344</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>41.645569620253156</v>
+      </c>
+      <c r="R71" s="1">
+        <v>22.91139240506329</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="T71" s="1">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>10.42</v>
+      </c>
+      <c r="C72" s="1">
+        <v>77.21518987341773</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0.21976967370441466</v>
+      </c>
+      <c r="E72" s="1">
+        <v>-0.66</v>
+      </c>
+      <c r="F72" s="1">
+        <v>-0.30326078534406276</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1.12</v>
+      </c>
+      <c r="H72" s="1">
+        <v>40.27</v>
+      </c>
+      <c r="I72" s="1">
+        <v>-10.32</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-0.0033509170299639633</v>
+      </c>
+      <c r="K72" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L69" s="3">
-        <v>-69</v>
-      </c>
-      <c r="M69" s="3">
-        <v>-0.282518267094781</v>
-      </c>
-      <c r="N69" s="3">
-        <v>-16.424005523604524</v>
-      </c>
-      <c r="O69" s="3">
-        <v>11.39240506329114</v>
-      </c>
-      <c r="P69" s="3">
-        <v>29.40035337282439</v>
-      </c>
-      <c r="Q69" s="3">
-        <v>36.20253164556962</v>
-      </c>
-      <c r="R69" s="3">
-        <v>24.303797468354432</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T69" s="3">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <v>18.19</v>
-      </c>
-      <c r="C70" s="1">
-        <v>93.67088607594937</v>
-      </c>
-      <c r="D70" s="1">
-        <v>-0.47608576140736675</v>
-      </c>
-      <c r="E70" s="1">
-        <v>-1.55</v>
-      </c>
-      <c r="F70" s="1">
-        <v>-0.16647888460362092</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.86</v>
-      </c>
-      <c r="H70" s="1">
-        <v>60.38</v>
-      </c>
-      <c r="I70" s="1">
-        <v>-7.5</v>
-      </c>
-      <c r="J70" s="1">
-        <v>-0.003719755361941329</v>
-      </c>
-      <c r="K70" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" s="1">
-        <v>-60</v>
-      </c>
-      <c r="M70" s="1">
-        <v>-0.18153283426384392</v>
-      </c>
-      <c r="N70" s="1">
-        <v>-6.325462240510812</v>
-      </c>
-      <c r="O70" s="1">
-        <v>26.582278481012654</v>
-      </c>
-      <c r="P70" s="1">
-        <v>31.450467124868602</v>
-      </c>
-      <c r="Q70" s="1">
-        <v>47.21518987341772</v>
-      </c>
-      <c r="R70" s="1">
-        <v>31.265822784810123</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="T70" s="1">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71" s="3">
-        <v>1.52</v>
-      </c>
-      <c r="C71" s="3">
-        <v>45.56962025316456</v>
-      </c>
-      <c r="D71" s="3">
-        <v>13.532894736842104</v>
-      </c>
-      <c r="E71" s="3">
-        <v>-0.71</v>
-      </c>
-      <c r="F71" s="3">
-        <v>-0.39152195576082705</v>
-      </c>
-      <c r="G71" s="3">
-        <v>1.13</v>
-      </c>
-      <c r="H71" s="3">
-        <v>65.43</v>
-      </c>
-      <c r="I71" s="3">
-        <v>-22.59</v>
-      </c>
-      <c r="J71" s="3">
-        <v>-0.019821917707988305</v>
-      </c>
-      <c r="K71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3">
-        <v>-99</v>
-      </c>
-      <c r="M71" s="3">
-        <v>-0.37754328821919136</v>
-      </c>
-      <c r="N71" s="3">
-        <v>-25.926507636045553</v>
-      </c>
-      <c r="O71" s="3">
-        <v>2.5316455696202533</v>
-      </c>
-      <c r="P71" s="3">
-        <v>36.83258048205344</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>44.303797468354425</v>
-      </c>
-      <c r="R71" s="3">
-        <v>23.037974683544302</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T71" s="3">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="3">
-        <v>10.42</v>
-      </c>
-      <c r="C72" s="3">
-        <v>78.48101265822784</v>
-      </c>
-     